--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="1801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="1802">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3028793334961</t>
+    <t xml:space="preserve">38.3028678894043</t>
   </si>
   <si>
     <t xml:space="preserve">LLY.DE</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7578201293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6800575256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.117504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5549621582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4298362731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9924125671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.2426147460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8051605224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3677139282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9302673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.023006439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5942993164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1717262268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8681297302246</t>
+    <t xml:space="preserve">38.7578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.680061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1175079345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5549468994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4298400878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9923896789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.2426300048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8051528930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3677177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9302749633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0229988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5943031311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1717147827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8681335449219</t>
   </si>
   <si>
     <t xml:space="preserve">54.7071495056152</t>
@@ -92,106 +92,106 @@
     <t xml:space="preserve">55.5907897949219</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3309440612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3598098754883</t>
+    <t xml:space="preserve">54.3309326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3598136901855</t>
   </si>
   <si>
     <t xml:space="preserve">54.015983581543</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2212677001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8039970397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3226585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4815902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2785110473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4021301269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0290031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5322914123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5963745117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4662132263184</t>
+    <t xml:space="preserve">54.221263885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8040046691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3226623535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4815979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.278507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4021339416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0290069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.532283782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.596378326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4662017822266</t>
   </si>
   <si>
     <t xml:space="preserve">55.2719650268555</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5721664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1218605041504</t>
+    <t xml:space="preserve">55.5721588134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1218795776367</t>
   </si>
   <si>
     <t xml:space="preserve">54.9276161193848</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9717597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6405143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2167053222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5787239074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0754241943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.808277130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0312843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4286079406738</t>
+    <t xml:space="preserve">54.9717636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.640510559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2167091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5787086486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.075439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8082733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0312881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4286041259766</t>
   </si>
   <si>
     <t xml:space="preserve">56.2961807250977</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8900146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4861450195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2323799133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9034118652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1130332946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3690910339355</t>
+    <t xml:space="preserve">55.8900184631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4861488342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2323837280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9034042358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.113037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.369083404541</t>
   </si>
   <si>
     <t xml:space="preserve">55.6251449584961</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9230499267578</t>
+    <t xml:space="preserve">56.9230651855469</t>
   </si>
   <si>
     <t xml:space="preserve">55.8811874389648</t>
@@ -200,142 +200,142 @@
     <t xml:space="preserve">55.5191841125488</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7641296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1019287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6934928894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5057907104492</t>
+    <t xml:space="preserve">56.7641258239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1019248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6935005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.505802154541</t>
   </si>
   <si>
     <t xml:space="preserve">57.161449432373</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9936943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5433921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9495429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.479305267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9119453430176</t>
+    <t xml:space="preserve">56.9936904907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5433959960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9495506286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4793128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9119415283203</t>
   </si>
   <si>
     <t xml:space="preserve">58.5829811096191</t>
   </si>
   <si>
-    <t xml:space="preserve">59.9162216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3665199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1899337768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.362247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6559066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6294136047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6271286010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7330741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5166244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0552101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5231819152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4452629089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7212371826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2998085021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8872909545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5134239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2433242797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2077331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.394645690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9376411437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4093933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1571044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5696258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6586227416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2105255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2550048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7979888916016</t>
+    <t xml:space="preserve">59.9162101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.366527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1899223327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3622436523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6558990478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6294021606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6271324157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7330856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5166130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0552253723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5231628417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4453010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7212181091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8872833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5134315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2433547973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2077407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3946723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9376258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.409423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.157096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5696334838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6586303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2105102539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.254997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.797981262207</t>
   </si>
   <si>
     <t xml:space="preserve">66.1006393432617</t>
   </si>
   <si>
-    <t xml:space="preserve">65.6911773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4967269897461</t>
+    <t xml:space="preserve">65.6911849975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4967498779297</t>
   </si>
   <si>
     <t xml:space="preserve">66.728157043457</t>
   </si>
   <si>
-    <t xml:space="preserve">65.8335952758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9582138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1615524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3039855957031</t>
+    <t xml:space="preserve">65.8335876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9582061767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1615447998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3039779663086</t>
   </si>
   <si>
     <t xml:space="preserve">65.5220642089844</t>
@@ -344,133 +344,133 @@
     <t xml:space="preserve">66.3320693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2608489990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8202285766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2563858032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5189895629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7860336303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3988265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3557205200195</t>
+    <t xml:space="preserve">66.2608642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8202514648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2564086914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5189971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7860260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3988189697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3557281494141</t>
   </si>
   <si>
     <t xml:space="preserve">68.121208190918</t>
   </si>
   <si>
-    <t xml:space="preserve">68.1657180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1568222045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6018829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3971481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.596061706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1448364257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6193923950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.5273590087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6221771240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5153579711914</t>
+    <t xml:space="preserve">68.1657409667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1567993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6018905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3971557617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5960540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1448669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6194076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.52734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.622200012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.515380859375</t>
   </si>
   <si>
     <t xml:space="preserve">74.9306564331055</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6961822509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2124557495117</t>
+    <t xml:space="preserve">75.696174621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2124633789062</t>
   </si>
   <si>
     <t xml:space="preserve">76.8355178833008</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4733657836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.9362182617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.5623779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7137222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8352355957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8441619873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8048324584961</t>
+    <t xml:space="preserve">78.4733734130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.9362487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5623931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.7137145996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8352279663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8441467285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8048248291016</t>
   </si>
   <si>
     <t xml:space="preserve">81.4318542480469</t>
   </si>
   <si>
-    <t xml:space="preserve">81.9513854980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5694427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7844161987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4587173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3691329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9033660888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6883850097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6346435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.5808944702148</t>
+    <t xml:space="preserve">81.9513778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5694580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7844314575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4587249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3691635131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9033737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6883926391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.634635925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.5809097290039</t>
   </si>
   <si>
     <t xml:space="preserve">80.9839935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">80.849609375</t>
+    <t xml:space="preserve">80.8496398925781</t>
   </si>
   <si>
     <t xml:space="preserve">81.2168731689453</t>
   </si>
   <si>
-    <t xml:space="preserve">81.0914764404297</t>
+    <t xml:space="preserve">81.0914840698242</t>
   </si>
   <si>
     <t xml:space="preserve">81.2527084350586</t>
@@ -479,208 +479,208 @@
     <t xml:space="preserve">80.2853012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3211441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4888305664062</t>
+    <t xml:space="preserve">80.3211059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4888229370117</t>
   </si>
   <si>
     <t xml:space="preserve">81.86181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7811889648438</t>
+    <t xml:space="preserve">81.7812042236328</t>
   </si>
   <si>
     <t xml:space="preserve">81.3960342407227</t>
   </si>
   <si>
-    <t xml:space="preserve">81.6110000610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9782409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3569412231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.1810531616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6077575683594</t>
+    <t xml:space="preserve">81.6110153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9782638549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3569717407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.181037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6077728271484</t>
   </si>
   <si>
     <t xml:space="preserve">81.0735473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">82.2380065917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1158599853516</t>
+    <t xml:space="preserve">82.2380218505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.115852355957</t>
   </si>
   <si>
     <t xml:space="preserve">83.2949752807617</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2810516357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2248153686523</t>
+    <t xml:space="preserve">87.2810363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2248077392578</t>
   </si>
   <si>
     <t xml:space="preserve">90.5057144165039</t>
   </si>
   <si>
-    <t xml:space="preserve">89.798095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1531372070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2476959228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4537200927734</t>
+    <t xml:space="preserve">89.7980728149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1531524658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2477111816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4537353515625</t>
   </si>
   <si>
     <t xml:space="preserve">85.8478622436523</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3014450073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.895866394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3200988769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9976119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7378540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3551864624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7435836791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1402206420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2681274414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2029190063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0660552978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8177490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6980819702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.1287612915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9725112915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2061462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7289047241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.2369842529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3591690063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9741516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7129364013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5325775146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5685043334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9740447998047</t>
+    <t xml:space="preserve">85.3014755249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8958892822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3200836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9976196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7378768920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3552169799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7435913085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1402282714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2681045532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2029113769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0660781860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8177642822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6980895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.128776550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.4472885131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9725341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2061767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7289199829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.2369918823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3591613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9741744995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7128982543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5325622558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5685348510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9740600585938</t>
   </si>
   <si>
     <t xml:space="preserve">88.3705215454102</t>
   </si>
   <si>
-    <t xml:space="preserve">90.1991729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8839874267578</t>
+    <t xml:space="preserve">90.1992111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8839721679688</t>
   </si>
   <si>
     <t xml:space="preserve">90.4063720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2171173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7665405273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8475036621094</t>
+    <t xml:space="preserve">91.2171249389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7665328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8475112915039</t>
   </si>
   <si>
     <t xml:space="preserve">94.0456848144531</t>
   </si>
   <si>
-    <t xml:space="preserve">90.1541213989258</t>
+    <t xml:space="preserve">90.1541519165039</t>
   </si>
   <si>
     <t xml:space="preserve">89.6046447753906</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3885498046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3162155151367</t>
+    <t xml:space="preserve">88.3885345458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3161926269531</t>
   </si>
   <si>
     <t xml:space="preserve">89.7487640380859</t>
   </si>
   <si>
-    <t xml:space="preserve">87.89306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8933563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8931732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0644226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2627716064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7760696411133</t>
+    <t xml:space="preserve">87.8930740356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8933639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8931579589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0644149780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2627868652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7760543823242</t>
   </si>
   <si>
     <t xml:space="preserve">88.5056457519531</t>
   </si>
   <si>
-    <t xml:space="preserve">90.325309753418</t>
+    <t xml:space="preserve">90.3252868652344</t>
   </si>
   <si>
     <t xml:space="preserve">89.0191040039062</t>
@@ -695,106 +695,106 @@
     <t xml:space="preserve">90.6135559082031</t>
   </si>
   <si>
-    <t xml:space="preserve">91.4513244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8748016357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6675872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9920043945312</t>
+    <t xml:space="preserve">91.4513168334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8747863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.667610168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9919815063477</t>
   </si>
   <si>
     <t xml:space="preserve">89.7217483520508</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3521423339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3700561523438</t>
+    <t xml:space="preserve">92.3521270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3700790405273</t>
   </si>
   <si>
     <t xml:space="preserve">91.6675186157227</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5863647460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4242095947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0998153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6674118041992</t>
+    <t xml:space="preserve">92.5863571166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4242172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0998229980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6674423217773</t>
   </si>
   <si>
     <t xml:space="preserve">90.6586074829102</t>
   </si>
   <si>
-    <t xml:space="preserve">90.0820693969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7666015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5051803588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4150238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7394104003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6852035522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0997467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4961776733398</t>
+    <t xml:space="preserve">90.0820541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7666168212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5052032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4150161743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7394027709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.685173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0997543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4961929321289</t>
   </si>
   <si>
     <t xml:space="preserve">92.6043701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">93.9646224975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3970031738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1717834472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.3154754638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6569595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0890884399414</t>
+    <t xml:space="preserve">93.9646072387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3970260620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1717987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.3154602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6569519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0890808105469</t>
   </si>
   <si>
     <t xml:space="preserve">97.6750793457031</t>
   </si>
   <si>
-    <t xml:space="preserve">97.7385559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2370758056641</t>
+    <t xml:space="preserve">97.7385330200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.237060546875</t>
   </si>
   <si>
     <t xml:space="preserve">99.0437622070312</t>
   </si>
   <si>
-    <t xml:space="preserve">99.2522506713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3247756958008</t>
+    <t xml:space="preserve">99.2522659301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3247680664062</t>
   </si>
   <si>
     <t xml:space="preserve">99.6963882446289</t>
@@ -803,67 +803,67 @@
     <t xml:space="preserve">100.52123260498</t>
   </si>
   <si>
-    <t xml:space="preserve">101.51830291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.475914001465</t>
+    <t xml:space="preserve">101.518295288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.47590637207</t>
   </si>
   <si>
     <t xml:space="preserve">102.189033508301</t>
   </si>
   <si>
-    <t xml:space="preserve">101.318862915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.234359741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.457794189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9078140258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4969863891602</t>
+    <t xml:space="preserve">101.318878173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.234336853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.457763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9078063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4970092773438</t>
   </si>
   <si>
     <t xml:space="preserve">99.1615982055664</t>
   </si>
   <si>
-    <t xml:space="preserve">99.5966567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.865661621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.034950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.524406433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.823524475098</t>
+    <t xml:space="preserve">99.5966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.865676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.034934997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.524398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.823509216309</t>
   </si>
   <si>
     <t xml:space="preserve">104.101554870605</t>
   </si>
   <si>
-    <t xml:space="preserve">105.588088989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.445999145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.862937927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.300964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.27082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.352394104004</t>
+    <t xml:space="preserve">105.588081359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.446014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.862945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.300979614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.352409362793</t>
   </si>
   <si>
     <t xml:space="preserve">103.494277954102</t>
@@ -872,130 +872,130 @@
     <t xml:space="preserve">101.346046447754</t>
   </si>
   <si>
-    <t xml:space="preserve">102.207160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.787269592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.068008422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0165786743164</t>
+    <t xml:space="preserve">102.207153320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.880836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.787261962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.068016052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0165710449219</t>
   </si>
   <si>
     <t xml:space="preserve">93.8862915039062</t>
   </si>
   <si>
-    <t xml:space="preserve">92.472282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7020568847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7716369628906</t>
+    <t xml:space="preserve">92.4722671508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7020645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7716064453125</t>
   </si>
   <si>
     <t xml:space="preserve">95.9347763061523</t>
   </si>
   <si>
-    <t xml:space="preserve">96.7868194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.058723449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5751266479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9739761352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9044189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7775268554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0494232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0342636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3816375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.43603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1430358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3061904907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7552337646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6241989135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.882926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4815902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3904113769531</t>
+    <t xml:space="preserve">96.7868118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0587310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5751419067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9739685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.904411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7775039672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0494384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0342483520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3816528320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4360275268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1430282592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3061828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7552719116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6242141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.882942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4816055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.390380859375</t>
   </si>
   <si>
     <t xml:space="preserve">95.0802612304688</t>
   </si>
   <si>
-    <t xml:space="preserve">95.1350021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4086303710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2228622436523</t>
+    <t xml:space="preserve">95.135009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4086456298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2228469848633</t>
   </si>
   <si>
     <t xml:space="preserve">95.9376678466797</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9890594482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5728149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6324310302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5628051757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0918121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5835037231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2128524780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7999267578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4201965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4931716918945</t>
+    <t xml:space="preserve">94.9890518188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5728073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6324157714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5627746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0918273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5834808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2128677368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7999572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4201889038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4931640625</t>
   </si>
   <si>
     <t xml:space="preserve">92.9093933105469</t>
@@ -1004,118 +1004,118 @@
     <t xml:space="preserve">92.6357650756836</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3107604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2608947753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8719940185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3098373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3405380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2709274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3621139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7567901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1249618530273</t>
+    <t xml:space="preserve">93.3107528686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2608871459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8720092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3098297119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3405532836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2709121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3621292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7567672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1249847412109</t>
   </si>
   <si>
     <t xml:space="preserve">89.3885879516602</t>
   </si>
   <si>
-    <t xml:space="preserve">86.6521835327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.564338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4764404296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0204010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5004806518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3819122314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.5245056152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9349517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9474105834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.306526184082</t>
+    <t xml:space="preserve">86.6521911621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5643157958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4764556884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.020393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5004653930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3818969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.5244827270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9349365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9474334716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3064956665039</t>
   </si>
   <si>
     <t xml:space="preserve">89.3703384399414</t>
   </si>
   <si>
-    <t xml:space="preserve">88.9507675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2244033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.118293762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7750091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3040466308594</t>
+    <t xml:space="preserve">88.9507446289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2243881225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1182861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7750244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3040390014648</t>
   </si>
   <si>
     <t xml:space="preserve">89.9176177978516</t>
   </si>
   <si>
-    <t xml:space="preserve">90.5469818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4980392456055</t>
+    <t xml:space="preserve">90.546989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4980316162109</t>
   </si>
   <si>
     <t xml:space="preserve">92.7452087402344</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7418823242188</t>
+    <t xml:space="preserve">91.7418746948242</t>
   </si>
   <si>
     <t xml:space="preserve">91.4317474365234</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0702362060547</t>
+    <t xml:space="preserve">92.0702590942383</t>
   </si>
   <si>
     <t xml:space="preserve">92.4236679077148</t>
   </si>
   <si>
-    <t xml:space="preserve">90.440803527832</t>
+    <t xml:space="preserve">90.440788269043</t>
   </si>
   <si>
     <t xml:space="preserve">90.7804565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7908706665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0479049682617</t>
+    <t xml:space="preserve">92.7908782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0479125976562</t>
   </si>
   <si>
     <t xml:space="preserve">92.074821472168</t>
@@ -1127,187 +1127,187 @@
     <t xml:space="preserve">91.9095916748047</t>
   </si>
   <si>
-    <t xml:space="preserve">92.754150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8190231323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.608512878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8104629516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2878189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0197525024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7712783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6990585327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9194030761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0381240844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6800918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7443618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9928207397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.93896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7015151977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4065551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6635589599609</t>
+    <t xml:space="preserve">92.7541656494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8190078735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6085052490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2878036499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0197296142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7712554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6990661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9193801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0381088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6801071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7443389892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9928131103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9389801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7015228271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4065246582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6635665893555</t>
   </si>
   <si>
     <t xml:space="preserve">93.433464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9940719604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4713897705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6354064941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9634552001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5044631958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4224472045898</t>
+    <t xml:space="preserve">94.9940490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4714202880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6354217529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9634399414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5044250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4224395751953</t>
   </si>
   <si>
     <t xml:space="preserve">90.8814468383789</t>
   </si>
   <si>
-    <t xml:space="preserve">91.340446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7969589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5588989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8165740966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2033309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6886672973633</t>
+    <t xml:space="preserve">91.3404312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7969741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5589218139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8165512084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2033462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6886596679688</t>
   </si>
   <si>
     <t xml:space="preserve">93.1397094726562</t>
   </si>
   <si>
-    <t xml:space="preserve">92.717414855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0944213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0932006835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.800651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.488525390625</t>
+    <t xml:space="preserve">92.7174530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0944137573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0931930541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8006591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4885482788086</t>
   </si>
   <si>
     <t xml:space="preserve">94.0209808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">94.1494903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4616165161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.450080871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6510009765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7433547973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4823989868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.0920867919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6856384277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.015869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5493621826172</t>
+    <t xml:space="preserve">94.1494827270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4616317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4500961303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.650993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7433700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4823837280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.0920944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6856231689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0158767700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5493545532227</t>
   </si>
   <si>
     <t xml:space="preserve">98.8634338378906</t>
   </si>
   <si>
-    <t xml:space="preserve">98.383056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1267395019531</t>
+    <t xml:space="preserve">98.3830795288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1267318725586</t>
   </si>
   <si>
     <t xml:space="preserve">98.4939498901367</t>
   </si>
   <si>
-    <t xml:space="preserve">100.600158691406</t>
+    <t xml:space="preserve">100.600166320801</t>
   </si>
   <si>
     <t xml:space="preserve">99.9165725708008</t>
   </si>
   <si>
-    <t xml:space="preserve">100.359992980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.212188720703</t>
+    <t xml:space="preserve">100.359985351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.212173461914</t>
   </si>
   <si>
     <t xml:space="preserve">100.784912109375</t>
   </si>
   <si>
-    <t xml:space="preserve">100.711029052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.727172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.202934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.269897460938</t>
+    <t xml:space="preserve">100.711013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.727188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.202941894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.269882202148</t>
   </si>
   <si>
     <t xml:space="preserve">108.008918762207</t>
@@ -1316,19 +1316,19 @@
     <t xml:space="preserve">110.429229736328</t>
   </si>
   <si>
-    <t xml:space="preserve">109.653266906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.988136291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.064338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.341491699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.265258789062</t>
+    <t xml:space="preserve">109.653251647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.988128662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.064323425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.341484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.265274047852</t>
   </si>
   <si>
     <t xml:space="preserve">109.135932922363</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">109.819534301758</t>
   </si>
   <si>
-    <t xml:space="preserve">109.893440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.886512756348</t>
+    <t xml:space="preserve">109.893432617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.886489868164</t>
   </si>
   <si>
     <t xml:space="preserve">114.105903625488</t>
   </si>
   <si>
-    <t xml:space="preserve">115.269882202148</t>
+    <t xml:space="preserve">115.26985168457</t>
   </si>
   <si>
     <t xml:space="preserve">115.454620361328</t>
@@ -1361,19 +1361,19 @@
     <t xml:space="preserve">117.376091003418</t>
   </si>
   <si>
-    <t xml:space="preserve">116.710952758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.486953735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.394569396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.320671081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.413047790527</t>
+    <t xml:space="preserve">116.710960388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.486946105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.394584655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.320655822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.413032531738</t>
   </si>
   <si>
     <t xml:space="preserve">116.322982788086</t>
@@ -1382,49 +1382,49 @@
     <t xml:space="preserve">118.115142822266</t>
   </si>
   <si>
-    <t xml:space="preserve">120.09203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.135917663574</t>
+    <t xml:space="preserve">120.092018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.135925292969</t>
   </si>
   <si>
     <t xml:space="preserve">117.339141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">119.61164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.62321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.156715393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473075866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.274467468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.292945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.586235046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.54906463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.248512268066</t>
+    <t xml:space="preserve">119.611633300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623184204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.156677246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473091125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.274452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.292930603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.586250305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.549087524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.248565673828</t>
   </si>
   <si>
     <t xml:space="preserve">120.616821289062</t>
   </si>
   <si>
-    <t xml:space="preserve">121.229957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.270401000977</t>
+    <t xml:space="preserve">121.229972839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.270408630371</t>
   </si>
   <si>
     <t xml:space="preserve">121.78734588623</t>
@@ -1433,19 +1433,19 @@
     <t xml:space="preserve">119.780769348145</t>
   </si>
   <si>
-    <t xml:space="preserve">117.049621582031</t>
+    <t xml:space="preserve">117.049606323242</t>
   </si>
   <si>
     <t xml:space="preserve">116.009162902832</t>
   </si>
   <si>
-    <t xml:space="preserve">113.017913818359</t>
+    <t xml:space="preserve">113.017890930176</t>
   </si>
   <si>
     <t xml:space="preserve">104.620063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">108.057235717773</t>
+    <t xml:space="preserve">108.05721282959</t>
   </si>
   <si>
     <t xml:space="preserve">112.441947937012</t>
@@ -1457,13 +1457,13 @@
     <t xml:space="preserve">116.306442260742</t>
   </si>
   <si>
-    <t xml:space="preserve">115.507522583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.881286621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.936996459961</t>
+    <t xml:space="preserve">115.507530212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.881294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.93701171875</t>
   </si>
   <si>
     <t xml:space="preserve">115.135948181152</t>
@@ -1475,73 +1475,73 @@
     <t xml:space="preserve">110.5654296875</t>
   </si>
   <si>
-    <t xml:space="preserve">112.609176635742</t>
+    <t xml:space="preserve">112.60913848877</t>
   </si>
   <si>
     <t xml:space="preserve">117.123931884766</t>
   </si>
   <si>
-    <t xml:space="preserve">114.597137451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.056190490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.120643615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.768692016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.27033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.771987915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.844139099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.680191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.365440368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.798233032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.694442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.300987243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623405456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.552391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.339248657227</t>
+    <t xml:space="preserve">114.597145080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.056175231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.120658874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.768684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.771957397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.844123840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.680183410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.365447998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.798240661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.694435119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.300979614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623390197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.552352905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.339225769043</t>
   </si>
   <si>
     <t xml:space="preserve">128.661666870117</t>
   </si>
   <si>
-    <t xml:space="preserve">131.913040161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.448608398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.62890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.377578735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.235443115234</t>
+    <t xml:space="preserve">131.913024902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.44856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.628890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.377517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.235473632812</t>
   </si>
   <si>
     <t xml:space="preserve">138.285766601562</t>
@@ -1550,238 +1550,238 @@
     <t xml:space="preserve">139.67919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">140.217971801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.557861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.232192993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.117416381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.367645263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.272613525391</t>
+    <t xml:space="preserve">140.218017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.557876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.232177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.117431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.367691040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.272583007812</t>
   </si>
   <si>
     <t xml:space="preserve">135.40592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">133.492294311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.154586791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.183044433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.263885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.83332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.889297485352</t>
+    <t xml:space="preserve">133.492279052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.154571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.182998657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.263854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.833282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.889282226562</t>
   </si>
   <si>
     <t xml:space="preserve">135.347747802734</t>
   </si>
   <si>
-    <t xml:space="preserve">136.561569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.050918579102</t>
+    <t xml:space="preserve">136.5615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.050903320312</t>
   </si>
   <si>
     <t xml:space="preserve">131.91178894043</t>
   </si>
   <si>
-    <t xml:space="preserve">128.942733764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.689575195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.399200439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.346984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.771881103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.766189575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.560791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.58975982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.954833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.180847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.002464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.873672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.143508911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.554321289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.846618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.016548156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.972724914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.142379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.077926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.011627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.650360107422</t>
+    <t xml:space="preserve">128.942642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.689605712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.399215698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.34700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.771903991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.766166687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.560745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.589752197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.95484161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.180816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.002487182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.873680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.143524169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.554298400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.846611022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.016555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.972732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.142364501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.077987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.011672973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.650329589844</t>
   </si>
   <si>
     <t xml:space="preserve">132.322631835938</t>
   </si>
   <si>
-    <t xml:space="preserve">133.984558105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.455230712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.621368408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.488754272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.619506835938</t>
+    <t xml:space="preserve">133.984603881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.45524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.621383666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.488784790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.619491577148</t>
   </si>
   <si>
     <t xml:space="preserve">136.412155151367</t>
   </si>
   <si>
-    <t xml:space="preserve">136.374816894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.441146850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.484970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.055465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.148849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.225433349609</t>
+    <t xml:space="preserve">136.37483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.441131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.484954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.055419921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.148803710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.225402832031</t>
   </si>
   <si>
     <t xml:space="preserve">135.123672485352</t>
   </si>
   <si>
-    <t xml:space="preserve">136.430862426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.208709716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.1796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.125518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.833297729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.795959472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.239501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.355392456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.448715209961</t>
+    <t xml:space="preserve">136.43083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.20866394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.179702758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.125579833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.833267211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.795928955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.239486694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.355354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.448738098145</t>
   </si>
   <si>
     <t xml:space="preserve">128.793243408203</t>
   </si>
   <si>
-    <t xml:space="preserve">120.334037780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.802780151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.473121643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.854988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.155685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.717781066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.800888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.875564575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.736434936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.221977233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.245338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.733657836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.409805297852</t>
+    <t xml:space="preserve">120.334007263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.802764892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.473129272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.85498046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.15567779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.717788696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.800857543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.875556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.736465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.221969604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.24535369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.733642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.409797668457</t>
   </si>
   <si>
     <t xml:space="preserve">120.578834533691</t>
   </si>
   <si>
-    <t xml:space="preserve">121.480339050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.071754455566</t>
+    <t xml:space="preserve">121.480369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.071746826172</t>
   </si>
   <si>
     <t xml:space="preserve">118.174774169922</t>
@@ -1790,55 +1790,55 @@
     <t xml:space="preserve">118.062072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">119.20777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.42350769043</t>
+    <t xml:space="preserve">119.207778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.423500061035</t>
   </si>
   <si>
     <t xml:space="preserve">119.170204162598</t>
   </si>
   <si>
-    <t xml:space="preserve">117.479843139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.446823120117</t>
+    <t xml:space="preserve">117.479835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.44686126709</t>
   </si>
   <si>
     <t xml:space="preserve">116.052444458008</t>
   </si>
   <si>
-    <t xml:space="preserve">118.832145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.30167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.099639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.625518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.79914855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.686965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.592529296875</t>
+    <t xml:space="preserve">118.83211517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.301681518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.099647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.625541687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.799140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.686958312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.592544555664</t>
   </si>
   <si>
     <t xml:space="preserve">117.554969787598</t>
   </si>
   <si>
-    <t xml:space="preserve">119.639747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.710289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.729080200195</t>
+    <t xml:space="preserve">119.639739990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.710296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.729095458984</t>
   </si>
   <si>
     <t xml:space="preserve">121.611846923828</t>
@@ -1847,37 +1847,37 @@
     <t xml:space="preserve">120.597610473633</t>
   </si>
   <si>
-    <t xml:space="preserve">120.334671020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.583396911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.785430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.193542480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.709815979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.97730255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.747360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.108772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.424003601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.335205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.546356201172</t>
+    <t xml:space="preserve">120.334663391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.583419799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.785423278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.193572998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.709770202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.977310180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.747352600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.108779907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.424018859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.335159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.546363830566</t>
   </si>
   <si>
     <t xml:space="preserve">122.231620788574</t>
@@ -1886,61 +1886,61 @@
     <t xml:space="preserve">118.869689941406</t>
   </si>
   <si>
-    <t xml:space="preserve">117.066635131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.348373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.150901794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.122482299805</t>
+    <t xml:space="preserve">117.06664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.34838104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.150909423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.122497558594</t>
   </si>
   <si>
     <t xml:space="preserve">112.615386962891</t>
   </si>
   <si>
-    <t xml:space="preserve">111.939224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.347869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.563606262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.22957611084</t>
+    <t xml:space="preserve">111.93921661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.347846984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.563591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.229583740234</t>
   </si>
   <si>
     <t xml:space="preserve">105.835166931152</t>
   </si>
   <si>
-    <t xml:space="preserve">106.530097961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.666114807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.684898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.511306762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.137222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.221473693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.202690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.573219299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.104225158691</t>
+    <t xml:space="preserve">106.530090332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.666137695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.684913635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.511299133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.13720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.221458435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.202705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.5732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.104202270508</t>
   </si>
   <si>
     <t xml:space="preserve">115.319938659668</t>
@@ -1949,124 +1949,124 @@
     <t xml:space="preserve">112.939094543457</t>
   </si>
   <si>
-    <t xml:space="preserve">113.978370666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.354820251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.221069335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.504501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.164367675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.359184265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.901306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.338829040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.449272155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.318466186523</t>
+    <t xml:space="preserve">113.97834777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.354804992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.221061706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.504508972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.16438293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.359199523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.901298522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.338836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.449287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.318481445312</t>
   </si>
   <si>
     <t xml:space="preserve">115.830123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">114.828636169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.846076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.447792053223</t>
+    <t xml:space="preserve">114.828651428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.846084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.447799682617</t>
   </si>
   <si>
     <t xml:space="preserve">114.469635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">116.1513671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.65145111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.841857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.843330383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.411682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.327453613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.94807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.267837524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.7373046875</t>
+    <t xml:space="preserve">116.151344299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.651435852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.841873168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.353530883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.843360900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.411697387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.32746887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.948089599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.267852783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.737289428711</t>
   </si>
   <si>
     <t xml:space="preserve">129.96403503418</t>
   </si>
   <si>
-    <t xml:space="preserve">129.416091918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.583183288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.471313476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.113723754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.827362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.392776489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.904426574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.016319274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.603561401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.118316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.978729248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.645980834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.11979675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.047134399414</t>
+    <t xml:space="preserve">129.416076660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.583206176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.471282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.113739013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.827377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.392761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.904441833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.016342163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.603546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.118301391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.978744506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.645950317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.119766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.047119140625</t>
   </si>
   <si>
     <t xml:space="preserve">147.839294433594</t>
@@ -2075,31 +2075,31 @@
     <t xml:space="preserve">152.714385986328</t>
   </si>
   <si>
-    <t xml:space="preserve">156.833602905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.076293945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.760940551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.032836914062</t>
+    <t xml:space="preserve">156.833618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.076324462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.760986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.032806396484</t>
   </si>
   <si>
     <t xml:space="preserve">164.996520996094</t>
   </si>
   <si>
-    <t xml:space="preserve">161.992111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.125839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.349685668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.804580688477</t>
+    <t xml:space="preserve">161.992080688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.12580871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.349716186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.804626464844</t>
   </si>
   <si>
     <t xml:space="preserve">156.720230102539</t>
@@ -2108,10 +2108,10 @@
     <t xml:space="preserve">154.962936401367</t>
   </si>
   <si>
-    <t xml:space="preserve">158.137420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.70426940918</t>
+    <t xml:space="preserve">158.137435913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.704254150391</t>
   </si>
   <si>
     <t xml:space="preserve">160.461563110352</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">156.814712524414</t>
   </si>
   <si>
-    <t xml:space="preserve">159.157821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.008819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.819519042969</t>
+    <t xml:space="preserve">159.157760620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.0087890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.819534301758</t>
   </si>
   <si>
     <t xml:space="preserve">164.560836791992</t>
@@ -2135,94 +2135,94 @@
     <t xml:space="preserve">159.793991088867</t>
   </si>
   <si>
-    <t xml:space="preserve">161.161376953125</t>
+    <t xml:space="preserve">161.161361694336</t>
   </si>
   <si>
     <t xml:space="preserve">159.832000732422</t>
   </si>
   <si>
-    <t xml:space="preserve">157.856857299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.932189941406</t>
+    <t xml:space="preserve">157.856842041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.932159423828</t>
   </si>
   <si>
     <t xml:space="preserve">159.20524597168</t>
   </si>
   <si>
-    <t xml:space="preserve">159.964889526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.970809936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.907943725586</t>
+    <t xml:space="preserve">159.964904785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.970779418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.907928466797</t>
   </si>
   <si>
     <t xml:space="preserve">162.376831054688</t>
   </si>
   <si>
-    <t xml:space="preserve">162.756652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.958343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.33821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.617141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.884368896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.409561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.890197753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.661666870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.326385498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.741607666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.931533813477</t>
+    <t xml:space="preserve">162.756607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.95832824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.338150024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.617172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.884338378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.409515380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.890243530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.661682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.326370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.741638183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.931549072266</t>
   </si>
   <si>
     <t xml:space="preserve">149.082794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">147.183624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.753387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.133255004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.462631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.474426269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.993728637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.892929077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.602111816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.792007446289</t>
+    <t xml:space="preserve">147.183670043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.753433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.133224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.462646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.474456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.993759155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.892913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.602127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.792053222656</t>
   </si>
   <si>
     <t xml:space="preserve">151.399749755859</t>
@@ -2237,133 +2237,133 @@
     <t xml:space="preserve">145.284530639648</t>
   </si>
   <si>
-    <t xml:space="preserve">146.234115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.854278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.904663085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.423980712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.323165893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.84245300293</t>
+    <t xml:space="preserve">146.234085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.854232788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.904724121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.42399597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.323150634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.842468261719</t>
   </si>
   <si>
     <t xml:space="preserve">150.412216186523</t>
   </si>
   <si>
-    <t xml:space="preserve">149.652572631836</t>
+    <t xml:space="preserve">149.652557373047</t>
   </si>
   <si>
     <t xml:space="preserve">148.513076782227</t>
   </si>
   <si>
-    <t xml:space="preserve">146.803833007812</t>
+    <t xml:space="preserve">146.803848266602</t>
   </si>
   <si>
     <t xml:space="preserve">143.955139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">140.346740722656</t>
+    <t xml:space="preserve">140.346755981445</t>
   </si>
   <si>
     <t xml:space="preserve">141.486251831055</t>
   </si>
   <si>
-    <t xml:space="preserve">143.575332641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.044174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.121429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.691162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.070983886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.836578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.69352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.220947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.457214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.929840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.979919433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.175521850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.702926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.984634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.361785888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.748260498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.225631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.83903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.366470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.803085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.640335083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.876678466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.076965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.000335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.365737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.749954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.840682983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.222503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.22721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.270248413086</t>
+    <t xml:space="preserve">143.575302124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.044158935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.121490478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.691177368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.071029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.836547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.693557739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.220932006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.457229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.929870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.979934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.175537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.702941894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.984603881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.361770629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.748306274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.225646972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.839065551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.366439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.803070068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.640365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.876647949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.076950073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.000305175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.36572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.749923706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.840713500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.222534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.227203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.270263671875</t>
   </si>
   <si>
     <t xml:space="preserve">179.038650512695</t>
@@ -2372,16 +2372,16 @@
     <t xml:space="preserve">178.800033569336</t>
   </si>
   <si>
-    <t xml:space="preserve">174.265533447266</t>
+    <t xml:space="preserve">174.265548706055</t>
   </si>
   <si>
     <t xml:space="preserve">185.243682861328</t>
   </si>
   <si>
-    <t xml:space="preserve">184.527725219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.09342956543</t>
+    <t xml:space="preserve">184.527694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.093414306641</t>
   </si>
   <si>
     <t xml:space="preserve">184.432220458984</t>
@@ -2390,46 +2390,46 @@
     <t xml:space="preserve">185.291397094727</t>
   </si>
   <si>
-    <t xml:space="preserve">186.102813720703</t>
+    <t xml:space="preserve">186.102798461914</t>
   </si>
   <si>
     <t xml:space="preserve">187.7734375</t>
   </si>
   <si>
-    <t xml:space="preserve">189.491714477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.918914794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.969039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.775726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.06916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.682632446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.446334838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.828186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.584823608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.677947998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.29606628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.591888427734</t>
+    <t xml:space="preserve">189.491760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.918930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.969024658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.775756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.069183349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.6826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.446365356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.828170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.584854125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.677963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.296112060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.591873168945</t>
   </si>
   <si>
     <t xml:space="preserve">191.973709106445</t>
@@ -2438,13 +2438,13 @@
     <t xml:space="preserve">193.88298034668</t>
   </si>
   <si>
-    <t xml:space="preserve">195.983123779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.415084838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.26953125</t>
+    <t xml:space="preserve">195.983139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.4150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.269515991211</t>
   </si>
   <si>
     <t xml:space="preserve">199.515197753906</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">197.319580078125</t>
   </si>
   <si>
-    <t xml:space="preserve">196.84228515625</t>
+    <t xml:space="preserve">196.842254638672</t>
   </si>
   <si>
     <t xml:space="preserve">197.987808227539</t>
@@ -2465,31 +2465,31 @@
     <t xml:space="preserve">213.739013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">212.975326538086</t>
+    <t xml:space="preserve">212.975341796875</t>
   </si>
   <si>
     <t xml:space="preserve">213.929946899414</t>
   </si>
   <si>
-    <t xml:space="preserve">218.321166992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.703002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.366577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.498092651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.564315795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.918029785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.930206298828</t>
+    <t xml:space="preserve">218.321151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.703033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.366592407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.498046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.564300537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.918045043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.930191040039</t>
   </si>
   <si>
     <t xml:space="preserve">221.534729003906</t>
@@ -2498,169 +2498,169 @@
     <t xml:space="preserve">223.067855834961</t>
   </si>
   <si>
-    <t xml:space="preserve">222.205444335938</t>
+    <t xml:space="preserve">222.205459594727</t>
   </si>
   <si>
     <t xml:space="preserve">214.444076538086</t>
   </si>
   <si>
-    <t xml:space="preserve">214.156600952148</t>
+    <t xml:space="preserve">214.156631469727</t>
   </si>
   <si>
     <t xml:space="preserve">213.294250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">212.048599243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.060791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.186187744141</t>
+    <t xml:space="preserve">212.048614501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.060821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.186218261719</t>
   </si>
   <si>
     <t xml:space="preserve">207.736694335938</t>
   </si>
   <si>
-    <t xml:space="preserve">208.982406616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.269805908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.994583129883</t>
+    <t xml:space="preserve">208.982345581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.269821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.994552612305</t>
   </si>
   <si>
     <t xml:space="preserve">209.461456298828</t>
   </si>
   <si>
-    <t xml:space="preserve">206.970184326172</t>
+    <t xml:space="preserve">206.970169067383</t>
   </si>
   <si>
     <t xml:space="preserve">198.058929443359</t>
   </si>
   <si>
-    <t xml:space="preserve">196.621643066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.447418212891</t>
+    <t xml:space="preserve">196.621658325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.447402954102</t>
   </si>
   <si>
     <t xml:space="preserve">190.920364379883</t>
   </si>
   <si>
-    <t xml:space="preserve">191.49528503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.902069091797</t>
+    <t xml:space="preserve">191.495330810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.902084350586</t>
   </si>
   <si>
     <t xml:space="preserve">187.087631225586</t>
   </si>
   <si>
-    <t xml:space="preserve">189.530990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.62678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.99787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.632919311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.537139892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.889892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.152923583984</t>
+    <t xml:space="preserve">189.531036376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.626815795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.997894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.632934570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.537094116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.889831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.152908325195</t>
   </si>
   <si>
     <t xml:space="preserve">188.572799682617</t>
   </si>
   <si>
-    <t xml:space="preserve">193.651260375977</t>
+    <t xml:space="preserve">193.651245117188</t>
   </si>
   <si>
     <t xml:space="preserve">189.770584106445</t>
   </si>
   <si>
-    <t xml:space="preserve">185.410781860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.39338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.237442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.501403808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.172134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.525833129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.555389404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.938720703125</t>
+    <t xml:space="preserve">185.410766601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.393341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.237457275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.501419067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.172180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.525848388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.555435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.938674926758</t>
   </si>
   <si>
     <t xml:space="preserve">194.992736816406</t>
   </si>
   <si>
-    <t xml:space="preserve">195.471817016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.442230224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.72966003418</t>
+    <t xml:space="preserve">195.47184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.442199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.729644775391</t>
   </si>
   <si>
     <t xml:space="preserve">200.358627319336</t>
   </si>
   <si>
-    <t xml:space="preserve">198.538070678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.921340942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.987564086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.849884033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.215835571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.832550048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.802917480469</t>
+    <t xml:space="preserve">198.538040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.921295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.987533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.849899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.2158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.83251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.802932739258</t>
   </si>
   <si>
     <t xml:space="preserve">207.353408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">213.006805419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.989395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.593902587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.97721862793</t>
+    <t xml:space="preserve">213.006774902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.98942565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.593887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.977172851562</t>
   </si>
   <si>
     <t xml:space="preserve">219.905776977539</t>
@@ -2669,49 +2669,49 @@
     <t xml:space="preserve">220.768157958984</t>
   </si>
   <si>
-    <t xml:space="preserve">218.892791748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.16162109375</t>
+    <t xml:space="preserve">218.892776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.161636352539</t>
   </si>
   <si>
     <t xml:space="preserve">219.277481079102</t>
   </si>
   <si>
-    <t xml:space="preserve">221.297149658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.200973510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.316787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.663238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.509140014648</t>
+    <t xml:space="preserve">221.297134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.200958251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.316772460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.663192749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.50910949707</t>
   </si>
   <si>
     <t xml:space="preserve">224.182342529297</t>
   </si>
   <si>
-    <t xml:space="preserve">227.067581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.162689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.064376831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.238159179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.198822021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.756210327148</t>
+    <t xml:space="preserve">227.067611694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.162704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.064361572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.238143920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.198806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.756195068359</t>
   </si>
   <si>
     <t xml:space="preserve">207.351852416992</t>
@@ -2720,82 +2720,82 @@
     <t xml:space="preserve">203.985733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">208.313598632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.640365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.507034301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.929931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.279586791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">237.646774291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.25993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">225.624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.567031860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">232.068634033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.819458007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.43473815918</t>
+    <t xml:space="preserve">208.313568115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.640335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.507019042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.929977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.279556274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.646759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.259918212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">225.624969482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.56706237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.068649291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.819442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.434753417969</t>
   </si>
   <si>
     <t xml:space="preserve">235.530944824219</t>
   </si>
   <si>
-    <t xml:space="preserve">228.317840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.644638061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220.527709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.662170410156</t>
+    <t xml:space="preserve">228.317855834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.644622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.527740478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.662155151367</t>
   </si>
   <si>
     <t xml:space="preserve">218.12336730957</t>
   </si>
   <si>
-    <t xml:space="preserve">219.373641967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.256713867188</t>
+    <t xml:space="preserve">219.373626708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.256759643555</t>
   </si>
   <si>
     <t xml:space="preserve">206.197738647461</t>
   </si>
   <si>
-    <t xml:space="preserve">207.544174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.409759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.102615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.94856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.15950012207</t>
+    <t xml:space="preserve">207.544219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.409774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.102645874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.948532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.159469604492</t>
   </si>
   <si>
     <t xml:space="preserve">200.042617797852</t>
@@ -2807,88 +2807,88 @@
     <t xml:space="preserve">205.813064575195</t>
   </si>
   <si>
-    <t xml:space="preserve">208.12126159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.928924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.986831665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.794464111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.352890014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.101623535156</t>
+    <t xml:space="preserve">208.121215820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.928863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.98681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.794448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.352920532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.101593017578</t>
   </si>
   <si>
     <t xml:space="preserve">202.639297485352</t>
   </si>
   <si>
-    <t xml:space="preserve">202.158386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.139862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.927841186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.234954833984</t>
+    <t xml:space="preserve">202.158432006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.139846801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.927810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.234939575195</t>
   </si>
   <si>
     <t xml:space="preserve">198.959442138672</t>
   </si>
   <si>
-    <t xml:space="preserve">207.076309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.525726318359</t>
+    <t xml:space="preserve">207.076324462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.525756835938</t>
   </si>
   <si>
     <t xml:space="preserve">206.593170166016</t>
   </si>
   <si>
-    <t xml:space="preserve">204.853820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.892013549805</t>
+    <t xml:space="preserve">204.853805541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.892044067383</t>
   </si>
   <si>
     <t xml:space="preserve">203.404373168945</t>
   </si>
   <si>
-    <t xml:space="preserve">205.916793823242</t>
+    <t xml:space="preserve">205.916763305664</t>
   </si>
   <si>
     <t xml:space="preserve">205.626876831055</t>
   </si>
   <si>
-    <t xml:space="preserve">216.256072998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.130233764648</t>
+    <t xml:space="preserve">216.256042480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.130249023438</t>
   </si>
   <si>
     <t xml:space="preserve">214.806625366211</t>
   </si>
   <si>
-    <t xml:space="preserve">221.95719909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.116729736328</t>
+    <t xml:space="preserve">221.957183837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.116744995117</t>
   </si>
   <si>
     <t xml:space="preserve">229.39762878418</t>
   </si>
   <si>
-    <t xml:space="preserve">231.90998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">233.262802124023</t>
+    <t xml:space="preserve">231.909973144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">233.262756347656</t>
   </si>
   <si>
     <t xml:space="preserve">232.393157958984</t>
@@ -2897,52 +2897,52 @@
     <t xml:space="preserve">231.233581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">237.417816162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">236.161651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.312225341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.40885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">246.307754516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.332458496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.65153503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">249.882965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.525726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.10546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.294235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.00439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.622375488281</t>
+    <t xml:space="preserve">237.417846679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">236.161666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.312240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.408874511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">246.307708740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.332443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.651519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">249.88298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.525680541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.105422973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.29426574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.004348754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.622329711914</t>
   </si>
   <si>
     <t xml:space="preserve">252.008834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">250.656066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.844757080078</t>
+    <t xml:space="preserve">250.655990600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.844833374023</t>
   </si>
   <si>
     <t xml:space="preserve">257.468414306641</t>
@@ -2951,10 +2951,10 @@
     <t xml:space="preserve">260.802093505859</t>
   </si>
   <si>
-    <t xml:space="preserve">266.020111083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.48974609375</t>
+    <t xml:space="preserve">266.020050048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.489807128906</t>
   </si>
   <si>
     <t xml:space="preserve">276.890869140625</t>
@@ -2963,100 +2963,100 @@
     <t xml:space="preserve">275.006622314453</t>
   </si>
   <si>
-    <t xml:space="preserve">274.668395996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.305419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.691925048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.29541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.555999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.796478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.347015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.869537353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.595367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.822296142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.730194091797</t>
+    <t xml:space="preserve">274.668365478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.305450439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.692016601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.295379638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.556030273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.796493530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.347045898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.869506835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.595306396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.822357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.730133056641</t>
   </si>
   <si>
     <t xml:space="preserve">265.536895751953</t>
   </si>
   <si>
-    <t xml:space="preserve">264.957214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.339202880859</t>
+    <t xml:space="preserve">264.957153320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.339172363281</t>
   </si>
   <si>
     <t xml:space="preserve">265.102111816406</t>
   </si>
   <si>
-    <t xml:space="preserve">263.942535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.579711914062</t>
+    <t xml:space="preserve">263.942504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.579681396484</t>
   </si>
   <si>
     <t xml:space="preserve">266.454895019531</t>
   </si>
   <si>
-    <t xml:space="preserve">267.405212402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">281.854309082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">277.005706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.290374755859</t>
+    <t xml:space="preserve">267.405242919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281.854339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">277.005615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.290405273438</t>
   </si>
   <si>
     <t xml:space="preserve">263.623291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">271.090240478516</t>
+    <t xml:space="preserve">271.090270996094</t>
   </si>
   <si>
     <t xml:space="preserve">275.599548339844</t>
   </si>
   <si>
-    <t xml:space="preserve">272.108459472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">280.642150878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">281.466430664062</t>
+    <t xml:space="preserve">272.108520507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">280.642181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281.466491699219</t>
   </si>
   <si>
     <t xml:space="preserve">282.630187988281</t>
   </si>
   <si>
-    <t xml:space="preserve">274.532836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">280.205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">278.411773681641</t>
+    <t xml:space="preserve">274.532806396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">280.205780029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">278.411804199219</t>
   </si>
   <si>
     <t xml:space="preserve">284.084777832031</t>
@@ -3065,76 +3065,76 @@
     <t xml:space="preserve">279.769439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">275.066192626953</t>
+    <t xml:space="preserve">275.066162109375</t>
   </si>
   <si>
     <t xml:space="preserve">270.750885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">268.471923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">271.817565917969</t>
+    <t xml:space="preserve">268.471984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271.817626953125</t>
   </si>
   <si>
     <t xml:space="preserve">265.611236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">272.25390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270.847808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.484313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.720977783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">284.763549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.291412353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.455078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.576110839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.552093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.679321289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.843048095703</t>
+    <t xml:space="preserve">272.253936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270.847778320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.484283447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.720947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">284.763610839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.291381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.455108642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.576141357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.552062988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.679260253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.842987060547</t>
   </si>
   <si>
     <t xml:space="preserve">302.946166992188</t>
   </si>
   <si>
-    <t xml:space="preserve">303.721984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.049621582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.740478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.019409179688</t>
+    <t xml:space="preserve">303.721954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.049682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.740539550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.019378662109</t>
   </si>
   <si>
     <t xml:space="preserve">318.364959716797</t>
   </si>
   <si>
-    <t xml:space="preserve">309.443328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.625274658203</t>
+    <t xml:space="preserve">309.443420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.625305175781</t>
   </si>
   <si>
     <t xml:space="preserve">318.12255859375</t>
@@ -3143,136 +3143,136 @@
     <t xml:space="preserve">315.213317871094</t>
   </si>
   <si>
-    <t xml:space="preserve">309.879730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.825073242188</t>
+    <t xml:space="preserve">309.879791259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.825103759766</t>
   </si>
   <si>
     <t xml:space="preserve">311.916229248047</t>
   </si>
   <si>
-    <t xml:space="preserve">312.837432861328</t>
+    <t xml:space="preserve">312.837493896484</t>
   </si>
   <si>
     <t xml:space="preserve">316.231567382812</t>
   </si>
   <si>
-    <t xml:space="preserve">313.467803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.631530761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.661743164062</t>
+    <t xml:space="preserve">313.467864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.631500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.661773681641</t>
   </si>
   <si>
     <t xml:space="preserve">308.425170898438</t>
   </si>
   <si>
-    <t xml:space="preserve">308.473693847656</t>
+    <t xml:space="preserve">308.473663330078</t>
   </si>
   <si>
     <t xml:space="preserve">300.667266845703</t>
   </si>
   <si>
-    <t xml:space="preserve">289.854705810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">288.836456298828</t>
+    <t xml:space="preserve">289.854736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">288.836517333984</t>
   </si>
   <si>
     <t xml:space="preserve">289.369812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">287.284820556641</t>
+    <t xml:space="preserve">287.284881591797</t>
   </si>
   <si>
     <t xml:space="preserve">285.539367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">283.842315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.806793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.298767089844</t>
+    <t xml:space="preserve">283.84228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.806823730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.298797607422</t>
   </si>
   <si>
     <t xml:space="preserve">298.369110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">305.812561035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.574676513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.428894042969</t>
+    <t xml:space="preserve">305.812530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.574645996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.428955078125</t>
   </si>
   <si>
     <t xml:space="preserve">316.126312255859</t>
   </si>
   <si>
-    <t xml:space="preserve">309.996490478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.358642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.41259765625</t>
+    <t xml:space="preserve">309.996429443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.358673095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.412628173828</t>
   </si>
   <si>
     <t xml:space="preserve">314.228973388672</t>
   </si>
   <si>
-    <t xml:space="preserve">303.234069824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.925903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294.185241699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.250152587891</t>
+    <t xml:space="preserve">303.234100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.925964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.185272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.250213623047</t>
   </si>
   <si>
     <t xml:space="preserve">300.217834472656</t>
   </si>
   <si>
-    <t xml:space="preserve">295.887969970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.596252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.963836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.688201904297</t>
+    <t xml:space="preserve">295.888000488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.596374511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.9638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.688262939453</t>
   </si>
   <si>
     <t xml:space="preserve">308.585571289062</t>
   </si>
   <si>
-    <t xml:space="preserve">306.299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.969207763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.412414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.342132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.796020507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.990692138672</t>
+    <t xml:space="preserve">306.299041748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.96923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.412475585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.342102050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.796112060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.990661621094</t>
   </si>
   <si>
     <t xml:space="preserve">297.104217529297</t>
@@ -3284,25 +3284,25 @@
     <t xml:space="preserve">311.845092773438</t>
   </si>
   <si>
-    <t xml:space="preserve">314.083038330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.883697509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327.656341552734</t>
+    <t xml:space="preserve">314.0830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.883666992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327.656311035156</t>
   </si>
   <si>
     <t xml:space="preserve">324.445434570312</t>
   </si>
   <si>
-    <t xml:space="preserve">316.612823486328</t>
+    <t xml:space="preserve">316.612762451172</t>
   </si>
   <si>
     <t xml:space="preserve">320.066955566406</t>
   </si>
   <si>
-    <t xml:space="preserve">324.348114013672</t>
+    <t xml:space="preserve">324.34814453125</t>
   </si>
   <si>
     <t xml:space="preserve">330.721252441406</t>
@@ -3317,40 +3317,40 @@
     <t xml:space="preserve">325.758941650391</t>
   </si>
   <si>
-    <t xml:space="preserve">327.315734863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.883270263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.380737304688</t>
+    <t xml:space="preserve">327.315704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.88330078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.380676269531</t>
   </si>
   <si>
     <t xml:space="preserve">332.521301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">328.580657958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">326.245452880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.710327148438</t>
+    <t xml:space="preserve">328.580688476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326.245422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.710296630859</t>
   </si>
   <si>
     <t xml:space="preserve">334.515899658203</t>
   </si>
   <si>
-    <t xml:space="preserve">343.759399414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.543121337891</t>
+    <t xml:space="preserve">343.759368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.543090820312</t>
   </si>
   <si>
     <t xml:space="preserve">347.456787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">347.748657226562</t>
+    <t xml:space="preserve">347.748687744141</t>
   </si>
   <si>
     <t xml:space="preserve">352.7109375</t>
@@ -3362,16 +3362,16 @@
     <t xml:space="preserve">341.424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">353.829864501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">358.257019042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.473083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.224487304688</t>
+    <t xml:space="preserve">353.829895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">358.256988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.473052978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.224456787109</t>
   </si>
   <si>
     <t xml:space="preserve">353.635284423828</t>
@@ -3380,10 +3380,10 @@
     <t xml:space="preserve">357.429992675781</t>
   </si>
   <si>
-    <t xml:space="preserve">349.013549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.672668457031</t>
+    <t xml:space="preserve">349.013519287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.672637939453</t>
   </si>
   <si>
     <t xml:space="preserve">334.946624755859</t>
@@ -3392,82 +3392,82 @@
     <t xml:space="preserve">331.531280517578</t>
   </si>
   <si>
-    <t xml:space="preserve">331.921569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.898651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.971984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.728912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.606689453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.581695556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.093811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.704345703125</t>
+    <t xml:space="preserve">331.921630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.898681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.972045898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.728881835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.606781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.581756591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.093780517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.704284667969</t>
   </si>
   <si>
     <t xml:space="preserve">345.095062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">341.435760498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">344.509552001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">344.119201660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">346.509979248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.826934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.070007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.582916259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.68017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.411163330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.801055908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.239410400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.751037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.945373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.994171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.116363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.118438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.654693603516</t>
+    <t xml:space="preserve">341.435729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.509521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.119232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">346.510009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.826904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.070037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.582946777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.680114746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.411193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.801116943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.239379882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.751068115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.945404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.116394042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.118408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.654724121094</t>
   </si>
   <si>
     <t xml:space="preserve">336.800659179688</t>
@@ -3476,25 +3476,25 @@
     <t xml:space="preserve">335.141784667969</t>
   </si>
   <si>
-    <t xml:space="preserve">338.605926513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.044250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.703063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.629699707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">337.28857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.897033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.4345703125</t>
+    <t xml:space="preserve">338.60595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.044189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.703094482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.629730224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">337.288513183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.897003173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.434539794922</t>
   </si>
   <si>
     <t xml:space="preserve">325.774047851562</t>
@@ -3503,70 +3503,70 @@
     <t xml:space="preserve">315.625610351562</t>
   </si>
   <si>
-    <t xml:space="preserve">321.529205322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">321.919525146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">326.018005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323.96875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.188507080078</t>
+    <t xml:space="preserve">321.529235839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">321.919586181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326.017974853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.968811035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.188568115234</t>
   </si>
   <si>
     <t xml:space="preserve">320.065521240234</t>
   </si>
   <si>
-    <t xml:space="preserve">317.528503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.088073730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.672698974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.428771972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">310.161041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.039703369141</t>
+    <t xml:space="preserve">317.528381347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.088043212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.672790527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.428833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">310.161102294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.039672851562</t>
   </si>
   <si>
     <t xml:space="preserve">308.794952392578</t>
   </si>
   <si>
-    <t xml:space="preserve">307.184814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.477172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.131958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.331176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.160217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.501770019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.575653076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.161437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.796569824219</t>
+    <t xml:space="preserve">307.184844970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.477264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.131927490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.331268310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.160247802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.501739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.575531005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.161499023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.796600341797</t>
   </si>
   <si>
     <t xml:space="preserve">316.503845214844</t>
@@ -3578,34 +3578,34 @@
     <t xml:space="preserve">313.595520019531</t>
   </si>
   <si>
-    <t xml:space="preserve">303.558471679688</t>
+    <t xml:space="preserve">303.558502197266</t>
   </si>
   <si>
     <t xml:space="preserve">301.942810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">300.571868896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.775177001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.146118164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.341888427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.886413574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294.011138916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.93994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290.192108154297</t>
+    <t xml:space="preserve">300.571899414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.775115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.146026611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.341918945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.886444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.011108398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">290.192169189453</t>
   </si>
   <si>
     <t xml:space="preserve">289.604644775391</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">293.080871582031</t>
   </si>
   <si>
-    <t xml:space="preserve">291.465148925781</t>
+    <t xml:space="preserve">291.465118408203</t>
   </si>
   <si>
     <t xml:space="preserve">289.702575683594</t>
@@ -3629,46 +3629,46 @@
     <t xml:space="preserve">292.052703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">295.528930664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.969543457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.195007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.390869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.089691162109</t>
+    <t xml:space="preserve">295.528900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.969573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.195037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.390838623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.089721679688</t>
   </si>
   <si>
     <t xml:space="preserve">303.411651611328</t>
   </si>
   <si>
-    <t xml:space="preserve">299.592742919922</t>
+    <t xml:space="preserve">299.592681884766</t>
   </si>
   <si>
     <t xml:space="preserve">301.110473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">299.984375</t>
+    <t xml:space="preserve">299.984344482422</t>
   </si>
   <si>
     <t xml:space="preserve">305.370086669922</t>
   </si>
   <si>
-    <t xml:space="preserve">304.488830566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.509552001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.419036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.9501953125</t>
+    <t xml:space="preserve">304.488800048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.509613037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.419006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.950134277344</t>
   </si>
   <si>
     <t xml:space="preserve">307.964996337891</t>
@@ -3677,13 +3677,13 @@
     <t xml:space="preserve">314.7216796875</t>
   </si>
   <si>
-    <t xml:space="preserve">318.442626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.884796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.018310546875</t>
+    <t xml:space="preserve">318.442718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.018280029297</t>
   </si>
   <si>
     <t xml:space="preserve">329.605834960938</t>
@@ -3692,10 +3692,10 @@
     <t xml:space="preserve">330.976715087891</t>
   </si>
   <si>
-    <t xml:space="preserve">333.326843261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.110260009766</t>
+    <t xml:space="preserve">333.326873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.110198974609</t>
   </si>
   <si>
     <t xml:space="preserve">332.543487548828</t>
@@ -3707,64 +3707,64 @@
     <t xml:space="preserve">341.944000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">340.768920898438</t>
+    <t xml:space="preserve">340.768951416016</t>
   </si>
   <si>
     <t xml:space="preserve">344.685821533203</t>
   </si>
   <si>
-    <t xml:space="preserve">352.323760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">358.78662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.433380126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">380.133605957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">382.679565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385.225555419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385.421417236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">386.204772949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389.338317871094</t>
+    <t xml:space="preserve">352.323699951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">358.786651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.433349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">380.133575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">382.679626464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385.2255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385.421447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">386.204803466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">389.338287353516</t>
   </si>
   <si>
     <t xml:space="preserve">395.358032226562</t>
   </si>
   <si>
-    <t xml:space="preserve">389.465942382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.39404296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.197662353516</t>
+    <t xml:space="preserve">389.465972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.394012451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.197631835938</t>
   </si>
   <si>
     <t xml:space="preserve">398.304046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">401.0537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.428527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.483947753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.091186523438</t>
+    <t xml:space="preserve">401.053680419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.428497314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.484008789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.091156005859</t>
   </si>
   <si>
     <t xml:space="preserve">387.109130859375</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">391.233581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">396.143707275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.680297851562</t>
+    <t xml:space="preserve">396.143615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.680328369141</t>
   </si>
   <si>
     <t xml:space="preserve">396.536407470703</t>
@@ -3788,10 +3788,10 @@
     <t xml:space="preserve">408.124206542969</t>
   </si>
   <si>
-    <t xml:space="preserve">404.785400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.963775634766</t>
+    <t xml:space="preserve">404.785339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.963745117188</t>
   </si>
   <si>
     <t xml:space="preserve">407.731384277344</t>
@@ -3809,49 +3809,49 @@
     <t xml:space="preserve">407.535003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">406.749389648438</t>
+    <t xml:space="preserve">406.749359130859</t>
   </si>
   <si>
     <t xml:space="preserve">413.034271240234</t>
   </si>
   <si>
-    <t xml:space="preserve">409.498992919922</t>
+    <t xml:space="preserve">409.4990234375</t>
   </si>
   <si>
     <t xml:space="preserve">417.551513671875</t>
   </si>
   <si>
-    <t xml:space="preserve">419.122680664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.479553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.980316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.711883544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">420.497528076172</t>
+    <t xml:space="preserve">419.122741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.479583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.980285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.711944580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420.497589111328</t>
   </si>
   <si>
     <t xml:space="preserve">405.570983886719</t>
   </si>
   <si>
-    <t xml:space="preserve">403.606994628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397.518463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">390.447967529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">383.377502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">391.82275390625</t>
+    <t xml:space="preserve">403.60693359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397.518402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">390.447998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">383.377471923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">391.822784423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.947265625</t>
@@ -3866,154 +3866,154 @@
     <t xml:space="preserve">410.284606933594</t>
   </si>
   <si>
-    <t xml:space="preserve">409.302551269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">408.320587158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.142211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.356567382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.232116699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.767364501953</t>
+    <t xml:space="preserve">409.302642822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">408.320617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.142181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.356597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.232147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.767395019531</t>
   </si>
   <si>
     <t xml:space="preserve">413.819854736328</t>
   </si>
   <si>
-    <t xml:space="preserve">404.588928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">400.464477539062</t>
+    <t xml:space="preserve">404.588958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400.464447021484</t>
   </si>
   <si>
     <t xml:space="preserve">403.410552978516</t>
   </si>
   <si>
-    <t xml:space="preserve">477.650604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">474.508209228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">470.187377929688</t>
+    <t xml:space="preserve">477.650634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">474.508270263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470.187316894531</t>
   </si>
   <si>
     <t xml:space="preserve">474.115386962891</t>
   </si>
   <si>
-    <t xml:space="preserve">486.252014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">488.614349365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">495.110900878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">493.634338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">492.157897949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">496.095153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.524627685547</t>
+    <t xml:space="preserve">486.251983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">488.614379882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">495.110870361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">493.634368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">492.157867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">496.095092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.524566650391</t>
   </si>
   <si>
     <t xml:space="preserve">499.048095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">503.477508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">503.969696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">501.016754150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">495.602966308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.032440185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">507.414733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">511.844177246094</t>
+    <t xml:space="preserve">503.4775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">503.9697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">501.016723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">495.602996826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.032470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">507.414764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">511.844268798828</t>
   </si>
   <si>
     <t xml:space="preserve">514.797180175781</t>
   </si>
   <si>
-    <t xml:space="preserve">509.383514404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">527.59326171875</t>
+    <t xml:space="preserve">509.383483886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">527.593200683594</t>
   </si>
   <si>
     <t xml:space="preserve">535.9599609375</t>
   </si>
   <si>
-    <t xml:space="preserve">547.279602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">546.295227050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">546.787536621094</t>
+    <t xml:space="preserve">547.279541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">546.295288085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">546.787414550781</t>
   </si>
   <si>
     <t xml:space="preserve">550.232482910156</t>
   </si>
   <si>
-    <t xml:space="preserve">539.897216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">528.08544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">526.116760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">512.336364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">510.859893798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">489.992431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.461853027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">517.750122070312</t>
+    <t xml:space="preserve">539.897277832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">528.085388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">526.116821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">512.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">510.859924316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">489.992401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.461822509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">517.750061035156</t>
   </si>
   <si>
     <t xml:space="preserve">532.514831542969</t>
   </si>
   <si>
-    <t xml:space="preserve">554.661987304688</t>
+    <t xml:space="preserve">554.661926269531</t>
   </si>
   <si>
     <t xml:space="preserve">568.4423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">567.9501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">575.824829101562</t>
+    <t xml:space="preserve">567.950134277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">575.82470703125</t>
   </si>
   <si>
     <t xml:space="preserve">561.552124023438</t>
@@ -4022,55 +4022,55 @@
     <t xml:space="preserve">569.426696777344</t>
   </si>
   <si>
-    <t xml:space="preserve">545.803100585938</t>
+    <t xml:space="preserve">545.803161621094</t>
   </si>
   <si>
     <t xml:space="preserve">543.342346191406</t>
   </si>
   <si>
-    <t xml:space="preserve">540.389465332031</t>
+    <t xml:space="preserve">540.389282226562</t>
   </si>
   <si>
     <t xml:space="preserve">549.248229980469</t>
   </si>
   <si>
-    <t xml:space="preserve">555.646240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.022705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">523.656005859375</t>
+    <t xml:space="preserve">555.646301269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.022644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">523.656066894531</t>
   </si>
   <si>
     <t xml:space="preserve">514.304992675781</t>
   </si>
   <si>
-    <t xml:space="preserve">517.257873535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">534.975646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">544.818786621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">553.185485839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">554.300048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">536.053466796875</t>
+    <t xml:space="preserve">517.258056640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534.975708007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">544.818725585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">553.185424804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">554.299926757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">536.053527832031</t>
   </si>
   <si>
     <t xml:space="preserve">532.108337402344</t>
   </si>
   <si>
-    <t xml:space="preserve">536.546630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">542.46435546875</t>
+    <t xml:space="preserve">536.546691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">542.464416503906</t>
   </si>
   <si>
     <t xml:space="preserve">537.532958984375</t>
@@ -4079,13 +4079,13 @@
     <t xml:space="preserve">541.478088378906</t>
   </si>
   <si>
-    <t xml:space="preserve">543.450805664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">533.094665527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">531.121948242188</t>
+    <t xml:space="preserve">543.450744628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">533.094604492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">531.122009277344</t>
   </si>
   <si>
     <t xml:space="preserve">538.026123046875</t>
@@ -4094,16 +4094,16 @@
     <t xml:space="preserve">540.491821289062</t>
   </si>
   <si>
-    <t xml:space="preserve">532.601379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.039794921875</t>
+    <t xml:space="preserve">532.601440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.039733886719</t>
   </si>
   <si>
     <t xml:space="preserve">534.080871582031</t>
   </si>
   <si>
-    <t xml:space="preserve">539.012329101562</t>
+    <t xml:space="preserve">539.012390136719</t>
   </si>
   <si>
     <t xml:space="preserve">526.190490722656</t>
@@ -4112,13 +4112,13 @@
     <t xml:space="preserve">531.615112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">517.806945800781</t>
+    <t xml:space="preserve">517.807006835938</t>
   </si>
   <si>
     <t xml:space="preserve">513.36865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">523.231628417969</t>
+    <t xml:space="preserve">523.231689453125</t>
   </si>
   <si>
     <t xml:space="preserve">519.779541015625</t>
@@ -4127,79 +4127,79 @@
     <t xml:space="preserve">511.88916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">509.916534423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">511.395965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">518.793212890625</t>
+    <t xml:space="preserve">509.916564941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">511.396026611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">518.793273925781</t>
   </si>
   <si>
     <t xml:space="preserve">520.765808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">527.669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">552.820556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567.121826171875</t>
+    <t xml:space="preserve">527.669982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">552.820617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567.121887207031</t>
   </si>
   <si>
     <t xml:space="preserve">557.258911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">567.615112304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">565.642456054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.108215332031</t>
+    <t xml:space="preserve">567.614990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">565.642395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.108154296875</t>
   </si>
   <si>
     <t xml:space="preserve">573.532775878906</t>
   </si>
   <si>
-    <t xml:space="preserve">581.423156738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">583.888977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">575.012329101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">561.697204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569.094482421875</t>
+    <t xml:space="preserve">581.423278808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">583.889038085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">575.012268066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">561.697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569.094421386719</t>
   </si>
   <si>
     <t xml:space="preserve">568.601318359375</t>
   </si>
   <si>
-    <t xml:space="preserve">577.47802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">572.053405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">577.971130371094</t>
+    <t xml:space="preserve">577.478088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">572.053344726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">577.97119140625</t>
   </si>
   <si>
     <t xml:space="preserve">587.341064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">587.834167480469</t>
+    <t xml:space="preserve">587.834228515625</t>
   </si>
   <si>
     <t xml:space="preserve">585.861572265625</t>
   </si>
   <si>
-    <t xml:space="preserve">593.751953125</t>
+    <t xml:space="preserve">593.752014160156</t>
   </si>
   <si>
     <t xml:space="preserve">609.039611816406</t>
@@ -4223,19 +4223,19 @@
     <t xml:space="preserve">671.176452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">679.559997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">695.172973632812</t>
+    <t xml:space="preserve">679.559936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">695.172912597656</t>
   </si>
   <si>
     <t xml:space="preserve">698.631469726562</t>
   </si>
   <si>
-    <t xml:space="preserve">722.841613769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">726.300048828125</t>
+    <t xml:space="preserve">722.841552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">726.300170898438</t>
   </si>
   <si>
     <t xml:space="preserve">700.11376953125</t>
@@ -4250,25 +4250,25 @@
     <t xml:space="preserve">697.643371582031</t>
   </si>
   <si>
-    <t xml:space="preserve">705.054626464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">699.125610351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">688.255920410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">686.279418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">709.995361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">722.347412109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">710.489440917969</t>
+    <t xml:space="preserve">705.054565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">699.125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">688.255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">686.279541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">709.995422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722.347534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">710.489379882812</t>
   </si>
   <si>
     <t xml:space="preserve">711.971740722656</t>
@@ -4277,64 +4277,64 @@
     <t xml:space="preserve">690.232116699219</t>
   </si>
   <si>
-    <t xml:space="preserve">660.587219238281</t>
+    <t xml:space="preserve">660.587280273438</t>
   </si>
   <si>
     <t xml:space="preserve">678.868225097656</t>
   </si>
   <si>
-    <t xml:space="preserve">683.31494140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">682.326843261719</t>
+    <t xml:space="preserve">683.315063476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">682.326904296875</t>
   </si>
   <si>
     <t xml:space="preserve">697.149291992188</t>
   </si>
   <si>
-    <t xml:space="preserve">704.560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.066467285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">706.042724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720.865173339844</t>
+    <t xml:space="preserve">704.560485839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.066345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706.042663574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720.865234375</t>
   </si>
   <si>
     <t xml:space="preserve">698.829162597656</t>
   </si>
   <si>
-    <t xml:space="preserve">709.896606445312</t>
+    <t xml:space="preserve">709.896667480469</t>
   </si>
   <si>
     <t xml:space="preserve">704.165222167969</t>
   </si>
   <si>
-    <t xml:space="preserve">709.204833984375</t>
+    <t xml:space="preserve">709.204956054688</t>
   </si>
   <si>
     <t xml:space="preserve">708.710815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">689.738037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">701.991333007812</t>
+    <t xml:space="preserve">689.737976074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">701.991271972656</t>
   </si>
   <si>
     <t xml:space="preserve">702.090087890625</t>
   </si>
   <si>
-    <t xml:space="preserve">706.141479492188</t>
+    <t xml:space="preserve">706.141540527344</t>
   </si>
   <si>
     <t xml:space="preserve">695.469360351562</t>
   </si>
   <si>
-    <t xml:space="preserve">694.283630371094</t>
+    <t xml:space="preserve">694.283569335938</t>
   </si>
   <si>
     <t xml:space="preserve">677.188354492188</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">676.694274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">685.390014648438</t>
+    <t xml:space="preserve">685.39013671875</t>
   </si>
   <si>
     <t xml:space="preserve">678.077697753906</t>
@@ -4352,13 +4352,13 @@
     <t xml:space="preserve">667.603149414062</t>
   </si>
   <si>
-    <t xml:space="preserve">680.745788574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">674.619079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">711.576477050781</t>
+    <t xml:space="preserve">680.745727539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">674.619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.576416015625</t>
   </si>
   <si>
     <t xml:space="preserve">674.520263671875</t>
@@ -4376,19 +4376,19 @@
     <t xml:space="preserve">690.13330078125</t>
   </si>
   <si>
-    <t xml:space="preserve">690.528564453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">710.32861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.576721191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">701.517639160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">712.407653808594</t>
+    <t xml:space="preserve">690.528503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">710.328674316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.57666015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">701.517578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">712.407592773438</t>
   </si>
   <si>
     <t xml:space="preserve">732.603820800781</t>
@@ -4397,40 +4397,40 @@
     <t xml:space="preserve">729.336791992188</t>
   </si>
   <si>
-    <t xml:space="preserve">744.186889648438</t>
+    <t xml:space="preserve">744.186828613281</t>
   </si>
   <si>
     <t xml:space="preserve">737.2568359375</t>
   </si>
   <si>
-    <t xml:space="preserve">739.434814453125</t>
+    <t xml:space="preserve">739.434936523438</t>
   </si>
   <si>
     <t xml:space="preserve">733.593811035156</t>
   </si>
   <si>
-    <t xml:space="preserve">744.087829589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">744.681823730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">746.661865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.640808105469</t>
+    <t xml:space="preserve">744.087768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">744.681884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">746.661926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.640930175781</t>
   </si>
   <si>
     <t xml:space="preserve">754.185852050781</t>
   </si>
   <si>
-    <t xml:space="preserve">757.75</t>
+    <t xml:space="preserve">757.749938964844</t>
   </si>
   <si>
     <t xml:space="preserve">762.204956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">778.242980957031</t>
+    <t xml:space="preserve">778.242919921875</t>
   </si>
   <si>
     <t xml:space="preserve">791.410095214844</t>
@@ -4442,16 +4442,16 @@
     <t xml:space="preserve">787.549072265625</t>
   </si>
   <si>
-    <t xml:space="preserve">807.250183105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">815.76416015625</t>
+    <t xml:space="preserve">807.250244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">815.764282226562</t>
   </si>
   <si>
     <t xml:space="preserve">815.962280273438</t>
   </si>
   <si>
-    <t xml:space="preserve">825.565307617188</t>
+    <t xml:space="preserve">825.565246582031</t>
   </si>
   <si>
     <t xml:space="preserve">823.288269042969</t>
@@ -4460,19 +4460,19 @@
     <t xml:space="preserve">833.386291503906</t>
   </si>
   <si>
-    <t xml:space="preserve">819.427185058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">828.337341308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">838.732421875</t>
+    <t xml:space="preserve">819.42724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">828.337280273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.732299804688</t>
   </si>
   <si>
     <t xml:space="preserve">835.267333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">833.980346679688</t>
+    <t xml:space="preserve">833.980407714844</t>
   </si>
   <si>
     <t xml:space="preserve">843.385375976562</t>
@@ -4490,70 +4490,70 @@
     <t xml:space="preserve">825.664306640625</t>
   </si>
   <si>
-    <t xml:space="preserve">834.970336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">839.722412109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">847.543334960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">861.403381347656</t>
+    <t xml:space="preserve">834.970397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">839.722290039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">847.543273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">861.403442382812</t>
   </si>
   <si>
     <t xml:space="preserve">845.563354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">859.720458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.9775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.482543945312</t>
+    <t xml:space="preserve">859.720397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.977478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.482482910156</t>
   </si>
   <si>
     <t xml:space="preserve">830.020263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">773.391967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">783.192993164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">784.282043457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">807.646118164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">782.401000976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760.224975585938</t>
+    <t xml:space="preserve">773.392028808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">783.193054199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">784.282104492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">807.646240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">782.401062011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760.224914550781</t>
   </si>
   <si>
     <t xml:space="preserve">743.790771484375</t>
   </si>
   <si>
-    <t xml:space="preserve">737.751892089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">726.465698242188</t>
+    <t xml:space="preserve">737.751831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">726.465759277344</t>
   </si>
   <si>
     <t xml:space="preserve">735.078796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">761.016906738281</t>
+    <t xml:space="preserve">761.016967773438</t>
   </si>
   <si>
     <t xml:space="preserve">720.030700683594</t>
   </si>
   <si>
-    <t xml:space="preserve">699.042602539062</t>
+    <t xml:space="preserve">699.042663574219</t>
   </si>
   <si>
     <t xml:space="preserve">720.327697753906</t>
@@ -4562,67 +4562,67 @@
     <t xml:space="preserve">702.8046875</t>
   </si>
   <si>
-    <t xml:space="preserve">755.967834472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812.794189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">806.359191894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">817.744323730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">838.138244628906</t>
+    <t xml:space="preserve">755.967895507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812.794250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">806.359130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">817.744262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.138305664062</t>
   </si>
   <si>
     <t xml:space="preserve">836.353576660156</t>
   </si>
   <si>
-    <t xml:space="preserve">824.752685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">846.169738769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">841.807006835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">855.886657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">840.220581054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">845.37646484375</t>
+    <t xml:space="preserve">824.752624511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">846.169677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">841.806884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">855.886779785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">840.220520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">845.376525878906</t>
   </si>
   <si>
     <t xml:space="preserve">851.028198242188</t>
   </si>
   <si>
-    <t xml:space="preserve">845.674011230469</t>
+    <t xml:space="preserve">845.673950195312</t>
   </si>
   <si>
     <t xml:space="preserve">850.631591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">846.7646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">858.563842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">867.586669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">852.218017578125</t>
+    <t xml:space="preserve">846.764587402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">858.563781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">867.586730957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">852.217956542969</t>
   </si>
   <si>
     <t xml:space="preserve">812.160278320312</t>
   </si>
   <si>
-    <t xml:space="preserve">806.012817382812</t>
+    <t xml:space="preserve">806.012878417969</t>
   </si>
   <si>
     <t xml:space="preserve">807.995910644531</t>
@@ -4631,10 +4631,10 @@
     <t xml:space="preserve">812.656066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">812.953491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">831.197631835938</t>
+    <t xml:space="preserve">812.95361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">831.197570800781</t>
   </si>
   <si>
     <t xml:space="preserve">835.064636230469</t>
@@ -4646,37 +4646,37 @@
     <t xml:space="preserve">812.556945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">808.987426757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">805.51708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">825.545959472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816.919677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819.695922851562</t>
+    <t xml:space="preserve">808.987487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">805.517150878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">825.5458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816.919738769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.695861816406</t>
   </si>
   <si>
     <t xml:space="preserve">821.579772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">813.845886230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">779.7373046875</t>
+    <t xml:space="preserve">813.845825195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">779.737365722656</t>
   </si>
   <si>
     <t xml:space="preserve">779.935668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">793.519592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">800.063659667969</t>
+    <t xml:space="preserve">793.519653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800.063720703125</t>
   </si>
   <si>
     <t xml:space="preserve">798.675476074219</t>
@@ -4685,49 +4685,49 @@
     <t xml:space="preserve">794.709411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">816.324768066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">826.636657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">829.313781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">836.948486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">829.809509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">832.982360839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">841.410339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">838.435729980469</t>
+    <t xml:space="preserve">816.324645996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">826.636596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">829.313720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">836.948547363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">829.809448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">832.982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">841.410400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.435791015625</t>
   </si>
   <si>
     <t xml:space="preserve">830.0078125</t>
   </si>
   <si>
-    <t xml:space="preserve">833.279907226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">823.662048339844</t>
+    <t xml:space="preserve">833.27978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">823.661987304688</t>
   </si>
   <si>
     <t xml:space="preserve">819.200134277344</t>
   </si>
   <si>
-    <t xml:space="preserve">822.868835449219</t>
+    <t xml:space="preserve">822.868774414062</t>
   </si>
   <si>
     <t xml:space="preserve">819.894287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">827.132385253906</t>
+    <t xml:space="preserve">827.13232421875</t>
   </si>
   <si>
     <t xml:space="preserve">761.790710449219</t>
@@ -4739,16 +4739,16 @@
     <t xml:space="preserve">754.651733398438</t>
   </si>
   <si>
-    <t xml:space="preserve">737.00244140625</t>
+    <t xml:space="preserve">737.002502441406</t>
   </si>
   <si>
     <t xml:space="preserve">726.492309570312</t>
   </si>
   <si>
-    <t xml:space="preserve">716.9736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">725.401611328125</t>
+    <t xml:space="preserve">716.973571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">725.401550292969</t>
   </si>
   <si>
     <t xml:space="preserve">766.550048828125</t>
@@ -4766,37 +4766,37 @@
     <t xml:space="preserve">750.090698242188</t>
   </si>
   <si>
-    <t xml:space="preserve">713.24169921875</t>
+    <t xml:space="preserve">713.241638183594</t>
   </si>
   <si>
     <t xml:space="preserve">680.464904785156</t>
   </si>
   <si>
-    <t xml:space="preserve">679.670349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">703.706665039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.295837402344</t>
+    <t xml:space="preserve">679.670288085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">703.706604003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.295715332031</t>
   </si>
   <si>
     <t xml:space="preserve">715.228088378906</t>
   </si>
   <si>
-    <t xml:space="preserve">760.916870117188</t>
+    <t xml:space="preserve">760.916931152344</t>
   </si>
   <si>
     <t xml:space="preserve">744.429260253906</t>
   </si>
   <si>
-    <t xml:space="preserve">749.89208984375</t>
+    <t xml:space="preserve">749.892028808594</t>
   </si>
   <si>
     <t xml:space="preserve">756.447387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">766.777038574219</t>
+    <t xml:space="preserve">766.776977539062</t>
   </si>
   <si>
     <t xml:space="preserve">790.416015625</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">774.623596191406</t>
   </si>
   <si>
-    <t xml:space="preserve">788.429504394531</t>
+    <t xml:space="preserve">788.429565429688</t>
   </si>
   <si>
     <t xml:space="preserve">760.519653320312</t>
@@ -4817,19 +4817,19 @@
     <t xml:space="preserve">748.104248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">747.408935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">740.952880859375</t>
+    <t xml:space="preserve">747.408996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">740.952941894531</t>
   </si>
   <si>
     <t xml:space="preserve">744.329956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">744.925842285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">735.788146972656</t>
+    <t xml:space="preserve">744.925903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">735.7880859375</t>
   </si>
   <si>
     <t xml:space="preserve">725.756469726562</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">738.569152832031</t>
   </si>
   <si>
-    <t xml:space="preserve">759.327758789062</t>
+    <t xml:space="preserve">759.327819824219</t>
   </si>
   <si>
     <t xml:space="preserve">753.070373535156</t>
@@ -4856,13 +4856,13 @@
     <t xml:space="preserve">739.860412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">740.158325195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.731872558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.433776855469</t>
+    <t xml:space="preserve">740.158386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.731811523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.433837890625</t>
   </si>
   <si>
     <t xml:space="preserve">765.386474609375</t>
@@ -4874,7 +4874,7 @@
     <t xml:space="preserve">718.505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">720.1943359375</t>
+    <t xml:space="preserve">720.194274902344</t>
   </si>
   <si>
     <t xml:space="preserve">734.993530273438</t>
@@ -4886,7 +4886,7 @@
     <t xml:space="preserve">693.674987792969</t>
   </si>
   <si>
-    <t xml:space="preserve">697.548583984375</t>
+    <t xml:space="preserve">697.548522949219</t>
   </si>
   <si>
     <t xml:space="preserve">724.663879394531</t>
@@ -4907,22 +4907,22 @@
     <t xml:space="preserve">768.068237304688</t>
   </si>
   <si>
-    <t xml:space="preserve">771.445190429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">784.555969238281</t>
+    <t xml:space="preserve">771.445251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">784.555908203125</t>
   </si>
   <si>
     <t xml:space="preserve">785.052551269531</t>
   </si>
   <si>
-    <t xml:space="preserve">775.914794921875</t>
+    <t xml:space="preserve">775.914855957031</t>
   </si>
   <si>
     <t xml:space="preserve">796.1767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">842.759460449219</t>
+    <t xml:space="preserve">842.759399414062</t>
   </si>
   <si>
     <t xml:space="preserve">843.752685546875</t>
@@ -4931,13 +4931,13 @@
     <t xml:space="preserve">834.813598632812</t>
   </si>
   <si>
-    <t xml:space="preserve">833.025756835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">831.734558105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">834.316955566406</t>
+    <t xml:space="preserve">833.025817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">831.734619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">834.317016601562</t>
   </si>
   <si>
     <t xml:space="preserve">816.108276367188</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">849.839111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">836.903930664062</t>
+    <t xml:space="preserve">836.903991699219</t>
   </si>
   <si>
     <t xml:space="preserve">852.426208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">863.96826171875</t>
+    <t xml:space="preserve">863.968322753906</t>
   </si>
   <si>
     <t xml:space="preserve">882.276489257812</t>
@@ -4982,13 +4982,13 @@
     <t xml:space="preserve">846.456115722656</t>
   </si>
   <si>
-    <t xml:space="preserve">849.043151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">797.700561523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">774.914733886719</t>
+    <t xml:space="preserve">849.043090820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">797.700500488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">774.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">745.064392089844</t>
@@ -5000,10 +5000,10 @@
     <t xml:space="preserve">734.517333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">740.785949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">749.143981933594</t>
+    <t xml:space="preserve">740.785888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">749.14404296875</t>
   </si>
   <si>
     <t xml:space="preserve">743.969909667969</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">774.21826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">787.053955078125</t>
+    <t xml:space="preserve">787.053894042969</t>
   </si>
   <si>
     <t xml:space="preserve">770.63623046875</t>
@@ -5036,13 +5036,13 @@
     <t xml:space="preserve">753.322998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">742.178894042969</t>
+    <t xml:space="preserve">742.178955078125</t>
   </si>
   <si>
     <t xml:space="preserve">718.497619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">679.891235351562</t>
+    <t xml:space="preserve">679.891174316406</t>
   </si>
   <si>
     <t xml:space="preserve">650.836853027344</t>
@@ -5054,7 +5054,7 @@
     <t xml:space="preserve">625.961608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">631.633117675781</t>
+    <t xml:space="preserve">631.633178710938</t>
   </si>
   <si>
     <t xml:space="preserve">630.837158203125</t>
@@ -5063,7 +5063,7 @@
     <t xml:space="preserve">655.612976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">669.443603515625</t>
+    <t xml:space="preserve">669.443542480469</t>
   </si>
   <si>
     <t xml:space="preserve">654.418884277344</t>
@@ -5075,7 +5075,7 @@
     <t xml:space="preserve">711.134582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">720.089660644531</t>
+    <t xml:space="preserve">720.089721679688</t>
   </si>
   <si>
     <t xml:space="preserve">743.074401855469</t>
@@ -5084,7 +5084,7 @@
     <t xml:space="preserve">758.397583007812</t>
   </si>
   <si>
-    <t xml:space="preserve">760.188598632812</t>
+    <t xml:space="preserve">760.188659667969</t>
   </si>
   <si>
     <t xml:space="preserve">774.516784667969</t>
@@ -5093,10 +5093,10 @@
     <t xml:space="preserve">784.765441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">721.184143066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">718.796142578125</t>
+    <t xml:space="preserve">721.184204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">718.796203613281</t>
   </si>
   <si>
     <t xml:space="preserve">697.204406738281</t>
@@ -5105,16 +5105,16 @@
     <t xml:space="preserve">680.289245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">657.901489257812</t>
+    <t xml:space="preserve">657.901428222656</t>
   </si>
   <si>
     <t xml:space="preserve">665.563110351562</t>
   </si>
   <si>
-    <t xml:space="preserve">672.528137207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">668.747009277344</t>
+    <t xml:space="preserve">672.528198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">668.7470703125</t>
   </si>
   <si>
     <t xml:space="preserve">643.274780273438</t>
@@ -5415,6 +5415,9 @@
   </si>
   <si>
     <t xml:space="preserve">728.200012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">716.599975585938</t>
   </si>
 </sst>
 </file>
@@ -70415,7 +70418,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45940.6497685185</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>2721</v>
@@ -70436,6 +70439,32 @@
         <v>1800</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45943.6499074074</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>3963</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>724.799987792969</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>712.700012207031</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>719.799987792969</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>716.599975585938</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1801</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="1802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="1803">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3028678894043</t>
+    <t xml:space="preserve">38.3028831481934</t>
   </si>
   <si>
     <t xml:space="preserve">LLY.DE</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.680061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1175079345703</t>
+    <t xml:space="preserve">38.7578239440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.680046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1175117492676</t>
   </si>
   <si>
     <t xml:space="preserve">62.5549468994141</t>
@@ -59,64 +59,64 @@
     <t xml:space="preserve">63.4298400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">62.9923896789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.2426300048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8051528930664</t>
+    <t xml:space="preserve">62.9924049377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.2425956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8051681518555</t>
   </si>
   <si>
     <t xml:space="preserve">60.3677177429199</t>
   </si>
   <si>
-    <t xml:space="preserve">59.9302749633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0229988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5943031311035</t>
+    <t xml:space="preserve">59.9302711486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.023006439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5942993164062</t>
   </si>
   <si>
     <t xml:space="preserve">58.1717147827148</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8681335449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7071495056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5907897949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3598136901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.015983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.221263885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8040046691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3226623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4815979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.278507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4021339416504</t>
+    <t xml:space="preserve">56.8681526184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7071418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5907936096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3309478759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3598098754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0159797668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2212562561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8040008544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3226547241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4815864562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2785110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4021186828613</t>
   </si>
   <si>
     <t xml:space="preserve">57.0290069580078</t>
@@ -125,58 +125,58 @@
     <t xml:space="preserve">57.532283782959</t>
   </si>
   <si>
-    <t xml:space="preserve">56.596378326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4662017822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2719650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5721588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1218795776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9276161193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9717636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.640510559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2167091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5787086486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.075439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8082733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0312881469727</t>
+    <t xml:space="preserve">56.5963554382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4662170410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2719612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5721626281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1218566894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.927619934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.971752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6405181884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2167129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5787124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0754280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.808277130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0312957763672</t>
   </si>
   <si>
     <t xml:space="preserve">56.4286041259766</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2961807250977</t>
+    <t xml:space="preserve">56.2961692810059</t>
   </si>
   <si>
     <t xml:space="preserve">55.8900184631348</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4861488342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2323837280273</t>
+    <t xml:space="preserve">54.4861526489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2323684692383</t>
   </si>
   <si>
     <t xml:space="preserve">53.9034042358398</t>
@@ -185,328 +185,328 @@
     <t xml:space="preserve">55.113037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">55.369083404541</t>
+    <t xml:space="preserve">55.3690757751465</t>
   </si>
   <si>
     <t xml:space="preserve">55.6251449584961</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9230651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8811874389648</t>
+    <t xml:space="preserve">56.9230575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8811950683594</t>
   </si>
   <si>
     <t xml:space="preserve">55.5191841125488</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7641258239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1019248962402</t>
+    <t xml:space="preserve">56.7641334533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1019287109375</t>
   </si>
   <si>
     <t xml:space="preserve">56.6935005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">57.505802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.161449432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9936904907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5433959960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9495506286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4793128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9119415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5829811096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9162101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.366527557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1899223327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3622436523438</t>
+    <t xml:space="preserve">57.5057907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1614570617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9936943054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.543399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9495429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4793090820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9119453430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5829887390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9162178039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3665084838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1899185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3622589111328</t>
   </si>
   <si>
     <t xml:space="preserve">57.6558990478516</t>
   </si>
   <si>
-    <t xml:space="preserve">57.6294021606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6271324157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7330856323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5166130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0552253723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5231628417969</t>
+    <t xml:space="preserve">57.6294059753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6271209716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7330780029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5166015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0552101135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5231704711914</t>
   </si>
   <si>
     <t xml:space="preserve">61.4453010559082</t>
   </si>
   <si>
-    <t xml:space="preserve">61.7212181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8872833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5134315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2433547973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2077407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3946723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9376258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.409423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.157096862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5696334838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6586303710938</t>
+    <t xml:space="preserve">61.7212257385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2997894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8872871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5134353637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.243350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2077255249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3946647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9375991821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4094009399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1571044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5696105957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6586151123047</t>
   </si>
   <si>
     <t xml:space="preserve">65.2105102539062</t>
   </si>
   <si>
-    <t xml:space="preserve">65.254997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.797981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1006393432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6911849975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4967498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.728157043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8335876464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9582061767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1615447998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3039779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5220642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3320693969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2608642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8202514648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2564086914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5189971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7860260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3988189697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3557281494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.121208190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1657409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1567993164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6018905639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3971557617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5960540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1448669433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6194076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.52734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.622200012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.515380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9306564331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.696174621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2124633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8355178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4733734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.9362487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.5623931884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7137145996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8352279663086</t>
+    <t xml:space="preserve">65.2550277709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1006469726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6911926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4967346191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7281799316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8335952758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9581985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1615524291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3039703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5220489501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3320770263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2608489990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8202438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2564010620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5190048217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7860412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3988265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3556976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1212310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1657257080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1568145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6018753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3971405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5960388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1448516845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6193923950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.5273361206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.622184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5153884887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9306716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6961669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2124481201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4733657836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.9362335205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5623779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.7136993408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8352584838867</t>
   </si>
   <si>
     <t xml:space="preserve">79.8441467285156</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8048248291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4318542480469</t>
+    <t xml:space="preserve">80.8048553466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4318389892578</t>
   </si>
   <si>
     <t xml:space="preserve">81.9513778686523</t>
   </si>
   <si>
-    <t xml:space="preserve">82.5694580078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7844314575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4587249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3691635131836</t>
+    <t xml:space="preserve">82.5694351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.784423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4587478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3691482543945</t>
   </si>
   <si>
     <t xml:space="preserve">80.9033737182617</t>
   </si>
   <si>
-    <t xml:space="preserve">80.6883926391602</t>
+    <t xml:space="preserve">80.6883850097656</t>
   </si>
   <si>
     <t xml:space="preserve">80.634635925293</t>
   </si>
   <si>
-    <t xml:space="preserve">80.5809097290039</t>
+    <t xml:space="preserve">80.5808868408203</t>
   </si>
   <si>
     <t xml:space="preserve">80.9839935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8496398925781</t>
+    <t xml:space="preserve">80.8496170043945</t>
   </si>
   <si>
     <t xml:space="preserve">81.2168731689453</t>
   </si>
   <si>
-    <t xml:space="preserve">81.0914840698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2527084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2853012084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3211059570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4888229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.86181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7812042236328</t>
+    <t xml:space="preserve">81.0914764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2527008056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2852935791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3211288452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4888153076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8617935180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7811965942383</t>
   </si>
   <si>
     <t xml:space="preserve">81.3960342407227</t>
   </si>
   <si>
-    <t xml:space="preserve">81.6110153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9782638549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3569717407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.181037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6077728271484</t>
+    <t xml:space="preserve">81.6109771728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9782485961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3569564819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1810531616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6077575683594</t>
   </si>
   <si>
     <t xml:space="preserve">81.0735473632812</t>
@@ -515,22 +515,22 @@
     <t xml:space="preserve">82.2380218505859</t>
   </si>
   <si>
-    <t xml:space="preserve">83.115852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2949752807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2810363769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2248077392578</t>
+    <t xml:space="preserve">83.1158294677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2949905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2810668945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2248001098633</t>
   </si>
   <si>
     <t xml:space="preserve">90.5057144165039</t>
   </si>
   <si>
-    <t xml:space="preserve">89.7980728149414</t>
+    <t xml:space="preserve">89.7980804443359</t>
   </si>
   <si>
     <t xml:space="preserve">89.1531524658203</t>
@@ -545,145 +545,145 @@
     <t xml:space="preserve">85.8478622436523</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3014755249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8958892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3200836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9976196289062</t>
+    <t xml:space="preserve">85.3014450073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8958740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3201065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9976272583008</t>
   </si>
   <si>
     <t xml:space="preserve">87.7378768920898</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3552169799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7435913085938</t>
+    <t xml:space="preserve">85.3551864624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7435989379883</t>
   </si>
   <si>
     <t xml:space="preserve">85.1402282714844</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2681045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2029113769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0660781860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8177642822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6980895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.128776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.4472885131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9725341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2061767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7289199829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.2369918823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3591613769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9741744995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7128982543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5325622558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5685348510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9740600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3705215454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1992111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8839721679688</t>
+    <t xml:space="preserve">83.2681274414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2029266357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0660629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.817741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6980819702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1287689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.4472579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.972541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2061462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7289123535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.2369766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3591842651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9741592407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7129135131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5325698852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5684967041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9740829467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3705139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1991882324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8839874267578</t>
   </si>
   <si>
     <t xml:space="preserve">90.4063720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2171249389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7665328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8475112915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0456848144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1541519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6046447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3885345458984</t>
+    <t xml:space="preserve">91.2171173095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7665252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8475036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0456924438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1541442871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6046524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3885269165039</t>
   </si>
   <si>
     <t xml:space="preserve">91.3161926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">89.7487640380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8930740356445</t>
+    <t xml:space="preserve">89.7487716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8930816650391</t>
   </si>
   <si>
     <t xml:space="preserve">84.8933639526367</t>
   </si>
   <si>
-    <t xml:space="preserve">86.8931579589844</t>
+    <t xml:space="preserve">86.8931732177734</t>
   </si>
   <si>
     <t xml:space="preserve">86.0644149780273</t>
   </si>
   <si>
-    <t xml:space="preserve">85.2627868652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7760543823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5056457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3252868652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0191040039062</t>
+    <t xml:space="preserve">85.2627639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7760696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5056381225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3252944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0190963745117</t>
   </si>
   <si>
     <t xml:space="preserve">89.1812591552734</t>
@@ -692,58 +692,58 @@
     <t xml:space="preserve">90.6315689086914</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6135559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4513168334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8747863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.667610168457</t>
+    <t xml:space="preserve">90.6135635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4513320922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8747787475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6676177978516</t>
   </si>
   <si>
     <t xml:space="preserve">89.9919815063477</t>
   </si>
   <si>
-    <t xml:space="preserve">89.7217483520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3521270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3700790405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6675186157227</t>
+    <t xml:space="preserve">89.7217330932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3521575927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3700561523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6675338745117</t>
   </si>
   <si>
     <t xml:space="preserve">92.5863571166992</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4242172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0998229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6674423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6586074829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.0820541381836</t>
+    <t xml:space="preserve">92.424201965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0998306274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6674270629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6585922241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0820846557617</t>
   </si>
   <si>
     <t xml:space="preserve">91.7666168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5052032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4150161743164</t>
+    <t xml:space="preserve">93.5051803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4150238037109</t>
   </si>
   <si>
     <t xml:space="preserve">93.7394027709961</t>
@@ -752,49 +752,49 @@
     <t xml:space="preserve">95.685173034668</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0997543334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4961929321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6043701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9646072387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3970260620117</t>
+    <t xml:space="preserve">94.099739074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4962005615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6043930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9646148681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3970031738281</t>
   </si>
   <si>
     <t xml:space="preserve">94.1717987060547</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3154602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6569519042969</t>
+    <t xml:space="preserve">96.3154678344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6569671630859</t>
   </si>
   <si>
     <t xml:space="preserve">99.0890808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6750793457031</t>
+    <t xml:space="preserve">97.6750717163086</t>
   </si>
   <si>
     <t xml:space="preserve">97.7385330200195</t>
   </si>
   <si>
-    <t xml:space="preserve">98.237060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0437622070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2522659301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3247680664062</t>
+    <t xml:space="preserve">98.2370758056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0437698364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2522430419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3247604370117</t>
   </si>
   <si>
     <t xml:space="preserve">99.6963882446289</t>
@@ -803,130 +803,130 @@
     <t xml:space="preserve">100.52123260498</t>
   </si>
   <si>
-    <t xml:space="preserve">101.518295288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.47590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.189033508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.318878173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.234336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.457763671875</t>
+    <t xml:space="preserve">101.518287658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.475898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.189025878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.318855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.234367370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.457786560059</t>
   </si>
   <si>
     <t xml:space="preserve">98.9078063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">99.4970092773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1615982055664</t>
+    <t xml:space="preserve">99.4969863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1616058349609</t>
   </si>
   <si>
     <t xml:space="preserve">99.5966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">100.865676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.034934997559</t>
+    <t xml:space="preserve">100.865669250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.034927368164</t>
   </si>
   <si>
     <t xml:space="preserve">102.524398803711</t>
   </si>
   <si>
-    <t xml:space="preserve">102.823509216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.101554870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.588081359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.446014404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.862945556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.300979614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.270843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.352409362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.494277954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.346046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.207153320312</t>
+    <t xml:space="preserve">102.823486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.101547241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.588088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.445991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.862937927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.300956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.27082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.352424621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.494247436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.346038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.207138061523</t>
   </si>
   <si>
     <t xml:space="preserve">101.880836486816</t>
   </si>
   <si>
-    <t xml:space="preserve">102.787261962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.068016052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0165710449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8862915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4722671508789</t>
+    <t xml:space="preserve">102.787254333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.068008422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0165786743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8862838745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4722747802734</t>
   </si>
   <si>
     <t xml:space="preserve">94.7020645141602</t>
   </si>
   <si>
-    <t xml:space="preserve">95.7716064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9347763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7868118286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0587310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5751419067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9739685058594</t>
+    <t xml:space="preserve">95.7716293334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9347686767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7867965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0587387084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5751647949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9739837646484</t>
   </si>
   <si>
     <t xml:space="preserve">93.904411315918</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7775039672852</t>
+    <t xml:space="preserve">93.7775344848633</t>
   </si>
   <si>
     <t xml:space="preserve">94.0494384765625</t>
   </si>
   <si>
-    <t xml:space="preserve">93.0342483520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3816528320312</t>
+    <t xml:space="preserve">93.0342636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3816604614258</t>
   </si>
   <si>
     <t xml:space="preserve">92.4360275268555</t>
@@ -935,61 +935,61 @@
     <t xml:space="preserve">93.1430282592773</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3061828613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7552719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6242141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.882942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4816055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.390380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.0802612304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.135009765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4086456298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2228469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9376678466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9890518188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5728073120117</t>
+    <t xml:space="preserve">93.3061676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7552642822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6242065429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8829345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4815979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3903884887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0802764892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.1350021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4086303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2228698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9376754760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9890441894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5728149414062</t>
   </si>
   <si>
     <t xml:space="preserve">91.6324157714844</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5627746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0918273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5834808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2128677368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7999572753906</t>
+    <t xml:space="preserve">92.5627975463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0918121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5834579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2128448486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7999420166016</t>
   </si>
   <si>
     <t xml:space="preserve">93.4201889038086</t>
@@ -998,10 +998,10 @@
     <t xml:space="preserve">93.4931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9093933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6357650756836</t>
+    <t xml:space="preserve">92.9094009399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6357727050781</t>
   </si>
   <si>
     <t xml:space="preserve">93.3107528686523</t>
@@ -1010,55 +1010,55 @@
     <t xml:space="preserve">89.2608871459961</t>
   </si>
   <si>
-    <t xml:space="preserve">89.8720092773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3098297119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3405532836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2709121704102</t>
+    <t xml:space="preserve">89.8720169067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3098526000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3405303955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2709274291992</t>
   </si>
   <si>
     <t xml:space="preserve">92.3621292114258</t>
   </si>
   <si>
-    <t xml:space="preserve">90.7567672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1249847412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3885879516602</t>
+    <t xml:space="preserve">90.7567825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1249694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3885955810547</t>
   </si>
   <si>
     <t xml:space="preserve">86.6521911621094</t>
   </si>
   <si>
-    <t xml:space="preserve">87.5643157958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4764556884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.020393371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5004653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3818969726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.5244827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9349365234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9474334716797</t>
+    <t xml:space="preserve">87.5643310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4764404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0203857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.50048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3818817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.5245208740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9349899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9474182128906</t>
   </si>
   <si>
     <t xml:space="preserve">89.3064956665039</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">89.3703384399414</t>
   </si>
   <si>
-    <t xml:space="preserve">88.9507446289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2243881225586</t>
+    <t xml:space="preserve">88.9507369995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2243957519531</t>
   </si>
   <si>
     <t xml:space="preserve">90.1182861328125</t>
@@ -1079,55 +1079,55 @@
     <t xml:space="preserve">90.7750244140625</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3040390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9176177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.546989440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4980316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7452087402344</t>
+    <t xml:space="preserve">91.3040466308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9176254272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5469665527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.498046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7452163696289</t>
   </si>
   <si>
     <t xml:space="preserve">91.7418746948242</t>
   </si>
   <si>
-    <t xml:space="preserve">91.4317474365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0702590942383</t>
+    <t xml:space="preserve">91.4317321777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0702362060547</t>
   </si>
   <si>
     <t xml:space="preserve">92.4236679077148</t>
   </si>
   <si>
-    <t xml:space="preserve">90.440788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7804565429688</t>
+    <t xml:space="preserve">90.440803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7804412841797</t>
   </si>
   <si>
     <t xml:space="preserve">92.7908782958984</t>
   </si>
   <si>
-    <t xml:space="preserve">93.0479125976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.074821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4230422973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.9095916748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7541656494141</t>
+    <t xml:space="preserve">93.0479202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.074836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4230499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9095993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7541580200195</t>
   </si>
   <si>
     <t xml:space="preserve">93.8190078735352</t>
@@ -1136,73 +1136,73 @@
     <t xml:space="preserve">94.6085052490234</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8104400634766</t>
+    <t xml:space="preserve">94.8104476928711</t>
   </si>
   <si>
     <t xml:space="preserve">95.2878036499023</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0197296142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7712554931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6990661621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9193801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0381088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6801071166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7443389892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9928131103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9389801025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7015228271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4065246582031</t>
+    <t xml:space="preserve">92.0197448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7712936401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6990737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9193954467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0381011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6800994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7443542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9927978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9389877319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7015075683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4065399169922</t>
   </si>
   <si>
     <t xml:space="preserve">94.6635665893555</t>
   </si>
   <si>
-    <t xml:space="preserve">93.433464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9940490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4714202880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6354217529297</t>
+    <t xml:space="preserve">93.4334564208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9940567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4713973999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6354370117188</t>
   </si>
   <si>
     <t xml:space="preserve">89.9634399414062</t>
   </si>
   <si>
-    <t xml:space="preserve">89.5044250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4224395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8814468383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3404312133789</t>
+    <t xml:space="preserve">89.5044479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4224472045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8814315795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3404235839844</t>
   </si>
   <si>
     <t xml:space="preserve">87.7969741821289</t>
@@ -1211,82 +1211,82 @@
     <t xml:space="preserve">88.5589218139648</t>
   </si>
   <si>
-    <t xml:space="preserve">89.8165512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2033462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6886596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1397094726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7174530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0944137573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0931930541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8006591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4885482788086</t>
+    <t xml:space="preserve">89.8165664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2033538818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6886749267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1397018432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7174301147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0944061279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0932006835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4885406494141</t>
   </si>
   <si>
     <t xml:space="preserve">94.0209808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">94.1494827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4616317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4500961303711</t>
+    <t xml:space="preserve">94.1494903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4616241455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4500732421875</t>
   </si>
   <si>
     <t xml:space="preserve">94.650993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7433700561523</t>
+    <t xml:space="preserve">94.7433776855469</t>
   </si>
   <si>
     <t xml:space="preserve">95.4823837280273</t>
   </si>
   <si>
-    <t xml:space="preserve">96.0920944213867</t>
+    <t xml:space="preserve">96.0920791625977</t>
   </si>
   <si>
     <t xml:space="preserve">95.6856231689453</t>
   </si>
   <si>
-    <t xml:space="preserve">97.0158767700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5493545532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8634338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3830795288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1267318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4939498901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.600166320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.9165725708008</t>
+    <t xml:space="preserve">97.0158615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5493774414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8634490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3830642700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1267395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4939346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.600173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.9165649414062</t>
   </si>
   <si>
     <t xml:space="preserve">100.359985351562</t>
@@ -1295,37 +1295,37 @@
     <t xml:space="preserve">100.212173461914</t>
   </si>
   <si>
-    <t xml:space="preserve">100.784912109375</t>
+    <t xml:space="preserve">100.784934997559</t>
   </si>
   <si>
     <t xml:space="preserve">100.711013793945</t>
   </si>
   <si>
-    <t xml:space="preserve">101.727188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.202941894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.269882202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.008918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.429229736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.653251647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.988128662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.064323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.341484069824</t>
+    <t xml:space="preserve">101.727195739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.202934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.269889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.008911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.429244995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.653259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.988136291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.064338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.341468811035</t>
   </si>
   <si>
     <t xml:space="preserve">109.265274047852</t>
@@ -1334,97 +1334,97 @@
     <t xml:space="preserve">109.135932922363</t>
   </si>
   <si>
-    <t xml:space="preserve">109.819534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.893432617188</t>
+    <t xml:space="preserve">109.81950378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.893424987793</t>
   </si>
   <si>
     <t xml:space="preserve">112.886489868164</t>
   </si>
   <si>
-    <t xml:space="preserve">114.105903625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.26985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.454620361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.507736206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.06201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.376091003418</t>
+    <t xml:space="preserve">114.105888366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.269859313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.454612731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.507743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.062004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.376083374023</t>
   </si>
   <si>
     <t xml:space="preserve">116.710960388184</t>
   </si>
   <si>
-    <t xml:space="preserve">117.486946105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.394584655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.320655822754</t>
+    <t xml:space="preserve">117.486968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.394561767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.320678710938</t>
   </si>
   <si>
     <t xml:space="preserve">117.413032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">116.322982788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.115142822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.092018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.135925292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.339141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.611633300781</t>
+    <t xml:space="preserve">116.322967529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.115119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.09203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.135917663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.339149475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.611671447754</t>
   </si>
   <si>
     <t xml:space="preserve">122.623184204102</t>
   </si>
   <si>
-    <t xml:space="preserve">124.156677246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473091125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.274452209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.292930603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.586250305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.549087524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.248565673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.616821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.229972839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.270408630371</t>
+    <t xml:space="preserve">124.156661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473075866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.274475097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.292922973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.586227416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.549095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.248542785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.616813659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.229957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.270393371582</t>
   </si>
   <si>
     <t xml:space="preserve">121.78734588623</t>
@@ -1436,166 +1436,166 @@
     <t xml:space="preserve">117.049606323242</t>
   </si>
   <si>
-    <t xml:space="preserve">116.009162902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.017890930176</t>
+    <t xml:space="preserve">116.009170532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.017906188965</t>
   </si>
   <si>
     <t xml:space="preserve">104.620063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">108.05721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.441947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.10424041748</t>
+    <t xml:space="preserve">108.057220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.441963195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.104232788086</t>
   </si>
   <si>
     <t xml:space="preserve">116.306442260742</t>
   </si>
   <si>
-    <t xml:space="preserve">115.507530212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.881294250488</t>
+    <t xml:space="preserve">115.507514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.881278991699</t>
   </si>
   <si>
     <t xml:space="preserve">110.93701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">115.135948181152</t>
+    <t xml:space="preserve">115.135940551758</t>
   </si>
   <si>
     <t xml:space="preserve">106.70093536377</t>
   </si>
   <si>
-    <t xml:space="preserve">110.5654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.60913848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.123931884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.597145080566</t>
+    <t xml:space="preserve">110.565437316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.609146118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.12393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.597137451172</t>
   </si>
   <si>
     <t xml:space="preserve">119.056175231934</t>
   </si>
   <si>
-    <t xml:space="preserve">116.120658874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.768684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.270324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.771957397461</t>
+    <t xml:space="preserve">116.120643615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.768676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270347595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.77197265625</t>
   </si>
   <si>
     <t xml:space="preserve">110.844123840332</t>
   </si>
   <si>
-    <t xml:space="preserve">111.680183410645</t>
+    <t xml:space="preserve">111.680198669434</t>
   </si>
   <si>
     <t xml:space="preserve">117.365447998047</t>
   </si>
   <si>
-    <t xml:space="preserve">113.798240661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.694435119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.300979614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623390197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.552352905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.339225769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.661666870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.913024902344</t>
+    <t xml:space="preserve">113.798233032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.694442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.300971984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623397827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.552391052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.339248657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.661651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.9130859375</t>
   </si>
   <si>
     <t xml:space="preserve">131.44856262207</t>
   </si>
   <si>
-    <t xml:space="preserve">135.628890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.377517700195</t>
+    <t xml:space="preserve">135.628936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.377548217773</t>
   </si>
   <si>
     <t xml:space="preserve">134.235473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">138.285766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.67919921875</t>
+    <t xml:space="preserve">138.285736083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.679153442383</t>
   </si>
   <si>
     <t xml:space="preserve">140.218017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">136.557876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.232177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.117431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.367691040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.272583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.40592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.492279052734</t>
+    <t xml:space="preserve">136.557891845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.232162475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.117416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.367721557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.27262878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.405975341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.492248535156</t>
   </si>
   <si>
     <t xml:space="preserve">132.154571533203</t>
   </si>
   <si>
-    <t xml:space="preserve">135.182998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.263854980469</t>
+    <t xml:space="preserve">135.183013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.263885498047</t>
   </si>
   <si>
     <t xml:space="preserve">135.833282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">135.889282226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.347747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.5615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.050903320312</t>
+    <t xml:space="preserve">135.889312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.347763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.561508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.050918579102</t>
   </si>
   <si>
     <t xml:space="preserve">131.91178894043</t>
@@ -1607,100 +1607,100 @@
     <t xml:space="preserve">129.689605712891</t>
   </si>
   <si>
-    <t xml:space="preserve">130.399215698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.34700012207</t>
+    <t xml:space="preserve">130.399230957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.346984863281</t>
   </si>
   <si>
     <t xml:space="preserve">121.771903991699</t>
   </si>
   <si>
-    <t xml:space="preserve">127.766166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.560745239258</t>
+    <t xml:space="preserve">127.766242980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.56078338623</t>
   </si>
   <si>
     <t xml:space="preserve">126.589752197266</t>
   </si>
   <si>
-    <t xml:space="preserve">125.95484161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.180816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.002487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.873680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.143524169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.554298400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.846611022949</t>
+    <t xml:space="preserve">125.95482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.180824279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.002479553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.873672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.143516540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.554306030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.846588134766</t>
   </si>
   <si>
     <t xml:space="preserve">120.016555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">116.972732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.142364501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.077987670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.011672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.650329589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.322631835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.984603881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.45524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.621383666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.488784790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.619491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.412155151367</t>
+    <t xml:space="preserve">116.97274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.142379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.07795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.011642456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.650344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.32258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.984588623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.455230712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.621398925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.488754272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.619476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.412170410156</t>
   </si>
   <si>
     <t xml:space="preserve">136.37483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">135.441131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.484954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.055419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.148803710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.225402832031</t>
+    <t xml:space="preserve">135.441162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.484970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.055480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.148834228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.225433349609</t>
   </si>
   <si>
     <t xml:space="preserve">135.123672485352</t>
@@ -1715,82 +1715,82 @@
     <t xml:space="preserve">135.179702758789</t>
   </si>
   <si>
-    <t xml:space="preserve">133.125579833984</t>
+    <t xml:space="preserve">133.125595092773</t>
   </si>
   <si>
     <t xml:space="preserve">135.833267211914</t>
   </si>
   <si>
-    <t xml:space="preserve">135.795928955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.239486694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.355354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.448738098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.793243408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.334007263184</t>
+    <t xml:space="preserve">135.795959472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.239532470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.355369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.448745727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.793258666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.334022521973</t>
   </si>
   <si>
     <t xml:space="preserve">118.802764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">121.473129272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.85498046875</t>
+    <t xml:space="preserve">121.473136901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.854988098145</t>
   </si>
   <si>
     <t xml:space="preserve">121.15567779541</t>
   </si>
   <si>
-    <t xml:space="preserve">119.717788696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.800857543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.875556945801</t>
+    <t xml:space="preserve">119.717781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.80086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.875549316406</t>
   </si>
   <si>
     <t xml:space="preserve">119.736465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">120.221969604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.24535369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.733642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.409797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.578834533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.480369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.071746826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.174774169922</t>
+    <t xml:space="preserve">120.221984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.245330810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.733657836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.409820556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.578842163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.480354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.071731567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.174781799316</t>
   </si>
   <si>
     <t xml:space="preserve">118.062072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">119.207778930664</t>
+    <t xml:space="preserve">119.207763671875</t>
   </si>
   <si>
     <t xml:space="preserve">117.423500061035</t>
@@ -1799,112 +1799,112 @@
     <t xml:space="preserve">119.170204162598</t>
   </si>
   <si>
-    <t xml:space="preserve">117.479835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.44686126709</t>
+    <t xml:space="preserve">117.479858398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.446838378906</t>
   </si>
   <si>
     <t xml:space="preserve">116.052444458008</t>
   </si>
   <si>
-    <t xml:space="preserve">118.83211517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.301681518555</t>
+    <t xml:space="preserve">118.832130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.30167388916</t>
   </si>
   <si>
     <t xml:space="preserve">118.099647521973</t>
   </si>
   <si>
-    <t xml:space="preserve">118.625541687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.799140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.686958312988</t>
+    <t xml:space="preserve">118.625556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.799125671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.686988830566</t>
   </si>
   <si>
     <t xml:space="preserve">117.592544555664</t>
   </si>
   <si>
-    <t xml:space="preserve">117.554969787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.639739990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.710296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.729095458984</t>
+    <t xml:space="preserve">117.554977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.639709472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.710311889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.72908782959</t>
   </si>
   <si>
     <t xml:space="preserve">121.611846923828</t>
   </si>
   <si>
-    <t xml:space="preserve">120.597610473633</t>
+    <t xml:space="preserve">120.597618103027</t>
   </si>
   <si>
     <t xml:space="preserve">120.334663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">119.583419799805</t>
+    <t xml:space="preserve">119.583381652832</t>
   </si>
   <si>
     <t xml:space="preserve">120.785423278809</t>
   </si>
   <si>
-    <t xml:space="preserve">118.193572998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.709770202637</t>
+    <t xml:space="preserve">118.193550109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.70979309082</t>
   </si>
   <si>
     <t xml:space="preserve">115.977310180664</t>
   </si>
   <si>
-    <t xml:space="preserve">116.747352600098</t>
+    <t xml:space="preserve">116.747367858887</t>
   </si>
   <si>
     <t xml:space="preserve">116.108779907227</t>
   </si>
   <si>
-    <t xml:space="preserve">121.424018859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.335159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.546363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.231620788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.869689941406</t>
+    <t xml:space="preserve">121.424011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.335205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.546356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.231636047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.869682312012</t>
   </si>
   <si>
     <t xml:space="preserve">117.06664276123</t>
   </si>
   <si>
-    <t xml:space="preserve">117.34838104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.150909423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.122497558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.615386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.93921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.347846984863</t>
+    <t xml:space="preserve">117.348365783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.150924682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.122482299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.615371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.939224243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.347854614258</t>
   </si>
   <si>
     <t xml:space="preserve">111.563591003418</t>
@@ -1916,13 +1916,13 @@
     <t xml:space="preserve">105.835166931152</t>
   </si>
   <si>
-    <t xml:space="preserve">106.530090332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.666137695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.684913635254</t>
+    <t xml:space="preserve">106.530075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.666114807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.684906005859</t>
   </si>
   <si>
     <t xml:space="preserve">106.511299133301</t>
@@ -1934,52 +1934,52 @@
     <t xml:space="preserve">116.221458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">116.202705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.5732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.104202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.319938659668</t>
+    <t xml:space="preserve">116.202682495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.573249816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.104217529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.319946289062</t>
   </si>
   <si>
     <t xml:space="preserve">112.939094543457</t>
   </si>
   <si>
-    <t xml:space="preserve">113.97834777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.354804992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.221061706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.504508972168</t>
+    <t xml:space="preserve">113.978355407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.35481262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.221038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.504501342773</t>
   </si>
   <si>
     <t xml:space="preserve">112.16438293457</t>
   </si>
   <si>
-    <t xml:space="preserve">116.359199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.901298522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.338836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.449287414551</t>
+    <t xml:space="preserve">116.35920715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.901313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.338859558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.449264526367</t>
   </si>
   <si>
     <t xml:space="preserve">114.318481445312</t>
   </si>
   <si>
-    <t xml:space="preserve">115.830123901367</t>
+    <t xml:space="preserve">115.830116271973</t>
   </si>
   <si>
     <t xml:space="preserve">114.828651428223</t>
@@ -1988,37 +1988,37 @@
     <t xml:space="preserve">113.846084594727</t>
   </si>
   <si>
-    <t xml:space="preserve">112.447799682617</t>
+    <t xml:space="preserve">112.447814941406</t>
   </si>
   <si>
     <t xml:space="preserve">114.469635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">116.151344299316</t>
+    <t xml:space="preserve">116.151351928711</t>
   </si>
   <si>
     <t xml:space="preserve">122.651435852051</t>
   </si>
   <si>
-    <t xml:space="preserve">123.841873168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.353530883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.843360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.411697387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.32746887207</t>
+    <t xml:space="preserve">123.841865539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.353492736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.843330383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.411659240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.327453613281</t>
   </si>
   <si>
     <t xml:space="preserve">131.948089599609</t>
   </si>
   <si>
-    <t xml:space="preserve">131.267852783203</t>
+    <t xml:space="preserve">131.267822265625</t>
   </si>
   <si>
     <t xml:space="preserve">129.737289428711</t>
@@ -2027,103 +2027,103 @@
     <t xml:space="preserve">129.96403503418</t>
   </si>
   <si>
-    <t xml:space="preserve">129.416076660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.583206176758</t>
+    <t xml:space="preserve">129.416091918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.583160400391</t>
   </si>
   <si>
     <t xml:space="preserve">128.471282958984</t>
   </si>
   <si>
-    <t xml:space="preserve">129.113739013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.827377319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.392761230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.904441833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.016342163086</t>
+    <t xml:space="preserve">129.11376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.82738494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.392784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.904403686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.01634979248</t>
   </si>
   <si>
     <t xml:space="preserve">128.603546142578</t>
   </si>
   <si>
-    <t xml:space="preserve">145.118301391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.978744506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.645950317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.119766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.047119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.839294433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.714385986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.833618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.076324462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.760986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.032806396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.996520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.992080688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.12580871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.349716186523</t>
+    <t xml:space="preserve">145.11833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.978729248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.645935058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.119812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.047134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.839279174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.71435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.833633422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.076293945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.760940551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.032852172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.996505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.992126464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.125885009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.349655151367</t>
   </si>
   <si>
     <t xml:space="preserve">162.804626464844</t>
   </si>
   <si>
-    <t xml:space="preserve">156.720230102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.962936401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.137435913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.704254150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.461563110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.814712524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.157760620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.0087890625</t>
+    <t xml:space="preserve">156.720245361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.962982177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.137420654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.70426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.461547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.814682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.157791137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.008758544922</t>
   </si>
   <si>
     <t xml:space="preserve">160.819534301758</t>
@@ -2132,52 +2132,52 @@
     <t xml:space="preserve">164.560836791992</t>
   </si>
   <si>
-    <t xml:space="preserve">159.793991088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.161361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.832000732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.856842041016</t>
+    <t xml:space="preserve">159.794006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.161392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.831924438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.856857299805</t>
   </si>
   <si>
     <t xml:space="preserve">154.932159423828</t>
   </si>
   <si>
-    <t xml:space="preserve">159.20524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.964904785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.970779418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.907928466797</t>
+    <t xml:space="preserve">159.205261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.964935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.970809936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.907958984375</t>
   </si>
   <si>
     <t xml:space="preserve">162.376831054688</t>
   </si>
   <si>
-    <t xml:space="preserve">162.756607055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.95832824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.338150024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.617172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.884338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.409515380859</t>
+    <t xml:space="preserve">162.756637573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.958343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.338195800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.617156982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.884323120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.409576416016</t>
   </si>
   <si>
     <t xml:space="preserve">165.890243530273</t>
@@ -2186,115 +2186,115 @@
     <t xml:space="preserve">162.661682128906</t>
   </si>
   <si>
-    <t xml:space="preserve">163.326370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.741638183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.931549072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.082794189453</t>
+    <t xml:space="preserve">163.326400756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.741653442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.931518554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.082809448242</t>
   </si>
   <si>
     <t xml:space="preserve">147.183670043945</t>
   </si>
   <si>
-    <t xml:space="preserve">147.753433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.133224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.462646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.474456787109</t>
+    <t xml:space="preserve">147.753402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.133239746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.462661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.474426269531</t>
   </si>
   <si>
     <t xml:space="preserve">146.993759155273</t>
   </si>
   <si>
-    <t xml:space="preserve">148.892913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.602127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.792053222656</t>
+    <t xml:space="preserve">148.892883300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.602142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.792022705078</t>
   </si>
   <si>
     <t xml:space="preserve">151.399749755859</t>
   </si>
   <si>
-    <t xml:space="preserve">151.456741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.702987670898</t>
+    <t xml:space="preserve">151.456756591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.703018188477</t>
   </si>
   <si>
     <t xml:space="preserve">145.284530639648</t>
   </si>
   <si>
-    <t xml:space="preserve">146.234085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.854232788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.904724121094</t>
+    <t xml:space="preserve">146.234100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.854263305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.904693603516</t>
   </si>
   <si>
     <t xml:space="preserve">146.42399597168</t>
   </si>
   <si>
-    <t xml:space="preserve">148.323150634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.842468261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.412216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.652557373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.513076782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.803848266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.955139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.346755981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.486251831055</t>
+    <t xml:space="preserve">148.323104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.84245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.412185668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.652542114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.513061523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.803833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.955123901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.346771240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.486221313477</t>
   </si>
   <si>
     <t xml:space="preserve">143.575302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">146.044158935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.121490478516</t>
+    <t xml:space="preserve">146.044174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.121429443359</t>
   </si>
   <si>
     <t xml:space="preserve">152.691177368164</t>
   </si>
   <si>
-    <t xml:space="preserve">153.071029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.836547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.693557739258</t>
+    <t xml:space="preserve">153.071014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.836532592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.693542480469</t>
   </si>
   <si>
     <t xml:space="preserve">155.220932006836</t>
@@ -2303,49 +2303,49 @@
     <t xml:space="preserve">154.457229614258</t>
   </si>
   <si>
-    <t xml:space="preserve">152.929870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.979934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.175537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.702941894531</t>
+    <t xml:space="preserve">152.92985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.175567626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.702911376953</t>
   </si>
   <si>
     <t xml:space="preserve">155.984603881836</t>
   </si>
   <si>
-    <t xml:space="preserve">154.361770629883</t>
+    <t xml:space="preserve">154.361785888672</t>
   </si>
   <si>
     <t xml:space="preserve">156.748306274414</t>
   </si>
   <si>
-    <t xml:space="preserve">157.225646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.839065551758</t>
+    <t xml:space="preserve">157.225662231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.839080810547</t>
   </si>
   <si>
     <t xml:space="preserve">156.366439819336</t>
   </si>
   <si>
-    <t xml:space="preserve">159.803070068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.640365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.876647949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.076950073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.000305175781</t>
+    <t xml:space="preserve">159.803100585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.640380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.876678466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.076995849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.000274658203</t>
   </si>
   <si>
     <t xml:space="preserve">176.36572265625</t>
@@ -2354,76 +2354,76 @@
     <t xml:space="preserve">177.749923706055</t>
   </si>
   <si>
-    <t xml:space="preserve">175.840713500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.222534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.227203369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.270263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.038650512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.800033569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.265548706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.243682861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.527694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.093414306641</t>
+    <t xml:space="preserve">175.84065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.222518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.227233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.270233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.038635253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.799987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.265563964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.24365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.527709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.093444824219</t>
   </si>
   <si>
     <t xml:space="preserve">184.432220458984</t>
   </si>
   <si>
-    <t xml:space="preserve">185.291397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.102798461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.7734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.491760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.918930053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.969024658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.775756835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.069183349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.6826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.446365356445</t>
+    <t xml:space="preserve">185.291381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.102828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.773422241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.491714477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.918975830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.969039916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.775741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.069198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.682647705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.446319580078</t>
   </si>
   <si>
     <t xml:space="preserve">190.828170776367</t>
   </si>
   <si>
-    <t xml:space="preserve">188.584854125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.677963256836</t>
+    <t xml:space="preserve">188.584838867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.677932739258</t>
   </si>
   <si>
     <t xml:space="preserve">187.296112060547</t>
@@ -2432,19 +2432,19 @@
     <t xml:space="preserve">191.591873168945</t>
   </si>
   <si>
-    <t xml:space="preserve">191.973709106445</t>
+    <t xml:space="preserve">191.973739624023</t>
   </si>
   <si>
     <t xml:space="preserve">193.88298034668</t>
   </si>
   <si>
-    <t xml:space="preserve">195.983139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.4150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.269515991211</t>
+    <t xml:space="preserve">195.983093261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.415069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.269561767578</t>
   </si>
   <si>
     <t xml:space="preserve">199.515197753906</t>
@@ -2453,40 +2453,40 @@
     <t xml:space="preserve">197.319580078125</t>
   </si>
   <si>
-    <t xml:space="preserve">196.842254638672</t>
+    <t xml:space="preserve">196.842300415039</t>
   </si>
   <si>
     <t xml:space="preserve">197.987808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">207.152145385742</t>
+    <t xml:space="preserve">207.152191162109</t>
   </si>
   <si>
     <t xml:space="preserve">213.739013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">212.975341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.929946899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.321151733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.703033447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.366592407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.498046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.564300537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.918045043945</t>
+    <t xml:space="preserve">212.975357055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.929962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.321182250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.703063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.366546630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.498092651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.564331054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.918014526367</t>
   </si>
   <si>
     <t xml:space="preserve">223.930191040039</t>
@@ -2495,142 +2495,142 @@
     <t xml:space="preserve">221.534729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">223.067855834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.205459594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.444076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.156631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.294250488281</t>
+    <t xml:space="preserve">223.067825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.205474853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.444061279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.156616210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.294235229492</t>
   </si>
   <si>
     <t xml:space="preserve">212.048614501953</t>
   </si>
   <si>
-    <t xml:space="preserve">214.060821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.186218261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.736694335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.982345581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.269821166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.994552612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.461456298828</t>
+    <t xml:space="preserve">214.060775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.186187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.736740112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.982406616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.269790649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.994567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.461471557617</t>
   </si>
   <si>
     <t xml:space="preserve">206.970169067383</t>
   </si>
   <si>
-    <t xml:space="preserve">198.058929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.621658325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.447402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.920364379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.495330810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.902084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.087631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.531036376953</t>
+    <t xml:space="preserve">198.058944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.621643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.447418212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.92041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.495315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.902053833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.087615966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.531005859375</t>
   </si>
   <si>
     <t xml:space="preserve">189.626815795898</t>
   </si>
   <si>
-    <t xml:space="preserve">187.997894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.632934570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.537094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.889831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.152908325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.572799682617</t>
+    <t xml:space="preserve">187.997909545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.632919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.889862060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.152893066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.572845458984</t>
   </si>
   <si>
     <t xml:space="preserve">193.651245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">189.770584106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.410766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.393341064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.237457275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.501419067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.172180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.525848388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.555435180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.938674926758</t>
+    <t xml:space="preserve">189.770553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.410797119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.393356323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.237442016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.501388549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.172119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.525833129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.555404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.938690185547</t>
   </si>
   <si>
     <t xml:space="preserve">194.992736816406</t>
   </si>
   <si>
-    <t xml:space="preserve">195.47184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.442199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.729644775391</t>
+    <t xml:space="preserve">195.471817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.44221496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.72966003418</t>
   </si>
   <si>
     <t xml:space="preserve">200.358627319336</t>
   </si>
   <si>
-    <t xml:space="preserve">198.538040161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.921295166016</t>
+    <t xml:space="preserve">198.538024902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.921310424805</t>
   </si>
   <si>
     <t xml:space="preserve">201.987533569336</t>
@@ -2639,22 +2639,22 @@
     <t xml:space="preserve">202.849899291992</t>
   </si>
   <si>
-    <t xml:space="preserve">208.2158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.83251953125</t>
+    <t xml:space="preserve">208.215835571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.832550048828</t>
   </si>
   <si>
     <t xml:space="preserve">210.802932739258</t>
   </si>
   <si>
-    <t xml:space="preserve">207.353408813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.006774902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.98942565918</t>
+    <t xml:space="preserve">207.353424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.006790161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.989410400391</t>
   </si>
   <si>
     <t xml:space="preserve">215.593887329102</t>
@@ -2663,10 +2663,10 @@
     <t xml:space="preserve">215.977172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">219.905776977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220.768157958984</t>
+    <t xml:space="preserve">219.905822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.768142700195</t>
   </si>
   <si>
     <t xml:space="preserve">218.892776489258</t>
@@ -2675,25 +2675,25 @@
     <t xml:space="preserve">217.161636352539</t>
   </si>
   <si>
-    <t xml:space="preserve">219.277481079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.297134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.200958251953</t>
+    <t xml:space="preserve">219.277450561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.297103881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.200942993164</t>
   </si>
   <si>
     <t xml:space="preserve">223.316772460938</t>
   </si>
   <si>
-    <t xml:space="preserve">224.663192749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.50910949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.182342529297</t>
+    <t xml:space="preserve">224.663238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.509140014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.182388305664</t>
   </si>
   <si>
     <t xml:space="preserve">227.067611694336</t>
@@ -2702,25 +2702,25 @@
     <t xml:space="preserve">222.162704467773</t>
   </si>
   <si>
-    <t xml:space="preserve">212.064361572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.238143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.198806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.756195068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.351852416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203.985733032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.313568115234</t>
+    <t xml:space="preserve">212.064392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.238128662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.198837280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.756240844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.351837158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203.985763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.313598632812</t>
   </si>
   <si>
     <t xml:space="preserve">207.640335083008</t>
@@ -2729,112 +2729,112 @@
     <t xml:space="preserve">213.507019042969</t>
   </si>
   <si>
-    <t xml:space="preserve">212.929977416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.279556274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">237.646759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.259918212891</t>
+    <t xml:space="preserve">212.929946899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.279586791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.646774291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.25993347168</t>
   </si>
   <si>
     <t xml:space="preserve">225.624969482422</t>
   </si>
   <si>
-    <t xml:space="preserve">224.56706237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">232.068649291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.819442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.434753417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.530944824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">228.317855834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.644622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220.527740478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.662155151367</t>
+    <t xml:space="preserve">224.567047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.068618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.819458007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.434799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.530914306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">228.317840576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.644638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.527709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.662139892578</t>
   </si>
   <si>
     <t xml:space="preserve">218.12336730957</t>
   </si>
   <si>
-    <t xml:space="preserve">219.373626708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.256759643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.197738647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.544219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.409774780273</t>
+    <t xml:space="preserve">219.373657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.256729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.197784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.544189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.409729003906</t>
   </si>
   <si>
     <t xml:space="preserve">211.102645874023</t>
   </si>
   <si>
-    <t xml:space="preserve">209.948532104492</t>
+    <t xml:space="preserve">209.948547363281</t>
   </si>
   <si>
     <t xml:space="preserve">207.159469604492</t>
   </si>
   <si>
-    <t xml:space="preserve">200.042617797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.869903564453</t>
+    <t xml:space="preserve">200.042587280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.869918823242</t>
   </si>
   <si>
     <t xml:space="preserve">205.813064575195</t>
   </si>
   <si>
-    <t xml:space="preserve">208.121215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.928863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.98681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.794448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.352920532227</t>
+    <t xml:space="preserve">208.121231079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.928894042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.986831665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.794464111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.352890014648</t>
   </si>
   <si>
     <t xml:space="preserve">206.101593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">202.639297485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.158432006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.139846801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.927810668945</t>
+    <t xml:space="preserve">202.639312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.158462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.139831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.927825927734</t>
   </si>
   <si>
     <t xml:space="preserve">200.234939575195</t>
@@ -2843,64 +2843,64 @@
     <t xml:space="preserve">198.959442138672</t>
   </si>
   <si>
-    <t xml:space="preserve">207.076324462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.525756835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.593170166016</t>
+    <t xml:space="preserve">207.076309204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.525741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.593139648438</t>
   </si>
   <si>
     <t xml:space="preserve">204.853805541992</t>
   </si>
   <si>
-    <t xml:space="preserve">200.892044067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203.404373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.916763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.626876831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">216.256042480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.130249023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.806625366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.957183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.116744995117</t>
+    <t xml:space="preserve">200.891998291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203.404388427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.916717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.626892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">216.256057739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.130233764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.95719909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.116729736328</t>
   </si>
   <si>
     <t xml:space="preserve">229.39762878418</t>
   </si>
   <si>
-    <t xml:space="preserve">231.909973144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">233.262756347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">232.393157958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.233581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">237.417846679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">236.161666870117</t>
+    <t xml:space="preserve">231.910003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">233.262802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.393127441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.233596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.417861938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">236.161682128906</t>
   </si>
   <si>
     <t xml:space="preserve">243.312240600586</t>
@@ -2915,37 +2915,37 @@
     <t xml:space="preserve">251.332443237305</t>
   </si>
   <si>
-    <t xml:space="preserve">253.651519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">249.88298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.525680541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.105422973633</t>
+    <t xml:space="preserve">253.651550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">249.883026123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.525695800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.105499267578</t>
   </si>
   <si>
     <t xml:space="preserve">255.29426574707</t>
   </si>
   <si>
-    <t xml:space="preserve">255.004348754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.622329711914</t>
+    <t xml:space="preserve">255.004379272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.622344970703</t>
   </si>
   <si>
     <t xml:space="preserve">252.008834838867</t>
   </si>
   <si>
-    <t xml:space="preserve">250.655990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.844833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">257.468414306641</t>
+    <t xml:space="preserve">250.656036376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.844818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">257.468444824219</t>
   </si>
   <si>
     <t xml:space="preserve">260.802093505859</t>
@@ -2954,193 +2954,193 @@
     <t xml:space="preserve">266.020050048828</t>
   </si>
   <si>
-    <t xml:space="preserve">275.489807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">276.890869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.006622314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.668365478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.305450439453</t>
+    <t xml:space="preserve">275.48974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">276.890838623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.006561279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.668334960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.305480957031</t>
   </si>
   <si>
     <t xml:space="preserve">269.692016601562</t>
   </si>
   <si>
-    <t xml:space="preserve">265.295379638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.556030273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.796493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.347045898438</t>
+    <t xml:space="preserve">265.29541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.555999755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.796463012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.347030639648</t>
   </si>
   <si>
     <t xml:space="preserve">258.869506835938</t>
   </si>
   <si>
-    <t xml:space="preserve">269.595306396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.822357177734</t>
+    <t xml:space="preserve">269.595336914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.822265625</t>
   </si>
   <si>
     <t xml:space="preserve">265.730133056641</t>
   </si>
   <si>
-    <t xml:space="preserve">265.536895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">264.957153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.339172363281</t>
+    <t xml:space="preserve">265.536865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">264.957214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.339263916016</t>
   </si>
   <si>
     <t xml:space="preserve">265.102111816406</t>
   </si>
   <si>
-    <t xml:space="preserve">263.942504882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.579681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266.454895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">267.405242919922</t>
+    <t xml:space="preserve">263.942535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.579711914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266.454925537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">267.4052734375</t>
   </si>
   <si>
     <t xml:space="preserve">281.854339599609</t>
   </si>
   <si>
-    <t xml:space="preserve">277.005615234375</t>
+    <t xml:space="preserve">277.005676269531</t>
   </si>
   <si>
     <t xml:space="preserve">274.290405273438</t>
   </si>
   <si>
-    <t xml:space="preserve">263.623291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">271.090270996094</t>
+    <t xml:space="preserve">263.623260498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271.090240478516</t>
   </si>
   <si>
     <t xml:space="preserve">275.599548339844</t>
   </si>
   <si>
-    <t xml:space="preserve">272.108520507812</t>
+    <t xml:space="preserve">272.108489990234</t>
   </si>
   <si>
     <t xml:space="preserve">280.642181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">281.466491699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">282.630187988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.532806396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">280.205780029297</t>
+    <t xml:space="preserve">281.466461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">282.630157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.532836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">280.205810546875</t>
   </si>
   <si>
     <t xml:space="preserve">278.411804199219</t>
   </si>
   <si>
-    <t xml:space="preserve">284.084777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.769439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.066162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270.750885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.471984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">271.817626953125</t>
+    <t xml:space="preserve">284.084747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.769378662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.066223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270.750823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.471954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271.817535400391</t>
   </si>
   <si>
     <t xml:space="preserve">265.611236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">272.253936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270.847778320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.484283447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.720947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">284.763610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.291381835938</t>
+    <t xml:space="preserve">272.253967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270.847869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.484344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.720916748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">284.763580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.291412353516</t>
   </si>
   <si>
     <t xml:space="preserve">299.455108642578</t>
   </si>
   <si>
-    <t xml:space="preserve">295.576141357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.552062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.679260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.842987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.946166992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.721954345703</t>
+    <t xml:space="preserve">295.576080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.552032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.679351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.842956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.946105957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.721984863281</t>
   </si>
   <si>
     <t xml:space="preserve">314.049682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">312.740539550781</t>
+    <t xml:space="preserve">312.740570068359</t>
   </si>
   <si>
     <t xml:space="preserve">315.019378662109</t>
   </si>
   <si>
-    <t xml:space="preserve">318.364959716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.443420410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.625305175781</t>
+    <t xml:space="preserve">318.364929199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.443389892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.625274658203</t>
   </si>
   <si>
     <t xml:space="preserve">318.12255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">315.213317871094</t>
+    <t xml:space="preserve">315.213348388672</t>
   </si>
   <si>
     <t xml:space="preserve">309.879791259766</t>
@@ -3149,79 +3149,79 @@
     <t xml:space="preserve">306.825103759766</t>
   </si>
   <si>
-    <t xml:space="preserve">311.916229248047</t>
+    <t xml:space="preserve">311.916290283203</t>
   </si>
   <si>
     <t xml:space="preserve">312.837493896484</t>
   </si>
   <si>
-    <t xml:space="preserve">316.231567382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.467864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.631500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.661773681641</t>
+    <t xml:space="preserve">316.231597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.467803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.631469726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.661865234375</t>
   </si>
   <si>
     <t xml:space="preserve">308.425170898438</t>
   </si>
   <si>
-    <t xml:space="preserve">308.473663330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.667266845703</t>
+    <t xml:space="preserve">308.473693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.667297363281</t>
   </si>
   <si>
     <t xml:space="preserve">289.854736328125</t>
   </si>
   <si>
-    <t xml:space="preserve">288.836517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.369812011719</t>
+    <t xml:space="preserve">288.836395263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.369842529297</t>
   </si>
   <si>
     <t xml:space="preserve">287.284881591797</t>
   </si>
   <si>
-    <t xml:space="preserve">285.539367675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">283.84228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.806823730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.298797607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.369110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.812530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.574645996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.428955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.126312255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.996429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.358673095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.412628173828</t>
+    <t xml:space="preserve">285.539398193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">283.842315673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.806732177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.298858642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.8125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.574615478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.428924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.126281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.996398925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.358642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.412689208984</t>
   </si>
   <si>
     <t xml:space="preserve">314.228973388672</t>
@@ -3230,46 +3230,46 @@
     <t xml:space="preserve">303.234100341797</t>
   </si>
   <si>
-    <t xml:space="preserve">299.925964355469</t>
+    <t xml:space="preserve">299.925933837891</t>
   </si>
   <si>
     <t xml:space="preserve">294.185272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">297.250213623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.217834472656</t>
+    <t xml:space="preserve">297.250152587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.217742919922</t>
   </si>
   <si>
     <t xml:space="preserve">295.888000488281</t>
   </si>
   <si>
-    <t xml:space="preserve">304.596374511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.9638671875</t>
+    <t xml:space="preserve">304.596343994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.963806152344</t>
   </si>
   <si>
     <t xml:space="preserve">306.688262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">308.585571289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.299041748047</t>
+    <t xml:space="preserve">308.585632324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.299011230469</t>
   </si>
   <si>
     <t xml:space="preserve">301.96923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">300.412475585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.342102050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.796112060547</t>
+    <t xml:space="preserve">300.412414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.342132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.796051025391</t>
   </si>
   <si>
     <t xml:space="preserve">293.990661621094</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">311.601867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">311.845092773438</t>
+    <t xml:space="preserve">311.845123291016</t>
   </si>
   <si>
     <t xml:space="preserve">314.0830078125</t>
@@ -3302,19 +3302,19 @@
     <t xml:space="preserve">320.066955566406</t>
   </si>
   <si>
-    <t xml:space="preserve">324.34814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.721252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.650939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323.375091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.758941650391</t>
+    <t xml:space="preserve">324.348114013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.721221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.650970458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.375122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.758972167969</t>
   </si>
   <si>
     <t xml:space="preserve">327.315704345703</t>
@@ -3329,64 +3329,64 @@
     <t xml:space="preserve">332.521301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">328.580688476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">326.245422363281</t>
+    <t xml:space="preserve">328.580627441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326.245361328125</t>
   </si>
   <si>
     <t xml:space="preserve">325.710296630859</t>
   </si>
   <si>
-    <t xml:space="preserve">334.515899658203</t>
+    <t xml:space="preserve">334.515930175781</t>
   </si>
   <si>
     <t xml:space="preserve">343.759368896484</t>
   </si>
   <si>
-    <t xml:space="preserve">342.543090820312</t>
+    <t xml:space="preserve">342.543121337891</t>
   </si>
   <si>
     <t xml:space="preserve">347.456787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">347.748687744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.7109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">354.802856445312</t>
+    <t xml:space="preserve">347.748626708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.710968017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">354.802825927734</t>
   </si>
   <si>
     <t xml:space="preserve">341.424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">353.829895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">358.256988525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.473052978516</t>
+    <t xml:space="preserve">353.829925537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">358.257080078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.473114013672</t>
   </si>
   <si>
     <t xml:space="preserve">352.224456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">353.635284423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.429992675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">349.013519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.672637939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.946624755859</t>
+    <t xml:space="preserve">353.635223388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.429931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">349.013549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.672576904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.946655273438</t>
   </si>
   <si>
     <t xml:space="preserve">331.531280517578</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">331.921630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">338.898681640625</t>
+    <t xml:space="preserve">338.898651123047</t>
   </si>
   <si>
     <t xml:space="preserve">339.972045898438</t>
@@ -3404,22 +3404,22 @@
     <t xml:space="preserve">343.728881835938</t>
   </si>
   <si>
-    <t xml:space="preserve">342.606781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.581756591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.093780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.704284667969</t>
+    <t xml:space="preserve">342.606750488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.581726074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.093841552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.704315185547</t>
   </si>
   <si>
     <t xml:space="preserve">345.095062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">341.435729980469</t>
+    <t xml:space="preserve">341.435760498047</t>
   </si>
   <si>
     <t xml:space="preserve">344.509521484375</t>
@@ -3428,40 +3428,40 @@
     <t xml:space="preserve">344.119232177734</t>
   </si>
   <si>
-    <t xml:space="preserve">346.510009765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.826904296875</t>
+    <t xml:space="preserve">346.509948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.826934814453</t>
   </si>
   <si>
     <t xml:space="preserve">342.070037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">345.582946777344</t>
+    <t xml:space="preserve">345.582916259766</t>
   </si>
   <si>
     <t xml:space="preserve">343.680114746094</t>
   </si>
   <si>
-    <t xml:space="preserve">340.411193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.801116943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.239379882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.751068115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.945404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.116394042969</t>
+    <t xml:space="preserve">340.411163330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.801086425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.239349365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.751037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.945465087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.994171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.116363525391</t>
   </si>
   <si>
     <t xml:space="preserve">340.118408203125</t>
@@ -3470,25 +3470,25 @@
     <t xml:space="preserve">338.654724121094</t>
   </si>
   <si>
-    <t xml:space="preserve">336.800659179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.141784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.60595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.044189453125</t>
+    <t xml:space="preserve">336.800628662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.141845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.605926513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.044219970703</t>
   </si>
   <si>
     <t xml:space="preserve">336.703094482422</t>
   </si>
   <si>
-    <t xml:space="preserve">335.629730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">337.288513183594</t>
+    <t xml:space="preserve">335.629699707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">337.288604736328</t>
   </si>
   <si>
     <t xml:space="preserve">330.897003173828</t>
@@ -3497,10 +3497,10 @@
     <t xml:space="preserve">335.434539794922</t>
   </si>
   <si>
-    <t xml:space="preserve">325.774047851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.625610351562</t>
+    <t xml:space="preserve">325.773986816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.625640869141</t>
   </si>
   <si>
     <t xml:space="preserve">321.529235839844</t>
@@ -3509,28 +3509,28 @@
     <t xml:space="preserve">321.919586181641</t>
   </si>
   <si>
-    <t xml:space="preserve">326.017974853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323.968811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.188568115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320.065521240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">317.528381347656</t>
+    <t xml:space="preserve">326.018005371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.968780517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.188507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320.065551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">317.528442382812</t>
   </si>
   <si>
     <t xml:space="preserve">311.088043212891</t>
   </si>
   <si>
-    <t xml:space="preserve">307.672790527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.428833007812</t>
+    <t xml:space="preserve">307.672760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.428802490234</t>
   </si>
   <si>
     <t xml:space="preserve">310.161102294922</t>
@@ -3539,82 +3539,82 @@
     <t xml:space="preserve">313.039672851562</t>
   </si>
   <si>
-    <t xml:space="preserve">308.794952392578</t>
+    <t xml:space="preserve">308.794982910156</t>
   </si>
   <si>
     <t xml:space="preserve">307.184844970703</t>
   </si>
   <si>
-    <t xml:space="preserve">305.477264404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.131927490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.331268310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.160247802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.501739501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.575531005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.161499023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.796600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.503845214844</t>
+    <t xml:space="preserve">305.477142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.131896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.331237792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.160278320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.501770019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.575592041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.161468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.796569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.50390625</t>
   </si>
   <si>
     <t xml:space="preserve">318.393707275391</t>
   </si>
   <si>
-    <t xml:space="preserve">313.595520019531</t>
+    <t xml:space="preserve">313.595550537109</t>
   </si>
   <si>
     <t xml:space="preserve">303.558502197266</t>
   </si>
   <si>
-    <t xml:space="preserve">301.942810058594</t>
+    <t xml:space="preserve">301.942779541016</t>
   </si>
   <si>
     <t xml:space="preserve">300.571899414062</t>
   </si>
   <si>
-    <t xml:space="preserve">302.775115966797</t>
+    <t xml:space="preserve">302.775146484375</t>
   </si>
   <si>
     <t xml:space="preserve">304.146026611328</t>
   </si>
   <si>
-    <t xml:space="preserve">304.341918945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.886444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294.011108398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.939971923828</t>
+    <t xml:space="preserve">304.341857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.886413574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.011138916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.93994140625</t>
   </si>
   <si>
     <t xml:space="preserve">290.192169189453</t>
   </si>
   <si>
-    <t xml:space="preserve">289.604644775391</t>
+    <t xml:space="preserve">289.604614257812</t>
   </si>
   <si>
     <t xml:space="preserve">293.080871582031</t>
   </si>
   <si>
-    <t xml:space="preserve">291.465118408203</t>
+    <t xml:space="preserve">291.465148925781</t>
   </si>
   <si>
     <t xml:space="preserve">289.702575683594</t>
@@ -3623,70 +3623,70 @@
     <t xml:space="preserve">288.380615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">293.129821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">292.052703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.528900146484</t>
+    <t xml:space="preserve">293.129852294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">292.052673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.528930664062</t>
   </si>
   <si>
     <t xml:space="preserve">295.969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">304.195037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.390838623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.089721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.411651611328</t>
+    <t xml:space="preserve">304.195007324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.390869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.089660644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.411682128906</t>
   </si>
   <si>
     <t xml:space="preserve">299.592681884766</t>
   </si>
   <si>
-    <t xml:space="preserve">301.110473632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.984344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.370086669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.488800048828</t>
+    <t xml:space="preserve">301.110443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.984405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.370025634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.488830566406</t>
   </si>
   <si>
     <t xml:space="preserve">303.509613037109</t>
   </si>
   <si>
-    <t xml:space="preserve">305.419006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.950134277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.964996337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.7216796875</t>
+    <t xml:space="preserve">305.419036865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.9501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.965026855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.721618652344</t>
   </si>
   <si>
     <t xml:space="preserve">318.442718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">325.884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.018280029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.605834960938</t>
+    <t xml:space="preserve">325.884826660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.018249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.605804443359</t>
   </si>
   <si>
     <t xml:space="preserve">330.976715087891</t>
@@ -3695,49 +3695,49 @@
     <t xml:space="preserve">333.326873779297</t>
   </si>
   <si>
-    <t xml:space="preserve">334.110198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.543487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.760101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.944000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.768951416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">344.685821533203</t>
+    <t xml:space="preserve">334.110229492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.54345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.760070800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.943969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.768920898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.685791015625</t>
   </si>
   <si>
     <t xml:space="preserve">352.323699951172</t>
   </si>
   <si>
-    <t xml:space="preserve">358.786651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.433349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">380.133575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">382.679626464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385.2255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385.421447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">386.204803466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389.338287353516</t>
+    <t xml:space="preserve">358.78662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.433319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">380.133636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">382.679534912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385.225555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385.421417236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">386.204772949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">389.338317871094</t>
   </si>
   <si>
     <t xml:space="preserve">395.358032226562</t>
@@ -3746,10 +3746,10 @@
     <t xml:space="preserve">389.465972900391</t>
   </si>
   <si>
-    <t xml:space="preserve">393.394012451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.197631835938</t>
+    <t xml:space="preserve">393.39404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.197601318359</t>
   </si>
   <si>
     <t xml:space="preserve">398.304046630859</t>
@@ -3758,10 +3758,10 @@
     <t xml:space="preserve">401.053680419922</t>
   </si>
   <si>
-    <t xml:space="preserve">402.428497314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.484008789062</t>
+    <t xml:space="preserve">402.428558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.483978271484</t>
   </si>
   <si>
     <t xml:space="preserve">388.091156005859</t>
@@ -3773,58 +3773,58 @@
     <t xml:space="preserve">391.233581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">396.143615722656</t>
+    <t xml:space="preserve">396.143585205078</t>
   </si>
   <si>
     <t xml:space="preserve">388.680328369141</t>
   </si>
   <si>
-    <t xml:space="preserve">396.536407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.160186767578</t>
+    <t xml:space="preserve">396.536437988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.160125732422</t>
   </si>
   <si>
     <t xml:space="preserve">408.124206542969</t>
   </si>
   <si>
-    <t xml:space="preserve">404.785339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.963745117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.731384277344</t>
+    <t xml:space="preserve">404.785400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.963775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.7314453125</t>
   </si>
   <si>
     <t xml:space="preserve">403.999725341797</t>
   </si>
   <si>
-    <t xml:space="preserve">405.178161621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.821350097656</t>
+    <t xml:space="preserve">405.178192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.821380615234</t>
   </si>
   <si>
     <t xml:space="preserve">407.535003662109</t>
   </si>
   <si>
-    <t xml:space="preserve">406.749359130859</t>
+    <t xml:space="preserve">406.749389648438</t>
   </si>
   <si>
     <t xml:space="preserve">413.034271240234</t>
   </si>
   <si>
-    <t xml:space="preserve">409.4990234375</t>
+    <t xml:space="preserve">409.498962402344</t>
   </si>
   <si>
     <t xml:space="preserve">417.551513671875</t>
   </si>
   <si>
-    <t xml:space="preserve">419.122741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.479583740234</t>
+    <t xml:space="preserve">419.122772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.479553222656</t>
   </si>
   <si>
     <t xml:space="preserve">415.980285644531</t>
@@ -3833,13 +3833,13 @@
     <t xml:space="preserve">419.711944580078</t>
   </si>
   <si>
-    <t xml:space="preserve">420.497589111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.570983886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">403.60693359375</t>
+    <t xml:space="preserve">420.49755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.570953369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">403.606964111328</t>
   </si>
   <si>
     <t xml:space="preserve">397.518402099609</t>
@@ -3848,13 +3848,13 @@
     <t xml:space="preserve">390.447998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">383.377471923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">391.822784423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">395.947265625</t>
+    <t xml:space="preserve">383.377502441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">391.82275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">395.947235107422</t>
   </si>
   <si>
     <t xml:space="preserve">394.572418212891</t>
@@ -3866,31 +3866,31 @@
     <t xml:space="preserve">410.284606933594</t>
   </si>
   <si>
-    <t xml:space="preserve">409.302642822266</t>
+    <t xml:space="preserve">409.302612304688</t>
   </si>
   <si>
     <t xml:space="preserve">408.320617675781</t>
   </si>
   <si>
-    <t xml:space="preserve">407.142181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.356597900391</t>
+    <t xml:space="preserve">407.142211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.356567382812</t>
   </si>
   <si>
     <t xml:space="preserve">402.232147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">405.767395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">413.819854736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404.588958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">400.464447021484</t>
+    <t xml:space="preserve">405.767425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413.819885253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404.588989257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400.464477539062</t>
   </si>
   <si>
     <t xml:space="preserve">403.410552978516</t>
@@ -3899,64 +3899,64 @@
     <t xml:space="preserve">477.650634765625</t>
   </si>
   <si>
-    <t xml:space="preserve">474.508270263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">470.187316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">474.115386962891</t>
+    <t xml:space="preserve">474.508209228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470.187408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">474.115356445312</t>
   </si>
   <si>
     <t xml:space="preserve">486.251983642578</t>
   </si>
   <si>
-    <t xml:space="preserve">488.614379882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">495.110870361328</t>
+    <t xml:space="preserve">488.614349365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">495.11083984375</t>
   </si>
   <si>
     <t xml:space="preserve">493.634368896484</t>
   </si>
   <si>
-    <t xml:space="preserve">492.157867431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">496.095092773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.524566650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.048095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">503.4775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">503.9697265625</t>
+    <t xml:space="preserve">492.157897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">496.095245361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.524597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.048126220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">503.477508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">503.969665527344</t>
   </si>
   <si>
     <t xml:space="preserve">501.016723632812</t>
   </si>
   <si>
-    <t xml:space="preserve">495.602996826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.032470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">507.414764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">511.844268798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.797180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.383483886719</t>
+    <t xml:space="preserve">495.60302734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.032409667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">507.414855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">511.844177246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.797241210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.383392333984</t>
   </si>
   <si>
     <t xml:space="preserve">527.593200683594</t>
@@ -3965,16 +3965,16 @@
     <t xml:space="preserve">535.9599609375</t>
   </si>
   <si>
-    <t xml:space="preserve">547.279541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">546.295288085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">546.787414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">550.232482910156</t>
+    <t xml:space="preserve">547.279479980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">546.295227050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">546.787475585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">550.232543945312</t>
   </si>
   <si>
     <t xml:space="preserve">539.897277832031</t>
@@ -3986,31 +3986,31 @@
     <t xml:space="preserve">526.116821289062</t>
   </si>
   <si>
-    <t xml:space="preserve">512.33642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">510.859924316406</t>
+    <t xml:space="preserve">512.336303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">510.859893798828</t>
   </si>
   <si>
     <t xml:space="preserve">489.992401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">504.461822509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">517.750061035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.514831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">554.661926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.4423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567.950134277344</t>
+    <t xml:space="preserve">504.461853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">517.750183105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.514892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">554.661987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.442321777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567.9501953125</t>
   </si>
   <si>
     <t xml:space="preserve">575.82470703125</t>
@@ -4025,49 +4025,49 @@
     <t xml:space="preserve">545.803161621094</t>
   </si>
   <si>
-    <t xml:space="preserve">543.342346191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">540.389282226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">549.248229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">555.646301269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.022644042969</t>
+    <t xml:space="preserve">543.34228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540.389343261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">549.248168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">555.646179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.022705078125</t>
   </si>
   <si>
     <t xml:space="preserve">523.656066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">514.304992675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">517.258056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">534.975708007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">544.818725585938</t>
+    <t xml:space="preserve">514.305053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">517.257873535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534.975524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">544.81884765625</t>
   </si>
   <si>
     <t xml:space="preserve">553.185424804688</t>
   </si>
   <si>
-    <t xml:space="preserve">554.299926757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">536.053527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.108337402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">536.546691894531</t>
+    <t xml:space="preserve">554.299987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">536.053344726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.108215332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">536.546752929688</t>
   </si>
   <si>
     <t xml:space="preserve">542.464416503906</t>
@@ -4085,43 +4085,43 @@
     <t xml:space="preserve">533.094604492188</t>
   </si>
   <si>
-    <t xml:space="preserve">531.122009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">538.026123046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">540.491821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.601440429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.039733886719</t>
+    <t xml:space="preserve">531.121948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">538.026062011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540.491760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.601379394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.039794921875</t>
   </si>
   <si>
     <t xml:space="preserve">534.080871582031</t>
   </si>
   <si>
-    <t xml:space="preserve">539.012390136719</t>
+    <t xml:space="preserve">539.012329101562</t>
   </si>
   <si>
     <t xml:space="preserve">526.190490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">531.615112304688</t>
+    <t xml:space="preserve">531.615173339844</t>
   </si>
   <si>
     <t xml:space="preserve">517.807006835938</t>
   </si>
   <si>
-    <t xml:space="preserve">513.36865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">523.231689453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">519.779541015625</t>
+    <t xml:space="preserve">513.368530273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">523.231567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">519.779479980469</t>
   </si>
   <si>
     <t xml:space="preserve">511.88916015625</t>
@@ -4130,19 +4130,19 @@
     <t xml:space="preserve">509.916564941406</t>
   </si>
   <si>
-    <t xml:space="preserve">511.396026611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">518.793273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">520.765808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">527.669982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">552.820617675781</t>
+    <t xml:space="preserve">511.395935058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">518.793334960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">520.765869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">527.669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">552.820556640625</t>
   </si>
   <si>
     <t xml:space="preserve">567.121887207031</t>
@@ -4151,40 +4151,40 @@
     <t xml:space="preserve">557.258911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">567.614990234375</t>
+    <t xml:space="preserve">567.615112304688</t>
   </si>
   <si>
     <t xml:space="preserve">565.642395019531</t>
   </si>
   <si>
-    <t xml:space="preserve">568.108154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">573.532775878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">581.423278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">583.889038085938</t>
+    <t xml:space="preserve">568.108215332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">573.532836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">581.423217773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">583.888977050781</t>
   </si>
   <si>
     <t xml:space="preserve">575.012268066406</t>
   </si>
   <si>
-    <t xml:space="preserve">561.697265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569.094421386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.601318359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">577.478088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">572.053344726562</t>
+    <t xml:space="preserve">561.697387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569.094482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.601379394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">577.477966308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">572.053466796875</t>
   </si>
   <si>
     <t xml:space="preserve">577.97119140625</t>
@@ -4193,61 +4193,61 @@
     <t xml:space="preserve">587.341064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">587.834228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">585.861572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">593.752014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">609.039611816406</t>
+    <t xml:space="preserve">587.834167480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">585.861633300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">593.751892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">609.039672851562</t>
   </si>
   <si>
     <t xml:space="preserve">646.025817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">642.080627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">668.217529296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">675.614807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677.094177246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">671.176452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">679.559936523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">695.172912597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">698.631469726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">722.841552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">726.300170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">700.11376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">681.338684082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">707.030883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">697.643371582031</t>
+    <t xml:space="preserve">642.08056640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">668.217468261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">675.614868164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">677.09423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">671.176391601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679.560119628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">695.172973632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">698.631530761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722.841491699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">726.300109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">700.113708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">681.338623046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">707.030944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">697.643310546875</t>
   </si>
   <si>
     <t xml:space="preserve">705.054565429688</t>
@@ -4259,124 +4259,124 @@
     <t xml:space="preserve">688.255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">686.279541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">709.995422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">722.347534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">710.489379882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">711.971740722656</t>
+    <t xml:space="preserve">686.279418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">709.995361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722.347351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">710.489440917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.971801757812</t>
   </si>
   <si>
     <t xml:space="preserve">690.232116699219</t>
   </si>
   <si>
-    <t xml:space="preserve">660.587280273438</t>
+    <t xml:space="preserve">660.587219238281</t>
   </si>
   <si>
     <t xml:space="preserve">678.868225097656</t>
   </si>
   <si>
-    <t xml:space="preserve">683.315063476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">682.326904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">697.149291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.560485839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.066345214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">706.042663574219</t>
+    <t xml:space="preserve">683.31494140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">682.326843261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">697.149353027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.06640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706.042724609375</t>
   </si>
   <si>
     <t xml:space="preserve">720.865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">698.829162597656</t>
+    <t xml:space="preserve">698.829223632812</t>
   </si>
   <si>
     <t xml:space="preserve">709.896667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">704.165222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">709.204956054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">708.710815429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">689.737976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">701.991271972656</t>
+    <t xml:space="preserve">704.165161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">709.204833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">708.710754394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">689.738037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">701.991333007812</t>
   </si>
   <si>
     <t xml:space="preserve">702.090087890625</t>
   </si>
   <si>
-    <t xml:space="preserve">706.141540527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">695.469360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">694.283569335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677.188354492188</t>
+    <t xml:space="preserve">706.141479492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">695.469421386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">694.283508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">677.188415527344</t>
   </si>
   <si>
     <t xml:space="preserve">676.694274902344</t>
   </si>
   <si>
-    <t xml:space="preserve">685.39013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">678.077697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">667.603149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">680.745727539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">674.619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">711.576416015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">674.520263671875</t>
+    <t xml:space="preserve">685.390075683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">678.077758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">667.603210449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">680.745849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">674.619262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.576477050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">674.520324707031</t>
   </si>
   <si>
     <t xml:space="preserve">688.8486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">709.106018066406</t>
+    <t xml:space="preserve">709.10595703125</t>
   </si>
   <si>
     <t xml:space="preserve">712.367065429688</t>
   </si>
   <si>
-    <t xml:space="preserve">690.13330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.528503417969</t>
+    <t xml:space="preserve">690.133361816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.528564453125</t>
   </si>
   <si>
     <t xml:space="preserve">710.328674316406</t>
@@ -4385,37 +4385,37 @@
     <t xml:space="preserve">705.57666015625</t>
   </si>
   <si>
-    <t xml:space="preserve">701.517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">712.407592773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">732.603820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">729.336791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">744.186828613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">737.2568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">739.434936523438</t>
+    <t xml:space="preserve">701.517639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">712.407653808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">732.603759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">729.336730957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">744.186889648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">737.256774902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">739.434875488281</t>
   </si>
   <si>
     <t xml:space="preserve">733.593811035156</t>
   </si>
   <si>
-    <t xml:space="preserve">744.087768554688</t>
+    <t xml:space="preserve">744.087890625</t>
   </si>
   <si>
     <t xml:space="preserve">744.681884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">746.661926269531</t>
+    <t xml:space="preserve">746.661865234375</t>
   </si>
   <si>
     <t xml:space="preserve">758.640930175781</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">762.204956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">778.242919921875</t>
+    <t xml:space="preserve">778.242980957031</t>
   </si>
   <si>
     <t xml:space="preserve">791.410095214844</t>
@@ -4439,52 +4439,52 @@
     <t xml:space="preserve">793.588134765625</t>
   </si>
   <si>
-    <t xml:space="preserve">787.549072265625</t>
+    <t xml:space="preserve">787.549011230469</t>
   </si>
   <si>
     <t xml:space="preserve">807.250244140625</t>
   </si>
   <si>
-    <t xml:space="preserve">815.764282226562</t>
+    <t xml:space="preserve">815.764221191406</t>
   </si>
   <si>
     <t xml:space="preserve">815.962280273438</t>
   </si>
   <si>
-    <t xml:space="preserve">825.565246582031</t>
+    <t xml:space="preserve">825.565307617188</t>
   </si>
   <si>
     <t xml:space="preserve">823.288269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">833.386291503906</t>
+    <t xml:space="preserve">833.386352539062</t>
   </si>
   <si>
     <t xml:space="preserve">819.42724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">828.337280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">838.732299804688</t>
+    <t xml:space="preserve">828.337341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.732360839844</t>
   </si>
   <si>
     <t xml:space="preserve">835.267333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">833.980407714844</t>
+    <t xml:space="preserve">833.980346679688</t>
   </si>
   <si>
     <t xml:space="preserve">843.385375976562</t>
   </si>
   <si>
-    <t xml:space="preserve">845.266418457031</t>
+    <t xml:space="preserve">845.266357421875</t>
   </si>
   <si>
     <t xml:space="preserve">828.931274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">818.932250976562</t>
+    <t xml:space="preserve">818.932189941406</t>
   </si>
   <si>
     <t xml:space="preserve">825.664306640625</t>
@@ -4493,10 +4493,10 @@
     <t xml:space="preserve">834.970397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">839.722290039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">847.543273925781</t>
+    <t xml:space="preserve">839.722351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">847.543334960938</t>
   </si>
   <si>
     <t xml:space="preserve">861.403442382812</t>
@@ -4505,40 +4505,40 @@
     <t xml:space="preserve">845.563354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">859.720397949219</t>
+    <t xml:space="preserve">859.720458984375</t>
   </si>
   <si>
     <t xml:space="preserve">863.977478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">863.482482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">830.020263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">773.392028808594</t>
+    <t xml:space="preserve">863.482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">830.020324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">773.39208984375</t>
   </si>
   <si>
     <t xml:space="preserve">783.193054199219</t>
   </si>
   <si>
-    <t xml:space="preserve">784.282104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">807.646240234375</t>
+    <t xml:space="preserve">784.282043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">807.646118164062</t>
   </si>
   <si>
     <t xml:space="preserve">782.401062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">760.224914550781</t>
+    <t xml:space="preserve">760.224975585938</t>
   </si>
   <si>
     <t xml:space="preserve">743.790771484375</t>
   </si>
   <si>
-    <t xml:space="preserve">737.751831054688</t>
+    <t xml:space="preserve">737.751892089844</t>
   </si>
   <si>
     <t xml:space="preserve">726.465759277344</t>
@@ -4547,13 +4547,13 @@
     <t xml:space="preserve">735.078796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">761.016967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720.030700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">699.042663574219</t>
+    <t xml:space="preserve">761.016906738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720.03076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">699.042724609375</t>
   </si>
   <si>
     <t xml:space="preserve">720.327697753906</t>
@@ -4565,106 +4565,106 @@
     <t xml:space="preserve">755.967895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">812.794250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">806.359130859375</t>
+    <t xml:space="preserve">812.794189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">806.359191894531</t>
   </si>
   <si>
     <t xml:space="preserve">817.744262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">838.138305664062</t>
+    <t xml:space="preserve">838.138366699219</t>
   </si>
   <si>
     <t xml:space="preserve">836.353576660156</t>
   </si>
   <si>
-    <t xml:space="preserve">824.752624511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">846.169677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">841.806884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">855.886779785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">840.220520019531</t>
+    <t xml:space="preserve">824.752685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">846.169738769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">841.806945800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">855.886657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">840.220581054688</t>
   </si>
   <si>
     <t xml:space="preserve">845.376525878906</t>
   </si>
   <si>
-    <t xml:space="preserve">851.028198242188</t>
+    <t xml:space="preserve">851.028137207031</t>
   </si>
   <si>
     <t xml:space="preserve">845.673950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">850.631591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">846.764587402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">858.563781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">867.586730957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">852.217956542969</t>
+    <t xml:space="preserve">850.631652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">846.7646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">858.563842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">867.586669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">852.218078613281</t>
   </si>
   <si>
     <t xml:space="preserve">812.160278320312</t>
   </si>
   <si>
-    <t xml:space="preserve">806.012878417969</t>
+    <t xml:space="preserve">806.012817382812</t>
   </si>
   <si>
     <t xml:space="preserve">807.995910644531</t>
   </si>
   <si>
-    <t xml:space="preserve">812.656066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812.95361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">831.197570800781</t>
+    <t xml:space="preserve">812.656005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812.953552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">831.197692871094</t>
   </si>
   <si>
     <t xml:space="preserve">835.064636230469</t>
   </si>
   <si>
-    <t xml:space="preserve">824.058654785156</t>
+    <t xml:space="preserve">824.05859375</t>
   </si>
   <si>
     <t xml:space="preserve">812.556945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">808.987487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">805.517150878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">825.5458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816.919738769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819.695861816406</t>
+    <t xml:space="preserve">808.987365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">805.51708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">825.545959472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816.919616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.695922851562</t>
   </si>
   <si>
     <t xml:space="preserve">821.579772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">813.845825195312</t>
+    <t xml:space="preserve">813.845886230469</t>
   </si>
   <si>
     <t xml:space="preserve">779.737365722656</t>
@@ -4673,70 +4673,70 @@
     <t xml:space="preserve">779.935668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">793.519653320312</t>
+    <t xml:space="preserve">793.519592285156</t>
   </si>
   <si>
     <t xml:space="preserve">800.063720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">798.675476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">794.709411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816.324645996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">826.636596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">829.313720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">836.948547363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">829.809448242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">832.982421875</t>
+    <t xml:space="preserve">798.675537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">794.70947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816.32470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">826.636657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">829.313781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">836.948486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">829.8095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">832.982360839844</t>
   </si>
   <si>
     <t xml:space="preserve">841.410400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">838.435791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">830.0078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">833.27978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">823.661987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819.200134277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">822.868774414062</t>
+    <t xml:space="preserve">838.435668945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">830.007751464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">833.279907226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">823.662048339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.2001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">822.868896484375</t>
   </si>
   <si>
     <t xml:space="preserve">819.894287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">827.13232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761.790710449219</t>
+    <t xml:space="preserve">827.132385253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761.790649414062</t>
   </si>
   <si>
     <t xml:space="preserve">778.646667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">754.651733398438</t>
+    <t xml:space="preserve">754.651672363281</t>
   </si>
   <si>
     <t xml:space="preserve">737.002502441406</t>
@@ -4745,10 +4745,10 @@
     <t xml:space="preserve">726.492309570312</t>
   </si>
   <si>
-    <t xml:space="preserve">716.973571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">725.401550292969</t>
+    <t xml:space="preserve">716.9736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">725.401611328125</t>
   </si>
   <si>
     <t xml:space="preserve">766.550048828125</t>
@@ -4757,28 +4757,28 @@
     <t xml:space="preserve">778.250061035156</t>
   </si>
   <si>
-    <t xml:space="preserve">761.691528320312</t>
+    <t xml:space="preserve">761.691589355469</t>
   </si>
   <si>
     <t xml:space="preserve">771.309387207031</t>
   </si>
   <si>
-    <t xml:space="preserve">750.090698242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">713.241638183594</t>
+    <t xml:space="preserve">750.090637207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">713.24169921875</t>
   </si>
   <si>
     <t xml:space="preserve">680.464904785156</t>
   </si>
   <si>
-    <t xml:space="preserve">679.670288085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">703.706604003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.295715332031</t>
+    <t xml:space="preserve">679.67041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">703.706665039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.295837402344</t>
   </si>
   <si>
     <t xml:space="preserve">715.228088378906</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">749.892028808594</t>
   </si>
   <si>
-    <t xml:space="preserve">756.447387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766.776977539062</t>
+    <t xml:space="preserve">756.447326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766.777038574219</t>
   </si>
   <si>
     <t xml:space="preserve">790.416015625</t>
@@ -4811,31 +4811,31 @@
     <t xml:space="preserve">760.519653320312</t>
   </si>
   <si>
-    <t xml:space="preserve">756.348083496094</t>
+    <t xml:space="preserve">756.348022460938</t>
   </si>
   <si>
     <t xml:space="preserve">748.104248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">747.408996582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">740.952941894531</t>
+    <t xml:space="preserve">747.408935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">740.952880859375</t>
   </si>
   <si>
     <t xml:space="preserve">744.329956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">744.925903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">735.7880859375</t>
+    <t xml:space="preserve">744.925842285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">735.788146972656</t>
   </si>
   <si>
     <t xml:space="preserve">725.756469726562</t>
   </si>
   <si>
-    <t xml:space="preserve">759.02978515625</t>
+    <t xml:space="preserve">759.029846191406</t>
   </si>
   <si>
     <t xml:space="preserve">745.521789550781</t>
@@ -4844,13 +4844,13 @@
     <t xml:space="preserve">748.700134277344</t>
   </si>
   <si>
-    <t xml:space="preserve">738.569152832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">759.327819824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">753.070373535156</t>
+    <t xml:space="preserve">738.569213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">759.327758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">753.070434570312</t>
   </si>
   <si>
     <t xml:space="preserve">739.860412597656</t>
@@ -4859,7 +4859,7 @@
     <t xml:space="preserve">740.158386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">758.731811523438</t>
+    <t xml:space="preserve">758.731872558594</t>
   </si>
   <si>
     <t xml:space="preserve">758.433837890625</t>
@@ -4874,7 +4874,7 @@
     <t xml:space="preserve">718.505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">720.194274902344</t>
+    <t xml:space="preserve">720.1943359375</t>
   </si>
   <si>
     <t xml:space="preserve">734.993530273438</t>
@@ -4886,7 +4886,7 @@
     <t xml:space="preserve">693.674987792969</t>
   </si>
   <si>
-    <t xml:space="preserve">697.548522949219</t>
+    <t xml:space="preserve">697.548583984375</t>
   </si>
   <si>
     <t xml:space="preserve">724.663879394531</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">741.846862792969</t>
   </si>
   <si>
-    <t xml:space="preserve">757.937194824219</t>
+    <t xml:space="preserve">757.937255859375</t>
   </si>
   <si>
     <t xml:space="preserve">766.181091308594</t>
@@ -4910,7 +4910,7 @@
     <t xml:space="preserve">771.445251464844</t>
   </si>
   <si>
-    <t xml:space="preserve">784.555908203125</t>
+    <t xml:space="preserve">784.555969238281</t>
   </si>
   <si>
     <t xml:space="preserve">785.052551269531</t>
@@ -4922,22 +4922,22 @@
     <t xml:space="preserve">796.1767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">842.759399414062</t>
+    <t xml:space="preserve">842.759460449219</t>
   </si>
   <si>
     <t xml:space="preserve">843.752685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">834.813598632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">833.025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">831.734619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">834.317016601562</t>
+    <t xml:space="preserve">834.813659667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">833.025756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">831.734558105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">834.316955566406</t>
   </si>
   <si>
     <t xml:space="preserve">816.108276367188</t>
@@ -5418,6 +5418,9 @@
   </si>
   <si>
     <t xml:space="preserve">716.599975585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">698.099975585938</t>
   </si>
 </sst>
 </file>
@@ -70444,7 +70447,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45943.6499074074</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>3963</v>
@@ -70465,6 +70468,32 @@
         <v>1801</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45944.6498842593</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>3646</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>709</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>696.900024414062</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>708.900024414062</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>698.099975585938</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="1810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="1811">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,202 +38,202 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3028869628906</t>
+    <t xml:space="preserve">38.3028831481934</t>
   </si>
   <si>
     <t xml:space="preserve">LLY.DE</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7578277587891</t>
+    <t xml:space="preserve">38.7578239440918</t>
   </si>
   <si>
     <t xml:space="preserve">61.680061340332</t>
   </si>
   <si>
-    <t xml:space="preserve">62.117488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5549430847168</t>
+    <t xml:space="preserve">62.117504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5549545288086</t>
   </si>
   <si>
     <t xml:space="preserve">63.4298400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">62.9924011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.2426300048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8051490783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3677101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9302711486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0230102539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5943069458008</t>
+    <t xml:space="preserve">62.9923934936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.2426147460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8051605224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3677215576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9302597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0229911804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5943145751953</t>
   </si>
   <si>
     <t xml:space="preserve">58.1717262268066</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8681259155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7071571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5908012390137</t>
+    <t xml:space="preserve">56.8681449890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7071418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5907974243164</t>
   </si>
   <si>
     <t xml:space="preserve">54.3309478759766</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3598175048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0159912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.221263885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8040008544922</t>
+    <t xml:space="preserve">53.3598022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0159759521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2212562561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8040161132812</t>
   </si>
   <si>
     <t xml:space="preserve">56.3226585388184</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4815940856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.278507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4021110534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0290222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.532283782959</t>
+    <t xml:space="preserve">56.4815902709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2785186767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4021263122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0290069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5322875976562</t>
   </si>
   <si>
     <t xml:space="preserve">56.5963668823242</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4662132263184</t>
+    <t xml:space="preserve">55.4662055969238</t>
   </si>
   <si>
     <t xml:space="preserve">55.2719573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5721549987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1218605041504</t>
+    <t xml:space="preserve">55.5721588134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1218643188477</t>
   </si>
   <si>
     <t xml:space="preserve">54.9276123046875</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9717597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6405181884766</t>
+    <t xml:space="preserve">54.9717636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6405220031738</t>
   </si>
   <si>
     <t xml:space="preserve">56.2167091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5787086486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.075439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8082695007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0312881469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4286231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2961730957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.890022277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.486156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2323722839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9034042358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1130294799805</t>
+    <t xml:space="preserve">56.5787124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0754432678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.808277130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0312843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4286041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2961769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8900108337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.486141204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2323837280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9034080505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.113037109375</t>
   </si>
   <si>
     <t xml:space="preserve">55.3690872192383</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6251449584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9230613708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.881175994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5191879272461</t>
+    <t xml:space="preserve">55.6251411437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9230499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8812026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5191802978516</t>
   </si>
   <si>
     <t xml:space="preserve">56.7641372680664</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1019287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6935005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5057983398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1614456176758</t>
+    <t xml:space="preserve">56.1019248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6934852600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.505786895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1614379882812</t>
   </si>
   <si>
     <t xml:space="preserve">56.9936943054199</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5433883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9495429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4793128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.911937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5829849243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9162254333496</t>
+    <t xml:space="preserve">56.5433921813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9495506286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4792976379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9119453430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5829811096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9162178039551</t>
   </si>
   <si>
     <t xml:space="preserve">60.3665199279785</t>
@@ -242,124 +242,124 @@
     <t xml:space="preserve">60.1899261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3622436523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6558952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6294021606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6271324157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.733081817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5166244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0552101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5231742858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4452857971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7212219238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8873023986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5134506225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2433471679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2077369689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3946304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9376449584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4093856811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1570892333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5696258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6586380004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2105102539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.255012512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7979888916016</t>
+    <t xml:space="preserve">58.3622398376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6559066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6294097900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6271209716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7330741882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5166091918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0552215576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5231704711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4452934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7212257385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2997970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8872947692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5134201049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2433433532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2077293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3946647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.937629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4093933105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1571044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5696105957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6586303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2105178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.254997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7979965209961</t>
   </si>
   <si>
     <t xml:space="preserve">66.1006240844727</t>
   </si>
   <si>
-    <t xml:space="preserve">65.6911849975586</t>
+    <t xml:space="preserve">65.6911697387695</t>
   </si>
   <si>
     <t xml:space="preserve">66.4967346191406</t>
   </si>
   <si>
-    <t xml:space="preserve">66.728157043457</t>
+    <t xml:space="preserve">66.7281646728516</t>
   </si>
   <si>
     <t xml:space="preserve">65.833610534668</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9582061767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1615676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3039855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5220642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3320541381836</t>
+    <t xml:space="preserve">65.9582214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1615371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3039779663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5220565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3320693969727</t>
   </si>
   <si>
     <t xml:space="preserve">66.2608489990234</t>
   </si>
   <si>
-    <t xml:space="preserve">65.8202362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2563858032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5189819335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7860336303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.398811340332</t>
+    <t xml:space="preserve">65.8202590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2564086914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5189743041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7860488891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3988342285156</t>
   </si>
   <si>
     <t xml:space="preserve">67.3557052612305</t>
@@ -368,94 +368,94 @@
     <t xml:space="preserve">68.1212158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">68.1657104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1568222045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6018981933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3971710205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.596061706543</t>
+    <t xml:space="preserve">68.1657180786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1568298339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6018676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3971557617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5960693359375</t>
   </si>
   <si>
     <t xml:space="preserve">69.1448669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">71.6194076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.5273361206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6221771240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.515380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9306869506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6961517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2124481201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8355484008789</t>
+    <t xml:space="preserve">71.6194000244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.5273208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.622184753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5153732299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9306793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6961822509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2124404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8355331420898</t>
   </si>
   <si>
     <t xml:space="preserve">78.4733734130859</t>
   </si>
   <si>
-    <t xml:space="preserve">78.9362335205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.562370300293</t>
+    <t xml:space="preserve">78.9362258911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5623779296875</t>
   </si>
   <si>
     <t xml:space="preserve">78.7137069702148</t>
   </si>
   <si>
-    <t xml:space="preserve">79.8352584838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8441390991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8048477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4318618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9513854980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5694580078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.784423828125</t>
+    <t xml:space="preserve">79.8352432250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8441467285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8048400878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4318695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9513778686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.569465637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7844009399414</t>
   </si>
   <si>
     <t xml:space="preserve">81.4587249755859</t>
   </si>
   <si>
-    <t xml:space="preserve">81.3691558837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9033508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6883926391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.634651184082</t>
+    <t xml:space="preserve">81.3691482543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9033737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6884002685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6346282958984</t>
   </si>
   <si>
     <t xml:space="preserve">80.5809097290039</t>
@@ -464,67 +464,67 @@
     <t xml:space="preserve">80.9839935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8496475219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2168731689453</t>
+    <t xml:space="preserve">80.8496322631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2168884277344</t>
   </si>
   <si>
     <t xml:space="preserve">81.0914688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">81.2526931762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2853012084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3211364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4888458251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8618087768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7811965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3960266113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6110076904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9782409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3569793701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.181037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6077499389648</t>
+    <t xml:space="preserve">81.2527008056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2852935791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.321159362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4888229370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8618011474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7812118530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3960189819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6109924316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9782485961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3569717407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1810455322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6077728271484</t>
   </si>
   <si>
     <t xml:space="preserve">81.0735473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">82.238037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1158447265625</t>
+    <t xml:space="preserve">82.2380294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.115852355957</t>
   </si>
   <si>
     <t xml:space="preserve">83.2949905395508</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2810592651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2248077392578</t>
+    <t xml:space="preserve">87.2810440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2248306274414</t>
   </si>
   <si>
     <t xml:space="preserve">90.5057067871094</t>
@@ -533,181 +533,181 @@
     <t xml:space="preserve">89.7980880737305</t>
   </si>
   <si>
-    <t xml:space="preserve">89.1531524658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2477188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4537200927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8478469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3014602661133</t>
+    <t xml:space="preserve">89.1531372070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2477111816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4537124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8478622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3014678955078</t>
   </si>
   <si>
     <t xml:space="preserve">86.8958740234375</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3200988769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9976348876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7378387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3552169799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7436141967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1402053833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2681198120117</t>
+    <t xml:space="preserve">88.3201065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9976577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7378616333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3552017211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7435836791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1402359008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2681274414062</t>
   </si>
   <si>
     <t xml:space="preserve">85.2029418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">87.0660552978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8177642822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6980819702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.128776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9725341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2061538696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7289047241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.2369918823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3591766357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9741363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7129058837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5325469970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5685195922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9740829467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3705215454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1991958618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8839797973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4063720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2171173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7665176391602</t>
+    <t xml:space="preserve">87.0660629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.817756652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6980972290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1287689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.4472808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9725189208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2061614990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7289276123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.2369766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3591613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9741668701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7129287719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5325698852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5685272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9740753173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3705062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1991653442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8839721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.406364440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2171020507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7665252685547</t>
   </si>
   <si>
     <t xml:space="preserve">93.8475036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0456771850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1541442871094</t>
+    <t xml:space="preserve">94.0457000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1541366577148</t>
   </si>
   <si>
     <t xml:space="preserve">89.6046447753906</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3885269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3162078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7487564086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8930816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8933486938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8931732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0644149780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2627639770508</t>
+    <t xml:space="preserve">88.388557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3162002563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7487640380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8930892944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8933563232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.893180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0643844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2627563476562</t>
   </si>
   <si>
     <t xml:space="preserve">86.7760620117188</t>
   </si>
   <si>
-    <t xml:space="preserve">88.5056610107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.325309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0191116333008</t>
+    <t xml:space="preserve">88.5056304931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3252868652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0190887451172</t>
   </si>
   <si>
     <t xml:space="preserve">89.1812744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6315612792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6135482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4513168334961</t>
+    <t xml:space="preserve">90.6315765380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6135559082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4513244628906</t>
   </si>
   <si>
     <t xml:space="preserve">90.8747863769531</t>
   </si>
   <si>
-    <t xml:space="preserve">90.667610168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9920120239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7217559814453</t>
+    <t xml:space="preserve">90.6676025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9919891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7217483520508</t>
   </si>
   <si>
     <t xml:space="preserve">92.3521347045898</t>
@@ -716,133 +716,133 @@
     <t xml:space="preserve">93.3700714111328</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5863571166992</t>
+    <t xml:space="preserve">91.6675186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5863647460938</t>
   </si>
   <si>
     <t xml:space="preserve">92.424201965332</t>
   </si>
   <si>
-    <t xml:space="preserve">93.0998306274414</t>
+    <t xml:space="preserve">93.0998153686523</t>
   </si>
   <si>
     <t xml:space="preserve">92.6674270629883</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6586074829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.0820541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7666015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5052108764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4150009155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7394180297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6851654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.099739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4961624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6043853759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9645919799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3970184326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1717758178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.3154754638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6569519042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0890884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6751022338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.7385330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2370681762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0437698364258</t>
+    <t xml:space="preserve">90.6585998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0820846557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7666168212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5052032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4150085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7394332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6852035522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0997161865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4961776733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.604362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9646148681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3970031738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1717910766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.3154602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6569442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0891036987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6750793457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.738525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2370452880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0437774658203</t>
   </si>
   <si>
     <t xml:space="preserve">99.2522506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">99.3247680664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6963806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.521224975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.518287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.475891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.189033508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.318885803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.234359741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.457778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9078140258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4969711303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1616287231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5966720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.865684509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.034942626953</t>
+    <t xml:space="preserve">99.3247528076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6963729858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.52123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.51830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.475898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.189018249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.318862915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.234352111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.45777130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.907829284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4969863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1616058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5966949462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.865646362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.034950256348</t>
   </si>
   <si>
     <t xml:space="preserve">102.524398803711</t>
   </si>
   <si>
-    <t xml:space="preserve">102.823516845703</t>
+    <t xml:space="preserve">102.823532104492</t>
   </si>
   <si>
     <t xml:space="preserve">104.101547241211</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">105.588081359863</t>
   </si>
   <si>
-    <t xml:space="preserve">104.445991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.86296081543</t>
+    <t xml:space="preserve">104.446006774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.862953186035</t>
   </si>
   <si>
     <t xml:space="preserve">104.300979614258</t>
@@ -863,34 +863,34 @@
     <t xml:space="preserve">105.270843505859</t>
   </si>
   <si>
-    <t xml:space="preserve">105.352416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.494277954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.346054077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.207145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.880844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.787246704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.068031311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0165939331055</t>
+    <t xml:space="preserve">105.352409362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.494262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.346076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.207160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.880836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.787261962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.068016052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0165863037109</t>
   </si>
   <si>
     <t xml:space="preserve">93.8862838745117</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4722747802734</t>
+    <t xml:space="preserve">92.4722595214844</t>
   </si>
   <si>
     <t xml:space="preserve">94.7020568847656</t>
@@ -899,40 +899,40 @@
     <t xml:space="preserve">95.7716369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">95.9347763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7868041992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0587310791016</t>
+    <t xml:space="preserve">95.9347915649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7867965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0587539672852</t>
   </si>
   <si>
     <t xml:space="preserve">94.5751571655273</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9739837646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.904411315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7775039672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.049446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0342407226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3816375732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4360122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1430130004883</t>
+    <t xml:space="preserve">94.9739990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9044036865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7775115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0494384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0342559814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3816299438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.43603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1430053710938</t>
   </si>
   <si>
     <t xml:space="preserve">93.3061828613281</t>
@@ -941,10 +941,10 @@
     <t xml:space="preserve">95.755241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6241836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.8829498291016</t>
+    <t xml:space="preserve">94.6242065429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.882942199707</t>
   </si>
   <si>
     <t xml:space="preserve">95.4816055297852</t>
@@ -953,43 +953,43 @@
     <t xml:space="preserve">95.3903884887695</t>
   </si>
   <si>
-    <t xml:space="preserve">95.0802841186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.1350021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4086380004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2228698730469</t>
+    <t xml:space="preserve">95.0802612304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.1350173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4086303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2228622436523</t>
   </si>
   <si>
     <t xml:space="preserve">95.9376754760742</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9890365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5728149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6324081420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5627822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0918273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5834579467773</t>
+    <t xml:space="preserve">94.9890594482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5728302001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6324234008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5627899169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0918426513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5834655761719</t>
   </si>
   <si>
     <t xml:space="preserve">91.2128448486328</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7999267578125</t>
+    <t xml:space="preserve">92.7999420166016</t>
   </si>
   <si>
     <t xml:space="preserve">93.4201965332031</t>
@@ -998,64 +998,64 @@
     <t xml:space="preserve">93.4931716918945</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9094085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6357498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3107376098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2609024047852</t>
+    <t xml:space="preserve">92.9094009399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6357574462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3107299804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2608795166016</t>
   </si>
   <si>
     <t xml:space="preserve">89.8720092773438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.3098602294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3405456542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2709197998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3621292114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7567901611328</t>
+    <t xml:space="preserve">90.3098220825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3405303955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2709121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3621139526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7567825317383</t>
   </si>
   <si>
     <t xml:space="preserve">92.1249694824219</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3885650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6522064208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5643081665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4764556884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0204010009766</t>
+    <t xml:space="preserve">89.3885803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6521987915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5643539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4764404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0204086303711</t>
   </si>
   <si>
     <t xml:space="preserve">87.5004959106445</t>
   </si>
   <si>
-    <t xml:space="preserve">87.3819198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.5245056152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9349594116211</t>
+    <t xml:space="preserve">87.3819122314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.5245132446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9349746704102</t>
   </si>
   <si>
     <t xml:space="preserve">87.9474258422852</t>
@@ -1064,52 +1064,52 @@
     <t xml:space="preserve">89.306510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3703460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9507675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2243957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.118293762207</t>
+    <t xml:space="preserve">89.3703536987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9507522583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2243804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1183013916016</t>
   </si>
   <si>
     <t xml:space="preserve">90.775016784668</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3040542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9176177978516</t>
+    <t xml:space="preserve">91.3040390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9176254272461</t>
   </si>
   <si>
     <t xml:space="preserve">90.5469818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">89.4980392456055</t>
+    <t xml:space="preserve">89.4980621337891</t>
   </si>
   <si>
     <t xml:space="preserve">92.7452239990234</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7418670654297</t>
+    <t xml:space="preserve">91.7418746948242</t>
   </si>
   <si>
     <t xml:space="preserve">91.431755065918</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0702362060547</t>
+    <t xml:space="preserve">92.0702667236328</t>
   </si>
   <si>
     <t xml:space="preserve">92.4236679077148</t>
   </si>
   <si>
-    <t xml:space="preserve">90.440788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7804641723633</t>
+    <t xml:space="preserve">90.4408187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7804565429688</t>
   </si>
   <si>
     <t xml:space="preserve">92.7908706665039</t>
@@ -1121,94 +1121,94 @@
     <t xml:space="preserve">92.074836730957</t>
   </si>
   <si>
-    <t xml:space="preserve">91.4230270385742</t>
+    <t xml:space="preserve">91.4230651855469</t>
   </si>
   <si>
     <t xml:space="preserve">91.9095993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7541351318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8189926147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.608512878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8104553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2878189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0197525024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7712707519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6990509033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9193878173828</t>
+    <t xml:space="preserve">92.7541427612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8190155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6085052490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8104476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2878265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0197601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7712783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6990814208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9193725585938</t>
   </si>
   <si>
     <t xml:space="preserve">92.0381164550781</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6800765991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7443618774414</t>
+    <t xml:space="preserve">91.6801071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7443466186523</t>
   </si>
   <si>
     <t xml:space="preserve">92.9928283691406</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9389801025391</t>
+    <t xml:space="preserve">94.9389877319336</t>
   </si>
   <si>
     <t xml:space="preserve">96.7015151977539</t>
   </si>
   <si>
-    <t xml:space="preserve">94.4065246582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6635818481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4334716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9940643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4713973999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6354141235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9634475708008</t>
+    <t xml:space="preserve">94.4065093994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.66357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.433464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9940414428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4714126586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6354217529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9634323120117</t>
   </si>
   <si>
     <t xml:space="preserve">89.5044403076172</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4224548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8814392089844</t>
+    <t xml:space="preserve">90.4224624633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8814544677734</t>
   </si>
   <si>
     <t xml:space="preserve">91.3404388427734</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7969818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5589218139648</t>
+    <t xml:space="preserve">87.7969665527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5589141845703</t>
   </si>
   <si>
     <t xml:space="preserve">89.8165512084961</t>
@@ -1217,292 +1217,292 @@
     <t xml:space="preserve">92.2033538818359</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6886444091797</t>
+    <t xml:space="preserve">90.6886596679688</t>
   </si>
   <si>
     <t xml:space="preserve">93.1397018432617</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7174301147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0944213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0931854248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8006591796875</t>
+    <t xml:space="preserve">92.7174224853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0944290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0931625366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8006820678711</t>
   </si>
   <si>
     <t xml:space="preserve">93.4885482788086</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0209655761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1494750976562</t>
+    <t xml:space="preserve">94.0209808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1495056152344</t>
   </si>
   <si>
     <t xml:space="preserve">94.4616165161133</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4500732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.651008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7433547973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4824066162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.0920867919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6856384277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.015869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5493545532227</t>
+    <t xml:space="preserve">93.450065612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6510009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7433776855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4823989868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.0920715332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6856155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0158767700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5493621826172</t>
   </si>
   <si>
     <t xml:space="preserve">98.8634414672852</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3830718994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1267395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4939193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.600135803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.9165725708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.360000610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.212181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.784927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.711013793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.727195739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.202926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.269889831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.008918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.429214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.653244018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.988143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.064331054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.341484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.265251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.135925292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.819526672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.893432617188</t>
+    <t xml:space="preserve">98.3830642700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1267242431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4939270019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.600173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.9165649414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.359977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.212173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.784912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.710990905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.727203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.202949523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.269897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.008903503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.429260253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.653251647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.988105773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.064353942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.341468811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.265266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.135917663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.819534301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.893447875977</t>
   </si>
   <si>
     <t xml:space="preserve">112.886497497559</t>
   </si>
   <si>
-    <t xml:space="preserve">114.105895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.269866943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.454612731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.507743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.061996459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.376106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.710975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.486953735352</t>
+    <t xml:space="preserve">114.10587310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.269874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.454620361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.50772857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.062019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.376098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.710960388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.486946105957</t>
   </si>
   <si>
     <t xml:space="preserve">117.394584655762</t>
   </si>
   <si>
-    <t xml:space="preserve">117.320663452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.413047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.322998046875</t>
+    <t xml:space="preserve">117.320678710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.413055419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.322975158691</t>
   </si>
   <si>
     <t xml:space="preserve">118.115119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">120.092018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.13591003418</t>
+    <t xml:space="preserve">120.092025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.135902404785</t>
   </si>
   <si>
     <t xml:space="preserve">117.339141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">119.61164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.156661987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473106384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.274459838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.292961120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.586235046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.549087524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.248550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.616859436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.229949951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.270408630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.787322998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.78076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.049591064453</t>
+    <t xml:space="preserve">119.611625671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623207092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.156677246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473091125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.274482727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.292953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.586242675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.549095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.248542785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.616836547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.229972839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.270393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.787338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.780769348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.049621582031</t>
   </si>
   <si>
     <t xml:space="preserve">116.009170532227</t>
   </si>
   <si>
-    <t xml:space="preserve">113.017890930176</t>
+    <t xml:space="preserve">113.01789855957</t>
   </si>
   <si>
     <t xml:space="preserve">104.620048522949</t>
   </si>
   <si>
-    <t xml:space="preserve">108.057235717773</t>
+    <t xml:space="preserve">108.05721282959</t>
   </si>
   <si>
     <t xml:space="preserve">112.441947937012</t>
   </si>
   <si>
-    <t xml:space="preserve">111.104225158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.306442260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.507507324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.881294250488</t>
+    <t xml:space="preserve">111.104232788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.306411743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.507514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.881271362305</t>
   </si>
   <si>
     <t xml:space="preserve">110.937004089355</t>
   </si>
   <si>
-    <t xml:space="preserve">115.135948181152</t>
+    <t xml:space="preserve">115.135940551758</t>
   </si>
   <si>
     <t xml:space="preserve">106.700927734375</t>
   </si>
   <si>
-    <t xml:space="preserve">110.565437316895</t>
+    <t xml:space="preserve">110.5654296875</t>
   </si>
   <si>
     <t xml:space="preserve">112.609176635742</t>
   </si>
   <si>
-    <t xml:space="preserve">117.123908996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.597145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.056159973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.120643615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.768684387207</t>
+    <t xml:space="preserve">117.123924255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.597152709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.056182861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.120651245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.768699645996</t>
   </si>
   <si>
     <t xml:space="preserve">105.270317077637</t>
   </si>
   <si>
-    <t xml:space="preserve">105.77197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.844108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.680198669434</t>
+    <t xml:space="preserve">105.771957397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.844116210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.680191040039</t>
   </si>
   <si>
     <t xml:space="preserve">117.365455627441</t>
@@ -1517,34 +1517,34 @@
     <t xml:space="preserve">120.300987243652</t>
   </si>
   <si>
-    <t xml:space="preserve">122.623443603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.552368164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.339263916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.661682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.9130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.448593139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.628936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.377563476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.235473632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.285736083984</t>
+    <t xml:space="preserve">122.623374938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.552383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.339248657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.661666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.913040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.448577880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.62890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.377532958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.235488891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.285751342773</t>
   </si>
   <si>
     <t xml:space="preserve">139.67919921875</t>
@@ -1553,121 +1553,121 @@
     <t xml:space="preserve">140.218002319336</t>
   </si>
   <si>
-    <t xml:space="preserve">136.557876586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.232162475586</t>
+    <t xml:space="preserve">136.557846069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.232192993164</t>
   </si>
   <si>
     <t xml:space="preserve">132.117446899414</t>
   </si>
   <si>
-    <t xml:space="preserve">129.367706298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.272644042969</t>
+    <t xml:space="preserve">129.367691040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.272598266602</t>
   </si>
   <si>
     <t xml:space="preserve">135.405960083008</t>
   </si>
   <si>
-    <t xml:space="preserve">133.492309570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.154571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.183013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.263870239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.833312988281</t>
+    <t xml:space="preserve">133.492294311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.154586791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.182998657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.263885498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.83332824707</t>
   </si>
   <si>
     <t xml:space="preserve">135.889297485352</t>
   </si>
   <si>
-    <t xml:space="preserve">135.347778320312</t>
+    <t xml:space="preserve">135.347793579102</t>
   </si>
   <si>
     <t xml:space="preserve">136.561569213867</t>
   </si>
   <si>
-    <t xml:space="preserve">133.050888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.91178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.942642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.689575195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.399230957031</t>
+    <t xml:space="preserve">133.050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.911758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.942657470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.689590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.399215698242</t>
   </si>
   <si>
     <t xml:space="preserve">126.347007751465</t>
   </si>
   <si>
-    <t xml:space="preserve">121.771919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.766220092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.560768127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.589721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.95484161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.180824279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.002456665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.873664855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.143516540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.554328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.846611022949</t>
+    <t xml:space="preserve">121.771903991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.76619720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.56078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.589736938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.954833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.180847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.002487182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.873687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.143493652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.554290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.846618652344</t>
   </si>
   <si>
     <t xml:space="preserve">120.016555786133</t>
   </si>
   <si>
-    <t xml:space="preserve">116.972747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.142349243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.077941894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.011627197266</t>
+    <t xml:space="preserve">116.97274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.142364501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.077972412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.011657714844</t>
   </si>
   <si>
     <t xml:space="preserve">131.650360107422</t>
   </si>
   <si>
-    <t xml:space="preserve">132.322616577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.984573364258</t>
+    <t xml:space="preserve">132.322647094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.984603881836</t>
   </si>
   <si>
     <t xml:space="preserve">130.455230712891</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">134.488754272461</t>
   </si>
   <si>
-    <t xml:space="preserve">134.619476318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.412185668945</t>
+    <t xml:space="preserve">134.61946105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.412170410156</t>
   </si>
   <si>
     <t xml:space="preserve">136.37483215332</t>
@@ -1691,106 +1691,106 @@
     <t xml:space="preserve">135.441146850586</t>
   </si>
   <si>
-    <t xml:space="preserve">138.484985351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.055480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.148849487305</t>
+    <t xml:space="preserve">138.484954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.055465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.148834228516</t>
   </si>
   <si>
     <t xml:space="preserve">136.225402832031</t>
   </si>
   <si>
-    <t xml:space="preserve">135.123672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.430847167969</t>
+    <t xml:space="preserve">135.12370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.43083190918</t>
   </si>
   <si>
     <t xml:space="preserve">134.208648681641</t>
   </si>
   <si>
-    <t xml:space="preserve">135.179718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.125595092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.833282470703</t>
+    <t xml:space="preserve">135.179733276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.833267211914</t>
   </si>
   <si>
     <t xml:space="preserve">135.795944213867</t>
   </si>
   <si>
-    <t xml:space="preserve">131.239501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.355331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.448768615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.793258666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.334014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.802772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.47314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.854995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.155662536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.717796325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.80086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.875579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.736457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.221969604492</t>
+    <t xml:space="preserve">131.239547729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.355377197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.448707580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.793273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.334037780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.802780151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.473129272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.854957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.155685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.717781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.800880432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.875564575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.736465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.221984863281</t>
   </si>
   <si>
     <t xml:space="preserve">119.245346069336</t>
   </si>
   <si>
-    <t xml:space="preserve">119.733642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.409790039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.578819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.480354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.071723937988</t>
+    <t xml:space="preserve">119.733673095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.409797668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.578826904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.480361938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.071746826172</t>
   </si>
   <si>
     <t xml:space="preserve">118.174758911133</t>
   </si>
   <si>
-    <t xml:space="preserve">118.062088012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.20777130127</t>
+    <t xml:space="preserve">118.062072753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.207786560059</t>
   </si>
   <si>
     <t xml:space="preserve">117.42350769043</t>
@@ -1799,16 +1799,16 @@
     <t xml:space="preserve">119.170196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">117.479858398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.446868896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.052421569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.832130432129</t>
+    <t xml:space="preserve">117.479850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.446846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.052436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.832122802734</t>
   </si>
   <si>
     <t xml:space="preserve">119.30167388916</t>
@@ -1820,37 +1820,37 @@
     <t xml:space="preserve">118.625518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">117.799118041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.686950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.592552185059</t>
+    <t xml:space="preserve">117.799140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.686965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.592529296875</t>
   </si>
   <si>
     <t xml:space="preserve">117.554969787598</t>
   </si>
   <si>
-    <t xml:space="preserve">119.639747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.710289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.729095458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.611831665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.597618103027</t>
+    <t xml:space="preserve">119.639755249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.710296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.729080200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.611854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.597633361816</t>
   </si>
   <si>
     <t xml:space="preserve">120.334671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">119.583389282227</t>
+    <t xml:space="preserve">119.58341217041</t>
   </si>
   <si>
     <t xml:space="preserve">120.785415649414</t>
@@ -1862,52 +1862,52 @@
     <t xml:space="preserve">116.709785461426</t>
   </si>
   <si>
-    <t xml:space="preserve">115.977317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.747337341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.108779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.424034118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.33519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.546333312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.231651306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.869697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.066635131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.348373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.150924682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.122482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.615386962891</t>
+    <t xml:space="preserve">115.97730255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.747352600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.108787536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.424011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.335205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.546356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.231628417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.86971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.06664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.34839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.150909423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.12247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.615371704102</t>
   </si>
   <si>
     <t xml:space="preserve">111.939239501953</t>
   </si>
   <si>
-    <t xml:space="preserve">113.347862243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.563591003418</t>
+    <t xml:space="preserve">113.347854614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.563598632812</t>
   </si>
   <si>
     <t xml:space="preserve">106.229591369629</t>
@@ -1916,145 +1916,145 @@
     <t xml:space="preserve">105.835151672363</t>
   </si>
   <si>
-    <t xml:space="preserve">106.530075073242</t>
+    <t xml:space="preserve">106.53010559082</t>
   </si>
   <si>
     <t xml:space="preserve">105.666114807129</t>
   </si>
   <si>
-    <t xml:space="preserve">105.684913635254</t>
+    <t xml:space="preserve">105.684906005859</t>
   </si>
   <si>
     <t xml:space="preserve">106.511299133301</t>
   </si>
   <si>
-    <t xml:space="preserve">118.13720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.221481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.202682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.573234558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.104209899902</t>
+    <t xml:space="preserve">118.137214660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.221473693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.202690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.573249816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.104194641113</t>
   </si>
   <si>
     <t xml:space="preserve">115.319946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">112.939086914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.978363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.354797363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.221054077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.504501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.16438293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.35920715332</t>
+    <t xml:space="preserve">112.939102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.97834777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.35481262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.221038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.504486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.164367675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.359199523926</t>
   </si>
   <si>
     <t xml:space="preserve">112.901306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">115.338829040527</t>
+    <t xml:space="preserve">115.338851928711</t>
   </si>
   <si>
     <t xml:space="preserve">113.449279785156</t>
   </si>
   <si>
-    <t xml:space="preserve">114.318466186523</t>
+    <t xml:space="preserve">114.318481445312</t>
   </si>
   <si>
     <t xml:space="preserve">115.830123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">114.828651428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.846076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.447799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.469635009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.151351928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.651443481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.841873168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.353500366211</t>
+    <t xml:space="preserve">114.828659057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.846092224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.447807312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.469627380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.151344299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.651466369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.841850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.353492736816</t>
   </si>
   <si>
     <t xml:space="preserve">124.84334564209</t>
   </si>
   <si>
-    <t xml:space="preserve">126.41170501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.327499389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.948089599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.267837524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.737289428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.964050292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.416061401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.583198547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.471267700195</t>
+    <t xml:space="preserve">126.411666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.327423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.948120117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.267868041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.737335205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.96403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.416076660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.583206176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.471298217773</t>
   </si>
   <si>
     <t xml:space="preserve">129.113754272461</t>
   </si>
   <si>
-    <t xml:space="preserve">126.827377319336</t>
+    <t xml:space="preserve">126.827392578125</t>
   </si>
   <si>
     <t xml:space="preserve">126.392753601074</t>
   </si>
   <si>
-    <t xml:space="preserve">127.904441833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.016357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.603546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.118347167969</t>
+    <t xml:space="preserve">127.904418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.016319274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.603485107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.11833190918</t>
   </si>
   <si>
     <t xml:space="preserve">139.978713989258</t>
@@ -2063,97 +2063,97 @@
     <t xml:space="preserve">144.645950317383</t>
   </si>
   <si>
-    <t xml:space="preserve">146.11979675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.047164916992</t>
+    <t xml:space="preserve">146.119781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.047134399414</t>
   </si>
   <si>
     <t xml:space="preserve">147.839263916016</t>
   </si>
   <si>
-    <t xml:space="preserve">152.71435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.833587646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.076324462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.760955810547</t>
+    <t xml:space="preserve">152.714370727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.833633422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.076309204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.760986328125</t>
   </si>
   <si>
     <t xml:space="preserve">164.032821655273</t>
   </si>
   <si>
-    <t xml:space="preserve">164.996520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.992111206055</t>
+    <t xml:space="preserve">164.996505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.992156982422</t>
   </si>
   <si>
     <t xml:space="preserve">163.125854492188</t>
   </si>
   <si>
-    <t xml:space="preserve">161.349655151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.804611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.720260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.962936401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.137390136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.704254150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.461547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.814697265625</t>
+    <t xml:space="preserve">161.349670410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.804656982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.72021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.962966918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.137405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.704284667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.461578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.814712524414</t>
   </si>
   <si>
     <t xml:space="preserve">159.157775878906</t>
   </si>
   <si>
-    <t xml:space="preserve">158.008773803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.81950378418</t>
+    <t xml:space="preserve">158.0087890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.819534301758</t>
   </si>
   <si>
     <t xml:space="preserve">164.560836791992</t>
   </si>
   <si>
-    <t xml:space="preserve">159.793960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.161392211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.831954956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.856857299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.932159423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.205215454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.964920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.970809936523</t>
+    <t xml:space="preserve">159.793975830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.161376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.832000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.856842041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.932144165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.20524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.964935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.970825195312</t>
   </si>
   <si>
     <t xml:space="preserve">159.907928466797</t>
@@ -2162,70 +2162,70 @@
     <t xml:space="preserve">162.376815795898</t>
   </si>
   <si>
-    <t xml:space="preserve">162.756637573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.958343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.33821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.617156982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.884368896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.409591674805</t>
+    <t xml:space="preserve">162.756622314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.958389282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.338165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.6171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.884338378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.409530639648</t>
   </si>
   <si>
     <t xml:space="preserve">165.890213012695</t>
   </si>
   <si>
-    <t xml:space="preserve">162.661682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.326416015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.741622924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.931533813477</t>
+    <t xml:space="preserve">162.661666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.326385498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.741607666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.93147277832</t>
   </si>
   <si>
     <t xml:space="preserve">149.08283996582</t>
   </si>
   <si>
-    <t xml:space="preserve">147.183670043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.75341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.133270263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.462631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.474426269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.993743896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.892883300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.602157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.792022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.399765014648</t>
+    <t xml:space="preserve">147.183685302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.753372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.133193969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.462615966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.474487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.993728637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.892929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.602127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.792068481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.399749755859</t>
   </si>
   <si>
     <t xml:space="preserve">151.456741333008</t>
@@ -2234,19 +2234,19 @@
     <t xml:space="preserve">148.703002929688</t>
   </si>
   <si>
-    <t xml:space="preserve">145.284530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.234085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.854263305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.904678344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.424011230469</t>
+    <t xml:space="preserve">145.284515380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.234100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.854293823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.904708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.424026489258</t>
   </si>
   <si>
     <t xml:space="preserve">148.323135375977</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">149.842468261719</t>
   </si>
   <si>
-    <t xml:space="preserve">150.412185668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.652542114258</t>
+    <t xml:space="preserve">150.412231445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.652526855469</t>
   </si>
   <si>
     <t xml:space="preserve">148.513076782227</t>
   </si>
   <si>
-    <t xml:space="preserve">146.803802490234</t>
+    <t xml:space="preserve">146.803833007812</t>
   </si>
   <si>
     <t xml:space="preserve">143.955139160156</t>
@@ -2273,16 +2273,16 @@
     <t xml:space="preserve">140.346740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">141.486236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.575286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.044174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.121459960938</t>
+    <t xml:space="preserve">141.486221313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.575271606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.044189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.121444702148</t>
   </si>
   <si>
     <t xml:space="preserve">152.691192626953</t>
@@ -2291,61 +2291,61 @@
     <t xml:space="preserve">153.071014404297</t>
   </si>
   <si>
-    <t xml:space="preserve">151.836563110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.69352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.220916748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.457214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.92985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.979919433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.175567626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.702911376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.984588623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.361785888672</t>
+    <t xml:space="preserve">151.836547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.693588256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.220932006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.457244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.929840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.175537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.702926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.984603881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.361755371094</t>
   </si>
   <si>
     <t xml:space="preserve">156.748306274414</t>
   </si>
   <si>
-    <t xml:space="preserve">157.225601196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.839080810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.366470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.803085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.640396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.876647949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.076965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.000305175781</t>
+    <t xml:space="preserve">157.225631713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.839096069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.366500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.803115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.640380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.876663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.07698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.000335693359</t>
   </si>
   <si>
     <t xml:space="preserve">176.365737915039</t>
@@ -2357,43 +2357,43 @@
     <t xml:space="preserve">175.840682983398</t>
   </si>
   <si>
-    <t xml:space="preserve">176.222518920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.227233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.270248413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.038665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.800018310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.265548706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.243667602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.527694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.093444824219</t>
+    <t xml:space="preserve">176.222534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.227203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.270263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.038635253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.799987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.265594482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.243698120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.527709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.093399047852</t>
   </si>
   <si>
     <t xml:space="preserve">184.432250976562</t>
   </si>
   <si>
-    <t xml:space="preserve">185.291427612305</t>
+    <t xml:space="preserve">185.291397094727</t>
   </si>
   <si>
     <t xml:space="preserve">186.102828979492</t>
   </si>
   <si>
-    <t xml:space="preserve">187.773361206055</t>
+    <t xml:space="preserve">187.7734375</t>
   </si>
   <si>
     <t xml:space="preserve">189.491744995117</t>
@@ -2402,43 +2402,43 @@
     <t xml:space="preserve">188.9189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">189.969009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.775756835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.069183349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.6826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.446334838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.828201293945</t>
+    <t xml:space="preserve">189.969024658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.775772094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.06916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.682678222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.446319580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.828186035156</t>
   </si>
   <si>
     <t xml:space="preserve">188.584854125977</t>
   </si>
   <si>
-    <t xml:space="preserve">187.677932739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.296112060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.591873168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.973724365234</t>
+    <t xml:space="preserve">187.677978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.296096801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.591857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.973709106445</t>
   </si>
   <si>
     <t xml:space="preserve">193.882965087891</t>
   </si>
   <si>
-    <t xml:space="preserve">195.983123779297</t>
+    <t xml:space="preserve">195.983139038086</t>
   </si>
   <si>
     <t xml:space="preserve">197.415069580078</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">196.269515991211</t>
   </si>
   <si>
-    <t xml:space="preserve">199.515213012695</t>
+    <t xml:space="preserve">199.515197753906</t>
   </si>
   <si>
     <t xml:space="preserve">197.319595336914</t>
   </si>
   <si>
-    <t xml:space="preserve">196.842269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.987777709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.152145385742</t>
+    <t xml:space="preserve">196.84228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.987838745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.152160644531</t>
   </si>
   <si>
     <t xml:space="preserve">213.738983154297</t>
@@ -2468,88 +2468,88 @@
     <t xml:space="preserve">212.975341796875</t>
   </si>
   <si>
-    <t xml:space="preserve">213.929962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.321182250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.703033447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.366577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.498077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.564331054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.918014526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.930206298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.534744262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.067855834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.205459594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.444107055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.156631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.29426574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.048568725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.060821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.18620300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.736709594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.982360839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.269836425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.994522094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.461471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.970138549805</t>
+    <t xml:space="preserve">213.929946899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.321151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.703048706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.366592407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.498092651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.564315795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.918045043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.930191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.534774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.06787109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.205490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.444061279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.156600952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.294250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.048614501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.060745239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.186218261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.736694335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.982376098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.269805908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.994567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.46142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.970153808594</t>
   </si>
   <si>
     <t xml:space="preserve">198.058929443359</t>
   </si>
   <si>
-    <t xml:space="preserve">196.621627807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.44743347168</t>
+    <t xml:space="preserve">196.621643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.447402954102</t>
   </si>
   <si>
     <t xml:space="preserve">190.920379638672</t>
   </si>
   <si>
-    <t xml:space="preserve">191.495315551758</t>
+    <t xml:space="preserve">191.495330810547</t>
   </si>
   <si>
     <t xml:space="preserve">187.902069091797</t>
@@ -2558,22 +2558,22 @@
     <t xml:space="preserve">187.087600708008</t>
   </si>
   <si>
-    <t xml:space="preserve">189.531036376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.626815795898</t>
+    <t xml:space="preserve">189.530990600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.626800537109</t>
   </si>
   <si>
     <t xml:space="preserve">187.997894287109</t>
   </si>
   <si>
-    <t xml:space="preserve">190.632934570312</t>
+    <t xml:space="preserve">190.632965087891</t>
   </si>
   <si>
     <t xml:space="preserve">190.537139892578</t>
   </si>
   <si>
-    <t xml:space="preserve">185.889862060547</t>
+    <t xml:space="preserve">185.889846801758</t>
   </si>
   <si>
     <t xml:space="preserve">182.152908325195</t>
@@ -2582,61 +2582,61 @@
     <t xml:space="preserve">188.572814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">193.651245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.770538330078</t>
+    <t xml:space="preserve">193.651260375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.770584106445</t>
   </si>
   <si>
     <t xml:space="preserve">185.410766601562</t>
   </si>
   <si>
-    <t xml:space="preserve">190.393371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.237411499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.501434326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.172149658203</t>
+    <t xml:space="preserve">190.39338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.237457275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.501403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.172180175781</t>
   </si>
   <si>
     <t xml:space="preserve">196.525817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">193.555374145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.938720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">194.992721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.47184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.442245483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.729675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.358612060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.538009643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.921340942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.987533569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.849914550781</t>
+    <t xml:space="preserve">193.555450439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.938705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194.992706298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.471817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.442230224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.729690551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.358627319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.538055419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.921310424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.987548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.849899291992</t>
   </si>
   <si>
     <t xml:space="preserve">208.2158203125</t>
@@ -2648,82 +2648,82 @@
     <t xml:space="preserve">210.802947998047</t>
   </si>
   <si>
-    <t xml:space="preserve">207.353424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.006790161133</t>
+    <t xml:space="preserve">207.353439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.006774902344</t>
   </si>
   <si>
     <t xml:space="preserve">217.989410400391</t>
   </si>
   <si>
-    <t xml:space="preserve">215.593933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.977172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.90576171875</t>
+    <t xml:space="preserve">215.593902587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.977188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.905807495117</t>
   </si>
   <si>
     <t xml:space="preserve">220.768173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">218.892791748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.161636352539</t>
+    <t xml:space="preserve">218.892776489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.161651611328</t>
   </si>
   <si>
     <t xml:space="preserve">219.277481079102</t>
   </si>
   <si>
-    <t xml:space="preserve">221.297103881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.200958251953</t>
+    <t xml:space="preserve">221.297119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.200942993164</t>
   </si>
   <si>
     <t xml:space="preserve">223.316787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">224.663238525391</t>
+    <t xml:space="preserve">224.663208007812</t>
   </si>
   <si>
     <t xml:space="preserve">223.509094238281</t>
   </si>
   <si>
-    <t xml:space="preserve">224.182373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.067596435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.162704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.064376831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.238143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.198806762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.756225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.351852416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203.985794067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.313568115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.640365600586</t>
+    <t xml:space="preserve">224.182357788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.067565917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.162719726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.064407348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.238128662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.198822021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.756210327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.351867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203.985763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.313583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.640380859375</t>
   </si>
   <si>
     <t xml:space="preserve">213.50700378418</t>
@@ -2732,16 +2732,16 @@
     <t xml:space="preserve">212.929962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">229.279571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">237.646789550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.259948730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">225.624969482422</t>
+    <t xml:space="preserve">229.279602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.646759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.25993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">225.625</t>
   </si>
   <si>
     <t xml:space="preserve">224.567031860352</t>
@@ -2753,22 +2753,22 @@
     <t xml:space="preserve">235.819458007812</t>
   </si>
   <si>
-    <t xml:space="preserve">235.43473815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.53092956543</t>
+    <t xml:space="preserve">235.434768676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.530914306641</t>
   </si>
   <si>
     <t xml:space="preserve">228.317840576172</t>
   </si>
   <si>
-    <t xml:space="preserve">227.644638061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220.527725219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.662170410156</t>
+    <t xml:space="preserve">227.644607543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.527709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.662139892578</t>
   </si>
   <si>
     <t xml:space="preserve">218.12336730957</t>
@@ -2777,22 +2777,22 @@
     <t xml:space="preserve">219.373641967773</t>
   </si>
   <si>
-    <t xml:space="preserve">212.256713867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.19775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.544189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.409790039062</t>
+    <t xml:space="preserve">212.256729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.197723388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.544204711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.409759521484</t>
   </si>
   <si>
     <t xml:space="preserve">211.102661132812</t>
   </si>
   <si>
-    <t xml:space="preserve">209.948577880859</t>
+    <t xml:space="preserve">209.948532104492</t>
   </si>
   <si>
     <t xml:space="preserve">207.15950012207</t>
@@ -2801,28 +2801,28 @@
     <t xml:space="preserve">200.042572021484</t>
   </si>
   <si>
-    <t xml:space="preserve">201.869857788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.813049316406</t>
+    <t xml:space="preserve">201.869888305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.813079833984</t>
   </si>
   <si>
     <t xml:space="preserve">208.121246337891</t>
   </si>
   <si>
-    <t xml:space="preserve">207.928909301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.986831665039</t>
+    <t xml:space="preserve">207.92887878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.98681640625</t>
   </si>
   <si>
     <t xml:space="preserve">208.794479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">212.352905273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.101593017578</t>
+    <t xml:space="preserve">212.352920532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.101623535156</t>
   </si>
   <si>
     <t xml:space="preserve">202.63932800293</t>
@@ -2837,43 +2837,43 @@
     <t xml:space="preserve">202.927841186523</t>
   </si>
   <si>
-    <t xml:space="preserve">200.234939575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.959442138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.076324462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.525741577148</t>
+    <t xml:space="preserve">200.234954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.959411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.076293945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.525726318359</t>
   </si>
   <si>
     <t xml:space="preserve">206.593139648438</t>
   </si>
   <si>
-    <t xml:space="preserve">204.85383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.892044067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203.404373168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.916763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.626861572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">216.256088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.130233764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.806625366211</t>
+    <t xml:space="preserve">204.853820800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.891998291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203.404388427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.916717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.626876831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">216.256072998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.130218505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.806640625</t>
   </si>
   <si>
     <t xml:space="preserve">221.957183837891</t>
@@ -2882,109 +2882,109 @@
     <t xml:space="preserve">223.116744995117</t>
   </si>
   <si>
-    <t xml:space="preserve">229.39762878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.910003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">233.262802124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">232.393157958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.233612060547</t>
+    <t xml:space="preserve">229.397613525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.909973144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">233.262786865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.393173217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.23356628418</t>
   </si>
   <si>
     <t xml:space="preserve">237.417831420898</t>
   </si>
   <si>
-    <t xml:space="preserve">236.161697387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.312240600586</t>
+    <t xml:space="preserve">236.161682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.312225341797</t>
   </si>
   <si>
     <t xml:space="preserve">243.408874511719</t>
   </si>
   <si>
-    <t xml:space="preserve">246.307739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.332443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.651611328125</t>
+    <t xml:space="preserve">246.307723999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.332458496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.651550292969</t>
   </si>
   <si>
     <t xml:space="preserve">249.882995605469</t>
   </si>
   <si>
-    <t xml:space="preserve">251.525695800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.105499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.294281005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.004348754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.622299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.008834838867</t>
+    <t xml:space="preserve">251.525680541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.105484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.294235229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.004333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.622344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.008850097656</t>
   </si>
   <si>
     <t xml:space="preserve">250.656036376953</t>
   </si>
   <si>
-    <t xml:space="preserve">253.844802856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">257.468444824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260.802093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266.020111083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.489685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">276.890777587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.006622314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.668395996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.305541992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.691986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.295349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.556030273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.796478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.347091674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.869506835938</t>
+    <t xml:space="preserve">253.844772338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">257.468414306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260.802062988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266.020050048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.48974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">276.890808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.006561279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.668365478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.305480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.692047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.295379638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.555969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.796463012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.347076416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.869537353516</t>
   </si>
   <si>
     <t xml:space="preserve">269.595397949219</t>
@@ -2993,10 +2993,10 @@
     <t xml:space="preserve">268.822357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">265.730163574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.536895751953</t>
+    <t xml:space="preserve">265.730194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.536926269531</t>
   </si>
   <si>
     <t xml:space="preserve">264.957153320312</t>
@@ -3008,34 +3008,34 @@
     <t xml:space="preserve">265.102111816406</t>
   </si>
   <si>
-    <t xml:space="preserve">263.942535400391</t>
+    <t xml:space="preserve">263.942596435547</t>
   </si>
   <si>
     <t xml:space="preserve">258.579620361328</t>
   </si>
   <si>
-    <t xml:space="preserve">266.454925537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">267.4052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">281.854400634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">277.005645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.290374755859</t>
+    <t xml:space="preserve">266.454895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">267.405242919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281.854339599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">277.005676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.290435791016</t>
   </si>
   <si>
     <t xml:space="preserve">263.623291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">271.090209960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.599578857422</t>
+    <t xml:space="preserve">271.090179443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.599517822266</t>
   </si>
   <si>
     <t xml:space="preserve">272.108459472656</t>
@@ -3044,82 +3044,82 @@
     <t xml:space="preserve">280.642181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">281.466430664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">282.630126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.532867431641</t>
+    <t xml:space="preserve">281.466491699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">282.630157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.532836914062</t>
   </si>
   <si>
     <t xml:space="preserve">280.205780029297</t>
   </si>
   <si>
-    <t xml:space="preserve">278.411804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">284.084747314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.769378662109</t>
+    <t xml:space="preserve">278.411834716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">284.084777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.769348144531</t>
   </si>
   <si>
     <t xml:space="preserve">275.066131591797</t>
   </si>
   <si>
-    <t xml:space="preserve">270.750823974609</t>
+    <t xml:space="preserve">270.750885009766</t>
   </si>
   <si>
     <t xml:space="preserve">268.471984863281</t>
   </si>
   <si>
-    <t xml:space="preserve">271.817565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.611206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.253967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270.847778320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.484313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.720947265625</t>
+    <t xml:space="preserve">271.817626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.611175537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.253936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270.847808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.484344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.720916748047</t>
   </si>
   <si>
     <t xml:space="preserve">284.763580322266</t>
   </si>
   <si>
-    <t xml:space="preserve">298.291351318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.455078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.576171875</t>
+    <t xml:space="preserve">298.291442871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.455017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.576141357422</t>
   </si>
   <si>
     <t xml:space="preserve">299.552062988281</t>
   </si>
   <si>
-    <t xml:space="preserve">298.679321289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.843017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.946166992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.721923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.049713134766</t>
+    <t xml:space="preserve">298.679260253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.842987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.946197509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.721954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.049682617188</t>
   </si>
   <si>
     <t xml:space="preserve">312.740539550781</t>
@@ -3137,58 +3137,58 @@
     <t xml:space="preserve">311.625305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">318.122528076172</t>
+    <t xml:space="preserve">318.122589111328</t>
   </si>
   <si>
     <t xml:space="preserve">315.213317871094</t>
   </si>
   <si>
-    <t xml:space="preserve">309.879699707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.825073242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.916198730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.837493896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.231567382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.467803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.631439208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.661743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.425140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.4736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.667266845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.854644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">288.836456298828</t>
+    <t xml:space="preserve">309.879791259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.825042724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.916168212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.837524414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.231506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.4677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.631469726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.661712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.425109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.473663330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.667236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.854705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">288.836486816406</t>
   </si>
   <si>
     <t xml:space="preserve">289.369812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">287.284912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">285.539398193359</t>
+    <t xml:space="preserve">287.284881591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">285.539367675781</t>
   </si>
   <si>
     <t xml:space="preserve">283.84228515625</t>
@@ -3200,16 +3200,16 @@
     <t xml:space="preserve">297.298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">298.369171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.812530517578</t>
+    <t xml:space="preserve">298.369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.812561035156</t>
   </si>
   <si>
     <t xml:space="preserve">303.574676513672</t>
   </si>
   <si>
-    <t xml:space="preserve">312.428955078125</t>
+    <t xml:space="preserve">312.429016113281</t>
   </si>
   <si>
     <t xml:space="preserve">316.126251220703</t>
@@ -3218,22 +3218,22 @@
     <t xml:space="preserve">309.996429443359</t>
   </si>
   <si>
-    <t xml:space="preserve">311.358612060547</t>
+    <t xml:space="preserve">311.358642578125</t>
   </si>
   <si>
     <t xml:space="preserve">309.412628173828</t>
   </si>
   <si>
-    <t xml:space="preserve">314.228973388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.234100341797</t>
+    <t xml:space="preserve">314.229034423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.234039306641</t>
   </si>
   <si>
     <t xml:space="preserve">299.925933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">294.185241699219</t>
+    <t xml:space="preserve">294.185272216797</t>
   </si>
   <si>
     <t xml:space="preserve">297.250152587891</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">295.888000488281</t>
   </si>
   <si>
-    <t xml:space="preserve">304.596313476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.963806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.688323974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.585601806641</t>
+    <t xml:space="preserve">304.596282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.963836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.688262939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.585571289062</t>
   </si>
   <si>
     <t xml:space="preserve">306.299011230469</t>
@@ -3263,85 +3263,85 @@
     <t xml:space="preserve">301.96923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">300.412475585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.342163085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.796020507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.990631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.104309082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.601837158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.845092773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.082977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.883697509766</t>
+    <t xml:space="preserve">300.412445068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.342132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.796081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.990661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.104248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.601928710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.845123291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.083038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.883666992188</t>
   </si>
   <si>
     <t xml:space="preserve">327.656280517578</t>
   </si>
   <si>
-    <t xml:space="preserve">324.445404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.612762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320.066925048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.348114013672</t>
+    <t xml:space="preserve">324.445495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.612884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320.066986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.348083496094</t>
   </si>
   <si>
     <t xml:space="preserve">330.721252441406</t>
   </si>
   <si>
-    <t xml:space="preserve">329.651000976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323.375183105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.758941650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327.315826416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.883239746094</t>
+    <t xml:space="preserve">329.650939941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.375152587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.758972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327.315704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.88330078125</t>
   </si>
   <si>
     <t xml:space="preserve">330.380706787109</t>
   </si>
   <si>
-    <t xml:space="preserve">332.521331787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.580688476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">326.245483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.710357666016</t>
+    <t xml:space="preserve">332.521270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.580718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326.245422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.710296630859</t>
   </si>
   <si>
     <t xml:space="preserve">334.515930175781</t>
   </si>
   <si>
-    <t xml:space="preserve">343.759368896484</t>
+    <t xml:space="preserve">343.759338378906</t>
   </si>
   <si>
     <t xml:space="preserve">342.543182373047</t>
@@ -3350,13 +3350,13 @@
     <t xml:space="preserve">347.456756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">347.748657226562</t>
+    <t xml:space="preserve">347.748687744141</t>
   </si>
   <si>
     <t xml:space="preserve">352.710968017578</t>
   </si>
   <si>
-    <t xml:space="preserve">354.802856445312</t>
+    <t xml:space="preserve">354.802886962891</t>
   </si>
   <si>
     <t xml:space="preserve">341.424163818359</t>
@@ -3365,16 +3365,16 @@
     <t xml:space="preserve">353.829864501953</t>
   </si>
   <si>
-    <t xml:space="preserve">358.257049560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.473083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.224395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">353.63525390625</t>
+    <t xml:space="preserve">358.257019042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.473052978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.224456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">353.635284423828</t>
   </si>
   <si>
     <t xml:space="preserve">357.429962158203</t>
@@ -3383,40 +3383,40 @@
     <t xml:space="preserve">349.013580322266</t>
   </si>
   <si>
-    <t xml:space="preserve">330.672607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.946655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.531311035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.921630859375</t>
+    <t xml:space="preserve">330.672546386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.946624755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.531280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.921691894531</t>
   </si>
   <si>
     <t xml:space="preserve">338.898681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">339.972045898438</t>
+    <t xml:space="preserve">339.972076416016</t>
   </si>
   <si>
     <t xml:space="preserve">343.728942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">342.606750488281</t>
+    <t xml:space="preserve">342.606811523438</t>
   </si>
   <si>
     <t xml:space="preserve">339.581726074219</t>
   </si>
   <si>
-    <t xml:space="preserve">339.093841552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.704315185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.094970703125</t>
+    <t xml:space="preserve">339.093811035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.704345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.095062255859</t>
   </si>
   <si>
     <t xml:space="preserve">341.435760498047</t>
@@ -3425,25 +3425,25 @@
     <t xml:space="preserve">344.509552001953</t>
   </si>
   <si>
-    <t xml:space="preserve">344.119201660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">346.510009765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.826934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.070068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.5830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.680114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.411163330078</t>
+    <t xml:space="preserve">344.119293212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">346.510040283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.826843261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.070037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.582916259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.68017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.411224365234</t>
   </si>
   <si>
     <t xml:space="preserve">338.801086425781</t>
@@ -3458,40 +3458,40 @@
     <t xml:space="preserve">328.945404052734</t>
   </si>
   <si>
-    <t xml:space="preserve">328.994232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.116302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.118438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.654724121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.800659179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.141845703125</t>
+    <t xml:space="preserve">328.994171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.116363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.118408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.654693603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.800628662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.141784667969</t>
   </si>
   <si>
     <t xml:space="preserve">338.605895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">335.044219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.703063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.629730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">337.288604736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.897064208984</t>
+    <t xml:space="preserve">335.044250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.703094482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.629760742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">337.28857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.897033691406</t>
   </si>
   <si>
     <t xml:space="preserve">335.434539794922</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">325.774047851562</t>
   </si>
   <si>
-    <t xml:space="preserve">315.625610351562</t>
+    <t xml:space="preserve">315.625579833984</t>
   </si>
   <si>
     <t xml:space="preserve">321.529235839844</t>
@@ -3509,37 +3509,37 @@
     <t xml:space="preserve">321.919586181641</t>
   </si>
   <si>
-    <t xml:space="preserve">326.017974853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323.968780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.188568115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320.065521240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">317.528411865234</t>
+    <t xml:space="preserve">326.018005371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.96875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.188537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320.065551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">317.528442382812</t>
   </si>
   <si>
     <t xml:space="preserve">311.088104248047</t>
   </si>
   <si>
-    <t xml:space="preserve">307.672760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.428802490234</t>
+    <t xml:space="preserve">307.672729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.428771972656</t>
   </si>
   <si>
     <t xml:space="preserve">310.161102294922</t>
   </si>
   <si>
-    <t xml:space="preserve">313.039703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.794921875</t>
+    <t xml:space="preserve">313.039672851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.794982910156</t>
   </si>
   <si>
     <t xml:space="preserve">307.184844970703</t>
@@ -3548,25 +3548,25 @@
     <t xml:space="preserve">305.477172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">287.131958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.331207275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.160247802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.501739501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.575622558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.161468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.796600341797</t>
+    <t xml:space="preserve">287.131927490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.331237792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.160217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.501770019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.575592041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.161407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.796539306641</t>
   </si>
   <si>
     <t xml:space="preserve">316.503845214844</t>
@@ -3578,19 +3578,19 @@
     <t xml:space="preserve">313.595550537109</t>
   </si>
   <si>
-    <t xml:space="preserve">303.558532714844</t>
+    <t xml:space="preserve">303.558563232422</t>
   </si>
   <si>
     <t xml:space="preserve">301.942810058594</t>
   </si>
   <si>
-    <t xml:space="preserve">300.571960449219</t>
+    <t xml:space="preserve">300.571899414062</t>
   </si>
   <si>
     <t xml:space="preserve">302.775146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">304.146026611328</t>
+    <t xml:space="preserve">304.146057128906</t>
   </si>
   <si>
     <t xml:space="preserve">304.341888427734</t>
@@ -3599,85 +3599,85 @@
     <t xml:space="preserve">299.886444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">294.011138916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.93994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290.192138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.604583740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.080871582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">291.465209960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.702606201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">288.380584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.129791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">292.052703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.528869628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.969543457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.195037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.390869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.089660644531</t>
+    <t xml:space="preserve">294.011077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">290.192199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.604644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.080841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">291.465118408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.702575683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">288.380645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.129821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">292.052673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.528900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.969573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.195007324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.390899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.089721679688</t>
   </si>
   <si>
     <t xml:space="preserve">303.411651611328</t>
   </si>
   <si>
-    <t xml:space="preserve">299.592651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.110504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.984344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.370086669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.488861083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.509613037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.419067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.950164794922</t>
+    <t xml:space="preserve">299.592712402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.110443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.984405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.3701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.48876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.509582519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.419097900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.9501953125</t>
   </si>
   <si>
     <t xml:space="preserve">307.964996337891</t>
   </si>
   <si>
-    <t xml:space="preserve">314.721649169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.442687988281</t>
+    <t xml:space="preserve">314.7216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.442749023438</t>
   </si>
   <si>
     <t xml:space="preserve">325.884765625</t>
@@ -3686,37 +3686,37 @@
     <t xml:space="preserve">329.018280029297</t>
   </si>
   <si>
-    <t xml:space="preserve">329.605773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.976745605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">333.326904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.110229492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.543487548828</t>
+    <t xml:space="preserve">329.605834960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.976715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">333.326873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.110198974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.543426513672</t>
   </si>
   <si>
     <t xml:space="preserve">331.760101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">341.944000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.768951416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">344.685821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.323699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">358.786590576172</t>
+    <t xml:space="preserve">341.943969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.768920898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.685852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.323791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">358.78662109375</t>
   </si>
   <si>
     <t xml:space="preserve">375.433319091797</t>
@@ -3728,85 +3728,85 @@
     <t xml:space="preserve">382.679534912109</t>
   </si>
   <si>
-    <t xml:space="preserve">385.225555419922</t>
+    <t xml:space="preserve">385.225616455078</t>
   </si>
   <si>
     <t xml:space="preserve">385.421478271484</t>
   </si>
   <si>
-    <t xml:space="preserve">386.204772949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389.338287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">395.358062744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389.465972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.394073486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.197631835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">398.304046630859</t>
+    <t xml:space="preserve">386.204742431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">389.338317871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">395.357971191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">389.465942382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.394012451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.197570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">398.304077148438</t>
   </si>
   <si>
     <t xml:space="preserve">401.053680419922</t>
   </si>
   <si>
-    <t xml:space="preserve">402.428527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.484008789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.091156005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">387.109130859375</t>
+    <t xml:space="preserve">402.428497314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.483978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.091186523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">387.109161376953</t>
   </si>
   <si>
     <t xml:space="preserve">391.233612060547</t>
   </si>
   <si>
-    <t xml:space="preserve">396.143646240234</t>
+    <t xml:space="preserve">396.143676757812</t>
   </si>
   <si>
     <t xml:space="preserve">388.680358886719</t>
   </si>
   <si>
-    <t xml:space="preserve">396.536437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.16015625</t>
+    <t xml:space="preserve">396.536407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.160186767578</t>
   </si>
   <si>
     <t xml:space="preserve">408.124176025391</t>
   </si>
   <si>
-    <t xml:space="preserve">404.785339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.963745117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.731414794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">403.999694824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.178131103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.821350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.534973144531</t>
+    <t xml:space="preserve">404.785369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.963775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.731384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">403.999725341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.178192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.821380615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.535034179688</t>
   </si>
   <si>
     <t xml:space="preserve">406.749359130859</t>
@@ -3815,31 +3815,31 @@
     <t xml:space="preserve">413.034301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">409.498962402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.551513671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.122680664062</t>
+    <t xml:space="preserve">409.498992919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.551544189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.122741699219</t>
   </si>
   <si>
     <t xml:space="preserve">421.479553222656</t>
   </si>
   <si>
-    <t xml:space="preserve">415.980285644531</t>
+    <t xml:space="preserve">415.980255126953</t>
   </si>
   <si>
     <t xml:space="preserve">419.711944580078</t>
   </si>
   <si>
-    <t xml:space="preserve">420.49755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.570922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">403.60693359375</t>
+    <t xml:space="preserve">420.497589111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.570983886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">403.606964111328</t>
   </si>
   <si>
     <t xml:space="preserve">397.518463134766</t>
@@ -3851,10 +3851,10 @@
     <t xml:space="preserve">383.377471923828</t>
   </si>
   <si>
-    <t xml:space="preserve">391.822784423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">395.947235107422</t>
+    <t xml:space="preserve">391.822814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">395.947265625</t>
   </si>
   <si>
     <t xml:space="preserve">394.572418212891</t>
@@ -3869,22 +3869,22 @@
     <t xml:space="preserve">409.302581787109</t>
   </si>
   <si>
-    <t xml:space="preserve">408.320556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.142181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.356536865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.232116699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.767395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">413.819854736328</t>
+    <t xml:space="preserve">408.320587158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.142211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.356567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.232147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.767364501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413.81982421875</t>
   </si>
   <si>
     <t xml:space="preserve">404.588928222656</t>
@@ -3902,25 +3902,25 @@
     <t xml:space="preserve">474.508209228516</t>
   </si>
   <si>
-    <t xml:space="preserve">470.187347412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">474.115386962891</t>
+    <t xml:space="preserve">470.187316894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">474.115417480469</t>
   </si>
   <si>
     <t xml:space="preserve">486.252014160156</t>
   </si>
   <si>
-    <t xml:space="preserve">488.614318847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">495.110870361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">493.634338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">492.157897949219</t>
+    <t xml:space="preserve">488.614349365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">495.11083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">493.634368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">492.157867431641</t>
   </si>
   <si>
     <t xml:space="preserve">496.095184326172</t>
@@ -3938,16 +3938,16 @@
     <t xml:space="preserve">503.969696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">501.016723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">495.60302734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.032379150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">507.414733886719</t>
+    <t xml:space="preserve">501.016815185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">495.602996826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.032440185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">507.414764404297</t>
   </si>
   <si>
     <t xml:space="preserve">511.844177246094</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">514.797119140625</t>
   </si>
   <si>
-    <t xml:space="preserve">509.383422851562</t>
+    <t xml:space="preserve">509.383453369141</t>
   </si>
   <si>
     <t xml:space="preserve">527.593200683594</t>
@@ -3965,34 +3965,34 @@
     <t xml:space="preserve">535.9599609375</t>
   </si>
   <si>
-    <t xml:space="preserve">547.279602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">546.295227050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">546.787414550781</t>
+    <t xml:space="preserve">547.279541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">546.295288085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">546.787475585938</t>
   </si>
   <si>
     <t xml:space="preserve">550.232543945312</t>
   </si>
   <si>
-    <t xml:space="preserve">539.897216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">528.08544921875</t>
+    <t xml:space="preserve">539.897277832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">528.085388183594</t>
   </si>
   <si>
     <t xml:space="preserve">526.116760253906</t>
   </si>
   <si>
-    <t xml:space="preserve">512.336364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">510.859832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">489.992401123047</t>
+    <t xml:space="preserve">512.33642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">510.859924316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">489.992370605469</t>
   </si>
   <si>
     <t xml:space="preserve">504.461853027344</t>
@@ -4001,61 +4001,61 @@
     <t xml:space="preserve">517.750122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">532.514953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">554.661926269531</t>
+    <t xml:space="preserve">532.514831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">554.662048339844</t>
   </si>
   <si>
     <t xml:space="preserve">568.442321777344</t>
   </si>
   <si>
-    <t xml:space="preserve">567.950134277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">575.82470703125</t>
+    <t xml:space="preserve">567.9501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">575.824768066406</t>
   </si>
   <si>
     <t xml:space="preserve">561.552185058594</t>
   </si>
   <si>
-    <t xml:space="preserve">569.426696777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">545.803100585938</t>
+    <t xml:space="preserve">569.426635742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">545.803039550781</t>
   </si>
   <si>
     <t xml:space="preserve">543.34228515625</t>
   </si>
   <si>
-    <t xml:space="preserve">540.389404296875</t>
+    <t xml:space="preserve">540.389343261719</t>
   </si>
   <si>
     <t xml:space="preserve">549.248229980469</t>
   </si>
   <si>
-    <t xml:space="preserve">555.646179199219</t>
+    <t xml:space="preserve">555.646301269531</t>
   </si>
   <si>
     <t xml:space="preserve">532.022766113281</t>
   </si>
   <si>
-    <t xml:space="preserve">523.656005859375</t>
+    <t xml:space="preserve">523.655944824219</t>
   </si>
   <si>
     <t xml:space="preserve">514.304992675781</t>
   </si>
   <si>
-    <t xml:space="preserve">517.257934570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">534.9755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">544.81884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">553.185424804688</t>
+    <t xml:space="preserve">517.257995605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534.975646972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">544.818725585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">553.185485839844</t>
   </si>
   <si>
     <t xml:space="preserve">554.299987792969</t>
@@ -4067,43 +4067,43 @@
     <t xml:space="preserve">532.108276367188</t>
   </si>
   <si>
-    <t xml:space="preserve">536.546630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">542.464416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.532958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">541.478149414062</t>
+    <t xml:space="preserve">536.546569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">542.464538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.532897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">541.478088378906</t>
   </si>
   <si>
     <t xml:space="preserve">543.450744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">533.094665527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">531.121948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">538.026062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">540.491760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.601440429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.039794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">534.080871582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">539.012451171875</t>
+    <t xml:space="preserve">533.094604492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">531.122009277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">538.026000976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540.491821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.601318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.039855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534.080810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">539.012390136719</t>
   </si>
   <si>
     <t xml:space="preserve">526.190490722656</t>
@@ -4115,22 +4115,22 @@
     <t xml:space="preserve">517.806945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">513.368591308594</t>
+    <t xml:space="preserve">513.36865234375</t>
   </si>
   <si>
     <t xml:space="preserve">523.231628417969</t>
   </si>
   <si>
-    <t xml:space="preserve">519.779541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">511.889099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.916595458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">511.396026611328</t>
+    <t xml:space="preserve">519.779602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">511.889221191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.91650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">511.395965576172</t>
   </si>
   <si>
     <t xml:space="preserve">518.793273925781</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">527.669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">552.820617675781</t>
+    <t xml:space="preserve">552.820556640625</t>
   </si>
   <si>
     <t xml:space="preserve">567.121887207031</t>
@@ -4154,106 +4154,106 @@
     <t xml:space="preserve">567.615051269531</t>
   </si>
   <si>
-    <t xml:space="preserve">565.642456054688</t>
+    <t xml:space="preserve">565.642517089844</t>
   </si>
   <si>
     <t xml:space="preserve">568.108154296875</t>
   </si>
   <si>
-    <t xml:space="preserve">573.532836914062</t>
+    <t xml:space="preserve">573.532897949219</t>
   </si>
   <si>
     <t xml:space="preserve">581.423217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">583.888916015625</t>
+    <t xml:space="preserve">583.889038085938</t>
   </si>
   <si>
     <t xml:space="preserve">575.012268066406</t>
   </si>
   <si>
-    <t xml:space="preserve">561.697265625</t>
+    <t xml:space="preserve">561.697204589844</t>
   </si>
   <si>
     <t xml:space="preserve">569.094482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">568.601379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">577.47802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">572.053466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">577.971130371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">587.341003417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">587.834167480469</t>
+    <t xml:space="preserve">568.601318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">577.478088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">572.053405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">577.97119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">587.341064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">587.834106445312</t>
   </si>
   <si>
     <t xml:space="preserve">585.861511230469</t>
   </si>
   <si>
-    <t xml:space="preserve">593.751892089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">609.039611816406</t>
+    <t xml:space="preserve">593.751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">609.03955078125</t>
   </si>
   <si>
     <t xml:space="preserve">646.025817871094</t>
   </si>
   <si>
-    <t xml:space="preserve">642.080688476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">668.217468261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">675.614807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677.09423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">671.176391601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">679.559997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">695.173034667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">698.631591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">722.841552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">726.300109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">700.113708496094</t>
+    <t xml:space="preserve">642.080627441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">668.217529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">675.61474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">677.094177246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">671.176452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679.559936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">695.172973632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">698.631530761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722.841613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">726.300048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">700.11376953125</t>
   </si>
   <si>
     <t xml:space="preserve">681.338623046875</t>
   </si>
   <si>
-    <t xml:space="preserve">707.030944824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">697.643310546875</t>
+    <t xml:space="preserve">707.031005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">697.643432617188</t>
   </si>
   <si>
     <t xml:space="preserve">705.054626464844</t>
   </si>
   <si>
-    <t xml:space="preserve">699.125671386719</t>
+    <t xml:space="preserve">699.125549316406</t>
   </si>
   <si>
     <t xml:space="preserve">688.255859375</t>
@@ -4268,46 +4268,46 @@
     <t xml:space="preserve">722.347412109375</t>
   </si>
   <si>
-    <t xml:space="preserve">710.489501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">711.971801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.232116699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">660.587219238281</t>
+    <t xml:space="preserve">710.489440917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.971740722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.232055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">660.587158203125</t>
   </si>
   <si>
     <t xml:space="preserve">678.868286132812</t>
   </si>
   <si>
-    <t xml:space="preserve">683.315002441406</t>
+    <t xml:space="preserve">683.31494140625</t>
   </si>
   <si>
     <t xml:space="preserve">682.326782226562</t>
   </si>
   <si>
-    <t xml:space="preserve">697.149291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.560424804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.06640625</t>
+    <t xml:space="preserve">697.149230957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.066467285156</t>
   </si>
   <si>
     <t xml:space="preserve">706.042785644531</t>
   </si>
   <si>
-    <t xml:space="preserve">720.865112304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">698.829162597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">709.896667480469</t>
+    <t xml:space="preserve">720.865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">698.829223632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">709.896606445312</t>
   </si>
   <si>
     <t xml:space="preserve">704.165222167969</t>
@@ -4316,19 +4316,19 @@
     <t xml:space="preserve">709.204833984375</t>
   </si>
   <si>
-    <t xml:space="preserve">708.710754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">689.738037109375</t>
+    <t xml:space="preserve">708.710815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">689.738098144531</t>
   </si>
   <si>
     <t xml:space="preserve">701.991333007812</t>
   </si>
   <si>
-    <t xml:space="preserve">702.090148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">706.141479492188</t>
+    <t xml:space="preserve">702.090209960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706.141540527344</t>
   </si>
   <si>
     <t xml:space="preserve">695.469360351562</t>
@@ -4340,10 +4340,10 @@
     <t xml:space="preserve">677.188354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">676.6943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">685.390075683594</t>
+    <t xml:space="preserve">676.694213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">685.39013671875</t>
   </si>
   <si>
     <t xml:space="preserve">678.077758789062</t>
@@ -4352,37 +4352,37 @@
     <t xml:space="preserve">667.603149414062</t>
   </si>
   <si>
-    <t xml:space="preserve">680.745727539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">674.619262695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">711.576477050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">674.520324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">688.848693847656</t>
+    <t xml:space="preserve">680.745788574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">674.619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.576416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">674.520263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">688.8486328125</t>
   </si>
   <si>
     <t xml:space="preserve">709.106018066406</t>
   </si>
   <si>
-    <t xml:space="preserve">712.367065429688</t>
+    <t xml:space="preserve">712.367004394531</t>
   </si>
   <si>
     <t xml:space="preserve">690.133361816406</t>
   </si>
   <si>
-    <t xml:space="preserve">690.528564453125</t>
+    <t xml:space="preserve">690.528503417969</t>
   </si>
   <si>
     <t xml:space="preserve">710.328674316406</t>
   </si>
   <si>
-    <t xml:space="preserve">705.57666015625</t>
+    <t xml:space="preserve">705.576721191406</t>
   </si>
   <si>
     <t xml:space="preserve">701.517639160156</t>
@@ -4397,124 +4397,124 @@
     <t xml:space="preserve">729.336730957031</t>
   </si>
   <si>
-    <t xml:space="preserve">744.186828613281</t>
+    <t xml:space="preserve">744.186889648438</t>
   </si>
   <si>
     <t xml:space="preserve">737.2568359375</t>
   </si>
   <si>
-    <t xml:space="preserve">739.434936523438</t>
+    <t xml:space="preserve">739.434875488281</t>
   </si>
   <si>
     <t xml:space="preserve">733.593872070312</t>
   </si>
   <si>
-    <t xml:space="preserve">744.087768554688</t>
+    <t xml:space="preserve">744.087829589844</t>
   </si>
   <si>
     <t xml:space="preserve">744.681823730469</t>
   </si>
   <si>
-    <t xml:space="preserve">746.661926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.640930175781</t>
+    <t xml:space="preserve">746.661804199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.640869140625</t>
   </si>
   <si>
     <t xml:space="preserve">754.185913085938</t>
   </si>
   <si>
-    <t xml:space="preserve">757.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">762.204956054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">778.243103027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">791.41015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">793.588012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">787.549072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">807.250244140625</t>
+    <t xml:space="preserve">757.749938964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">762.205017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">778.243041992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">791.410095214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">793.588073730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">787.549011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">807.250183105469</t>
   </si>
   <si>
     <t xml:space="preserve">815.764221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">815.962219238281</t>
+    <t xml:space="preserve">815.962280273438</t>
   </si>
   <si>
     <t xml:space="preserve">825.565307617188</t>
   </si>
   <si>
-    <t xml:space="preserve">823.288269042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">833.38623046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819.427307128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">828.337219238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">838.732360839844</t>
+    <t xml:space="preserve">823.288208007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">833.386291503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.427185058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">828.337280273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.732421875</t>
   </si>
   <si>
     <t xml:space="preserve">835.267333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">833.980346679688</t>
+    <t xml:space="preserve">833.980285644531</t>
   </si>
   <si>
     <t xml:space="preserve">843.385375976562</t>
   </si>
   <si>
-    <t xml:space="preserve">845.266357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">828.931335449219</t>
+    <t xml:space="preserve">845.266418457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">828.931274414062</t>
   </si>
   <si>
     <t xml:space="preserve">818.932189941406</t>
   </si>
   <si>
-    <t xml:space="preserve">825.664245605469</t>
+    <t xml:space="preserve">825.664306640625</t>
   </si>
   <si>
     <t xml:space="preserve">834.970336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">839.722412109375</t>
+    <t xml:space="preserve">839.722351074219</t>
   </si>
   <si>
     <t xml:space="preserve">847.543395996094</t>
   </si>
   <si>
-    <t xml:space="preserve">861.403381347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">845.563415527344</t>
+    <t xml:space="preserve">861.403442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">845.563354492188</t>
   </si>
   <si>
     <t xml:space="preserve">859.720458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">863.977416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">830.020385742188</t>
+    <t xml:space="preserve">863.9775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.482543945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">830.020263671875</t>
   </si>
   <si>
     <t xml:space="preserve">773.392028808594</t>
@@ -4538,19 +4538,19 @@
     <t xml:space="preserve">743.790832519531</t>
   </si>
   <si>
-    <t xml:space="preserve">737.751831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">726.4658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">735.078796386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761.016906738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720.030639648438</t>
+    <t xml:space="preserve">737.751892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">726.465637207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">735.078735351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761.016967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720.03076171875</t>
   </si>
   <si>
     <t xml:space="preserve">699.042541503906</t>
@@ -4568,88 +4568,88 @@
     <t xml:space="preserve">812.794189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">806.359191894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">817.744140625</t>
+    <t xml:space="preserve">806.359130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">817.744201660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.138366699219</t>
   </si>
   <si>
     <t xml:space="preserve">838.138305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">838.138244628906</t>
-  </si>
-  <si>
     <t xml:space="preserve">836.353576660156</t>
   </si>
   <si>
-    <t xml:space="preserve">824.752685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">846.169677734375</t>
+    <t xml:space="preserve">824.752746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">846.169738769531</t>
   </si>
   <si>
     <t xml:space="preserve">841.806945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">855.88671875</t>
+    <t xml:space="preserve">855.886657714844</t>
   </si>
   <si>
     <t xml:space="preserve">840.220581054688</t>
   </si>
   <si>
-    <t xml:space="preserve">845.376403808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">851.028198242188</t>
+    <t xml:space="preserve">845.37646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">851.028137207031</t>
   </si>
   <si>
     <t xml:space="preserve">845.673950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">850.631591796875</t>
+    <t xml:space="preserve">850.631652832031</t>
   </si>
   <si>
     <t xml:space="preserve">846.7646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">858.563781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">867.586730957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">852.218017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812.160278320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">806.012878417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">807.995849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812.656005859375</t>
+    <t xml:space="preserve">858.563842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">867.586669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">852.218078613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812.160339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">806.012817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">807.995910644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812.656066894531</t>
   </si>
   <si>
     <t xml:space="preserve">812.953491210938</t>
   </si>
   <si>
-    <t xml:space="preserve">831.197692871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">835.064575195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">824.058654785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812.556945800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">808.987426757812</t>
+    <t xml:space="preserve">831.197631835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">835.064636230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">824.05859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812.556884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">808.987365722656</t>
   </si>
   <si>
     <t xml:space="preserve">805.51708984375</t>
@@ -4658,7 +4658,7 @@
     <t xml:space="preserve">825.5458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">816.919677734375</t>
+    <t xml:space="preserve">816.919616699219</t>
   </si>
   <si>
     <t xml:space="preserve">819.695922851562</t>
@@ -4670,46 +4670,46 @@
     <t xml:space="preserve">813.845886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">779.7373046875</t>
+    <t xml:space="preserve">779.737365722656</t>
   </si>
   <si>
     <t xml:space="preserve">779.935668945312</t>
   </si>
   <si>
-    <t xml:space="preserve">793.51953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">800.063720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">798.675537109375</t>
+    <t xml:space="preserve">793.519592285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800.063781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">798.675598144531</t>
   </si>
   <si>
     <t xml:space="preserve">794.709411621094</t>
   </si>
   <si>
-    <t xml:space="preserve">816.324645996094</t>
+    <t xml:space="preserve">816.32470703125</t>
   </si>
   <si>
     <t xml:space="preserve">826.636657714844</t>
   </si>
   <si>
-    <t xml:space="preserve">829.313720703125</t>
+    <t xml:space="preserve">829.313781738281</t>
   </si>
   <si>
     <t xml:space="preserve">836.948486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">829.809509277344</t>
+    <t xml:space="preserve">829.8095703125</t>
   </si>
   <si>
     <t xml:space="preserve">832.982360839844</t>
   </si>
   <si>
-    <t xml:space="preserve">841.410400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">838.435791015625</t>
+    <t xml:space="preserve">841.410339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.435729980469</t>
   </si>
   <si>
     <t xml:space="preserve">830.0078125</t>
@@ -4718,22 +4718,22 @@
     <t xml:space="preserve">833.279846191406</t>
   </si>
   <si>
-    <t xml:space="preserve">823.662048339844</t>
+    <t xml:space="preserve">823.661987304688</t>
   </si>
   <si>
     <t xml:space="preserve">819.2001953125</t>
   </si>
   <si>
-    <t xml:space="preserve">822.868835449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819.894226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">827.132446289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761.790710449219</t>
+    <t xml:space="preserve">822.868896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.894287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">827.132385253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761.790649414062</t>
   </si>
   <si>
     <t xml:space="preserve">778.646667480469</t>
@@ -4745,10 +4745,10 @@
     <t xml:space="preserve">737.002502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">726.492370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">716.9736328125</t>
+    <t xml:space="preserve">726.492309570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">716.973571777344</t>
   </si>
   <si>
     <t xml:space="preserve">725.401611328125</t>
@@ -4760,10 +4760,10 @@
     <t xml:space="preserve">778.250061035156</t>
   </si>
   <si>
-    <t xml:space="preserve">761.691528320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">771.309448242188</t>
+    <t xml:space="preserve">761.691589355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">771.309387207031</t>
   </si>
   <si>
     <t xml:space="preserve">750.090637207031</t>
@@ -4772,22 +4772,22 @@
     <t xml:space="preserve">713.24169921875</t>
   </si>
   <si>
-    <t xml:space="preserve">680.464965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">679.670349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">703.706604003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.295776367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">715.228149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760.916870117188</t>
+    <t xml:space="preserve">680.464904785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679.67041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">703.706665039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.295837402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">715.228088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760.916931152344</t>
   </si>
   <si>
     <t xml:space="preserve">744.429260253906</t>
@@ -4796,10 +4796,10 @@
     <t xml:space="preserve">749.892028808594</t>
   </si>
   <si>
-    <t xml:space="preserve">756.447387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766.776977539062</t>
+    <t xml:space="preserve">756.447326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766.777038574219</t>
   </si>
   <si>
     <t xml:space="preserve">790.416015625</t>
@@ -4808,13 +4808,13 @@
     <t xml:space="preserve">774.623596191406</t>
   </si>
   <si>
-    <t xml:space="preserve">788.429504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760.519714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">756.34814453125</t>
+    <t xml:space="preserve">788.429565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760.519653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">756.348022460938</t>
   </si>
   <si>
     <t xml:space="preserve">748.104248046875</t>
@@ -4823,22 +4823,22 @@
     <t xml:space="preserve">747.408935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">740.952941894531</t>
+    <t xml:space="preserve">740.952880859375</t>
   </si>
   <si>
     <t xml:space="preserve">744.329956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">744.925903320312</t>
+    <t xml:space="preserve">744.925842285156</t>
   </si>
   <si>
     <t xml:space="preserve">735.788146972656</t>
   </si>
   <si>
-    <t xml:space="preserve">725.756408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">759.02978515625</t>
+    <t xml:space="preserve">725.756469726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">759.029846191406</t>
   </si>
   <si>
     <t xml:space="preserve">745.521789550781</t>
@@ -4847,22 +4847,22 @@
     <t xml:space="preserve">748.700134277344</t>
   </si>
   <si>
-    <t xml:space="preserve">738.569152832031</t>
+    <t xml:space="preserve">738.569213867188</t>
   </si>
   <si>
     <t xml:space="preserve">759.327758789062</t>
   </si>
   <si>
-    <t xml:space="preserve">753.070373535156</t>
+    <t xml:space="preserve">753.070434570312</t>
   </si>
   <si>
     <t xml:space="preserve">739.860412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">740.158325195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.731811523438</t>
+    <t xml:space="preserve">740.158386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.731872558594</t>
   </si>
   <si>
     <t xml:space="preserve">758.433837890625</t>
@@ -4874,7 +4874,7 @@
     <t xml:space="preserve">769.359436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">718.505798339844</t>
+    <t xml:space="preserve">718.505859375</t>
   </si>
   <si>
     <t xml:space="preserve">720.1943359375</t>
@@ -4886,7 +4886,7 @@
     <t xml:space="preserve">714.731506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">693.675048828125</t>
+    <t xml:space="preserve">693.674987792969</t>
   </si>
   <si>
     <t xml:space="preserve">697.548583984375</t>
@@ -4901,16 +4901,16 @@
     <t xml:space="preserve">741.846862792969</t>
   </si>
   <si>
-    <t xml:space="preserve">757.937194824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766.18115234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">768.068176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">771.445190429688</t>
+    <t xml:space="preserve">757.937255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766.181091308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">768.068237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">771.445251464844</t>
   </si>
   <si>
     <t xml:space="preserve">784.555969238281</t>
@@ -4919,10 +4919,10 @@
     <t xml:space="preserve">785.052551269531</t>
   </si>
   <si>
-    <t xml:space="preserve">775.914794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">796.176696777344</t>
+    <t xml:space="preserve">775.914855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">796.1767578125</t>
   </si>
   <si>
     <t xml:space="preserve">842.759460449219</t>
@@ -4931,7 +4931,7 @@
     <t xml:space="preserve">843.752685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">834.813598632812</t>
+    <t xml:space="preserve">834.813659667969</t>
   </si>
   <si>
     <t xml:space="preserve">833.025756835938</t>
@@ -4961,13 +4961,13 @@
     <t xml:space="preserve">849.839111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">836.903930664062</t>
+    <t xml:space="preserve">836.903991699219</t>
   </si>
   <si>
     <t xml:space="preserve">852.426208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">863.96826171875</t>
+    <t xml:space="preserve">863.968322753906</t>
   </si>
   <si>
     <t xml:space="preserve">882.276489257812</t>
@@ -4985,13 +4985,13 @@
     <t xml:space="preserve">846.456115722656</t>
   </si>
   <si>
-    <t xml:space="preserve">849.043151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">797.700561523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">774.914733886719</t>
+    <t xml:space="preserve">849.043090820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">797.700500488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">774.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">745.064392089844</t>
@@ -5003,10 +5003,10 @@
     <t xml:space="preserve">734.517333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">740.785949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">749.143981933594</t>
+    <t xml:space="preserve">740.785888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">749.14404296875</t>
   </si>
   <si>
     <t xml:space="preserve">743.969909667969</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">774.21826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">787.053955078125</t>
+    <t xml:space="preserve">787.053894042969</t>
   </si>
   <si>
     <t xml:space="preserve">770.63623046875</t>
@@ -5039,13 +5039,13 @@
     <t xml:space="preserve">753.322998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">742.178894042969</t>
+    <t xml:space="preserve">742.178955078125</t>
   </si>
   <si>
     <t xml:space="preserve">718.497619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">679.891235351562</t>
+    <t xml:space="preserve">679.891174316406</t>
   </si>
   <si>
     <t xml:space="preserve">650.836853027344</t>
@@ -5057,7 +5057,7 @@
     <t xml:space="preserve">625.961608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">631.633117675781</t>
+    <t xml:space="preserve">631.633178710938</t>
   </si>
   <si>
     <t xml:space="preserve">630.837158203125</t>
@@ -5066,7 +5066,7 @@
     <t xml:space="preserve">655.612976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">669.443603515625</t>
+    <t xml:space="preserve">669.443542480469</t>
   </si>
   <si>
     <t xml:space="preserve">654.418884277344</t>
@@ -5078,7 +5078,7 @@
     <t xml:space="preserve">711.134582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">720.089660644531</t>
+    <t xml:space="preserve">720.089721679688</t>
   </si>
   <si>
     <t xml:space="preserve">743.074401855469</t>
@@ -5087,7 +5087,7 @@
     <t xml:space="preserve">758.397583007812</t>
   </si>
   <si>
-    <t xml:space="preserve">760.188598632812</t>
+    <t xml:space="preserve">760.188659667969</t>
   </si>
   <si>
     <t xml:space="preserve">774.516784667969</t>
@@ -5096,10 +5096,10 @@
     <t xml:space="preserve">784.765441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">721.184143066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">718.796142578125</t>
+    <t xml:space="preserve">721.184204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">718.796203613281</t>
   </si>
   <si>
     <t xml:space="preserve">697.204406738281</t>
@@ -5108,16 +5108,16 @@
     <t xml:space="preserve">680.289245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">657.901489257812</t>
+    <t xml:space="preserve">657.901428222656</t>
   </si>
   <si>
     <t xml:space="preserve">665.563110351562</t>
   </si>
   <si>
-    <t xml:space="preserve">672.528137207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">668.747009277344</t>
+    <t xml:space="preserve">672.528198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">668.7470703125</t>
   </si>
   <si>
     <t xml:space="preserve">643.274780273438</t>
@@ -5442,6 +5442,9 @@
   </si>
   <si>
     <t xml:space="preserve">696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">707</t>
   </si>
 </sst>
 </file>
@@ -70650,7 +70653,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45952.6497453704</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>2016</v>
@@ -70671,6 +70674,32 @@
         <v>1809</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45953.6498263889</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>1927</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>709.299987792969</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>694</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>701.799987792969</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>707</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>1810</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -38,304 +38,304 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3028831481934</t>
+    <t xml:space="preserve">38.3028793334961</t>
   </si>
   <si>
     <t xml:space="preserve">LLY.DE</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7578239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.680061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.117504119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5549545288086</t>
+    <t xml:space="preserve">38.7578201293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1175079345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5549659729004</t>
   </si>
   <si>
     <t xml:space="preserve">63.4298400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">62.9923934936523</t>
+    <t xml:space="preserve">62.9923973083496</t>
   </si>
   <si>
     <t xml:space="preserve">61.2426147460938</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8051605224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3677215576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9302597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0229911804199</t>
+    <t xml:space="preserve">60.8051681518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3677139282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9302673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0229949951172</t>
   </si>
   <si>
     <t xml:space="preserve">57.5943145751953</t>
   </si>
   <si>
-    <t xml:space="preserve">58.1717262268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8681449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7071418762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5907974243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3309478759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3598022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0159759521484</t>
+    <t xml:space="preserve">58.1717300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8681373596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.707145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5907936096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.330940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3598136901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0159912109375</t>
   </si>
   <si>
     <t xml:space="preserve">54.2212562561035</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8040161132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3226585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4815902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2785186767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4021263122559</t>
+    <t xml:space="preserve">54.8040084838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3226623535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4815940856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2785263061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4021186828613</t>
   </si>
   <si>
     <t xml:space="preserve">57.0290069580078</t>
   </si>
   <si>
-    <t xml:space="preserve">57.5322875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5963668823242</t>
+    <t xml:space="preserve">57.532283782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5963706970215</t>
   </si>
   <si>
     <t xml:space="preserve">55.4662055969238</t>
   </si>
   <si>
-    <t xml:space="preserve">55.2719573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5721588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1218643188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9276123046875</t>
+    <t xml:space="preserve">55.2719535827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5721664428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1218719482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9276161193848</t>
   </si>
   <si>
     <t xml:space="preserve">54.9717636108398</t>
   </si>
   <si>
-    <t xml:space="preserve">56.6405220031738</t>
+    <t xml:space="preserve">56.6405181884766</t>
   </si>
   <si>
     <t xml:space="preserve">56.2167091369629</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5787124633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0754432678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.808277130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0312843322754</t>
+    <t xml:space="preserve">56.5787086486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0754318237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8082656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0312881469727</t>
   </si>
   <si>
     <t xml:space="preserve">56.4286041259766</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2961769104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8900108337402</t>
+    <t xml:space="preserve">56.2961692810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8900184631348</t>
   </si>
   <si>
     <t xml:space="preserve">54.486141204834</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2323837280273</t>
+    <t xml:space="preserve">53.2323684692383</t>
   </si>
   <si>
     <t xml:space="preserve">53.9034080505371</t>
   </si>
   <si>
-    <t xml:space="preserve">55.113037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3690872192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6251411437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9230499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8812026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5191802978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7641372680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1019248962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6934852600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.505786895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1614379882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9936943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5433921813965</t>
+    <t xml:space="preserve">55.1130409240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.369083404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.625129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9230461120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8811874389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5191879272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7641296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1019287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.693489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5057907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1614418029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9937019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5434036254883</t>
   </si>
   <si>
     <t xml:space="preserve">56.9495506286621</t>
   </si>
   <si>
-    <t xml:space="preserve">57.4792976379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9119453430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5829811096191</t>
+    <t xml:space="preserve">57.4793090820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.911937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5829734802246</t>
   </si>
   <si>
     <t xml:space="preserve">59.9162178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">60.3665199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1899261474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3622398376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6559066772461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6294097900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6271209716797</t>
+    <t xml:space="preserve">60.366527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1899147033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3622436523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.655891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6293983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6271171569824</t>
   </si>
   <si>
     <t xml:space="preserve">58.7330741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">60.5166091918945</t>
+    <t xml:space="preserve">60.5166053771973</t>
   </si>
   <si>
     <t xml:space="preserve">61.0552215576172</t>
   </si>
   <si>
-    <t xml:space="preserve">61.5231704711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4452934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7212257385254</t>
+    <t xml:space="preserve">61.5231666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4452857971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7212409973145</t>
   </si>
   <si>
     <t xml:space="preserve">62.2997970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8872947692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5134201049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2433433532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2077293395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3946647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.937629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4093933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1571044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5696105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6586303710938</t>
+    <t xml:space="preserve">62.887279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5134468078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2433280944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2077178955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3946380615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9376411437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4094085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1570816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5696411132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6586532592773</t>
   </si>
   <si>
     <t xml:space="preserve">65.2105178833008</t>
   </si>
   <si>
-    <t xml:space="preserve">65.254997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7979965209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1006240844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6911697387695</t>
+    <t xml:space="preserve">65.2550201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7980117797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1006317138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6912002563477</t>
   </si>
   <si>
     <t xml:space="preserve">66.4967346191406</t>
   </si>
   <si>
-    <t xml:space="preserve">66.7281646728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.833610534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9582214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1615371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3039779663086</t>
+    <t xml:space="preserve">66.728157043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8335876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9582061767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1615447998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3039855957031</t>
   </si>
   <si>
     <t xml:space="preserve">65.5220565795898</t>
@@ -344,46 +344,46 @@
     <t xml:space="preserve">66.3320693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2608489990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8202590942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2564086914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5189743041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7860488891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3988342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3557052612305</t>
+    <t xml:space="preserve">66.260856628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8202362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2563705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5190048217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7860260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3988189697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3556900024414</t>
   </si>
   <si>
     <t xml:space="preserve">68.1212158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">68.1657180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1568298339844</t>
+    <t xml:space="preserve">68.1657333374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1567916870117</t>
   </si>
   <si>
     <t xml:space="preserve">68.6018676757812</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3971557617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5960693359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1448669433594</t>
+    <t xml:space="preserve">68.3971328735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5960540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.144889831543</t>
   </si>
   <si>
     <t xml:space="preserve">71.6194000244141</t>
@@ -392,154 +392,154 @@
     <t xml:space="preserve">72.5273208618164</t>
   </si>
   <si>
-    <t xml:space="preserve">73.622184753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5153732299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9306793212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6961822509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2124404907227</t>
+    <t xml:space="preserve">73.6221771240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5153656005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6961898803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2124633789062</t>
   </si>
   <si>
     <t xml:space="preserve">76.8355331420898</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4733734130859</t>
+    <t xml:space="preserve">78.4733505249023</t>
   </si>
   <si>
     <t xml:space="preserve">78.9362258911133</t>
   </si>
   <si>
-    <t xml:space="preserve">78.5623779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7137069702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8352432250977</t>
+    <t xml:space="preserve">78.5623931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.7136993408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8352584838867</t>
   </si>
   <si>
     <t xml:space="preserve">79.8441467285156</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8048400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4318695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9513778686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.569465637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7844009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4587249755859</t>
+    <t xml:space="preserve">80.8048324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4318771362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9513702392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5694274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7844161987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4587326049805</t>
   </si>
   <si>
     <t xml:space="preserve">81.3691482543945</t>
   </si>
   <si>
-    <t xml:space="preserve">80.9033737182617</t>
+    <t xml:space="preserve">80.9033584594727</t>
   </si>
   <si>
     <t xml:space="preserve">80.6884002685547</t>
   </si>
   <si>
-    <t xml:space="preserve">80.6346282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.5809097290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9839935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8496322631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2168884277344</t>
+    <t xml:space="preserve">80.6346588134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.5809020996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9839859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8496170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2168731689453</t>
   </si>
   <si>
     <t xml:space="preserve">81.0914688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">81.2527008056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2852935791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.321159362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4888229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8618011474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7812118530273</t>
+    <t xml:space="preserve">81.2526931762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2853240966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3211441040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4888381958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8618240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7811965942383</t>
   </si>
   <si>
     <t xml:space="preserve">81.3960189819336</t>
   </si>
   <si>
-    <t xml:space="preserve">81.6109924316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9782485961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3569717407227</t>
+    <t xml:space="preserve">81.6110000610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9782562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3569641113281</t>
   </si>
   <si>
     <t xml:space="preserve">81.1810455322266</t>
   </si>
   <si>
-    <t xml:space="preserve">80.6077728271484</t>
+    <t xml:space="preserve">80.6077651977539</t>
   </si>
   <si>
     <t xml:space="preserve">81.0735473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">82.2380294799805</t>
+    <t xml:space="preserve">82.2380142211914</t>
   </si>
   <si>
     <t xml:space="preserve">83.115852355957</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2949905395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2810440063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2248306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5057067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7980880737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1531372070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2477111816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4537124633789</t>
+    <t xml:space="preserve">83.2949829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2810287475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2248153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5056991577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7980728149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1531600952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2477188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4537353515625</t>
   </si>
   <si>
     <t xml:space="preserve">85.8478622436523</t>
@@ -548,40 +548,40 @@
     <t xml:space="preserve">85.3014678955078</t>
   </si>
   <si>
-    <t xml:space="preserve">86.8958740234375</t>
+    <t xml:space="preserve">86.895881652832</t>
   </si>
   <si>
     <t xml:space="preserve">88.3201065063477</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9976577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7378616333008</t>
+    <t xml:space="preserve">87.9976196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7378921508789</t>
   </si>
   <si>
     <t xml:space="preserve">85.3552017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7435836791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1402359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2681274414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2029418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0660629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.817756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6980972290039</t>
+    <t xml:space="preserve">86.7436065673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1402282714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2681198120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2029266357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0660781860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8177337646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6980667114258</t>
   </si>
   <si>
     <t xml:space="preserve">87.1287689208984</t>
@@ -593,55 +593,55 @@
     <t xml:space="preserve">82.9725189208984</t>
   </si>
   <si>
-    <t xml:space="preserve">86.2061614990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7289276123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.2369766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3591613769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9741668701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7129287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5325698852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5685272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9740753173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3705062866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1991653442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8839721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.406364440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2171020507812</t>
+    <t xml:space="preserve">86.2061462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7289047241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.2370071411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3591766357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9741516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7129364013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5325546264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5685195922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9740600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3705215454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1991882324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8839645385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.406379699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2171096801758</t>
   </si>
   <si>
     <t xml:space="preserve">92.7665252685547</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8475036621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0457000732422</t>
+    <t xml:space="preserve">93.8475112915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0456771850586</t>
   </si>
   <si>
     <t xml:space="preserve">90.1541366577148</t>
@@ -650,145 +650,145 @@
     <t xml:space="preserve">89.6046447753906</t>
   </si>
   <si>
-    <t xml:space="preserve">88.388557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3162002563477</t>
+    <t xml:space="preserve">88.3885345458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3161926269531</t>
   </si>
   <si>
     <t xml:space="preserve">89.7487640380859</t>
   </si>
   <si>
-    <t xml:space="preserve">87.8930892944336</t>
+    <t xml:space="preserve">87.8930969238281</t>
   </si>
   <si>
     <t xml:space="preserve">84.8933563232422</t>
   </si>
   <si>
-    <t xml:space="preserve">86.893180847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0643844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2627563476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7760620117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5056304931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3252868652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0190887451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1812744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6315765380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6135559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4513244628906</t>
+    <t xml:space="preserve">86.8931579589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0644378662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2627639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7760543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5056457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3252944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0190963745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1812591552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6315689086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6135635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4513320922852</t>
   </si>
   <si>
     <t xml:space="preserve">90.8747863769531</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6676025390625</t>
+    <t xml:space="preserve">90.667610168457</t>
   </si>
   <si>
     <t xml:space="preserve">89.9919891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">89.7217483520508</t>
+    <t xml:space="preserve">89.7217636108398</t>
   </si>
   <si>
     <t xml:space="preserve">92.3521347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3700714111328</t>
+    <t xml:space="preserve">93.3700866699219</t>
   </si>
   <si>
     <t xml:space="preserve">91.6675186157227</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5863647460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.424201965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0998153686523</t>
+    <t xml:space="preserve">92.5863494873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4242095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0998229980469</t>
   </si>
   <si>
     <t xml:space="preserve">92.6674270629883</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6585998535156</t>
+    <t xml:space="preserve">90.6585922241211</t>
   </si>
   <si>
     <t xml:space="preserve">90.0820846557617</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7666168212891</t>
+    <t xml:space="preserve">91.7665939331055</t>
   </si>
   <si>
     <t xml:space="preserve">93.5052032470703</t>
   </si>
   <si>
-    <t xml:space="preserve">94.4150085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7394332885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6852035522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0997161865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4961776733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.604362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9646148681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3970031738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1717910766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.3154602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6569442749023</t>
+    <t xml:space="preserve">94.4150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7393951416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.685173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0997467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4961929321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.604377746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9646072387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3970184326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1717987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.3154830932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6569519042969</t>
   </si>
   <si>
     <t xml:space="preserve">99.0891036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6750793457031</t>
+    <t xml:space="preserve">97.6750869750977</t>
   </si>
   <si>
     <t xml:space="preserve">97.738525390625</t>
   </si>
   <si>
-    <t xml:space="preserve">98.2370452880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0437774658203</t>
+    <t xml:space="preserve">98.2370529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0437850952148</t>
   </si>
   <si>
     <t xml:space="preserve">99.2522506713867</t>
@@ -797,19 +797,19 @@
     <t xml:space="preserve">99.3247528076172</t>
   </si>
   <si>
-    <t xml:space="preserve">99.6963729858398</t>
+    <t xml:space="preserve">99.696403503418</t>
   </si>
   <si>
     <t xml:space="preserve">100.52123260498</t>
   </si>
   <si>
-    <t xml:space="preserve">101.51830291748</t>
+    <t xml:space="preserve">101.518287658691</t>
   </si>
   <si>
     <t xml:space="preserve">100.475898742676</t>
   </si>
   <si>
-    <t xml:space="preserve">102.189018249512</t>
+    <t xml:space="preserve">102.189033508301</t>
   </si>
   <si>
     <t xml:space="preserve">101.318862915039</t>
@@ -824,31 +824,31 @@
     <t xml:space="preserve">98.907829284668</t>
   </si>
   <si>
-    <t xml:space="preserve">99.4969863891602</t>
+    <t xml:space="preserve">99.4969787597656</t>
   </si>
   <si>
     <t xml:space="preserve">99.1616058349609</t>
   </si>
   <si>
-    <t xml:space="preserve">99.5966949462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.865646362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.034950256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.524398803711</t>
+    <t xml:space="preserve">99.5966720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.865684509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.034912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.524406433105</t>
   </si>
   <si>
     <t xml:space="preserve">102.823532104492</t>
   </si>
   <si>
-    <t xml:space="preserve">104.101547241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.588081359863</t>
+    <t xml:space="preserve">104.1015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.588088989258</t>
   </si>
   <si>
     <t xml:space="preserve">104.446006774902</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">104.862953186035</t>
   </si>
   <si>
-    <t xml:space="preserve">104.300979614258</t>
+    <t xml:space="preserve">104.300971984863</t>
   </si>
   <si>
     <t xml:space="preserve">105.270843505859</t>
@@ -866,145 +866,145 @@
     <t xml:space="preserve">105.352409362793</t>
   </si>
   <si>
-    <t xml:space="preserve">103.494262695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.346076965332</t>
+    <t xml:space="preserve">103.494270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.346038818359</t>
   </si>
   <si>
     <t xml:space="preserve">102.207160949707</t>
   </si>
   <si>
-    <t xml:space="preserve">101.880836486816</t>
+    <t xml:space="preserve">101.880851745605</t>
   </si>
   <si>
     <t xml:space="preserve">102.787261962891</t>
   </si>
   <si>
-    <t xml:space="preserve">100.068016052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0165863037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8862838745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4722595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7020568847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7716369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9347915649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7867965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0587539672852</t>
+    <t xml:space="preserve">100.068023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0165710449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8862762451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.472282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7020645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7716217041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9347686767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7868118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0587463378906</t>
   </si>
   <si>
     <t xml:space="preserve">94.5751571655273</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9739990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9044036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7775115966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0494384765625</t>
+    <t xml:space="preserve">94.9739685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9043884277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7775268554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.049446105957</t>
   </si>
   <si>
     <t xml:space="preserve">93.0342559814453</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3816299438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.43603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1430053710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3061828613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.755241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6242065429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.882942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4816055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3903884887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.0802612304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.1350173950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4086303710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2228622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9376754760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9890594482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5728302001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6324234008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5627899169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0918426513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5834655761719</t>
+    <t xml:space="preserve">92.3816528320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4360427856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1430358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3061752319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7552490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6241912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.882926940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4815979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.390380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0802459716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.1349945068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4086227416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2228851318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9376678466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9890441894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5728073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6324157714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5627975463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0918197631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5834579467773</t>
   </si>
   <si>
     <t xml:space="preserve">91.2128448486328</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7999420166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4201965332031</t>
+    <t xml:space="preserve">92.7999572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4202041625977</t>
   </si>
   <si>
     <t xml:space="preserve">93.4931716918945</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9094009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6357574462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3107299804688</t>
+    <t xml:space="preserve">92.9094085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6357650756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3107376098633</t>
   </si>
   <si>
     <t xml:space="preserve">89.2608795166016</t>
@@ -1013,70 +1013,70 @@
     <t xml:space="preserve">89.8720092773438</t>
   </si>
   <si>
-    <t xml:space="preserve">90.3098220825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3405303955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2709121704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3621139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7567825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1249694824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3885803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6521987915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5643539428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4764404296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0204086303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5004959106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3819122314453</t>
+    <t xml:space="preserve">90.3098373413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3405380249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2709197998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3621292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7567749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1249618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3885955810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6521911621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.564323425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4764556884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0203857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5004653930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3818817138672</t>
   </si>
   <si>
     <t xml:space="preserve">86.5245132446289</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9349746704102</t>
+    <t xml:space="preserve">86.934944152832</t>
   </si>
   <si>
     <t xml:space="preserve">87.9474258422852</t>
   </si>
   <si>
-    <t xml:space="preserve">89.306510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3703536987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9507522583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2243804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1183013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.775016784668</t>
+    <t xml:space="preserve">89.3064880371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3703460693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9507598876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2244033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.118278503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7750091552734</t>
   </si>
   <si>
     <t xml:space="preserve">91.3040390014648</t>
@@ -1085,34 +1085,34 @@
     <t xml:space="preserve">89.9176254272461</t>
   </si>
   <si>
-    <t xml:space="preserve">90.5469818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4980621337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7452239990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7418746948242</t>
+    <t xml:space="preserve">90.5469741821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.498046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7452087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7418670654297</t>
   </si>
   <si>
     <t xml:space="preserve">91.431755065918</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0702667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4236679077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4408187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7804565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7908706665039</t>
+    <t xml:space="preserve">92.0702362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4236602783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.440788269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7804718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7908554077148</t>
   </si>
   <si>
     <t xml:space="preserve">93.0479125976562</t>
@@ -1121,37 +1121,37 @@
     <t xml:space="preserve">92.074836730957</t>
   </si>
   <si>
-    <t xml:space="preserve">91.4230651855469</t>
+    <t xml:space="preserve">91.4230422973633</t>
   </si>
   <si>
     <t xml:space="preserve">91.9095993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7541427612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8190155029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6085052490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8104476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2878265380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0197601318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7712783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6990814208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9193725585938</t>
+    <t xml:space="preserve">92.7541656494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8190078735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6084823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8104553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2878036499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0197677612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7712631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6990737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9193801879883</t>
   </si>
   <si>
     <t xml:space="preserve">92.0381164550781</t>
@@ -1160,196 +1160,196 @@
     <t xml:space="preserve">91.6801071166992</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7443466186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9928283691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9389877319336</t>
+    <t xml:space="preserve">91.7443542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9928131103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9389724731445</t>
   </si>
   <si>
     <t xml:space="preserve">96.7015151977539</t>
   </si>
   <si>
-    <t xml:space="preserve">94.4065093994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.66357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.433464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9940414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4714126586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6354217529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9634323120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5044403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4224624633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8814544677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3404388427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7969665527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5589141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8165512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2033538818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6886596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1397018432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7174224853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0944290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0931625366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8006820678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4885482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0209808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1495056152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4616165161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.450065612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6510009765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7433776855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4823989868164</t>
+    <t xml:space="preserve">94.4065322875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6635818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4334411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9940567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4714279174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6354293823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9634552001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5044326782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4224243164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8814392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3404541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7969589233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5589294433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8165664672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.203369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6886672973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1396865844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7174301147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0944366455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0931854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4885406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0209884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1494903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4616470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4500579833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.651008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7433624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4824066162109</t>
   </si>
   <si>
     <t xml:space="preserve">96.0920715332031</t>
   </si>
   <si>
-    <t xml:space="preserve">95.6856155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0158767700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5493621826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8634414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3830642700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1267242431641</t>
+    <t xml:space="preserve">95.6856384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0158920288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5493545532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8634338378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3830718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1267395019531</t>
   </si>
   <si>
     <t xml:space="preserve">98.4939270019531</t>
   </si>
   <si>
-    <t xml:space="preserve">100.600173950195</t>
+    <t xml:space="preserve">100.600166320801</t>
   </si>
   <si>
     <t xml:space="preserve">99.9165649414062</t>
   </si>
   <si>
-    <t xml:space="preserve">100.359977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.212173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.784912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.710990905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.727203369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.202949523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.269897460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.008903503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.429260253906</t>
+    <t xml:space="preserve">100.359985351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.212158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.78491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.711013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.727180480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.202941894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.269905090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.008926391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.429214477539</t>
   </si>
   <si>
     <t xml:space="preserve">109.653251647949</t>
   </si>
   <si>
-    <t xml:space="preserve">108.988105773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.064353942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.341468811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.265266418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.135917663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.819534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.893447875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.886497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.10587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.269874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.454620361328</t>
+    <t xml:space="preserve">108.988128662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.064331054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.34147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.265258789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.135940551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.819519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.893455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.886489868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.105903625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.269844055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.454627990723</t>
   </si>
   <si>
     <t xml:space="preserve">116.50772857666</t>
@@ -1361,10 +1361,10 @@
     <t xml:space="preserve">117.376098632812</t>
   </si>
   <si>
-    <t xml:space="preserve">116.710960388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.486946105957</t>
+    <t xml:space="preserve">116.710983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.486961364746</t>
   </si>
   <si>
     <t xml:space="preserve">117.394584655762</t>
@@ -1373,67 +1373,67 @@
     <t xml:space="preserve">117.320678710938</t>
   </si>
   <si>
-    <t xml:space="preserve">117.413055419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.322975158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.115119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.092025756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.135902404785</t>
+    <t xml:space="preserve">117.413040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.32299041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.115142822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.09203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.135932922363</t>
   </si>
   <si>
     <t xml:space="preserve">117.339141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">119.611625671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623207092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.156677246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473091125488</t>
+    <t xml:space="preserve">119.61164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623176574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.156661987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473121643066</t>
   </si>
   <si>
     <t xml:space="preserve">121.274482727051</t>
   </si>
   <si>
-    <t xml:space="preserve">121.292953491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.586242675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.549095153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.248542785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.616836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.229972839355</t>
+    <t xml:space="preserve">121.292930603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.586235046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.549102783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.248558044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.616844177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.229927062988</t>
   </si>
   <si>
     <t xml:space="preserve">122.270393371582</t>
   </si>
   <si>
-    <t xml:space="preserve">121.787338256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.780769348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.049621582031</t>
+    <t xml:space="preserve">121.787322998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.78076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.049629211426</t>
   </si>
   <si>
     <t xml:space="preserve">116.009170532227</t>
@@ -1442,181 +1442,181 @@
     <t xml:space="preserve">113.01789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">104.620048522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.05721282959</t>
+    <t xml:space="preserve">104.620056152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.057235717773</t>
   </si>
   <si>
     <t xml:space="preserve">112.441947937012</t>
   </si>
   <si>
-    <t xml:space="preserve">111.104232788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.306411743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.507514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.881271362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.937004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.135940551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.700927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.5654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.609176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.123924255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.597152709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.056182861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.120651245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.768699645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.270317077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.771957397461</t>
+    <t xml:space="preserve">111.104248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.306442260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.507530212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.881278991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.937019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.135963439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.700942993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.565437316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.609153747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.12393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.597137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.056167602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.120620727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.768692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270332336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.771965026855</t>
   </si>
   <si>
     <t xml:space="preserve">110.844116210938</t>
   </si>
   <si>
-    <t xml:space="preserve">111.680191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.365455627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.798248291016</t>
+    <t xml:space="preserve">111.680198669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.36547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.798240661621</t>
   </si>
   <si>
     <t xml:space="preserve">121.694427490234</t>
   </si>
   <si>
-    <t xml:space="preserve">120.300987243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623374938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.552383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.339248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.661666870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.913040161133</t>
+    <t xml:space="preserve">120.300979614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623413085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.552345275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.339263916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.661682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.913024902344</t>
   </si>
   <si>
     <t xml:space="preserve">131.448577880859</t>
   </si>
   <si>
-    <t xml:space="preserve">135.62890625</t>
+    <t xml:space="preserve">135.628921508789</t>
   </si>
   <si>
     <t xml:space="preserve">132.377532958984</t>
   </si>
   <si>
-    <t xml:space="preserve">134.235488891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.285751342773</t>
+    <t xml:space="preserve">134.235473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.285781860352</t>
   </si>
   <si>
     <t xml:space="preserve">139.67919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">140.218002319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.557846069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.232192993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.117446899414</t>
+    <t xml:space="preserve">140.217956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.557876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.232177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.117401123047</t>
   </si>
   <si>
     <t xml:space="preserve">129.367691040039</t>
   </si>
   <si>
-    <t xml:space="preserve">134.272598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.405960083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.492294311523</t>
+    <t xml:space="preserve">134.27262878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.405944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.492279052734</t>
   </si>
   <si>
     <t xml:space="preserve">132.154586791992</t>
   </si>
   <si>
-    <t xml:space="preserve">135.182998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.263885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.83332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.889297485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.347793579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.561569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.911758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.942657470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.689590454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.399215698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.347007751465</t>
+    <t xml:space="preserve">135.183013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.263900756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.833297729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.889282226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.347778320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.561584472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.050903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.91178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.942672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.689605712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.399185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.346992492676</t>
   </si>
   <si>
     <t xml:space="preserve">121.771903991699</t>
   </si>
   <si>
-    <t xml:space="preserve">127.76619720459</t>
+    <t xml:space="preserve">127.766166687012</t>
   </si>
   <si>
     <t xml:space="preserve">127.56078338623</t>
@@ -1625,115 +1625,115 @@
     <t xml:space="preserve">126.589736938477</t>
   </si>
   <si>
-    <t xml:space="preserve">125.954833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.180847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.002487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.873687744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.143493652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.554290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.846618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.016555786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.97274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.142364501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.077972412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.011657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.650360107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.322647094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.984603881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.455230712891</t>
+    <t xml:space="preserve">125.954849243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.180793762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.002449035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.873672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.143478393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.554275512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.846572875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.016548156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.972724914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.142349243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.07795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.011627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.650344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.32258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.984588623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.455200195312</t>
   </si>
   <si>
     <t xml:space="preserve">132.621368408203</t>
   </si>
   <si>
-    <t xml:space="preserve">134.488754272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.61946105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.412170410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.37483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.441146850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.484954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.055465698242</t>
+    <t xml:space="preserve">134.488739013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.619522094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.412155151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.374847412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.441116333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.484970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.055480957031</t>
   </si>
   <si>
     <t xml:space="preserve">138.148834228516</t>
   </si>
   <si>
-    <t xml:space="preserve">136.225402832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.12370300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.43083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.208648681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.179733276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.125549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.833267211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.795944213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.239547729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.355377197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.448707580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.793273925781</t>
+    <t xml:space="preserve">136.225387573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.123687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.430877685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.208679199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.179702758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.125610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.833282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.795913696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.239517211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.355361938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.448745727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.793243408203</t>
   </si>
   <si>
     <t xml:space="preserve">120.334037780762</t>
@@ -1745,70 +1745,70 @@
     <t xml:space="preserve">121.473129272461</t>
   </si>
   <si>
-    <t xml:space="preserve">122.854957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.155685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.717781066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.800880432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.875564575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.736465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.221984863281</t>
+    <t xml:space="preserve">122.854995727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.155662536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.717803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.80086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.875556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.736473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.221977233887</t>
   </si>
   <si>
     <t xml:space="preserve">119.245346069336</t>
   </si>
   <si>
-    <t xml:space="preserve">119.733673095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.409797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.578826904297</t>
+    <t xml:space="preserve">119.733665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.409805297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.578834533691</t>
   </si>
   <si>
     <t xml:space="preserve">121.480361938477</t>
   </si>
   <si>
-    <t xml:space="preserve">120.071746826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.174758911133</t>
+    <t xml:space="preserve">120.071739196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.174766540527</t>
   </si>
   <si>
     <t xml:space="preserve">118.062072753906</t>
   </si>
   <si>
-    <t xml:space="preserve">119.207786560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.42350769043</t>
+    <t xml:space="preserve">119.207763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.423492431641</t>
   </si>
   <si>
     <t xml:space="preserve">119.170196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">117.479850769043</t>
+    <t xml:space="preserve">117.479835510254</t>
   </si>
   <si>
     <t xml:space="preserve">116.446846008301</t>
   </si>
   <si>
-    <t xml:space="preserve">116.052436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.832122802734</t>
+    <t xml:space="preserve">116.052421569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.832138061523</t>
   </si>
   <si>
     <t xml:space="preserve">119.30167388916</t>
@@ -1817,22 +1817,22 @@
     <t xml:space="preserve">118.099647521973</t>
   </si>
   <si>
-    <t xml:space="preserve">118.625518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.799140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.686965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.592529296875</t>
+    <t xml:space="preserve">118.625541687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.799133300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.686935424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.592544555664</t>
   </si>
   <si>
     <t xml:space="preserve">117.554969787598</t>
   </si>
   <si>
-    <t xml:space="preserve">119.639755249023</t>
+    <t xml:space="preserve">119.639747619629</t>
   </si>
   <si>
     <t xml:space="preserve">120.710296630859</t>
@@ -1841,145 +1841,145 @@
     <t xml:space="preserve">120.729080200195</t>
   </si>
   <si>
-    <t xml:space="preserve">121.611854553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.597633361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.334671020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.58341217041</t>
+    <t xml:space="preserve">121.611824035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.597625732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.334655761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.583389282227</t>
   </si>
   <si>
     <t xml:space="preserve">120.785415649414</t>
   </si>
   <si>
-    <t xml:space="preserve">118.193550109863</t>
+    <t xml:space="preserve">118.193557739258</t>
   </si>
   <si>
     <t xml:space="preserve">116.709785461426</t>
   </si>
   <si>
-    <t xml:space="preserve">115.97730255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.747352600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.108787536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.424011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.335205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.546356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.231628417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.86971282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.06664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.34839630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.150909423828</t>
+    <t xml:space="preserve">115.977294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.747360229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.108764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.42399597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.335189819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.546333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.23161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.869689941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.066635131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.348373413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.150901794434</t>
   </si>
   <si>
     <t xml:space="preserve">113.12247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">112.615371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.939239501953</t>
+    <t xml:space="preserve">112.615364074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.939231872559</t>
   </si>
   <si>
     <t xml:space="preserve">113.347854614258</t>
   </si>
   <si>
-    <t xml:space="preserve">111.563598632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.229591369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.835151672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.53010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.666114807129</t>
+    <t xml:space="preserve">111.563591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.229583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.835166931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.530090332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.666107177734</t>
   </si>
   <si>
     <t xml:space="preserve">105.684906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">106.511299133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.137214660645</t>
+    <t xml:space="preserve">106.511306762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.137237548828</t>
   </si>
   <si>
     <t xml:space="preserve">116.221473693848</t>
   </si>
   <si>
-    <t xml:space="preserve">116.202690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.573249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.104194641113</t>
+    <t xml:space="preserve">116.202697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.5732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.104217529297</t>
   </si>
   <si>
     <t xml:space="preserve">115.319946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">112.939102172852</t>
+    <t xml:space="preserve">112.939086914062</t>
   </si>
   <si>
     <t xml:space="preserve">113.97834777832</t>
   </si>
   <si>
-    <t xml:space="preserve">113.35481262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.221038818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.504486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.164367675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.359199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.901306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.338851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.449279785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.318481445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.830123901367</t>
+    <t xml:space="preserve">113.354804992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.221069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.504501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.164398193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.35920715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.90128326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.338844299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.449287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.318458557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.830116271973</t>
   </si>
   <si>
     <t xml:space="preserve">114.828659057617</t>
@@ -1991,301 +1991,301 @@
     <t xml:space="preserve">112.447807312012</t>
   </si>
   <si>
-    <t xml:space="preserve">114.469627380371</t>
+    <t xml:space="preserve">114.469657897949</t>
   </si>
   <si>
     <t xml:space="preserve">116.151344299316</t>
   </si>
   <si>
-    <t xml:space="preserve">122.651466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.841850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.353492736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.84334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.411666870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.327423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.948120117188</t>
+    <t xml:space="preserve">122.651420593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.841873168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.353500366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.843353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.411651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.327438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.948104858398</t>
   </si>
   <si>
     <t xml:space="preserve">131.267868041992</t>
   </si>
   <si>
-    <t xml:space="preserve">129.737335205078</t>
+    <t xml:space="preserve">129.737274169922</t>
   </si>
   <si>
     <t xml:space="preserve">129.96403503418</t>
   </si>
   <si>
-    <t xml:space="preserve">129.416076660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.583206176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.471298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.113754272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.827392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.392753601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.904418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.016319274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.603485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.11833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.978713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.645950317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.119781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.047134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.839263916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.714370727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.833633422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.076309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.760986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.032821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.996505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.992156982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.125854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.349670410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.804656982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.72021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.962966918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.137405395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.704284667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.461578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.814712524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.157775878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.0087890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.819534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.560836791992</t>
+    <t xml:space="preserve">129.416046142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.58317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.471282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.113739013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.827407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.392784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.904449462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.016288757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.603546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.118347167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.978729248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.645919799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.11979675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.047164916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.839233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.71435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.833587646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.076324462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.760940551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.032836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.996536254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.992141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.125839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.349716186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.804641723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.720260620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.962951660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.137390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.70426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.461547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.814697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.157791137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.008773803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.819519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.56086730957</t>
   </si>
   <si>
     <t xml:space="preserve">159.793975830078</t>
   </si>
   <si>
-    <t xml:space="preserve">161.161376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.832000732422</t>
+    <t xml:space="preserve">161.161346435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.831985473633</t>
   </si>
   <si>
     <t xml:space="preserve">157.856842041016</t>
   </si>
   <si>
-    <t xml:space="preserve">154.932144165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.20524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.964935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.970825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.907928466797</t>
+    <t xml:space="preserve">154.932159423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.205261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.964920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.970809936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.907913208008</t>
   </si>
   <si>
     <t xml:space="preserve">162.376815795898</t>
   </si>
   <si>
-    <t xml:space="preserve">162.756622314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.958389282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.338165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.6171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.884338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.409530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.890213012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.661666870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.326385498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.741607666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.93147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.08283996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.183685302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.753372192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.133193969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.462615966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.474487304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.993728637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.892929077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.602127075195</t>
+    <t xml:space="preserve">162.756652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.95832824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.338180541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.617126464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.884323120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.409515380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.890274047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.661697387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.326400756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.741592407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.931549072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.082809448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.183670043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.75341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.133239746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.462631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.47444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.993774414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.89289855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.602142333984</t>
   </si>
   <si>
     <t xml:space="preserve">150.792068481445</t>
   </si>
   <si>
-    <t xml:space="preserve">151.399749755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.456741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.703002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.284515380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.234100341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.854293823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.904708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.424026489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.323135375977</t>
+    <t xml:space="preserve">151.399765014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.456756591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.702987670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.284530639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.234115600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.854263305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.904693603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.424041748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.323165893555</t>
   </si>
   <si>
     <t xml:space="preserve">149.842468261719</t>
   </si>
   <si>
-    <t xml:space="preserve">150.412231445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.652526855469</t>
+    <t xml:space="preserve">150.412200927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.652557373047</t>
   </si>
   <si>
     <t xml:space="preserve">148.513076782227</t>
   </si>
   <si>
-    <t xml:space="preserve">146.803833007812</t>
+    <t xml:space="preserve">146.80387878418</t>
   </si>
   <si>
     <t xml:space="preserve">143.955139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">140.346740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.486221313477</t>
+    <t xml:space="preserve">140.346771240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.486236572266</t>
   </si>
   <si>
     <t xml:space="preserve">143.575271606445</t>
   </si>
   <si>
-    <t xml:space="preserve">146.044189453125</t>
+    <t xml:space="preserve">146.044174194336</t>
   </si>
   <si>
     <t xml:space="preserve">152.121444702148</t>
   </si>
   <si>
-    <t xml:space="preserve">152.691192626953</t>
+    <t xml:space="preserve">152.691207885742</t>
   </si>
   <si>
     <t xml:space="preserve">153.071014404297</t>
@@ -2294,34 +2294,34 @@
     <t xml:space="preserve">151.836547851562</t>
   </si>
   <si>
-    <t xml:space="preserve">153.693588256836</t>
+    <t xml:space="preserve">153.693542480469</t>
   </si>
   <si>
     <t xml:space="preserve">155.220932006836</t>
   </si>
   <si>
-    <t xml:space="preserve">154.457244873047</t>
+    <t xml:space="preserve">154.457214355469</t>
   </si>
   <si>
     <t xml:space="preserve">152.929840087891</t>
   </si>
   <si>
-    <t xml:space="preserve">153.979888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.175537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.702926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.984603881836</t>
+    <t xml:space="preserve">153.979919433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.175521850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.702941894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.984588623047</t>
   </si>
   <si>
     <t xml:space="preserve">154.361755371094</t>
   </si>
   <si>
-    <t xml:space="preserve">156.748306274414</t>
+    <t xml:space="preserve">156.748291015625</t>
   </si>
   <si>
     <t xml:space="preserve">157.225631713867</t>
@@ -2330,31 +2330,31 @@
     <t xml:space="preserve">154.839096069336</t>
   </si>
   <si>
-    <t xml:space="preserve">156.366500854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.803115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.640380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.876663208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.07698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.000335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.365737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.749923706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.840682983398</t>
+    <t xml:space="preserve">156.366470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.803085327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.640365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.876678466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.077011108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.00032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.36572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.749893188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.84065246582</t>
   </si>
   <si>
     <t xml:space="preserve">176.222534179688</t>
@@ -2366,73 +2366,73 @@
     <t xml:space="preserve">176.270263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">179.038635253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.799987792969</t>
+    <t xml:space="preserve">179.038665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.800018310547</t>
   </si>
   <si>
     <t xml:space="preserve">174.265594482422</t>
   </si>
   <si>
-    <t xml:space="preserve">185.243698120117</t>
+    <t xml:space="preserve">185.243637084961</t>
   </si>
   <si>
     <t xml:space="preserve">184.527709960938</t>
   </si>
   <si>
-    <t xml:space="preserve">182.093399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.432250976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.291397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.102828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.7734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.491744995117</t>
+    <t xml:space="preserve">182.093414306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.432235717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.291412353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.102813720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.773406982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.491760253906</t>
   </si>
   <si>
     <t xml:space="preserve">188.9189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">189.969024658203</t>
+    <t xml:space="preserve">189.969039916992</t>
   </si>
   <si>
     <t xml:space="preserve">188.775772094727</t>
   </si>
   <si>
-    <t xml:space="preserve">192.06916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.682678222656</t>
+    <t xml:space="preserve">192.069198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.682647705078</t>
   </si>
   <si>
     <t xml:space="preserve">190.446319580078</t>
   </si>
   <si>
-    <t xml:space="preserve">190.828186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.584854125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.677978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.296096801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.591857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.973709106445</t>
+    <t xml:space="preserve">190.828155517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.584823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.677963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.296051025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.591873168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.973724365234</t>
   </si>
   <si>
     <t xml:space="preserve">193.882965087891</t>
@@ -2444,94 +2444,94 @@
     <t xml:space="preserve">197.415069580078</t>
   </si>
   <si>
-    <t xml:space="preserve">196.269515991211</t>
+    <t xml:space="preserve">196.269546508789</t>
   </si>
   <si>
     <t xml:space="preserve">199.515197753906</t>
   </si>
   <si>
-    <t xml:space="preserve">197.319595336914</t>
+    <t xml:space="preserve">197.319580078125</t>
   </si>
   <si>
     <t xml:space="preserve">196.84228515625</t>
   </si>
   <si>
-    <t xml:space="preserve">197.987838745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.152160644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.738983154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.975341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.929946899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.321151733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.703048706055</t>
+    <t xml:space="preserve">197.987854003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.15217590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.739013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.975357055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.929977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.321182250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.703018188477</t>
   </si>
   <si>
     <t xml:space="preserve">217.366592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">215.498092651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.564315795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.918045043945</t>
+    <t xml:space="preserve">215.498107910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.564361572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.918029785156</t>
   </si>
   <si>
     <t xml:space="preserve">223.930191040039</t>
   </si>
   <si>
-    <t xml:space="preserve">221.534774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.06787109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.205490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.444061279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.156600952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.294250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.048614501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.060745239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.186218261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.736694335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.982376098633</t>
+    <t xml:space="preserve">221.534729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.067825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.205444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.444091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.156631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.29426574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.048599243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.060806274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.186187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.736709594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.982360839844</t>
   </si>
   <si>
     <t xml:space="preserve">209.269805908203</t>
   </si>
   <si>
-    <t xml:space="preserve">210.994567871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.46142578125</t>
+    <t xml:space="preserve">210.994552612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.461471557617</t>
   </si>
   <si>
     <t xml:space="preserve">206.970153808594</t>
@@ -2543,34 +2543,34 @@
     <t xml:space="preserve">196.621643066406</t>
   </si>
   <si>
-    <t xml:space="preserve">191.447402954102</t>
+    <t xml:space="preserve">191.447418212891</t>
   </si>
   <si>
     <t xml:space="preserve">190.920379638672</t>
   </si>
   <si>
-    <t xml:space="preserve">191.495330810547</t>
+    <t xml:space="preserve">191.495300292969</t>
   </si>
   <si>
     <t xml:space="preserve">187.902069091797</t>
   </si>
   <si>
-    <t xml:space="preserve">187.087600708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.530990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.626800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.997894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.632965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.537139892578</t>
+    <t xml:space="preserve">187.087615966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.531005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.626815795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.997848510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.632919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.537124633789</t>
   </si>
   <si>
     <t xml:space="preserve">185.889846801758</t>
@@ -2582,34 +2582,34 @@
     <t xml:space="preserve">188.572814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">193.651260375977</t>
+    <t xml:space="preserve">193.651245117188</t>
   </si>
   <si>
     <t xml:space="preserve">189.770584106445</t>
   </si>
   <si>
-    <t xml:space="preserve">185.410766601562</t>
+    <t xml:space="preserve">185.410781860352</t>
   </si>
   <si>
     <t xml:space="preserve">190.39338684082</t>
   </si>
   <si>
-    <t xml:space="preserve">188.237457275391</t>
+    <t xml:space="preserve">188.237442016602</t>
   </si>
   <si>
     <t xml:space="preserve">192.501403808594</t>
   </si>
   <si>
-    <t xml:space="preserve">193.172180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.525817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.555450439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.938705444336</t>
+    <t xml:space="preserve">193.172164916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.525863647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.555404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.938674926758</t>
   </si>
   <si>
     <t xml:space="preserve">194.992706298828</t>
@@ -2621,190 +2621,190 @@
     <t xml:space="preserve">198.442230224609</t>
   </si>
   <si>
-    <t xml:space="preserve">198.729690551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.358627319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.538055419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.921310424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.987548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.849899291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.2158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.83251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.802947998047</t>
+    <t xml:space="preserve">198.729705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.358596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.538024902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.921325683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.987564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.849945068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.215805053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.832550048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.802932739258</t>
   </si>
   <si>
     <t xml:space="preserve">207.353439331055</t>
   </si>
   <si>
-    <t xml:space="preserve">213.006774902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.989410400391</t>
+    <t xml:space="preserve">213.006790161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.989379882812</t>
   </si>
   <si>
     <t xml:space="preserve">215.593902587891</t>
   </si>
   <si>
-    <t xml:space="preserve">215.977188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.905807495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220.768173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.892776489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.161651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.277481079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.297119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.200942993164</t>
+    <t xml:space="preserve">215.977203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.90576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.768142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.892791748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.161666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.277450561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.297149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.200958251953</t>
   </si>
   <si>
     <t xml:space="preserve">223.316787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">224.663208007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.509094238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.182357788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.067565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.162719726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.064407348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.238128662109</t>
+    <t xml:space="preserve">224.663238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.50910949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.182373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.067581176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.162704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.064392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.238159179688</t>
   </si>
   <si>
     <t xml:space="preserve">211.198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">209.756210327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.351867675781</t>
+    <t xml:space="preserve">209.756195068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.35188293457</t>
   </si>
   <si>
     <t xml:space="preserve">203.985763549805</t>
   </si>
   <si>
-    <t xml:space="preserve">208.313583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.640380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.50700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.929962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.279602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">237.646759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.25993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">225.625</t>
+    <t xml:space="preserve">208.313598632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.640350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.506973266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.929931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.279571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.646789550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.259948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">225.624969482422</t>
   </si>
   <si>
     <t xml:space="preserve">224.567031860352</t>
   </si>
   <si>
-    <t xml:space="preserve">232.068634033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.819458007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.434768676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.530914306641</t>
+    <t xml:space="preserve">232.068664550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.819427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.43473815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.53092956543</t>
   </si>
   <si>
     <t xml:space="preserve">228.317840576172</t>
   </si>
   <si>
-    <t xml:space="preserve">227.644607543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220.527709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.662139892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.12336730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.373641967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.256729125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.197723388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.544204711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.409759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.102661132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.948532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.15950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.042572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.869888305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.813079833984</t>
+    <t xml:space="preserve">227.644592285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.527755737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.662170410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.123382568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.373687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.256744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.19775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.544189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.409774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.102615356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.948577880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.159454345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.042633056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.869903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.813064575195</t>
   </si>
   <si>
     <t xml:space="preserve">208.121246337891</t>
@@ -2813,34 +2813,34 @@
     <t xml:space="preserve">207.92887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">208.98681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.794479370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.352920532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.101623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.63932800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.158432006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.139831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.927841186523</t>
+    <t xml:space="preserve">208.986801147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.794464111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.352890014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.101593017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.639282226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.158416748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.139846801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.927780151367</t>
   </si>
   <si>
     <t xml:space="preserve">200.234954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">198.959411621094</t>
+    <t xml:space="preserve">198.959442138672</t>
   </si>
   <si>
     <t xml:space="preserve">207.076293945312</t>
@@ -2849,22 +2849,22 @@
     <t xml:space="preserve">208.525726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">206.593139648438</t>
+    <t xml:space="preserve">206.593154907227</t>
   </si>
   <si>
     <t xml:space="preserve">204.853820800781</t>
   </si>
   <si>
-    <t xml:space="preserve">200.891998291016</t>
+    <t xml:space="preserve">200.892044067383</t>
   </si>
   <si>
     <t xml:space="preserve">203.404388427734</t>
   </si>
   <si>
-    <t xml:space="preserve">205.916717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.626876831055</t>
+    <t xml:space="preserve">205.916763305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.626846313477</t>
   </si>
   <si>
     <t xml:space="preserve">216.256072998047</t>
@@ -2876,61 +2876,61 @@
     <t xml:space="preserve">214.806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">221.957183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.116744995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.397613525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.909973144531</t>
+    <t xml:space="preserve">221.957153320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.116714477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.397644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.909957885742</t>
   </si>
   <si>
     <t xml:space="preserve">233.262786865234</t>
   </si>
   <si>
-    <t xml:space="preserve">232.393173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.23356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">237.417831420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">236.161682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.312225341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.408874511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">246.307723999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.332458496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.651550292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">249.882995605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.525680541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.105484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.294235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.004333496094</t>
+    <t xml:space="preserve">232.393157958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.233612060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.417877197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">236.161651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.312240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.40885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">246.307708740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.332443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.65153503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">249.883026123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.52571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.105514526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.294281005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.004302978516</t>
   </si>
   <si>
     <t xml:space="preserve">251.622344970703</t>
@@ -2939,28 +2939,28 @@
     <t xml:space="preserve">252.008850097656</t>
   </si>
   <si>
-    <t xml:space="preserve">250.656036376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.844772338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">257.468414306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260.802062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266.020050048828</t>
+    <t xml:space="preserve">250.656021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.844833374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">257.468353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260.802093505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266.02001953125</t>
   </si>
   <si>
     <t xml:space="preserve">275.48974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">276.890808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.006561279297</t>
+    <t xml:space="preserve">276.890869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.006530761719</t>
   </si>
   <si>
     <t xml:space="preserve">274.668365478516</t>
@@ -2969,31 +2969,31 @@
     <t xml:space="preserve">269.305480957031</t>
   </si>
   <si>
-    <t xml:space="preserve">269.692047119141</t>
+    <t xml:space="preserve">269.691955566406</t>
   </si>
   <si>
     <t xml:space="preserve">265.295379638672</t>
   </si>
   <si>
-    <t xml:space="preserve">263.555969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.796463012695</t>
+    <t xml:space="preserve">263.556030273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.796432495117</t>
   </si>
   <si>
     <t xml:space="preserve">252.347076416016</t>
   </si>
   <si>
-    <t xml:space="preserve">258.869537353516</t>
+    <t xml:space="preserve">258.869598388672</t>
   </si>
   <si>
     <t xml:space="preserve">269.595397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">268.822357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.730194091797</t>
+    <t xml:space="preserve">268.822418212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.730224609375</t>
   </si>
   <si>
     <t xml:space="preserve">265.536926269531</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">265.102111816406</t>
   </si>
   <si>
-    <t xml:space="preserve">263.942596435547</t>
+    <t xml:space="preserve">263.942565917969</t>
   </si>
   <si>
     <t xml:space="preserve">258.579620361328</t>
   </si>
   <si>
-    <t xml:space="preserve">266.454895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">267.405242919922</t>
+    <t xml:space="preserve">266.454864501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">267.405212402344</t>
   </si>
   <si>
     <t xml:space="preserve">281.854339599609</t>
@@ -3026,19 +3026,19 @@
     <t xml:space="preserve">277.005676269531</t>
   </si>
   <si>
-    <t xml:space="preserve">274.290435791016</t>
+    <t xml:space="preserve">274.290344238281</t>
   </si>
   <si>
     <t xml:space="preserve">263.623291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">271.090179443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.599517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.108459472656</t>
+    <t xml:space="preserve">271.090240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.599487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.108520507812</t>
   </si>
   <si>
     <t xml:space="preserve">280.642181396484</t>
@@ -3047,46 +3047,46 @@
     <t xml:space="preserve">281.466491699219</t>
   </si>
   <si>
-    <t xml:space="preserve">282.630157470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.532836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">280.205780029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">278.411834716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">284.084777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.769348144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.066131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270.750885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.471984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">271.817626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.611175537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.253936767578</t>
+    <t xml:space="preserve">282.630218505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.532806396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">280.205749511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">278.411804199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">284.084716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.769439697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.066192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270.750823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.472045898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271.817565917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.611236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.253967285156</t>
   </si>
   <si>
     <t xml:space="preserve">270.847808837891</t>
   </si>
   <si>
-    <t xml:space="preserve">274.484344482422</t>
+    <t xml:space="preserve">274.484313964844</t>
   </si>
   <si>
     <t xml:space="preserve">279.720916748047</t>
@@ -3095,103 +3095,103 @@
     <t xml:space="preserve">284.763580322266</t>
   </si>
   <si>
-    <t xml:space="preserve">298.291442871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.455017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.576141357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.552062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.679260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.842987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.946197509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.721954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.049682617188</t>
+    <t xml:space="preserve">298.291412353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.455139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.552093505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.679321289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.843017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.946166992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.721923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.049713134766</t>
   </si>
   <si>
     <t xml:space="preserve">312.740539550781</t>
   </si>
   <si>
-    <t xml:space="preserve">315.019378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.364990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.443389892578</t>
+    <t xml:space="preserve">315.019409179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.364929199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.443420410156</t>
   </si>
   <si>
     <t xml:space="preserve">311.625305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">318.122589111328</t>
+    <t xml:space="preserve">318.122528076172</t>
   </si>
   <si>
     <t xml:space="preserve">315.213317871094</t>
   </si>
   <si>
-    <t xml:space="preserve">309.879791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.825042724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.916168212891</t>
+    <t xml:space="preserve">309.879760742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.825073242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.916229248047</t>
   </si>
   <si>
     <t xml:space="preserve">312.837524414062</t>
   </si>
   <si>
-    <t xml:space="preserve">316.231506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.4677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.631469726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.661712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.425109863281</t>
+    <t xml:space="preserve">316.231567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.467864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.631500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.661743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.425201416016</t>
   </si>
   <si>
     <t xml:space="preserve">308.473663330078</t>
   </si>
   <si>
-    <t xml:space="preserve">300.667236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.854705810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">288.836486816406</t>
+    <t xml:space="preserve">300.667205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.854675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">288.836456298828</t>
   </si>
   <si>
     <t xml:space="preserve">289.369812011719</t>
   </si>
   <si>
-    <t xml:space="preserve">287.284881591797</t>
+    <t xml:space="preserve">287.284912109375</t>
   </si>
   <si>
     <t xml:space="preserve">285.539367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">283.84228515625</t>
+    <t xml:space="preserve">283.842315673828</t>
   </si>
   <si>
     <t xml:space="preserve">289.806793212891</t>
@@ -3200,112 +3200,112 @@
     <t xml:space="preserve">297.298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">298.369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.812561035156</t>
+    <t xml:space="preserve">298.369079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.8125</t>
   </si>
   <si>
     <t xml:space="preserve">303.574676513672</t>
   </si>
   <si>
-    <t xml:space="preserve">312.429016113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.126251220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.996429443359</t>
+    <t xml:space="preserve">312.428955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.126312255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.996398925781</t>
   </si>
   <si>
     <t xml:space="preserve">311.358642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">309.412628173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.229034423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.234039306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.925933837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294.185272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.250152587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.217834472656</t>
+    <t xml:space="preserve">309.412658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.228942871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.234161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.925903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.185241699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.250213623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.217926025391</t>
   </si>
   <si>
     <t xml:space="preserve">295.888000488281</t>
   </si>
   <si>
-    <t xml:space="preserve">304.596282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.963836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.688262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.585571289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.96923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.412445068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.342132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.796081542969</t>
+    <t xml:space="preserve">304.596313476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.9638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.688232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.585540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.298980712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.969207763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.412414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.342102050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.796112060547</t>
   </si>
   <si>
     <t xml:space="preserve">293.990661621094</t>
   </si>
   <si>
-    <t xml:space="preserve">297.104248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.601928710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.845123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.083038330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.883666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327.656280517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.445495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.612884521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320.066986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.348083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.721252441406</t>
+    <t xml:space="preserve">297.104217529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.601837158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.845153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.0830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.883728027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327.656311035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.445373535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.612823486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320.066925048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.348114013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.721221923828</t>
   </si>
   <si>
     <t xml:space="preserve">329.650939941406</t>
@@ -3314,13 +3314,13 @@
     <t xml:space="preserve">323.375152587891</t>
   </si>
   <si>
-    <t xml:space="preserve">325.758972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327.315704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.88330078125</t>
+    <t xml:space="preserve">325.758941650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327.315734863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.883270263672</t>
   </si>
   <si>
     <t xml:space="preserve">330.380706787109</t>
@@ -3329,28 +3329,28 @@
     <t xml:space="preserve">332.521270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">328.580718994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">326.245422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.710296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.515930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.759338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.543182373047</t>
+    <t xml:space="preserve">328.580688476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326.245452880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.710327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.515899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.759368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.543090820312</t>
   </si>
   <si>
     <t xml:space="preserve">347.456756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">347.748687744141</t>
+    <t xml:space="preserve">347.748657226562</t>
   </si>
   <si>
     <t xml:space="preserve">352.710968017578</t>
@@ -3362,13 +3362,13 @@
     <t xml:space="preserve">341.424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">353.829864501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">358.257019042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.473052978516</t>
+    <t xml:space="preserve">353.829833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">358.256958007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.473022460938</t>
   </si>
   <si>
     <t xml:space="preserve">352.224456787109</t>
@@ -3377,115 +3377,115 @@
     <t xml:space="preserve">353.635284423828</t>
   </si>
   <si>
-    <t xml:space="preserve">357.429962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">349.013580322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.672546386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.946624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.531280517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.921691894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.898681640625</t>
+    <t xml:space="preserve">357.430023193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">349.013549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.672607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.946594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.531311035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.921600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.898651123047</t>
   </si>
   <si>
     <t xml:space="preserve">339.972076416016</t>
   </si>
   <si>
-    <t xml:space="preserve">343.728942871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.606811523438</t>
+    <t xml:space="preserve">343.728973388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.606750488281</t>
   </si>
   <si>
     <t xml:space="preserve">339.581726074219</t>
   </si>
   <si>
-    <t xml:space="preserve">339.093811035156</t>
+    <t xml:space="preserve">339.093780517578</t>
   </si>
   <si>
     <t xml:space="preserve">342.704345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">345.095062255859</t>
+    <t xml:space="preserve">345.095031738281</t>
   </si>
   <si>
     <t xml:space="preserve">341.435760498047</t>
   </si>
   <si>
-    <t xml:space="preserve">344.509552001953</t>
+    <t xml:space="preserve">344.509582519531</t>
   </si>
   <si>
     <t xml:space="preserve">344.119293212891</t>
   </si>
   <si>
-    <t xml:space="preserve">346.510040283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.826843261719</t>
+    <t xml:space="preserve">346.509948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.826873779297</t>
   </si>
   <si>
     <t xml:space="preserve">342.070037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">345.582916259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.68017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.411224365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.801086425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.239349365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.751068115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.945404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.994171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.116363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.118408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.654693603516</t>
+    <t xml:space="preserve">345.582946777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.680145263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.411163330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.801116943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.239379882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.751037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.945373535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.994201660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.116333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.118377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.654663085938</t>
   </si>
   <si>
     <t xml:space="preserve">336.800628662109</t>
   </si>
   <si>
-    <t xml:space="preserve">335.141784667969</t>
+    <t xml:space="preserve">335.141845703125</t>
   </si>
   <si>
     <t xml:space="preserve">338.605895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">335.044250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.703094482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.629760742188</t>
+    <t xml:space="preserve">335.044219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.703063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.629730224609</t>
   </si>
   <si>
     <t xml:space="preserve">337.28857421875</t>
@@ -3494,13 +3494,13 @@
     <t xml:space="preserve">330.897033691406</t>
   </si>
   <si>
-    <t xml:space="preserve">335.434539794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.774047851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.625579833984</t>
+    <t xml:space="preserve">335.434509277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.773956298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.625549316406</t>
   </si>
   <si>
     <t xml:space="preserve">321.529235839844</t>
@@ -3518,139 +3518,139 @@
     <t xml:space="preserve">325.188537597656</t>
   </si>
   <si>
-    <t xml:space="preserve">320.065551757812</t>
+    <t xml:space="preserve">320.065490722656</t>
   </si>
   <si>
     <t xml:space="preserve">317.528442382812</t>
   </si>
   <si>
-    <t xml:space="preserve">311.088104248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.672729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.428771972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">310.161102294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.039672851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.794982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.184844970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.477172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.131927490234</t>
+    <t xml:space="preserve">311.088043212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.672698974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.428802490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">310.1611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.039703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.794952392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.184814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.477203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.131988525391</t>
   </si>
   <si>
     <t xml:space="preserve">307.331237792969</t>
   </si>
   <si>
-    <t xml:space="preserve">306.160217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.501770019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.575592041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.161407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.796539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.503845214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.393707275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.595550537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.558563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.942810058594</t>
+    <t xml:space="preserve">306.160247802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.501708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.575653076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.161437988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.796569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.503784179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.393768310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.595581054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.558532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.942840576172</t>
   </si>
   <si>
     <t xml:space="preserve">300.571899414062</t>
   </si>
   <si>
-    <t xml:space="preserve">302.775146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.146057128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.341888427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.886444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294.011077880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290.192199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.604644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.080841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">291.465118408203</t>
+    <t xml:space="preserve">302.775115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.146087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.341857910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.886474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.011169433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.93994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">290.192138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.604614257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.080871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">291.465148925781</t>
   </si>
   <si>
     <t xml:space="preserve">289.702575683594</t>
   </si>
   <si>
-    <t xml:space="preserve">288.380645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.129821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">292.052673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.528900146484</t>
+    <t xml:space="preserve">288.380584716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.129852294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">292.052642822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.528930664062</t>
   </si>
   <si>
     <t xml:space="preserve">295.969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">304.195007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.390899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.089721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.411651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.592712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.110443115234</t>
+    <t xml:space="preserve">304.195037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.390869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.089691162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.41162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.592681884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.110473632812</t>
   </si>
   <si>
     <t xml:space="preserve">299.984405517578</t>
@@ -3659,31 +3659,31 @@
     <t xml:space="preserve">305.3701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">304.48876953125</t>
+    <t xml:space="preserve">304.488830566406</t>
   </si>
   <si>
     <t xml:space="preserve">303.509582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">305.419097900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.9501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.964996337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.7216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.442749023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.018280029297</t>
+    <t xml:space="preserve">305.419006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.950225830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.965026855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.721618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.442657470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.884735107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.018310546875</t>
   </si>
   <si>
     <t xml:space="preserve">329.605834960938</t>
@@ -3692,34 +3692,34 @@
     <t xml:space="preserve">330.976715087891</t>
   </si>
   <si>
-    <t xml:space="preserve">333.326873779297</t>
+    <t xml:space="preserve">333.326782226562</t>
   </si>
   <si>
     <t xml:space="preserve">334.110198974609</t>
   </si>
   <si>
-    <t xml:space="preserve">332.543426513672</t>
+    <t xml:space="preserve">332.54345703125</t>
   </si>
   <si>
     <t xml:space="preserve">331.760101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">341.943969726562</t>
+    <t xml:space="preserve">341.944000244141</t>
   </si>
   <si>
     <t xml:space="preserve">340.768920898438</t>
   </si>
   <si>
-    <t xml:space="preserve">344.685852050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.323791503906</t>
+    <t xml:space="preserve">344.685821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.323699951172</t>
   </si>
   <si>
     <t xml:space="preserve">358.78662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">375.433319091797</t>
+    <t xml:space="preserve">375.433349609375</t>
   </si>
   <si>
     <t xml:space="preserve">380.133636474609</t>
@@ -3728,19 +3728,19 @@
     <t xml:space="preserve">382.679534912109</t>
   </si>
   <si>
-    <t xml:space="preserve">385.225616455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385.421478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">386.204742431641</t>
+    <t xml:space="preserve">385.2255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385.421417236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">386.204772949219</t>
   </si>
   <si>
     <t xml:space="preserve">389.338317871094</t>
   </si>
   <si>
-    <t xml:space="preserve">395.357971191406</t>
+    <t xml:space="preserve">395.358062744141</t>
   </si>
   <si>
     <t xml:space="preserve">389.465942382812</t>
@@ -3749,22 +3749,22 @@
     <t xml:space="preserve">393.394012451172</t>
   </si>
   <si>
-    <t xml:space="preserve">393.197570800781</t>
+    <t xml:space="preserve">393.197601318359</t>
   </si>
   <si>
     <t xml:space="preserve">398.304077148438</t>
   </si>
   <si>
-    <t xml:space="preserve">401.053680419922</t>
+    <t xml:space="preserve">401.0537109375</t>
   </si>
   <si>
     <t xml:space="preserve">402.428497314453</t>
   </si>
   <si>
-    <t xml:space="preserve">388.483978271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.091186523438</t>
+    <t xml:space="preserve">388.483947753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.091125488281</t>
   </si>
   <si>
     <t xml:space="preserve">387.109161376953</t>
@@ -3773,73 +3773,73 @@
     <t xml:space="preserve">391.233612060547</t>
   </si>
   <si>
-    <t xml:space="preserve">396.143676757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.680358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">396.536407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.160186767578</t>
+    <t xml:space="preserve">396.143646240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.680328369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">396.536437988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.16015625</t>
   </si>
   <si>
     <t xml:space="preserve">408.124176025391</t>
   </si>
   <si>
-    <t xml:space="preserve">404.785369873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.963775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.731384277344</t>
+    <t xml:space="preserve">404.785339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.963745117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.731353759766</t>
   </si>
   <si>
     <t xml:space="preserve">403.999725341797</t>
   </si>
   <si>
-    <t xml:space="preserve">405.178192138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.821380615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.535034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.749359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">413.034301757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">409.498992919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.551544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.122741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.479553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.980255126953</t>
+    <t xml:space="preserve">405.178161621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.821319580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.534973144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.749389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413.034271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409.498962402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.551513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.122711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.479583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.980316162109</t>
   </si>
   <si>
     <t xml:space="preserve">419.711944580078</t>
   </si>
   <si>
-    <t xml:space="preserve">420.497589111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.570983886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">403.606964111328</t>
+    <t xml:space="preserve">420.497619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.570953369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">403.60693359375</t>
   </si>
   <si>
     <t xml:space="preserve">397.518463134766</t>
@@ -3851,97 +3851,97 @@
     <t xml:space="preserve">383.377471923828</t>
   </si>
   <si>
-    <t xml:space="preserve">391.822814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">395.947265625</t>
+    <t xml:space="preserve">391.822784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">395.947296142578</t>
   </si>
   <si>
     <t xml:space="preserve">394.572418212891</t>
   </si>
   <si>
-    <t xml:space="preserve">407.338592529297</t>
+    <t xml:space="preserve">407.338562011719</t>
   </si>
   <si>
     <t xml:space="preserve">410.284606933594</t>
   </si>
   <si>
-    <t xml:space="preserve">409.302581787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">408.320587158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.142211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.356567382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.232147216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.767364501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">413.81982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404.588928222656</t>
+    <t xml:space="preserve">409.302642822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">408.320556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.142181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.356536865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.232116699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.767395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413.819854736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404.588958740234</t>
   </si>
   <si>
     <t xml:space="preserve">400.464477539062</t>
   </si>
   <si>
-    <t xml:space="preserve">403.410552978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">477.650634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">474.508209228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">470.187316894531</t>
+    <t xml:space="preserve">403.410522460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">477.650604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">474.508270263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470.187347412109</t>
   </si>
   <si>
     <t xml:space="preserve">474.115417480469</t>
   </si>
   <si>
-    <t xml:space="preserve">486.252014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">488.614349365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">495.11083984375</t>
+    <t xml:space="preserve">486.251983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">488.614318847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">495.110809326172</t>
   </si>
   <si>
     <t xml:space="preserve">493.634368896484</t>
   </si>
   <si>
-    <t xml:space="preserve">492.157867431641</t>
+    <t xml:space="preserve">492.157897949219</t>
   </si>
   <si>
     <t xml:space="preserve">496.095184326172</t>
   </si>
   <si>
-    <t xml:space="preserve">500.524597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.048095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">503.4775390625</t>
+    <t xml:space="preserve">500.524627685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.048126220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">503.477508544922</t>
   </si>
   <si>
     <t xml:space="preserve">503.969696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">501.016815185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">495.602996826172</t>
+    <t xml:space="preserve">501.016754150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">495.60302734375</t>
   </si>
   <si>
     <t xml:space="preserve">500.032440185547</t>
@@ -3956,13 +3956,13 @@
     <t xml:space="preserve">514.797119140625</t>
   </si>
   <si>
-    <t xml:space="preserve">509.383453369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">527.593200683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">535.9599609375</t>
+    <t xml:space="preserve">509.383361816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">527.593322753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">535.959899902344</t>
   </si>
   <si>
     <t xml:space="preserve">547.279541015625</t>
@@ -3971,43 +3971,43 @@
     <t xml:space="preserve">546.295288085938</t>
   </si>
   <si>
-    <t xml:space="preserve">546.787475585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">550.232543945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">539.897277832031</t>
+    <t xml:space="preserve">546.787414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">550.232604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">539.897155761719</t>
   </si>
   <si>
     <t xml:space="preserve">528.085388183594</t>
   </si>
   <si>
-    <t xml:space="preserve">526.116760253906</t>
+    <t xml:space="preserve">526.116821289062</t>
   </si>
   <si>
     <t xml:space="preserve">512.33642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">510.859924316406</t>
+    <t xml:space="preserve">510.85986328125</t>
   </si>
   <si>
     <t xml:space="preserve">489.992370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">504.461853027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">517.750122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.514831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">554.662048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.442321777344</t>
+    <t xml:space="preserve">504.461822509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">517.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.514770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">554.661865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.4423828125</t>
   </si>
   <si>
     <t xml:space="preserve">567.9501953125</t>
@@ -4022,10 +4022,10 @@
     <t xml:space="preserve">569.426635742188</t>
   </si>
   <si>
-    <t xml:space="preserve">545.803039550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">543.34228515625</t>
+    <t xml:space="preserve">545.803100585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">543.342346191406</t>
   </si>
   <si>
     <t xml:space="preserve">540.389343261719</t>
@@ -4034,46 +4034,46 @@
     <t xml:space="preserve">549.248229980469</t>
   </si>
   <si>
-    <t xml:space="preserve">555.646301269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.022766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">523.655944824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.304992675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">517.257995605469</t>
+    <t xml:space="preserve">555.646179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.022705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">523.656005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.305053710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">517.257934570312</t>
   </si>
   <si>
     <t xml:space="preserve">534.975646972656</t>
   </si>
   <si>
-    <t xml:space="preserve">544.818725585938</t>
+    <t xml:space="preserve">544.818786621094</t>
   </si>
   <si>
     <t xml:space="preserve">553.185485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">554.299987792969</t>
+    <t xml:space="preserve">554.300048828125</t>
   </si>
   <si>
     <t xml:space="preserve">536.053466796875</t>
   </si>
   <si>
-    <t xml:space="preserve">532.108276367188</t>
+    <t xml:space="preserve">532.108215332031</t>
   </si>
   <si>
     <t xml:space="preserve">536.546569824219</t>
   </si>
   <si>
-    <t xml:space="preserve">542.464538574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.532897949219</t>
+    <t xml:space="preserve">542.464416503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.532836914062</t>
   </si>
   <si>
     <t xml:space="preserve">541.478088378906</t>
@@ -4082,25 +4082,25 @@
     <t xml:space="preserve">543.450744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">533.094604492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">531.122009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">538.026000976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">540.491821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.601318359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.039855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">534.080810546875</t>
+    <t xml:space="preserve">533.094543457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">531.121948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">538.026123046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540.491760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.601440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.039733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534.080871582031</t>
   </si>
   <si>
     <t xml:space="preserve">539.012390136719</t>
@@ -4109,10 +4109,10 @@
     <t xml:space="preserve">526.190490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">531.615112304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">517.806945800781</t>
+    <t xml:space="preserve">531.615173339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">517.807006835938</t>
   </si>
   <si>
     <t xml:space="preserve">513.36865234375</t>
@@ -4124,34 +4124,34 @@
     <t xml:space="preserve">519.779602050781</t>
   </si>
   <si>
-    <t xml:space="preserve">511.889221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">509.91650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">511.395965576172</t>
+    <t xml:space="preserve">511.88916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">509.916534423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">511.396026611328</t>
   </si>
   <si>
     <t xml:space="preserve">518.793273925781</t>
   </si>
   <si>
-    <t xml:space="preserve">520.765808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">527.669921875</t>
+    <t xml:space="preserve">520.765869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">527.669982910156</t>
   </si>
   <si>
     <t xml:space="preserve">552.820556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">567.121887207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">557.258911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567.615051269531</t>
+    <t xml:space="preserve">567.121826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">557.258972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567.614990234375</t>
   </si>
   <si>
     <t xml:space="preserve">565.642517089844</t>
@@ -4160,52 +4160,52 @@
     <t xml:space="preserve">568.108154296875</t>
   </si>
   <si>
-    <t xml:space="preserve">573.532897949219</t>
+    <t xml:space="preserve">573.532836914062</t>
   </si>
   <si>
     <t xml:space="preserve">581.423217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">583.889038085938</t>
+    <t xml:space="preserve">583.888977050781</t>
   </si>
   <si>
     <t xml:space="preserve">575.012268066406</t>
   </si>
   <si>
-    <t xml:space="preserve">561.697204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569.094482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.601318359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">577.478088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">572.053405761719</t>
+    <t xml:space="preserve">561.697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569.094543457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.601379394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">577.477966308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">572.053344726562</t>
   </si>
   <si>
     <t xml:space="preserve">577.97119140625</t>
   </si>
   <si>
-    <t xml:space="preserve">587.341064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">587.834106445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">585.861511230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">593.751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">609.03955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">646.025817871094</t>
+    <t xml:space="preserve">587.341003417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">587.834167480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">585.861572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">593.751892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">609.039611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">646.025756835938</t>
   </si>
   <si>
     <t xml:space="preserve">642.080627441406</t>
@@ -4214,7 +4214,7 @@
     <t xml:space="preserve">668.217529296875</t>
   </si>
   <si>
-    <t xml:space="preserve">675.61474609375</t>
+    <t xml:space="preserve">675.614868164062</t>
   </si>
   <si>
     <t xml:space="preserve">677.094177246094</t>
@@ -4223,28 +4223,28 @@
     <t xml:space="preserve">671.176452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">679.559936523438</t>
+    <t xml:space="preserve">679.559997558594</t>
   </si>
   <si>
     <t xml:space="preserve">695.172973632812</t>
   </si>
   <si>
-    <t xml:space="preserve">698.631530761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">722.841613769531</t>
+    <t xml:space="preserve">698.631591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722.841552734375</t>
   </si>
   <si>
     <t xml:space="preserve">726.300048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">700.11376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">681.338623046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">707.031005859375</t>
+    <t xml:space="preserve">700.113708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">681.338684082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">707.030883789062</t>
   </si>
   <si>
     <t xml:space="preserve">697.643432617188</t>
@@ -4256,52 +4256,52 @@
     <t xml:space="preserve">699.125549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">688.255859375</t>
+    <t xml:space="preserve">688.255798339844</t>
   </si>
   <si>
     <t xml:space="preserve">686.279479980469</t>
   </si>
   <si>
-    <t xml:space="preserve">709.995361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">722.347412109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">710.489440917969</t>
+    <t xml:space="preserve">709.995422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722.347473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">710.489501953125</t>
   </si>
   <si>
     <t xml:space="preserve">711.971740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">690.232055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">660.587158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">678.868286132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">683.31494140625</t>
+    <t xml:space="preserve">690.232116699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">660.587280273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">678.868225097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">683.315002441406</t>
   </si>
   <si>
     <t xml:space="preserve">682.326782226562</t>
   </si>
   <si>
-    <t xml:space="preserve">697.149230957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.560546875</t>
+    <t xml:space="preserve">697.149291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.560424804688</t>
   </si>
   <si>
     <t xml:space="preserve">704.066467285156</t>
   </si>
   <si>
-    <t xml:space="preserve">706.042785644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720.865234375</t>
+    <t xml:space="preserve">706.042724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720.865173339844</t>
   </si>
   <si>
     <t xml:space="preserve">698.829223632812</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">709.896606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">704.165222167969</t>
+    <t xml:space="preserve">704.165283203125</t>
   </si>
   <si>
     <t xml:space="preserve">709.204833984375</t>
@@ -4319,13 +4319,13 @@
     <t xml:space="preserve">708.710815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">689.738098144531</t>
+    <t xml:space="preserve">689.738037109375</t>
   </si>
   <si>
     <t xml:space="preserve">701.991333007812</t>
   </si>
   <si>
-    <t xml:space="preserve">702.090209960938</t>
+    <t xml:space="preserve">702.090148925781</t>
   </si>
   <si>
     <t xml:space="preserve">706.141540527344</t>
@@ -4340,28 +4340,28 @@
     <t xml:space="preserve">677.188354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">676.694213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">685.39013671875</t>
+    <t xml:space="preserve">676.694274902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">685.390075683594</t>
   </si>
   <si>
     <t xml:space="preserve">678.077758789062</t>
   </si>
   <si>
-    <t xml:space="preserve">667.603149414062</t>
+    <t xml:space="preserve">667.603088378906</t>
   </si>
   <si>
     <t xml:space="preserve">680.745788574219</t>
   </si>
   <si>
-    <t xml:space="preserve">674.619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">711.576416015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">674.520263671875</t>
+    <t xml:space="preserve">674.619201660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.576477050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">674.520324707031</t>
   </si>
   <si>
     <t xml:space="preserve">688.8486328125</t>
@@ -4370,22 +4370,22 @@
     <t xml:space="preserve">709.106018066406</t>
   </si>
   <si>
-    <t xml:space="preserve">712.367004394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.133361816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.528503417969</t>
+    <t xml:space="preserve">712.367065429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.133422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.528564453125</t>
   </si>
   <si>
     <t xml:space="preserve">710.328674316406</t>
   </si>
   <si>
-    <t xml:space="preserve">705.576721191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">701.517639160156</t>
+    <t xml:space="preserve">705.57666015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">701.517700195312</t>
   </si>
   <si>
     <t xml:space="preserve">712.40771484375</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">729.336730957031</t>
   </si>
   <si>
-    <t xml:space="preserve">744.186889648438</t>
+    <t xml:space="preserve">744.186828613281</t>
   </si>
   <si>
     <t xml:space="preserve">737.2568359375</t>
@@ -4409,64 +4409,64 @@
     <t xml:space="preserve">733.593872070312</t>
   </si>
   <si>
-    <t xml:space="preserve">744.087829589844</t>
+    <t xml:space="preserve">744.087768554688</t>
   </si>
   <si>
     <t xml:space="preserve">744.681823730469</t>
   </si>
   <si>
-    <t xml:space="preserve">746.661804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.640869140625</t>
+    <t xml:space="preserve">746.661865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.640930175781</t>
   </si>
   <si>
     <t xml:space="preserve">754.185913085938</t>
   </si>
   <si>
-    <t xml:space="preserve">757.749938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">762.205017089844</t>
+    <t xml:space="preserve">757.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">762.204956054688</t>
   </si>
   <si>
     <t xml:space="preserve">778.243041992188</t>
   </si>
   <si>
-    <t xml:space="preserve">791.410095214844</t>
+    <t xml:space="preserve">791.41015625</t>
   </si>
   <si>
     <t xml:space="preserve">793.588073730469</t>
   </si>
   <si>
-    <t xml:space="preserve">787.549011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">807.250183105469</t>
+    <t xml:space="preserve">787.549072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">807.250305175781</t>
   </si>
   <si>
     <t xml:space="preserve">815.764221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">815.962280273438</t>
+    <t xml:space="preserve">815.962158203125</t>
   </si>
   <si>
     <t xml:space="preserve">825.565307617188</t>
   </si>
   <si>
-    <t xml:space="preserve">823.288208007812</t>
+    <t xml:space="preserve">823.288330078125</t>
   </si>
   <si>
     <t xml:space="preserve">833.386291503906</t>
   </si>
   <si>
-    <t xml:space="preserve">819.427185058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">828.337280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">838.732421875</t>
+    <t xml:space="preserve">819.42724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">828.337219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.732360839844</t>
   </si>
   <si>
     <t xml:space="preserve">835.267333984375</t>
@@ -4478,28 +4478,28 @@
     <t xml:space="preserve">843.385375976562</t>
   </si>
   <si>
-    <t xml:space="preserve">845.266418457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">828.931274414062</t>
+    <t xml:space="preserve">845.266357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">828.931335449219</t>
   </si>
   <si>
     <t xml:space="preserve">818.932189941406</t>
   </si>
   <si>
-    <t xml:space="preserve">825.664306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">834.970336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">839.722351074219</t>
+    <t xml:space="preserve">825.664245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">834.970275878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">839.722412109375</t>
   </si>
   <si>
     <t xml:space="preserve">847.543395996094</t>
   </si>
   <si>
-    <t xml:space="preserve">861.403442382812</t>
+    <t xml:space="preserve">861.403381347656</t>
   </si>
   <si>
     <t xml:space="preserve">845.563354492188</t>
@@ -4508,22 +4508,22 @@
     <t xml:space="preserve">859.720458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">863.9775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.482543945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">830.020263671875</t>
+    <t xml:space="preserve">863.977478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.482482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">830.020385742188</t>
   </si>
   <si>
     <t xml:space="preserve">773.392028808594</t>
   </si>
   <si>
-    <t xml:space="preserve">783.193054199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">784.282104492188</t>
+    <t xml:space="preserve">783.192993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">784.282043457031</t>
   </si>
   <si>
     <t xml:space="preserve">807.646179199219</t>
@@ -4532,43 +4532,43 @@
     <t xml:space="preserve">782.401000976562</t>
   </si>
   <si>
-    <t xml:space="preserve">760.224975585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">743.790832519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">737.751892089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">726.465637207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">735.078735351562</t>
+    <t xml:space="preserve">760.224914550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">743.790893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">737.751831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">726.4658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">735.078796386719</t>
   </si>
   <si>
     <t xml:space="preserve">761.016967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">720.03076171875</t>
+    <t xml:space="preserve">720.030639648438</t>
   </si>
   <si>
     <t xml:space="preserve">699.042541503906</t>
   </si>
   <si>
-    <t xml:space="preserve">720.327758789062</t>
+    <t xml:space="preserve">720.327697753906</t>
   </si>
   <si>
     <t xml:space="preserve">702.804748535156</t>
   </si>
   <si>
-    <t xml:space="preserve">755.967895507812</t>
+    <t xml:space="preserve">755.967956542969</t>
   </si>
   <si>
     <t xml:space="preserve">812.794189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">806.359130859375</t>
+    <t xml:space="preserve">806.359191894531</t>
   </si>
   <si>
     <t xml:space="preserve">817.744201660156</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">836.353576660156</t>
   </si>
   <si>
-    <t xml:space="preserve">824.752746582031</t>
+    <t xml:space="preserve">824.752685546875</t>
   </si>
   <si>
     <t xml:space="preserve">846.169738769531</t>
@@ -4598,16 +4598,16 @@
     <t xml:space="preserve">840.220581054688</t>
   </si>
   <si>
-    <t xml:space="preserve">845.37646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">851.028137207031</t>
+    <t xml:space="preserve">845.376403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">851.028198242188</t>
   </si>
   <si>
     <t xml:space="preserve">845.673950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">850.631652832031</t>
+    <t xml:space="preserve">850.631591796875</t>
   </si>
   <si>
     <t xml:space="preserve">846.7646484375</t>
@@ -4616,13 +4616,13 @@
     <t xml:space="preserve">858.563842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">867.586669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">852.218078613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812.160339355469</t>
+    <t xml:space="preserve">867.586730957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">852.218017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812.160278320312</t>
   </si>
   <si>
     <t xml:space="preserve">806.012817382812</t>
@@ -4631,34 +4631,34 @@
     <t xml:space="preserve">807.995910644531</t>
   </si>
   <si>
-    <t xml:space="preserve">812.656066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812.953491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">831.197631835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">835.064636230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">824.05859375</t>
+    <t xml:space="preserve">812.656005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812.953552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">831.197692871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">835.064575195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">824.058654785156</t>
   </si>
   <si>
     <t xml:space="preserve">812.556884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">808.987365722656</t>
+    <t xml:space="preserve">808.987487792969</t>
   </si>
   <si>
     <t xml:space="preserve">805.51708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">825.5458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816.919616699219</t>
+    <t xml:space="preserve">825.545959472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816.919677734375</t>
   </si>
   <si>
     <t xml:space="preserve">819.695922851562</t>
@@ -4670,7 +4670,7 @@
     <t xml:space="preserve">813.845886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">779.737365722656</t>
+    <t xml:space="preserve">779.7373046875</t>
   </si>
   <si>
     <t xml:space="preserve">779.935668945312</t>
@@ -4679,13 +4679,13 @@
     <t xml:space="preserve">793.519592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">800.063781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">798.675598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">794.709411621094</t>
+    <t xml:space="preserve">800.063659667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">798.675537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">794.70947265625</t>
   </si>
   <si>
     <t xml:space="preserve">816.32470703125</t>
@@ -4694,22 +4694,22 @@
     <t xml:space="preserve">826.636657714844</t>
   </si>
   <si>
-    <t xml:space="preserve">829.313781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">836.948486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">829.8095703125</t>
+    <t xml:space="preserve">829.313720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">836.948547363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">829.809509277344</t>
   </si>
   <si>
     <t xml:space="preserve">832.982360839844</t>
   </si>
   <si>
-    <t xml:space="preserve">841.410339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">838.435729980469</t>
+    <t xml:space="preserve">841.410400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.435791015625</t>
   </si>
   <si>
     <t xml:space="preserve">830.0078125</t>
@@ -4718,40 +4718,40 @@
     <t xml:space="preserve">833.279846191406</t>
   </si>
   <si>
-    <t xml:space="preserve">823.661987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819.2001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">822.868896484375</t>
+    <t xml:space="preserve">823.662048339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.200134277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">822.868774414062</t>
   </si>
   <si>
     <t xml:space="preserve">819.894287109375</t>
   </si>
   <si>
-    <t xml:space="preserve">827.132385253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761.790649414062</t>
+    <t xml:space="preserve">827.132446289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761.790710449219</t>
   </si>
   <si>
     <t xml:space="preserve">778.646667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">754.651672363281</t>
+    <t xml:space="preserve">754.651611328125</t>
   </si>
   <si>
     <t xml:space="preserve">737.002502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">726.492309570312</t>
+    <t xml:space="preserve">726.492370605469</t>
   </si>
   <si>
     <t xml:space="preserve">716.973571777344</t>
   </si>
   <si>
-    <t xml:space="preserve">725.401611328125</t>
+    <t xml:space="preserve">725.401672363281</t>
   </si>
   <si>
     <t xml:space="preserve">766.549987792969</t>
@@ -4763,31 +4763,31 @@
     <t xml:space="preserve">761.691589355469</t>
   </si>
   <si>
-    <t xml:space="preserve">771.309387207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">750.090637207031</t>
+    <t xml:space="preserve">771.309448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">750.090698242188</t>
   </si>
   <si>
     <t xml:space="preserve">713.24169921875</t>
   </si>
   <si>
-    <t xml:space="preserve">680.464904785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">679.67041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">703.706665039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.295837402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">715.228088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760.916931152344</t>
+    <t xml:space="preserve">680.464965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679.670349121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">703.706604003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.295776367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">715.228149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760.916870117188</t>
   </si>
   <si>
     <t xml:space="preserve">744.429260253906</t>
@@ -4796,10 +4796,10 @@
     <t xml:space="preserve">749.892028808594</t>
   </si>
   <si>
-    <t xml:space="preserve">756.447326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766.777038574219</t>
+    <t xml:space="preserve">756.447387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766.776977539062</t>
   </si>
   <si>
     <t xml:space="preserve">790.416015625</t>
@@ -4808,13 +4808,13 @@
     <t xml:space="preserve">774.623596191406</t>
   </si>
   <si>
-    <t xml:space="preserve">788.429565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760.519653320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">756.348022460938</t>
+    <t xml:space="preserve">788.429504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760.519714355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">756.34814453125</t>
   </si>
   <si>
     <t xml:space="preserve">748.104248046875</t>
@@ -4823,22 +4823,22 @@
     <t xml:space="preserve">747.408935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">740.952880859375</t>
+    <t xml:space="preserve">740.952941894531</t>
   </si>
   <si>
     <t xml:space="preserve">744.329956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">744.925842285156</t>
+    <t xml:space="preserve">744.925903320312</t>
   </si>
   <si>
     <t xml:space="preserve">735.788146972656</t>
   </si>
   <si>
-    <t xml:space="preserve">725.756469726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">759.029846191406</t>
+    <t xml:space="preserve">725.756408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">759.02978515625</t>
   </si>
   <si>
     <t xml:space="preserve">745.521789550781</t>
@@ -4847,22 +4847,22 @@
     <t xml:space="preserve">748.700134277344</t>
   </si>
   <si>
-    <t xml:space="preserve">738.569213867188</t>
+    <t xml:space="preserve">738.569152832031</t>
   </si>
   <si>
     <t xml:space="preserve">759.327758789062</t>
   </si>
   <si>
-    <t xml:space="preserve">753.070434570312</t>
+    <t xml:space="preserve">753.070373535156</t>
   </si>
   <si>
     <t xml:space="preserve">739.860412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">740.158386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.731872558594</t>
+    <t xml:space="preserve">740.158325195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.731811523438</t>
   </si>
   <si>
     <t xml:space="preserve">758.433837890625</t>
@@ -4874,7 +4874,7 @@
     <t xml:space="preserve">769.359436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">718.505859375</t>
+    <t xml:space="preserve">718.505798339844</t>
   </si>
   <si>
     <t xml:space="preserve">720.1943359375</t>
@@ -4886,7 +4886,7 @@
     <t xml:space="preserve">714.731506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">693.674987792969</t>
+    <t xml:space="preserve">693.675048828125</t>
   </si>
   <si>
     <t xml:space="preserve">697.548583984375</t>
@@ -4901,16 +4901,16 @@
     <t xml:space="preserve">741.846862792969</t>
   </si>
   <si>
-    <t xml:space="preserve">757.937255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766.181091308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">768.068237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">771.445251464844</t>
+    <t xml:space="preserve">757.937194824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766.18115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">768.068176269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">771.445190429688</t>
   </si>
   <si>
     <t xml:space="preserve">784.555969238281</t>
@@ -4919,10 +4919,10 @@
     <t xml:space="preserve">785.052551269531</t>
   </si>
   <si>
-    <t xml:space="preserve">775.914855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">796.1767578125</t>
+    <t xml:space="preserve">775.914794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">796.176696777344</t>
   </si>
   <si>
     <t xml:space="preserve">842.759460449219</t>
@@ -4931,7 +4931,7 @@
     <t xml:space="preserve">843.752685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">834.813659667969</t>
+    <t xml:space="preserve">834.813598632812</t>
   </si>
   <si>
     <t xml:space="preserve">833.025756835938</t>
@@ -4961,13 +4961,13 @@
     <t xml:space="preserve">849.839111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">836.903991699219</t>
+    <t xml:space="preserve">836.903930664062</t>
   </si>
   <si>
     <t xml:space="preserve">852.426208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">863.968322753906</t>
+    <t xml:space="preserve">863.96826171875</t>
   </si>
   <si>
     <t xml:space="preserve">882.276489257812</t>
@@ -4985,13 +4985,13 @@
     <t xml:space="preserve">846.456115722656</t>
   </si>
   <si>
-    <t xml:space="preserve">849.043090820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">797.700500488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">774.914794921875</t>
+    <t xml:space="preserve">849.043151855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">797.700561523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">774.914733886719</t>
   </si>
   <si>
     <t xml:space="preserve">745.064392089844</t>
@@ -5003,10 +5003,10 @@
     <t xml:space="preserve">734.517333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">740.785888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">749.14404296875</t>
+    <t xml:space="preserve">740.785949707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">749.143981933594</t>
   </si>
   <si>
     <t xml:space="preserve">743.969909667969</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">774.21826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">787.053894042969</t>
+    <t xml:space="preserve">787.053955078125</t>
   </si>
   <si>
     <t xml:space="preserve">770.63623046875</t>
@@ -5039,13 +5039,13 @@
     <t xml:space="preserve">753.322998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">742.178955078125</t>
+    <t xml:space="preserve">742.178894042969</t>
   </si>
   <si>
     <t xml:space="preserve">718.497619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">679.891174316406</t>
+    <t xml:space="preserve">679.891235351562</t>
   </si>
   <si>
     <t xml:space="preserve">650.836853027344</t>
@@ -5057,7 +5057,7 @@
     <t xml:space="preserve">625.961608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">631.633178710938</t>
+    <t xml:space="preserve">631.633117675781</t>
   </si>
   <si>
     <t xml:space="preserve">630.837158203125</t>
@@ -5066,7 +5066,7 @@
     <t xml:space="preserve">655.612976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">669.443542480469</t>
+    <t xml:space="preserve">669.443603515625</t>
   </si>
   <si>
     <t xml:space="preserve">654.418884277344</t>
@@ -5078,7 +5078,7 @@
     <t xml:space="preserve">711.134582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">720.089721679688</t>
+    <t xml:space="preserve">720.089660644531</t>
   </si>
   <si>
     <t xml:space="preserve">743.074401855469</t>
@@ -5087,7 +5087,7 @@
     <t xml:space="preserve">758.397583007812</t>
   </si>
   <si>
-    <t xml:space="preserve">760.188659667969</t>
+    <t xml:space="preserve">760.188598632812</t>
   </si>
   <si>
     <t xml:space="preserve">774.516784667969</t>
@@ -5096,10 +5096,10 @@
     <t xml:space="preserve">784.765441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">721.184204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">718.796203613281</t>
+    <t xml:space="preserve">721.184143066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">718.796142578125</t>
   </si>
   <si>
     <t xml:space="preserve">697.204406738281</t>
@@ -5108,16 +5108,16 @@
     <t xml:space="preserve">680.289245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">657.901428222656</t>
+    <t xml:space="preserve">657.901489257812</t>
   </si>
   <si>
     <t xml:space="preserve">665.563110351562</t>
   </si>
   <si>
-    <t xml:space="preserve">672.528198242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">668.7470703125</t>
+    <t xml:space="preserve">672.528137207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">668.747009277344</t>
   </si>
   <si>
     <t xml:space="preserve">643.274780273438</t>
@@ -70679,7 +70679,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45953.6498263889</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>1927</v>
@@ -70700,6 +70700,32 @@
         <v>1810</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45954.6497337963</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>1317</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>716.799987792969</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>699.900024414062</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>706.5</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>716.599975585938</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1802</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="1811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="1812">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,172 +38,172 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3028717041016</t>
+    <t xml:space="preserve">38.3028831481934</t>
   </si>
   <si>
     <t xml:space="preserve">LLY.DE</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7578239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6800689697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1175155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5549430847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.429859161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9924163818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.242603302002</t>
+    <t xml:space="preserve">38.7578315734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6800727844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1175117492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5549507141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4298477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9923858642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.2426109313965</t>
   </si>
   <si>
     <t xml:space="preserve">60.8051567077637</t>
   </si>
   <si>
-    <t xml:space="preserve">60.3677215576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9302673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0230102539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5943069458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1717109680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8681373596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7071495056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5908012390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3309516906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3598175048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0159797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2212677001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8040084838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3226509094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4815940856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2785110473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4021263122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0290069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5322875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5963706970215</t>
+    <t xml:space="preserve">60.3677024841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9302711486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0230026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5943031311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1717262268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8681449890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7071533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5907859802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3309440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3598022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0159759521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2212753295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.804012298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3226661682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4815902709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.278507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4021110534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0289993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5322914123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.596363067627</t>
   </si>
   <si>
     <t xml:space="preserve">55.4662055969238</t>
   </si>
   <si>
-    <t xml:space="preserve">55.2719573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5721664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1218719482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.927619934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9717674255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6405143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2167015075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5787010192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0754547119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.808277130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0312919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4286079406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2961616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8900184631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4861488342285</t>
+    <t xml:space="preserve">55.2719650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5721549987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1218605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9276161193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9717597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6405220031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2167091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5787200927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0754356384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8082733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0312881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4286231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2961769104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.890022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4861450195312</t>
   </si>
   <si>
     <t xml:space="preserve">53.2323760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9034080505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1130409240723</t>
+    <t xml:space="preserve">53.9034004211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.113037109375</t>
   </si>
   <si>
     <t xml:space="preserve">55.3690910339355</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6251373291016</t>
+    <t xml:space="preserve">55.6251449584961</t>
   </si>
   <si>
     <t xml:space="preserve">56.9230575561523</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8811912536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5191917419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7641258239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1019287109375</t>
+    <t xml:space="preserve">55.8811874389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5191879272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7641372680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1019134521484</t>
   </si>
   <si>
     <t xml:space="preserve">56.693489074707</t>
@@ -212,181 +212,181 @@
     <t xml:space="preserve">57.5057907104492</t>
   </si>
   <si>
-    <t xml:space="preserve">57.1614532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9936904907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5433921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9495582580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4792976379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9119453430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5829734802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9162139892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3665390014648</t>
+    <t xml:space="preserve">57.161449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9936981201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5433959960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9495544433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4793090820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9119567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5829849243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9162178039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3665046691895</t>
   </si>
   <si>
     <t xml:space="preserve">60.1899185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3622360229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6559143066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.62939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6271286010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7330894470215</t>
+    <t xml:space="preserve">58.3622550964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6559028625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6294136047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.627124786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.733081817627</t>
   </si>
   <si>
     <t xml:space="preserve">60.5166282653809</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0552253723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5231590270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4452896118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7212104797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2998008728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8873023986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.513427734375</t>
+    <t xml:space="preserve">61.0552101135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5231742858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4452781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7212028503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2997817993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8872947692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5134544372559</t>
   </si>
   <si>
     <t xml:space="preserve">63.2433280944824</t>
   </si>
   <si>
-    <t xml:space="preserve">63.2077331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3946495056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9376373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4093856811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1570816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5696029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6586380004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2105255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2550048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7980117797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1006469726562</t>
+    <t xml:space="preserve">63.2077255249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.394660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9376258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4093780517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1571273803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5696105957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6586151123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2105178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2550277709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7979965209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1006393432617</t>
   </si>
   <si>
     <t xml:space="preserve">65.6911773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">66.4967269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7281723022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8336181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9582138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1615600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3039932250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5220565795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3320693969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.260871887207</t>
+    <t xml:space="preserve">66.4967498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7281646728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8335952758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9582061767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1615676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3039703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5220642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3320617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2608489990234</t>
   </si>
   <si>
     <t xml:space="preserve">65.8202362060547</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2563858032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5189971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.786018371582</t>
+    <t xml:space="preserve">66.2564163208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5189895629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7860260009766</t>
   </si>
   <si>
     <t xml:space="preserve">66.3988189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">67.3557205200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1212005615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1657485961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1568298339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6018829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3971481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5960311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1448593139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6194229125977</t>
+    <t xml:space="preserve">67.3557052612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1212387084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1657257080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1568145751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6018676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3971633911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5960540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1448745727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6194076538086</t>
   </si>
   <si>
     <t xml:space="preserve">72.5273208618164</t>
@@ -395,91 +395,91 @@
     <t xml:space="preserve">73.622200012207</t>
   </si>
   <si>
-    <t xml:space="preserve">73.5153579711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9306945800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6961669921875</t>
+    <t xml:space="preserve">73.5153427124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9306716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6961822509766</t>
   </si>
   <si>
     <t xml:space="preserve">76.2124481201172</t>
   </si>
   <si>
-    <t xml:space="preserve">76.8355407714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4733505249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.9362411499023</t>
+    <t xml:space="preserve">76.8355255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4733810424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.9362335205078</t>
   </si>
   <si>
     <t xml:space="preserve">78.562385559082</t>
   </si>
   <si>
-    <t xml:space="preserve">78.7136764526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8352508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8441619873047</t>
+    <t xml:space="preserve">78.7136840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8352432250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8441467285156</t>
   </si>
   <si>
     <t xml:space="preserve">80.8048324584961</t>
   </si>
   <si>
-    <t xml:space="preserve">81.4318771362305</t>
+    <t xml:space="preserve">81.4318542480469</t>
   </si>
   <si>
     <t xml:space="preserve">81.9513854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">82.569450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.784423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4587249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3691635131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9033966064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6884078979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6346588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.5808944702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9839935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8496322631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2168807983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0914688110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2527160644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.285285949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3211059570312</t>
+    <t xml:space="preserve">82.5694351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7844161987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4587173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3691482543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9033660888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6883773803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6346282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.5809020996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.984001159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8496170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2168502807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0914764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2527084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2853164672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3211364746094</t>
   </si>
   <si>
     <t xml:space="preserve">82.4888381958008</t>
@@ -488,13 +488,13 @@
     <t xml:space="preserve">81.8618087768555</t>
   </si>
   <si>
-    <t xml:space="preserve">81.7812118530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3960342407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6110000610352</t>
+    <t xml:space="preserve">81.7811889648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3960189819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6110153198242</t>
   </si>
   <si>
     <t xml:space="preserve">81.9782485961914</t>
@@ -503,163 +503,163 @@
     <t xml:space="preserve">80.3569793701172</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1810531616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6077651977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0735549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2380218505859</t>
+    <t xml:space="preserve">81.1810302734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6077728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0735473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2379989624023</t>
   </si>
   <si>
     <t xml:space="preserve">83.1158447265625</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2950134277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2810211181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2248077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5057144165039</t>
+    <t xml:space="preserve">83.2949981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2810440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2247848510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5057373046875</t>
   </si>
   <si>
     <t xml:space="preserve">89.7980651855469</t>
   </si>
   <si>
-    <t xml:space="preserve">89.1531600952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2477111816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4537200927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8478775024414</t>
+    <t xml:space="preserve">89.1531448364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2477035522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.453742980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8478622436523</t>
   </si>
   <si>
     <t xml:space="preserve">85.3014450073242</t>
   </si>
   <si>
-    <t xml:space="preserve">86.895881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3201065063477</t>
+    <t xml:space="preserve">86.8958587646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3200988769531</t>
   </si>
   <si>
     <t xml:space="preserve">87.9976501464844</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7378616333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3552093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7435836791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1402282714844</t>
+    <t xml:space="preserve">87.7378540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3551864624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7435913085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1402359008789</t>
   </si>
   <si>
     <t xml:space="preserve">83.2681198120117</t>
   </si>
   <si>
-    <t xml:space="preserve">85.2029190063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0660247802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8177642822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6980819702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.1287612915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.4472732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9725112915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2061309814453</t>
+    <t xml:space="preserve">85.2029342651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0660552978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.817756652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6980895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.128791809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.972541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2061614990234</t>
   </si>
   <si>
     <t xml:space="preserve">87.7289199829102</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2369842529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3591766357422</t>
+    <t xml:space="preserve">90.2369995117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3591690063477</t>
   </si>
   <si>
     <t xml:space="preserve">87.9741592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7129287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5325698852539</t>
+    <t xml:space="preserve">87.7129364013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5325775146484</t>
   </si>
   <si>
     <t xml:space="preserve">90.5685119628906</t>
   </si>
   <si>
-    <t xml:space="preserve">88.9740371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3705215454102</t>
+    <t xml:space="preserve">88.9740524291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3704986572266</t>
   </si>
   <si>
     <t xml:space="preserve">90.1991806030273</t>
   </si>
   <si>
-    <t xml:space="preserve">88.8839950561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4063568115234</t>
+    <t xml:space="preserve">88.8839797973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.406364440918</t>
   </si>
   <si>
     <t xml:space="preserve">91.2171020507812</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7665176391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8474884033203</t>
+    <t xml:space="preserve">92.7665252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8475036621094</t>
   </si>
   <si>
     <t xml:space="preserve">94.0456924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">90.1541519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.604621887207</t>
+    <t xml:space="preserve">90.1541290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6046371459961</t>
   </si>
   <si>
     <t xml:space="preserve">88.388542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3161849975586</t>
+    <t xml:space="preserve">91.3161926269531</t>
   </si>
   <si>
     <t xml:space="preserve">89.7487640380859</t>
   </si>
   <si>
-    <t xml:space="preserve">87.8930816650391</t>
+    <t xml:space="preserve">87.8930740356445</t>
   </si>
   <si>
     <t xml:space="preserve">84.8933563232422</t>
@@ -668,52 +668,52 @@
     <t xml:space="preserve">86.8931732177734</t>
   </si>
   <si>
-    <t xml:space="preserve">86.0644302368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2627868652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7760467529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5056304931641</t>
+    <t xml:space="preserve">86.0644073486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2627639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7760543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5056457519531</t>
   </si>
   <si>
     <t xml:space="preserve">90.3252868652344</t>
   </si>
   <si>
-    <t xml:space="preserve">89.0191192626953</t>
+    <t xml:space="preserve">89.0191116333008</t>
   </si>
   <si>
     <t xml:space="preserve">89.1812362670898</t>
   </si>
   <si>
-    <t xml:space="preserve">90.631591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6135559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4513320922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8747940063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.667610168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9919967651367</t>
+    <t xml:space="preserve">90.6315689086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6135406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4513397216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8747787475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6676025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9919891357422</t>
   </si>
   <si>
     <t xml:space="preserve">89.7217483520508</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3521347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3700637817383</t>
+    <t xml:space="preserve">92.3521423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3700866699219</t>
   </si>
   <si>
     <t xml:space="preserve">91.6675186157227</t>
@@ -722,145 +722,145 @@
     <t xml:space="preserve">92.5863571166992</t>
   </si>
   <si>
-    <t xml:space="preserve">92.424201965332</t>
+    <t xml:space="preserve">92.424186706543</t>
   </si>
   <si>
     <t xml:space="preserve">93.0998229980469</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6674346923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6585922241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.0820693969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7666168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5052032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7394104003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.685188293457</t>
+    <t xml:space="preserve">92.6674423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6585845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0820922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7666091918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5051879882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4150238037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.739387512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6851959228516</t>
   </si>
   <si>
     <t xml:space="preserve">94.0997314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4961700439453</t>
+    <t xml:space="preserve">93.4961929321289</t>
   </si>
   <si>
     <t xml:space="preserve">92.604377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">93.964599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3970031738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1717910766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.3154830932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6569595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0890960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6750946044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.738525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.237060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0437774658203</t>
+    <t xml:space="preserve">93.9645919799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3969879150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1717987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.3154678344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6569671630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0891036987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6751098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.7385101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2370529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0437698364258</t>
   </si>
   <si>
     <t xml:space="preserve">99.2522430419922</t>
   </si>
   <si>
-    <t xml:space="preserve">99.3247451782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.696403503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.521240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.518287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.475891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.189025878906</t>
+    <t xml:space="preserve">99.3247604370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6963882446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.52123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.518257141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.475898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.189018249512</t>
   </si>
   <si>
     <t xml:space="preserve">101.318878173828</t>
   </si>
   <si>
-    <t xml:space="preserve">102.234352111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.457786560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9078216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4969635009766</t>
+    <t xml:space="preserve">102.234359741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.457778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9078063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4969787597656</t>
   </si>
   <si>
     <t xml:space="preserve">99.1615982055664</t>
   </si>
   <si>
-    <t xml:space="preserve">99.5966949462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.865676879883</t>
+    <t xml:space="preserve">99.5966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.865646362305</t>
   </si>
   <si>
     <t xml:space="preserve">102.034927368164</t>
   </si>
   <si>
-    <t xml:space="preserve">102.524383544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.823532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.101570129395</t>
+    <t xml:space="preserve">102.524391174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.823516845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.101554870605</t>
   </si>
   <si>
     <t xml:space="preserve">105.588081359863</t>
   </si>
   <si>
-    <t xml:space="preserve">104.446014404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.862945556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.300979614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.270820617676</t>
+    <t xml:space="preserve">104.445991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.86296081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.300956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270843505859</t>
   </si>
   <si>
     <t xml:space="preserve">105.352416992188</t>
@@ -869,184 +869,184 @@
     <t xml:space="preserve">103.494270324707</t>
   </si>
   <si>
-    <t xml:space="preserve">101.346061706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.207176208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.880851745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.787246704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.068031311035</t>
+    <t xml:space="preserve">101.346046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.207160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.880844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.787269592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.068023681641</t>
   </si>
   <si>
     <t xml:space="preserve">99.0165939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8862762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4722671508789</t>
+    <t xml:space="preserve">93.8862609863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4722900390625</t>
   </si>
   <si>
     <t xml:space="preserve">94.7020568847656</t>
   </si>
   <si>
-    <t xml:space="preserve">95.771614074707</t>
+    <t xml:space="preserve">95.7716293334961</t>
   </si>
   <si>
     <t xml:space="preserve">95.9347763061523</t>
   </si>
   <si>
-    <t xml:space="preserve">96.7868041992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0587310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5751495361328</t>
+    <t xml:space="preserve">96.7868118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0587387084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5751571655273</t>
   </si>
   <si>
     <t xml:space="preserve">94.9739685058594</t>
   </si>
   <si>
-    <t xml:space="preserve">93.904426574707</t>
+    <t xml:space="preserve">93.9044189453125</t>
   </si>
   <si>
     <t xml:space="preserve">93.7775115966797</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0494384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0342636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3816299438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4360275268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1430130004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3061904907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.755256652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6241912841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.8829574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4816055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.390380859375</t>
+    <t xml:space="preserve">94.0494232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0342559814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3816375732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4360122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1430358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3061676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7552490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6242065429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8829498291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4815902709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3904037475586</t>
   </si>
   <si>
     <t xml:space="preserve">95.0802459716797</t>
   </si>
   <si>
-    <t xml:space="preserve">95.1350173950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4086227416992</t>
+    <t xml:space="preserve">95.1349945068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4086380004883</t>
   </si>
   <si>
     <t xml:space="preserve">94.2228698730469</t>
   </si>
   <si>
-    <t xml:space="preserve">95.9376525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9890518188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5728073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6324005126953</t>
+    <t xml:space="preserve">95.9376449584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9890594482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5727996826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6324234008789</t>
   </si>
   <si>
     <t xml:space="preserve">92.5628051757812</t>
   </si>
   <si>
-    <t xml:space="preserve">93.0918350219727</t>
+    <t xml:space="preserve">93.0918121337891</t>
   </si>
   <si>
     <t xml:space="preserve">90.5834732055664</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2128295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7999420166016</t>
+    <t xml:space="preserve">91.2128448486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7999267578125</t>
   </si>
   <si>
     <t xml:space="preserve">93.4201889038086</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4931793212891</t>
+    <t xml:space="preserve">93.4931564331055</t>
   </si>
   <si>
     <t xml:space="preserve">92.9094085693359</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6357574462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3107452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2608947753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8720245361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3098220825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3405227661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2709274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3621139526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7567977905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1249618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3885726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.652214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5643463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4764633178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0203857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5004730224609</t>
+    <t xml:space="preserve">92.6357498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3107223510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2609024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8720092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3098449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3405380249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2709121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3621292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7567672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1249694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3885879516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6521835327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5643310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.476448059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0204010009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.50048828125</t>
   </si>
   <si>
     <t xml:space="preserve">87.3819046020508</t>
@@ -1055,139 +1055,139 @@
     <t xml:space="preserve">86.5244903564453</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9349517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9474105834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3065032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3703536987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9507751464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2244186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.118278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7750244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3040390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9176025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5469818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4980392456055</t>
+    <t xml:space="preserve">86.9349594116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9474334716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3064956665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3703384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9507369995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2243957519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.118293762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.775016784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3040466308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9176330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5469970703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.498046875</t>
   </si>
   <si>
     <t xml:space="preserve">92.7452087402344</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7418670654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4317398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0702438354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4236831665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.440788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7804641723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7908782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0479049682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0748291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4230575561523</t>
+    <t xml:space="preserve">91.7418746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4317321777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0702285766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4236679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.440803527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7804565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7908706665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0478973388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.074836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4230422973633</t>
   </si>
   <si>
     <t xml:space="preserve">91.9095916748047</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7541427612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8190078735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6084823608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8104629516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2878265380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0197525024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7712783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6990432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9193725585938</t>
+    <t xml:space="preserve">92.7541656494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8190002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6084976196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8104553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2878189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0197372436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7712860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6990737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9193801879883</t>
   </si>
   <si>
     <t xml:space="preserve">92.0381164550781</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6800994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7443466186523</t>
+    <t xml:space="preserve">91.6800918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7443542480469</t>
   </si>
   <si>
     <t xml:space="preserve">92.9928283691406</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9389877319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7015228271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4065170288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6635818481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4334487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9940338134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4713973999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6354217529297</t>
+    <t xml:space="preserve">94.93896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.701530456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4065551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6635589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4334564208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9940567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4714050292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6354293823242</t>
   </si>
   <si>
     <t xml:space="preserve">89.9634399414062</t>
@@ -1196,148 +1196,148 @@
     <t xml:space="preserve">89.5044555664062</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4224395751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8814315795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.340461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7969741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5589294433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8165664672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2033615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6886672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1396942138672</t>
+    <t xml:space="preserve">90.4224319458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8814392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3404159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7969818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5589141845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8165512084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.203369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6886596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1396865844727</t>
   </si>
   <si>
     <t xml:space="preserve">92.7174377441406</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0944442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0931701660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.800666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4885406494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0209808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1494827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4616241455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4500885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6509780883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7433547973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4823837280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.0920867919922</t>
+    <t xml:space="preserve">94.0943908691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0932006835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8006744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.488525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0209579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1494979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4616165161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4500579833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.650993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7433624267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4823913574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.0920944213867</t>
   </si>
   <si>
     <t xml:space="preserve">95.6856307983398</t>
   </si>
   <si>
-    <t xml:space="preserve">97.015869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5493774414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8634643554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3830718994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1267395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4939498901367</t>
+    <t xml:space="preserve">97.0158615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5493545532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8634262084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.383056640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1267242431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4939422607422</t>
   </si>
   <si>
     <t xml:space="preserve">100.600158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">99.9165802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.359970092773</t>
+    <t xml:space="preserve">99.9165954589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.359977722168</t>
   </si>
   <si>
     <t xml:space="preserve">100.212181091309</t>
   </si>
   <si>
-    <t xml:space="preserve">100.784912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.711006164551</t>
+    <t xml:space="preserve">100.78491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.711013793945</t>
   </si>
   <si>
     <t xml:space="preserve">101.727180480957</t>
   </si>
   <si>
-    <t xml:space="preserve">104.202926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.269897460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.008918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.429237365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.65323638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.988128662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.064353942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.341484069824</t>
+    <t xml:space="preserve">104.202911376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.269912719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.008911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.429229736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.653259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.988136291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.06436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.34147644043</t>
   </si>
   <si>
     <t xml:space="preserve">109.265258789062</t>
   </si>
   <si>
-    <t xml:space="preserve">109.135925292969</t>
+    <t xml:space="preserve">109.135932922363</t>
   </si>
   <si>
     <t xml:space="preserve">109.819526672363</t>
   </si>
   <si>
-    <t xml:space="preserve">109.893440246582</t>
+    <t xml:space="preserve">109.893432617188</t>
   </si>
   <si>
     <t xml:space="preserve">112.886497497559</t>
@@ -1349,61 +1349,61 @@
     <t xml:space="preserve">115.269874572754</t>
   </si>
   <si>
-    <t xml:space="preserve">115.454627990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.507736206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.062004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.376091003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.710983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.486946105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.394554138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.320663452148</t>
+    <t xml:space="preserve">115.454605102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.507720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.061996459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.376098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.710990905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.486953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.394561767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.320693969727</t>
   </si>
   <si>
     <t xml:space="preserve">117.413040161133</t>
   </si>
   <si>
-    <t xml:space="preserve">116.322982788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.115112304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.092018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.135932922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.339134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.611656188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623207092285</t>
+    <t xml:space="preserve">116.32299041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.115127563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.092041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.13591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.339149475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.611640930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.62321472168</t>
   </si>
   <si>
     <t xml:space="preserve">124.156669616699</t>
   </si>
   <si>
-    <t xml:space="preserve">123.473091125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.274459838867</t>
+    <t xml:space="preserve">123.473098754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.274467468262</t>
   </si>
   <si>
     <t xml:space="preserve">121.292945861816</t>
@@ -1412,46 +1412,46 @@
     <t xml:space="preserve">122.586242675781</t>
   </si>
   <si>
-    <t xml:space="preserve">122.54906463623</t>
+    <t xml:space="preserve">122.549087524414</t>
   </si>
   <si>
     <t xml:space="preserve">121.24853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">120.616813659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.229949951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.270378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.787353515625</t>
+    <t xml:space="preserve">120.616851806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.229957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.270393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.787322998047</t>
   </si>
   <si>
     <t xml:space="preserve">119.780776977539</t>
   </si>
   <si>
-    <t xml:space="preserve">117.049621582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.009162902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.01789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.620048522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.057235717773</t>
+    <t xml:space="preserve">117.049606323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.009178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.017890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.620056152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.05721282959</t>
   </si>
   <si>
     <t xml:space="preserve">112.441947937012</t>
   </si>
   <si>
-    <t xml:space="preserve">111.104225158691</t>
+    <t xml:space="preserve">111.104232788086</t>
   </si>
   <si>
     <t xml:space="preserve">116.306434631348</t>
@@ -1460,76 +1460,76 @@
     <t xml:space="preserve">115.507514953613</t>
   </si>
   <si>
-    <t xml:space="preserve">110.881294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.93701171875</t>
+    <t xml:space="preserve">110.881278991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.937026977539</t>
   </si>
   <si>
     <t xml:space="preserve">115.135948181152</t>
   </si>
   <si>
-    <t xml:space="preserve">106.700950622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.565437316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.609153747559</t>
+    <t xml:space="preserve">106.700942993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.565422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.609161376953</t>
   </si>
   <si>
     <t xml:space="preserve">117.123916625977</t>
   </si>
   <si>
-    <t xml:space="preserve">114.597137451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.056182861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.120658874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.768692016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.27033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.771980285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.844123840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.680198669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.36547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.798225402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.69441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.300994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623397827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.552375793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.339218139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.661651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.913040161133</t>
+    <t xml:space="preserve">114.597129821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.056190490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.120651245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.768699645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.771957397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.844116210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.680206298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.365432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.798233032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.694435119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.300979614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623428344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.552337646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.339248657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.661712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.913070678711</t>
   </si>
   <si>
     <t xml:space="preserve">131.44856262207</t>
@@ -1538,316 +1538,316 @@
     <t xml:space="preserve">135.628921508789</t>
   </si>
   <si>
-    <t xml:space="preserve">132.377578735352</t>
+    <t xml:space="preserve">132.377532958984</t>
   </si>
   <si>
     <t xml:space="preserve">134.235488891602</t>
   </si>
   <si>
-    <t xml:space="preserve">138.285720825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.679183959961</t>
+    <t xml:space="preserve">138.285751342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.679214477539</t>
   </si>
   <si>
     <t xml:space="preserve">140.218002319336</t>
   </si>
   <si>
-    <t xml:space="preserve">136.557846069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.232208251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.117431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.367691040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.272644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.405960083008</t>
+    <t xml:space="preserve">136.557876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.232162475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.117446899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.36767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.272613525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.405990600586</t>
   </si>
   <si>
     <t xml:space="preserve">133.492279052734</t>
   </si>
   <si>
-    <t xml:space="preserve">132.154541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.183044433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.263854980469</t>
+    <t xml:space="preserve">132.154571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.183013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.263885498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.833297729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.889297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.347763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.561553955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.050903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.911773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.942657470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.689590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.399215698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.34700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.771896362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.766227722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.560737609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.589775085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.954833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.180809020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.002464294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.873664855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.143478393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.554313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.84659576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.016555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.972732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.142364501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.077911376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.011642456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.650360107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.32258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.984573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.45524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.621398925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.48876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.619491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.412170410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.37483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.441131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.484970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.055480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.148864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.225463867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.123672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.430801391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.20866394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.179672241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.125564575195</t>
   </si>
   <si>
     <t xml:space="preserve">135.833267211914</t>
   </si>
   <si>
-    <t xml:space="preserve">135.88932800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.347793579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.561584472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.050903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.91178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.942687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.689605712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.39924621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.347007751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.77188873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.766212463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.560760498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.589714050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.954818725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.180847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.002487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.873680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.143486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.554306030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.846588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.016578674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.972732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.142349243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.077972412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.011642456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.650375366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.32258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.984588623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.455261230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.621398925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.488739013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.619476318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.412185668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.374801635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.441162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.484985351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.055480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.148849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.22541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.123672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.430816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.208709716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.179718017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.125579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.833251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.795959472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.239501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.355346679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.448738098145</t>
+    <t xml:space="preserve">135.795928955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.239547729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.355354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.448745727539</t>
   </si>
   <si>
     <t xml:space="preserve">128.793273925781</t>
   </si>
   <si>
-    <t xml:space="preserve">120.334022521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.802772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.473121643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.854988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.155647277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.717788696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.800872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.875556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.736465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.22200012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.245330810547</t>
+    <t xml:space="preserve">120.334037780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.802780151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.47314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.855003356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.155670166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.717781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.80086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.87557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.736457824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.221984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.245323181152</t>
   </si>
   <si>
     <t xml:space="preserve">119.73365020752</t>
   </si>
   <si>
-    <t xml:space="preserve">120.409797668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.578834533691</t>
+    <t xml:space="preserve">120.409782409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.578842163086</t>
   </si>
   <si>
     <t xml:space="preserve">121.480369567871</t>
   </si>
   <si>
-    <t xml:space="preserve">120.071716308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.174781799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.062072753906</t>
+    <t xml:space="preserve">120.071739196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.174758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.06209564209</t>
   </si>
   <si>
     <t xml:space="preserve">119.207763671875</t>
   </si>
   <si>
-    <t xml:space="preserve">117.423492431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.170196533203</t>
+    <t xml:space="preserve">117.423500061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.170211791992</t>
   </si>
   <si>
     <t xml:space="preserve">117.479835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">116.446846008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.052436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.832130432129</t>
+    <t xml:space="preserve">116.44686126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.05241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.832122802734</t>
   </si>
   <si>
     <t xml:space="preserve">119.30167388916</t>
   </si>
   <si>
-    <t xml:space="preserve">118.099647521973</t>
+    <t xml:space="preserve">118.099662780762</t>
   </si>
   <si>
     <t xml:space="preserve">118.625526428223</t>
   </si>
   <si>
-    <t xml:space="preserve">117.79914855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.686958312988</t>
+    <t xml:space="preserve">117.799140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.686950683594</t>
   </si>
   <si>
     <t xml:space="preserve">117.59253692627</t>
   </si>
   <si>
-    <t xml:space="preserve">117.554969787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.639770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.710319519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.729095458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.611846923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.597618103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.334671020508</t>
+    <t xml:space="preserve">117.554977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.639755249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.710311889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.729072570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.611831665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.597625732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.334663391113</t>
   </si>
   <si>
     <t xml:space="preserve">119.583404541016</t>
@@ -1856,34 +1856,34 @@
     <t xml:space="preserve">120.785438537598</t>
   </si>
   <si>
-    <t xml:space="preserve">118.193572998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.709777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.977294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.747344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.108787536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.424018859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.335189819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.546363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.231628417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.869697570801</t>
+    <t xml:space="preserve">118.193557739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.709785461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.97730255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.747367858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.108779907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.424026489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.335159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.546340942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.231620788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.869705200195</t>
   </si>
   <si>
     <t xml:space="preserve">117.06665802002</t>
@@ -1892,106 +1892,106 @@
     <t xml:space="preserve">117.348358154297</t>
   </si>
   <si>
-    <t xml:space="preserve">115.150894165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.12247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.615364074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.939239501953</t>
+    <t xml:space="preserve">115.150917053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.122482299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.615379333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.93921661377</t>
   </si>
   <si>
     <t xml:space="preserve">113.347846984863</t>
   </si>
   <si>
-    <t xml:space="preserve">111.563598632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.22957611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.835166931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.530090332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.666130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.684898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.51131439209</t>
+    <t xml:space="preserve">111.563591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.229568481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.835151672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.53010559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.666122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.684906005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.511306762695</t>
   </si>
   <si>
     <t xml:space="preserve">118.13720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">116.221481323242</t>
+    <t xml:space="preserve">116.221488952637</t>
   </si>
   <si>
     <t xml:space="preserve">116.202690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">113.5732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.104217529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.319938659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.939102172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.978355407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.35481262207</t>
+    <t xml:space="preserve">113.573249816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.104209899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.319931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.939094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.97834777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.354789733887</t>
   </si>
   <si>
     <t xml:space="preserve">112.221061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">112.504493713379</t>
+    <t xml:space="preserve">112.504486083984</t>
   </si>
   <si>
     <t xml:space="preserve">112.164367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">116.35920715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.901298522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.338836669922</t>
+    <t xml:space="preserve">116.359199523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.901306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.338829040527</t>
   </si>
   <si>
     <t xml:space="preserve">113.449264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">114.318504333496</t>
+    <t xml:space="preserve">114.318473815918</t>
   </si>
   <si>
     <t xml:space="preserve">115.830123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">114.828659057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.846076965332</t>
+    <t xml:space="preserve">114.828666687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.846084594727</t>
   </si>
   <si>
     <t xml:space="preserve">112.447814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">114.469635009766</t>
+    <t xml:space="preserve">114.469657897949</t>
   </si>
   <si>
     <t xml:space="preserve">116.151351928711</t>
@@ -2000,154 +2000,154 @@
     <t xml:space="preserve">122.65145111084</t>
   </si>
   <si>
-    <t xml:space="preserve">123.841865539551</t>
+    <t xml:space="preserve">123.841850280762</t>
   </si>
   <si>
     <t xml:space="preserve">125.353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">124.843330383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.411674499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.32746887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.948089599609</t>
+    <t xml:space="preserve">124.843353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.411682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.327453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.948059082031</t>
   </si>
   <si>
     <t xml:space="preserve">131.267837524414</t>
   </si>
   <si>
-    <t xml:space="preserve">129.7373046875</t>
+    <t xml:space="preserve">129.737289428711</t>
   </si>
   <si>
     <t xml:space="preserve">129.96403503418</t>
   </si>
   <si>
-    <t xml:space="preserve">129.416091918945</t>
+    <t xml:space="preserve">129.416076660156</t>
   </si>
   <si>
     <t xml:space="preserve">127.583190917969</t>
   </si>
   <si>
-    <t xml:space="preserve">128.471282958984</t>
+    <t xml:space="preserve">128.471267700195</t>
   </si>
   <si>
     <t xml:space="preserve">129.113754272461</t>
   </si>
   <si>
-    <t xml:space="preserve">126.82738494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.392791748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.904441833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.016326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.603576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.118347167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.978698730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.645950317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.119812011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.047134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.839294433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.71435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.833633422852</t>
+    <t xml:space="preserve">126.827407836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.392784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.904418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.016296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.118316650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.978729248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.645935058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.119827270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.047149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.839233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.714340209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.833618164062</t>
   </si>
   <si>
     <t xml:space="preserve">155.076309204102</t>
   </si>
   <si>
-    <t xml:space="preserve">158.760971069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.032821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.996490478516</t>
+    <t xml:space="preserve">158.760986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.032836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.996505737305</t>
   </si>
   <si>
     <t xml:space="preserve">161.992126464844</t>
   </si>
   <si>
-    <t xml:space="preserve">163.125854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.349639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.804626464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.720245361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.962921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.137405395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.704284667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.461563110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.814682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.157791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.0087890625</t>
+    <t xml:space="preserve">163.125823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.349655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.804580688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.72021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.962951660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.137390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.704299926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.461578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.814727783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.157745361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.008758544922</t>
   </si>
   <si>
     <t xml:space="preserve">160.819549560547</t>
   </si>
   <si>
-    <t xml:space="preserve">164.560852050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.793975830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.161376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.831970214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.856872558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.932159423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.205276489258</t>
+    <t xml:space="preserve">164.560836791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.794006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.161392211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.831985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.856887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.932174682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.20524597168</t>
   </si>
   <si>
     <t xml:space="preserve">159.964889526367</t>
@@ -2156,28 +2156,28 @@
     <t xml:space="preserve">157.970794677734</t>
   </si>
   <si>
-    <t xml:space="preserve">159.907928466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.376815795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.75666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.958343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.338195800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.617172241211</t>
+    <t xml:space="preserve">159.907913208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.376800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.756637573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.958358764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.338165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.617156982422</t>
   </si>
   <si>
     <t xml:space="preserve">167.884338378906</t>
   </si>
   <si>
-    <t xml:space="preserve">167.409545898438</t>
+    <t xml:space="preserve">167.409561157227</t>
   </si>
   <si>
     <t xml:space="preserve">165.890243530273</t>
@@ -2186,127 +2186,127 @@
     <t xml:space="preserve">162.661697387695</t>
   </si>
   <si>
-    <t xml:space="preserve">163.326385498047</t>
+    <t xml:space="preserve">163.326370239258</t>
   </si>
   <si>
     <t xml:space="preserve">151.741592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">151.931503295898</t>
+    <t xml:space="preserve">151.931549072266</t>
   </si>
   <si>
     <t xml:space="preserve">149.082809448242</t>
   </si>
   <si>
-    <t xml:space="preserve">147.183670043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.75341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.133239746094</t>
+    <t xml:space="preserve">147.183654785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.753402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.133255004883</t>
   </si>
   <si>
     <t xml:space="preserve">149.462615966797</t>
   </si>
   <si>
-    <t xml:space="preserve">145.47444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.993774414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.892868041992</t>
+    <t xml:space="preserve">145.474456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.993759155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.892913818359</t>
   </si>
   <si>
     <t xml:space="preserve">150.602127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">150.792053222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.39973449707</t>
+    <t xml:space="preserve">150.792037963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.399780273438</t>
   </si>
   <si>
     <t xml:space="preserve">151.456741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">148.702972412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.28450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.234100341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.854293823242</t>
+    <t xml:space="preserve">148.703002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.284515380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.234069824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.854248046875</t>
   </si>
   <si>
     <t xml:space="preserve">144.904708862305</t>
   </si>
   <si>
-    <t xml:space="preserve">146.424011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.323120117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.84245300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.412170410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.652587890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.513031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.803848266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.955108642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.346786499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.486251831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.575302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.044189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.12141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.691192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.071044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.836578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.693557739258</t>
+    <t xml:space="preserve">146.42399597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.323135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.842468261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.412185668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.652557373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.513046264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.803833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.955139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.346755981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.486236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.575332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.044143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.121475219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.691177368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.071014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.836563110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.693511962891</t>
   </si>
   <si>
     <t xml:space="preserve">155.220947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">154.457229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.929824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.979919433594</t>
+    <t xml:space="preserve">154.457244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.929870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">156.175552368164</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">157.702926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">155.984603881836</t>
+    <t xml:space="preserve">155.984619140625</t>
   </si>
   <si>
     <t xml:space="preserve">154.361785888672</t>
@@ -2330,28 +2330,28 @@
     <t xml:space="preserve">154.839065551758</t>
   </si>
   <si>
-    <t xml:space="preserve">156.366455078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.803085327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.640380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.876678466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.07698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.000305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.365737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.749893188477</t>
+    <t xml:space="preserve">156.366485595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.803100585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.640365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.876663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.076965332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.000274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.365707397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.749908447266</t>
   </si>
   <si>
     <t xml:space="preserve">175.840667724609</t>
@@ -2360,124 +2360,124 @@
     <t xml:space="preserve">176.222534179688</t>
   </si>
   <si>
-    <t xml:space="preserve">178.22721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.270217895508</t>
+    <t xml:space="preserve">178.227188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.270233154297</t>
   </si>
   <si>
     <t xml:space="preserve">179.038650512695</t>
   </si>
   <si>
-    <t xml:space="preserve">178.799987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.265579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.243682861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.527709960938</t>
+    <t xml:space="preserve">178.800033569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.265548706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.243667602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.52766418457</t>
   </si>
   <si>
     <t xml:space="preserve">182.09342956543</t>
   </si>
   <si>
-    <t xml:space="preserve">184.432205200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.291397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.102813720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.7734375</t>
+    <t xml:space="preserve">184.432250976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.291412353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.102828979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.773345947266</t>
   </si>
   <si>
     <t xml:space="preserve">189.49169921875</t>
   </si>
   <si>
-    <t xml:space="preserve">188.918914794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.969039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.775772094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.069213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.682662963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.446304321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.828201293945</t>
+    <t xml:space="preserve">188.918960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.969024658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.775756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.069183349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.6826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.446350097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.828170776367</t>
   </si>
   <si>
     <t xml:space="preserve">188.584854125977</t>
   </si>
   <si>
-    <t xml:space="preserve">187.677917480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.296127319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.591873168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.973724365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.882995605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.983139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.415069580078</t>
+    <t xml:space="preserve">187.677963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.296112060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.591888427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.973754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.882965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.983123779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.415054321289</t>
   </si>
   <si>
     <t xml:space="preserve">196.269515991211</t>
   </si>
   <si>
-    <t xml:space="preserve">199.515213012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.319610595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.842315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.987823486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.152160644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.739028930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.975326538086</t>
+    <t xml:space="preserve">199.515228271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.319580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.842269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.987808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.152130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.739013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.975311279297</t>
   </si>
   <si>
     <t xml:space="preserve">213.929946899414</t>
   </si>
   <si>
-    <t xml:space="preserve">218.321166992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.703048706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.366592407227</t>
+    <t xml:space="preserve">218.321182250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.703063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.366546630859</t>
   </si>
   <si>
     <t xml:space="preserve">215.498092651367</t>
@@ -2495,187 +2495,187 @@
     <t xml:space="preserve">221.534729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">223.067840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.205429077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.444076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.156616210938</t>
+    <t xml:space="preserve">223.067810058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.205459594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.444061279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.156631469727</t>
   </si>
   <si>
     <t xml:space="preserve">213.294250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">212.048599243164</t>
+    <t xml:space="preserve">212.048583984375</t>
   </si>
   <si>
     <t xml:space="preserve">214.060775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">211.186218261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.736709594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.982360839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.269805908203</t>
+    <t xml:space="preserve">211.18620300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.736724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.982345581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.269790649414</t>
   </si>
   <si>
     <t xml:space="preserve">210.994567871094</t>
   </si>
   <si>
-    <t xml:space="preserve">209.461486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.970153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.058959960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.621643066406</t>
+    <t xml:space="preserve">209.461441040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.970169067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.058944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.621627807617</t>
   </si>
   <si>
     <t xml:space="preserve">191.447387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">190.92041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.495315551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.902069091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.087615966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.530990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.626800537109</t>
+    <t xml:space="preserve">190.920394897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.495300292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.902084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.087600708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.531005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.626846313477</t>
   </si>
   <si>
     <t xml:space="preserve">187.997924804688</t>
   </si>
   <si>
-    <t xml:space="preserve">190.632904052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.537139892578</t>
+    <t xml:space="preserve">190.632919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.537109375</t>
   </si>
   <si>
     <t xml:space="preserve">185.889862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">182.152923583984</t>
+    <t xml:space="preserve">182.152908325195</t>
   </si>
   <si>
     <t xml:space="preserve">188.572830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">193.651275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.770553588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.410766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.39338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.237442016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.501434326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.172149658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.525833129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.555450439453</t>
+    <t xml:space="preserve">193.651229858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.770568847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.410751342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.393356323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.237457275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.501403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.172134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.525817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.555419921875</t>
   </si>
   <si>
     <t xml:space="preserve">193.938690185547</t>
   </si>
   <si>
-    <t xml:space="preserve">194.992706298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.471817016602</t>
+    <t xml:space="preserve">194.992721557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.471786499023</t>
   </si>
   <si>
     <t xml:space="preserve">198.442245483398</t>
   </si>
   <si>
-    <t xml:space="preserve">198.729675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.358612060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.538040161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.921340942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.987564086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.84992980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.215805053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.832534790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.802917480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.353439331055</t>
+    <t xml:space="preserve">198.72966003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.358596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.538024902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.921356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.987533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.849884033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.2158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.832504272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.802947998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.353424072266</t>
   </si>
   <si>
     <t xml:space="preserve">213.006790161133</t>
   </si>
   <si>
-    <t xml:space="preserve">217.989379882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.593902587891</t>
+    <t xml:space="preserve">217.989410400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.593948364258</t>
   </si>
   <si>
     <t xml:space="preserve">215.977188110352</t>
   </si>
   <si>
-    <t xml:space="preserve">219.905807495117</t>
+    <t xml:space="preserve">219.90576171875</t>
   </si>
   <si>
     <t xml:space="preserve">220.768173217773</t>
   </si>
   <si>
-    <t xml:space="preserve">218.892761230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.16162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.277465820312</t>
+    <t xml:space="preserve">218.892791748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.161651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.277481079102</t>
   </si>
   <si>
     <t xml:space="preserve">221.297134399414</t>
@@ -2684,94 +2684,94 @@
     <t xml:space="preserve">221.200942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">223.316787719727</t>
+    <t xml:space="preserve">223.316757202148</t>
   </si>
   <si>
     <t xml:space="preserve">224.663223266602</t>
   </si>
   <si>
-    <t xml:space="preserve">223.509124755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.182403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.067581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.162704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.064407348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.238143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.198822021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.756195068359</t>
+    <t xml:space="preserve">223.50910949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.182357788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.067596435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.162673950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.064376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.23811340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.198852539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.756240844727</t>
   </si>
   <si>
     <t xml:space="preserve">207.351837158203</t>
   </si>
   <si>
-    <t xml:space="preserve">203.985733032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.313598632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.640365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.50700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.929946899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.279602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">237.646759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.259948730469</t>
+    <t xml:space="preserve">203.985763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.313583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.640335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.506988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.929977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.279586791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.646774291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.259963989258</t>
   </si>
   <si>
     <t xml:space="preserve">225.624969482422</t>
   </si>
   <si>
-    <t xml:space="preserve">224.56706237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">232.068649291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.819427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.434753417969</t>
+    <t xml:space="preserve">224.567031860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.068664550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.819458007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.43473815918</t>
   </si>
   <si>
     <t xml:space="preserve">235.530899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">228.317855834961</t>
+    <t xml:space="preserve">228.317825317383</t>
   </si>
   <si>
     <t xml:space="preserve">227.644607543945</t>
   </si>
   <si>
-    <t xml:space="preserve">220.527725219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.662155151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.123382568359</t>
+    <t xml:space="preserve">220.527694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.662139892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.12336730957</t>
   </si>
   <si>
     <t xml:space="preserve">219.373641967773</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">207.544189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">208.409744262695</t>
+    <t xml:space="preserve">208.409774780273</t>
   </si>
   <si>
     <t xml:space="preserve">211.102645874023</t>
@@ -2795,76 +2795,76 @@
     <t xml:space="preserve">209.948547363281</t>
   </si>
   <si>
-    <t xml:space="preserve">207.15950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.042587280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.869888305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.813034057617</t>
+    <t xml:space="preserve">207.159454345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.042572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.869903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.813049316406</t>
   </si>
   <si>
     <t xml:space="preserve">208.121246337891</t>
   </si>
   <si>
-    <t xml:space="preserve">207.92887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.98681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.794479370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.352935791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.1015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.639297485352</t>
+    <t xml:space="preserve">207.928863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.986831665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.794448852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.352890014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.101593017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.639282226562</t>
   </si>
   <si>
     <t xml:space="preserve">202.158447265625</t>
   </si>
   <si>
-    <t xml:space="preserve">205.139831542969</t>
+    <t xml:space="preserve">205.139846801758</t>
   </si>
   <si>
     <t xml:space="preserve">202.927825927734</t>
   </si>
   <si>
-    <t xml:space="preserve">200.234954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.959426879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.076293945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.525741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.593139648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204.853820800781</t>
+    <t xml:space="preserve">200.234939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.959442138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.076278686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.525756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.593170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">204.853851318359</t>
   </si>
   <si>
     <t xml:space="preserve">200.892013549805</t>
   </si>
   <si>
-    <t xml:space="preserve">203.404388427734</t>
+    <t xml:space="preserve">203.404403686523</t>
   </si>
   <si>
     <t xml:space="preserve">205.916748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">205.626876831055</t>
+    <t xml:space="preserve">205.626861572266</t>
   </si>
   <si>
     <t xml:space="preserve">216.256072998047</t>
@@ -2873,64 +2873,64 @@
     <t xml:space="preserve">214.130233764648</t>
   </si>
   <si>
-    <t xml:space="preserve">214.806655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.957168579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.116714477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.397644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.90998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">233.262786865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">232.393157958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.233596801758</t>
+    <t xml:space="preserve">214.806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.957183837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.116729736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.397598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.910003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">233.262802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.393127441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.233581542969</t>
   </si>
   <si>
     <t xml:space="preserve">237.417846679688</t>
   </si>
   <si>
-    <t xml:space="preserve">236.161666870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.312240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.408843994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">246.307739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.33251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.651519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">249.88298034668</t>
+    <t xml:space="preserve">236.161651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.312255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.408874511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">246.307754516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.332473754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.651580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">249.883026123047</t>
   </si>
   <si>
     <t xml:space="preserve">251.525680541992</t>
   </si>
   <si>
-    <t xml:space="preserve">252.105484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.29426574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.004348754883</t>
+    <t xml:space="preserve">252.105453491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.294219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.004302978516</t>
   </si>
   <si>
     <t xml:space="preserve">251.622314453125</t>
@@ -2939,106 +2939,106 @@
     <t xml:space="preserve">252.008880615234</t>
   </si>
   <si>
-    <t xml:space="preserve">250.656005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.844879150391</t>
+    <t xml:space="preserve">250.656051635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.844802856445</t>
   </si>
   <si>
     <t xml:space="preserve">257.468414306641</t>
   </si>
   <si>
-    <t xml:space="preserve">260.802093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266.020111083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.489776611328</t>
+    <t xml:space="preserve">260.802124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266.02001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.48974609375</t>
   </si>
   <si>
     <t xml:space="preserve">276.890808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">275.006561279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.668395996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.305511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.692016601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.295349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.556060791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.796463012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.347030639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.869476318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.595367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.822357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.730194091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.536895751953</t>
+    <t xml:space="preserve">275.006591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.668365478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.305480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.691986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.295318603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.556030273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.796539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.347045898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.869537353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.595489501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.822326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.730163574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.536834716797</t>
   </si>
   <si>
     <t xml:space="preserve">264.957153320312</t>
   </si>
   <si>
-    <t xml:space="preserve">268.339233398438</t>
+    <t xml:space="preserve">268.339202880859</t>
   </si>
   <si>
     <t xml:space="preserve">265.102111816406</t>
   </si>
   <si>
-    <t xml:space="preserve">263.942504882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.57958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266.454925537109</t>
+    <t xml:space="preserve">263.942596435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.579650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266.454956054688</t>
   </si>
   <si>
     <t xml:space="preserve">267.4052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">281.854339599609</t>
+    <t xml:space="preserve">281.854309082031</t>
   </si>
   <si>
     <t xml:space="preserve">277.005706787109</t>
   </si>
   <si>
-    <t xml:space="preserve">274.290405273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.623229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">271.09033203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.599517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.108489990234</t>
+    <t xml:space="preserve">274.290435791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.623260498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271.090240478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.599548339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.108520507812</t>
   </si>
   <si>
     <t xml:space="preserve">280.642150878906</t>
@@ -3047,19 +3047,19 @@
     <t xml:space="preserve">281.466461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">282.630187988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.532806396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">280.205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">278.411773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">284.084777832031</t>
+    <t xml:space="preserve">282.630157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.532867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">280.205780029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">278.411743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">284.084808349609</t>
   </si>
   <si>
     <t xml:space="preserve">279.769378662109</t>
@@ -3068,67 +3068,67 @@
     <t xml:space="preserve">275.066192626953</t>
   </si>
   <si>
-    <t xml:space="preserve">270.750854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.471923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">271.817504882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.611175537109</t>
+    <t xml:space="preserve">270.750823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.471954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271.817596435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.611267089844</t>
   </si>
   <si>
     <t xml:space="preserve">272.253936767578</t>
   </si>
   <si>
-    <t xml:space="preserve">270.847747802734</t>
+    <t xml:space="preserve">270.847808837891</t>
   </si>
   <si>
     <t xml:space="preserve">274.484375</t>
   </si>
   <si>
-    <t xml:space="preserve">279.720916748047</t>
+    <t xml:space="preserve">279.720977783203</t>
   </si>
   <si>
     <t xml:space="preserve">284.763549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">298.291381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.455078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.576141357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.552032470703</t>
+    <t xml:space="preserve">298.291351318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.455017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.576080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.552062988281</t>
   </si>
   <si>
     <t xml:space="preserve">298.679260253906</t>
   </si>
   <si>
-    <t xml:space="preserve">299.843078613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.946136474609</t>
+    <t xml:space="preserve">299.842987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.946197509766</t>
   </si>
   <si>
     <t xml:space="preserve">303.721923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">314.049652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.740478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.019378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.364959716797</t>
+    <t xml:space="preserve">314.049682617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.740509033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.019439697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.364990234375</t>
   </si>
   <si>
     <t xml:space="preserve">309.443420410156</t>
@@ -3137,10 +3137,10 @@
     <t xml:space="preserve">311.625305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">318.122528076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.213317871094</t>
+    <t xml:space="preserve">318.12255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.21337890625</t>
   </si>
   <si>
     <t xml:space="preserve">309.879760742188</t>
@@ -3149,118 +3149,118 @@
     <t xml:space="preserve">306.825103759766</t>
   </si>
   <si>
-    <t xml:space="preserve">311.916198730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.837463378906</t>
+    <t xml:space="preserve">311.916229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.837524414062</t>
   </si>
   <si>
     <t xml:space="preserve">316.231536865234</t>
   </si>
   <si>
-    <t xml:space="preserve">313.467803955078</t>
+    <t xml:space="preserve">313.4677734375</t>
   </si>
   <si>
     <t xml:space="preserve">314.631500244141</t>
   </si>
   <si>
-    <t xml:space="preserve">313.661834716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.425170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.473693847656</t>
+    <t xml:space="preserve">313.661773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.425140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.473663330078</t>
   </si>
   <si>
     <t xml:space="preserve">300.667266845703</t>
   </si>
   <si>
-    <t xml:space="preserve">289.854614257812</t>
+    <t xml:space="preserve">289.854736328125</t>
   </si>
   <si>
     <t xml:space="preserve">288.836456298828</t>
   </si>
   <si>
-    <t xml:space="preserve">289.369873046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.284881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">285.539367675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">283.842346191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.806793212891</t>
+    <t xml:space="preserve">289.369903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.284912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">285.539306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">283.84228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.806762695312</t>
   </si>
   <si>
     <t xml:space="preserve">297.298797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">298.369049072266</t>
+    <t xml:space="preserve">298.369110107422</t>
   </si>
   <si>
     <t xml:space="preserve">305.812530517578</t>
   </si>
   <si>
-    <t xml:space="preserve">303.57470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.428955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.126312255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.996398925781</t>
+    <t xml:space="preserve">303.574645996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.428924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.126281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.996429443359</t>
   </si>
   <si>
     <t xml:space="preserve">311.358612060547</t>
   </si>
   <si>
-    <t xml:space="preserve">309.412658691406</t>
+    <t xml:space="preserve">309.41259765625</t>
   </si>
   <si>
     <t xml:space="preserve">314.228942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">303.234039306641</t>
+    <t xml:space="preserve">303.234069824219</t>
   </si>
   <si>
     <t xml:space="preserve">299.925903320312</t>
   </si>
   <si>
-    <t xml:space="preserve">294.185241699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.250183105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.217864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.888000488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.596313476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.963836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.688323974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.585571289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.299072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.96923828125</t>
+    <t xml:space="preserve">294.185272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.250152587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.217742919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.887969970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.596282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.9638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.688262939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.585632324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.298980712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.969207763672</t>
   </si>
   <si>
     <t xml:space="preserve">300.412384033203</t>
@@ -3269,28 +3269,28 @@
     <t xml:space="preserve">299.342102050781</t>
   </si>
   <si>
-    <t xml:space="preserve">293.796051025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.990631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.104217529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.601867675781</t>
+    <t xml:space="preserve">293.796112060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.990661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.104248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.601806640625</t>
   </si>
   <si>
     <t xml:space="preserve">311.845123291016</t>
   </si>
   <si>
-    <t xml:space="preserve">314.082977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.883728027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327.656311035156</t>
+    <t xml:space="preserve">314.083038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.883636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327.656280517578</t>
   </si>
   <si>
     <t xml:space="preserve">324.445404052734</t>
@@ -3299,151 +3299,151 @@
     <t xml:space="preserve">316.612823486328</t>
   </si>
   <si>
-    <t xml:space="preserve">320.067016601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.348114013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.721282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.650939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323.375091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.758972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327.315673828125</t>
+    <t xml:space="preserve">320.066925048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.348083496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.721252441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.650909423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.375122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.758911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327.315704345703</t>
   </si>
   <si>
     <t xml:space="preserve">324.883239746094</t>
   </si>
   <si>
-    <t xml:space="preserve">330.380645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.521301269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.580657958984</t>
+    <t xml:space="preserve">330.380676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.521270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.580627441406</t>
   </si>
   <si>
     <t xml:space="preserve">326.245422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">325.710357666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.515899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.759338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.543121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.456787109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.748718261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.710876464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">354.802886962891</t>
+    <t xml:space="preserve">325.710327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.515869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.759399414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.543151855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.456756591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.748687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.7109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">354.802856445312</t>
   </si>
   <si>
     <t xml:space="preserve">341.424194335938</t>
   </si>
   <si>
-    <t xml:space="preserve">353.829925537109</t>
+    <t xml:space="preserve">353.829895019531</t>
   </si>
   <si>
     <t xml:space="preserve">358.257019042969</t>
   </si>
   <si>
-    <t xml:space="preserve">350.473052978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.224487304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">353.635314941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.429962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">349.013610839844</t>
+    <t xml:space="preserve">350.473083496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.224426269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">353.63525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.429992675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">349.013580322266</t>
   </si>
   <si>
     <t xml:space="preserve">330.672576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">334.946685791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.531311035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.921600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.898681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.972045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.728912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.606719970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.581665039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.093780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.704376220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.095031738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.435760498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">344.509521484375</t>
+    <t xml:space="preserve">334.946594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.531280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.921630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.898651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.972015380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.728973388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.606781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.581726074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.093872070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.704345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.095062255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.435729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.509552001953</t>
   </si>
   <si>
     <t xml:space="preserve">344.119262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">346.509948730469</t>
+    <t xml:space="preserve">346.509979248047</t>
   </si>
   <si>
     <t xml:space="preserve">345.826904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">342.070037841797</t>
+    <t xml:space="preserve">342.070007324219</t>
   </si>
   <si>
     <t xml:space="preserve">345.582946777344</t>
   </si>
   <si>
-    <t xml:space="preserve">343.680084228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.411102294922</t>
+    <t xml:space="preserve">343.68017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.411163330078</t>
   </si>
   <si>
     <t xml:space="preserve">338.801086425781</t>
@@ -3452,13 +3452,13 @@
     <t xml:space="preserve">335.239379882812</t>
   </si>
   <si>
-    <t xml:space="preserve">332.751068115234</t>
+    <t xml:space="preserve">332.751037597656</t>
   </si>
   <si>
     <t xml:space="preserve">328.945373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">328.994171142578</t>
+    <t xml:space="preserve">328.994201660156</t>
   </si>
   <si>
     <t xml:space="preserve">330.116363525391</t>
@@ -3467,55 +3467,55 @@
     <t xml:space="preserve">340.118408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">338.654693603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.800689697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.141845703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.605987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.044219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.703094482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.629730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">337.288513183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.897033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.434478759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.774078369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.625610351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">321.529266357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">321.919647216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">326.018005371094</t>
+    <t xml:space="preserve">338.654724121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.800659179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.141784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.605865478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.044189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.629669189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">337.28857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.89697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.434509277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.774017333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.625579833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">321.529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">321.919586181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326.017974853516</t>
   </si>
   <si>
     <t xml:space="preserve">323.968811035156</t>
   </si>
   <si>
-    <t xml:space="preserve">325.1884765625</t>
+    <t xml:space="preserve">325.188568115234</t>
   </si>
   <si>
     <t xml:space="preserve">320.065551757812</t>
@@ -3524,25 +3524,25 @@
     <t xml:space="preserve">317.528442382812</t>
   </si>
   <si>
-    <t xml:space="preserve">311.088134765625</t>
+    <t xml:space="preserve">311.088104248047</t>
   </si>
   <si>
     <t xml:space="preserve">307.672729492188</t>
   </si>
   <si>
-    <t xml:space="preserve">307.428771972656</t>
+    <t xml:space="preserve">307.428833007812</t>
   </si>
   <si>
     <t xml:space="preserve">310.161071777344</t>
   </si>
   <si>
-    <t xml:space="preserve">313.039642333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.794952392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.184844970703</t>
+    <t xml:space="preserve">313.039733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.184783935547</t>
   </si>
   <si>
     <t xml:space="preserve">305.477142333984</t>
@@ -3554,34 +3554,34 @@
     <t xml:space="preserve">307.331237792969</t>
   </si>
   <si>
-    <t xml:space="preserve">306.160217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.501770019531</t>
+    <t xml:space="preserve">306.160247802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.501800537109</t>
   </si>
   <si>
     <t xml:space="preserve">309.575561523438</t>
   </si>
   <si>
-    <t xml:space="preserve">312.161499023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.796600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.503845214844</t>
+    <t xml:space="preserve">312.161529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.796569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.503875732422</t>
   </si>
   <si>
     <t xml:space="preserve">318.393707275391</t>
   </si>
   <si>
-    <t xml:space="preserve">313.595550537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.558563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.942810058594</t>
+    <t xml:space="preserve">313.595520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.558532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.942840576172</t>
   </si>
   <si>
     <t xml:space="preserve">300.571899414062</t>
@@ -3596,46 +3596,46 @@
     <t xml:space="preserve">304.341888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">299.886383056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294.011138916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.939971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290.192138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.604644775391</t>
+    <t xml:space="preserve">299.886444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.011108398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.939910888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">290.192199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.604614257812</t>
   </si>
   <si>
     <t xml:space="preserve">293.080841064453</t>
   </si>
   <si>
-    <t xml:space="preserve">291.465148925781</t>
+    <t xml:space="preserve">291.465118408203</t>
   </si>
   <si>
     <t xml:space="preserve">289.702545166016</t>
   </si>
   <si>
-    <t xml:space="preserve">288.380584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.129852294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">292.052703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.528930664062</t>
+    <t xml:space="preserve">288.380676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.129821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">292.052673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.528900146484</t>
   </si>
   <si>
     <t xml:space="preserve">295.969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">304.195037841797</t>
+    <t xml:space="preserve">304.195007324219</t>
   </si>
   <si>
     <t xml:space="preserve">304.390869140625</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">303.411651611328</t>
   </si>
   <si>
-    <t xml:space="preserve">299.592681884766</t>
+    <t xml:space="preserve">299.592651367188</t>
   </si>
   <si>
     <t xml:space="preserve">301.110473632812</t>
@@ -3656,16 +3656,16 @@
     <t xml:space="preserve">299.984344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">305.370086669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.488800048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.509582519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.419036865234</t>
+    <t xml:space="preserve">305.3701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.488830566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.509552001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.419006347656</t>
   </si>
   <si>
     <t xml:space="preserve">303.950225830078</t>
@@ -3680,13 +3680,13 @@
     <t xml:space="preserve">318.442687988281</t>
   </si>
   <si>
-    <t xml:space="preserve">325.884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.018280029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.605773925781</t>
+    <t xml:space="preserve">325.884796142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.018249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.605804443359</t>
   </si>
   <si>
     <t xml:space="preserve">330.976684570312</t>
@@ -3698,61 +3698,61 @@
     <t xml:space="preserve">334.110229492188</t>
   </si>
   <si>
-    <t xml:space="preserve">332.543487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.760070800781</t>
+    <t xml:space="preserve">332.543518066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.760040283203</t>
   </si>
   <si>
     <t xml:space="preserve">341.944000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">340.768890380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">344.685821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.32373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">358.786590576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.433349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">380.133666992188</t>
+    <t xml:space="preserve">340.768951416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.685791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.323669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">358.786560058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.433319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">380.133575439453</t>
   </si>
   <si>
     <t xml:space="preserve">382.679534912109</t>
   </si>
   <si>
-    <t xml:space="preserve">385.2255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385.421447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">386.204803466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389.338317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">395.358062744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389.466003417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.394012451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.197570800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">398.304107666016</t>
+    <t xml:space="preserve">385.225555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385.42138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">386.204833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">389.338287353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">395.358032226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">389.465972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.393981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.197601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">398.304077148438</t>
   </si>
   <si>
     <t xml:space="preserve">401.0537109375</t>
@@ -3767,58 +3767,58 @@
     <t xml:space="preserve">388.091156005859</t>
   </si>
   <si>
-    <t xml:space="preserve">387.109191894531</t>
+    <t xml:space="preserve">387.109130859375</t>
   </si>
   <si>
     <t xml:space="preserve">391.233551025391</t>
   </si>
   <si>
-    <t xml:space="preserve">396.143646240234</t>
+    <t xml:space="preserve">396.143615722656</t>
   </si>
   <si>
     <t xml:space="preserve">388.680328369141</t>
   </si>
   <si>
-    <t xml:space="preserve">396.536468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.160125732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">408.124145507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404.785369873047</t>
+    <t xml:space="preserve">396.536437988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.16015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">408.124206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404.785308837891</t>
   </si>
   <si>
     <t xml:space="preserve">405.963775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">407.731353759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">403.999725341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.178131103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.821319580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.535003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.749420166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">413.034271240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">409.498962402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.551513671875</t>
+    <t xml:space="preserve">407.731384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">403.999786376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.178161621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.821350097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.534973144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.749389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413.034301757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409.498992919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.551544189453</t>
   </si>
   <si>
     <t xml:space="preserve">419.122711181641</t>
@@ -3827,16 +3827,16 @@
     <t xml:space="preserve">421.479583740234</t>
   </si>
   <si>
-    <t xml:space="preserve">415.980316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.7119140625</t>
+    <t xml:space="preserve">415.980285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.711883544922</t>
   </si>
   <si>
     <t xml:space="preserve">420.497528076172</t>
   </si>
   <si>
-    <t xml:space="preserve">405.570953369141</t>
+    <t xml:space="preserve">405.570983886719</t>
   </si>
   <si>
     <t xml:space="preserve">403.606903076172</t>
@@ -3848,19 +3848,19 @@
     <t xml:space="preserve">390.447967529297</t>
   </si>
   <si>
-    <t xml:space="preserve">383.377471923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">391.822784423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">395.947204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">394.572448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.338562011719</t>
+    <t xml:space="preserve">383.377502441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">391.822814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">395.947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">394.572418212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.338592529297</t>
   </si>
   <si>
     <t xml:space="preserve">410.284606933594</t>
@@ -3869,46 +3869,46 @@
     <t xml:space="preserve">409.302612304688</t>
   </si>
   <si>
-    <t xml:space="preserve">408.320556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.142181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.356597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.232086181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.767395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">413.819885253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404.588989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">400.464508056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">403.410491943359</t>
+    <t xml:space="preserve">408.320617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.142211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.356506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.232116699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.767364501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413.819854736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404.588958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400.464477539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">403.410522460938</t>
   </si>
   <si>
     <t xml:space="preserve">477.650634765625</t>
   </si>
   <si>
-    <t xml:space="preserve">474.508270263672</t>
+    <t xml:space="preserve">474.508209228516</t>
   </si>
   <si>
     <t xml:space="preserve">470.187347412109</t>
   </si>
   <si>
-    <t xml:space="preserve">474.115417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">486.251953125</t>
+    <t xml:space="preserve">474.115386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">486.251983642578</t>
   </si>
   <si>
     <t xml:space="preserve">488.614349365234</t>
@@ -3917,55 +3917,55 @@
     <t xml:space="preserve">495.11083984375</t>
   </si>
   <si>
-    <t xml:space="preserve">493.634368896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">492.157928466797</t>
+    <t xml:space="preserve">493.634399414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">492.157867431641</t>
   </si>
   <si>
     <t xml:space="preserve">496.095153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">500.524597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.048126220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">503.477508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">503.969696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">501.016723632812</t>
+    <t xml:space="preserve">500.524536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.048095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">503.477569580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">503.969665527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">501.016693115234</t>
   </si>
   <si>
     <t xml:space="preserve">495.602996826172</t>
   </si>
   <si>
-    <t xml:space="preserve">500.032409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">507.414825439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">511.844146728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.797058105469</t>
+    <t xml:space="preserve">500.032379150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">507.414764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">511.844177246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.797180175781</t>
   </si>
   <si>
     <t xml:space="preserve">509.383453369141</t>
   </si>
   <si>
-    <t xml:space="preserve">527.593322753906</t>
+    <t xml:space="preserve">527.59326171875</t>
   </si>
   <si>
     <t xml:space="preserve">535.960021972656</t>
   </si>
   <si>
-    <t xml:space="preserve">547.279602050781</t>
+    <t xml:space="preserve">547.279479980469</t>
   </si>
   <si>
     <t xml:space="preserve">546.295288085938</t>
@@ -3974,73 +3974,73 @@
     <t xml:space="preserve">546.787414550781</t>
   </si>
   <si>
-    <t xml:space="preserve">550.232482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">539.897277832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">528.08544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">526.116821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">512.336364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">510.85986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">489.992431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.461883544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">517.750061035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.514770507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">554.661926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.442443847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567.950134277344</t>
+    <t xml:space="preserve">550.232604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">539.897216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">528.085388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">526.116760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">512.336486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">510.859954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">489.992401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.461853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">517.750183105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.514892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">554.661987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.4423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567.9501953125</t>
   </si>
   <si>
     <t xml:space="preserve">575.824768066406</t>
   </si>
   <si>
-    <t xml:space="preserve">561.552124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569.426696777344</t>
+    <t xml:space="preserve">561.552062988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569.426635742188</t>
   </si>
   <si>
     <t xml:space="preserve">545.803100585938</t>
   </si>
   <si>
-    <t xml:space="preserve">543.342346191406</t>
+    <t xml:space="preserve">543.34228515625</t>
   </si>
   <si>
     <t xml:space="preserve">540.389404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">549.248229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">555.646179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.022766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">523.656005859375</t>
+    <t xml:space="preserve">549.248107910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">555.646301269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.022705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">523.655944824219</t>
   </si>
   <si>
     <t xml:space="preserve">514.304992675781</t>
@@ -4049,43 +4049,43 @@
     <t xml:space="preserve">517.257934570312</t>
   </si>
   <si>
-    <t xml:space="preserve">534.975646972656</t>
+    <t xml:space="preserve">534.975708007812</t>
   </si>
   <si>
     <t xml:space="preserve">544.818786621094</t>
   </si>
   <si>
-    <t xml:space="preserve">553.185424804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">554.299987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">536.053466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.108215332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">536.546508789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">542.46435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.532958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">541.478210449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">543.45068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">533.094543457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">531.122009277344</t>
+    <t xml:space="preserve">553.185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">554.300048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">536.053405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.108276367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">536.546691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">542.464477539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.532897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">541.478088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">543.450744628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">533.094604492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">531.121948242188</t>
   </si>
   <si>
     <t xml:space="preserve">538.026062011719</t>
@@ -4094,34 +4094,34 @@
     <t xml:space="preserve">540.491821289062</t>
   </si>
   <si>
-    <t xml:space="preserve">532.601440429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.039855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">534.080871582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">539.012390136719</t>
+    <t xml:space="preserve">532.601379394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.039794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534.080932617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">539.012329101562</t>
   </si>
   <si>
     <t xml:space="preserve">526.190490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">531.615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">517.806945800781</t>
+    <t xml:space="preserve">531.615051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">517.807006835938</t>
   </si>
   <si>
     <t xml:space="preserve">513.368591308594</t>
   </si>
   <si>
-    <t xml:space="preserve">523.231628417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">519.779541015625</t>
+    <t xml:space="preserve">523.231567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">519.779479980469</t>
   </si>
   <si>
     <t xml:space="preserve">511.88916015625</t>
@@ -4133,16 +4133,16 @@
     <t xml:space="preserve">511.39599609375</t>
   </si>
   <si>
-    <t xml:space="preserve">518.793273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">520.765930175781</t>
+    <t xml:space="preserve">518.793334960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">520.765869140625</t>
   </si>
   <si>
     <t xml:space="preserve">527.669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">552.820495605469</t>
+    <t xml:space="preserve">552.820556640625</t>
   </si>
   <si>
     <t xml:space="preserve">567.121887207031</t>
@@ -4154,34 +4154,34 @@
     <t xml:space="preserve">567.615112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">565.642395019531</t>
+    <t xml:space="preserve">565.642456054688</t>
   </si>
   <si>
     <t xml:space="preserve">568.108215332031</t>
   </si>
   <si>
-    <t xml:space="preserve">573.532775878906</t>
+    <t xml:space="preserve">573.532897949219</t>
   </si>
   <si>
     <t xml:space="preserve">581.423217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">583.889038085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">575.012268066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">561.697204589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569.094421386719</t>
+    <t xml:space="preserve">583.888916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">575.012329101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">561.697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569.094543457031</t>
   </si>
   <si>
     <t xml:space="preserve">568.601379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">577.47802734375</t>
+    <t xml:space="preserve">577.478088378906</t>
   </si>
   <si>
     <t xml:space="preserve">572.053405761719</t>
@@ -4190,58 +4190,58 @@
     <t xml:space="preserve">577.97119140625</t>
   </si>
   <si>
-    <t xml:space="preserve">587.341003417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">587.834167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">585.861511230469</t>
+    <t xml:space="preserve">587.341064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">587.834228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">585.861633300781</t>
   </si>
   <si>
     <t xml:space="preserve">593.751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">609.03955078125</t>
+    <t xml:space="preserve">609.039611816406</t>
   </si>
   <si>
     <t xml:space="preserve">646.025756835938</t>
   </si>
   <si>
-    <t xml:space="preserve">642.08056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">668.217529296875</t>
+    <t xml:space="preserve">642.080627441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">668.217468261719</t>
   </si>
   <si>
     <t xml:space="preserve">675.614868164062</t>
   </si>
   <si>
-    <t xml:space="preserve">677.09423828125</t>
+    <t xml:space="preserve">677.094177246094</t>
   </si>
   <si>
     <t xml:space="preserve">671.176452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">679.559997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">695.172973632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">698.631591796875</t>
+    <t xml:space="preserve">679.56005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">695.172912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">698.631469726562</t>
   </si>
   <si>
     <t xml:space="preserve">722.841491699219</t>
   </si>
   <si>
-    <t xml:space="preserve">726.300048828125</t>
+    <t xml:space="preserve">726.300109863281</t>
   </si>
   <si>
     <t xml:space="preserve">700.113708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">681.338623046875</t>
+    <t xml:space="preserve">681.338562011719</t>
   </si>
   <si>
     <t xml:space="preserve">707.030944824219</t>
@@ -4250,61 +4250,61 @@
     <t xml:space="preserve">697.643310546875</t>
   </si>
   <si>
-    <t xml:space="preserve">705.054626464844</t>
+    <t xml:space="preserve">705.054565429688</t>
   </si>
   <si>
     <t xml:space="preserve">699.125610351562</t>
   </si>
   <si>
-    <t xml:space="preserve">688.255798339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">686.279541015625</t>
+    <t xml:space="preserve">688.255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">686.279418945312</t>
   </si>
   <si>
     <t xml:space="preserve">709.995422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">722.347473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">710.489501953125</t>
+    <t xml:space="preserve">722.347412109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">710.489562988281</t>
   </si>
   <si>
     <t xml:space="preserve">711.971740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">690.232177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">660.587219238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">678.868286132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">683.315002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">682.326843261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">697.149230957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.066467285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">706.042663574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720.865173339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">698.829223632812</t>
+    <t xml:space="preserve">690.232116699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">660.587280273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">678.868225097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">683.31494140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">682.326782226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">697.149291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.560485839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.066528320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706.042724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720.865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">698.829162597656</t>
   </si>
   <si>
     <t xml:space="preserve">709.896606445312</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">704.165222167969</t>
   </si>
   <si>
-    <t xml:space="preserve">709.204956054688</t>
+    <t xml:space="preserve">709.204895019531</t>
   </si>
   <si>
     <t xml:space="preserve">708.710815429688</t>
@@ -4328,16 +4328,16 @@
     <t xml:space="preserve">702.090087890625</t>
   </si>
   <si>
-    <t xml:space="preserve">706.1416015625</t>
+    <t xml:space="preserve">706.141540527344</t>
   </si>
   <si>
     <t xml:space="preserve">695.469421386719</t>
   </si>
   <si>
-    <t xml:space="preserve">694.283569335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677.188293457031</t>
+    <t xml:space="preserve">694.283630371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">677.188354492188</t>
   </si>
   <si>
     <t xml:space="preserve">676.6943359375</t>
@@ -4352,16 +4352,16 @@
     <t xml:space="preserve">667.603149414062</t>
   </si>
   <si>
-    <t xml:space="preserve">680.745788574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">674.619201660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">711.576477050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">674.520324707031</t>
+    <t xml:space="preserve">680.745849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">674.619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.576538085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">674.520263671875</t>
   </si>
   <si>
     <t xml:space="preserve">688.8486328125</t>
@@ -4373,7 +4373,7 @@
     <t xml:space="preserve">712.367004394531</t>
   </si>
   <si>
-    <t xml:space="preserve">690.13330078125</t>
+    <t xml:space="preserve">690.133361816406</t>
   </si>
   <si>
     <t xml:space="preserve">690.528564453125</t>
@@ -4385,13 +4385,13 @@
     <t xml:space="preserve">705.57666015625</t>
   </si>
   <si>
-    <t xml:space="preserve">701.517639160156</t>
+    <t xml:space="preserve">701.517578125</t>
   </si>
   <si>
     <t xml:space="preserve">712.407653808594</t>
   </si>
   <si>
-    <t xml:space="preserve">732.603820800781</t>
+    <t xml:space="preserve">732.603759765625</t>
   </si>
   <si>
     <t xml:space="preserve">729.336791992188</t>
@@ -4406,13 +4406,13 @@
     <t xml:space="preserve">739.434875488281</t>
   </si>
   <si>
-    <t xml:space="preserve">733.593872070312</t>
+    <t xml:space="preserve">733.593811035156</t>
   </si>
   <si>
     <t xml:space="preserve">744.087829589844</t>
   </si>
   <si>
-    <t xml:space="preserve">744.681945800781</t>
+    <t xml:space="preserve">744.681884765625</t>
   </si>
   <si>
     <t xml:space="preserve">746.661865234375</t>
@@ -4421,34 +4421,34 @@
     <t xml:space="preserve">758.640930175781</t>
   </si>
   <si>
-    <t xml:space="preserve">754.185913085938</t>
+    <t xml:space="preserve">754.185791015625</t>
   </si>
   <si>
     <t xml:space="preserve">757.749938964844</t>
   </si>
   <si>
-    <t xml:space="preserve">762.204895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">778.242980957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">791.410217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">793.588195800781</t>
+    <t xml:space="preserve">762.205017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">778.243041992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">791.41015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">793.588134765625</t>
   </si>
   <si>
     <t xml:space="preserve">787.549072265625</t>
   </si>
   <si>
-    <t xml:space="preserve">807.250183105469</t>
+    <t xml:space="preserve">807.250244140625</t>
   </si>
   <si>
     <t xml:space="preserve">815.764221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">815.962158203125</t>
+    <t xml:space="preserve">815.962280273438</t>
   </si>
   <si>
     <t xml:space="preserve">825.565307617188</t>
@@ -4481,16 +4481,16 @@
     <t xml:space="preserve">845.266357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">828.931335449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">818.932250976562</t>
+    <t xml:space="preserve">828.931274414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">818.932189941406</t>
   </si>
   <si>
     <t xml:space="preserve">825.664245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">834.970336914062</t>
+    <t xml:space="preserve">834.970458984375</t>
   </si>
   <si>
     <t xml:space="preserve">839.722351074219</t>
@@ -4502,19 +4502,19 @@
     <t xml:space="preserve">861.403442382812</t>
   </si>
   <si>
-    <t xml:space="preserve">845.563354492188</t>
+    <t xml:space="preserve">845.563293457031</t>
   </si>
   <si>
     <t xml:space="preserve">859.720458984375</t>
   </si>
   <si>
-    <t xml:space="preserve">863.9775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.482482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">830.020385742188</t>
+    <t xml:space="preserve">863.977416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">830.020324707031</t>
   </si>
   <si>
     <t xml:space="preserve">773.392028808594</t>
@@ -4526,13 +4526,13 @@
     <t xml:space="preserve">784.282043457031</t>
   </si>
   <si>
-    <t xml:space="preserve">807.646179199219</t>
+    <t xml:space="preserve">807.646118164062</t>
   </si>
   <si>
     <t xml:space="preserve">782.401062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">760.224975585938</t>
+    <t xml:space="preserve">760.224914550781</t>
   </si>
   <si>
     <t xml:space="preserve">743.790832519531</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">737.751831054688</t>
   </si>
   <si>
-    <t xml:space="preserve">726.4658203125</t>
+    <t xml:space="preserve">726.465759277344</t>
   </si>
   <si>
     <t xml:space="preserve">735.078796386719</t>
@@ -4553,34 +4553,34 @@
     <t xml:space="preserve">720.030700683594</t>
   </si>
   <si>
-    <t xml:space="preserve">699.042602539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720.327697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">702.8046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">755.967956542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812.794250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">806.359191894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">817.744201660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">838.138305664062</t>
+    <t xml:space="preserve">699.042663574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720.32763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">702.804626464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">755.967895507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812.794189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">806.359252929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">817.744262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.138366699219</t>
   </si>
   <si>
     <t xml:space="preserve">836.353576660156</t>
   </si>
   <si>
-    <t xml:space="preserve">824.752624511719</t>
+    <t xml:space="preserve">824.752685546875</t>
   </si>
   <si>
     <t xml:space="preserve">846.169738769531</t>
@@ -4595,25 +4595,25 @@
     <t xml:space="preserve">840.220581054688</t>
   </si>
   <si>
-    <t xml:space="preserve">845.37646484375</t>
+    <t xml:space="preserve">845.376525878906</t>
   </si>
   <si>
     <t xml:space="preserve">851.028137207031</t>
   </si>
   <si>
-    <t xml:space="preserve">845.673889160156</t>
+    <t xml:space="preserve">845.673950195312</t>
   </si>
   <si>
     <t xml:space="preserve">850.631652832031</t>
   </si>
   <si>
-    <t xml:space="preserve">846.764587402344</t>
+    <t xml:space="preserve">846.7646484375</t>
   </si>
   <si>
     <t xml:space="preserve">858.563842773438</t>
   </si>
   <si>
-    <t xml:space="preserve">867.586730957031</t>
+    <t xml:space="preserve">867.586669921875</t>
   </si>
   <si>
     <t xml:space="preserve">852.218078613281</t>
@@ -4634,10 +4634,10 @@
     <t xml:space="preserve">812.953552246094</t>
   </si>
   <si>
-    <t xml:space="preserve">831.197631835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">835.064575195312</t>
+    <t xml:space="preserve">831.197692871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">835.064636230469</t>
   </si>
   <si>
     <t xml:space="preserve">824.05859375</t>
@@ -4646,19 +4646,19 @@
     <t xml:space="preserve">812.556945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">808.987426757812</t>
+    <t xml:space="preserve">808.987365722656</t>
   </si>
   <si>
     <t xml:space="preserve">805.51708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">825.5458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816.919677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819.695983886719</t>
+    <t xml:space="preserve">825.545959472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816.919616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.695922851562</t>
   </si>
   <si>
     <t xml:space="preserve">821.579772949219</t>
@@ -4688,16 +4688,16 @@
     <t xml:space="preserve">816.32470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">826.636596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">829.313720703125</t>
+    <t xml:space="preserve">826.636657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">829.313781738281</t>
   </si>
   <si>
     <t xml:space="preserve">836.948486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">829.809509277344</t>
+    <t xml:space="preserve">829.8095703125</t>
   </si>
   <si>
     <t xml:space="preserve">832.982360839844</t>
@@ -4706,25 +4706,25 @@
     <t xml:space="preserve">841.410400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">838.435791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">830.0078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">833.27978515625</t>
+    <t xml:space="preserve">838.435668945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">830.007751464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">833.279907226562</t>
   </si>
   <si>
     <t xml:space="preserve">823.662048339844</t>
   </si>
   <si>
-    <t xml:space="preserve">819.200134277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">822.868835449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819.894226074219</t>
+    <t xml:space="preserve">819.2001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">822.868896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.894287109375</t>
   </si>
   <si>
     <t xml:space="preserve">827.132385253906</t>
@@ -4736,22 +4736,22 @@
     <t xml:space="preserve">778.646667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">754.651611328125</t>
+    <t xml:space="preserve">754.651672363281</t>
   </si>
   <si>
     <t xml:space="preserve">737.002502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">726.492370605469</t>
+    <t xml:space="preserve">726.492309570312</t>
   </si>
   <si>
     <t xml:space="preserve">716.9736328125</t>
   </si>
   <si>
-    <t xml:space="preserve">725.401672363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766.549987792969</t>
+    <t xml:space="preserve">725.401611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766.550048828125</t>
   </si>
   <si>
     <t xml:space="preserve">778.250061035156</t>
@@ -4763,28 +4763,28 @@
     <t xml:space="preserve">771.309387207031</t>
   </si>
   <si>
-    <t xml:space="preserve">750.090698242188</t>
+    <t xml:space="preserve">750.090637207031</t>
   </si>
   <si>
     <t xml:space="preserve">713.24169921875</t>
   </si>
   <si>
-    <t xml:space="preserve">680.464965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">679.670349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">703.706604003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.295776367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">715.228149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760.916870117188</t>
+    <t xml:space="preserve">680.464904785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679.67041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">703.706665039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.295837402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">715.228088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760.916931152344</t>
   </si>
   <si>
     <t xml:space="preserve">744.429260253906</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">749.892028808594</t>
   </si>
   <si>
-    <t xml:space="preserve">756.447387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766.776977539062</t>
+    <t xml:space="preserve">756.447326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766.777038574219</t>
   </si>
   <si>
     <t xml:space="preserve">790.416015625</t>
@@ -4805,13 +4805,13 @@
     <t xml:space="preserve">774.623596191406</t>
   </si>
   <si>
-    <t xml:space="preserve">788.429504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760.519714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">756.34814453125</t>
+    <t xml:space="preserve">788.429565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760.519653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">756.348022460938</t>
   </si>
   <si>
     <t xml:space="preserve">748.104248046875</t>
@@ -4820,22 +4820,22 @@
     <t xml:space="preserve">747.408935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">740.952941894531</t>
+    <t xml:space="preserve">740.952880859375</t>
   </si>
   <si>
     <t xml:space="preserve">744.329956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">744.925903320312</t>
+    <t xml:space="preserve">744.925842285156</t>
   </si>
   <si>
     <t xml:space="preserve">735.788146972656</t>
   </si>
   <si>
-    <t xml:space="preserve">725.756408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">759.02978515625</t>
+    <t xml:space="preserve">725.756469726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">759.029846191406</t>
   </si>
   <si>
     <t xml:space="preserve">745.521789550781</t>
@@ -4844,22 +4844,22 @@
     <t xml:space="preserve">748.700134277344</t>
   </si>
   <si>
-    <t xml:space="preserve">738.569152832031</t>
+    <t xml:space="preserve">738.569213867188</t>
   </si>
   <si>
     <t xml:space="preserve">759.327758789062</t>
   </si>
   <si>
-    <t xml:space="preserve">753.070373535156</t>
+    <t xml:space="preserve">753.070434570312</t>
   </si>
   <si>
     <t xml:space="preserve">739.860412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">740.158325195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.731811523438</t>
+    <t xml:space="preserve">740.158386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.731872558594</t>
   </si>
   <si>
     <t xml:space="preserve">758.433837890625</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">769.359436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">718.505798339844</t>
+    <t xml:space="preserve">718.505859375</t>
   </si>
   <si>
     <t xml:space="preserve">720.1943359375</t>
@@ -4883,7 +4883,7 @@
     <t xml:space="preserve">714.731506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">693.675048828125</t>
+    <t xml:space="preserve">693.674987792969</t>
   </si>
   <si>
     <t xml:space="preserve">697.548583984375</t>
@@ -4898,16 +4898,16 @@
     <t xml:space="preserve">741.846862792969</t>
   </si>
   <si>
-    <t xml:space="preserve">757.937194824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766.18115234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">768.068176269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">771.445190429688</t>
+    <t xml:space="preserve">757.937255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766.181091308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">768.068237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">771.445251464844</t>
   </si>
   <si>
     <t xml:space="preserve">784.555969238281</t>
@@ -4916,10 +4916,10 @@
     <t xml:space="preserve">785.052551269531</t>
   </si>
   <si>
-    <t xml:space="preserve">775.914794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">796.176696777344</t>
+    <t xml:space="preserve">775.914855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">796.1767578125</t>
   </si>
   <si>
     <t xml:space="preserve">842.759460449219</t>
@@ -4928,7 +4928,7 @@
     <t xml:space="preserve">843.752685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">834.813598632812</t>
+    <t xml:space="preserve">834.813659667969</t>
   </si>
   <si>
     <t xml:space="preserve">833.025756835938</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">849.839111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">836.903930664062</t>
+    <t xml:space="preserve">836.903991699219</t>
   </si>
   <si>
     <t xml:space="preserve">852.426208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">863.96826171875</t>
+    <t xml:space="preserve">863.968322753906</t>
   </si>
   <si>
     <t xml:space="preserve">882.276489257812</t>
@@ -4982,13 +4982,13 @@
     <t xml:space="preserve">846.456115722656</t>
   </si>
   <si>
-    <t xml:space="preserve">849.043151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">797.700561523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">774.914733886719</t>
+    <t xml:space="preserve">849.043090820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">797.700500488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">774.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">745.064392089844</t>
@@ -5000,10 +5000,10 @@
     <t xml:space="preserve">734.517333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">740.785949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">749.143981933594</t>
+    <t xml:space="preserve">740.785888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">749.14404296875</t>
   </si>
   <si>
     <t xml:space="preserve">743.969909667969</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">774.21826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">787.053955078125</t>
+    <t xml:space="preserve">787.053894042969</t>
   </si>
   <si>
     <t xml:space="preserve">770.63623046875</t>
@@ -5036,13 +5036,13 @@
     <t xml:space="preserve">753.322998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">742.178894042969</t>
+    <t xml:space="preserve">742.178955078125</t>
   </si>
   <si>
     <t xml:space="preserve">718.497619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">679.891235351562</t>
+    <t xml:space="preserve">679.891174316406</t>
   </si>
   <si>
     <t xml:space="preserve">650.836853027344</t>
@@ -5054,7 +5054,7 @@
     <t xml:space="preserve">625.961608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">631.633117675781</t>
+    <t xml:space="preserve">631.633178710938</t>
   </si>
   <si>
     <t xml:space="preserve">630.837158203125</t>
@@ -5063,7 +5063,7 @@
     <t xml:space="preserve">655.612976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">669.443603515625</t>
+    <t xml:space="preserve">669.443542480469</t>
   </si>
   <si>
     <t xml:space="preserve">654.418884277344</t>
@@ -5075,7 +5075,7 @@
     <t xml:space="preserve">711.134582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">720.089660644531</t>
+    <t xml:space="preserve">720.089721679688</t>
   </si>
   <si>
     <t xml:space="preserve">743.074401855469</t>
@@ -5084,7 +5084,7 @@
     <t xml:space="preserve">758.397583007812</t>
   </si>
   <si>
-    <t xml:space="preserve">760.188598632812</t>
+    <t xml:space="preserve">760.188659667969</t>
   </si>
   <si>
     <t xml:space="preserve">774.516784667969</t>
@@ -5093,10 +5093,10 @@
     <t xml:space="preserve">784.765441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">721.184143066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">718.796142578125</t>
+    <t xml:space="preserve">721.184204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">718.796203613281</t>
   </si>
   <si>
     <t xml:space="preserve">697.204406738281</t>
@@ -5105,16 +5105,16 @@
     <t xml:space="preserve">680.289245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">657.901489257812</t>
+    <t xml:space="preserve">657.901428222656</t>
   </si>
   <si>
     <t xml:space="preserve">665.563110351562</t>
   </si>
   <si>
-    <t xml:space="preserve">672.528137207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">668.747009277344</t>
+    <t xml:space="preserve">672.528198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">668.7470703125</t>
   </si>
   <si>
     <t xml:space="preserve">643.274780273438</t>
@@ -5445,6 +5445,9 @@
   </si>
   <si>
     <t xml:space="preserve">705.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.799987792969</t>
   </si>
 </sst>
 </file>
@@ -70731,7 +70734,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45957.6913773148</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>1846</v>
@@ -70752,6 +70755,32 @@
         <v>1810</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45958.6915856482</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>1767</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>712</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>700</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>708.200012207031</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>704.799987792969</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1811</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="1812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="1813">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3028831481934</t>
+    <t xml:space="preserve">38.3028755187988</t>
   </si>
   <si>
     <t xml:space="preserve">LLY.DE</t>
@@ -47,43 +47,43 @@
     <t xml:space="preserve">38.7578315734863</t>
   </si>
   <si>
-    <t xml:space="preserve">61.6800727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1175117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5549507141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4298477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9923858642578</t>
+    <t xml:space="preserve">61.680046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1175270080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5549545288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4298515319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9924201965332</t>
   </si>
   <si>
     <t xml:space="preserve">61.2426109313965</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8051567077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3677024841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9302711486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0230026245117</t>
+    <t xml:space="preserve">60.8051795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3677253723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9302673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0229988098145</t>
   </si>
   <si>
     <t xml:space="preserve">57.5943031311035</t>
   </si>
   <si>
-    <t xml:space="preserve">58.1717262268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8681449890137</t>
+    <t xml:space="preserve">58.1717185974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8681373596191</t>
   </si>
   <si>
     <t xml:space="preserve">54.7071533203125</t>
@@ -92,121 +92,121 @@
     <t xml:space="preserve">55.5907859802246</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3309440612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3598022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0159759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2212753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.804012298584</t>
+    <t xml:space="preserve">54.3309478759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3598175048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.015983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.221263885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8039970397949</t>
   </si>
   <si>
     <t xml:space="preserve">56.3226661682129</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4815902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.278507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4021110534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0289993286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5322914123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.596363067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4662055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2719650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5721549987793</t>
+    <t xml:space="preserve">56.4815826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2785224914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4021224975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0290069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5322875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5963592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4662094116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2719612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5721664428711</t>
   </si>
   <si>
     <t xml:space="preserve">55.1218605041504</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9276161193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9717597961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6405220031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2167091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5787200927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0754356384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8082733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0312881469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4286231994629</t>
+    <t xml:space="preserve">54.927619934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.971752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6405143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2167053222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5787086486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0754280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8082695007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0312805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4286155700684</t>
   </si>
   <si>
     <t xml:space="preserve">56.2961769104004</t>
   </si>
   <si>
-    <t xml:space="preserve">55.890022277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4861450195312</t>
+    <t xml:space="preserve">55.8900260925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4861488342285</t>
   </si>
   <si>
     <t xml:space="preserve">53.2323760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9034004211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.113037109375</t>
+    <t xml:space="preserve">53.9034042358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1130409240723</t>
   </si>
   <si>
     <t xml:space="preserve">55.3690910339355</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6251449584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9230575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8811874389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5191879272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7641372680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1019134521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.693489074707</t>
+    <t xml:space="preserve">55.6251373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9230499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8811950683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5191764831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7641334533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1019248962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6935005187988</t>
   </si>
   <si>
     <t xml:space="preserve">57.5057907104492</t>
@@ -218,16 +218,16 @@
     <t xml:space="preserve">56.9936981201172</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5433959960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9495544433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4793090820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9119567871094</t>
+    <t xml:space="preserve">56.543399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9495429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4793167114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9119491577148</t>
   </si>
   <si>
     <t xml:space="preserve">58.5829849243164</t>
@@ -236,139 +236,139 @@
     <t xml:space="preserve">59.9162178039551</t>
   </si>
   <si>
-    <t xml:space="preserve">60.3665046691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1899185180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3622550964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6559028625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6294136047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.627124786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.733081817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5166282653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0552101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5231742858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4452781677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7212028503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2997817993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8872947692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5134544372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2433280944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2077255249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.394660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9376258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4093780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1571273803711</t>
+    <t xml:space="preserve">60.3665084838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1899261474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3622436523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6558990478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6294021606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6271286010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7330856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5166168212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0552177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5231704711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4452896118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7212295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2998008728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8872833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5134391784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2433319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2077369689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3946533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9376220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4093933105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1571197509766</t>
   </si>
   <si>
     <t xml:space="preserve">64.5696105957031</t>
   </si>
   <si>
-    <t xml:space="preserve">64.6586151123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2105178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2550277709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7979965209961</t>
+    <t xml:space="preserve">64.6586303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2105026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.254997253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7979888916016</t>
   </si>
   <si>
     <t xml:space="preserve">66.1006393432617</t>
   </si>
   <si>
-    <t xml:space="preserve">65.6911773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4967498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7281646728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8335952758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9582061767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1615676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3039703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5220642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3320617675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2608489990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8202362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2564163208008</t>
+    <t xml:space="preserve">65.6911849975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4967346191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7281799316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8335876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9582214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1615524291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3039855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5220336914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3320465087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.260871887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8202438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2564086914062</t>
   </si>
   <si>
     <t xml:space="preserve">66.5189895629883</t>
   </si>
   <si>
-    <t xml:space="preserve">66.7860260009766</t>
+    <t xml:space="preserve">66.786003112793</t>
   </si>
   <si>
     <t xml:space="preserve">66.3988189697266</t>
   </si>
   <si>
-    <t xml:space="preserve">67.3557052612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1212387084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1657257080078</t>
+    <t xml:space="preserve">67.3557357788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1212005615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1657333374023</t>
   </si>
   <si>
     <t xml:space="preserve">68.1568145751953</t>
@@ -377,214 +377,214 @@
     <t xml:space="preserve">68.6018676757812</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3971633911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5960540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1448745727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6194076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.5273208618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.622200012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5153427124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9306716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6961822509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2124481201172</t>
+    <t xml:space="preserve">68.3971481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5960464477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1448440551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6194152832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.52734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6221923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5153656005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6961975097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2124633789062</t>
   </si>
   <si>
     <t xml:space="preserve">76.8355255126953</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4733810424805</t>
+    <t xml:space="preserve">78.4733734130859</t>
   </si>
   <si>
     <t xml:space="preserve">78.9362335205078</t>
   </si>
   <si>
-    <t xml:space="preserve">78.562385559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7136840820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8352432250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8441467285156</t>
+    <t xml:space="preserve">78.5623550415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.7136993408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8352508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8441619873047</t>
   </si>
   <si>
     <t xml:space="preserve">80.8048324584961</t>
   </si>
   <si>
-    <t xml:space="preserve">81.4318542480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9513854980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5694351196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7844161987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4587173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3691482543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9033660888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6883773803711</t>
+    <t xml:space="preserve">81.4318771362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9514007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5694198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7844085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4587478637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3691635131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9033889770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6883926391602</t>
   </si>
   <si>
     <t xml:space="preserve">80.6346282958984</t>
   </si>
   <si>
-    <t xml:space="preserve">80.5809020996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.984001159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8496170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2168502807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0914764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2527084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2853164672852</t>
+    <t xml:space="preserve">80.5809097290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9840087890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8496246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2168426513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0914611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2527008056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2853088378906</t>
   </si>
   <si>
     <t xml:space="preserve">80.3211364746094</t>
   </si>
   <si>
-    <t xml:space="preserve">82.4888381958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8618087768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7811889648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3960189819336</t>
+    <t xml:space="preserve">82.4888305664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8617935180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7811965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3960266113281</t>
   </si>
   <si>
     <t xml:space="preserve">81.6110153198242</t>
   </si>
   <si>
-    <t xml:space="preserve">81.9782485961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3569793701172</t>
+    <t xml:space="preserve">81.9782333374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3569564819336</t>
   </si>
   <si>
     <t xml:space="preserve">81.1810302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">80.6077728271484</t>
+    <t xml:space="preserve">80.6077880859375</t>
   </si>
   <si>
     <t xml:space="preserve">81.0735473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">82.2379989624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1158447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2949981689453</t>
+    <t xml:space="preserve">82.2380142211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.115837097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2949829101562</t>
   </si>
   <si>
     <t xml:space="preserve">87.2810440063477</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2247848510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5057373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7980651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1531448364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2477035522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.453742980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8478622436523</t>
+    <t xml:space="preserve">89.2248077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5057067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7980804443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1531524658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2477111816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4537582397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8478469848633</t>
   </si>
   <si>
     <t xml:space="preserve">85.3014450073242</t>
   </si>
   <si>
-    <t xml:space="preserve">86.8958587646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3200988769531</t>
+    <t xml:space="preserve">86.895881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3200912475586</t>
   </si>
   <si>
     <t xml:space="preserve">87.9976501464844</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7378540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3551864624023</t>
+    <t xml:space="preserve">87.7378692626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3552093505859</t>
   </si>
   <si>
     <t xml:space="preserve">86.7435913085938</t>
   </si>
   <si>
-    <t xml:space="preserve">85.1402359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2681198120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2029342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0660552978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.817756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6980895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.128791809082</t>
+    <t xml:space="preserve">85.1402282714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2681045532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2029113769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0660705566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8177719116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6980819702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1287612915039</t>
   </si>
   <si>
     <t xml:space="preserve">83.447265625</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">82.972541809082</t>
   </si>
   <si>
-    <t xml:space="preserve">86.2061614990234</t>
+    <t xml:space="preserve">86.2061538696289</t>
   </si>
   <si>
     <t xml:space="preserve">87.7289199829102</t>
@@ -602,100 +602,100 @@
     <t xml:space="preserve">90.2369995117188</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3591690063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9741592407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7129364013672</t>
+    <t xml:space="preserve">89.3591613769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9741516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7129135131836</t>
   </si>
   <si>
     <t xml:space="preserve">89.5325775146484</t>
   </si>
   <si>
-    <t xml:space="preserve">90.5685119628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9740524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3704986572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1991806030273</t>
+    <t xml:space="preserve">90.5685195922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9740753173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3705215454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1991577148438</t>
   </si>
   <si>
     <t xml:space="preserve">88.8839797973633</t>
   </si>
   <si>
-    <t xml:space="preserve">90.406364440918</t>
+    <t xml:space="preserve">90.4063720703125</t>
   </si>
   <si>
     <t xml:space="preserve">91.2171020507812</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7665252685547</t>
+    <t xml:space="preserve">92.7665328979492</t>
   </si>
   <si>
     <t xml:space="preserve">93.8475036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0456924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1541290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6046371459961</t>
+    <t xml:space="preserve">94.0457000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1541519165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6046295166016</t>
   </si>
   <si>
     <t xml:space="preserve">88.388542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3161926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7487640380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8930740356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8933563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8931732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0644073486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2627639770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7760543823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5056457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3252868652344</t>
+    <t xml:space="preserve">91.3162155151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7487716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8930816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8933410644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8931503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0644226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2627792358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7760620117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5056381225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3253021240234</t>
   </si>
   <si>
     <t xml:space="preserve">89.0191116333008</t>
   </si>
   <si>
-    <t xml:space="preserve">89.1812362670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6315689086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6135406494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4513397216797</t>
+    <t xml:space="preserve">89.1812515258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6315841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6135635375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4513168334961</t>
   </si>
   <si>
     <t xml:space="preserve">90.8747787475586</t>
@@ -704,70 +704,70 @@
     <t xml:space="preserve">90.6676025390625</t>
   </si>
   <si>
-    <t xml:space="preserve">89.9919891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7217483520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3521423339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3700866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6675186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5863571166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.424186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0998229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6674423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6585845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.0820922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7666091918945</t>
+    <t xml:space="preserve">89.9920043945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7217559814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3521270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3700637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6675109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5863647460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4242095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0998306274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6674346923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6586151123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0820693969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7666168212891</t>
   </si>
   <si>
     <t xml:space="preserve">93.5051879882812</t>
   </si>
   <si>
-    <t xml:space="preserve">94.4150238037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.739387512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6851959228516</t>
+    <t xml:space="preserve">94.4150009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7394180297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.685188293457</t>
   </si>
   <si>
     <t xml:space="preserve">94.0997314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4961929321289</t>
+    <t xml:space="preserve">93.4962005615234</t>
   </si>
   <si>
     <t xml:space="preserve">92.604377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">93.9645919799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3969879150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1717987060547</t>
+    <t xml:space="preserve">93.9646148681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3970031738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1717910766602</t>
   </si>
   <si>
     <t xml:space="preserve">96.3154678344727</t>
@@ -776,22 +776,22 @@
     <t xml:space="preserve">97.6569671630859</t>
   </si>
   <si>
-    <t xml:space="preserve">99.0891036987305</t>
+    <t xml:space="preserve">99.0890960693359</t>
   </si>
   <si>
     <t xml:space="preserve">97.6751098632812</t>
   </si>
   <si>
-    <t xml:space="preserve">97.7385101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2370529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0437698364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2522430419922</t>
+    <t xml:space="preserve">97.7385406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2370681762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0437850952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2522506713867</t>
   </si>
   <si>
     <t xml:space="preserve">99.3247604370117</t>
@@ -800,70 +800,70 @@
     <t xml:space="preserve">99.6963882446289</t>
   </si>
   <si>
-    <t xml:space="preserve">100.52123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.518257141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.475898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.189018249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.318878173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.234359741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.457778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9078063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4969787597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1615982055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.865646362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.034927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.524391174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.823516845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.101554870605</t>
+    <t xml:space="preserve">100.521224975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.518264770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.475914001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.189025878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.318855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.234344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.457763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9078216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4969711303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1616058349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5966873168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.865669250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.034942626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.524398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.823539733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.101547241211</t>
   </si>
   <si>
     <t xml:space="preserve">105.588081359863</t>
   </si>
   <si>
-    <t xml:space="preserve">104.445991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.86296081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.300956726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.270843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.352416992188</t>
+    <t xml:space="preserve">104.446022033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.862968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.300971984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270858764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.352432250977</t>
   </si>
   <si>
     <t xml:space="preserve">103.494270324707</t>
@@ -872,25 +872,25 @@
     <t xml:space="preserve">101.346046447754</t>
   </si>
   <si>
-    <t xml:space="preserve">102.207160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.880844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.787269592285</t>
+    <t xml:space="preserve">102.207153320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.78727722168</t>
   </si>
   <si>
     <t xml:space="preserve">100.068023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">99.0165939331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8862609863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4722900390625</t>
+    <t xml:space="preserve">99.0165786743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8862686157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.472282409668</t>
   </si>
   <si>
     <t xml:space="preserve">94.7020568847656</t>
@@ -899,91 +899,91 @@
     <t xml:space="preserve">95.7716293334961</t>
   </si>
   <si>
-    <t xml:space="preserve">95.9347763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7868118286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0587387084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5751571655273</t>
+    <t xml:space="preserve">95.9347686767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7868270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.058723449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5751419067383</t>
   </si>
   <si>
     <t xml:space="preserve">94.9739685058594</t>
   </si>
   <si>
-    <t xml:space="preserve">93.9044189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7775115966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0494232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0342559814453</t>
+    <t xml:space="preserve">93.904426574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7775039672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0494384765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0342636108398</t>
   </si>
   <si>
     <t xml:space="preserve">92.3816375732422</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4360122680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1430358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3061676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7552490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6242065429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.8829498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4815902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3904037475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.0802459716797</t>
+    <t xml:space="preserve">92.4360275268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1430206298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3061828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.755241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6241989135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.882942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4815826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3903961181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0802536010742</t>
   </si>
   <si>
     <t xml:space="preserve">95.1349945068359</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4086380004883</t>
+    <t xml:space="preserve">95.4086303710938</t>
   </si>
   <si>
     <t xml:space="preserve">94.2228698730469</t>
   </si>
   <si>
-    <t xml:space="preserve">95.9376449584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9890594482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5727996826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6324234008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5628051757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0918121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5834732055664</t>
+    <t xml:space="preserve">95.9376525878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9890670776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5728073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6324157714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5628128051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0918350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5834808349609</t>
   </si>
   <si>
     <t xml:space="preserve">91.2128448486328</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">92.7999267578125</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4201889038086</t>
+    <t xml:space="preserve">93.4201965332031</t>
   </si>
   <si>
     <t xml:space="preserve">93.4931564331055</t>
@@ -1001,55 +1001,55 @@
     <t xml:space="preserve">92.9094085693359</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6357498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3107223510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2609024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8720092773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3098449707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3405380249023</t>
+    <t xml:space="preserve">92.6357574462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3107376098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2608871459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8720016479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3098220825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3405303955078</t>
   </si>
   <si>
     <t xml:space="preserve">92.2709121704102</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3621292114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7567672729492</t>
+    <t xml:space="preserve">92.3621215820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7567825317383</t>
   </si>
   <si>
     <t xml:space="preserve">92.1249694824219</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3885879516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6521835327148</t>
+    <t xml:space="preserve">89.3885726928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.652214050293</t>
   </si>
   <si>
     <t xml:space="preserve">87.5643310546875</t>
   </si>
   <si>
-    <t xml:space="preserve">88.476448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0204010009766</t>
+    <t xml:space="preserve">88.4764633178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0203857421875</t>
   </si>
   <si>
     <t xml:space="preserve">87.50048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">87.3819046020508</t>
+    <t xml:space="preserve">87.3819122314453</t>
   </si>
   <si>
     <t xml:space="preserve">86.5244903564453</t>
@@ -1058,40 +1058,40 @@
     <t xml:space="preserve">86.9349594116211</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9474334716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3064956665039</t>
+    <t xml:space="preserve">87.9474029541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3065032958984</t>
   </si>
   <si>
     <t xml:space="preserve">89.3703384399414</t>
   </si>
   <si>
-    <t xml:space="preserve">88.9507369995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2243957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.118293762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.775016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3040466308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9176330566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5469970703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.498046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7452087402344</t>
+    <t xml:space="preserve">88.9507675170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2243804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1183090209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.775032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3040542602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.917610168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5469818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7452163696289</t>
   </si>
   <si>
     <t xml:space="preserve">91.7418746948242</t>
@@ -1100,40 +1100,40 @@
     <t xml:space="preserve">91.4317321777344</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0702285766602</t>
+    <t xml:space="preserve">92.0702362060547</t>
   </si>
   <si>
     <t xml:space="preserve">92.4236679077148</t>
   </si>
   <si>
-    <t xml:space="preserve">90.440803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7804565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7908706665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0478973388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.074836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4230422973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.9095916748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7541656494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8190002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6084976196289</t>
+    <t xml:space="preserve">90.4407958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7804489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7908782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0479202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0748138427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4230499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9095993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7541351318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8190078735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6084899902344</t>
   </si>
   <si>
     <t xml:space="preserve">94.8104553222656</t>
@@ -1142,193 +1142,193 @@
     <t xml:space="preserve">95.2878189086914</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0197372436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7712860107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6990737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9193801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0381164550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6800918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7443542480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9928283691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.93896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.701530456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4065551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6635589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4334564208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9940567016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4714050292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6354293823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9634399414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5044555664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4224319458008</t>
+    <t xml:space="preserve">92.0197448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7712783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6990432739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9194030761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0381011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6800994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7443695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9928207397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9389724731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7015075683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4065475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6635665893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4334716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9940490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4713897705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6354064941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9634552001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5044326782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4224243164062</t>
   </si>
   <si>
     <t xml:space="preserve">90.8814392089844</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3404159545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7969818115234</t>
+    <t xml:space="preserve">91.3404312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.796989440918</t>
   </si>
   <si>
     <t xml:space="preserve">88.5589141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">89.8165512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.203369140625</t>
+    <t xml:space="preserve">89.8165588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2033462524414</t>
   </si>
   <si>
     <t xml:space="preserve">90.6886596679688</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1396865844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7174377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0943908691406</t>
+    <t xml:space="preserve">93.1397094726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7174301147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0944061279297</t>
   </si>
   <si>
     <t xml:space="preserve">92.0932006835938</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8006744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.488525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0209579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1494979858398</t>
+    <t xml:space="preserve">93.8006591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4885330200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0209884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1495056152344</t>
   </si>
   <si>
     <t xml:space="preserve">94.4616165161133</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4500579833984</t>
+    <t xml:space="preserve">93.4500732421875</t>
   </si>
   <si>
     <t xml:space="preserve">94.650993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7433624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4823913574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.0920944213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6856307983398</t>
+    <t xml:space="preserve">94.7433700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4824142456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.0921020507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6856231689453</t>
   </si>
   <si>
     <t xml:space="preserve">97.0158615112305</t>
   </si>
   <si>
-    <t xml:space="preserve">98.5493545532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8634262084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.383056640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1267242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4939422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.600158691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.9165954589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.359977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.212181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.78491973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.711013793945</t>
+    <t xml:space="preserve">98.5493774414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8634338378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3830795288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1267318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4939346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.600173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.9165573120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.359970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.21216583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.784927368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.711029052734</t>
   </si>
   <si>
     <t xml:space="preserve">101.727180480957</t>
   </si>
   <si>
-    <t xml:space="preserve">104.202911376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.269912719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.008911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.429229736328</t>
+    <t xml:space="preserve">104.202926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.269905090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.008918762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.429237365723</t>
   </si>
   <si>
     <t xml:space="preserve">109.653259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">108.988136291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.06436920166</t>
+    <t xml:space="preserve">108.988143920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.064353942871</t>
   </si>
   <si>
     <t xml:space="preserve">108.34147644043</t>
   </si>
   <si>
-    <t xml:space="preserve">109.265258789062</t>
+    <t xml:space="preserve">109.265251159668</t>
   </si>
   <si>
     <t xml:space="preserve">109.135932922363</t>
@@ -1337,46 +1337,46 @@
     <t xml:space="preserve">109.819526672363</t>
   </si>
   <si>
-    <t xml:space="preserve">109.893432617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.886497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.105880737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.269874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.454605102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.507720947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.061996459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.376098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.710990905762</t>
+    <t xml:space="preserve">109.893424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.886489868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.105888366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.269866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.454635620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.50772857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.062019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.376083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.710983276367</t>
   </si>
   <si>
     <t xml:space="preserve">117.486953735352</t>
   </si>
   <si>
-    <t xml:space="preserve">117.394561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.320693969727</t>
+    <t xml:space="preserve">117.394554138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.320655822754</t>
   </si>
   <si>
     <t xml:space="preserve">117.413040161133</t>
   </si>
   <si>
-    <t xml:space="preserve">116.32299041748</t>
+    <t xml:space="preserve">116.322982788086</t>
   </si>
   <si>
     <t xml:space="preserve">118.115127563477</t>
@@ -1385,67 +1385,67 @@
     <t xml:space="preserve">120.092041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">117.13591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.339149475098</t>
+    <t xml:space="preserve">117.135917663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.339141845703</t>
   </si>
   <si>
     <t xml:space="preserve">119.611640930176</t>
   </si>
   <si>
-    <t xml:space="preserve">122.62321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.156669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473098754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.274467468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.292945861816</t>
+    <t xml:space="preserve">122.623229980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.156677246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473052978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.274459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.292961120605</t>
   </si>
   <si>
     <t xml:space="preserve">122.586242675781</t>
   </si>
   <si>
-    <t xml:space="preserve">122.549087524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.24853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.616851806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.229957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.270393371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.787322998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.780776977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.049606323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.009178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.017890930176</t>
+    <t xml:space="preserve">122.549072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.248527526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.616844177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.229949951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.270385742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.78736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.780769348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.04963684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.009170532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.01789855957</t>
   </si>
   <si>
     <t xml:space="preserve">104.620056152344</t>
   </si>
   <si>
-    <t xml:space="preserve">108.05721282959</t>
+    <t xml:space="preserve">108.057220458984</t>
   </si>
   <si>
     <t xml:space="preserve">112.441947937012</t>
@@ -1454,238 +1454,238 @@
     <t xml:space="preserve">111.104232788086</t>
   </si>
   <si>
-    <t xml:space="preserve">116.306434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.507514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.881278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.937026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.135948181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.700942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.565422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.609161376953</t>
+    <t xml:space="preserve">116.306442260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.507537841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.881294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.937019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.135963439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.70093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.565437316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.609169006348</t>
   </si>
   <si>
     <t xml:space="preserve">117.123916625977</t>
   </si>
   <si>
-    <t xml:space="preserve">114.597129821777</t>
+    <t xml:space="preserve">114.597137451172</t>
   </si>
   <si>
     <t xml:space="preserve">119.056190490723</t>
   </si>
   <si>
-    <t xml:space="preserve">116.120651245117</t>
+    <t xml:space="preserve">116.120635986328</t>
   </si>
   <si>
     <t xml:space="preserve">104.768699645996</t>
   </si>
   <si>
-    <t xml:space="preserve">105.270324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.771957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.844116210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.680206298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.365432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.798233032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.694435119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.300979614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.552337646484</t>
+    <t xml:space="preserve">105.270347595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.771987915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.844123840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.680213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.365447998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.798225402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.694427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.300971984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.552383422852</t>
   </si>
   <si>
     <t xml:space="preserve">126.339248657227</t>
   </si>
   <si>
-    <t xml:space="preserve">128.661712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.913070678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.44856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.628921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.377532958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.235488891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.285751342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.679214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.218002319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.557876586914</t>
+    <t xml:space="preserve">128.661666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.913116455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.448577880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.628875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.377548217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.235458374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.285781860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.67919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.217987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.557907104492</t>
   </si>
   <si>
     <t xml:space="preserve">133.232162475586</t>
   </si>
   <si>
-    <t xml:space="preserve">132.117446899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.36767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.272613525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.405990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.492279052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.154571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.183013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.263885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.833297729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.889297485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.347763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.561553955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.050903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.911773681641</t>
+    <t xml:space="preserve">132.117416381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.367706298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.27262878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.405960083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.492248535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.154602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.183029174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.263870239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.833236694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.88932800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.347778320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.561569213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.050888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.911804199219</t>
   </si>
   <si>
     <t xml:space="preserve">128.942657470703</t>
   </si>
   <si>
-    <t xml:space="preserve">129.689590454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.399215698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.34700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.771896362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.766227722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.560737609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.589775085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.954833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.180809020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.002464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.873664855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.143478393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.554313659668</t>
+    <t xml:space="preserve">129.689559936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.399230957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.346977233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.77188873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.766159057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.560791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.589736938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.95482635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.180839538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.002471923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.873672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.143501281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.554298400879</t>
   </si>
   <si>
     <t xml:space="preserve">121.84659576416</t>
   </si>
   <si>
-    <t xml:space="preserve">120.016555786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.972732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.142364501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.077911376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.011642456055</t>
+    <t xml:space="preserve">120.016563415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.972724914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.142349243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.077941894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.011672973633</t>
   </si>
   <si>
     <t xml:space="preserve">131.650360107422</t>
   </si>
   <si>
-    <t xml:space="preserve">132.32258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.984573364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.45524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.621398925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.48876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.619491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.412170410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.37483215332</t>
+    <t xml:space="preserve">132.322647094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.984588623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.455215454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.621383666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.488754272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.619476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.412231445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.374847412109</t>
   </si>
   <si>
     <t xml:space="preserve">135.441131591797</t>
@@ -1694,7 +1694,7 @@
     <t xml:space="preserve">138.484970092773</t>
   </si>
   <si>
-    <t xml:space="preserve">138.055480957031</t>
+    <t xml:space="preserve">138.05549621582</t>
   </si>
   <si>
     <t xml:space="preserve">138.148864746094</t>
@@ -1703,22 +1703,22 @@
     <t xml:space="preserve">136.225463867188</t>
   </si>
   <si>
-    <t xml:space="preserve">135.123672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.430801391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.20866394043</t>
+    <t xml:space="preserve">135.123687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.430847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.208679199219</t>
   </si>
   <si>
     <t xml:space="preserve">135.179672241211</t>
   </si>
   <si>
-    <t xml:space="preserve">133.125564575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.833267211914</t>
+    <t xml:space="preserve">133.125579833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.833282470703</t>
   </si>
   <si>
     <t xml:space="preserve">135.795928955078</t>
@@ -1727,67 +1727,67 @@
     <t xml:space="preserve">131.239547729492</t>
   </si>
   <si>
-    <t xml:space="preserve">127.355354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.448745727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.793273925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.334037780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.802780151367</t>
+    <t xml:space="preserve">127.355361938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.448753356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.793228149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.334007263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.802795410156</t>
   </si>
   <si>
     <t xml:space="preserve">121.47314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">122.855003356934</t>
+    <t xml:space="preserve">122.854988098145</t>
   </si>
   <si>
     <t xml:space="preserve">121.155670166016</t>
   </si>
   <si>
-    <t xml:space="preserve">119.717781066895</t>
+    <t xml:space="preserve">119.717803955078</t>
   </si>
   <si>
     <t xml:space="preserve">120.80086517334</t>
   </si>
   <si>
-    <t xml:space="preserve">120.87557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.736457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.221984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.245323181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.73365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.409782409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.578842163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.480369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.071739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.174758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.06209564209</t>
+    <t xml:space="preserve">120.875549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.736465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.221977233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.245338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.733657836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.409812927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.578834533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.480346679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.071731567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.174774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.062088012695</t>
   </si>
   <si>
     <t xml:space="preserve">119.207763671875</t>
@@ -1799,37 +1799,37 @@
     <t xml:space="preserve">119.170211791992</t>
   </si>
   <si>
-    <t xml:space="preserve">117.479835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.44686126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.05241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.832122802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.30167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.099662780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.625526428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.799140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.686950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.59253692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.554977416992</t>
+    <t xml:space="preserve">117.479827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.446846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.052429199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.832130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.301666259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.099655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.625518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.799133300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.686973571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.592544555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.554969787598</t>
   </si>
   <si>
     <t xml:space="preserve">119.639755249023</t>
@@ -1838,73 +1838,73 @@
     <t xml:space="preserve">120.710311889648</t>
   </si>
   <si>
-    <t xml:space="preserve">120.729072570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.611831665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.597625732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.334663391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.583404541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.785438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.193557739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.709785461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.97730255127</t>
+    <t xml:space="preserve">120.729095458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.611824035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.597618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.334671020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.583389282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.785430908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.193550109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.709800720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.977279663086</t>
   </si>
   <si>
     <t xml:space="preserve">116.747367858887</t>
   </si>
   <si>
-    <t xml:space="preserve">116.108779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.424026489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.335159301758</t>
+    <t xml:space="preserve">116.108772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.424018859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.335166931152</t>
   </si>
   <si>
     <t xml:space="preserve">123.546340942383</t>
   </si>
   <si>
-    <t xml:space="preserve">122.231620788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.869705200195</t>
+    <t xml:space="preserve">122.231636047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.869689941406</t>
   </si>
   <si>
     <t xml:space="preserve">117.06665802002</t>
   </si>
   <si>
-    <t xml:space="preserve">117.348358154297</t>
+    <t xml:space="preserve">117.34838104248</t>
   </si>
   <si>
     <t xml:space="preserve">115.150917053223</t>
   </si>
   <si>
-    <t xml:space="preserve">113.122482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.615379333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.93921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.347846984863</t>
+    <t xml:space="preserve">113.122467041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.615371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.939224243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.347854614258</t>
   </si>
   <si>
     <t xml:space="preserve">111.563591003418</t>
@@ -1913,16 +1913,16 @@
     <t xml:space="preserve">106.229568481445</t>
   </si>
   <si>
-    <t xml:space="preserve">105.835151672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.53010559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.666122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.684906005859</t>
+    <t xml:space="preserve">105.835166931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.530082702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.666130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.684913635254</t>
   </si>
   <si>
     <t xml:space="preserve">106.511306762695</t>
@@ -1931,70 +1931,70 @@
     <t xml:space="preserve">118.13720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">116.221488952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.202690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.573249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.104209899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.319931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.939094543457</t>
+    <t xml:space="preserve">116.221481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.202659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.5732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.104225158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.319946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.939117431641</t>
   </si>
   <si>
     <t xml:space="preserve">113.97834777832</t>
   </si>
   <si>
-    <t xml:space="preserve">113.354789733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.221061706543</t>
+    <t xml:space="preserve">113.354804992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.221076965332</t>
   </si>
   <si>
     <t xml:space="preserve">112.504486083984</t>
   </si>
   <si>
-    <t xml:space="preserve">112.164367675781</t>
+    <t xml:space="preserve">112.164375305176</t>
   </si>
   <si>
     <t xml:space="preserve">116.359199523926</t>
   </si>
   <si>
-    <t xml:space="preserve">112.901306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.338829040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.449264526367</t>
+    <t xml:space="preserve">112.901290893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.338821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.449279785156</t>
   </si>
   <si>
     <t xml:space="preserve">114.318473815918</t>
   </si>
   <si>
-    <t xml:space="preserve">115.830123901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.828666687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.846084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.447814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.469657897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.151351928711</t>
+    <t xml:space="preserve">115.830108642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.828643798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.846076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.447807312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.469650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.151344299316</t>
   </si>
   <si>
     <t xml:space="preserve">122.65145111084</t>
@@ -2003,79 +2003,79 @@
     <t xml:space="preserve">123.841850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">125.353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.843353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.411682128906</t>
+    <t xml:space="preserve">125.353507995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.843322753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.411666870117</t>
   </si>
   <si>
     <t xml:space="preserve">133.327453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">131.948059082031</t>
+    <t xml:space="preserve">131.948104858398</t>
   </si>
   <si>
     <t xml:space="preserve">131.267837524414</t>
   </si>
   <si>
-    <t xml:space="preserve">129.737289428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.96403503418</t>
+    <t xml:space="preserve">129.737319946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.964019775391</t>
   </si>
   <si>
     <t xml:space="preserve">129.416076660156</t>
   </si>
   <si>
-    <t xml:space="preserve">127.583190917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.471267700195</t>
+    <t xml:space="preserve">127.583183288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.471282958984</t>
   </si>
   <si>
     <t xml:space="preserve">129.113754272461</t>
   </si>
   <si>
-    <t xml:space="preserve">126.827407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.392784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.904418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.016296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.118316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.978729248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.645935058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.119827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.047149658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.839233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.714340209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.833618164062</t>
+    <t xml:space="preserve">126.827392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.392761230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.904411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.016311645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.603546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.118347167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.978668212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.645965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.11979675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.047164916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.839309692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.714370727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.833633422852</t>
   </si>
   <si>
     <t xml:space="preserve">155.076309204102</t>
@@ -2084,133 +2084,133 @@
     <t xml:space="preserve">158.760986328125</t>
   </si>
   <si>
-    <t xml:space="preserve">164.032836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.996505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.992126464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.125823974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.349655151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.804580688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.72021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.962951660156</t>
+    <t xml:space="preserve">164.032821655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.996490478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.992111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.125854492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.349670410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.804641723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.720260620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.962936401367</t>
   </si>
   <si>
     <t xml:space="preserve">158.137390136719</t>
   </si>
   <si>
-    <t xml:space="preserve">158.704299926758</t>
+    <t xml:space="preserve">158.704284667969</t>
   </si>
   <si>
     <t xml:space="preserve">160.461578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">156.814727783203</t>
+    <t xml:space="preserve">156.814697265625</t>
   </si>
   <si>
     <t xml:space="preserve">159.157745361328</t>
   </si>
   <si>
-    <t xml:space="preserve">158.008758544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.819549560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.560836791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.794006347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.161392211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.831985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.856887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.932174682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.20524597168</t>
+    <t xml:space="preserve">158.008773803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.819519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.560806274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.794036865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.161407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.831954956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.856872558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.932189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.205276489258</t>
   </si>
   <si>
     <t xml:space="preserve">159.964889526367</t>
   </si>
   <si>
-    <t xml:space="preserve">157.970794677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.907913208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.376800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.756637573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.958358764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.338165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.617156982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.884338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.409561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.890243530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.661697387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.326370239258</t>
+    <t xml:space="preserve">157.970809936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.907897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.376815795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.75666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.958374023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.338195800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.617126464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.884353637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.409545898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.890197753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.661682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.326385498047</t>
   </si>
   <si>
     <t xml:space="preserve">151.741592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">151.931549072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.082809448242</t>
+    <t xml:space="preserve">151.931533813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.082824707031</t>
   </si>
   <si>
     <t xml:space="preserve">147.183654785156</t>
   </si>
   <si>
-    <t xml:space="preserve">147.753402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.133255004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.462615966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.474456787109</t>
+    <t xml:space="preserve">147.753433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.133239746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.462631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.47444152832</t>
   </si>
   <si>
     <t xml:space="preserve">146.993759155273</t>
@@ -2219,13 +2219,13 @@
     <t xml:space="preserve">148.892913818359</t>
   </si>
   <si>
-    <t xml:space="preserve">150.602127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.792037963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.399780273438</t>
+    <t xml:space="preserve">150.602142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.792022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.399765014648</t>
   </si>
   <si>
     <t xml:space="preserve">151.456741333008</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">148.703002929688</t>
   </si>
   <si>
-    <t xml:space="preserve">145.284515380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.234069824219</t>
+    <t xml:space="preserve">145.284530639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.234115600586</t>
   </si>
   <si>
     <t xml:space="preserve">145.854248046875</t>
@@ -2246,82 +2246,82 @@
     <t xml:space="preserve">144.904708862305</t>
   </si>
   <si>
-    <t xml:space="preserve">146.42399597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.842468261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.412185668945</t>
+    <t xml:space="preserve">146.424011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.323150634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.84245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.412216186523</t>
   </si>
   <si>
     <t xml:space="preserve">149.652557373047</t>
   </si>
   <si>
-    <t xml:space="preserve">148.513046264648</t>
+    <t xml:space="preserve">148.513061523438</t>
   </si>
   <si>
     <t xml:space="preserve">146.803833007812</t>
   </si>
   <si>
-    <t xml:space="preserve">143.955139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.346755981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.486236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.575332641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.044143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.121475219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.691177368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.071014404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.836563110352</t>
+    <t xml:space="preserve">143.955108642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.346740722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.486251831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.575271606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.044174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.121444702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.691162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.071029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.83659362793</t>
   </si>
   <si>
     <t xml:space="preserve">153.693511962891</t>
   </si>
   <si>
-    <t xml:space="preserve">155.220947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.457244873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.929870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.979888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.175552368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.702926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.984619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.361785888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.748306274414</t>
+    <t xml:space="preserve">155.220932006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.457229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.92985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.979919433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.175537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.70295715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.984634399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.361801147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.748291015625</t>
   </si>
   <si>
     <t xml:space="preserve">157.225631713867</t>
@@ -2330,55 +2330,55 @@
     <t xml:space="preserve">154.839065551758</t>
   </si>
   <si>
-    <t xml:space="preserve">156.366485595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.803100585938</t>
+    <t xml:space="preserve">156.366500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.803070068359</t>
   </si>
   <si>
     <t xml:space="preserve">171.640365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">170.876663208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.076965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.000274658203</t>
+    <t xml:space="preserve">170.876678466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.07698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.000305175781</t>
   </si>
   <si>
     <t xml:space="preserve">176.365707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">177.749908447266</t>
+    <t xml:space="preserve">177.749923706055</t>
   </si>
   <si>
     <t xml:space="preserve">175.840667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">176.222534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.227188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.270233154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.038650512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.800033569336</t>
+    <t xml:space="preserve">176.222518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.22721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.270263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.038665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.799987792969</t>
   </si>
   <si>
     <t xml:space="preserve">174.265548706055</t>
   </si>
   <si>
-    <t xml:space="preserve">185.243667602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.52766418457</t>
+    <t xml:space="preserve">185.243682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.527740478516</t>
   </si>
   <si>
     <t xml:space="preserve">182.09342956543</t>
@@ -2387,70 +2387,70 @@
     <t xml:space="preserve">184.432250976562</t>
   </si>
   <si>
-    <t xml:space="preserve">185.291412353516</t>
+    <t xml:space="preserve">185.291397094727</t>
   </si>
   <si>
     <t xml:space="preserve">186.102828979492</t>
   </si>
   <si>
-    <t xml:space="preserve">187.773345947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.49169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.918960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.969024658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.775756835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.069183349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.6826171875</t>
+    <t xml:space="preserve">187.773391723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.491714477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.9189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.969039916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.775741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.069229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.682662963867</t>
   </si>
   <si>
     <t xml:space="preserve">190.446350097656</t>
   </si>
   <si>
-    <t xml:space="preserve">190.828170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.584854125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.677963256836</t>
+    <t xml:space="preserve">190.828201293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.584838867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.677947998047</t>
   </si>
   <si>
     <t xml:space="preserve">187.296112060547</t>
   </si>
   <si>
-    <t xml:space="preserve">191.591888427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.973754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.882965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.983123779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.415054321289</t>
+    <t xml:space="preserve">191.591873168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.973724365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.882949829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.983139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.415084838867</t>
   </si>
   <si>
     <t xml:space="preserve">196.269515991211</t>
   </si>
   <si>
-    <t xml:space="preserve">199.515228271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.319580078125</t>
+    <t xml:space="preserve">199.515213012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.319610595703</t>
   </si>
   <si>
     <t xml:space="preserve">196.842269897461</t>
@@ -2459,49 +2459,49 @@
     <t xml:space="preserve">197.987808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">207.152130126953</t>
+    <t xml:space="preserve">207.15217590332</t>
   </si>
   <si>
     <t xml:space="preserve">213.739013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">212.975311279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.929946899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.321182250977</t>
+    <t xml:space="preserve">212.975341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.929962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.321151733398</t>
   </si>
   <si>
     <t xml:space="preserve">218.703063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">217.366546630859</t>
+    <t xml:space="preserve">217.366592407227</t>
   </si>
   <si>
     <t xml:space="preserve">215.498092651367</t>
   </si>
   <si>
-    <t xml:space="preserve">218.564315795898</t>
+    <t xml:space="preserve">218.564331054688</t>
   </si>
   <si>
     <t xml:space="preserve">221.917999267578</t>
   </si>
   <si>
-    <t xml:space="preserve">223.930206298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.534729003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.067810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.205459594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.444061279297</t>
+    <t xml:space="preserve">223.930191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.534713745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.067840576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.205444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.444076538086</t>
   </si>
   <si>
     <t xml:space="preserve">214.156631469727</t>
@@ -2510,46 +2510,46 @@
     <t xml:space="preserve">213.294250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">212.048583984375</t>
+    <t xml:space="preserve">212.048614501953</t>
   </si>
   <si>
     <t xml:space="preserve">214.060775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">211.18620300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.736724853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.982345581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.269790649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.994567871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.461441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.970169067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.058944702148</t>
+    <t xml:space="preserve">211.186218261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.736694335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.982360839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.269805908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.994598388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.461486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.970153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.058959960938</t>
   </si>
   <si>
     <t xml:space="preserve">196.621627807617</t>
   </si>
   <si>
-    <t xml:space="preserve">191.447387695312</t>
+    <t xml:space="preserve">191.447418212891</t>
   </si>
   <si>
     <t xml:space="preserve">190.920394897461</t>
   </si>
   <si>
-    <t xml:space="preserve">191.495300292969</t>
+    <t xml:space="preserve">191.495315551758</t>
   </si>
   <si>
     <t xml:space="preserve">187.902084350586</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">189.531005859375</t>
   </si>
   <si>
-    <t xml:space="preserve">189.626846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.997924804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.632919311523</t>
+    <t xml:space="preserve">189.626815795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.997894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.632949829102</t>
   </si>
   <si>
     <t xml:space="preserve">190.537109375</t>
@@ -2576,43 +2576,43 @@
     <t xml:space="preserve">185.889862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">182.152908325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.572830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.651229858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.770568847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.410751342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.393356323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.237457275391</t>
+    <t xml:space="preserve">182.152862548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.572799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.651245117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.770538330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.410781860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.39338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.237426757812</t>
   </si>
   <si>
     <t xml:space="preserve">192.501403808594</t>
   </si>
   <si>
-    <t xml:space="preserve">193.172134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.525817871094</t>
+    <t xml:space="preserve">193.172149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.525833129883</t>
   </si>
   <si>
     <t xml:space="preserve">193.555419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">193.938690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">194.992721557617</t>
+    <t xml:space="preserve">193.938705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194.992706298828</t>
   </si>
   <si>
     <t xml:space="preserve">195.471786499023</t>
@@ -2627,151 +2627,151 @@
     <t xml:space="preserve">200.358596801758</t>
   </si>
   <si>
-    <t xml:space="preserve">198.538024902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.921356201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.987533569336</t>
+    <t xml:space="preserve">198.538040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.921340942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.987564086914</t>
   </si>
   <si>
     <t xml:space="preserve">202.849884033203</t>
   </si>
   <si>
-    <t xml:space="preserve">208.2158203125</t>
+    <t xml:space="preserve">208.215835571289</t>
   </si>
   <si>
     <t xml:space="preserve">207.832504272461</t>
   </si>
   <si>
-    <t xml:space="preserve">210.802947998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.353424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.006790161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.989410400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.593948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.977188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.90576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220.768173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.892791748047</t>
+    <t xml:space="preserve">210.802886962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.353393554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.006805419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.989395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.593887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.977203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.905792236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.768127441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.892761230469</t>
   </si>
   <si>
     <t xml:space="preserve">217.161651611328</t>
   </si>
   <si>
-    <t xml:space="preserve">219.277481079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.297134399414</t>
+    <t xml:space="preserve">219.277450561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.297103881836</t>
   </si>
   <si>
     <t xml:space="preserve">221.200942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">223.316757202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.663223266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.50910949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.182357788086</t>
+    <t xml:space="preserve">223.316787719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.66325378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.509124755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.182342529297</t>
   </si>
   <si>
     <t xml:space="preserve">227.067596435547</t>
   </si>
   <si>
-    <t xml:space="preserve">222.162673950195</t>
+    <t xml:space="preserve">222.162704467773</t>
   </si>
   <si>
     <t xml:space="preserve">212.064376831055</t>
   </si>
   <si>
-    <t xml:space="preserve">215.23811340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.198852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.756240844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.351837158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203.985763549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.313583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.640335083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.506988525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.929977416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.279586791992</t>
+    <t xml:space="preserve">215.238128662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.198791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.756195068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.351852416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203.985748291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.313598632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.640365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.507019042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.929946899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.279602050781</t>
   </si>
   <si>
     <t xml:space="preserve">237.646774291992</t>
   </si>
   <si>
-    <t xml:space="preserve">227.259963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">225.624969482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.567031860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">232.068664550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.819458007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.43473815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.530899047852</t>
+    <t xml:space="preserve">227.25993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">225.625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.567047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.068649291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.819442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.434722900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.53092956543</t>
   </si>
   <si>
     <t xml:space="preserve">228.317825317383</t>
   </si>
   <si>
-    <t xml:space="preserve">227.644607543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220.527694702148</t>
+    <t xml:space="preserve">227.644622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.527709960938</t>
   </si>
   <si>
     <t xml:space="preserve">219.662139892578</t>
   </si>
   <si>
-    <t xml:space="preserve">218.12336730957</t>
+    <t xml:space="preserve">218.123336791992</t>
   </si>
   <si>
     <t xml:space="preserve">219.373641967773</t>
@@ -2783,19 +2783,19 @@
     <t xml:space="preserve">206.19775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">207.544189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.409774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.102645874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.948547363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.159454345703</t>
+    <t xml:space="preserve">207.544219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.409759521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.102630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.948577880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.15950012207</t>
   </si>
   <si>
     <t xml:space="preserve">200.042572021484</t>
@@ -2807,31 +2807,31 @@
     <t xml:space="preserve">205.813049316406</t>
   </si>
   <si>
-    <t xml:space="preserve">208.121246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.928863525391</t>
+    <t xml:space="preserve">208.121215820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.928894042969</t>
   </si>
   <si>
     <t xml:space="preserve">208.986831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">208.794448852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.352890014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.101593017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.639282226562</t>
+    <t xml:space="preserve">208.794464111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.352935791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.101577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.639312744141</t>
   </si>
   <si>
     <t xml:space="preserve">202.158447265625</t>
   </si>
   <si>
-    <t xml:space="preserve">205.139846801758</t>
+    <t xml:space="preserve">205.139862060547</t>
   </si>
   <si>
     <t xml:space="preserve">202.927825927734</t>
@@ -2840,22 +2840,22 @@
     <t xml:space="preserve">200.234939575195</t>
   </si>
   <si>
-    <t xml:space="preserve">198.959442138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.076278686523</t>
+    <t xml:space="preserve">198.959457397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.076293945312</t>
   </si>
   <si>
     <t xml:space="preserve">208.525756835938</t>
   </si>
   <si>
-    <t xml:space="preserve">206.593170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204.853851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.892013549805</t>
+    <t xml:space="preserve">206.593154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">204.853820800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.892028808594</t>
   </si>
   <si>
     <t xml:space="preserve">203.404403686523</t>
@@ -2864,85 +2864,85 @@
     <t xml:space="preserve">205.916748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">205.626861572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">216.256072998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.130233764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.957183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.116729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.397598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.910003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">233.262802124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">232.393127441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.233581542969</t>
+    <t xml:space="preserve">205.626846313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">216.256057739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.130218505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.806655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.957214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.116714477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.39762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.90998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">233.262786865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.393157958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.233551025391</t>
   </si>
   <si>
     <t xml:space="preserve">237.417846679688</t>
   </si>
   <si>
-    <t xml:space="preserve">236.161651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.312255859375</t>
+    <t xml:space="preserve">236.161636352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.312225341797</t>
   </si>
   <si>
     <t xml:space="preserve">243.408874511719</t>
   </si>
   <si>
-    <t xml:space="preserve">246.307754516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.332473754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.651580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">249.883026123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.525680541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.105453491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.294219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.004302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.622314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.008880615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250.656051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.844802856445</t>
+    <t xml:space="preserve">246.307723999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.332458496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.651519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">249.883010864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.52571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.105484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.294235229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.004364013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.622344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.008865356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250.656066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.844787597656</t>
   </si>
   <si>
     <t xml:space="preserve">257.468414306641</t>
@@ -2951,43 +2951,43 @@
     <t xml:space="preserve">260.802124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">266.02001953125</t>
+    <t xml:space="preserve">266.020050048828</t>
   </si>
   <si>
     <t xml:space="preserve">275.48974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">276.890808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.006591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.668365478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.305480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.691986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.295318603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.556030273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.796539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.347045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.869537353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.595489501953</t>
+    <t xml:space="preserve">276.890838623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.006652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.668395996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.305511474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.692016601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.295349121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.555999755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.796478271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.347015380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.869567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.595367431641</t>
   </si>
   <si>
     <t xml:space="preserve">268.822326660156</t>
@@ -2996,31 +2996,31 @@
     <t xml:space="preserve">265.730163574219</t>
   </si>
   <si>
-    <t xml:space="preserve">265.536834716797</t>
+    <t xml:space="preserve">265.536895751953</t>
   </si>
   <si>
     <t xml:space="preserve">264.957153320312</t>
   </si>
   <si>
-    <t xml:space="preserve">268.339202880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.102111816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.942596435547</t>
+    <t xml:space="preserve">268.339233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.102081298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.942565917969</t>
   </si>
   <si>
     <t xml:space="preserve">258.579650878906</t>
   </si>
   <si>
-    <t xml:space="preserve">266.454956054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">267.4052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">281.854309082031</t>
+    <t xml:space="preserve">266.454895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">267.405242919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281.854370117188</t>
   </si>
   <si>
     <t xml:space="preserve">277.005706787109</t>
@@ -3029,109 +3029,109 @@
     <t xml:space="preserve">274.290435791016</t>
   </si>
   <si>
-    <t xml:space="preserve">263.623260498047</t>
+    <t xml:space="preserve">263.623291015625</t>
   </si>
   <si>
     <t xml:space="preserve">271.090240478516</t>
   </si>
   <si>
-    <t xml:space="preserve">275.599548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.108520507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">280.642150878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">281.466461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">282.630157470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.532867431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">280.205780029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">278.411743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">284.084808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.769378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.066192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270.750823974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.471954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">271.817596435547</t>
+    <t xml:space="preserve">275.599517822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.108428955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">280.642181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281.466491699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">282.630249023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.532836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">280.205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">278.411773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">284.084716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.769439697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.066223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270.750885009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.472015380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271.817535400391</t>
   </si>
   <si>
     <t xml:space="preserve">265.611267089844</t>
   </si>
   <si>
-    <t xml:space="preserve">272.253936767578</t>
+    <t xml:space="preserve">272.253967285156</t>
   </si>
   <si>
     <t xml:space="preserve">270.847808837891</t>
   </si>
   <si>
-    <t xml:space="preserve">274.484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.720977783203</t>
+    <t xml:space="preserve">274.484313964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.720947265625</t>
   </si>
   <si>
     <t xml:space="preserve">284.763549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">298.291351318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.455017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.576080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.552062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.679260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.842987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.946197509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.721923828125</t>
+    <t xml:space="preserve">298.291412353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.455078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.576110839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.552032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.679321289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.843017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.946166992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.721984863281</t>
   </si>
   <si>
     <t xml:space="preserve">314.049682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">312.740509033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.019439697266</t>
+    <t xml:space="preserve">312.740478515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.019378662109</t>
   </si>
   <si>
     <t xml:space="preserve">318.364990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">309.443420410156</t>
+    <t xml:space="preserve">309.443450927734</t>
   </si>
   <si>
     <t xml:space="preserve">311.625305175781</t>
@@ -3140,64 +3140,64 @@
     <t xml:space="preserve">318.12255859375</t>
   </si>
   <si>
-    <t xml:space="preserve">315.21337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.879760742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.825103759766</t>
+    <t xml:space="preserve">315.213317871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.879791259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.825164794922</t>
   </si>
   <si>
     <t xml:space="preserve">311.916229248047</t>
   </si>
   <si>
-    <t xml:space="preserve">312.837524414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.231536865234</t>
+    <t xml:space="preserve">312.837493896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.231567382812</t>
   </si>
   <si>
     <t xml:space="preserve">313.4677734375</t>
   </si>
   <si>
-    <t xml:space="preserve">314.631500244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.661773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.425140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.473663330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.667266845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.854736328125</t>
+    <t xml:space="preserve">314.631469726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.661804199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.425170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.473724365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.667236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.854705810547</t>
   </si>
   <si>
     <t xml:space="preserve">288.836456298828</t>
   </si>
   <si>
-    <t xml:space="preserve">289.369903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.284912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">285.539306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">283.84228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.806762695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.298797607422</t>
+    <t xml:space="preserve">289.369842529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.284851074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">285.539367675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">283.842315673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.806793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.298828125</t>
   </si>
   <si>
     <t xml:space="preserve">298.369110107422</t>
@@ -3212,40 +3212,40 @@
     <t xml:space="preserve">312.428924560547</t>
   </si>
   <si>
-    <t xml:space="preserve">316.126281738281</t>
+    <t xml:space="preserve">316.126312255859</t>
   </si>
   <si>
     <t xml:space="preserve">309.996429443359</t>
   </si>
   <si>
-    <t xml:space="preserve">311.358612060547</t>
+    <t xml:space="preserve">311.358673095703</t>
   </si>
   <si>
     <t xml:space="preserve">309.41259765625</t>
   </si>
   <si>
-    <t xml:space="preserve">314.228942871094</t>
+    <t xml:space="preserve">314.22900390625</t>
   </si>
   <si>
     <t xml:space="preserve">303.234069824219</t>
   </si>
   <si>
-    <t xml:space="preserve">299.925903320312</t>
+    <t xml:space="preserve">299.925933837891</t>
   </si>
   <si>
     <t xml:space="preserve">294.185272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">297.250152587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.217742919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.887969970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.596282958984</t>
+    <t xml:space="preserve">297.250183105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.217803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.888031005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.596252441406</t>
   </si>
   <si>
     <t xml:space="preserve">303.9638671875</t>
@@ -3254,37 +3254,37 @@
     <t xml:space="preserve">306.688262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">308.585632324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.298980712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.969207763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.412384033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.342102050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.796112060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.990661621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.104248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.601806640625</t>
+    <t xml:space="preserve">308.585540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.299011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.969177246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.412414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.342132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.796081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.990692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.104278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.601867675781</t>
   </si>
   <si>
     <t xml:space="preserve">311.845123291016</t>
   </si>
   <si>
-    <t xml:space="preserve">314.083038330078</t>
+    <t xml:space="preserve">314.0830078125</t>
   </si>
   <si>
     <t xml:space="preserve">342.883636474609</t>
@@ -3293,91 +3293,91 @@
     <t xml:space="preserve">327.656280517578</t>
   </si>
   <si>
-    <t xml:space="preserve">324.445404052734</t>
+    <t xml:space="preserve">324.445434570312</t>
   </si>
   <si>
     <t xml:space="preserve">316.612823486328</t>
   </si>
   <si>
-    <t xml:space="preserve">320.066925048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.348083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.721252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.650909423828</t>
+    <t xml:space="preserve">320.06689453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.34814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.721221923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.65087890625</t>
   </si>
   <si>
     <t xml:space="preserve">323.375122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">325.758911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327.315704345703</t>
+    <t xml:space="preserve">325.758941650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327.315765380859</t>
   </si>
   <si>
     <t xml:space="preserve">324.883239746094</t>
   </si>
   <si>
-    <t xml:space="preserve">330.380676269531</t>
+    <t xml:space="preserve">330.380737304688</t>
   </si>
   <si>
     <t xml:space="preserve">332.521270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">328.580627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">326.245422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.710327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.515869140625</t>
+    <t xml:space="preserve">328.580688476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326.245452880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.710357666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.515838623047</t>
   </si>
   <si>
     <t xml:space="preserve">343.759399414062</t>
   </si>
   <si>
-    <t xml:space="preserve">342.543151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.456756591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.748687744141</t>
+    <t xml:space="preserve">342.543121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.456787109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.748626708984</t>
   </si>
   <si>
     <t xml:space="preserve">352.7109375</t>
   </si>
   <si>
-    <t xml:space="preserve">354.802856445312</t>
+    <t xml:space="preserve">354.802825927734</t>
   </si>
   <si>
     <t xml:space="preserve">341.424194335938</t>
   </si>
   <si>
-    <t xml:space="preserve">353.829895019531</t>
+    <t xml:space="preserve">353.829803466797</t>
   </si>
   <si>
     <t xml:space="preserve">358.257019042969</t>
   </si>
   <si>
-    <t xml:space="preserve">350.473083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.224426269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">353.63525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.429992675781</t>
+    <t xml:space="preserve">350.473022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.224456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">353.635284423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.429962158203</t>
   </si>
   <si>
     <t xml:space="preserve">349.013580322266</t>
@@ -3386,31 +3386,31 @@
     <t xml:space="preserve">330.672576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">334.946594238281</t>
+    <t xml:space="preserve">334.946655273438</t>
   </si>
   <si>
     <t xml:space="preserve">331.531280517578</t>
   </si>
   <si>
-    <t xml:space="preserve">331.921630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.898651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.972015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.728973388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.606781005859</t>
+    <t xml:space="preserve">331.921600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.898620605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.972076416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.728851318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.606750488281</t>
   </si>
   <si>
     <t xml:space="preserve">339.581726074219</t>
   </si>
   <si>
-    <t xml:space="preserve">339.093872070312</t>
+    <t xml:space="preserve">339.093811035156</t>
   </si>
   <si>
     <t xml:space="preserve">342.704345703125</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">345.095062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">341.435729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">344.509552001953</t>
+    <t xml:space="preserve">341.435699462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.509582519531</t>
   </si>
   <si>
     <t xml:space="preserve">344.119262695312</t>
@@ -3434,16 +3434,16 @@
     <t xml:space="preserve">345.826904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">342.070007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.582946777344</t>
+    <t xml:space="preserve">342.070098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.582916259766</t>
   </si>
   <si>
     <t xml:space="preserve">343.68017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">340.411163330078</t>
+    <t xml:space="preserve">340.411193847656</t>
   </si>
   <si>
     <t xml:space="preserve">338.801086425781</t>
@@ -3452,16 +3452,16 @@
     <t xml:space="preserve">335.239379882812</t>
   </si>
   <si>
-    <t xml:space="preserve">332.751037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.945373535156</t>
+    <t xml:space="preserve">332.751007080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.945434570312</t>
   </si>
   <si>
     <t xml:space="preserve">328.994201660156</t>
   </si>
   <si>
-    <t xml:space="preserve">330.116363525391</t>
+    <t xml:space="preserve">330.116333007812</t>
   </si>
   <si>
     <t xml:space="preserve">340.118408203125</t>
@@ -3473,22 +3473,22 @@
     <t xml:space="preserve">336.800659179688</t>
   </si>
   <si>
-    <t xml:space="preserve">335.141784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.605865478516</t>
+    <t xml:space="preserve">335.141815185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.60595703125</t>
   </si>
   <si>
     <t xml:space="preserve">335.044189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">336.703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.629669189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">337.28857421875</t>
+    <t xml:space="preserve">336.703063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.629730224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">337.288543701172</t>
   </si>
   <si>
     <t xml:space="preserve">330.89697265625</t>
@@ -3500,22 +3500,22 @@
     <t xml:space="preserve">325.774017333984</t>
   </si>
   <si>
-    <t xml:space="preserve">315.625579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">321.529296875</t>
+    <t xml:space="preserve">315.625610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">321.529266357422</t>
   </si>
   <si>
     <t xml:space="preserve">321.919586181641</t>
   </si>
   <si>
-    <t xml:space="preserve">326.017974853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323.968811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.188568115234</t>
+    <t xml:space="preserve">326.017913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.96875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.188537597656</t>
   </si>
   <si>
     <t xml:space="preserve">320.065551757812</t>
@@ -3527,19 +3527,19 @@
     <t xml:space="preserve">311.088104248047</t>
   </si>
   <si>
-    <t xml:space="preserve">307.672729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.428833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">310.161071777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.039733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.794982910156</t>
+    <t xml:space="preserve">307.672790527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.428771972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">310.1611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.039672851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.794921875</t>
   </si>
   <si>
     <t xml:space="preserve">307.184783935547</t>
@@ -3551,7 +3551,7 @@
     <t xml:space="preserve">287.131958007812</t>
   </si>
   <si>
-    <t xml:space="preserve">307.331237792969</t>
+    <t xml:space="preserve">307.331207275391</t>
   </si>
   <si>
     <t xml:space="preserve">306.160247802734</t>
@@ -3563,43 +3563,43 @@
     <t xml:space="preserve">309.575561523438</t>
   </si>
   <si>
-    <t xml:space="preserve">312.161529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.796569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.503875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.393707275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.595520019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.558532714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.942840576172</t>
+    <t xml:space="preserve">312.161499023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.796600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.503814697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.393768310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.595581054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.558563232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.942810058594</t>
   </si>
   <si>
     <t xml:space="preserve">300.571899414062</t>
   </si>
   <si>
-    <t xml:space="preserve">302.775177001953</t>
+    <t xml:space="preserve">302.775115966797</t>
   </si>
   <si>
     <t xml:space="preserve">304.146087646484</t>
   </si>
   <si>
-    <t xml:space="preserve">304.341888427734</t>
+    <t xml:space="preserve">304.341918945312</t>
   </si>
   <si>
     <t xml:space="preserve">299.886444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">294.011108398438</t>
+    <t xml:space="preserve">294.011138916016</t>
   </si>
   <si>
     <t xml:space="preserve">287.939910888672</t>
@@ -3611,58 +3611,58 @@
     <t xml:space="preserve">289.604614257812</t>
   </si>
   <si>
-    <t xml:space="preserve">293.080841064453</t>
+    <t xml:space="preserve">293.080810546875</t>
   </si>
   <si>
     <t xml:space="preserve">291.465118408203</t>
   </si>
   <si>
-    <t xml:space="preserve">289.702545166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">288.380676269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.129821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">292.052673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.528900146484</t>
+    <t xml:space="preserve">289.702575683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">288.380584716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.129791259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">292.052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.528930664062</t>
   </si>
   <si>
     <t xml:space="preserve">295.969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">304.195007324219</t>
+    <t xml:space="preserve">304.194976806641</t>
   </si>
   <si>
     <t xml:space="preserve">304.390869140625</t>
   </si>
   <si>
-    <t xml:space="preserve">302.089721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.411651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.592651367188</t>
+    <t xml:space="preserve">302.089691162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.411590576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.592742919922</t>
   </si>
   <si>
     <t xml:space="preserve">301.110473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">299.984344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.3701171875</t>
+    <t xml:space="preserve">299.984436035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.370086669922</t>
   </si>
   <si>
     <t xml:space="preserve">304.488830566406</t>
   </si>
   <si>
-    <t xml:space="preserve">303.509552001953</t>
+    <t xml:space="preserve">303.509582519531</t>
   </si>
   <si>
     <t xml:space="preserve">305.419006347656</t>
@@ -3671,10 +3671,10 @@
     <t xml:space="preserve">303.950225830078</t>
   </si>
   <si>
-    <t xml:space="preserve">307.965026855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.721618652344</t>
+    <t xml:space="preserve">307.964935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.721588134766</t>
   </si>
   <si>
     <t xml:space="preserve">318.442687988281</t>
@@ -3683,58 +3683,58 @@
     <t xml:space="preserve">325.884796142578</t>
   </si>
   <si>
-    <t xml:space="preserve">329.018249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.605804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.976684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">333.326812744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.110229492188</t>
+    <t xml:space="preserve">329.018310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.605773925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.976715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">333.326873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.110198974609</t>
   </si>
   <si>
     <t xml:space="preserve">332.543518066406</t>
   </si>
   <si>
-    <t xml:space="preserve">331.760040283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.944000244141</t>
+    <t xml:space="preserve">331.760070800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.944030761719</t>
   </si>
   <si>
     <t xml:space="preserve">340.768951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">344.685791015625</t>
+    <t xml:space="preserve">344.685821533203</t>
   </si>
   <si>
     <t xml:space="preserve">352.323669433594</t>
   </si>
   <si>
-    <t xml:space="preserve">358.786560058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.433319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">380.133575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">382.679534912109</t>
+    <t xml:space="preserve">358.786590576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.433380126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">380.133636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">382.679565429688</t>
   </si>
   <si>
     <t xml:space="preserve">385.225555419922</t>
   </si>
   <si>
-    <t xml:space="preserve">385.42138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">386.204833984375</t>
+    <t xml:space="preserve">385.421417236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">386.204772949219</t>
   </si>
   <si>
     <t xml:space="preserve">389.338287353516</t>
@@ -3746,19 +3746,19 @@
     <t xml:space="preserve">389.465972900391</t>
   </si>
   <si>
-    <t xml:space="preserve">393.393981933594</t>
+    <t xml:space="preserve">393.394012451172</t>
   </si>
   <si>
     <t xml:space="preserve">393.197601318359</t>
   </si>
   <si>
-    <t xml:space="preserve">398.304077148438</t>
+    <t xml:space="preserve">398.304107666016</t>
   </si>
   <si>
     <t xml:space="preserve">401.0537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">402.428497314453</t>
+    <t xml:space="preserve">402.428466796875</t>
   </si>
   <si>
     <t xml:space="preserve">388.483947753906</t>
@@ -3767,16 +3767,16 @@
     <t xml:space="preserve">388.091156005859</t>
   </si>
   <si>
-    <t xml:space="preserve">387.109130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">391.233551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">396.143615722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.680328369141</t>
+    <t xml:space="preserve">387.109100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">391.233581542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">396.143646240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.680358886719</t>
   </si>
   <si>
     <t xml:space="preserve">396.536437988281</t>
@@ -3785,100 +3785,100 @@
     <t xml:space="preserve">406.16015625</t>
   </si>
   <si>
-    <t xml:space="preserve">408.124206542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404.785308837891</t>
+    <t xml:space="preserve">408.124176025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404.785400390625</t>
   </si>
   <si>
     <t xml:space="preserve">405.963775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">407.731384277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">403.999786376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.178161621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.821350097656</t>
+    <t xml:space="preserve">407.731414794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">403.999694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.178131103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.821319580078</t>
   </si>
   <si>
     <t xml:space="preserve">407.534973144531</t>
   </si>
   <si>
-    <t xml:space="preserve">406.749389648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">413.034301757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">409.498992919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">417.551544189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.122711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.479583740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.980285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.711883544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">420.497528076172</t>
+    <t xml:space="preserve">406.749359130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413.034240722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409.4990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">417.551513671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.122680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.479522705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.980316162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.711944580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420.49755859375</t>
   </si>
   <si>
     <t xml:space="preserve">405.570983886719</t>
   </si>
   <si>
-    <t xml:space="preserve">403.606903076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397.518432617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">390.447967529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">383.377502441406</t>
+    <t xml:space="preserve">403.606964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397.518402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">390.447998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">383.377471923828</t>
   </si>
   <si>
     <t xml:space="preserve">391.822814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">395.947265625</t>
+    <t xml:space="preserve">395.947235107422</t>
   </si>
   <si>
     <t xml:space="preserve">394.572418212891</t>
   </si>
   <si>
-    <t xml:space="preserve">407.338592529297</t>
+    <t xml:space="preserve">407.338531494141</t>
   </si>
   <si>
     <t xml:space="preserve">410.284606933594</t>
   </si>
   <si>
-    <t xml:space="preserve">409.302612304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">408.320617675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.142211914062</t>
+    <t xml:space="preserve">409.302581787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">408.320556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.142181396484</t>
   </si>
   <si>
     <t xml:space="preserve">406.356506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">402.232116699219</t>
+    <t xml:space="preserve">402.232086181641</t>
   </si>
   <si>
     <t xml:space="preserve">405.767364501953</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">404.588958740234</t>
   </si>
   <si>
-    <t xml:space="preserve">400.464477539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">403.410522460938</t>
+    <t xml:space="preserve">400.464508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">403.410552978516</t>
   </si>
   <si>
     <t xml:space="preserve">477.650634765625</t>
@@ -3902,58 +3902,58 @@
     <t xml:space="preserve">474.508209228516</t>
   </si>
   <si>
-    <t xml:space="preserve">470.187347412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">474.115386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">486.251983642578</t>
+    <t xml:space="preserve">470.187377929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">474.115356445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">486.252014160156</t>
   </si>
   <si>
     <t xml:space="preserve">488.614349365234</t>
   </si>
   <si>
-    <t xml:space="preserve">495.11083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">493.634399414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">492.157867431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">496.095153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.524536132812</t>
+    <t xml:space="preserve">495.110870361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">493.634338378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">492.157928466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">496.095184326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.524566650391</t>
   </si>
   <si>
     <t xml:space="preserve">499.048095703125</t>
   </si>
   <si>
-    <t xml:space="preserve">503.477569580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">503.969665527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">501.016693115234</t>
+    <t xml:space="preserve">503.477508544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">503.969696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">501.016723632812</t>
   </si>
   <si>
     <t xml:space="preserve">495.602996826172</t>
   </si>
   <si>
-    <t xml:space="preserve">500.032379150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">507.414764404297</t>
+    <t xml:space="preserve">500.032409667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">507.414794921875</t>
   </si>
   <si>
     <t xml:space="preserve">511.844177246094</t>
   </si>
   <si>
-    <t xml:space="preserve">514.797180175781</t>
+    <t xml:space="preserve">514.797119140625</t>
   </si>
   <si>
     <t xml:space="preserve">509.383453369141</t>
@@ -3962,19 +3962,19 @@
     <t xml:space="preserve">527.59326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">535.960021972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">547.279479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">546.295288085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">546.787414550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">550.232604980469</t>
+    <t xml:space="preserve">535.9599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">547.279602050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">546.295227050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">546.787475585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">550.232543945312</t>
   </si>
   <si>
     <t xml:space="preserve">539.897216796875</t>
@@ -3986,61 +3986,61 @@
     <t xml:space="preserve">526.116760253906</t>
   </si>
   <si>
-    <t xml:space="preserve">512.336486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">510.859954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">489.992401123047</t>
+    <t xml:space="preserve">512.336303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">510.859893798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">489.992370605469</t>
   </si>
   <si>
     <t xml:space="preserve">504.461853027344</t>
   </si>
   <si>
-    <t xml:space="preserve">517.750183105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.514892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">554.661987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.4423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567.9501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">575.824768066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">561.552062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569.426635742188</t>
+    <t xml:space="preserve">517.750244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.514831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">554.661865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.442443847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567.950256347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">575.82470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">561.552185058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569.426696777344</t>
   </si>
   <si>
     <t xml:space="preserve">545.803100585938</t>
   </si>
   <si>
-    <t xml:space="preserve">543.34228515625</t>
+    <t xml:space="preserve">543.342407226562</t>
   </si>
   <si>
     <t xml:space="preserve">540.389404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">549.248107910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">555.646301269531</t>
+    <t xml:space="preserve">549.248168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">555.646240234375</t>
   </si>
   <si>
     <t xml:space="preserve">532.022705078125</t>
   </si>
   <si>
-    <t xml:space="preserve">523.655944824219</t>
+    <t xml:space="preserve">523.656005859375</t>
   </si>
   <si>
     <t xml:space="preserve">514.304992675781</t>
@@ -4049,37 +4049,37 @@
     <t xml:space="preserve">517.257934570312</t>
   </si>
   <si>
-    <t xml:space="preserve">534.975708007812</t>
+    <t xml:space="preserve">534.975646972656</t>
   </si>
   <si>
     <t xml:space="preserve">544.818786621094</t>
   </si>
   <si>
-    <t xml:space="preserve">553.185546875</t>
+    <t xml:space="preserve">553.185485839844</t>
   </si>
   <si>
     <t xml:space="preserve">554.300048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">536.053405761719</t>
+    <t xml:space="preserve">536.053466796875</t>
   </si>
   <si>
     <t xml:space="preserve">532.108276367188</t>
   </si>
   <si>
-    <t xml:space="preserve">536.546691894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">542.464477539062</t>
+    <t xml:space="preserve">536.546630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">542.464416503906</t>
   </si>
   <si>
     <t xml:space="preserve">537.532897949219</t>
   </si>
   <si>
-    <t xml:space="preserve">541.478088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">543.450744628906</t>
+    <t xml:space="preserve">541.478149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">543.450805664062</t>
   </si>
   <si>
     <t xml:space="preserve">533.094604492188</t>
@@ -4091,16 +4091,16 @@
     <t xml:space="preserve">538.026062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">540.491821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.601379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.039794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">534.080932617188</t>
+    <t xml:space="preserve">540.491760253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.601501464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.039733886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534.080810546875</t>
   </si>
   <si>
     <t xml:space="preserve">539.012329101562</t>
@@ -4109,82 +4109,82 @@
     <t xml:space="preserve">526.190490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">531.615051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">517.807006835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">513.368591308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">523.231567382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">519.779479980469</t>
+    <t xml:space="preserve">531.615112304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">517.806884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">513.368530273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">523.231689453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">519.779541015625</t>
   </si>
   <si>
     <t xml:space="preserve">511.88916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">509.916564941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">511.39599609375</t>
+    <t xml:space="preserve">509.91650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">511.395965576172</t>
   </si>
   <si>
     <t xml:space="preserve">518.793334960938</t>
   </si>
   <si>
-    <t xml:space="preserve">520.765869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">527.669921875</t>
+    <t xml:space="preserve">520.765808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">527.669982910156</t>
   </si>
   <si>
     <t xml:space="preserve">552.820556640625</t>
   </si>
   <si>
-    <t xml:space="preserve">567.121887207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">557.258850097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567.615112304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">565.642456054688</t>
+    <t xml:space="preserve">567.121948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">557.258911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567.615051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">565.642517089844</t>
   </si>
   <si>
     <t xml:space="preserve">568.108215332031</t>
   </si>
   <si>
-    <t xml:space="preserve">573.532897949219</t>
+    <t xml:space="preserve">573.532836914062</t>
   </si>
   <si>
     <t xml:space="preserve">581.423217773438</t>
   </si>
   <si>
-    <t xml:space="preserve">583.888916015625</t>
+    <t xml:space="preserve">583.888977050781</t>
   </si>
   <si>
     <t xml:space="preserve">575.012329101562</t>
   </si>
   <si>
-    <t xml:space="preserve">561.697265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569.094543457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.601379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">577.478088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">572.053405761719</t>
+    <t xml:space="preserve">561.697143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569.094482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.601257324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">577.47802734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">572.053344726562</t>
   </si>
   <si>
     <t xml:space="preserve">577.97119140625</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">593.751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">609.039611816406</t>
+    <t xml:space="preserve">609.039672851562</t>
   </si>
   <si>
     <t xml:space="preserve">646.025756835938</t>
@@ -4211,16 +4211,16 @@
     <t xml:space="preserve">642.080627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">668.217468261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">675.614868164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677.094177246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">671.176452636719</t>
+    <t xml:space="preserve">668.217529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">675.614807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">677.09423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">671.176391601562</t>
   </si>
   <si>
     <t xml:space="preserve">679.56005859375</t>
@@ -4229,10 +4229,10 @@
     <t xml:space="preserve">695.172912597656</t>
   </si>
   <si>
-    <t xml:space="preserve">698.631469726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">722.841491699219</t>
+    <t xml:space="preserve">698.631530761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722.841552734375</t>
   </si>
   <si>
     <t xml:space="preserve">726.300109863281</t>
@@ -4241,64 +4241,64 @@
     <t xml:space="preserve">700.113708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">681.338562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">707.030944824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">697.643310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.054565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">699.125610351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">688.255859375</t>
+    <t xml:space="preserve">681.338684082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">707.030883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">697.643371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.054626464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">699.125732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">688.255798339844</t>
   </si>
   <si>
     <t xml:space="preserve">686.279418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">709.995422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">722.347412109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">710.489562988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">711.971740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.232116699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">660.587280273438</t>
+    <t xml:space="preserve">709.995361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722.347473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">710.489501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.971801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.232177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">660.587219238281</t>
   </si>
   <si>
     <t xml:space="preserve">678.868225097656</t>
   </si>
   <si>
-    <t xml:space="preserve">683.31494140625</t>
+    <t xml:space="preserve">683.315002441406</t>
   </si>
   <si>
     <t xml:space="preserve">682.326782226562</t>
   </si>
   <si>
-    <t xml:space="preserve">697.149291992188</t>
+    <t xml:space="preserve">697.149353027344</t>
   </si>
   <si>
     <t xml:space="preserve">704.560485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">704.066528320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">706.042724609375</t>
+    <t xml:space="preserve">704.066467285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706.042785644531</t>
   </si>
   <si>
     <t xml:space="preserve">720.865234375</t>
@@ -4310,16 +4310,16 @@
     <t xml:space="preserve">709.896606445312</t>
   </si>
   <si>
-    <t xml:space="preserve">704.165222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">709.204895019531</t>
+    <t xml:space="preserve">704.165161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">709.204833984375</t>
   </si>
   <si>
     <t xml:space="preserve">708.710815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">689.738037109375</t>
+    <t xml:space="preserve">689.738098144531</t>
   </si>
   <si>
     <t xml:space="preserve">701.991333007812</t>
@@ -4331,13 +4331,13 @@
     <t xml:space="preserve">706.141540527344</t>
   </si>
   <si>
-    <t xml:space="preserve">695.469421386719</t>
+    <t xml:space="preserve">695.469360351562</t>
   </si>
   <si>
     <t xml:space="preserve">694.283630371094</t>
   </si>
   <si>
-    <t xml:space="preserve">677.188354492188</t>
+    <t xml:space="preserve">677.188415527344</t>
   </si>
   <si>
     <t xml:space="preserve">676.6943359375</t>
@@ -4346,7 +4346,7 @@
     <t xml:space="preserve">685.390075683594</t>
   </si>
   <si>
-    <t xml:space="preserve">678.077758789062</t>
+    <t xml:space="preserve">678.077697753906</t>
   </si>
   <si>
     <t xml:space="preserve">667.603149414062</t>
@@ -4355,28 +4355,28 @@
     <t xml:space="preserve">680.745849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">674.619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">711.576538085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">674.520263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">688.8486328125</t>
+    <t xml:space="preserve">674.619079589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.576477050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">674.520324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">688.848693847656</t>
   </si>
   <si>
     <t xml:space="preserve">709.106018066406</t>
   </si>
   <si>
-    <t xml:space="preserve">712.367004394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.133361816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.528564453125</t>
+    <t xml:space="preserve">712.367065429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.133422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.528625488281</t>
   </si>
   <si>
     <t xml:space="preserve">710.328674316406</t>
@@ -4385,10 +4385,10 @@
     <t xml:space="preserve">705.57666015625</t>
   </si>
   <si>
-    <t xml:space="preserve">701.517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">712.407653808594</t>
+    <t xml:space="preserve">701.517639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">712.407592773438</t>
   </si>
   <si>
     <t xml:space="preserve">732.603759765625</t>
@@ -4400,10 +4400,10 @@
     <t xml:space="preserve">744.186889648438</t>
   </si>
   <si>
-    <t xml:space="preserve">737.2568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">739.434875488281</t>
+    <t xml:space="preserve">737.256896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">739.434814453125</t>
   </si>
   <si>
     <t xml:space="preserve">733.593811035156</t>
@@ -4418,16 +4418,16 @@
     <t xml:space="preserve">746.661865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">758.640930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">754.185791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">757.749938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">762.205017089844</t>
+    <t xml:space="preserve">758.640869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">754.185852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">762.204956054688</t>
   </si>
   <si>
     <t xml:space="preserve">778.243041992188</t>
@@ -4436,10 +4436,10 @@
     <t xml:space="preserve">791.41015625</t>
   </si>
   <si>
-    <t xml:space="preserve">793.588134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">787.549072265625</t>
+    <t xml:space="preserve">793.588073730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">787.549133300781</t>
   </si>
   <si>
     <t xml:space="preserve">807.250244140625</t>
@@ -4448,22 +4448,22 @@
     <t xml:space="preserve">815.764221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">815.962280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">825.565307617188</t>
+    <t xml:space="preserve">815.962219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">825.565368652344</t>
   </si>
   <si>
     <t xml:space="preserve">823.288208007812</t>
   </si>
   <si>
-    <t xml:space="preserve">833.386291503906</t>
+    <t xml:space="preserve">833.38623046875</t>
   </si>
   <si>
     <t xml:space="preserve">819.42724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">828.337280273438</t>
+    <t xml:space="preserve">828.337341308594</t>
   </si>
   <si>
     <t xml:space="preserve">838.732360839844</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">828.931274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">818.932189941406</t>
+    <t xml:space="preserve">818.932250976562</t>
   </si>
   <si>
     <t xml:space="preserve">825.664245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">834.970458984375</t>
+    <t xml:space="preserve">834.970397949219</t>
   </si>
   <si>
     <t xml:space="preserve">839.722351074219</t>
@@ -4505,76 +4505,76 @@
     <t xml:space="preserve">845.563293457031</t>
   </si>
   <si>
-    <t xml:space="preserve">859.720458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.977416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">830.020324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">773.392028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">783.192993164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">784.282043457031</t>
+    <t xml:space="preserve">859.720520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.977478027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.482482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">830.020263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">773.391967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">783.193054199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">784.282104492188</t>
   </si>
   <si>
     <t xml:space="preserve">807.646118164062</t>
   </si>
   <si>
-    <t xml:space="preserve">782.401062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760.224914550781</t>
+    <t xml:space="preserve">782.401000976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760.224975585938</t>
   </si>
   <si>
     <t xml:space="preserve">743.790832519531</t>
   </si>
   <si>
-    <t xml:space="preserve">737.751831054688</t>
+    <t xml:space="preserve">737.751892089844</t>
   </si>
   <si>
     <t xml:space="preserve">726.465759277344</t>
   </si>
   <si>
-    <t xml:space="preserve">735.078796386719</t>
+    <t xml:space="preserve">735.078735351562</t>
   </si>
   <si>
     <t xml:space="preserve">761.016967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">720.030700683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">699.042663574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720.32763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">702.804626464844</t>
+    <t xml:space="preserve">720.030639648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">699.042602539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720.327758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">702.8046875</t>
   </si>
   <si>
     <t xml:space="preserve">755.967895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">812.794189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">806.359252929688</t>
+    <t xml:space="preserve">812.794250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">806.359191894531</t>
   </si>
   <si>
     <t xml:space="preserve">817.744262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">838.138366699219</t>
+    <t xml:space="preserve">838.138305664062</t>
   </si>
   <si>
     <t xml:space="preserve">836.353576660156</t>
@@ -4586,37 +4586,37 @@
     <t xml:space="preserve">846.169738769531</t>
   </si>
   <si>
-    <t xml:space="preserve">841.806945800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">855.886657714844</t>
+    <t xml:space="preserve">841.807006835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">855.88671875</t>
   </si>
   <si>
     <t xml:space="preserve">840.220581054688</t>
   </si>
   <si>
-    <t xml:space="preserve">845.376525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">851.028137207031</t>
+    <t xml:space="preserve">845.37646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">851.028198242188</t>
   </si>
   <si>
     <t xml:space="preserve">845.673950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">850.631652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">846.7646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">858.563842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">867.586669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">852.218078613281</t>
+    <t xml:space="preserve">850.631591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">846.764587402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">858.563781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">867.586730957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">852.217956542969</t>
   </si>
   <si>
     <t xml:space="preserve">812.160278320312</t>
@@ -4628,16 +4628,16 @@
     <t xml:space="preserve">807.995910644531</t>
   </si>
   <si>
-    <t xml:space="preserve">812.656005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812.953552246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">831.197692871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">835.064636230469</t>
+    <t xml:space="preserve">812.656066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812.95361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">831.197631835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">835.064575195312</t>
   </si>
   <si>
     <t xml:space="preserve">824.05859375</t>
@@ -4646,16 +4646,16 @@
     <t xml:space="preserve">812.556945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">808.987365722656</t>
+    <t xml:space="preserve">808.987487792969</t>
   </si>
   <si>
     <t xml:space="preserve">805.51708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">825.545959472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">816.919616699219</t>
+    <t xml:space="preserve">825.5458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">816.919677734375</t>
   </si>
   <si>
     <t xml:space="preserve">819.695922851562</t>
@@ -4670,67 +4670,67 @@
     <t xml:space="preserve">779.737365722656</t>
   </si>
   <si>
-    <t xml:space="preserve">779.935668945312</t>
+    <t xml:space="preserve">779.935607910156</t>
   </si>
   <si>
     <t xml:space="preserve">793.519592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">800.063720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">798.675537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">794.70947265625</t>
+    <t xml:space="preserve">800.063659667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">798.675476074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">794.709411621094</t>
   </si>
   <si>
     <t xml:space="preserve">816.32470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">826.636657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">829.313781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">836.948486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">829.8095703125</t>
+    <t xml:space="preserve">826.636596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">829.313720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">836.948547363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">829.809509277344</t>
   </si>
   <si>
     <t xml:space="preserve">832.982360839844</t>
   </si>
   <si>
-    <t xml:space="preserve">841.410400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">838.435668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">830.007751464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">833.279907226562</t>
+    <t xml:space="preserve">841.410339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.435791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">830.0078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">833.279846191406</t>
   </si>
   <si>
     <t xml:space="preserve">823.662048339844</t>
   </si>
   <si>
-    <t xml:space="preserve">819.2001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">822.868896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819.894287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">827.132385253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761.790649414062</t>
+    <t xml:space="preserve">819.200134277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">822.868774414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.894226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">827.132446289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761.790710449219</t>
   </si>
   <si>
     <t xml:space="preserve">778.646667480469</t>
@@ -4742,43 +4742,43 @@
     <t xml:space="preserve">737.002502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">726.492309570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">716.9736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">725.401611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766.550048828125</t>
+    <t xml:space="preserve">726.492248535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">716.973571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">725.401550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766.549987792969</t>
   </si>
   <si>
     <t xml:space="preserve">778.250061035156</t>
   </si>
   <si>
-    <t xml:space="preserve">761.691589355469</t>
+    <t xml:space="preserve">761.691528320312</t>
   </si>
   <si>
     <t xml:space="preserve">771.309387207031</t>
   </si>
   <si>
-    <t xml:space="preserve">750.090637207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">713.24169921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">680.464904785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">679.67041015625</t>
+    <t xml:space="preserve">750.090759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">713.241638183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">680.464965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679.670349121094</t>
   </si>
   <si>
     <t xml:space="preserve">703.706665039062</t>
   </si>
   <si>
-    <t xml:space="preserve">705.295837402344</t>
+    <t xml:space="preserve">705.295776367188</t>
   </si>
   <si>
     <t xml:space="preserve">715.228088378906</t>
@@ -4793,10 +4793,10 @@
     <t xml:space="preserve">749.892028808594</t>
   </si>
   <si>
-    <t xml:space="preserve">756.447326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766.777038574219</t>
+    <t xml:space="preserve">756.447387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766.776977539062</t>
   </si>
   <si>
     <t xml:space="preserve">790.416015625</t>
@@ -4811,7 +4811,7 @@
     <t xml:space="preserve">760.519653320312</t>
   </si>
   <si>
-    <t xml:space="preserve">756.348022460938</t>
+    <t xml:space="preserve">756.348083496094</t>
   </si>
   <si>
     <t xml:space="preserve">748.104248046875</t>
@@ -4820,16 +4820,16 @@
     <t xml:space="preserve">747.408935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">740.952880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">744.329956054688</t>
+    <t xml:space="preserve">740.952941894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">744.330017089844</t>
   </si>
   <si>
     <t xml:space="preserve">744.925842285156</t>
   </si>
   <si>
-    <t xml:space="preserve">735.788146972656</t>
+    <t xml:space="preserve">735.7880859375</t>
   </si>
   <si>
     <t xml:space="preserve">725.756469726562</t>
@@ -4844,10 +4844,10 @@
     <t xml:space="preserve">748.700134277344</t>
   </si>
   <si>
-    <t xml:space="preserve">738.569213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">759.327758789062</t>
+    <t xml:space="preserve">738.569152832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">759.327819824219</t>
   </si>
   <si>
     <t xml:space="preserve">753.070434570312</t>
@@ -4856,7 +4856,7 @@
     <t xml:space="preserve">739.860412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">740.158386230469</t>
+    <t xml:space="preserve">740.158325195312</t>
   </si>
   <si>
     <t xml:space="preserve">758.731872558594</t>
@@ -4874,7 +4874,7 @@
     <t xml:space="preserve">718.505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">720.1943359375</t>
+    <t xml:space="preserve">720.194274902344</t>
   </si>
   <si>
     <t xml:space="preserve">734.993530273438</t>
@@ -4883,7 +4883,7 @@
     <t xml:space="preserve">714.731506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">693.674987792969</t>
+    <t xml:space="preserve">693.674926757812</t>
   </si>
   <si>
     <t xml:space="preserve">697.548583984375</t>
@@ -4895,7 +4895,7 @@
     <t xml:space="preserve">722.876037597656</t>
   </si>
   <si>
-    <t xml:space="preserve">741.846862792969</t>
+    <t xml:space="preserve">741.846923828125</t>
   </si>
   <si>
     <t xml:space="preserve">757.937255859375</t>
@@ -4904,7 +4904,7 @@
     <t xml:space="preserve">766.181091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">768.068237304688</t>
+    <t xml:space="preserve">768.068176269531</t>
   </si>
   <si>
     <t xml:space="preserve">771.445251464844</t>
@@ -4919,10 +4919,10 @@
     <t xml:space="preserve">775.914855957031</t>
   </si>
   <si>
-    <t xml:space="preserve">796.1767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">842.759460449219</t>
+    <t xml:space="preserve">796.176696777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">842.759399414062</t>
   </si>
   <si>
     <t xml:space="preserve">843.752685546875</t>
@@ -5448,6 +5448,9 @@
   </si>
   <si>
     <t xml:space="preserve">704.799987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.599975585938</t>
   </si>
 </sst>
 </file>
@@ -70760,7 +70763,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45958.6915856482</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>1767</v>
@@ -70781,6 +70784,32 @@
         <v>1811</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45959.6916550926</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>3523</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>715.799987792969</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>703.5</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>706</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>711.599975585938</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1812</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="1813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="1814">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,139 +38,139 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3028755187988</t>
+    <t xml:space="preserve">38.3028717041016</t>
   </si>
   <si>
     <t xml:space="preserve">LLY.DE</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7578315734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.680046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1175270080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5549545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4298515319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9924201965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.2426109313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8051795959473</t>
+    <t xml:space="preserve">38.7578163146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1174964904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5549392700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4298439025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9924049377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.2425994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8051681518555</t>
   </si>
   <si>
     <t xml:space="preserve">60.3677253723145</t>
   </si>
   <si>
-    <t xml:space="preserve">59.9302673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0229988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5943031311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1717185974121</t>
+    <t xml:space="preserve">59.9302635192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0229949951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5942916870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1717262268066</t>
   </si>
   <si>
     <t xml:space="preserve">56.8681373596191</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7071533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5907859802246</t>
+    <t xml:space="preserve">54.7071418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5907974243164</t>
   </si>
   <si>
     <t xml:space="preserve">54.3309478759766</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3598175048828</t>
+    <t xml:space="preserve">53.359806060791</t>
   </si>
   <si>
     <t xml:space="preserve">54.015983581543</t>
   </si>
   <si>
-    <t xml:space="preserve">54.221263885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8039970397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3226661682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4815826416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2785224914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4021224975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0290069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5322875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5963592529297</t>
+    <t xml:space="preserve">54.2212677001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8040046691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3226585388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4815940856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2785263061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4021263122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0290107727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5322952270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5963745117188</t>
   </si>
   <si>
     <t xml:space="preserve">55.4662094116211</t>
   </si>
   <si>
-    <t xml:space="preserve">55.2719612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5721664428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1218605041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.927619934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.971752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6405143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2167053222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5787086486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0754280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8082695007324</t>
+    <t xml:space="preserve">55.2719650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5721549987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1218681335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9276237487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9717597961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6405181884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2167015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5787162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0754432678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8082733154297</t>
   </si>
   <si>
     <t xml:space="preserve">56.0312805175781</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4286155700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2961769104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8900260925293</t>
+    <t xml:space="preserve">56.4286117553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2961692810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8900146484375</t>
   </si>
   <si>
     <t xml:space="preserve">54.4861488342285</t>
@@ -179,340 +179,340 @@
     <t xml:space="preserve">53.2323760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9034042358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1130409240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3690910339355</t>
+    <t xml:space="preserve">53.9034080505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1130294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3690795898438</t>
   </si>
   <si>
     <t xml:space="preserve">55.6251373291016</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9230499267578</t>
+    <t xml:space="preserve">56.9230575561523</t>
   </si>
   <si>
     <t xml:space="preserve">55.8811950683594</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5191764831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7641334533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1019248962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6935005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5057907104492</t>
+    <t xml:space="preserve">55.5191955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7641220092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1019172668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6934967041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5057945251465</t>
   </si>
   <si>
     <t xml:space="preserve">57.161449432373</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9936981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.543399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9495429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4793167114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9119491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5829849243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9162178039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3665084838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1899261474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3622436523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6558990478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6294021606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6271286010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7330856323242</t>
+    <t xml:space="preserve">56.9937019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5433883666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9495544433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4793128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9119415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5829620361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9162292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3665199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1899185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.362247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6558952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6294059753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6271324157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7330741882324</t>
   </si>
   <si>
     <t xml:space="preserve">60.5166168212891</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0552177429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5231704711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4452896118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7212295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2998008728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8872833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5134391784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2433319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2077369689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3946533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9376220703125</t>
+    <t xml:space="preserve">61.0552062988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5231781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4452667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7212104797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2997817993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8872718811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5134315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2433280944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2077140808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.394645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9376411437988</t>
   </si>
   <si>
     <t xml:space="preserve">64.4093933105469</t>
   </si>
   <si>
-    <t xml:space="preserve">65.1571197509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5696105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6586303710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2105026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.254997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7979888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1006393432617</t>
+    <t xml:space="preserve">65.1571044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5696258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6586227416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2105178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2549819946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.797981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1006317138672</t>
   </si>
   <si>
     <t xml:space="preserve">65.6911849975586</t>
   </si>
   <si>
-    <t xml:space="preserve">66.4967346191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7281799316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8335876464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9582214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1615524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3039855957031</t>
+    <t xml:space="preserve">66.4967422485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7281646728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8336029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9582061767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1615447998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3039779663086</t>
   </si>
   <si>
     <t xml:space="preserve">65.5220336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">66.3320465087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.260871887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8202438354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2564086914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5189895629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.786003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3988189697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3557357788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1212005615234</t>
+    <t xml:space="preserve">66.3320770263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2608413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8202362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2563858032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5190124511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7860260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3988418579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3556976318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1212158203125</t>
   </si>
   <si>
     <t xml:space="preserve">68.1657333374023</t>
   </si>
   <si>
-    <t xml:space="preserve">68.1568145751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6018676757812</t>
+    <t xml:space="preserve">68.1568069458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6018829345703</t>
   </si>
   <si>
     <t xml:space="preserve">68.3971481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5960464477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1448440551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6194152832031</t>
+    <t xml:space="preserve">67.5960388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1448516845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6194305419922</t>
   </si>
   <si>
     <t xml:space="preserve">72.52734375</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6221923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5153656005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9306640625</t>
+    <t xml:space="preserve">73.6221618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5153732299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9306716918945</t>
   </si>
   <si>
     <t xml:space="preserve">75.6961975097656</t>
   </si>
   <si>
-    <t xml:space="preserve">76.2124633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8355255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4733734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.9362335205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.5623550415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7136993408203</t>
+    <t xml:space="preserve">76.2124481201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8355331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4733352661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.9362106323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.562385559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.7136840820312</t>
   </si>
   <si>
     <t xml:space="preserve">79.8352508544922</t>
   </si>
   <si>
-    <t xml:space="preserve">79.8441619873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8048324584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4318771362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9514007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5694198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7844085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4587478637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3691635131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9033889770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6883926391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6346282958984</t>
+    <t xml:space="preserve">79.8441390991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8048477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4318618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9513702392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5694351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7844390869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4587249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3691253662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9033660888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6883850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.634651184082</t>
   </si>
   <si>
     <t xml:space="preserve">80.5809097290039</t>
   </si>
   <si>
-    <t xml:space="preserve">80.9840087890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8496246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2168426513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0914611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2527008056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2853088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3211364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4888305664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8617935180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7811965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3960266113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6110153198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9782333374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3569564819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.1810302734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6077880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0735473632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2380142211914</t>
+    <t xml:space="preserve">80.9839782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2168807983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0914916992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2527084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2853012084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3211288452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4888381958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8618087768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7811889648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3960418701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6110076904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9782485961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3569488525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1810531616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6077575683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0735549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2380294799805</t>
   </si>
   <si>
     <t xml:space="preserve">83.115837097168</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">83.2949829101562</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2810440063477</t>
+    <t xml:space="preserve">87.2810516357422</t>
   </si>
   <si>
     <t xml:space="preserve">89.2248077392578</t>
   </si>
   <si>
-    <t xml:space="preserve">90.5057067871094</t>
+    <t xml:space="preserve">90.5057144165039</t>
   </si>
   <si>
     <t xml:space="preserve">89.7980804443359</t>
@@ -536,25 +536,25 @@
     <t xml:space="preserve">89.1531524658203</t>
   </si>
   <si>
-    <t xml:space="preserve">85.2477111816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4537582397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8478469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3014450073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.895881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3200912475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9976501464844</t>
+    <t xml:space="preserve">85.2477188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.453727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8478317260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3014373779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8958892822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3201065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9976425170898</t>
   </si>
   <si>
     <t xml:space="preserve">87.7378692626953</t>
@@ -563,268 +563,268 @@
     <t xml:space="preserve">85.3552093505859</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7435913085938</t>
+    <t xml:space="preserve">86.7435989379883</t>
   </si>
   <si>
     <t xml:space="preserve">85.1402282714844</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2681045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2029113769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0660705566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8177719116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6980819702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.1287612915039</t>
+    <t xml:space="preserve">83.2681121826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2029037475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0660552978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.817756652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6980895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.128776550293</t>
   </si>
   <si>
     <t xml:space="preserve">83.447265625</t>
   </si>
   <si>
-    <t xml:space="preserve">82.972541809082</t>
+    <t xml:space="preserve">82.9725112915039</t>
   </si>
   <si>
     <t xml:space="preserve">86.2061538696289</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7289199829102</t>
+    <t xml:space="preserve">87.7289047241211</t>
   </si>
   <si>
     <t xml:space="preserve">90.2369995117188</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3591613769531</t>
+    <t xml:space="preserve">89.3591537475586</t>
   </si>
   <si>
     <t xml:space="preserve">87.9741516113281</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7129135131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5325775146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5685195922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9740753173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3705215454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1991577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8839797973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4063720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2171020507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7665328979492</t>
+    <t xml:space="preserve">87.7128982543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5325927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5685348510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9740600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3705139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1991882324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8840026855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.406379699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2171173095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7665176391602</t>
   </si>
   <si>
     <t xml:space="preserve">93.8475036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0457000732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1541519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6046295166016</t>
+    <t xml:space="preserve">94.0457077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1541366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6046371459961</t>
   </si>
   <si>
     <t xml:space="preserve">88.388542175293</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3162155151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7487716674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8930816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8933410644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8931503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0644226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2627792358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7760620117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5056381225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3253021240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0191116333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1812515258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6315841674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6135635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4513168334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8747787475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6676025390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9920043945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7217559814453</t>
+    <t xml:space="preserve">91.3162002563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.748779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.89306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8933486938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8931655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0644149780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2627868652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7760696411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5056533813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.325309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0190887451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1812438964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6315994262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6135330200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4513092041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8747863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6676177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9919967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7217407226562</t>
   </si>
   <si>
     <t xml:space="preserve">92.3521270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3700637817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6675109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5863647460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4242095947266</t>
+    <t xml:space="preserve">93.3700714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6675338745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5863418579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.424201965332</t>
   </si>
   <si>
     <t xml:space="preserve">93.0998306274414</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6674346923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6586151123047</t>
+    <t xml:space="preserve">92.6674423217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6585998535156</t>
   </si>
   <si>
     <t xml:space="preserve">90.0820693969727</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7666168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5051879882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4150009155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7394180297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.685188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0997314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4962005615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.604377746582</t>
+    <t xml:space="preserve">91.7666091918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5051803588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4150085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7394027709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6851806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0997161865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4961700439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6043548583984</t>
   </si>
   <si>
     <t xml:space="preserve">93.9646148681641</t>
   </si>
   <si>
-    <t xml:space="preserve">94.3970031738281</t>
+    <t xml:space="preserve">94.3970108032227</t>
   </si>
   <si>
     <t xml:space="preserve">94.1717910766602</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3154678344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6569671630859</t>
+    <t xml:space="preserve">96.3154830932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6569595336914</t>
   </si>
   <si>
     <t xml:space="preserve">99.0890960693359</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6751098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.7385406494141</t>
+    <t xml:space="preserve">97.6750640869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.7385482788086</t>
   </si>
   <si>
     <t xml:space="preserve">98.2370681762695</t>
   </si>
   <si>
-    <t xml:space="preserve">99.0437850952148</t>
+    <t xml:space="preserve">99.0437698364258</t>
   </si>
   <si>
     <t xml:space="preserve">99.2522506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">99.3247604370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6963882446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.521224975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.518264770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.475914001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.189025878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.318855285645</t>
+    <t xml:space="preserve">99.3247756958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6963806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.521240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.518272399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.475921630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.189033508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.318870544434</t>
   </si>
   <si>
     <t xml:space="preserve">102.234344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">100.457763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9078216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4969711303711</t>
+    <t xml:space="preserve">100.45777130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9078140258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4969940185547</t>
   </si>
   <si>
     <t xml:space="preserve">99.1616058349609</t>
@@ -833,127 +833,127 @@
     <t xml:space="preserve">99.5966873168945</t>
   </si>
   <si>
-    <t xml:space="preserve">100.865669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.034942626953</t>
+    <t xml:space="preserve">100.865661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.034934997559</t>
   </si>
   <si>
     <t xml:space="preserve">102.524398803711</t>
   </si>
   <si>
-    <t xml:space="preserve">102.823539733887</t>
+    <t xml:space="preserve">102.823532104492</t>
   </si>
   <si>
     <t xml:space="preserve">104.101547241211</t>
   </si>
   <si>
-    <t xml:space="preserve">105.588081359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.446022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.862968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.300971984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.270858764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.352432250977</t>
+    <t xml:space="preserve">105.588088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.446006774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.86296081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.300987243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.27082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.352416992188</t>
   </si>
   <si>
     <t xml:space="preserve">103.494270324707</t>
   </si>
   <si>
-    <t xml:space="preserve">101.346046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.207153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.78727722168</t>
+    <t xml:space="preserve">101.346061706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.207160949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.880851745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.787269592285</t>
   </si>
   <si>
     <t xml:space="preserve">100.068023681641</t>
   </si>
   <si>
-    <t xml:space="preserve">99.0165786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8862686157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.472282409668</t>
+    <t xml:space="preserve">99.0165939331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8862762451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4722671508789</t>
   </si>
   <si>
     <t xml:space="preserve">94.7020568847656</t>
   </si>
   <si>
-    <t xml:space="preserve">95.7716293334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9347686767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7868270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.058723449707</t>
+    <t xml:space="preserve">95.7716217041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9347610473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7867889404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0587310791016</t>
   </si>
   <si>
     <t xml:space="preserve">94.5751419067383</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9739685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.904426574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7775039672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0494384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0342636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3816375732422</t>
+    <t xml:space="preserve">94.9739837646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9044036865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7775192260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0494232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0342483520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3816299438477</t>
   </si>
   <si>
     <t xml:space="preserve">92.4360275268555</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1430206298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3061828613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.755241394043</t>
+    <t xml:space="preserve">93.1430358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3061676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7552490234375</t>
   </si>
   <si>
     <t xml:space="preserve">94.6241989135742</t>
   </si>
   <si>
-    <t xml:space="preserve">95.882942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4815826416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3903961181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.0802536010742</t>
+    <t xml:space="preserve">95.8829574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4816131591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3903732299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0802764892578</t>
   </si>
   <si>
     <t xml:space="preserve">95.1349945068359</t>
@@ -962,133 +962,133 @@
     <t xml:space="preserve">95.4086303710938</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2228698730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9376525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9890670776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5728073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6324157714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5628128051758</t>
+    <t xml:space="preserve">94.2228775024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9376754760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9890518188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5728225708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6324234008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5628051757812</t>
   </si>
   <si>
     <t xml:space="preserve">93.0918350219727</t>
   </si>
   <si>
-    <t xml:space="preserve">90.5834808349609</t>
+    <t xml:space="preserve">90.5834732055664</t>
   </si>
   <si>
     <t xml:space="preserve">91.2128448486328</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7999267578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4201965332031</t>
+    <t xml:space="preserve">92.7999496459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4201812744141</t>
   </si>
   <si>
     <t xml:space="preserve">93.4931564331055</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9094085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6357574462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3107376098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2608871459961</t>
+    <t xml:space="preserve">92.9094009399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6357345581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3107452392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2608947753906</t>
   </si>
   <si>
     <t xml:space="preserve">89.8720016479492</t>
   </si>
   <si>
-    <t xml:space="preserve">90.3098220825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3405303955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2709121704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3621215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7567825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1249694824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3885726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.652214050293</t>
+    <t xml:space="preserve">90.3098297119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3405380249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2709274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3621368408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7567672729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1249771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3885803222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6522064208984</t>
   </si>
   <si>
     <t xml:space="preserve">87.5643310546875</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4764633178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0203857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.50048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3819122314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.5244903564453</t>
+    <t xml:space="preserve">88.4764556884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.020378112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5004959106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3818969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.5244750976562</t>
   </si>
   <si>
     <t xml:space="preserve">86.9349594116211</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9474029541016</t>
+    <t xml:space="preserve">87.9474182128906</t>
   </si>
   <si>
     <t xml:space="preserve">89.3065032958984</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3703384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9507675170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2243804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1183090209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.775032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3040542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.917610168457</t>
+    <t xml:space="preserve">89.3703460693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9507598876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2243881225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1183013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7750091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.304069519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">90.5469818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">89.4980545043945</t>
+    <t xml:space="preserve">89.498046875</t>
   </si>
   <si>
     <t xml:space="preserve">92.7452163696289</t>
@@ -1097,31 +1097,31 @@
     <t xml:space="preserve">91.7418746948242</t>
   </si>
   <si>
-    <t xml:space="preserve">91.4317321777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0702362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4236679077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4407958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7804489135742</t>
+    <t xml:space="preserve">91.4317474365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0702438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4236602783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4407806396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7804641723633</t>
   </si>
   <si>
     <t xml:space="preserve">92.7908782958984</t>
   </si>
   <si>
-    <t xml:space="preserve">93.0479202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0748138427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4230499267578</t>
+    <t xml:space="preserve">93.0479125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.074836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4230270385742</t>
   </si>
   <si>
     <t xml:space="preserve">91.9095993041992</t>
@@ -1130,127 +1130,127 @@
     <t xml:space="preserve">92.7541351318359</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8190078735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6084899902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8104553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2878189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0197448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7712783813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6990432739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9194030761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0381011962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6800994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7443695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9928207397461</t>
+    <t xml:space="preserve">93.8190155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6085052490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8104705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2878265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0197601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7712936401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6990661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9193954467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0381164550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6800918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7443618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9928359985352</t>
   </si>
   <si>
     <t xml:space="preserve">94.9389724731445</t>
   </si>
   <si>
-    <t xml:space="preserve">96.7015075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4065475463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6635665893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4334716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9940490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4713897705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6354064941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9634552001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5044326782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4224243164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8814392089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3404312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.796989440918</t>
+    <t xml:space="preserve">96.7015151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4065322875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6635818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4334487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9940567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4713973999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6353988647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9634246826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5044479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4224472045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8814315795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3404235839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7969741821289</t>
   </si>
   <si>
     <t xml:space="preserve">88.5589141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">89.8165588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2033462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6886596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1397094726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7174301147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0944061279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0932006835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8006591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4885330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0209884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1495056152344</t>
+    <t xml:space="preserve">89.8165817260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2033538818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6886672973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1396942138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7174224853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0944290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0931701660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.800666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4885406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0209579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1494903564453</t>
   </si>
   <si>
     <t xml:space="preserve">94.4616165161133</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4500732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.650993347168</t>
+    <t xml:space="preserve">93.4500885009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6510009765625</t>
   </si>
   <si>
     <t xml:space="preserve">94.7433700561523</t>
@@ -1259,37 +1259,37 @@
     <t xml:space="preserve">95.4824142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">96.0921020507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6856231689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0158615112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5493774414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8634338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3830795288086</t>
+    <t xml:space="preserve">96.0920944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6856307983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0158767700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5493698120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8634490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3830718994141</t>
   </si>
   <si>
     <t xml:space="preserve">97.1267318725586</t>
   </si>
   <si>
-    <t xml:space="preserve">98.4939346313477</t>
+    <t xml:space="preserve">98.4939422607422</t>
   </si>
   <si>
     <t xml:space="preserve">100.600173950195</t>
   </si>
   <si>
-    <t xml:space="preserve">99.9165573120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.359970092773</t>
+    <t xml:space="preserve">99.9165649414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.359985351562</t>
   </si>
   <si>
     <t xml:space="preserve">100.21216583252</t>
@@ -1298,79 +1298,79 @@
     <t xml:space="preserve">100.784927368164</t>
   </si>
   <si>
-    <t xml:space="preserve">100.711029052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.727180480957</t>
+    <t xml:space="preserve">100.71102142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.727172851562</t>
   </si>
   <si>
     <t xml:space="preserve">104.202926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">107.269905090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.008918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.429237365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.653259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.988143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.064353942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.34147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.265251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.135932922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.819526672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.893424987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.886489868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.105888366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.269866943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.454635620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.50772857666</t>
+    <t xml:space="preserve">107.269897460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.008911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.429214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.653251647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.988136291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.064346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.341484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.265266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.135925292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.819541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.893432617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.886505126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.105895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.269874572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.454643249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.507743835449</t>
   </si>
   <si>
     <t xml:space="preserve">117.062019348145</t>
   </si>
   <si>
-    <t xml:space="preserve">117.376083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.710983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.486953735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.394554138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.320655822754</t>
+    <t xml:space="preserve">117.376106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.710952758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.486946105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.394569396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.320693969727</t>
   </si>
   <si>
     <t xml:space="preserve">117.413040161133</t>
@@ -1382,58 +1382,58 @@
     <t xml:space="preserve">118.115127563477</t>
   </si>
   <si>
-    <t xml:space="preserve">120.092041015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.135917663574</t>
+    <t xml:space="preserve">120.092018127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.135902404785</t>
   </si>
   <si>
     <t xml:space="preserve">117.339141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">119.611640930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.156677246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473052978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.274459838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.292961120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.586242675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.549072265625</t>
+    <t xml:space="preserve">119.61164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.156684875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473098754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.274482727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.292945861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.586280822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.549049377441</t>
   </si>
   <si>
     <t xml:space="preserve">121.248527526855</t>
   </si>
   <si>
-    <t xml:space="preserve">120.616844177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.229949951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.270385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.78736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.780769348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.04963684082</t>
+    <t xml:space="preserve">120.616836547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.229957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.270370483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.787353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.780784606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.049621582031</t>
   </si>
   <si>
     <t xml:space="preserve">116.009170532227</t>
@@ -1442,103 +1442,103 @@
     <t xml:space="preserve">113.01789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">104.620056152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.057220458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.441947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.104232788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.306442260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.507537841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.881294250488</t>
+    <t xml:space="preserve">104.620063781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.057228088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.441932678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.10424041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.306434631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.507522583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.881278991699</t>
   </si>
   <si>
     <t xml:space="preserve">110.937019348145</t>
   </si>
   <si>
-    <t xml:space="preserve">115.135963439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.70093536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.565437316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.609169006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.123916625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.597137451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.056190490723</t>
+    <t xml:space="preserve">115.135955810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.700942993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.5654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.609161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.123924255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.597145080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.056182861328</t>
   </si>
   <si>
     <t xml:space="preserve">116.120635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">104.768699645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.270347595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.771987915039</t>
+    <t xml:space="preserve">104.768684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270332336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.77197265625</t>
   </si>
   <si>
     <t xml:space="preserve">110.844123840332</t>
   </si>
   <si>
-    <t xml:space="preserve">111.680213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.365447998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.798225402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.694427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.300971984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623405456543</t>
+    <t xml:space="preserve">111.680198669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.365455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.79825592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.694450378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.300964355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623413085938</t>
   </si>
   <si>
     <t xml:space="preserve">123.552383422852</t>
   </si>
   <si>
-    <t xml:space="preserve">126.339248657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.661666870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.913116455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.448577880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.628875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.377548217773</t>
+    <t xml:space="preserve">126.339294433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.661651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.913055419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.44856262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.628921508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.377487182617</t>
   </si>
   <si>
     <t xml:space="preserve">134.235458374023</t>
@@ -1550,277 +1550,277 @@
     <t xml:space="preserve">139.67919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">140.217987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.557907104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.232162475586</t>
+    <t xml:space="preserve">140.218017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.557861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.232177734375</t>
   </si>
   <si>
     <t xml:space="preserve">132.117416381836</t>
   </si>
   <si>
-    <t xml:space="preserve">129.367706298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.27262878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.405960083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.492248535156</t>
+    <t xml:space="preserve">129.367645263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.272598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.405975341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.492294311523</t>
   </si>
   <si>
     <t xml:space="preserve">132.154602050781</t>
   </si>
   <si>
-    <t xml:space="preserve">135.183029174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.263870239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.833236694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.88932800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.347778320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.561569213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.050888061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.911804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.942657470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.689559936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.399230957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.346977233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.77188873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.766159057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.560791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.589736938477</t>
+    <t xml:space="preserve">135.183013916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.263900756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.833297729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.889312744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.347763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.561584472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.050872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.911773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.942642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.689590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.399185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.346992492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.771926879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.76619720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.560775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.589744567871</t>
   </si>
   <si>
     <t xml:space="preserve">125.95482635498</t>
   </si>
   <si>
-    <t xml:space="preserve">124.180839538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.002471923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.873672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.143501281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.554298400879</t>
+    <t xml:space="preserve">124.180847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.002464294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.873664855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.143486022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.554260253906</t>
   </si>
   <si>
     <t xml:space="preserve">121.84659576416</t>
   </si>
   <si>
-    <t xml:space="preserve">120.016563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.972724914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.142349243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.077941894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.011672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.650360107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.322647094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.984588623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.455215454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.621383666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.488754272461</t>
+    <t xml:space="preserve">120.016571044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.972732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.142364501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.077972412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.011657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.650314331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.322601318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.984558105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.455230712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.621353149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.488800048828</t>
   </si>
   <si>
     <t xml:space="preserve">134.619476318359</t>
   </si>
   <si>
-    <t xml:space="preserve">136.412231445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.374847412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.441131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.484970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.05549621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.148864746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.225463867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.123687744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.430847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.208679199219</t>
+    <t xml:space="preserve">136.412185668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.374816894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.441116333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.484985351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.055511474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.148834228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.225387573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.123657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.43083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.208694458008</t>
   </si>
   <si>
     <t xml:space="preserve">135.179672241211</t>
   </si>
   <si>
-    <t xml:space="preserve">133.125579833984</t>
+    <t xml:space="preserve">133.125640869141</t>
   </si>
   <si>
     <t xml:space="preserve">135.833282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">135.795928955078</t>
+    <t xml:space="preserve">135.795974731445</t>
   </si>
   <si>
     <t xml:space="preserve">131.239547729492</t>
   </si>
   <si>
-    <t xml:space="preserve">127.355361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.448753356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.793228149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.334007263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.802795410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.47314453125</t>
+    <t xml:space="preserve">127.355377197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.448776245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.79328918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.334022521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.802772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.473136901855</t>
   </si>
   <si>
     <t xml:space="preserve">122.854988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">121.155670166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.717803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.80086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.875549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.736465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.221977233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.245338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.733657836914</t>
+    <t xml:space="preserve">121.155693054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.717796325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.800880432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.87557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.736473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.221992492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.245346069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.733673095703</t>
   </si>
   <si>
     <t xml:space="preserve">120.409812927246</t>
   </si>
   <si>
-    <t xml:space="preserve">120.578834533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.480346679688</t>
+    <t xml:space="preserve">120.578804016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.48038482666</t>
   </si>
   <si>
     <t xml:space="preserve">120.071731567383</t>
   </si>
   <si>
-    <t xml:space="preserve">118.174774169922</t>
+    <t xml:space="preserve">118.174758911133</t>
   </si>
   <si>
     <t xml:space="preserve">118.062088012695</t>
   </si>
   <si>
-    <t xml:space="preserve">119.207763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.423500061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.170211791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.479827880859</t>
+    <t xml:space="preserve">119.20777130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.42350769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.170204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.479850769043</t>
   </si>
   <si>
     <t xml:space="preserve">116.446846008301</t>
   </si>
   <si>
-    <t xml:space="preserve">116.052429199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.832130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.301666259766</t>
+    <t xml:space="preserve">116.052436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.832138061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.30167388916</t>
   </si>
   <si>
     <t xml:space="preserve">118.099655151367</t>
   </si>
   <si>
-    <t xml:space="preserve">118.625518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.799133300781</t>
+    <t xml:space="preserve">118.625526428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.799156188965</t>
   </si>
   <si>
     <t xml:space="preserve">121.686973571777</t>
@@ -1829,22 +1829,22 @@
     <t xml:space="preserve">117.592544555664</t>
   </si>
   <si>
-    <t xml:space="preserve">117.554969787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.639755249023</t>
+    <t xml:space="preserve">117.554962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.639747619629</t>
   </si>
   <si>
     <t xml:space="preserve">120.710311889648</t>
   </si>
   <si>
-    <t xml:space="preserve">120.729095458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.611824035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.597618103027</t>
+    <t xml:space="preserve">120.729072570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.61181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.597595214844</t>
   </si>
   <si>
     <t xml:space="preserve">120.334671020508</t>
@@ -1856,97 +1856,97 @@
     <t xml:space="preserve">120.785430908203</t>
   </si>
   <si>
-    <t xml:space="preserve">118.193550109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.709800720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.977279663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.747367858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.108772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.424018859863</t>
+    <t xml:space="preserve">118.193557739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.70979309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.977317810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.747375488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.108764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.424026489258</t>
   </si>
   <si>
     <t xml:space="preserve">124.335166931152</t>
   </si>
   <si>
-    <t xml:space="preserve">123.546340942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.231636047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.869689941406</t>
+    <t xml:space="preserve">123.546379089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.23161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.869705200195</t>
   </si>
   <si>
     <t xml:space="preserve">117.06665802002</t>
   </si>
   <si>
-    <t xml:space="preserve">117.34838104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.150917053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.122467041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.615371704102</t>
+    <t xml:space="preserve">117.348365783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.150901794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.12247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.615379333496</t>
   </si>
   <si>
     <t xml:space="preserve">111.939224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">113.347854614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.563591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.229568481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.835166931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.530082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.666130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.684913635254</t>
+    <t xml:space="preserve">113.347869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.563606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.229598999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.835159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.530097961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.666122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.684906005859</t>
   </si>
   <si>
     <t xml:space="preserve">106.511306762695</t>
   </si>
   <si>
-    <t xml:space="preserve">118.13720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.221481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.202659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.5732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.104225158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.319946289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.939117431641</t>
+    <t xml:space="preserve">118.137229919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.221473693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.202682495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.573249816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.104217529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.319953918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.939102172852</t>
   </si>
   <si>
     <t xml:space="preserve">113.97834777832</t>
@@ -1955,61 +1955,61 @@
     <t xml:space="preserve">113.354804992676</t>
   </si>
   <si>
-    <t xml:space="preserve">112.221076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.504486083984</t>
+    <t xml:space="preserve">112.221069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.504493713379</t>
   </si>
   <si>
     <t xml:space="preserve">112.164375305176</t>
   </si>
   <si>
-    <t xml:space="preserve">116.359199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.901290893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.338821411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.449279785156</t>
+    <t xml:space="preserve">116.359222412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.901298522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.338829040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.449264526367</t>
   </si>
   <si>
     <t xml:space="preserve">114.318473815918</t>
   </si>
   <si>
-    <t xml:space="preserve">115.830108642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.828643798828</t>
+    <t xml:space="preserve">115.830116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.828666687012</t>
   </si>
   <si>
     <t xml:space="preserve">113.846076965332</t>
   </si>
   <si>
-    <t xml:space="preserve">112.447807312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.469650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.151344299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.65145111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.841850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.353507995605</t>
+    <t xml:space="preserve">112.447799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.469635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.151336669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.651428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.841835021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.353492736816</t>
   </si>
   <si>
     <t xml:space="preserve">124.843322753906</t>
   </si>
   <si>
-    <t xml:space="preserve">126.411666870117</t>
+    <t xml:space="preserve">126.411643981934</t>
   </si>
   <si>
     <t xml:space="preserve">133.327453613281</t>
@@ -2021,178 +2021,178 @@
     <t xml:space="preserve">131.267837524414</t>
   </si>
   <si>
-    <t xml:space="preserve">129.737319946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.964019775391</t>
+    <t xml:space="preserve">129.737289428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.96403503418</t>
   </si>
   <si>
     <t xml:space="preserve">129.416076660156</t>
   </si>
   <si>
-    <t xml:space="preserve">127.583183288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.471282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.113754272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.827392578125</t>
+    <t xml:space="preserve">127.58317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.471267700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.113723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.827362060547</t>
   </si>
   <si>
     <t xml:space="preserve">126.392761230469</t>
   </si>
   <si>
-    <t xml:space="preserve">127.904411315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.016311645508</t>
+    <t xml:space="preserve">127.904449462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.016342163086</t>
   </si>
   <si>
     <t xml:space="preserve">128.603546142578</t>
   </si>
   <si>
-    <t xml:space="preserve">145.118347167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.978668212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.645965576172</t>
+    <t xml:space="preserve">145.11833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.978713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.645904541016</t>
   </si>
   <si>
     <t xml:space="preserve">146.11979675293</t>
   </si>
   <si>
-    <t xml:space="preserve">148.047164916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.839309692383</t>
+    <t xml:space="preserve">148.047119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.839279174805</t>
   </si>
   <si>
     <t xml:space="preserve">152.714370727539</t>
   </si>
   <si>
-    <t xml:space="preserve">156.833633422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.076309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.760986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.032821655273</t>
+    <t xml:space="preserve">156.833602905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.076324462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.760925292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.032836914062</t>
   </si>
   <si>
     <t xml:space="preserve">164.996490478516</t>
   </si>
   <si>
-    <t xml:space="preserve">161.992111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.125854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.349670410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.804641723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.720260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.962936401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.137390136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.704284667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.461578369141</t>
+    <t xml:space="preserve">161.992141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.125823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.349685668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.804656982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.72021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.962966918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.137435913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.704299926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.461547851562</t>
   </si>
   <si>
     <t xml:space="preserve">156.814697265625</t>
   </si>
   <si>
-    <t xml:space="preserve">159.157745361328</t>
+    <t xml:space="preserve">159.157760620117</t>
   </si>
   <si>
     <t xml:space="preserve">158.008773803711</t>
   </si>
   <si>
-    <t xml:space="preserve">160.819519042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.560806274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.794036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.161407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.831954956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.856872558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.932189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.205276489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.964889526367</t>
+    <t xml:space="preserve">160.819534301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.56086730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.793991088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.161361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.831985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.856842041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.932159423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.205261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.964920043945</t>
   </si>
   <si>
     <t xml:space="preserve">157.970809936523</t>
   </si>
   <si>
-    <t xml:space="preserve">159.907897949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.376815795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.75666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.958374023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.338195800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.617126464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.884353637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.409545898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.890197753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.661682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.326385498047</t>
+    <t xml:space="preserve">159.907943725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.376846313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.756652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.958358764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.338180541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.617172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.884338378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.409561157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.890243530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.661666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.326370239258</t>
   </si>
   <si>
     <t xml:space="preserve">151.741592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">151.931533813477</t>
+    <t xml:space="preserve">151.931518554688</t>
   </si>
   <si>
     <t xml:space="preserve">149.082824707031</t>
@@ -2201,10 +2201,10 @@
     <t xml:space="preserve">147.183654785156</t>
   </si>
   <si>
-    <t xml:space="preserve">147.753433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.133239746094</t>
+    <t xml:space="preserve">147.753387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.133224487305</t>
   </si>
   <si>
     <t xml:space="preserve">149.462631225586</t>
@@ -2213,16 +2213,16 @@
     <t xml:space="preserve">145.47444152832</t>
   </si>
   <si>
-    <t xml:space="preserve">146.993759155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.892913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.602142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.792022705078</t>
+    <t xml:space="preserve">146.993774414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.89289855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.602111816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.792007446289</t>
   </si>
   <si>
     <t xml:space="preserve">151.399765014648</t>
@@ -2231,22 +2231,22 @@
     <t xml:space="preserve">151.456741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">148.703002929688</t>
+    <t xml:space="preserve">148.703018188477</t>
   </si>
   <si>
     <t xml:space="preserve">145.284530639648</t>
   </si>
   <si>
-    <t xml:space="preserve">146.234115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.854248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.904708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.424011230469</t>
+    <t xml:space="preserve">146.234100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.854278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.904678344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.424026489258</t>
   </si>
   <si>
     <t xml:space="preserve">148.323150634766</t>
@@ -2255,202 +2255,202 @@
     <t xml:space="preserve">149.84245300293</t>
   </si>
   <si>
-    <t xml:space="preserve">150.412216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.652557373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.513061523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.803833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.955108642578</t>
+    <t xml:space="preserve">150.412200927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.652587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.513076782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.803848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.955123901367</t>
   </si>
   <si>
     <t xml:space="preserve">140.346740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">141.486251831055</t>
+    <t xml:space="preserve">141.486221313477</t>
   </si>
   <si>
     <t xml:space="preserve">143.575271606445</t>
   </si>
   <si>
-    <t xml:space="preserve">146.044174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.121444702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.691162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.071029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.83659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.693511962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.220932006836</t>
+    <t xml:space="preserve">146.044189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.121429443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.691192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.070983886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.836578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.693557739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.220916748047</t>
   </si>
   <si>
     <t xml:space="preserve">154.457229614258</t>
   </si>
   <si>
-    <t xml:space="preserve">152.92985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.979919433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.175537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.70295715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.984634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.361801147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.748291015625</t>
+    <t xml:space="preserve">152.929840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.979904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.175506591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.702941894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.984619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.361755371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.748321533203</t>
   </si>
   <si>
     <t xml:space="preserve">157.225631713867</t>
   </si>
   <si>
-    <t xml:space="preserve">154.839065551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.366500854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.803070068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.640365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.876678466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.07698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.000305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.365707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.749923706055</t>
+    <t xml:space="preserve">154.839080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.366485595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.803115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.640380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.876663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.076965332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.00032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.365737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.749938964844</t>
   </si>
   <si>
     <t xml:space="preserve">175.840667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">176.222518920898</t>
+    <t xml:space="preserve">176.222549438477</t>
   </si>
   <si>
     <t xml:space="preserve">178.22721862793</t>
   </si>
   <si>
-    <t xml:space="preserve">176.270263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.038665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.799987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.265548706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.243682861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.527740478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.09342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.432250976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.291397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.102828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.773391723633</t>
+    <t xml:space="preserve">176.270248413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.038650512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.800003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.265563964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.243667602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.527694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.093414306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.432205200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.291412353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.102813720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.773406982422</t>
   </si>
   <si>
     <t xml:space="preserve">189.491714477539</t>
   </si>
   <si>
-    <t xml:space="preserve">188.9189453125</t>
+    <t xml:space="preserve">188.918960571289</t>
   </si>
   <si>
     <t xml:space="preserve">189.969039916992</t>
   </si>
   <si>
-    <t xml:space="preserve">188.775741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.069229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.682662963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.446350097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.828201293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.584838867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.677947998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.296112060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.591873168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.973724365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.882949829102</t>
+    <t xml:space="preserve">188.775756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.069198608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.682632446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.446334838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.828186035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.584823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.677932739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.296081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.591888427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.973739624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.882995605469</t>
   </si>
   <si>
     <t xml:space="preserve">195.983139038086</t>
   </si>
   <si>
-    <t xml:space="preserve">197.415084838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.269515991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">199.515213012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.319610595703</t>
+    <t xml:space="preserve">197.415054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.26953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">199.515243530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.319564819336</t>
   </si>
   <si>
     <t xml:space="preserve">196.842269897461</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">197.987808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">207.15217590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.739013671875</t>
+    <t xml:space="preserve">207.152145385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.739028930664</t>
   </si>
   <si>
     <t xml:space="preserve">212.975341796875</t>
@@ -2471,34 +2471,34 @@
     <t xml:space="preserve">213.929962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">218.321151733398</t>
+    <t xml:space="preserve">218.321197509766</t>
   </si>
   <si>
     <t xml:space="preserve">218.703063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">217.366592407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.498092651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.564331054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.917999267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.930191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.534713745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.067840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.205444335938</t>
+    <t xml:space="preserve">217.366546630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.498077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.564315795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.917984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.930221557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.534729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.067810058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.205490112305</t>
   </si>
   <si>
     <t xml:space="preserve">214.444076538086</t>
@@ -2507,67 +2507,67 @@
     <t xml:space="preserve">214.156631469727</t>
   </si>
   <si>
-    <t xml:space="preserve">213.294250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.048614501953</t>
+    <t xml:space="preserve">213.294235229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.048599243164</t>
   </si>
   <si>
     <t xml:space="preserve">214.060775756836</t>
   </si>
   <si>
-    <t xml:space="preserve">211.186218261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.736694335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.982360839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.269805908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.994598388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.461486816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.970153808594</t>
+    <t xml:space="preserve">211.186233520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.736724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.982376098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.269836425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.994552612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.46142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.970123291016</t>
   </si>
   <si>
     <t xml:space="preserve">198.058959960938</t>
   </si>
   <si>
-    <t xml:space="preserve">196.621627807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.447418212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.920394897461</t>
+    <t xml:space="preserve">196.621612548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.447402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.920364379883</t>
   </si>
   <si>
     <t xml:space="preserve">191.495315551758</t>
   </si>
   <si>
-    <t xml:space="preserve">187.902084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.087600708008</t>
+    <t xml:space="preserve">187.902069091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.087615966797</t>
   </si>
   <si>
     <t xml:space="preserve">189.531005859375</t>
   </si>
   <si>
-    <t xml:space="preserve">189.626815795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.997894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.632949829102</t>
+    <t xml:space="preserve">189.626800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.99787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.632934570312</t>
   </si>
   <si>
     <t xml:space="preserve">190.537109375</t>
@@ -2576,28 +2576,28 @@
     <t xml:space="preserve">185.889862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">182.152862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.572799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.651245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.770538330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.410781860352</t>
+    <t xml:space="preserve">182.152893066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.572814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.651260375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.770553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.410766601562</t>
   </si>
   <si>
     <t xml:space="preserve">190.39338684082</t>
   </si>
   <si>
-    <t xml:space="preserve">188.237426757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.501403808594</t>
+    <t xml:space="preserve">188.237411499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.501419067383</t>
   </si>
   <si>
     <t xml:space="preserve">193.172149658203</t>
@@ -2609,145 +2609,145 @@
     <t xml:space="preserve">193.555419921875</t>
   </si>
   <si>
-    <t xml:space="preserve">193.938705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">194.992706298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.471786499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.442245483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.72966003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.358596801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.538040161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.921340942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.987564086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.849884033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.215835571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.832504272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.802886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.353393554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.006805419922</t>
+    <t xml:space="preserve">193.938674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194.992721557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.471801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.442230224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.729690551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.358612060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.538055419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.921325683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.987548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.849945068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.2158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.832534790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.802932739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.353439331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.006790161133</t>
   </si>
   <si>
     <t xml:space="preserve">217.989395141602</t>
   </si>
   <si>
-    <t xml:space="preserve">215.593887329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.977203369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.905792236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220.768127441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.892761230469</t>
+    <t xml:space="preserve">215.593902587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.977188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.905807495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.768142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.892776489258</t>
   </si>
   <si>
     <t xml:space="preserve">217.161651611328</t>
   </si>
   <si>
-    <t xml:space="preserve">219.277450561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.297103881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.200942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.316787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.66325378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.509124755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.182342529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.067596435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.162704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.064376831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.238128662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.198791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.756195068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.351852416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203.985748291016</t>
+    <t xml:space="preserve">219.277465820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.297134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.200958251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.316802978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.663238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.509140014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.182373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.06755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.162658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.064392089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.23811340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.198822021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.756210327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.351837158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203.985763549805</t>
   </si>
   <si>
     <t xml:space="preserve">208.313598632812</t>
   </si>
   <si>
-    <t xml:space="preserve">207.640365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.507019042969</t>
+    <t xml:space="preserve">207.640335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.506988525391</t>
   </si>
   <si>
     <t xml:space="preserve">212.929946899414</t>
   </si>
   <si>
-    <t xml:space="preserve">229.279602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">237.646774291992</t>
+    <t xml:space="preserve">229.279541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.646759033203</t>
   </si>
   <si>
     <t xml:space="preserve">227.25993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">225.625</t>
+    <t xml:space="preserve">225.624969482422</t>
   </si>
   <si>
     <t xml:space="preserve">224.567047119141</t>
   </si>
   <si>
-    <t xml:space="preserve">232.068649291992</t>
+    <t xml:space="preserve">232.068634033203</t>
   </si>
   <si>
     <t xml:space="preserve">235.819442749023</t>
@@ -2756,52 +2756,52 @@
     <t xml:space="preserve">235.434722900391</t>
   </si>
   <si>
-    <t xml:space="preserve">235.53092956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">228.317825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.644622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220.527709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.662139892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.123336791992</t>
+    <t xml:space="preserve">235.530914306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">228.317840576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.644638061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.527725219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.662170410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.123352050781</t>
   </si>
   <si>
     <t xml:space="preserve">219.373641967773</t>
   </si>
   <si>
-    <t xml:space="preserve">212.256713867188</t>
+    <t xml:space="preserve">212.256744384766</t>
   </si>
   <si>
     <t xml:space="preserve">206.19775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">207.544219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.409759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.102630615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.948577880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.15950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.042572021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.869903564453</t>
+    <t xml:space="preserve">207.544204711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.409729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.102661132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.948547363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.159530639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.042602539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.869918823242</t>
   </si>
   <si>
     <t xml:space="preserve">205.813049316406</t>
@@ -2813,34 +2813,34 @@
     <t xml:space="preserve">207.928894042969</t>
   </si>
   <si>
-    <t xml:space="preserve">208.986831665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.794464111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.352935791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.101577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.639312744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.158447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.139862060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.927825927734</t>
+    <t xml:space="preserve">208.98681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.794479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.352890014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.101608276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.639297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.158432006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.139831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.927810668945</t>
   </si>
   <si>
     <t xml:space="preserve">200.234939575195</t>
   </si>
   <si>
-    <t xml:space="preserve">198.959457397461</t>
+    <t xml:space="preserve">198.959442138672</t>
   </si>
   <si>
     <t xml:space="preserve">207.076293945312</t>
@@ -2858,19 +2858,19 @@
     <t xml:space="preserve">200.892028808594</t>
   </si>
   <si>
-    <t xml:space="preserve">203.404403686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.916748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.626846313477</t>
+    <t xml:space="preserve">203.404357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.916763305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.626861572266</t>
   </si>
   <si>
     <t xml:space="preserve">216.256057739258</t>
   </si>
   <si>
-    <t xml:space="preserve">214.130218505859</t>
+    <t xml:space="preserve">214.130249023438</t>
   </si>
   <si>
     <t xml:space="preserve">214.806655883789</t>
@@ -2882,79 +2882,79 @@
     <t xml:space="preserve">223.116714477539</t>
   </si>
   <si>
-    <t xml:space="preserve">229.39762878418</t>
+    <t xml:space="preserve">229.397613525391</t>
   </si>
   <si>
     <t xml:space="preserve">231.90998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">233.262786865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">232.393157958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.233551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">237.417846679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">236.161636352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.312225341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.408874511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">246.307723999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.332458496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.651519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">249.883010864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.52571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.105484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.294235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.004364013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.622344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.008865356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250.656066894531</t>
+    <t xml:space="preserve">233.262802124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.393127441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.233596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.417861938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">236.161666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.312255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.40885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">246.307693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.332443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.651550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">249.883041381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.525756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.105499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.294250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.004348754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.622283935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.008880615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250.656051635742</t>
   </si>
   <si>
     <t xml:space="preserve">253.844787597656</t>
   </si>
   <si>
-    <t xml:space="preserve">257.468414306641</t>
+    <t xml:space="preserve">257.468444824219</t>
   </si>
   <si>
     <t xml:space="preserve">260.802124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">266.020050048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.48974609375</t>
+    <t xml:space="preserve">266.020080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.489776611328</t>
   </si>
   <si>
     <t xml:space="preserve">276.890838623047</t>
@@ -2963,67 +2963,67 @@
     <t xml:space="preserve">275.006652832031</t>
   </si>
   <si>
-    <t xml:space="preserve">274.668395996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.305511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.692016601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.295349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.555999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.796478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.347015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.869567871094</t>
+    <t xml:space="preserve">274.66845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.305480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.691925048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.295318603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.556060791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.79655456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.347091674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.869537353516</t>
   </si>
   <si>
     <t xml:space="preserve">269.595367431641</t>
   </si>
   <si>
-    <t xml:space="preserve">268.822326660156</t>
+    <t xml:space="preserve">268.822387695312</t>
   </si>
   <si>
     <t xml:space="preserve">265.730163574219</t>
   </si>
   <si>
-    <t xml:space="preserve">265.536895751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">264.957153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.339233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.102081298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.942565917969</t>
+    <t xml:space="preserve">265.536926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">264.957183837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.339202880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.102142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.942504882812</t>
   </si>
   <si>
     <t xml:space="preserve">258.579650878906</t>
   </si>
   <si>
-    <t xml:space="preserve">266.454895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">267.405242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">281.854370117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">277.005706787109</t>
+    <t xml:space="preserve">266.454986572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">267.405303955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281.854309082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">277.005615234375</t>
   </si>
   <si>
     <t xml:space="preserve">274.290435791016</t>
@@ -3032,169 +3032,169 @@
     <t xml:space="preserve">263.623291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">271.090240478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.599517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.108428955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">280.642181396484</t>
+    <t xml:space="preserve">271.090209960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.599578857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.108520507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">280.642211914062</t>
   </si>
   <si>
     <t xml:space="preserve">281.466491699219</t>
   </si>
   <si>
-    <t xml:space="preserve">282.630249023438</t>
+    <t xml:space="preserve">282.630157470703</t>
   </si>
   <si>
     <t xml:space="preserve">274.532836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">280.205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">278.411773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">284.084716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.769439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.066223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270.750885009766</t>
+    <t xml:space="preserve">280.205780029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">278.411804199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">284.084777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.769409179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.066192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270.750854492188</t>
   </si>
   <si>
     <t xml:space="preserve">268.472015380859</t>
   </si>
   <si>
-    <t xml:space="preserve">271.817535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.611267089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.253967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270.847808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.484313964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.720947265625</t>
+    <t xml:space="preserve">271.817565917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.611236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.253936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270.847747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.720916748047</t>
   </si>
   <si>
     <t xml:space="preserve">284.763549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">298.291412353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.455078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.576110839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.552032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.679321289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.843017578125</t>
+    <t xml:space="preserve">298.291473388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.455108642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.576141357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.552093505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.679290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.842987060547</t>
   </si>
   <si>
     <t xml:space="preserve">302.946166992188</t>
   </si>
   <si>
-    <t xml:space="preserve">303.721984863281</t>
+    <t xml:space="preserve">303.721954345703</t>
   </si>
   <si>
     <t xml:space="preserve">314.049682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">312.740478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.019378662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.364990234375</t>
+    <t xml:space="preserve">312.740539550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.019409179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.364929199219</t>
   </si>
   <si>
     <t xml:space="preserve">309.443450927734</t>
   </si>
   <si>
-    <t xml:space="preserve">311.625305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.12255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.213317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.879791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.825164794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.916229248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.837493896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.231567382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.4677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.631469726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.661804199219</t>
+    <t xml:space="preserve">311.625335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.122528076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.213287353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.879760742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.825042724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.916259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.837432861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.231536865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.467803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.631530761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.661834716797</t>
   </si>
   <si>
     <t xml:space="preserve">308.425170898438</t>
   </si>
   <si>
-    <t xml:space="preserve">308.473724365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.667236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.854705810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">288.836456298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.369842529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.284851074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">285.539367675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">283.842315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.806793212891</t>
+    <t xml:space="preserve">308.4736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.667266845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.854675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">288.836517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.369812011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.284912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">285.539428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">283.842376708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.806823730469</t>
   </si>
   <si>
     <t xml:space="preserve">297.298828125</t>
@@ -3203,10 +3203,10 @@
     <t xml:space="preserve">298.369110107422</t>
   </si>
   <si>
-    <t xml:space="preserve">305.812530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.574645996094</t>
+    <t xml:space="preserve">305.812561035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.574676513672</t>
   </si>
   <si>
     <t xml:space="preserve">312.428924560547</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">309.996429443359</t>
   </si>
   <si>
-    <t xml:space="preserve">311.358673095703</t>
+    <t xml:space="preserve">311.358642578125</t>
   </si>
   <si>
     <t xml:space="preserve">309.41259765625</t>
@@ -3227,43 +3227,43 @@
     <t xml:space="preserve">314.22900390625</t>
   </si>
   <si>
-    <t xml:space="preserve">303.234069824219</t>
+    <t xml:space="preserve">303.234130859375</t>
   </si>
   <si>
     <t xml:space="preserve">299.925933837891</t>
   </si>
   <si>
-    <t xml:space="preserve">294.185272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.250183105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.217803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.888031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.596252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.9638671875</t>
+    <t xml:space="preserve">294.185241699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.250152587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.217834472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.888000488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.596282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.963836669922</t>
   </si>
   <si>
     <t xml:space="preserve">306.688262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">308.585540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.969177246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.412414550781</t>
+    <t xml:space="preserve">308.585632324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.299041748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.969268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.412445068359</t>
   </si>
   <si>
     <t xml:space="preserve">299.342132568359</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">293.796081542969</t>
   </si>
   <si>
-    <t xml:space="preserve">293.990692138672</t>
+    <t xml:space="preserve">293.990661621094</t>
   </si>
   <si>
     <t xml:space="preserve">297.104278564453</t>
@@ -3281,25 +3281,25 @@
     <t xml:space="preserve">311.601867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">311.845123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.0830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.883636474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327.656280517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.445434570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.612823486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320.06689453125</t>
+    <t xml:space="preserve">311.845092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.082977294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.883697509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327.656311035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.445465087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.61279296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320.066986083984</t>
   </si>
   <si>
     <t xml:space="preserve">324.34814453125</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">330.721221923828</t>
   </si>
   <si>
-    <t xml:space="preserve">329.65087890625</t>
+    <t xml:space="preserve">329.650939941406</t>
   </si>
   <si>
     <t xml:space="preserve">323.375122070312</t>
@@ -3320,25 +3320,25 @@
     <t xml:space="preserve">327.315765380859</t>
   </si>
   <si>
-    <t xml:space="preserve">324.883239746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.380737304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.521270751953</t>
+    <t xml:space="preserve">324.883270263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.380676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.521240234375</t>
   </si>
   <si>
     <t xml:space="preserve">328.580688476562</t>
   </si>
   <si>
-    <t xml:space="preserve">326.245452880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.710357666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.515838623047</t>
+    <t xml:space="preserve">326.245422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.710327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.515930175781</t>
   </si>
   <si>
     <t xml:space="preserve">343.759399414062</t>
@@ -3350,67 +3350,67 @@
     <t xml:space="preserve">347.456787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">347.748626708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.7109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">354.802825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.424194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">353.829803466797</t>
+    <t xml:space="preserve">347.748687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.710968017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">354.802856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.424133300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">353.829925537109</t>
   </si>
   <si>
     <t xml:space="preserve">358.257019042969</t>
   </si>
   <si>
-    <t xml:space="preserve">350.473022460938</t>
+    <t xml:space="preserve">350.473114013672</t>
   </si>
   <si>
     <t xml:space="preserve">352.224456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">353.635284423828</t>
+    <t xml:space="preserve">353.63525390625</t>
   </si>
   <si>
     <t xml:space="preserve">357.429962158203</t>
   </si>
   <si>
-    <t xml:space="preserve">349.013580322266</t>
+    <t xml:space="preserve">349.013519287109</t>
   </si>
   <si>
     <t xml:space="preserve">330.672576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">334.946655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.531280517578</t>
+    <t xml:space="preserve">334.946594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.531341552734</t>
   </si>
   <si>
     <t xml:space="preserve">331.921600341797</t>
   </si>
   <si>
-    <t xml:space="preserve">338.898620605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.972076416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.728851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.606750488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.581726074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.093811035156</t>
+    <t xml:space="preserve">338.898651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.972045898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.728912353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.606689453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.581695556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.093872070312</t>
   </si>
   <si>
     <t xml:space="preserve">342.704345703125</t>
@@ -3419,40 +3419,40 @@
     <t xml:space="preserve">345.095062255859</t>
   </si>
   <si>
-    <t xml:space="preserve">341.435699462891</t>
+    <t xml:space="preserve">341.435729980469</t>
   </si>
   <si>
     <t xml:space="preserve">344.509582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">344.119262695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">346.509979248047</t>
+    <t xml:space="preserve">344.119232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">346.510040283203</t>
   </si>
   <si>
     <t xml:space="preserve">345.826904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">342.070098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.582916259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.68017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.411193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.801086425781</t>
+    <t xml:space="preserve">342.070037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.582946777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.680206298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.411224365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.801147460938</t>
   </si>
   <si>
     <t xml:space="preserve">335.239379882812</t>
   </si>
   <si>
-    <t xml:space="preserve">332.751007080078</t>
+    <t xml:space="preserve">332.751098632812</t>
   </si>
   <si>
     <t xml:space="preserve">328.945434570312</t>
@@ -3461,43 +3461,43 @@
     <t xml:space="preserve">328.994201660156</t>
   </si>
   <si>
-    <t xml:space="preserve">330.116333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.118408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.654724121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.800659179688</t>
+    <t xml:space="preserve">330.116363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.118377685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.654693603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.800689697266</t>
   </si>
   <si>
     <t xml:space="preserve">335.141815185547</t>
   </si>
   <si>
-    <t xml:space="preserve">338.60595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.044189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.703063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.629730224609</t>
+    <t xml:space="preserve">338.605895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.044219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.629699707031</t>
   </si>
   <si>
     <t xml:space="preserve">337.288543701172</t>
   </si>
   <si>
-    <t xml:space="preserve">330.89697265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.434509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.774017333984</t>
+    <t xml:space="preserve">330.897033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.434478759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.773986816406</t>
   </si>
   <si>
     <t xml:space="preserve">315.625610351562</t>
@@ -3509,31 +3509,31 @@
     <t xml:space="preserve">321.919586181641</t>
   </si>
   <si>
-    <t xml:space="preserve">326.017913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323.96875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.188537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320.065551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">317.528442382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.088104248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.672790527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.428771972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">310.1611328125</t>
+    <t xml:space="preserve">326.017944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.968811035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.188507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320.065521240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">317.528411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.088043212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.672729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.428741455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">310.161041259766</t>
   </si>
   <si>
     <t xml:space="preserve">313.039672851562</t>
@@ -3542,43 +3542,43 @@
     <t xml:space="preserve">308.794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">307.184783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.477142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.131958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.331207275391</t>
+    <t xml:space="preserve">307.184875488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.477172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.131988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.331237792969</t>
   </si>
   <si>
     <t xml:space="preserve">306.160247802734</t>
   </si>
   <si>
-    <t xml:space="preserve">306.501800537109</t>
+    <t xml:space="preserve">306.501770019531</t>
   </si>
   <si>
     <t xml:space="preserve">309.575561523438</t>
   </si>
   <si>
-    <t xml:space="preserve">312.161499023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.796600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.503814697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.393768310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.595581054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.558563232422</t>
+    <t xml:space="preserve">312.161468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.796630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.503845214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.393707275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.595550537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.558532714844</t>
   </si>
   <si>
     <t xml:space="preserve">301.942810058594</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">300.571899414062</t>
   </si>
   <si>
-    <t xml:space="preserve">302.775115966797</t>
+    <t xml:space="preserve">302.775177001953</t>
   </si>
   <si>
     <t xml:space="preserve">304.146087646484</t>
@@ -3596,28 +3596,28 @@
     <t xml:space="preserve">304.341918945312</t>
   </si>
   <si>
-    <t xml:space="preserve">299.886444091797</t>
+    <t xml:space="preserve">299.886413574219</t>
   </si>
   <si>
     <t xml:space="preserve">294.011138916016</t>
   </si>
   <si>
-    <t xml:space="preserve">287.939910888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290.192199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.604614257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.080810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">291.465118408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.702575683594</t>
+    <t xml:space="preserve">287.939971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">290.192169189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.604644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.080841064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">291.465148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.702514648438</t>
   </si>
   <si>
     <t xml:space="preserve">288.380584716797</t>
@@ -3626,55 +3626,55 @@
     <t xml:space="preserve">293.129791259766</t>
   </si>
   <si>
-    <t xml:space="preserve">292.052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.528930664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.969573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.194976806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.390869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.089691162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.411590576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.592742919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.110473632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.984436035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.370086669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.488830566406</t>
+    <t xml:space="preserve">292.052703857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.528900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.969543457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.195007324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.390838623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.089782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.411651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.592712402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.110504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.984344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.3701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.48876953125</t>
   </si>
   <si>
     <t xml:space="preserve">303.509582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">305.419006347656</t>
+    <t xml:space="preserve">305.419067382812</t>
   </si>
   <si>
     <t xml:space="preserve">303.950225830078</t>
   </si>
   <si>
-    <t xml:space="preserve">307.964935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.721588134766</t>
+    <t xml:space="preserve">307.965026855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.721618652344</t>
   </si>
   <si>
     <t xml:space="preserve">318.442687988281</t>
@@ -3683,52 +3683,52 @@
     <t xml:space="preserve">325.884796142578</t>
   </si>
   <si>
-    <t xml:space="preserve">329.018310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.605773925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.976715087891</t>
+    <t xml:space="preserve">329.018280029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.605804443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.976684570312</t>
   </si>
   <si>
     <t xml:space="preserve">333.326873779297</t>
   </si>
   <si>
-    <t xml:space="preserve">334.110198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.543518066406</t>
+    <t xml:space="preserve">334.110260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.54345703125</t>
   </si>
   <si>
     <t xml:space="preserve">331.760070800781</t>
   </si>
   <si>
-    <t xml:space="preserve">341.944030761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.768951416016</t>
+    <t xml:space="preserve">341.944000244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.768890380859</t>
   </si>
   <si>
     <t xml:space="preserve">344.685821533203</t>
   </si>
   <si>
-    <t xml:space="preserve">352.323669433594</t>
+    <t xml:space="preserve">352.323699951172</t>
   </si>
   <si>
     <t xml:space="preserve">358.786590576172</t>
   </si>
   <si>
-    <t xml:space="preserve">375.433380126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">380.133636474609</t>
+    <t xml:space="preserve">375.433349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">380.133666992188</t>
   </si>
   <si>
     <t xml:space="preserve">382.679565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">385.225555419922</t>
+    <t xml:space="preserve">385.225524902344</t>
   </si>
   <si>
     <t xml:space="preserve">385.421417236328</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">395.358032226562</t>
   </si>
   <si>
-    <t xml:space="preserve">389.465972900391</t>
+    <t xml:space="preserve">389.466003417969</t>
   </si>
   <si>
     <t xml:space="preserve">393.394012451172</t>
@@ -3758,103 +3758,103 @@
     <t xml:space="preserve">401.0537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">402.428466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.483947753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.091156005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">387.109100341797</t>
+    <t xml:space="preserve">402.428527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.483917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.091217041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">387.109069824219</t>
   </si>
   <si>
     <t xml:space="preserve">391.233581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">396.143646240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.680358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">396.536437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.16015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">408.124176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404.785400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.963775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.731414794922</t>
+    <t xml:space="preserve">396.143615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.680328369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">396.536407470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.160125732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">408.124145507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404.785369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.963714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.731384277344</t>
   </si>
   <si>
     <t xml:space="preserve">403.999694824219</t>
   </si>
   <si>
-    <t xml:space="preserve">405.178131103516</t>
+    <t xml:space="preserve">405.178192138672</t>
   </si>
   <si>
     <t xml:space="preserve">402.821319580078</t>
   </si>
   <si>
-    <t xml:space="preserve">407.534973144531</t>
+    <t xml:space="preserve">407.534942626953</t>
   </si>
   <si>
     <t xml:space="preserve">406.749359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">413.034240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">409.4990234375</t>
+    <t xml:space="preserve">413.034271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409.498992919922</t>
   </si>
   <si>
     <t xml:space="preserve">417.551513671875</t>
   </si>
   <si>
-    <t xml:space="preserve">419.122680664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.479522705078</t>
+    <t xml:space="preserve">419.122711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.479553222656</t>
   </si>
   <si>
     <t xml:space="preserve">415.980316162109</t>
   </si>
   <si>
-    <t xml:space="preserve">419.711944580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">420.49755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.570983886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">403.606964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">397.518402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">390.447998046875</t>
+    <t xml:space="preserve">419.711883544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420.497528076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.570922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">403.60693359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397.518432617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">390.447967529297</t>
   </si>
   <si>
     <t xml:space="preserve">383.377471923828</t>
   </si>
   <si>
-    <t xml:space="preserve">391.822814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">395.947235107422</t>
+    <t xml:space="preserve">391.822784423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">395.947174072266</t>
   </si>
   <si>
     <t xml:space="preserve">394.572418212891</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">407.338531494141</t>
   </si>
   <si>
-    <t xml:space="preserve">410.284606933594</t>
+    <t xml:space="preserve">410.284637451172</t>
   </si>
   <si>
     <t xml:space="preserve">409.302581787109</t>
@@ -3875,61 +3875,61 @@
     <t xml:space="preserve">407.142181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">406.356506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.232086181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.767364501953</t>
+    <t xml:space="preserve">406.356536865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.232177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.767395019531</t>
   </si>
   <si>
     <t xml:space="preserve">413.819854736328</t>
   </si>
   <si>
-    <t xml:space="preserve">404.588958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">400.464508056641</t>
+    <t xml:space="preserve">404.588989257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400.464477539062</t>
   </si>
   <si>
     <t xml:space="preserve">403.410552978516</t>
   </si>
   <si>
-    <t xml:space="preserve">477.650634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">474.508209228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">470.187377929688</t>
+    <t xml:space="preserve">477.650604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">474.508239746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470.187286376953</t>
   </si>
   <si>
     <t xml:space="preserve">474.115356445312</t>
   </si>
   <si>
-    <t xml:space="preserve">486.252014160156</t>
+    <t xml:space="preserve">486.252044677734</t>
   </si>
   <si>
     <t xml:space="preserve">488.614349365234</t>
   </si>
   <si>
-    <t xml:space="preserve">495.110870361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">493.634338378906</t>
+    <t xml:space="preserve">495.11083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">493.634399414062</t>
   </si>
   <si>
     <t xml:space="preserve">492.157928466797</t>
   </si>
   <si>
-    <t xml:space="preserve">496.095184326172</t>
+    <t xml:space="preserve">496.095123291016</t>
   </si>
   <si>
     <t xml:space="preserve">500.524566650391</t>
   </si>
   <si>
-    <t xml:space="preserve">499.048095703125</t>
+    <t xml:space="preserve">499.048065185547</t>
   </si>
   <si>
     <t xml:space="preserve">503.477508544922</t>
@@ -3941,31 +3941,31 @@
     <t xml:space="preserve">501.016723632812</t>
   </si>
   <si>
-    <t xml:space="preserve">495.602996826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.032409667969</t>
+    <t xml:space="preserve">495.60302734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.032440185547</t>
   </si>
   <si>
     <t xml:space="preserve">507.414794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">511.844177246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.797119140625</t>
+    <t xml:space="preserve">511.844207763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.797180175781</t>
   </si>
   <si>
     <t xml:space="preserve">509.383453369141</t>
   </si>
   <si>
-    <t xml:space="preserve">527.59326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">535.9599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">547.279602050781</t>
+    <t xml:space="preserve">527.593383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">535.959838867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">547.279541015625</t>
   </si>
   <si>
     <t xml:space="preserve">546.295227050781</t>
@@ -3974,19 +3974,19 @@
     <t xml:space="preserve">546.787475585938</t>
   </si>
   <si>
-    <t xml:space="preserve">550.232543945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">539.897216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">528.085388183594</t>
+    <t xml:space="preserve">550.232482910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">539.897277832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">528.08544921875</t>
   </si>
   <si>
     <t xml:space="preserve">526.116760253906</t>
   </si>
   <si>
-    <t xml:space="preserve">512.336303710938</t>
+    <t xml:space="preserve">512.336364746094</t>
   </si>
   <si>
     <t xml:space="preserve">510.859893798828</t>
@@ -3998,40 +3998,40 @@
     <t xml:space="preserve">504.461853027344</t>
   </si>
   <si>
-    <t xml:space="preserve">517.750244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.514831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">554.661865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.442443847656</t>
+    <t xml:space="preserve">517.750122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.514892578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">554.661926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.4423828125</t>
   </si>
   <si>
     <t xml:space="preserve">567.950256347656</t>
   </si>
   <si>
-    <t xml:space="preserve">575.82470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">561.552185058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569.426696777344</t>
+    <t xml:space="preserve">575.824768066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">561.552124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569.4267578125</t>
   </si>
   <si>
     <t xml:space="preserve">545.803100585938</t>
   </si>
   <si>
-    <t xml:space="preserve">543.342407226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">540.389404296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">549.248168945312</t>
+    <t xml:space="preserve">543.342224121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540.389343261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">549.248229980469</t>
   </si>
   <si>
     <t xml:space="preserve">555.646240234375</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">523.656005859375</t>
   </si>
   <si>
-    <t xml:space="preserve">514.304992675781</t>
+    <t xml:space="preserve">514.304931640625</t>
   </si>
   <si>
     <t xml:space="preserve">517.257934570312</t>
@@ -4058,25 +4058,25 @@
     <t xml:space="preserve">553.185485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">554.300048828125</t>
+    <t xml:space="preserve">554.299987792969</t>
   </si>
   <si>
     <t xml:space="preserve">536.053466796875</t>
   </si>
   <si>
-    <t xml:space="preserve">532.108276367188</t>
+    <t xml:space="preserve">532.108215332031</t>
   </si>
   <si>
     <t xml:space="preserve">536.546630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">542.464416503906</t>
+    <t xml:space="preserve">542.46435546875</t>
   </si>
   <si>
     <t xml:space="preserve">537.532897949219</t>
   </si>
   <si>
-    <t xml:space="preserve">541.478149414062</t>
+    <t xml:space="preserve">541.478088378906</t>
   </si>
   <si>
     <t xml:space="preserve">543.450805664062</t>
@@ -4088,34 +4088,34 @@
     <t xml:space="preserve">531.121948242188</t>
   </si>
   <si>
-    <t xml:space="preserve">538.026062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">540.491760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.601501464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.039733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">534.080810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">539.012329101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">526.190490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">531.615112304688</t>
+    <t xml:space="preserve">538.026000976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540.491821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.601379394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.039794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534.080871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">539.012390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">526.1904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">531.615173339844</t>
   </si>
   <si>
     <t xml:space="preserve">517.806884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">513.368530273438</t>
+    <t xml:space="preserve">513.368591308594</t>
   </si>
   <si>
     <t xml:space="preserve">523.231689453125</t>
@@ -4127,40 +4127,40 @@
     <t xml:space="preserve">511.88916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">509.91650390625</t>
+    <t xml:space="preserve">509.916564941406</t>
   </si>
   <si>
     <t xml:space="preserve">511.395965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">518.793334960938</t>
+    <t xml:space="preserve">518.793212890625</t>
   </si>
   <si>
     <t xml:space="preserve">520.765808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">527.669982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">552.820556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567.121948242188</t>
+    <t xml:space="preserve">527.669860839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">552.820495605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567.121887207031</t>
   </si>
   <si>
     <t xml:space="preserve">557.258911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">567.615051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">565.642517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.108215332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">573.532836914062</t>
+    <t xml:space="preserve">567.615112304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">565.642395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.108154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">573.53271484375</t>
   </si>
   <si>
     <t xml:space="preserve">581.423217773438</t>
@@ -4169,22 +4169,22 @@
     <t xml:space="preserve">583.888977050781</t>
   </si>
   <si>
-    <t xml:space="preserve">575.012329101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">561.697143554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569.094482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.601257324219</t>
+    <t xml:space="preserve">575.012268066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">561.697204589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569.094421386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.601440429688</t>
   </si>
   <si>
     <t xml:space="preserve">577.47802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">572.053344726562</t>
+    <t xml:space="preserve">572.053466796875</t>
   </si>
   <si>
     <t xml:space="preserve">577.97119140625</t>
@@ -4193,7 +4193,7 @@
     <t xml:space="preserve">587.341064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">587.834228515625</t>
+    <t xml:space="preserve">587.834167480469</t>
   </si>
   <si>
     <t xml:space="preserve">585.861633300781</t>
@@ -4202,64 +4202,64 @@
     <t xml:space="preserve">593.751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">609.039672851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">646.025756835938</t>
+    <t xml:space="preserve">609.039611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">646.02587890625</t>
   </si>
   <si>
     <t xml:space="preserve">642.080627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">668.217529296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">675.614807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677.09423828125</t>
+    <t xml:space="preserve">668.217468261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">675.61474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">677.094299316406</t>
   </si>
   <si>
     <t xml:space="preserve">671.176391601562</t>
   </si>
   <si>
-    <t xml:space="preserve">679.56005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">695.172912597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">698.631530761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">722.841552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">726.300109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">700.113708496094</t>
+    <t xml:space="preserve">679.559997558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">695.172973632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">698.631591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722.841491699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">726.300170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">700.11376953125</t>
   </si>
   <si>
     <t xml:space="preserve">681.338684082031</t>
   </si>
   <si>
-    <t xml:space="preserve">707.030883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">697.643371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.054626464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">699.125732421875</t>
+    <t xml:space="preserve">707.030944824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">697.643310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.054565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">699.125671386719</t>
   </si>
   <si>
     <t xml:space="preserve">688.255798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">686.279418945312</t>
+    <t xml:space="preserve">686.279479980469</t>
   </si>
   <si>
     <t xml:space="preserve">709.995361328125</t>
@@ -4271,124 +4271,124 @@
     <t xml:space="preserve">710.489501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">711.971801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.232177734375</t>
+    <t xml:space="preserve">711.971740722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.232116699219</t>
   </si>
   <si>
     <t xml:space="preserve">660.587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">678.868225097656</t>
+    <t xml:space="preserve">678.868286132812</t>
   </si>
   <si>
     <t xml:space="preserve">683.315002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">682.326782226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">697.149353027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.560485839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.066467285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">706.042785644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720.865234375</t>
+    <t xml:space="preserve">682.326904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">697.149291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.066345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706.042663574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720.865173339844</t>
   </si>
   <si>
     <t xml:space="preserve">698.829162597656</t>
   </si>
   <si>
-    <t xml:space="preserve">709.896606445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.165161132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">709.204833984375</t>
+    <t xml:space="preserve">709.896667480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.165222167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">709.204956054688</t>
   </si>
   <si>
     <t xml:space="preserve">708.710815429688</t>
   </si>
   <si>
-    <t xml:space="preserve">689.738098144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">701.991333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">702.090087890625</t>
+    <t xml:space="preserve">689.737976074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">701.991271972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">702.090026855469</t>
   </si>
   <si>
     <t xml:space="preserve">706.141540527344</t>
   </si>
   <si>
-    <t xml:space="preserve">695.469360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">694.283630371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677.188415527344</t>
+    <t xml:space="preserve">695.469482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">694.283569335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">677.188354492188</t>
   </si>
   <si>
     <t xml:space="preserve">676.6943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">685.390075683594</t>
+    <t xml:space="preserve">685.39013671875</t>
   </si>
   <si>
     <t xml:space="preserve">678.077697753906</t>
   </si>
   <si>
-    <t xml:space="preserve">667.603149414062</t>
+    <t xml:space="preserve">667.603210449219</t>
   </si>
   <si>
     <t xml:space="preserve">680.745849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">674.619079589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">711.576477050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">674.520324707031</t>
+    <t xml:space="preserve">674.619201660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.576416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">674.520263671875</t>
   </si>
   <si>
     <t xml:space="preserve">688.848693847656</t>
   </si>
   <si>
-    <t xml:space="preserve">709.106018066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">712.367065429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.133422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.528625488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">710.328674316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.57666015625</t>
+    <t xml:space="preserve">709.106079101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">712.367004394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.133361816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.528564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">710.328735351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.576721191406</t>
   </si>
   <si>
     <t xml:space="preserve">701.517639160156</t>
   </si>
   <si>
-    <t xml:space="preserve">712.407592773438</t>
+    <t xml:space="preserve">712.407653808594</t>
   </si>
   <si>
     <t xml:space="preserve">732.603759765625</t>
@@ -4397,13 +4397,13 @@
     <t xml:space="preserve">729.336791992188</t>
   </si>
   <si>
-    <t xml:space="preserve">744.186889648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">737.256896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">739.434814453125</t>
+    <t xml:space="preserve">744.186828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">737.2568359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">739.434875488281</t>
   </si>
   <si>
     <t xml:space="preserve">733.593811035156</t>
@@ -4418,19 +4418,19 @@
     <t xml:space="preserve">746.661865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">758.640869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">754.185852050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">757.75</t>
+    <t xml:space="preserve">758.640930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">754.185791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.749938964844</t>
   </si>
   <si>
     <t xml:space="preserve">762.204956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">778.243041992188</t>
+    <t xml:space="preserve">778.242980957031</t>
   </si>
   <si>
     <t xml:space="preserve">791.41015625</t>
@@ -4442,28 +4442,28 @@
     <t xml:space="preserve">787.549133300781</t>
   </si>
   <si>
-    <t xml:space="preserve">807.250244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">815.764221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">815.962219238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">825.565368652344</t>
+    <t xml:space="preserve">807.250122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">815.764343261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">815.962280273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">825.565246582031</t>
   </si>
   <si>
     <t xml:space="preserve">823.288208007812</t>
   </si>
   <si>
-    <t xml:space="preserve">833.38623046875</t>
+    <t xml:space="preserve">833.386291503906</t>
   </si>
   <si>
     <t xml:space="preserve">819.42724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">828.337341308594</t>
+    <t xml:space="preserve">828.337280273438</t>
   </si>
   <si>
     <t xml:space="preserve">838.732360839844</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">845.266357421875</t>
   </si>
   <si>
-    <t xml:space="preserve">828.931274414062</t>
+    <t xml:space="preserve">828.931335449219</t>
   </si>
   <si>
     <t xml:space="preserve">818.932250976562</t>
   </si>
   <si>
-    <t xml:space="preserve">825.664245605469</t>
+    <t xml:space="preserve">825.664306640625</t>
   </si>
   <si>
     <t xml:space="preserve">834.970397949219</t>
@@ -4499,10 +4499,10 @@
     <t xml:space="preserve">847.543334960938</t>
   </si>
   <si>
-    <t xml:space="preserve">861.403442382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">845.563293457031</t>
+    <t xml:space="preserve">861.403503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">845.563354492188</t>
   </si>
   <si>
     <t xml:space="preserve">859.720520019531</t>
@@ -4514,64 +4514,64 @@
     <t xml:space="preserve">863.482482910156</t>
   </si>
   <si>
-    <t xml:space="preserve">830.020263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">773.391967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">783.193054199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">784.282104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">807.646118164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">782.401000976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760.224975585938</t>
+    <t xml:space="preserve">830.020324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">773.392028808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">783.192993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">784.282043457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">807.646179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">782.400939941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760.224914550781</t>
   </si>
   <si>
     <t xml:space="preserve">743.790832519531</t>
   </si>
   <si>
-    <t xml:space="preserve">737.751892089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">726.465759277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">735.078735351562</t>
+    <t xml:space="preserve">737.751831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">726.465698242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">735.078796386719</t>
   </si>
   <si>
     <t xml:space="preserve">761.016967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">720.030639648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">699.042602539062</t>
+    <t xml:space="preserve">720.030700683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">699.042663574219</t>
   </si>
   <si>
     <t xml:space="preserve">720.327758789062</t>
   </si>
   <si>
-    <t xml:space="preserve">702.8046875</t>
+    <t xml:space="preserve">702.804626464844</t>
   </si>
   <si>
     <t xml:space="preserve">755.967895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">812.794250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">806.359191894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">817.744262695312</t>
+    <t xml:space="preserve">812.794189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">806.359252929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">817.744201660156</t>
   </si>
   <si>
     <t xml:space="preserve">838.138305664062</t>
@@ -4583,13 +4583,13 @@
     <t xml:space="preserve">824.752685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">846.169738769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">841.807006835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">855.88671875</t>
+    <t xml:space="preserve">846.169677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">841.806945800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">855.886657714844</t>
   </si>
   <si>
     <t xml:space="preserve">840.220581054688</t>
@@ -4598,31 +4598,31 @@
     <t xml:space="preserve">845.37646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">851.028198242188</t>
+    <t xml:space="preserve">851.028137207031</t>
   </si>
   <si>
     <t xml:space="preserve">845.673950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">850.631591796875</t>
+    <t xml:space="preserve">850.631652832031</t>
   </si>
   <si>
     <t xml:space="preserve">846.764587402344</t>
   </si>
   <si>
-    <t xml:space="preserve">858.563781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">867.586730957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">852.217956542969</t>
+    <t xml:space="preserve">858.563842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">867.586669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">852.218017578125</t>
   </si>
   <si>
     <t xml:space="preserve">812.160278320312</t>
   </si>
   <si>
-    <t xml:space="preserve">806.012817382812</t>
+    <t xml:space="preserve">806.012878417969</t>
   </si>
   <si>
     <t xml:space="preserve">807.995910644531</t>
@@ -4631,13 +4631,13 @@
     <t xml:space="preserve">812.656066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">812.95361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">831.197631835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">835.064575195312</t>
+    <t xml:space="preserve">812.953491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">831.197570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">835.064636230469</t>
   </si>
   <si>
     <t xml:space="preserve">824.05859375</t>
@@ -4646,10 +4646,10 @@
     <t xml:space="preserve">812.556945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">808.987487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">805.51708984375</t>
+    <t xml:space="preserve">808.987426757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">805.517150878906</t>
   </si>
   <si>
     <t xml:space="preserve">825.5458984375</t>
@@ -4658,10 +4658,10 @@
     <t xml:space="preserve">816.919677734375</t>
   </si>
   <si>
-    <t xml:space="preserve">819.695922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">821.579772949219</t>
+    <t xml:space="preserve">819.695861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">821.579833984375</t>
   </si>
   <si>
     <t xml:space="preserve">813.845886230469</t>
@@ -4670,16 +4670,16 @@
     <t xml:space="preserve">779.737365722656</t>
   </si>
   <si>
-    <t xml:space="preserve">779.935607910156</t>
+    <t xml:space="preserve">779.935668945312</t>
   </si>
   <si>
     <t xml:space="preserve">793.519592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">800.063659667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">798.675476074219</t>
+    <t xml:space="preserve">800.063720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">798.675537109375</t>
   </si>
   <si>
     <t xml:space="preserve">794.709411621094</t>
@@ -4694,13 +4694,13 @@
     <t xml:space="preserve">829.313720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">836.948547363281</t>
+    <t xml:space="preserve">836.948486328125</t>
   </si>
   <si>
     <t xml:space="preserve">829.809509277344</t>
   </si>
   <si>
-    <t xml:space="preserve">832.982360839844</t>
+    <t xml:space="preserve">832.982421875</t>
   </si>
   <si>
     <t xml:space="preserve">841.410339355469</t>
@@ -4709,46 +4709,46 @@
     <t xml:space="preserve">838.435791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">830.0078125</t>
+    <t xml:space="preserve">830.007751464844</t>
   </si>
   <si>
     <t xml:space="preserve">833.279846191406</t>
   </si>
   <si>
-    <t xml:space="preserve">823.662048339844</t>
+    <t xml:space="preserve">823.661987304688</t>
   </si>
   <si>
     <t xml:space="preserve">819.200134277344</t>
   </si>
   <si>
-    <t xml:space="preserve">822.868774414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819.894226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">827.132446289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761.790710449219</t>
+    <t xml:space="preserve">822.868835449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.894287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">827.13232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761.790649414062</t>
   </si>
   <si>
     <t xml:space="preserve">778.646667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">754.651672363281</t>
+    <t xml:space="preserve">754.651733398438</t>
   </si>
   <si>
     <t xml:space="preserve">737.002502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">726.492248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">716.973571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">725.401550292969</t>
+    <t xml:space="preserve">726.492309570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">716.9736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">725.401611328125</t>
   </si>
   <si>
     <t xml:space="preserve">766.549987792969</t>
@@ -4763,22 +4763,22 @@
     <t xml:space="preserve">771.309387207031</t>
   </si>
   <si>
-    <t xml:space="preserve">750.090759277344</t>
+    <t xml:space="preserve">750.090637207031</t>
   </si>
   <si>
     <t xml:space="preserve">713.241638183594</t>
   </si>
   <si>
-    <t xml:space="preserve">680.464965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">679.670349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">703.706665039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.295776367188</t>
+    <t xml:space="preserve">680.464904785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679.670288085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">703.706604003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.295715332031</t>
   </si>
   <si>
     <t xml:space="preserve">715.228088378906</t>
@@ -4817,16 +4817,16 @@
     <t xml:space="preserve">748.104248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">747.408935546875</t>
+    <t xml:space="preserve">747.408996582031</t>
   </si>
   <si>
     <t xml:space="preserve">740.952941894531</t>
   </si>
   <si>
-    <t xml:space="preserve">744.330017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">744.925842285156</t>
+    <t xml:space="preserve">744.329956054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">744.925903320312</t>
   </si>
   <si>
     <t xml:space="preserve">735.7880859375</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">725.756469726562</t>
   </si>
   <si>
-    <t xml:space="preserve">759.029846191406</t>
+    <t xml:space="preserve">759.02978515625</t>
   </si>
   <si>
     <t xml:space="preserve">745.521789550781</t>
@@ -4850,16 +4850,16 @@
     <t xml:space="preserve">759.327819824219</t>
   </si>
   <si>
-    <t xml:space="preserve">753.070434570312</t>
+    <t xml:space="preserve">753.070373535156</t>
   </si>
   <si>
     <t xml:space="preserve">739.860412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">740.158325195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.731872558594</t>
+    <t xml:space="preserve">740.158386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.731811523438</t>
   </si>
   <si>
     <t xml:space="preserve">758.433837890625</t>
@@ -4883,10 +4883,10 @@
     <t xml:space="preserve">714.731506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">693.674926757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">697.548583984375</t>
+    <t xml:space="preserve">693.674987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">697.548522949219</t>
   </si>
   <si>
     <t xml:space="preserve">724.663879394531</t>
@@ -4895,22 +4895,22 @@
     <t xml:space="preserve">722.876037597656</t>
   </si>
   <si>
-    <t xml:space="preserve">741.846923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">757.937255859375</t>
+    <t xml:space="preserve">741.846862792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.937194824219</t>
   </si>
   <si>
     <t xml:space="preserve">766.181091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">768.068176269531</t>
+    <t xml:space="preserve">768.068237304688</t>
   </si>
   <si>
     <t xml:space="preserve">771.445251464844</t>
   </si>
   <si>
-    <t xml:space="preserve">784.555969238281</t>
+    <t xml:space="preserve">784.555908203125</t>
   </si>
   <si>
     <t xml:space="preserve">785.052551269531</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">775.914855957031</t>
   </si>
   <si>
-    <t xml:space="preserve">796.176696777344</t>
+    <t xml:space="preserve">796.1767578125</t>
   </si>
   <si>
     <t xml:space="preserve">842.759399414062</t>
@@ -4928,16 +4928,16 @@
     <t xml:space="preserve">843.752685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">834.813659667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">833.025756835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">831.734558105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">834.316955566406</t>
+    <t xml:space="preserve">834.813598632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">833.025817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">831.734619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">834.317016601562</t>
   </si>
   <si>
     <t xml:space="preserve">816.108276367188</t>
@@ -5451,6 +5451,9 @@
   </si>
   <si>
     <t xml:space="preserve">711.599975585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">728</t>
   </si>
 </sst>
 </file>
@@ -70789,7 +70792,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45959.6916550926</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>3523</v>
@@ -70810,6 +70813,32 @@
         <v>1812</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45960.6916319444</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>13843</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>751.200012207031</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>697.700012207031</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>697.700012207031</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>728</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1813</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="1814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="1815">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,58 +47,58 @@
     <t xml:space="preserve">38.7578163146973</t>
   </si>
   <si>
-    <t xml:space="preserve">61.6800651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1174964904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5549392700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4298439025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9924049377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.2425994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8051681518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3677253723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9302635192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0229949951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5942916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1717262268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8681373596191</t>
+    <t xml:space="preserve">61.680046081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1175155639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5549583435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4298477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9923973083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.2426147460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8051528930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3677177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9302673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0229988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5942878723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1717185974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8681449890137</t>
   </si>
   <si>
     <t xml:space="preserve">54.7071418762207</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5907974243164</t>
+    <t xml:space="preserve">55.5908012390137</t>
   </si>
   <si>
     <t xml:space="preserve">54.3309478759766</t>
   </si>
   <si>
-    <t xml:space="preserve">53.359806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.015983581543</t>
+    <t xml:space="preserve">53.3598175048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0159759521484</t>
   </si>
   <si>
     <t xml:space="preserve">54.2212677001953</t>
@@ -110,37 +110,37 @@
     <t xml:space="preserve">56.3226585388184</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4815940856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2785263061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4021263122559</t>
+    <t xml:space="preserve">56.4815864562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2785148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4021186828613</t>
   </si>
   <si>
     <t xml:space="preserve">57.0290107727051</t>
   </si>
   <si>
-    <t xml:space="preserve">57.5322952270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5963745117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4662094116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2719650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5721549987793</t>
+    <t xml:space="preserve">57.5322799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5963821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4662132263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2719573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5721626281738</t>
   </si>
   <si>
     <t xml:space="preserve">55.1218681335449</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9276237487793</t>
+    <t xml:space="preserve">54.9276123046875</t>
   </si>
   <si>
     <t xml:space="preserve">54.9717597961426</t>
@@ -149,277 +149,277 @@
     <t xml:space="preserve">56.6405181884766</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2167015075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5787162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0754432678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8082733154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0312805175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4286117553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2961692810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8900146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4861488342285</t>
+    <t xml:space="preserve">56.2167091369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5787124633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0754356384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8082656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0312881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4286155700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2961578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8900108337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.486141204834</t>
   </si>
   <si>
     <t xml:space="preserve">53.2323760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9034080505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1130294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3690795898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6251373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9230575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8811950683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5191955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7641220092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1019172668457</t>
+    <t xml:space="preserve">53.9033966064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.113037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3690948486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6251411437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9230651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8811912536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5191841125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7641334533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1019287109375</t>
   </si>
   <si>
     <t xml:space="preserve">56.6934967041016</t>
   </si>
   <si>
-    <t xml:space="preserve">57.5057945251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.161449432373</t>
+    <t xml:space="preserve">57.5057907104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1614608764648</t>
   </si>
   <si>
     <t xml:space="preserve">56.9937019348145</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5433883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9495544433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4793128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9119415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5829620361328</t>
+    <t xml:space="preserve">56.5433959960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9495429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.4793090820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9119453430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5829811096191</t>
   </si>
   <si>
     <t xml:space="preserve">59.9162292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">60.3665199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1899185180664</t>
+    <t xml:space="preserve">60.3665237426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1899261474609</t>
   </si>
   <si>
     <t xml:space="preserve">58.362247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">57.6558952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6294059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6271324157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7330741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5166168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0552062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5231781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4452667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7212104797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2997817993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8872718811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5134315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2433280944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2077140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.394645690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9376411437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4093933105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1571044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5696258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6586227416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2105178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2549819946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.797981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1006317138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6911849975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4967422485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7281646728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8336029052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9582061767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1615447998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3039779663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5220336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3320770263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2608413696289</t>
+    <t xml:space="preserve">57.6559028625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.62939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6271209716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7330780029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5166358947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0552177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5231704711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4452781677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7212409973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8872947692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5134544372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2433395385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2077255249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3946647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.937629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4093780517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.157096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5696334838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6586456298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2105026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.255012512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1006240844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6912002563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4967498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7281799316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8335952758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9582138061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1615600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3039703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5220413208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3320541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2608642578125</t>
   </si>
   <si>
     <t xml:space="preserve">65.8202362060547</t>
   </si>
   <si>
-    <t xml:space="preserve">66.2563858032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5190124511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7860260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3988418579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3556976318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1212158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1657333374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1568069458008</t>
+    <t xml:space="preserve">66.2564086914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5190048217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.786018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3988342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3556900024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.121208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1657180786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1568222045898</t>
   </si>
   <si>
     <t xml:space="preserve">68.6018829345703</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3971481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5960388183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1448516845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6194305419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.52734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6221618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5153732299805</t>
+    <t xml:space="preserve">68.3971710205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5960464477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1448593139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6194229125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.5273361206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.622200012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5153503417969</t>
   </si>
   <si>
     <t xml:space="preserve">74.9306716918945</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6961975097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2124481201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8355331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4733352661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.9362106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.562385559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7136840820312</t>
+    <t xml:space="preserve">75.6961822509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2124328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8355255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4733810424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.9362258911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5623779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.7136688232422</t>
   </si>
   <si>
     <t xml:space="preserve">79.8352508544922</t>
@@ -428,91 +428,91 @@
     <t xml:space="preserve">79.8441390991211</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8048477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4318618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9513702392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5694351196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.7844390869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4587249755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3691253662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9033660888672</t>
+    <t xml:space="preserve">80.8048324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4318466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9513626098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5694580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7844161987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4587173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3691482543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9033584594727</t>
   </si>
   <si>
     <t xml:space="preserve">80.6883850097656</t>
   </si>
   <si>
-    <t xml:space="preserve">80.634651184082</t>
+    <t xml:space="preserve">80.634635925293</t>
   </si>
   <si>
     <t xml:space="preserve">80.5809097290039</t>
   </si>
   <si>
-    <t xml:space="preserve">80.9839782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2168807983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0914916992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2527084350586</t>
+    <t xml:space="preserve">80.9839935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8496398925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2168655395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0914688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2527008056641</t>
   </si>
   <si>
     <t xml:space="preserve">80.2853012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3211288452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4888381958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8618087768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7811889648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3960418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6110076904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9782485961914</t>
+    <t xml:space="preserve">80.3211441040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4887924194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8617858886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7811965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3960113525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6110000610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9782409667969</t>
   </si>
   <si>
     <t xml:space="preserve">80.3569488525391</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1810531616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6077575683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0735549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2380294799805</t>
+    <t xml:space="preserve">81.181037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6077651977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0735626220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2379989624023</t>
   </si>
   <si>
     <t xml:space="preserve">83.115837097168</t>
@@ -521,145 +521,145 @@
     <t xml:space="preserve">83.2949829101562</t>
   </si>
   <si>
-    <t xml:space="preserve">87.2810516357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2248077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5057144165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7980804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1531524658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2477188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.453727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8478317260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3014373779297</t>
+    <t xml:space="preserve">87.2810363769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2247924804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5056991577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.798095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1531372070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2476959228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4537200927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8478546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3014602661133</t>
   </si>
   <si>
     <t xml:space="preserve">86.8958892822266</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3201065063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9976425170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7378692626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3552093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7435989379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1402282714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2681121826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2029037475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0660552978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.817756652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6980895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.128776550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9725112915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2061538696289</t>
+    <t xml:space="preserve">88.3200836181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9976501464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7378768920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3551788330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7435836791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1402206420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2681274414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2029190063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0660629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.817741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6980819702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1287384033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.4472732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.972526550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2061309814453</t>
   </si>
   <si>
     <t xml:space="preserve">87.7289047241211</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2369995117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3591537475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9741516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7128982543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5325927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5685348510742</t>
+    <t xml:space="preserve">90.2369689941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3591918945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9741363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7129364013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5325698852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5685195922852</t>
   </si>
   <si>
     <t xml:space="preserve">88.9740600585938</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3705139160156</t>
+    <t xml:space="preserve">88.3705062866211</t>
   </si>
   <si>
     <t xml:space="preserve">90.1991882324219</t>
   </si>
   <si>
-    <t xml:space="preserve">88.8840026855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.406379699707</t>
+    <t xml:space="preserve">88.8839721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4063720703125</t>
   </si>
   <si>
     <t xml:space="preserve">91.2171173095703</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7665176391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8475036621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0457077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1541366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6046371459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.388542175293</t>
+    <t xml:space="preserve">92.7665328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8474960327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0456848144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.154167175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6046524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3885269165039</t>
   </si>
   <si>
     <t xml:space="preserve">91.3162002563477</t>
   </si>
   <si>
-    <t xml:space="preserve">89.748779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.89306640625</t>
+    <t xml:space="preserve">89.7487640380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8930740356445</t>
   </si>
   <si>
     <t xml:space="preserve">84.8933486938477</t>
@@ -668,259 +668,259 @@
     <t xml:space="preserve">86.8931655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">86.0644149780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2627868652344</t>
+    <t xml:space="preserve">86.0644073486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2627792358398</t>
   </si>
   <si>
     <t xml:space="preserve">86.7760696411133</t>
   </si>
   <si>
-    <t xml:space="preserve">88.5056533813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.325309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0190887451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1812438964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6315994262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6135330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4513092041016</t>
+    <t xml:space="preserve">88.5056304931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3252792358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0191040039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1812591552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.631591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6135711669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4512939453125</t>
   </si>
   <si>
     <t xml:space="preserve">90.8747863769531</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6676177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9919967651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7217407226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3521270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3700714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6675338745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5863418579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.424201965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0998306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6674423217773</t>
+    <t xml:space="preserve">90.667610168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9919738769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7217636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3521423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3700790405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6675186157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5863571166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4241943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0998229980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6674194335938</t>
   </si>
   <si>
     <t xml:space="preserve">90.6585998535156</t>
   </si>
   <si>
-    <t xml:space="preserve">90.0820693969727</t>
+    <t xml:space="preserve">90.0820541381836</t>
   </si>
   <si>
     <t xml:space="preserve">91.7666091918945</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5051803588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4150085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7394027709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6851806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0997161865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4961700439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6043548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9646148681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3970108032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1717910766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.3154830932617</t>
+    <t xml:space="preserve">93.5051879882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4150161743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7394256591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.685173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0997314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4962005615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.604377746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.964599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3970031738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1717987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.3154754638672</t>
   </si>
   <si>
     <t xml:space="preserve">97.6569595336914</t>
   </si>
   <si>
-    <t xml:space="preserve">99.0890960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6750640869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.7385482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2370681762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0437698364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2522506713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3247756958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6963806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.521240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.518272399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.475921630859</t>
+    <t xml:space="preserve">99.0890808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6750946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.7385330200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2370758056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0437774658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2522354125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3247680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6963958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.52123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.518287658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.475914001465</t>
   </si>
   <si>
     <t xml:space="preserve">102.189033508301</t>
   </si>
   <si>
-    <t xml:space="preserve">101.318870544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.234344482422</t>
+    <t xml:space="preserve">101.318885803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.234336853027</t>
   </si>
   <si>
     <t xml:space="preserve">100.45777130127</t>
   </si>
   <si>
-    <t xml:space="preserve">98.9078140258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4969940185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1616058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5966873168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.865661621094</t>
+    <t xml:space="preserve">98.9078063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4969711303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1615905761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5966720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.865676879883</t>
   </si>
   <si>
     <t xml:space="preserve">102.034934997559</t>
   </si>
   <si>
-    <t xml:space="preserve">102.524398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.823532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.101547241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.588088989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.446006774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.86296081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.300987243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.27082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.352416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.494270324707</t>
+    <t xml:space="preserve">102.5244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.823539733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.101570129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.58805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.445991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.862945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.300956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270820617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.352409362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.494262695312</t>
   </si>
   <si>
     <t xml:space="preserve">101.346061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">102.207160949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.880851745605</t>
+    <t xml:space="preserve">102.207153320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.880836486816</t>
   </si>
   <si>
     <t xml:space="preserve">102.787269592285</t>
   </si>
   <si>
-    <t xml:space="preserve">100.068023681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0165939331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8862762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4722671508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7020568847656</t>
+    <t xml:space="preserve">100.068016052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0166015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8862915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.472282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7020492553711</t>
   </si>
   <si>
     <t xml:space="preserve">95.7716217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">95.9347610473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7867889404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0587310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5751419067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9739837646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9044036865234</t>
+    <t xml:space="preserve">95.9347686767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7868194580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0587387084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5751571655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.973991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9044189453125</t>
   </si>
   <si>
     <t xml:space="preserve">93.7775192260742</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0494232177734</t>
+    <t xml:space="preserve">94.0494384765625</t>
   </si>
   <si>
     <t xml:space="preserve">93.0342483520508</t>
@@ -932,13 +932,13 @@
     <t xml:space="preserve">92.4360275268555</t>
   </si>
   <si>
-    <t xml:space="preserve">93.1430358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3061676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7552490234375</t>
+    <t xml:space="preserve">93.1430130004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3061828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.755241394043</t>
   </si>
   <si>
     <t xml:space="preserve">94.6241989135742</t>
@@ -947,28 +947,28 @@
     <t xml:space="preserve">95.8829574584961</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4816131591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3903732299805</t>
+    <t xml:space="preserve">95.4815979003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3903961181641</t>
   </si>
   <si>
     <t xml:space="preserve">95.0802764892578</t>
   </si>
   <si>
-    <t xml:space="preserve">95.1349945068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4086303710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2228775024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9376754760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9890518188477</t>
+    <t xml:space="preserve">95.1350021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4086227416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2228698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9376831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9890670776367</t>
   </si>
   <si>
     <t xml:space="preserve">95.5728225708008</t>
@@ -983,112 +983,112 @@
     <t xml:space="preserve">93.0918350219727</t>
   </si>
   <si>
-    <t xml:space="preserve">90.5834732055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2128448486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7999496459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4201812744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4931564331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9094009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6357345581055</t>
+    <t xml:space="preserve">90.5834808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2128295898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.799934387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4201736450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4931716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9094161987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6357650756836</t>
   </si>
   <si>
     <t xml:space="preserve">93.3107452392578</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2608947753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8720016479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3098297119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3405380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2709274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3621368408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7567672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1249771118164</t>
+    <t xml:space="preserve">89.2609024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8720092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3098373413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3405456542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2709121704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3621444702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7567749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1249618530273</t>
   </si>
   <si>
     <t xml:space="preserve">89.3885803222656</t>
   </si>
   <si>
-    <t xml:space="preserve">86.6522064208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5643310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4764556884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.020378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5004959106445</t>
+    <t xml:space="preserve">86.6521911621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.564323425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4764709472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0204010009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5004730224609</t>
   </si>
   <si>
     <t xml:space="preserve">87.3818969726562</t>
   </si>
   <si>
-    <t xml:space="preserve">86.5244750976562</t>
+    <t xml:space="preserve">86.5244979858398</t>
   </si>
   <si>
     <t xml:space="preserve">86.9349594116211</t>
   </si>
   <si>
-    <t xml:space="preserve">87.9474182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3065032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3703460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9507598876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2243881225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1183013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7750091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.304069519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9176406860352</t>
+    <t xml:space="preserve">87.9474258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3064956665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3703384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9507446289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2244033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1182861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.775032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3040618896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.917610168457</t>
   </si>
   <si>
     <t xml:space="preserve">90.5469818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">89.498046875</t>
+    <t xml:space="preserve">89.4980392456055</t>
   </si>
   <si>
     <t xml:space="preserve">92.7452163696289</t>
@@ -1097,166 +1097,166 @@
     <t xml:space="preserve">91.7418746948242</t>
   </si>
   <si>
-    <t xml:space="preserve">91.4317474365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0702438354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4236602783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4407806396484</t>
+    <t xml:space="preserve">91.4317398071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0702362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4236755371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.440803527832</t>
   </si>
   <si>
     <t xml:space="preserve">90.7804641723633</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7908782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0479125976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.074836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4230270385742</t>
+    <t xml:space="preserve">92.7908935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0478897094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0748291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4230422973633</t>
   </si>
   <si>
     <t xml:space="preserve">91.9095993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7541351318359</t>
+    <t xml:space="preserve">92.754150390625</t>
   </si>
   <si>
     <t xml:space="preserve">93.8190155029297</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6085052490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8104705810547</t>
+    <t xml:space="preserve">94.6084976196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8104629516602</t>
   </si>
   <si>
     <t xml:space="preserve">95.2878265380859</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0197601318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7712936401367</t>
+    <t xml:space="preserve">92.0197448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7712631225586</t>
   </si>
   <si>
     <t xml:space="preserve">92.6990661621094</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9193954467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0381164550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6800918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7443618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9928359985352</t>
+    <t xml:space="preserve">92.9193801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0381240844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6801071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7443237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9928207397461</t>
   </si>
   <si>
     <t xml:space="preserve">94.9389724731445</t>
   </si>
   <si>
-    <t xml:space="preserve">96.7015151977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4065322875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6635818481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4334487915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9940567016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4713973999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6353988647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9634246826172</t>
+    <t xml:space="preserve">96.7015075683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4065399169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.66357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.433464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9940338134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4714202880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6354217529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9634552001953</t>
   </si>
   <si>
     <t xml:space="preserve">89.5044479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4224472045898</t>
+    <t xml:space="preserve">90.4224319458008</t>
   </si>
   <si>
     <t xml:space="preserve">90.8814315795898</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3404235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7969741821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5589141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8165817260742</t>
+    <t xml:space="preserve">91.340446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7969970703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5589294433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8165512084961</t>
   </si>
   <si>
     <t xml:space="preserve">92.2033538818359</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6886672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1396942138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7174224853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0944290161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0931701660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.800666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4885406494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0209579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1494903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4616165161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4500885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6510009765625</t>
+    <t xml:space="preserve">90.6886444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1397094726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.717414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0944213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0931854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8006744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4885330200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0209732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1494979858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4616012573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4500732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6509780883789</t>
   </si>
   <si>
     <t xml:space="preserve">94.7433700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4824142456055</t>
+    <t xml:space="preserve">95.4823989868164</t>
   </si>
   <si>
     <t xml:space="preserve">96.0920944213867</t>
@@ -1265,34 +1265,34 @@
     <t xml:space="preserve">95.6856307983398</t>
   </si>
   <si>
-    <t xml:space="preserve">97.0158767700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5493698120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8634490966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3830718994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1267318725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4939422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.600173950195</t>
+    <t xml:space="preserve">97.0158843994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5493621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8634567260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3830871582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1267395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4939346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.600158691406</t>
   </si>
   <si>
     <t xml:space="preserve">99.9165649414062</t>
   </si>
   <si>
-    <t xml:space="preserve">100.359985351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.21216583252</t>
+    <t xml:space="preserve">100.359977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.212196350098</t>
   </si>
   <si>
     <t xml:space="preserve">100.784927368164</t>
@@ -1301,154 +1301,154 @@
     <t xml:space="preserve">100.71102142334</t>
   </si>
   <si>
-    <t xml:space="preserve">101.727172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.202926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.269897460938</t>
+    <t xml:space="preserve">101.727195739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.202934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.269905090332</t>
   </si>
   <si>
     <t xml:space="preserve">108.008911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">110.429214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.653251647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.988136291504</t>
+    <t xml:space="preserve">110.429237365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.653259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.988121032715</t>
   </si>
   <si>
     <t xml:space="preserve">108.064346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">108.341484069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.265266418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.135925292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.819541931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.893432617188</t>
+    <t xml:space="preserve">108.34147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.265251159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.135917663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.819526672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.893447875977</t>
   </si>
   <si>
     <t xml:space="preserve">112.886505126953</t>
   </si>
   <si>
-    <t xml:space="preserve">114.105895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.269874572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.454643249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.507743835449</t>
+    <t xml:space="preserve">114.105888366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.269859313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.454635620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.507751464844</t>
   </si>
   <si>
     <t xml:space="preserve">117.062019348145</t>
   </si>
   <si>
-    <t xml:space="preserve">117.376106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.710952758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.486946105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.394569396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.320693969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.413040161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.322982788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.115127563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.092018127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.135902404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.339141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.61164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.156684875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473098754883</t>
+    <t xml:space="preserve">117.376098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.710975646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.486953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.394554138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.320671081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.413055419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.32299041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.115112304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.092025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.135925292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.339157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.611656188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623176574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.156608581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473091125488</t>
   </si>
   <si>
     <t xml:space="preserve">121.274482727051</t>
   </si>
   <si>
-    <t xml:space="preserve">121.292945861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.586280822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.549049377441</t>
+    <t xml:space="preserve">121.292930603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.586250305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.549072265625</t>
   </si>
   <si>
     <t xml:space="preserve">121.248527526855</t>
   </si>
   <si>
-    <t xml:space="preserve">120.616836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.229957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.270370483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.787353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.780784606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.049621582031</t>
+    <t xml:space="preserve">120.616821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.229942321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.270378112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.787330627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.780769348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.049598693848</t>
   </si>
   <si>
     <t xml:space="preserve">116.009170532227</t>
   </si>
   <si>
-    <t xml:space="preserve">113.01789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.620063781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.057228088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.441932678223</t>
+    <t xml:space="preserve">113.017913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.620056152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.057235717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.441955566406</t>
   </si>
   <si>
     <t xml:space="preserve">111.10424041748</t>
@@ -1460,16 +1460,16 @@
     <t xml:space="preserve">115.507522583008</t>
   </si>
   <si>
-    <t xml:space="preserve">110.881278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.937019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.135955810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.700942993164</t>
+    <t xml:space="preserve">110.88126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.93701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.135932922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.700950622559</t>
   </si>
   <si>
     <t xml:space="preserve">110.5654296875</t>
@@ -1478,148 +1478,148 @@
     <t xml:space="preserve">112.609161376953</t>
   </si>
   <si>
-    <t xml:space="preserve">117.123924255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.597145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.056182861328</t>
+    <t xml:space="preserve">117.123931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.597152709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.056175231934</t>
   </si>
   <si>
     <t xml:space="preserve">116.120635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">104.768684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.270332336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.77197265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.844123840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.680198669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.365455627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.79825592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.694450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.300964355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623413085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.552383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.339294433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.661651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.913055419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.44856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.628921508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.377487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.235458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.285781860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.67919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.218017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.557861328125</t>
+    <t xml:space="preserve">104.768676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.27033996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.771980285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.844131469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.680191040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.36547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.798233032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.694427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.300987243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623397827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.552337646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.339241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.661682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.913024902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.448547363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.628890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.377532958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.235427856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.285751342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.679214477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.218002319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.557907104492</t>
   </si>
   <si>
     <t xml:space="preserve">133.232177734375</t>
   </si>
   <si>
-    <t xml:space="preserve">132.117416381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.367645263672</t>
+    <t xml:space="preserve">132.117401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.36767578125</t>
   </si>
   <si>
     <t xml:space="preserve">134.272598266602</t>
   </si>
   <si>
-    <t xml:space="preserve">135.405975341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.492294311523</t>
+    <t xml:space="preserve">135.405960083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.492309570312</t>
   </si>
   <si>
     <t xml:space="preserve">132.154602050781</t>
   </si>
   <si>
-    <t xml:space="preserve">135.183013916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.263900756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.833297729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.889312744141</t>
+    <t xml:space="preserve">135.182968139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.263885498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.833312988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.889297485352</t>
   </si>
   <si>
     <t xml:space="preserve">135.347763061523</t>
   </si>
   <si>
-    <t xml:space="preserve">136.561584472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.050872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.911773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.942642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.689590454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.399185180664</t>
+    <t xml:space="preserve">136.561553955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.050933837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.91178894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.942626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.689605712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.399215698242</t>
   </si>
   <si>
     <t xml:space="preserve">126.346992492676</t>
   </si>
   <si>
-    <t xml:space="preserve">121.771926879883</t>
+    <t xml:space="preserve">121.771903991699</t>
   </si>
   <si>
     <t xml:space="preserve">127.76619720459</t>
   </si>
   <si>
-    <t xml:space="preserve">127.560775756836</t>
+    <t xml:space="preserve">127.560760498047</t>
   </si>
   <si>
     <t xml:space="preserve">126.589744567871</t>
@@ -1628,118 +1628,118 @@
     <t xml:space="preserve">125.95482635498</t>
   </si>
   <si>
-    <t xml:space="preserve">124.180847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.002464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.873664855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.143486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.554260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.84659576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.016571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.972732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.142364501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.077972412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.011657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.650314331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.322601318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.984558105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.455230712891</t>
+    <t xml:space="preserve">124.180816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.002479553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.873657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.14347076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.554290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.846618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.016563415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.97274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.14241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.077926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.011611938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.650360107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.322616577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.984588623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.455215454102</t>
   </si>
   <si>
     <t xml:space="preserve">132.621353149414</t>
   </si>
   <si>
-    <t xml:space="preserve">134.488800048828</t>
+    <t xml:space="preserve">134.488754272461</t>
   </si>
   <si>
     <t xml:space="preserve">134.619476318359</t>
   </si>
   <si>
-    <t xml:space="preserve">136.412185668945</t>
+    <t xml:space="preserve">136.412170410156</t>
   </si>
   <si>
     <t xml:space="preserve">136.374816894531</t>
   </si>
   <si>
-    <t xml:space="preserve">135.441116333008</t>
+    <t xml:space="preserve">135.441131591797</t>
   </si>
   <si>
     <t xml:space="preserve">138.484985351562</t>
   </si>
   <si>
-    <t xml:space="preserve">138.055511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.148834228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.225387573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.123657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.43083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.208694458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.179672241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.125640869141</t>
+    <t xml:space="preserve">138.055465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.148864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.22541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.12370300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.430847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.20866394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.179718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.125564575195</t>
   </si>
   <si>
     <t xml:space="preserve">135.833282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">135.795974731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.239547729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.355377197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.448776245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.79328918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.334022521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.802772521973</t>
+    <t xml:space="preserve">135.795913696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.239532470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.355354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.448738098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.793243408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.334045410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.802780151367</t>
   </si>
   <si>
     <t xml:space="preserve">121.473136901855</t>
@@ -1748,121 +1748,121 @@
     <t xml:space="preserve">122.854988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">121.155693054199</t>
+    <t xml:space="preserve">121.155670166016</t>
   </si>
   <si>
     <t xml:space="preserve">119.717796325684</t>
   </si>
   <si>
-    <t xml:space="preserve">120.800880432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.87557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.736473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.221992492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.245346069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.733673095703</t>
+    <t xml:space="preserve">120.80086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.875595092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.736457824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.221977233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.245338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.733642578125</t>
   </si>
   <si>
     <t xml:space="preserve">120.409812927246</t>
   </si>
   <si>
-    <t xml:space="preserve">120.578804016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.48038482666</t>
+    <t xml:space="preserve">120.578834533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.480361938477</t>
   </si>
   <si>
     <t xml:space="preserve">120.071731567383</t>
   </si>
   <si>
-    <t xml:space="preserve">118.174758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.062088012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.20777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.42350769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.170204162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.479850769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.446846008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.052436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.832138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.30167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.099655151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.625526428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.799156188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.686973571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.592544555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.554962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.639747619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.710311889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.729072570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.61181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.597595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.334671020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.583389282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.785430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.193557739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.70979309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.977317810059</t>
+    <t xml:space="preserve">118.174766540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.062080383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.207763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.423522949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.170211791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.479843139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.446830749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.052429199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.832130432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.301689147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.099632263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.625534057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.799140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.686965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.592529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.554969787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.63973236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.710296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.729095458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.611824035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.597625732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.334678649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.583396911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.785438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.193542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.709762573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.97728729248</t>
   </si>
   <si>
     <t xml:space="preserve">116.747375488281</t>
@@ -1871,67 +1871,67 @@
     <t xml:space="preserve">116.108764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">121.424026489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.335166931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.546379089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.23161315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.869705200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.06665802002</t>
+    <t xml:space="preserve">121.424018859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.335182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.546333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.231620788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.869682312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.06664276123</t>
   </si>
   <si>
     <t xml:space="preserve">117.348365783691</t>
   </si>
   <si>
-    <t xml:space="preserve">115.150901794434</t>
+    <t xml:space="preserve">115.150894165039</t>
   </si>
   <si>
     <t xml:space="preserve">113.12247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">112.615379333496</t>
+    <t xml:space="preserve">112.615364074707</t>
   </si>
   <si>
     <t xml:space="preserve">111.939224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">113.347869873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.563606262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.229598999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.835159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.530097961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.666122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.684906005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.511306762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.137229919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.221473693848</t>
+    <t xml:space="preserve">113.347862243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.563583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.22957611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.835151672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.530082702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.666114807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.68489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.511299133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.137199401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.221466064453</t>
   </si>
   <si>
     <t xml:space="preserve">116.202682495117</t>
@@ -1940,31 +1940,31 @@
     <t xml:space="preserve">113.573249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">117.104217529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.319953918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.939102172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.97834777832</t>
+    <t xml:space="preserve">117.104209899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.319946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.939109802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.978363037109</t>
   </si>
   <si>
     <t xml:space="preserve">113.354804992676</t>
   </si>
   <si>
-    <t xml:space="preserve">112.221069335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.504493713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.164375305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.359222412109</t>
+    <t xml:space="preserve">112.221054077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.504501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.164360046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.359184265137</t>
   </si>
   <si>
     <t xml:space="preserve">112.901298522949</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">115.338829040527</t>
   </si>
   <si>
-    <t xml:space="preserve">113.449264526367</t>
+    <t xml:space="preserve">113.449272155762</t>
   </si>
   <si>
     <t xml:space="preserve">114.318473815918</t>
@@ -1982,40 +1982,40 @@
     <t xml:space="preserve">115.830116271973</t>
   </si>
   <si>
-    <t xml:space="preserve">114.828666687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.846076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.447799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.469635009766</t>
+    <t xml:space="preserve">114.828659057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.846084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.447814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.469650268555</t>
   </si>
   <si>
     <t xml:space="preserve">116.151336669922</t>
   </si>
   <si>
-    <t xml:space="preserve">122.651428222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.841835021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.353492736816</t>
+    <t xml:space="preserve">122.65145111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.84188079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.353515625</t>
   </si>
   <si>
     <t xml:space="preserve">124.843322753906</t>
   </si>
   <si>
-    <t xml:space="preserve">126.411643981934</t>
+    <t xml:space="preserve">126.41170501709</t>
   </si>
   <si>
     <t xml:space="preserve">133.327453613281</t>
   </si>
   <si>
-    <t xml:space="preserve">131.948104858398</t>
+    <t xml:space="preserve">131.948059082031</t>
   </si>
   <si>
     <t xml:space="preserve">131.267837524414</t>
@@ -2024,154 +2024,154 @@
     <t xml:space="preserve">129.737289428711</t>
   </si>
   <si>
-    <t xml:space="preserve">129.96403503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.416076660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.58317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.471267700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.113723754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.827362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.392761230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.904449462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.016342163086</t>
+    <t xml:space="preserve">129.964050292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.416061401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.583168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.471298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.11376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.827377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.392768859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.904434204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.016311645508</t>
   </si>
   <si>
     <t xml:space="preserve">128.603546142578</t>
   </si>
   <si>
-    <t xml:space="preserve">145.11833190918</t>
+    <t xml:space="preserve">145.118316650391</t>
   </si>
   <si>
     <t xml:space="preserve">139.978713989258</t>
   </si>
   <si>
-    <t xml:space="preserve">144.645904541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.11979675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.047119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.839279174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.714370727539</t>
+    <t xml:space="preserve">144.645935058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.119781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.047164916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.839324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.714385986328</t>
   </si>
   <si>
     <t xml:space="preserve">156.833602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">155.076324462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.760925292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.032836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.996490478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.992141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.125823974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.349685668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.804656982422</t>
+    <t xml:space="preserve">155.076309204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.760955810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.032821655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.996505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.992080688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.125854492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.349655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.804626464844</t>
   </si>
   <si>
     <t xml:space="preserve">156.72021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">154.962966918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.137435913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.704299926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.461547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.814697265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.157760620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.008773803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.819534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.56086730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.793991088867</t>
+    <t xml:space="preserve">154.962936401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.137420654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.70426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.461563110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.814712524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.157730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.0087890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.819549560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.560791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.793975830078</t>
   </si>
   <si>
     <t xml:space="preserve">161.161361694336</t>
   </si>
   <si>
-    <t xml:space="preserve">159.831985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.856842041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.932159423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.205261230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.964920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.970809936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.907943725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.376846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.756652832031</t>
+    <t xml:space="preserve">159.831954956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.856826782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.932189941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.20524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.964889526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.970825195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.907913208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.376800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.756607055664</t>
   </si>
   <si>
     <t xml:space="preserve">158.958358764648</t>
   </si>
   <si>
-    <t xml:space="preserve">159.338180541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.617172241211</t>
+    <t xml:space="preserve">159.338150024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.617141723633</t>
   </si>
   <si>
     <t xml:space="preserve">167.884338378906</t>
@@ -2180,49 +2180,49 @@
     <t xml:space="preserve">167.409561157227</t>
   </si>
   <si>
-    <t xml:space="preserve">165.890243530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.661666870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.326370239258</t>
+    <t xml:space="preserve">165.890213012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.661697387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.326385498047</t>
   </si>
   <si>
     <t xml:space="preserve">151.741592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">151.931518554688</t>
+    <t xml:space="preserve">151.931533813477</t>
   </si>
   <si>
     <t xml:space="preserve">149.082824707031</t>
   </si>
   <si>
-    <t xml:space="preserve">147.183654785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.753387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.133224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.462631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.47444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.993774414062</t>
+    <t xml:space="preserve">147.183639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.753402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.133285522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.462600708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.474411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.993759155273</t>
   </si>
   <si>
     <t xml:space="preserve">148.89289855957</t>
   </si>
   <si>
-    <t xml:space="preserve">150.602111816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.792007446289</t>
+    <t xml:space="preserve">150.602142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.792037963867</t>
   </si>
   <si>
     <t xml:space="preserve">151.399765014648</t>
@@ -2231,10 +2231,10 @@
     <t xml:space="preserve">151.456741333008</t>
   </si>
   <si>
-    <t xml:space="preserve">148.703018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.284530639648</t>
+    <t xml:space="preserve">148.702972412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.284484863281</t>
   </si>
   <si>
     <t xml:space="preserve">146.234100341797</t>
@@ -2243,28 +2243,28 @@
     <t xml:space="preserve">145.854278564453</t>
   </si>
   <si>
-    <t xml:space="preserve">144.904678344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.424026489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.323150634766</t>
+    <t xml:space="preserve">144.904663085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.424011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.323135375977</t>
   </si>
   <si>
     <t xml:space="preserve">149.84245300293</t>
   </si>
   <si>
-    <t xml:space="preserve">150.412200927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.652587890625</t>
+    <t xml:space="preserve">150.412231445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.652572631836</t>
   </si>
   <si>
     <t xml:space="preserve">148.513076782227</t>
   </si>
   <si>
-    <t xml:space="preserve">146.803848266602</t>
+    <t xml:space="preserve">146.803863525391</t>
   </si>
   <si>
     <t xml:space="preserve">143.955123901367</t>
@@ -2273,7 +2273,7 @@
     <t xml:space="preserve">140.346740722656</t>
   </si>
   <si>
-    <t xml:space="preserve">141.486221313477</t>
+    <t xml:space="preserve">141.486251831055</t>
   </si>
   <si>
     <t xml:space="preserve">143.575271606445</t>
@@ -2282,49 +2282,49 @@
     <t xml:space="preserve">146.044189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">152.121429443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.691192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.070983886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.836578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.693557739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.220916748047</t>
+    <t xml:space="preserve">152.12141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.691223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.071014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.83659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.69352722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.220932006836</t>
   </si>
   <si>
     <t xml:space="preserve">154.457229614258</t>
   </si>
   <si>
-    <t xml:space="preserve">152.929840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.979904174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.175506591797</t>
+    <t xml:space="preserve">152.929824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.979949951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.175567626953</t>
   </si>
   <si>
     <t xml:space="preserve">157.702941894531</t>
   </si>
   <si>
-    <t xml:space="preserve">155.984619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.361755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.748321533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.225631713867</t>
+    <t xml:space="preserve">155.984588623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.361770629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.748306274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.225646972656</t>
   </si>
   <si>
     <t xml:space="preserve">154.839080810547</t>
@@ -2333,130 +2333,130 @@
     <t xml:space="preserve">156.366485595703</t>
   </si>
   <si>
-    <t xml:space="preserve">159.803115844727</t>
+    <t xml:space="preserve">159.803085327148</t>
   </si>
   <si>
     <t xml:space="preserve">171.640380859375</t>
   </si>
   <si>
-    <t xml:space="preserve">170.876663208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.076965332031</t>
+    <t xml:space="preserve">170.876647949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.076995849609</t>
   </si>
   <si>
     <t xml:space="preserve">183.00032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">176.365737915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.749938964844</t>
+    <t xml:space="preserve">176.36572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.749908447266</t>
   </si>
   <si>
     <t xml:space="preserve">175.840667724609</t>
   </si>
   <si>
-    <t xml:space="preserve">176.222549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.22721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.270248413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.038650512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.800003051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.265563964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.243667602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.527694702148</t>
+    <t xml:space="preserve">176.222534179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.227188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.270278930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.038681030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.800033569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.265548706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.243682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.527709960938</t>
   </si>
   <si>
     <t xml:space="preserve">182.093414306641</t>
   </si>
   <si>
-    <t xml:space="preserve">184.432205200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.291412353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.102813720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.773406982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.491714477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.918960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.969039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.775756835938</t>
+    <t xml:space="preserve">184.432235717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.291442871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.102798461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.773391723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.491729736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.918930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.968994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.775787353516</t>
   </si>
   <si>
     <t xml:space="preserve">192.069198608398</t>
   </si>
   <si>
-    <t xml:space="preserve">189.682632446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.446334838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.828186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.584823608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.677932739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.296081542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.591888427734</t>
+    <t xml:space="preserve">189.682647705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.446365356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.828155517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.584838867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.677947998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.296112060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.591873168945</t>
   </si>
   <si>
     <t xml:space="preserve">191.973739624023</t>
   </si>
   <si>
-    <t xml:space="preserve">193.882995605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.983139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.415054321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.26953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">199.515243530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.319564819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.842269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.987808227539</t>
+    <t xml:space="preserve">193.882965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.983093261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.415069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.269500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">199.515213012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.319580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.84228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.987838745117</t>
   </si>
   <si>
     <t xml:space="preserve">207.152145385742</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">213.739028930664</t>
   </si>
   <si>
-    <t xml:space="preserve">212.975341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.929962158203</t>
+    <t xml:space="preserve">212.975357055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.929946899414</t>
   </si>
   <si>
     <t xml:space="preserve">218.321197509766</t>
@@ -2477,16 +2477,16 @@
     <t xml:space="preserve">218.703063964844</t>
   </si>
   <si>
-    <t xml:space="preserve">217.366546630859</t>
+    <t xml:space="preserve">217.366561889648</t>
   </si>
   <si>
     <t xml:space="preserve">215.498077392578</t>
   </si>
   <si>
-    <t xml:space="preserve">218.564315795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.917984008789</t>
+    <t xml:space="preserve">218.564300537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.917999267578</t>
   </si>
   <si>
     <t xml:space="preserve">223.930221557617</t>
@@ -2495,28 +2495,28 @@
     <t xml:space="preserve">221.534729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">223.067810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.205490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.444076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.156631469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.294235229492</t>
+    <t xml:space="preserve">223.067825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.205474853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.444107055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.156616210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.29426574707</t>
   </si>
   <si>
     <t xml:space="preserve">212.048599243164</t>
   </si>
   <si>
-    <t xml:space="preserve">214.060775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.186233520508</t>
+    <t xml:space="preserve">214.060791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.18620300293</t>
   </si>
   <si>
     <t xml:space="preserve">207.736724853516</t>
@@ -2528,22 +2528,22 @@
     <t xml:space="preserve">209.269836425781</t>
   </si>
   <si>
-    <t xml:space="preserve">210.994552612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.46142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.970123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.058959960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.621612548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.447402954102</t>
+    <t xml:space="preserve">210.994583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.461471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.970199584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.058929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.621658325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.447387695312</t>
   </si>
   <si>
     <t xml:space="preserve">190.920364379883</t>
@@ -2552,31 +2552,31 @@
     <t xml:space="preserve">191.495315551758</t>
   </si>
   <si>
-    <t xml:space="preserve">187.902069091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.087615966797</t>
+    <t xml:space="preserve">187.902099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.087600708008</t>
   </si>
   <si>
     <t xml:space="preserve">189.531005859375</t>
   </si>
   <si>
-    <t xml:space="preserve">189.626800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.99787902832</t>
+    <t xml:space="preserve">189.626815795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.997909545898</t>
   </si>
   <si>
     <t xml:space="preserve">190.632934570312</t>
   </si>
   <si>
-    <t xml:space="preserve">190.537109375</t>
+    <t xml:space="preserve">190.537124633789</t>
   </si>
   <si>
     <t xml:space="preserve">185.889862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">182.152893066406</t>
+    <t xml:space="preserve">182.152877807617</t>
   </si>
   <si>
     <t xml:space="preserve">188.572814941406</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">193.651260375977</t>
   </si>
   <si>
-    <t xml:space="preserve">189.770553588867</t>
+    <t xml:space="preserve">189.770568847656</t>
   </si>
   <si>
     <t xml:space="preserve">185.410766601562</t>
@@ -2594,31 +2594,31 @@
     <t xml:space="preserve">190.39338684082</t>
   </si>
   <si>
-    <t xml:space="preserve">188.237411499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.501419067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.172149658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.525833129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.555419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.938674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">194.992721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.471801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.442230224609</t>
+    <t xml:space="preserve">188.237426757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.501403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.172180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.525817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.555435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.938690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194.992706298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.471817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.442260742188</t>
   </si>
   <si>
     <t xml:space="preserve">198.729690551758</t>
@@ -2627,43 +2627,43 @@
     <t xml:space="preserve">200.358612060547</t>
   </si>
   <si>
-    <t xml:space="preserve">198.538055419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.921325683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.987548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.849945068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.2158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.832534790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.802932739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.353439331055</t>
+    <t xml:space="preserve">198.538040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.921356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.987533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.84992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.215774536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.83251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.802963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.353454589844</t>
   </si>
   <si>
     <t xml:space="preserve">213.006790161133</t>
   </si>
   <si>
-    <t xml:space="preserve">217.989395141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.593902587891</t>
+    <t xml:space="preserve">217.989410400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.593933105469</t>
   </si>
   <si>
     <t xml:space="preserve">215.977188110352</t>
   </si>
   <si>
-    <t xml:space="preserve">219.905807495117</t>
+    <t xml:space="preserve">219.905776977539</t>
   </si>
   <si>
     <t xml:space="preserve">220.768142700195</t>
@@ -2672,67 +2672,67 @@
     <t xml:space="preserve">218.892776489258</t>
   </si>
   <si>
-    <t xml:space="preserve">217.161651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.277465820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.297134399414</t>
+    <t xml:space="preserve">217.161636352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.277450561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.297119140625</t>
   </si>
   <si>
     <t xml:space="preserve">221.200958251953</t>
   </si>
   <si>
-    <t xml:space="preserve">223.316802978516</t>
+    <t xml:space="preserve">223.316772460938</t>
   </si>
   <si>
     <t xml:space="preserve">224.663238525391</t>
   </si>
   <si>
-    <t xml:space="preserve">223.509140014648</t>
+    <t xml:space="preserve">223.509155273438</t>
   </si>
   <si>
     <t xml:space="preserve">224.182373046875</t>
   </si>
   <si>
-    <t xml:space="preserve">227.06755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.162658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.064392089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.23811340332</t>
+    <t xml:space="preserve">227.067626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.162704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.064376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.238174438477</t>
   </si>
   <si>
     <t xml:space="preserve">211.198822021484</t>
   </si>
   <si>
-    <t xml:space="preserve">209.756210327148</t>
+    <t xml:space="preserve">209.756195068359</t>
   </si>
   <si>
     <t xml:space="preserve">207.351837158203</t>
   </si>
   <si>
-    <t xml:space="preserve">203.985763549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.313598632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.640335083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.506988525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.929946899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.279541015625</t>
+    <t xml:space="preserve">203.985748291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.313583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.640350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.507019042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.929931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.279586791992</t>
   </si>
   <si>
     <t xml:space="preserve">237.646759033203</t>
@@ -2741,88 +2741,88 @@
     <t xml:space="preserve">227.25993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">225.624969482422</t>
+    <t xml:space="preserve">225.624954223633</t>
   </si>
   <si>
     <t xml:space="preserve">224.567047119141</t>
   </si>
   <si>
-    <t xml:space="preserve">232.068634033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.819442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.434722900391</t>
+    <t xml:space="preserve">232.068649291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.81950378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.43473815918</t>
   </si>
   <si>
     <t xml:space="preserve">235.530914306641</t>
   </si>
   <si>
-    <t xml:space="preserve">228.317840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.644638061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220.527725219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.662170410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.123352050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.373641967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.256744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.19775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.544204711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.409729003906</t>
+    <t xml:space="preserve">228.317855834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.644622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.527740478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.662155151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.12336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.373626708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.256729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.197738647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.544174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.409759521484</t>
   </si>
   <si>
     <t xml:space="preserve">211.102661132812</t>
   </si>
   <si>
-    <t xml:space="preserve">209.948547363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.159530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.042602539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.869918823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.813049316406</t>
+    <t xml:space="preserve">209.948577880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.15950012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.042617797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.869903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.813064575195</t>
   </si>
   <si>
     <t xml:space="preserve">208.121215820312</t>
   </si>
   <si>
-    <t xml:space="preserve">207.928894042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.98681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.794479370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.352890014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.101608276367</t>
+    <t xml:space="preserve">207.928924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.986801147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.794494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.352920532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.101593017578</t>
   </si>
   <si>
     <t xml:space="preserve">202.639297485352</t>
@@ -2831,127 +2831,127 @@
     <t xml:space="preserve">202.158432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">205.139831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.927810668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.234939575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.959442138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.076293945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.525756835938</t>
+    <t xml:space="preserve">205.139877319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.927841186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.234924316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.959426879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.076309204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.525726318359</t>
   </si>
   <si>
     <t xml:space="preserve">206.593154907227</t>
   </si>
   <si>
-    <t xml:space="preserve">204.853820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.892028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203.404357910156</t>
+    <t xml:space="preserve">204.85383605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.892044067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203.404388427734</t>
   </si>
   <si>
     <t xml:space="preserve">205.916763305664</t>
   </si>
   <si>
-    <t xml:space="preserve">205.626861572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">216.256057739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.130249023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.806655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.957214355469</t>
+    <t xml:space="preserve">205.626846313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">216.256103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.13020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.957183837891</t>
   </si>
   <si>
     <t xml:space="preserve">223.116714477539</t>
   </si>
   <si>
-    <t xml:space="preserve">229.397613525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.90998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">233.262802124023</t>
+    <t xml:space="preserve">229.39762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.910018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">233.262786865234</t>
   </si>
   <si>
     <t xml:space="preserve">232.393127441406</t>
   </si>
   <si>
-    <t xml:space="preserve">231.233596801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">237.417861938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">236.161666870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.312255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.40885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">246.307693481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.332443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.651550292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">249.883041381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.525756835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.105499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.294250488281</t>
+    <t xml:space="preserve">231.233581542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.417846679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">236.161651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.312240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.408843994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">246.307708740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.332473754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.65153503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">249.883026123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.525695800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.105529785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.29426574707</t>
   </si>
   <si>
     <t xml:space="preserve">255.004348754883</t>
   </si>
   <si>
-    <t xml:space="preserve">251.622283935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.008880615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250.656051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.844787597656</t>
+    <t xml:space="preserve">251.622344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.008865356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250.656066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.844833374023</t>
   </si>
   <si>
     <t xml:space="preserve">257.468444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">260.802124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266.020080566406</t>
+    <t xml:space="preserve">260.802062988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266.020111083984</t>
   </si>
   <si>
     <t xml:space="preserve">275.489776611328</t>
@@ -2960,16 +2960,16 @@
     <t xml:space="preserve">276.890838623047</t>
   </si>
   <si>
-    <t xml:space="preserve">275.006652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.66845703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.305480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.691925048828</t>
+    <t xml:space="preserve">275.006622314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.668395996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.305511474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.692047119141</t>
   </si>
   <si>
     <t xml:space="preserve">265.295318603516</t>
@@ -2978,115 +2978,115 @@
     <t xml:space="preserve">263.556060791016</t>
   </si>
   <si>
-    <t xml:space="preserve">253.79655456543</t>
+    <t xml:space="preserve">253.796447753906</t>
   </si>
   <si>
     <t xml:space="preserve">252.347091674805</t>
   </si>
   <si>
-    <t xml:space="preserve">258.869537353516</t>
+    <t xml:space="preserve">258.869476318359</t>
   </si>
   <si>
     <t xml:space="preserve">269.595367431641</t>
   </si>
   <si>
-    <t xml:space="preserve">268.822387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.730163574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.536926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">264.957183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.339202880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.102142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.942504882812</t>
+    <t xml:space="preserve">268.822326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.730102539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.536956787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">264.957153320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.339233398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.10205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.942565917969</t>
   </si>
   <si>
     <t xml:space="preserve">258.579650878906</t>
   </si>
   <si>
-    <t xml:space="preserve">266.454986572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">267.405303955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">281.854309082031</t>
+    <t xml:space="preserve">266.454895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">267.405212402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281.854370117188</t>
   </si>
   <si>
     <t xml:space="preserve">277.005615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">274.290435791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.623291015625</t>
+    <t xml:space="preserve">274.290344238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.623260498047</t>
   </si>
   <si>
     <t xml:space="preserve">271.090209960938</t>
   </si>
   <si>
-    <t xml:space="preserve">275.599578857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.108520507812</t>
+    <t xml:space="preserve">275.599517822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.108551025391</t>
   </si>
   <si>
     <t xml:space="preserve">280.642211914062</t>
   </si>
   <si>
-    <t xml:space="preserve">281.466491699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">282.630157470703</t>
+    <t xml:space="preserve">281.466461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">282.630187988281</t>
   </si>
   <si>
     <t xml:space="preserve">274.532836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">280.205780029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">278.411804199219</t>
+    <t xml:space="preserve">280.205810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">278.411773681641</t>
   </si>
   <si>
     <t xml:space="preserve">284.084777832031</t>
   </si>
   <si>
-    <t xml:space="preserve">279.769409179688</t>
+    <t xml:space="preserve">279.769439697266</t>
   </si>
   <si>
     <t xml:space="preserve">275.066192626953</t>
   </si>
   <si>
-    <t xml:space="preserve">270.750854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.472015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">271.817565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.611236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.253936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270.847747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.484375</t>
+    <t xml:space="preserve">270.750885009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.471984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271.817474365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.611267089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.253997802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270.847808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.484344482422</t>
   </si>
   <si>
     <t xml:space="preserve">279.720916748047</t>
@@ -3095,19 +3095,19 @@
     <t xml:space="preserve">284.763549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">298.291473388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.455108642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.576141357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.552093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.679290771484</t>
+    <t xml:space="preserve">298.291381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.455047607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.552062988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.679321289062</t>
   </si>
   <si>
     <t xml:space="preserve">299.842987060547</t>
@@ -3128,97 +3128,97 @@
     <t xml:space="preserve">315.019409179688</t>
   </si>
   <si>
-    <t xml:space="preserve">318.364929199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.443450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.625335693359</t>
+    <t xml:space="preserve">318.365020751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.443389892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.625305175781</t>
   </si>
   <si>
     <t xml:space="preserve">318.122528076172</t>
   </si>
   <si>
-    <t xml:space="preserve">315.213287353516</t>
+    <t xml:space="preserve">315.21337890625</t>
   </si>
   <si>
     <t xml:space="preserve">309.879760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">306.825042724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.916259765625</t>
+    <t xml:space="preserve">306.825073242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.916168212891</t>
   </si>
   <si>
     <t xml:space="preserve">312.837432861328</t>
   </si>
   <si>
-    <t xml:space="preserve">316.231536865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.467803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.631530761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.661834716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.425170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.4736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.667266845703</t>
+    <t xml:space="preserve">316.231506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.4677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.631591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.661773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.425140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.473663330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.667297363281</t>
   </si>
   <si>
     <t xml:space="preserve">289.854675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">288.836517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.369812011719</t>
+    <t xml:space="preserve">288.836486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.369873046875</t>
   </si>
   <si>
     <t xml:space="preserve">287.284912109375</t>
   </si>
   <si>
-    <t xml:space="preserve">285.539428710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">283.842376708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.806823730469</t>
+    <t xml:space="preserve">285.539367675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">283.842315673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.806762695312</t>
   </si>
   <si>
     <t xml:space="preserve">297.298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">298.369110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.812561035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.574676513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.428924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.126312255859</t>
+    <t xml:space="preserve">298.369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.812591552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.574615478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.428894042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.126281738281</t>
   </si>
   <si>
     <t xml:space="preserve">309.996429443359</t>
   </si>
   <si>
-    <t xml:space="preserve">311.358642578125</t>
+    <t xml:space="preserve">311.358612060547</t>
   </si>
   <si>
     <t xml:space="preserve">309.41259765625</t>
@@ -3230,13 +3230,13 @@
     <t xml:space="preserve">303.234130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">299.925933837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294.185241699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.250152587891</t>
+    <t xml:space="preserve">299.925903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.185272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.250244140625</t>
   </si>
   <si>
     <t xml:space="preserve">300.217834472656</t>
@@ -3248,76 +3248,76 @@
     <t xml:space="preserve">304.596282958984</t>
   </si>
   <si>
-    <t xml:space="preserve">303.963836669922</t>
+    <t xml:space="preserve">303.963806152344</t>
   </si>
   <si>
     <t xml:space="preserve">306.688262939453</t>
   </si>
   <si>
-    <t xml:space="preserve">308.585632324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.299041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.969268798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.412445068359</t>
+    <t xml:space="preserve">308.585571289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.299011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.969207763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.412414550781</t>
   </si>
   <si>
     <t xml:space="preserve">299.342132568359</t>
   </si>
   <si>
-    <t xml:space="preserve">293.796081542969</t>
+    <t xml:space="preserve">293.796020507812</t>
   </si>
   <si>
     <t xml:space="preserve">293.990661621094</t>
   </si>
   <si>
-    <t xml:space="preserve">297.104278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.601867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.845092773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.082977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.883697509766</t>
+    <t xml:space="preserve">297.104248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.601928710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.845184326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.0830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.883666992188</t>
   </si>
   <si>
     <t xml:space="preserve">327.656311035156</t>
   </si>
   <si>
-    <t xml:space="preserve">324.445465087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.61279296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320.066986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.34814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.721221923828</t>
+    <t xml:space="preserve">324.445404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.612823486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320.066955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.348114013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.721282958984</t>
   </si>
   <si>
     <t xml:space="preserve">329.650939941406</t>
   </si>
   <si>
-    <t xml:space="preserve">323.375122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.758941650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327.315765380859</t>
+    <t xml:space="preserve">323.375152587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.758911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327.315795898438</t>
   </si>
   <si>
     <t xml:space="preserve">324.883270263672</t>
@@ -3326,34 +3326,34 @@
     <t xml:space="preserve">330.380676269531</t>
   </si>
   <si>
-    <t xml:space="preserve">332.521240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.580688476562</t>
+    <t xml:space="preserve">332.521331787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.580718994141</t>
   </si>
   <si>
     <t xml:space="preserve">326.245422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">325.710327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.515930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.759399414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.543121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.456787109375</t>
+    <t xml:space="preserve">325.710266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.515869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.759338378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.543151855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.456756591797</t>
   </si>
   <si>
     <t xml:space="preserve">347.748687744141</t>
   </si>
   <si>
-    <t xml:space="preserve">352.710968017578</t>
+    <t xml:space="preserve">352.710906982422</t>
   </si>
   <si>
     <t xml:space="preserve">354.802856445312</t>
@@ -3365,76 +3365,76 @@
     <t xml:space="preserve">353.829925537109</t>
   </si>
   <si>
-    <t xml:space="preserve">358.257019042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.473114013672</t>
+    <t xml:space="preserve">358.257049560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.473083496094</t>
   </si>
   <si>
     <t xml:space="preserve">352.224456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">353.63525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.429962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">349.013519287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.672576904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.946594238281</t>
+    <t xml:space="preserve">353.635284423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.429992675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">349.013580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.672546386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.946655273438</t>
   </si>
   <si>
     <t xml:space="preserve">331.531341552734</t>
   </si>
   <si>
-    <t xml:space="preserve">331.921600341797</t>
+    <t xml:space="preserve">331.921630859375</t>
   </si>
   <si>
     <t xml:space="preserve">338.898651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">339.972045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.728912353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.606689453125</t>
+    <t xml:space="preserve">339.972076416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.728942871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.606750488281</t>
   </si>
   <si>
     <t xml:space="preserve">339.581695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">339.093872070312</t>
+    <t xml:space="preserve">339.093811035156</t>
   </si>
   <si>
     <t xml:space="preserve">342.704345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">345.095062255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.435729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">344.509582519531</t>
+    <t xml:space="preserve">345.095031738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.435760498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.509552001953</t>
   </si>
   <si>
     <t xml:space="preserve">344.119232177734</t>
   </si>
   <si>
-    <t xml:space="preserve">346.510040283203</t>
+    <t xml:space="preserve">346.509979248047</t>
   </si>
   <si>
     <t xml:space="preserve">345.826904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">342.070037841797</t>
+    <t xml:space="preserve">342.070007324219</t>
   </si>
   <si>
     <t xml:space="preserve">345.582946777344</t>
@@ -3443,19 +3443,19 @@
     <t xml:space="preserve">343.680206298828</t>
   </si>
   <si>
-    <t xml:space="preserve">340.411224365234</t>
+    <t xml:space="preserve">340.4111328125</t>
   </si>
   <si>
     <t xml:space="preserve">338.801147460938</t>
   </si>
   <si>
-    <t xml:space="preserve">335.239379882812</t>
+    <t xml:space="preserve">335.239318847656</t>
   </si>
   <si>
     <t xml:space="preserve">332.751098632812</t>
   </si>
   <si>
-    <t xml:space="preserve">328.945434570312</t>
+    <t xml:space="preserve">328.945404052734</t>
   </si>
   <si>
     <t xml:space="preserve">328.994201660156</t>
@@ -3464,31 +3464,31 @@
     <t xml:space="preserve">330.116363525391</t>
   </si>
   <si>
-    <t xml:space="preserve">340.118377685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.654693603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.800689697266</t>
+    <t xml:space="preserve">340.118408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.654724121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.800659179688</t>
   </si>
   <si>
     <t xml:space="preserve">335.141815185547</t>
   </si>
   <si>
-    <t xml:space="preserve">338.605895996094</t>
+    <t xml:space="preserve">338.605926513672</t>
   </si>
   <si>
     <t xml:space="preserve">335.044219970703</t>
   </si>
   <si>
-    <t xml:space="preserve">336.703125</t>
+    <t xml:space="preserve">336.703033447266</t>
   </si>
   <si>
     <t xml:space="preserve">335.629699707031</t>
   </si>
   <si>
-    <t xml:space="preserve">337.288543701172</t>
+    <t xml:space="preserve">337.28857421875</t>
   </si>
   <si>
     <t xml:space="preserve">330.897033691406</t>
@@ -3497,28 +3497,28 @@
     <t xml:space="preserve">335.434478759766</t>
   </si>
   <si>
-    <t xml:space="preserve">325.773986816406</t>
+    <t xml:space="preserve">325.774047851562</t>
   </si>
   <si>
     <t xml:space="preserve">315.625610351562</t>
   </si>
   <si>
-    <t xml:space="preserve">321.529266357422</t>
+    <t xml:space="preserve">321.529235839844</t>
   </si>
   <si>
     <t xml:space="preserve">321.919586181641</t>
   </si>
   <si>
-    <t xml:space="preserve">326.017944335938</t>
+    <t xml:space="preserve">326.017974853516</t>
   </si>
   <si>
     <t xml:space="preserve">323.968811035156</t>
   </si>
   <si>
-    <t xml:space="preserve">325.188507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320.065521240234</t>
+    <t xml:space="preserve">325.188537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320.065490722656</t>
   </si>
   <si>
     <t xml:space="preserve">317.528411865234</t>
@@ -3527,145 +3527,145 @@
     <t xml:space="preserve">311.088043212891</t>
   </si>
   <si>
-    <t xml:space="preserve">307.672729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.428741455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">310.161041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.039672851562</t>
+    <t xml:space="preserve">307.672668457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.428833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">310.161102294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.039703369141</t>
   </si>
   <si>
     <t xml:space="preserve">308.794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">307.184875488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.477172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.131988525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.331237792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.160247802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.501770019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.575561523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.161468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.796630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.503845214844</t>
+    <t xml:space="preserve">307.184844970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.477203369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.131896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.331268310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.160217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.501800537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.575592041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.161499023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.796508789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.503814697266</t>
   </si>
   <si>
     <t xml:space="preserve">318.393707275391</t>
   </si>
   <si>
-    <t xml:space="preserve">313.595550537109</t>
+    <t xml:space="preserve">313.595581054688</t>
   </si>
   <si>
     <t xml:space="preserve">303.558532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">301.942810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.571899414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.775177001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.146087646484</t>
+    <t xml:space="preserve">301.942779541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.571929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.775146484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.146057128906</t>
   </si>
   <si>
     <t xml:space="preserve">304.341918945312</t>
   </si>
   <si>
-    <t xml:space="preserve">299.886413574219</t>
+    <t xml:space="preserve">299.886444091797</t>
   </si>
   <si>
     <t xml:space="preserve">294.011138916016</t>
   </si>
   <si>
-    <t xml:space="preserve">287.939971923828</t>
+    <t xml:space="preserve">287.939910888672</t>
   </si>
   <si>
     <t xml:space="preserve">290.192169189453</t>
   </si>
   <si>
-    <t xml:space="preserve">289.604644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.080841064453</t>
+    <t xml:space="preserve">289.604614257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.080902099609</t>
   </si>
   <si>
     <t xml:space="preserve">291.465148925781</t>
   </si>
   <si>
-    <t xml:space="preserve">289.702514648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">288.380584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.129791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">292.052703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.528900146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.969543457031</t>
+    <t xml:space="preserve">289.702545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">288.380615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.129821777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">292.052673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.528869628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.969573974609</t>
   </si>
   <si>
     <t xml:space="preserve">304.195007324219</t>
   </si>
   <si>
-    <t xml:space="preserve">304.390838623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.089782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.411651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.592712402344</t>
+    <t xml:space="preserve">304.390869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.089721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.411682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.592651367188</t>
   </si>
   <si>
     <t xml:space="preserve">301.110504150391</t>
   </si>
   <si>
-    <t xml:space="preserve">299.984344482422</t>
+    <t xml:space="preserve">299.984405517578</t>
   </si>
   <si>
     <t xml:space="preserve">305.3701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">304.48876953125</t>
+    <t xml:space="preserve">304.488800048828</t>
   </si>
   <si>
     <t xml:space="preserve">303.509582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">305.419067382812</t>
+    <t xml:space="preserve">305.419036865234</t>
   </si>
   <si>
     <t xml:space="preserve">303.950225830078</t>
@@ -3674,85 +3674,85 @@
     <t xml:space="preserve">307.965026855469</t>
   </si>
   <si>
-    <t xml:space="preserve">314.721618652344</t>
+    <t xml:space="preserve">314.721649169922</t>
   </si>
   <si>
     <t xml:space="preserve">318.442687988281</t>
   </si>
   <si>
-    <t xml:space="preserve">325.884796142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.018280029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.605804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.976684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">333.326873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.110260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.54345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.760070800781</t>
+    <t xml:space="preserve">325.884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.018249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.605834960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.976715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">333.326843261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.110198974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.543548583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.760040283203</t>
   </si>
   <si>
     <t xml:space="preserve">341.944000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">340.768890380859</t>
+    <t xml:space="preserve">340.768981933594</t>
   </si>
   <si>
     <t xml:space="preserve">344.685821533203</t>
   </si>
   <si>
-    <t xml:space="preserve">352.323699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">358.786590576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.433349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">380.133666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">382.679565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385.225524902344</t>
+    <t xml:space="preserve">352.32373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">358.786529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.433380126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">380.133636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">382.679534912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385.225555419922</t>
   </si>
   <si>
     <t xml:space="preserve">385.421417236328</t>
   </si>
   <si>
-    <t xml:space="preserve">386.204772949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389.338287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">395.358032226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389.466003417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.394012451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.197601318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">398.304107666016</t>
+    <t xml:space="preserve">386.204803466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">389.338256835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">395.358062744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">389.465972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.393981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.197570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">398.304016113281</t>
   </si>
   <si>
     <t xml:space="preserve">401.0537109375</t>
@@ -3764,34 +3764,34 @@
     <t xml:space="preserve">388.483917236328</t>
   </si>
   <si>
-    <t xml:space="preserve">388.091217041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">387.109069824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">391.233581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">396.143615722656</t>
+    <t xml:space="preserve">388.091156005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">387.109130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">391.233612060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">396.143646240234</t>
   </si>
   <si>
     <t xml:space="preserve">388.680328369141</t>
   </si>
   <si>
-    <t xml:space="preserve">396.536407470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.160125732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">408.124145507812</t>
+    <t xml:space="preserve">396.536437988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.160217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">408.124206542969</t>
   </si>
   <si>
     <t xml:space="preserve">404.785369873047</t>
   </si>
   <si>
-    <t xml:space="preserve">405.963714599609</t>
+    <t xml:space="preserve">405.963745117188</t>
   </si>
   <si>
     <t xml:space="preserve">407.731384277344</t>
@@ -3800,19 +3800,19 @@
     <t xml:space="preserve">403.999694824219</t>
   </si>
   <si>
-    <t xml:space="preserve">405.178192138672</t>
+    <t xml:space="preserve">405.178131103516</t>
   </si>
   <si>
     <t xml:space="preserve">402.821319580078</t>
   </si>
   <si>
-    <t xml:space="preserve">407.534942626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.749359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">413.034271240234</t>
+    <t xml:space="preserve">407.534973144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.749389648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413.034240722656</t>
   </si>
   <si>
     <t xml:space="preserve">409.498992919922</t>
@@ -3821,19 +3821,19 @@
     <t xml:space="preserve">417.551513671875</t>
   </si>
   <si>
-    <t xml:space="preserve">419.122711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.479553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.980316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.711883544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">420.497528076172</t>
+    <t xml:space="preserve">419.122741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.479583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.980255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.711944580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420.497497558594</t>
   </si>
   <si>
     <t xml:space="preserve">405.570922851562</t>
@@ -3854,34 +3854,34 @@
     <t xml:space="preserve">391.822784423828</t>
   </si>
   <si>
-    <t xml:space="preserve">395.947174072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">394.572418212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.338531494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">410.284637451172</t>
+    <t xml:space="preserve">395.947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">394.572387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.338562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">410.284606933594</t>
   </si>
   <si>
     <t xml:space="preserve">409.302581787109</t>
   </si>
   <si>
-    <t xml:space="preserve">408.320556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.142181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.356536865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.232177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.767395019531</t>
+    <t xml:space="preserve">408.320587158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.142211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.356567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.232116699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.767425537109</t>
   </si>
   <si>
     <t xml:space="preserve">413.819854736328</t>
@@ -3896,37 +3896,37 @@
     <t xml:space="preserve">403.410552978516</t>
   </si>
   <si>
-    <t xml:space="preserve">477.650604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">474.508239746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">470.187286376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">474.115356445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">486.252044677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">488.614349365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">495.11083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">493.634399414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">492.157928466797</t>
+    <t xml:space="preserve">477.650665283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">474.508209228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470.187316894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">474.115417480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">486.251983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">488.614379882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">495.110870361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">493.634429931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">492.157897949219</t>
   </si>
   <si>
     <t xml:space="preserve">496.095123291016</t>
   </si>
   <si>
-    <t xml:space="preserve">500.524566650391</t>
+    <t xml:space="preserve">500.524597167969</t>
   </si>
   <si>
     <t xml:space="preserve">499.048065185547</t>
@@ -3938,31 +3938,31 @@
     <t xml:space="preserve">503.969696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">501.016723632812</t>
+    <t xml:space="preserve">501.016754150391</t>
   </si>
   <si>
     <t xml:space="preserve">495.60302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">500.032440185547</t>
+    <t xml:space="preserve">500.032379150391</t>
   </si>
   <si>
     <t xml:space="preserve">507.414794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">511.844207763672</t>
+    <t xml:space="preserve">511.844177246094</t>
   </si>
   <si>
     <t xml:space="preserve">514.797180175781</t>
   </si>
   <si>
-    <t xml:space="preserve">509.383453369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">527.593383789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">535.959838867188</t>
+    <t xml:space="preserve">509.383544921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">527.59326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">535.9599609375</t>
   </si>
   <si>
     <t xml:space="preserve">547.279541015625</t>
@@ -3974,37 +3974,37 @@
     <t xml:space="preserve">546.787475585938</t>
   </si>
   <si>
-    <t xml:space="preserve">550.232482910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">539.897277832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">528.08544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">526.116760253906</t>
+    <t xml:space="preserve">550.232543945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">539.897216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">528.085388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">526.116821289062</t>
   </si>
   <si>
     <t xml:space="preserve">512.336364746094</t>
   </si>
   <si>
-    <t xml:space="preserve">510.859893798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">489.992370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.461853027344</t>
+    <t xml:space="preserve">510.859832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">489.992431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.461822509766</t>
   </si>
   <si>
     <t xml:space="preserve">517.750122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">532.514892578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">554.661926269531</t>
+    <t xml:space="preserve">532.514953613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">554.662048339844</t>
   </si>
   <si>
     <t xml:space="preserve">568.4423828125</t>
@@ -4016,37 +4016,37 @@
     <t xml:space="preserve">575.824768066406</t>
   </si>
   <si>
-    <t xml:space="preserve">561.552124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569.4267578125</t>
+    <t xml:space="preserve">561.552185058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569.426696777344</t>
   </si>
   <si>
     <t xml:space="preserve">545.803100585938</t>
   </si>
   <si>
-    <t xml:space="preserve">543.342224121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">540.389343261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">549.248229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">555.646240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.022705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">523.656005859375</t>
+    <t xml:space="preserve">543.34228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540.389404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">549.248291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">555.646301269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.022766113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">523.655944824219</t>
   </si>
   <si>
     <t xml:space="preserve">514.304931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">517.257934570312</t>
+    <t xml:space="preserve">517.257873535156</t>
   </si>
   <si>
     <t xml:space="preserve">534.975646972656</t>
@@ -4058,19 +4058,19 @@
     <t xml:space="preserve">553.185485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">554.299987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">536.053466796875</t>
+    <t xml:space="preserve">554.300109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">536.053527832031</t>
   </si>
   <si>
     <t xml:space="preserve">532.108215332031</t>
   </si>
   <si>
-    <t xml:space="preserve">536.546630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">542.46435546875</t>
+    <t xml:space="preserve">536.546691894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">542.464416503906</t>
   </si>
   <si>
     <t xml:space="preserve">537.532897949219</t>
@@ -4079,46 +4079,46 @@
     <t xml:space="preserve">541.478088378906</t>
   </si>
   <si>
-    <t xml:space="preserve">543.450805664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">533.094604492188</t>
+    <t xml:space="preserve">543.45068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">533.094421386719</t>
   </si>
   <si>
     <t xml:space="preserve">531.121948242188</t>
   </si>
   <si>
-    <t xml:space="preserve">538.026000976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">540.491821289062</t>
+    <t xml:space="preserve">538.026123046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540.491760253906</t>
   </si>
   <si>
     <t xml:space="preserve">532.601379394531</t>
   </si>
   <si>
-    <t xml:space="preserve">537.039794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">534.080871582031</t>
+    <t xml:space="preserve">537.039855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534.080932617188</t>
   </si>
   <si>
     <t xml:space="preserve">539.012390136719</t>
   </si>
   <si>
-    <t xml:space="preserve">526.1904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">531.615173339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">517.806884765625</t>
+    <t xml:space="preserve">526.190551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">531.615112304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">517.806945800781</t>
   </si>
   <si>
     <t xml:space="preserve">513.368591308594</t>
   </si>
   <si>
-    <t xml:space="preserve">523.231689453125</t>
+    <t xml:space="preserve">523.231628417969</t>
   </si>
   <si>
     <t xml:space="preserve">519.779541015625</t>
@@ -4130,22 +4130,22 @@
     <t xml:space="preserve">509.916564941406</t>
   </si>
   <si>
-    <t xml:space="preserve">511.395965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">518.793212890625</t>
+    <t xml:space="preserve">511.396057128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">518.793273925781</t>
   </si>
   <si>
     <t xml:space="preserve">520.765808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">527.669860839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">552.820495605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567.121887207031</t>
+    <t xml:space="preserve">527.669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">552.820617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567.121826171875</t>
   </si>
   <si>
     <t xml:space="preserve">557.258911132812</t>
@@ -4160,31 +4160,31 @@
     <t xml:space="preserve">568.108154296875</t>
   </si>
   <si>
-    <t xml:space="preserve">573.53271484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">581.423217773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">583.888977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">575.012268066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">561.697204589844</t>
+    <t xml:space="preserve">573.532897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">581.423278808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">583.888916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">575.012390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">561.697326660156</t>
   </si>
   <si>
     <t xml:space="preserve">569.094421386719</t>
   </si>
   <si>
-    <t xml:space="preserve">568.601440429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">577.47802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">572.053466796875</t>
+    <t xml:space="preserve">568.601318359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">577.477966308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">572.053405761719</t>
   </si>
   <si>
     <t xml:space="preserve">577.97119140625</t>
@@ -4193,34 +4193,34 @@
     <t xml:space="preserve">587.341064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">587.834167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">585.861633300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">593.751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">609.039611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">646.02587890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">642.080627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">668.217468261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">675.61474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677.094299316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">671.176391601562</t>
+    <t xml:space="preserve">587.834228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">585.861572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">593.751892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">609.03955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">646.025817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">642.08056640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">668.217529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">675.614807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">677.09423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">671.176513671875</t>
   </si>
   <si>
     <t xml:space="preserve">679.559997558594</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">695.172973632812</t>
   </si>
   <si>
-    <t xml:space="preserve">698.631591796875</t>
+    <t xml:space="preserve">698.631530761719</t>
   </si>
   <si>
     <t xml:space="preserve">722.841491699219</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">726.300170898438</t>
   </si>
   <si>
-    <t xml:space="preserve">700.11376953125</t>
+    <t xml:space="preserve">700.113708496094</t>
   </si>
   <si>
     <t xml:space="preserve">681.338684082031</t>
@@ -4250,13 +4250,13 @@
     <t xml:space="preserve">697.643310546875</t>
   </si>
   <si>
-    <t xml:space="preserve">705.054565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">699.125671386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">688.255798339844</t>
+    <t xml:space="preserve">705.054504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">699.125610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">688.255859375</t>
   </si>
   <si>
     <t xml:space="preserve">686.279479980469</t>
@@ -4265,13 +4265,13 @@
     <t xml:space="preserve">709.995361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">722.347473144531</t>
+    <t xml:space="preserve">722.347412109375</t>
   </si>
   <si>
     <t xml:space="preserve">710.489501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">711.971740722656</t>
+    <t xml:space="preserve">711.971618652344</t>
   </si>
   <si>
     <t xml:space="preserve">690.232116699219</t>
@@ -4280,7 +4280,7 @@
     <t xml:space="preserve">660.587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">678.868286132812</t>
+    <t xml:space="preserve">678.868225097656</t>
   </si>
   <si>
     <t xml:space="preserve">683.315002441406</t>
@@ -4289,22 +4289,22 @@
     <t xml:space="preserve">682.326904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">697.149291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">704.066345214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">706.042663574219</t>
+    <t xml:space="preserve">697.149353027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.560485839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">704.066467285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706.042724609375</t>
   </si>
   <si>
     <t xml:space="preserve">720.865173339844</t>
   </si>
   <si>
-    <t xml:space="preserve">698.829162597656</t>
+    <t xml:space="preserve">698.829223632812</t>
   </si>
   <si>
     <t xml:space="preserve">709.896667480469</t>
@@ -4313,37 +4313,37 @@
     <t xml:space="preserve">704.165222167969</t>
   </si>
   <si>
-    <t xml:space="preserve">709.204956054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">708.710815429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">689.737976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">701.991271972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">702.090026855469</t>
+    <t xml:space="preserve">709.204895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">708.710876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">689.738037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">701.991333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">702.090148925781</t>
   </si>
   <si>
     <t xml:space="preserve">706.141540527344</t>
   </si>
   <si>
-    <t xml:space="preserve">695.469482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">694.283569335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677.188354492188</t>
+    <t xml:space="preserve">695.469421386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">694.283630371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">677.188415527344</t>
   </si>
   <si>
     <t xml:space="preserve">676.6943359375</t>
   </si>
   <si>
-    <t xml:space="preserve">685.39013671875</t>
+    <t xml:space="preserve">685.390075683594</t>
   </si>
   <si>
     <t xml:space="preserve">678.077697753906</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">667.603210449219</t>
   </si>
   <si>
-    <t xml:space="preserve">680.745849609375</t>
+    <t xml:space="preserve">680.745788574219</t>
   </si>
   <si>
     <t xml:space="preserve">674.619201660156</t>
@@ -4361,31 +4361,31 @@
     <t xml:space="preserve">711.576416015625</t>
   </si>
   <si>
-    <t xml:space="preserve">674.520263671875</t>
+    <t xml:space="preserve">674.520324707031</t>
   </si>
   <si>
     <t xml:space="preserve">688.848693847656</t>
   </si>
   <si>
-    <t xml:space="preserve">709.106079101562</t>
+    <t xml:space="preserve">709.106018066406</t>
   </si>
   <si>
     <t xml:space="preserve">712.367004394531</t>
   </si>
   <si>
-    <t xml:space="preserve">690.133361816406</t>
+    <t xml:space="preserve">690.13330078125</t>
   </si>
   <si>
     <t xml:space="preserve">690.528564453125</t>
   </si>
   <si>
-    <t xml:space="preserve">710.328735351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.576721191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">701.517639160156</t>
+    <t xml:space="preserve">710.328674316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.57666015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">701.517700195312</t>
   </si>
   <si>
     <t xml:space="preserve">712.407653808594</t>
@@ -4394,10 +4394,10 @@
     <t xml:space="preserve">732.603759765625</t>
   </si>
   <si>
-    <t xml:space="preserve">729.336791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">744.186828613281</t>
+    <t xml:space="preserve">729.336730957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">744.186889648438</t>
   </si>
   <si>
     <t xml:space="preserve">737.2568359375</t>
@@ -4406,52 +4406,52 @@
     <t xml:space="preserve">739.434875488281</t>
   </si>
   <si>
-    <t xml:space="preserve">733.593811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">744.087829589844</t>
+    <t xml:space="preserve">733.59375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">744.087890625</t>
   </si>
   <si>
     <t xml:space="preserve">744.681884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">746.661865234375</t>
+    <t xml:space="preserve">746.661926269531</t>
   </si>
   <si>
     <t xml:space="preserve">758.640930175781</t>
   </si>
   <si>
-    <t xml:space="preserve">754.185791015625</t>
+    <t xml:space="preserve">754.185852050781</t>
   </si>
   <si>
     <t xml:space="preserve">757.749938964844</t>
   </si>
   <si>
-    <t xml:space="preserve">762.204956054688</t>
+    <t xml:space="preserve">762.204895019531</t>
   </si>
   <si>
     <t xml:space="preserve">778.242980957031</t>
   </si>
   <si>
-    <t xml:space="preserve">791.41015625</t>
+    <t xml:space="preserve">791.410095214844</t>
   </si>
   <si>
     <t xml:space="preserve">793.588073730469</t>
   </si>
   <si>
-    <t xml:space="preserve">787.549133300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">807.250122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">815.764343261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">815.962280273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">825.565246582031</t>
+    <t xml:space="preserve">787.549072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">807.250183105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">815.764282226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">815.962219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">825.565307617188</t>
   </si>
   <si>
     <t xml:space="preserve">823.288208007812</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">828.337280273438</t>
   </si>
   <si>
-    <t xml:space="preserve">838.732360839844</t>
+    <t xml:space="preserve">838.732299804688</t>
   </si>
   <si>
     <t xml:space="preserve">835.267333984375</t>
@@ -4475,16 +4475,16 @@
     <t xml:space="preserve">833.980346679688</t>
   </si>
   <si>
-    <t xml:space="preserve">843.385375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">845.266357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">828.931335449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">818.932250976562</t>
+    <t xml:space="preserve">843.385437011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">845.266296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">828.931213378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">818.932189941406</t>
   </si>
   <si>
     <t xml:space="preserve">825.664306640625</t>
@@ -4496,67 +4496,67 @@
     <t xml:space="preserve">839.722351074219</t>
   </si>
   <si>
-    <t xml:space="preserve">847.543334960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">861.403503417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">845.563354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">859.720520019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.977478027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.482482910156</t>
+    <t xml:space="preserve">847.543273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">861.403442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">845.563415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">859.720458984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.977416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.482421875</t>
   </si>
   <si>
     <t xml:space="preserve">830.020324707031</t>
   </si>
   <si>
-    <t xml:space="preserve">773.392028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">783.192993164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">784.282043457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">807.646179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">782.400939941406</t>
+    <t xml:space="preserve">773.39208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">783.193054199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">784.282104492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">807.646118164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">782.401062011719</t>
   </si>
   <si>
     <t xml:space="preserve">760.224914550781</t>
   </si>
   <si>
-    <t xml:space="preserve">743.790832519531</t>
+    <t xml:space="preserve">743.790771484375</t>
   </si>
   <si>
     <t xml:space="preserve">737.751831054688</t>
   </si>
   <si>
-    <t xml:space="preserve">726.465698242188</t>
+    <t xml:space="preserve">726.4658203125</t>
   </si>
   <si>
     <t xml:space="preserve">735.078796386719</t>
   </si>
   <si>
-    <t xml:space="preserve">761.016967773438</t>
+    <t xml:space="preserve">761.016906738281</t>
   </si>
   <si>
     <t xml:space="preserve">720.030700683594</t>
   </si>
   <si>
-    <t xml:space="preserve">699.042663574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720.327758789062</t>
+    <t xml:space="preserve">699.042724609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720.327697753906</t>
   </si>
   <si>
     <t xml:space="preserve">702.804626464844</t>
@@ -4565,34 +4565,34 @@
     <t xml:space="preserve">755.967895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">812.794189453125</t>
+    <t xml:space="preserve">812.794250488281</t>
   </si>
   <si>
     <t xml:space="preserve">806.359252929688</t>
   </si>
   <si>
-    <t xml:space="preserve">817.744201660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">838.138305664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">836.353576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">824.752685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">846.169677734375</t>
+    <t xml:space="preserve">817.744323730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.138366699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">836.353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">824.752746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">846.169738769531</t>
   </si>
   <si>
     <t xml:space="preserve">841.806945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">855.886657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">840.220581054688</t>
+    <t xml:space="preserve">855.88671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">840.220520019531</t>
   </si>
   <si>
     <t xml:space="preserve">845.37646484375</t>
@@ -4607,13 +4607,13 @@
     <t xml:space="preserve">850.631652832031</t>
   </si>
   <si>
-    <t xml:space="preserve">846.764587402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">858.563842773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">867.586669921875</t>
+    <t xml:space="preserve">846.7646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">858.563781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">867.586730957031</t>
   </si>
   <si>
     <t xml:space="preserve">852.218017578125</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">812.160278320312</t>
   </si>
   <si>
-    <t xml:space="preserve">806.012878417969</t>
+    <t xml:space="preserve">806.012817382812</t>
   </si>
   <si>
     <t xml:space="preserve">807.995910644531</t>
@@ -4631,10 +4631,10 @@
     <t xml:space="preserve">812.656066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">812.953491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">831.197570800781</t>
+    <t xml:space="preserve">812.953552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">831.197631835938</t>
   </si>
   <si>
     <t xml:space="preserve">835.064636230469</t>
@@ -4649,7 +4649,7 @@
     <t xml:space="preserve">808.987426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">805.517150878906</t>
+    <t xml:space="preserve">805.51708984375</t>
   </si>
   <si>
     <t xml:space="preserve">825.5458984375</t>
@@ -4658,19 +4658,19 @@
     <t xml:space="preserve">816.919677734375</t>
   </si>
   <si>
-    <t xml:space="preserve">819.695861816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">821.579833984375</t>
+    <t xml:space="preserve">819.695922851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">821.579772949219</t>
   </si>
   <si>
     <t xml:space="preserve">813.845886230469</t>
   </si>
   <si>
-    <t xml:space="preserve">779.737365722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">779.935668945312</t>
+    <t xml:space="preserve">779.737426757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">779.935607910156</t>
   </si>
   <si>
     <t xml:space="preserve">793.519592285156</t>
@@ -4694,13 +4694,13 @@
     <t xml:space="preserve">829.313720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">836.948486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">829.809509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">832.982421875</t>
+    <t xml:space="preserve">836.948547363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">829.8095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">832.982360839844</t>
   </si>
   <si>
     <t xml:space="preserve">841.410339355469</t>
@@ -4709,25 +4709,25 @@
     <t xml:space="preserve">838.435791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">830.007751464844</t>
+    <t xml:space="preserve">830.0078125</t>
   </si>
   <si>
     <t xml:space="preserve">833.279846191406</t>
   </si>
   <si>
-    <t xml:space="preserve">823.661987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819.200134277344</t>
+    <t xml:space="preserve">823.662048339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.2001953125</t>
   </si>
   <si>
     <t xml:space="preserve">822.868835449219</t>
   </si>
   <si>
-    <t xml:space="preserve">819.894287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">827.13232421875</t>
+    <t xml:space="preserve">819.894226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">827.132385253906</t>
   </si>
   <si>
     <t xml:space="preserve">761.790649414062</t>
@@ -4736,49 +4736,49 @@
     <t xml:space="preserve">778.646667480469</t>
   </si>
   <si>
-    <t xml:space="preserve">754.651733398438</t>
+    <t xml:space="preserve">754.651672363281</t>
   </si>
   <si>
     <t xml:space="preserve">737.002502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">726.492309570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">716.9736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">725.401611328125</t>
+    <t xml:space="preserve">726.492248535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">716.973571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">725.401550292969</t>
   </si>
   <si>
     <t xml:space="preserve">766.549987792969</t>
   </si>
   <si>
-    <t xml:space="preserve">778.250061035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761.691528320312</t>
+    <t xml:space="preserve">778.250122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761.691589355469</t>
   </si>
   <si>
     <t xml:space="preserve">771.309387207031</t>
   </si>
   <si>
-    <t xml:space="preserve">750.090637207031</t>
+    <t xml:space="preserve">750.090698242188</t>
   </si>
   <si>
     <t xml:space="preserve">713.241638183594</t>
   </si>
   <si>
-    <t xml:space="preserve">680.464904785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">679.670288085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">703.706604003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.295715332031</t>
+    <t xml:space="preserve">680.464965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679.670349121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">703.706665039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.295776367188</t>
   </si>
   <si>
     <t xml:space="preserve">715.228088378906</t>
@@ -4817,16 +4817,16 @@
     <t xml:space="preserve">748.104248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">747.408996582031</t>
+    <t xml:space="preserve">747.408935546875</t>
   </si>
   <si>
     <t xml:space="preserve">740.952941894531</t>
   </si>
   <si>
-    <t xml:space="preserve">744.329956054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">744.925903320312</t>
+    <t xml:space="preserve">744.330017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">744.925842285156</t>
   </si>
   <si>
     <t xml:space="preserve">735.7880859375</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">725.756469726562</t>
   </si>
   <si>
-    <t xml:space="preserve">759.02978515625</t>
+    <t xml:space="preserve">759.029846191406</t>
   </si>
   <si>
     <t xml:space="preserve">745.521789550781</t>
@@ -4850,16 +4850,16 @@
     <t xml:space="preserve">759.327819824219</t>
   </si>
   <si>
-    <t xml:space="preserve">753.070373535156</t>
+    <t xml:space="preserve">753.070434570312</t>
   </si>
   <si>
     <t xml:space="preserve">739.860412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">740.158386230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.731811523438</t>
+    <t xml:space="preserve">740.158325195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.731872558594</t>
   </si>
   <si>
     <t xml:space="preserve">758.433837890625</t>
@@ -4883,10 +4883,10 @@
     <t xml:space="preserve">714.731506347656</t>
   </si>
   <si>
-    <t xml:space="preserve">693.674987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">697.548522949219</t>
+    <t xml:space="preserve">693.674926757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">697.548583984375</t>
   </si>
   <si>
     <t xml:space="preserve">724.663879394531</t>
@@ -4895,22 +4895,22 @@
     <t xml:space="preserve">722.876037597656</t>
   </si>
   <si>
-    <t xml:space="preserve">741.846862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">757.937194824219</t>
+    <t xml:space="preserve">741.846923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.937255859375</t>
   </si>
   <si>
     <t xml:space="preserve">766.181091308594</t>
   </si>
   <si>
-    <t xml:space="preserve">768.068237304688</t>
+    <t xml:space="preserve">768.068176269531</t>
   </si>
   <si>
     <t xml:space="preserve">771.445251464844</t>
   </si>
   <si>
-    <t xml:space="preserve">784.555908203125</t>
+    <t xml:space="preserve">784.555969238281</t>
   </si>
   <si>
     <t xml:space="preserve">785.052551269531</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">775.914855957031</t>
   </si>
   <si>
-    <t xml:space="preserve">796.1767578125</t>
+    <t xml:space="preserve">796.176696777344</t>
   </si>
   <si>
     <t xml:space="preserve">842.759399414062</t>
@@ -4928,16 +4928,16 @@
     <t xml:space="preserve">843.752685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">834.813598632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">833.025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">831.734619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">834.317016601562</t>
+    <t xml:space="preserve">834.813659667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">833.025756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">831.734558105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">834.316955566406</t>
   </si>
   <si>
     <t xml:space="preserve">816.108276367188</t>
@@ -5454,6 +5454,9 @@
   </si>
   <si>
     <t xml:space="preserve">728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">742.799987792969</t>
   </si>
 </sst>
 </file>
@@ -70818,7 +70821,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45960.6916319444</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>13843</v>
@@ -70839,6 +70842,32 @@
         <v>1813</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45961.6914930556</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>3506</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>743.5</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>723.099975585938</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>728.400024414062</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>742.799987792969</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1814</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="1815">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="1816">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,154 +44,154 @@
     <t xml:space="preserve">LLY.DE</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7578163146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.680046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1175155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5549583435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4298477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9923973083496</t>
+    <t xml:space="preserve">38.7578277587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.680061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1174964904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5549354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4298324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9923858642578</t>
   </si>
   <si>
     <t xml:space="preserve">61.2426147460938</t>
   </si>
   <si>
-    <t xml:space="preserve">60.8051528930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3677177429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9302673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0229988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5942878723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1717185974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8681449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7071418762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5908012390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3309478759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3598175048828</t>
+    <t xml:space="preserve">60.8051681518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3677062988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9302825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0229911804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5942993164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1717300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8681335449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.707145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5907974243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3309364318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.359806060791</t>
   </si>
   <si>
     <t xml:space="preserve">54.0159759521484</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2212677001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8040046691895</t>
+    <t xml:space="preserve">54.221263885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8039970397949</t>
   </si>
   <si>
     <t xml:space="preserve">56.3226585388184</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4815864562988</t>
+    <t xml:space="preserve">56.4815902709961</t>
   </si>
   <si>
     <t xml:space="preserve">56.2785148620605</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4021186828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.0290107727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5322799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5963821411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4662132263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2719573974609</t>
+    <t xml:space="preserve">56.4021224975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.028995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5322914123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5963745117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4662055969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2719650268555</t>
   </si>
   <si>
     <t xml:space="preserve">55.5721626281738</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1218681335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9276123046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9717597961426</t>
+    <t xml:space="preserve">55.1218605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9276161193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9717750549316</t>
   </si>
   <si>
     <t xml:space="preserve">56.6405181884766</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2167091369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5787124633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0754356384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8082656860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0312881469727</t>
+    <t xml:space="preserve">56.2167129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5787162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0754280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8082618713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0312919616699</t>
   </si>
   <si>
     <t xml:space="preserve">56.4286155700684</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2961578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8900108337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.486141204834</t>
+    <t xml:space="preserve">56.2961730957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.890022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4861373901367</t>
   </si>
   <si>
     <t xml:space="preserve">53.2323760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9033966064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.113037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3690948486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6251411437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9230651855469</t>
+    <t xml:space="preserve">53.9034042358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1130256652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.369083404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6251335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9230690002441</t>
   </si>
   <si>
     <t xml:space="preserve">55.8811912536621</t>
@@ -200,10 +200,10 @@
     <t xml:space="preserve">55.5191841125488</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7641334533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1019287109375</t>
+    <t xml:space="preserve">56.7641296386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1019325256348</t>
   </si>
   <si>
     <t xml:space="preserve">56.6934967041016</t>
@@ -212,265 +212,265 @@
     <t xml:space="preserve">57.5057907104492</t>
   </si>
   <si>
-    <t xml:space="preserve">57.1614608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9937019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5433959960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9495429992676</t>
+    <t xml:space="preserve">57.1614532470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9936943054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.543399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.949535369873</t>
   </si>
   <si>
     <t xml:space="preserve">57.4793090820312</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9119453430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5829811096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9162292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3665237426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1899261474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.362247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6559028625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.62939453125</t>
+    <t xml:space="preserve">57.9119415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5829620361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9162216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.366512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.18994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3622436523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.655891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6294097900391</t>
   </si>
   <si>
     <t xml:space="preserve">58.6271209716797</t>
   </si>
   <si>
-    <t xml:space="preserve">58.7330780029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5166358947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0552177429199</t>
+    <t xml:space="preserve">58.733081817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5166244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0552024841309</t>
   </si>
   <si>
     <t xml:space="preserve">61.5231704711914</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4452781677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7212409973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8872947692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5134544372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2433395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2077255249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3946647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.937629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4093780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.157096862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5696334838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6586456298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2105026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.255012512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7979888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1006240844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6912002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4967498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7281799316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8335952758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9582138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1615600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3039703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5220413208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3320541381836</t>
+    <t xml:space="preserve">61.4452857971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7212257385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2998123168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.887279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5134429931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.243335723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2077217102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.394660949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9376525878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4093933105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1571044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5696029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6586151123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2105102539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2549896240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7980117797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1006393432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6911926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4967269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.728157043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8336181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9582366943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1615524291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.303955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5220489501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3320617675781</t>
   </si>
   <si>
     <t xml:space="preserve">66.2608642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">65.8202362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2564086914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5190048217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.786018371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3988342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3556900024414</t>
+    <t xml:space="preserve">65.8202667236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2563934326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5189971923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7860336303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3988265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3557052612305</t>
   </si>
   <si>
     <t xml:space="preserve">68.121208190918</t>
   </si>
   <si>
-    <t xml:space="preserve">68.1657180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1568222045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6018829345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3971710205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5960464477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1448593139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6194229125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.5273361206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.622200012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5153503417969</t>
+    <t xml:space="preserve">68.1657257080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1568298339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6018753051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3971405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5960235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1448669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6194152832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.5273208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6221771240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5153579711914</t>
   </si>
   <si>
     <t xml:space="preserve">74.9306716918945</t>
   </si>
   <si>
-    <t xml:space="preserve">75.6961822509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2124328613281</t>
+    <t xml:space="preserve">75.696174621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2124481201172</t>
   </si>
   <si>
     <t xml:space="preserve">76.8355255126953</t>
   </si>
   <si>
-    <t xml:space="preserve">78.4733810424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.9362258911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.5623779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.7136688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8352508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8441390991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8048324584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4318466186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9513626098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5694580078125</t>
+    <t xml:space="preserve">78.4733657836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.9362182617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5623550415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.7136917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8352661132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8441467285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.804817199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4318771362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9513931274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5694351196289</t>
   </si>
   <si>
     <t xml:space="preserve">82.7844161987305</t>
   </si>
   <si>
-    <t xml:space="preserve">81.4587173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3691482543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9033584594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6883850097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.634635925293</t>
+    <t xml:space="preserve">81.4587326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3691329956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9033813476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6883926391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6346588134766</t>
   </si>
   <si>
     <t xml:space="preserve">80.5809097290039</t>
   </si>
   <si>
-    <t xml:space="preserve">80.9839935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8496398925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2168655395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0914688110352</t>
+    <t xml:space="preserve">80.9839782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8496170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2168807983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">81.2527008056641</t>
@@ -479,121 +479,121 @@
     <t xml:space="preserve">80.2853012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">80.3211441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4887924194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8617858886719</t>
+    <t xml:space="preserve">80.3211212158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4888153076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.86181640625</t>
   </si>
   <si>
     <t xml:space="preserve">81.7811965942383</t>
   </si>
   <si>
-    <t xml:space="preserve">81.3960113525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6110000610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9782409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3569488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.181037902832</t>
+    <t xml:space="preserve">81.3960189819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6109924316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9782638549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3569717407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1810455322266</t>
   </si>
   <si>
     <t xml:space="preserve">80.6077651977539</t>
   </si>
   <si>
-    <t xml:space="preserve">81.0735626220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2379989624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.115837097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2949829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2810363769531</t>
+    <t xml:space="preserve">81.0735778808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2380065917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1158447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2949981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2810440063477</t>
   </si>
   <si>
     <t xml:space="preserve">89.2247924804688</t>
   </si>
   <si>
-    <t xml:space="preserve">90.5056991577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.798095703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1531372070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2476959228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4537200927734</t>
+    <t xml:space="preserve">90.5057220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7980804443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1531600952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2477035522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4537353515625</t>
   </si>
   <si>
     <t xml:space="preserve">85.8478546142578</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3014602661133</t>
+    <t xml:space="preserve">85.3014755249023</t>
   </si>
   <si>
     <t xml:space="preserve">86.8958892822266</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3200836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9976501464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7378768920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3551788330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7435836791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1402206420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2681274414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2029190063477</t>
+    <t xml:space="preserve">88.3201065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9976196289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7378616333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3552017211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7436065673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1402435302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2680969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2029113769531</t>
   </si>
   <si>
     <t xml:space="preserve">87.0660629272461</t>
   </si>
   <si>
-    <t xml:space="preserve">84.817741394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6980819702148</t>
+    <t xml:space="preserve">84.8177490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6980895996094</t>
   </si>
   <si>
     <t xml:space="preserve">87.1287384033203</t>
   </si>
   <si>
-    <t xml:space="preserve">83.4472732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.972526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2061309814453</t>
+    <t xml:space="preserve">83.4472808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9725112915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2061462402344</t>
   </si>
   <si>
     <t xml:space="preserve">87.7289047241211</t>
@@ -602,82 +602,82 @@
     <t xml:space="preserve">90.2369689941406</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3591918945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9741363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7129364013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5325698852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5685195922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9740600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3705062866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1991882324219</t>
+    <t xml:space="preserve">89.3591690063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9741439819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7129211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.532600402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5685272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9740447998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3705139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1991729736328</t>
   </si>
   <si>
     <t xml:space="preserve">88.8839721679688</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4063720703125</t>
+    <t xml:space="preserve">90.406379699707</t>
   </si>
   <si>
     <t xml:space="preserve">91.2171173095703</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7665328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8474960327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0456848144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.154167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6046524047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3885269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3162002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7487640380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8930740356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8933486938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8931655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0644073486328</t>
+    <t xml:space="preserve">92.7665176391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8475112915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0456924438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1541442871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6046447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.388542175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3161849975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7487564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.89306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8933334350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.893180847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0644226074219</t>
   </si>
   <si>
     <t xml:space="preserve">85.2627792358398</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7760696411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5056304931641</t>
+    <t xml:space="preserve">86.7760467529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5056076049805</t>
   </si>
   <si>
     <t xml:space="preserve">90.3252792358398</t>
@@ -686,205 +686,205 @@
     <t xml:space="preserve">89.0191040039062</t>
   </si>
   <si>
-    <t xml:space="preserve">89.1812591552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.631591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6135711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4512939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8747863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.667610168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9919738769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7217636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3521423339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3700790405273</t>
+    <t xml:space="preserve">89.1812515258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6315765380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6135482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4513092041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8748168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6676025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9919815063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7217483520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3521347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3700714111328</t>
   </si>
   <si>
     <t xml:space="preserve">91.6675186157227</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5863571166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4241943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0998229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6674194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6585998535156</t>
+    <t xml:space="preserve">92.5863723754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.424201965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0998382568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6674270629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6586074829102</t>
   </si>
   <si>
     <t xml:space="preserve">90.0820541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7666091918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5051879882812</t>
+    <t xml:space="preserve">91.7666168212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5051803588867</t>
   </si>
   <si>
     <t xml:space="preserve">94.4150161743164</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7394256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.685173034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0997314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4962005615234</t>
+    <t xml:space="preserve">93.7394104003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6852035522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.099739074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4961853027344</t>
   </si>
   <si>
     <t xml:space="preserve">92.604377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">93.964599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3970031738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1717987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.3154754638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6569595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0890808105469</t>
+    <t xml:space="preserve">93.9646072387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3969955444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1718139648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.3154678344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6569442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0890884399414</t>
   </si>
   <si>
     <t xml:space="preserve">97.6750946044922</t>
   </si>
   <si>
-    <t xml:space="preserve">97.7385330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.2370758056641</t>
+    <t xml:space="preserve">97.7385482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2370376586914</t>
   </si>
   <si>
     <t xml:space="preserve">99.0437774658203</t>
   </si>
   <si>
-    <t xml:space="preserve">99.2522354125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3247680664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6963958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.52123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.518287658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.475914001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.189033508301</t>
+    <t xml:space="preserve">99.2522430419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3247528076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6963882446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.521224975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.518272399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.475898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.189025878906</t>
   </si>
   <si>
     <t xml:space="preserve">101.318885803223</t>
   </si>
   <si>
-    <t xml:space="preserve">102.234336853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.45777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9078063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4969711303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1615905761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.5966720581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.865676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.034934997559</t>
+    <t xml:space="preserve">102.234352111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.457778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9078369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4970016479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1616134643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5967025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.865669250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.034965515137</t>
   </si>
   <si>
     <t xml:space="preserve">102.5244140625</t>
   </si>
   <si>
-    <t xml:space="preserve">102.823539733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.101570129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.58805847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.445991516113</t>
+    <t xml:space="preserve">102.823532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.1015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.588066101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.446006774902</t>
   </si>
   <si>
     <t xml:space="preserve">104.862945556641</t>
   </si>
   <si>
-    <t xml:space="preserve">104.300956726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.270820617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.352409362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.494262695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.346061706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.207153320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.880836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.787269592285</t>
+    <t xml:space="preserve">104.300987243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270851135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.352401733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.494270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.346069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.207145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.880851745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.78727722168</t>
   </si>
   <si>
     <t xml:space="preserve">100.068016052246</t>
   </si>
   <si>
-    <t xml:space="preserve">99.0166015625</t>
+    <t xml:space="preserve">99.0165786743164</t>
   </si>
   <si>
     <t xml:space="preserve">93.8862915039062</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">92.472282409668</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7020492553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7716217041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9347686767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7868194580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0587387084961</t>
+    <t xml:space="preserve">94.7020645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.771614074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9347763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7867965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0587158203125</t>
   </si>
   <si>
     <t xml:space="preserve">94.5751571655273</t>
@@ -917,25 +917,25 @@
     <t xml:space="preserve">93.9044189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7775192260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0494384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0342483520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3816299438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4360275268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1430130004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3061828613281</t>
+    <t xml:space="preserve">93.7775039672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.049430847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0342407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3816452026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4360427856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1430435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3061752319336</t>
   </si>
   <si>
     <t xml:space="preserve">95.755241394043</t>
@@ -944,85 +944,85 @@
     <t xml:space="preserve">94.6241989135742</t>
   </si>
   <si>
-    <t xml:space="preserve">95.8829574584961</t>
+    <t xml:space="preserve">95.8829498291016</t>
   </si>
   <si>
     <t xml:space="preserve">95.4815979003906</t>
   </si>
   <si>
-    <t xml:space="preserve">95.3903961181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.0802764892578</t>
+    <t xml:space="preserve">95.3903732299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0802459716797</t>
   </si>
   <si>
     <t xml:space="preserve">95.1350021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4086227416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2228698730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9376831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9890670776367</t>
+    <t xml:space="preserve">95.4086151123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2228546142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9376449584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9890518188477</t>
   </si>
   <si>
     <t xml:space="preserve">95.5728225708008</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6324234008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5628051757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0918350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5834808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2128295898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.799934387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4201736450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4931716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9094161987305</t>
+    <t xml:space="preserve">91.6324081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5627822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0918197631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5834732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2128524780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7999496459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4201889038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9093856811523</t>
   </si>
   <si>
     <t xml:space="preserve">92.6357650756836</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3107452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2609024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8720092773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3098373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3405456542969</t>
+    <t xml:space="preserve">93.3107528686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2608871459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8719940185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3098526000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3405303955078</t>
   </si>
   <si>
     <t xml:space="preserve">92.2709121704102</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3621444702148</t>
+    <t xml:space="preserve">92.3621063232422</t>
   </si>
   <si>
     <t xml:space="preserve">90.7567749023438</t>
@@ -1037,85 +1037,85 @@
     <t xml:space="preserve">86.6521911621094</t>
   </si>
   <si>
-    <t xml:space="preserve">87.564323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4764709472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0204010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5004730224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3818969726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.5244979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9349594116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9474258422852</t>
+    <t xml:space="preserve">87.5643310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.476448059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.020378112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5004806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3818893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.5245056152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9349670410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9474334716797</t>
   </si>
   <si>
     <t xml:space="preserve">89.3064956665039</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3703384399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9507446289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2244033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1182861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.775032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3040618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.917610168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5469818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4980392456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7452163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7418746948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4317398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0702362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4236755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.440803527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7804641723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7908935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0478897094727</t>
+    <t xml:space="preserve">89.3703460693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9507598876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2243957519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.118278503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.775016784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3040390014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9176254272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5469665527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4980316162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.745231628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7418823242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.431755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0702590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4236679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.440788269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7804565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.790885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0479049682617</t>
   </si>
   <si>
     <t xml:space="preserve">92.0748291015625</t>
@@ -1130,49 +1130,49 @@
     <t xml:space="preserve">92.754150390625</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8190155029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6084976196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8104629516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2878265380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0197448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7712631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6990661621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9193801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0381240844727</t>
+    <t xml:space="preserve">93.8190231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6084899902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2878112792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0197525024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7712783813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6990737915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9193878173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0381088256836</t>
   </si>
   <si>
     <t xml:space="preserve">91.6801071166992</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7443237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9928207397461</t>
+    <t xml:space="preserve">91.7443618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9928283691406</t>
   </si>
   <si>
     <t xml:space="preserve">94.9389724731445</t>
   </si>
   <si>
-    <t xml:space="preserve">96.7015075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4065399169922</t>
+    <t xml:space="preserve">96.7015151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4065322875977</t>
   </si>
   <si>
     <t xml:space="preserve">94.66357421875</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">93.433464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9940338134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4714202880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6354217529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9634552001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.5044479370117</t>
+    <t xml:space="preserve">94.9940643310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4714126586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6354141235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9634399414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.5044326782227</t>
   </si>
   <si>
     <t xml:space="preserve">90.4224319458008</t>
@@ -1202,106 +1202,106 @@
     <t xml:space="preserve">90.8814315795898</t>
   </si>
   <si>
-    <t xml:space="preserve">91.340446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7969970703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5589294433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8165512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2033538818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6886444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1397094726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.717414855957</t>
+    <t xml:space="preserve">91.3404312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.796989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5589218139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8165588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2033462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6886596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1397171020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7174224853516</t>
   </si>
   <si>
     <t xml:space="preserve">94.0944213867188</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0931854248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8006744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4885330200195</t>
+    <t xml:space="preserve">92.0931930541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.800666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.488525390625</t>
   </si>
   <si>
     <t xml:space="preserve">94.0209732055664</t>
   </si>
   <si>
-    <t xml:space="preserve">94.1494979858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4616012573242</t>
+    <t xml:space="preserve">94.1494903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4616165161133</t>
   </si>
   <si>
     <t xml:space="preserve">93.4500732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6509780883789</t>
+    <t xml:space="preserve">94.6509704589844</t>
   </si>
   <si>
     <t xml:space="preserve">94.7433700561523</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4823989868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.0920944213867</t>
+    <t xml:space="preserve">95.4824142456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.0920791625977</t>
   </si>
   <si>
     <t xml:space="preserve">95.6856307983398</t>
   </si>
   <si>
-    <t xml:space="preserve">97.0158843994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5493621826172</t>
+    <t xml:space="preserve">97.0158920288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5493469238281</t>
   </si>
   <si>
     <t xml:space="preserve">98.8634567260742</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3830871582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1267395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4939346313477</t>
+    <t xml:space="preserve">98.3830947875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1267471313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4939498901367</t>
   </si>
   <si>
     <t xml:space="preserve">100.600158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">99.9165649414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.359977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.212196350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.784927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.71102142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.727195739746</t>
+    <t xml:space="preserve">99.9165725708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.359985351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.212188720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.78491973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.711013793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.727188110352</t>
   </si>
   <si>
     <t xml:space="preserve">104.202934265137</t>
@@ -1310,28 +1310,28 @@
     <t xml:space="preserve">107.269905090332</t>
   </si>
   <si>
-    <t xml:space="preserve">108.008911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.429237365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.653259277344</t>
+    <t xml:space="preserve">108.008918762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.429244995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.653244018555</t>
   </si>
   <si>
     <t xml:space="preserve">108.988121032715</t>
   </si>
   <si>
-    <t xml:space="preserve">108.064346313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.34147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.265251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.135917663574</t>
+    <t xml:space="preserve">108.064338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.341499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.265274047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.135925292969</t>
   </si>
   <si>
     <t xml:space="preserve">109.819526672363</t>
@@ -1340,34 +1340,34 @@
     <t xml:space="preserve">109.893447875977</t>
   </si>
   <si>
-    <t xml:space="preserve">112.886505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.105888366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.269859313965</t>
+    <t xml:space="preserve">112.886512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.105895996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.269866943359</t>
   </si>
   <si>
     <t xml:space="preserve">115.454635620117</t>
   </si>
   <si>
-    <t xml:space="preserve">116.507751464844</t>
+    <t xml:space="preserve">116.507759094238</t>
   </si>
   <si>
     <t xml:space="preserve">117.062019348145</t>
   </si>
   <si>
-    <t xml:space="preserve">117.376098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.710975646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.486953735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.394554138184</t>
+    <t xml:space="preserve">117.376091003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.710983276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.486938476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.394584655762</t>
   </si>
   <si>
     <t xml:space="preserve">117.320671081543</t>
@@ -1376,151 +1376,151 @@
     <t xml:space="preserve">117.413055419922</t>
   </si>
   <si>
-    <t xml:space="preserve">116.32299041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.115112304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.092025756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.135925292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.339157104492</t>
+    <t xml:space="preserve">116.322982788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.115127563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.092002868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.135894775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.339141845703</t>
   </si>
   <si>
     <t xml:space="preserve">119.611656188965</t>
   </si>
   <si>
-    <t xml:space="preserve">122.623176574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.156608581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473091125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.274482727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.292930603027</t>
+    <t xml:space="preserve">122.623184204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.156669616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473075866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.274467468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.292938232422</t>
   </si>
   <si>
     <t xml:space="preserve">122.586250305176</t>
   </si>
   <si>
-    <t xml:space="preserve">122.549072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.248527526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.616821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.229942321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.270378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.787330627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.780769348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.049598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.009170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.017913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.620056152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.057235717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.441955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.10424041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.306434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.507522583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.88126373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.93701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.135932922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.700950622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.5654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.609161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.123931884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.597152709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.056175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.120635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.768676757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.27033996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.771980285645</t>
+    <t xml:space="preserve">122.54907989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.24853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.616844177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.229927062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.270416259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.78734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.780776977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.049629211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.009162902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.01789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.620063781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.057220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.441940307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.104232788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.306419372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.507530212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.881286621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.936988830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.135940551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.700942993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.565444946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.609153747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.123954772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.597137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.056182861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.120643615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.768692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270347595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.771995544434</t>
   </si>
   <si>
     <t xml:space="preserve">110.844131469727</t>
   </si>
   <si>
-    <t xml:space="preserve">111.680191040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.36547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.798233032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.694427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.300987243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623397827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.552337646484</t>
+    <t xml:space="preserve">111.680183410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.365455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.798225402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.694465637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.301002502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623382568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.552368164062</t>
   </si>
   <si>
     <t xml:space="preserve">126.339241027832</t>
@@ -1529,142 +1529,142 @@
     <t xml:space="preserve">128.661682128906</t>
   </si>
   <si>
-    <t xml:space="preserve">131.913024902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.448547363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.628890991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.377532958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.235427856445</t>
+    <t xml:space="preserve">131.913009643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.448577880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.628952026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.377563476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.235458374023</t>
   </si>
   <si>
     <t xml:space="preserve">138.285751342773</t>
   </si>
   <si>
-    <t xml:space="preserve">139.679214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.218002319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.557907104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.232177734375</t>
+    <t xml:space="preserve">139.679183959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.217987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.557861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.232192993164</t>
   </si>
   <si>
     <t xml:space="preserve">132.117401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">129.36767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.272598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.405960083008</t>
+    <t xml:space="preserve">129.367660522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.272644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.40592956543</t>
   </si>
   <si>
     <t xml:space="preserve">133.492309570312</t>
   </si>
   <si>
-    <t xml:space="preserve">132.154602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.182968139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.263885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.833312988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.889297485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.347763061523</t>
+    <t xml:space="preserve">132.154571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.182998657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.263870239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.833282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.889282226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.347732543945</t>
   </si>
   <si>
     <t xml:space="preserve">136.561553955078</t>
   </si>
   <si>
-    <t xml:space="preserve">133.050933837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.91178894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.942626953125</t>
+    <t xml:space="preserve">133.050918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.911758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.942642211914</t>
   </si>
   <si>
     <t xml:space="preserve">129.689605712891</t>
   </si>
   <si>
-    <t xml:space="preserve">130.399215698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.346992492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.771903991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.76619720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.560760498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.589744567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.95482635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.180816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.002479553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.873657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.14347076416</t>
+    <t xml:space="preserve">130.399200439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.34700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.771919250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.766189575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.56079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.589752197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.95484161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.18083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.002456665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.873672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.143516540527</t>
   </si>
   <si>
     <t xml:space="preserve">124.554290771484</t>
   </si>
   <si>
-    <t xml:space="preserve">121.846618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.016563415527</t>
+    <t xml:space="preserve">121.846572875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.016548156738</t>
   </si>
   <si>
     <t xml:space="preserve">116.97274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">135.14241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.077926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.011611938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.650360107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.322616577148</t>
+    <t xml:space="preserve">135.142364501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.07795715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.011642456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.650344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.322601318359</t>
   </si>
   <si>
     <t xml:space="preserve">133.984588623047</t>
@@ -1673,76 +1673,76 @@
     <t xml:space="preserve">130.455215454102</t>
   </si>
   <si>
-    <t xml:space="preserve">132.621353149414</t>
+    <t xml:space="preserve">132.62141418457</t>
   </si>
   <si>
     <t xml:space="preserve">134.488754272461</t>
   </si>
   <si>
-    <t xml:space="preserve">134.619476318359</t>
+    <t xml:space="preserve">134.61946105957</t>
   </si>
   <si>
     <t xml:space="preserve">136.412170410156</t>
   </si>
   <si>
-    <t xml:space="preserve">136.374816894531</t>
+    <t xml:space="preserve">136.374801635742</t>
   </si>
   <si>
     <t xml:space="preserve">135.441131591797</t>
   </si>
   <si>
-    <t xml:space="preserve">138.484985351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.055465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.148864746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.22541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.12370300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.430847167969</t>
+    <t xml:space="preserve">138.484970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.055480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.148834228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.225402832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.123687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.43083190918</t>
   </si>
   <si>
     <t xml:space="preserve">134.20866394043</t>
   </si>
   <si>
-    <t xml:space="preserve">135.179718017578</t>
+    <t xml:space="preserve">135.179672241211</t>
   </si>
   <si>
     <t xml:space="preserve">133.125564575195</t>
   </si>
   <si>
-    <t xml:space="preserve">135.833282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.795913696289</t>
+    <t xml:space="preserve">135.833251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.795959472656</t>
   </si>
   <si>
     <t xml:space="preserve">131.239532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">127.355354309082</t>
+    <t xml:space="preserve">127.355369567871</t>
   </si>
   <si>
     <t xml:space="preserve">127.448738098145</t>
   </si>
   <si>
-    <t xml:space="preserve">128.793243408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.334045410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.802780151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.473136901855</t>
+    <t xml:space="preserve">128.793273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.334030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.802764892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.47314453125</t>
   </si>
   <si>
     <t xml:space="preserve">122.854988098145</t>
@@ -1754,100 +1754,100 @@
     <t xml:space="preserve">119.717796325684</t>
   </si>
   <si>
-    <t xml:space="preserve">120.80086517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.875595092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.736457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.221977233887</t>
+    <t xml:space="preserve">120.800872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.875556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.736473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.221984863281</t>
   </si>
   <si>
     <t xml:space="preserve">119.245338439941</t>
   </si>
   <si>
-    <t xml:space="preserve">119.733642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.409812927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.578834533691</t>
+    <t xml:space="preserve">119.733657836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.409805297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.578819274902</t>
   </si>
   <si>
     <t xml:space="preserve">121.480361938477</t>
   </si>
   <si>
-    <t xml:space="preserve">120.071731567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.174766540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.062080383301</t>
+    <t xml:space="preserve">120.071723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.174781799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.062065124512</t>
   </si>
   <si>
     <t xml:space="preserve">119.207763671875</t>
   </si>
   <si>
-    <t xml:space="preserve">117.423522949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.170211791992</t>
+    <t xml:space="preserve">117.42350769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.170196533203</t>
   </si>
   <si>
     <t xml:space="preserve">117.479843139648</t>
   </si>
   <si>
-    <t xml:space="preserve">116.446830749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.052429199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.832130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.301689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.099632263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.625534057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.799140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.686965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.592529296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.554969787598</t>
+    <t xml:space="preserve">116.446853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.052436828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.832138061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.30167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.099647521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.625518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.799133300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.686973571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.59252166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.554977416992</t>
   </si>
   <si>
     <t xml:space="preserve">119.63973236084</t>
   </si>
   <si>
-    <t xml:space="preserve">120.710296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.729095458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.611824035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.597625732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.334678649902</t>
+    <t xml:space="preserve">120.710289001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.729064941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.611839294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.597595214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.334663391113</t>
   </si>
   <si>
     <t xml:space="preserve">119.583396911621</t>
@@ -1859,118 +1859,118 @@
     <t xml:space="preserve">118.193542480469</t>
   </si>
   <si>
-    <t xml:space="preserve">116.709762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.97728729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.747375488281</t>
+    <t xml:space="preserve">116.709800720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.977317810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.747352600098</t>
   </si>
   <si>
     <t xml:space="preserve">116.108764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">121.424018859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.335182189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.546333312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.231620788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.869682312012</t>
+    <t xml:space="preserve">121.424011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.335174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.546340942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.23161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.869697570801</t>
   </si>
   <si>
     <t xml:space="preserve">117.06664276123</t>
   </si>
   <si>
-    <t xml:space="preserve">117.348365783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.150894165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.12247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.615364074707</t>
+    <t xml:space="preserve">117.34838104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.150901794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.122459411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.615379333496</t>
   </si>
   <si>
     <t xml:space="preserve">111.939224243164</t>
   </si>
   <si>
-    <t xml:space="preserve">113.347862243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.563583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.22957611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.835151672363</t>
+    <t xml:space="preserve">113.347854614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.563591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.229583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.835144042969</t>
   </si>
   <si>
     <t xml:space="preserve">106.530082702637</t>
   </si>
   <si>
-    <t xml:space="preserve">105.666114807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.68489074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.511299133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.137199401855</t>
+    <t xml:space="preserve">105.666122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.684906005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.511291503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.137214660645</t>
   </si>
   <si>
     <t xml:space="preserve">116.221466064453</t>
   </si>
   <si>
-    <t xml:space="preserve">116.202682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.573249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.104209899902</t>
+    <t xml:space="preserve">116.202674865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.5732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.104217529297</t>
   </si>
   <si>
     <t xml:space="preserve">115.319946289062</t>
   </si>
   <si>
-    <t xml:space="preserve">112.939109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.978363037109</t>
+    <t xml:space="preserve">112.939094543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.97834777832</t>
   </si>
   <si>
     <t xml:space="preserve">113.354804992676</t>
   </si>
   <si>
-    <t xml:space="preserve">112.221054077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.504501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.164360046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.359184265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.901298522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.338829040527</t>
+    <t xml:space="preserve">112.221061706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.504486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.164375305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.359214782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.901306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.338844299316</t>
   </si>
   <si>
     <t xml:space="preserve">113.449272155762</t>
@@ -1979,85 +1979,85 @@
     <t xml:space="preserve">114.318473815918</t>
   </si>
   <si>
-    <t xml:space="preserve">115.830116271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.828659057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.846084594727</t>
+    <t xml:space="preserve">115.830123901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.828666687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.846099853516</t>
   </si>
   <si>
     <t xml:space="preserve">112.447814941406</t>
   </si>
   <si>
-    <t xml:space="preserve">114.469650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.151336669922</t>
+    <t xml:space="preserve">114.469627380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.151351928711</t>
   </si>
   <si>
     <t xml:space="preserve">122.65145111084</t>
   </si>
   <si>
-    <t xml:space="preserve">123.84188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.843322753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.41170501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.327453613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.948059082031</t>
+    <t xml:space="preserve">123.841842651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.353507995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.843338012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.411689758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.327438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.94807434082</t>
   </si>
   <si>
     <t xml:space="preserve">131.267837524414</t>
   </si>
   <si>
-    <t xml:space="preserve">129.737289428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.964050292969</t>
+    <t xml:space="preserve">129.7373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.964065551758</t>
   </si>
   <si>
     <t xml:space="preserve">129.416061401367</t>
   </si>
   <si>
-    <t xml:space="preserve">127.583168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.471298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.11376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.827377319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.392768859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.904434204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.016311645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.603546142578</t>
+    <t xml:space="preserve">127.583183288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.471282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.113754272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.827392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.392753601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.904396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.016326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.603561401367</t>
   </si>
   <si>
     <t xml:space="preserve">145.118316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">139.978713989258</t>
+    <t xml:space="preserve">139.978698730469</t>
   </si>
   <si>
     <t xml:space="preserve">144.645935058594</t>
@@ -2066,10 +2066,10 @@
     <t xml:space="preserve">146.119781494141</t>
   </si>
   <si>
-    <t xml:space="preserve">148.047164916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.839324951172</t>
+    <t xml:space="preserve">148.047119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.839294433594</t>
   </si>
   <si>
     <t xml:space="preserve">152.714385986328</t>
@@ -2078,100 +2078,100 @@
     <t xml:space="preserve">156.833602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">155.076309204102</t>
+    <t xml:space="preserve">155.076293945312</t>
   </si>
   <si>
     <t xml:space="preserve">158.760955810547</t>
   </si>
   <si>
-    <t xml:space="preserve">164.032821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.996505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.992080688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.125854492188</t>
+    <t xml:space="preserve">164.032836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.996536254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.992111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.125823974609</t>
   </si>
   <si>
     <t xml:space="preserve">161.349655151367</t>
   </si>
   <si>
-    <t xml:space="preserve">162.804626464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.72021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.962936401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.137420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.70426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.461563110352</t>
+    <t xml:space="preserve">162.804641723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.720275878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.962921142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.13737487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.704284667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.461578369141</t>
   </si>
   <si>
     <t xml:space="preserve">156.814712524414</t>
   </si>
   <si>
-    <t xml:space="preserve">159.157730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.0087890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.819549560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.560791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.793975830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.161361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.831954956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.856826782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.932189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.20524597168</t>
+    <t xml:space="preserve">159.157775878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.008773803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.819519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.560836791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.794006347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.161376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.831985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.856857299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.932159423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.205276489258</t>
   </si>
   <si>
     <t xml:space="preserve">159.964889526367</t>
   </si>
   <si>
-    <t xml:space="preserve">157.970825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.907913208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.376800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.756607055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.958358764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.338150024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.617141723633</t>
+    <t xml:space="preserve">157.970794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.907928466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.376815795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.756637573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.958343505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.338195800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.617156982422</t>
   </si>
   <si>
     <t xml:space="preserve">167.884338378906</t>
@@ -2183,37 +2183,37 @@
     <t xml:space="preserve">165.890213012695</t>
   </si>
   <si>
-    <t xml:space="preserve">162.661697387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.326385498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.741592407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.931533813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.082824707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.183639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.753402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.133285522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.462600708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.474411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.993759155273</t>
+    <t xml:space="preserve">162.661712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.326370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.741622924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.931518554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.082794189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.183670043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.753387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.133224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.462661743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.474426269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.993743896484</t>
   </si>
   <si>
     <t xml:space="preserve">148.89289855957</t>
@@ -2225,49 +2225,49 @@
     <t xml:space="preserve">150.792037963867</t>
   </si>
   <si>
-    <t xml:space="preserve">151.399765014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.456741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.702972412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.284484863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.234100341797</t>
+    <t xml:space="preserve">151.399780273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.45671081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.703002929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.284530639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.234115600586</t>
   </si>
   <si>
     <t xml:space="preserve">145.854278564453</t>
   </si>
   <si>
-    <t xml:space="preserve">144.904663085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.424011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.323135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.84245300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.412231445312</t>
+    <t xml:space="preserve">144.904708862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.424041748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.323165893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.842483520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.412185668945</t>
   </si>
   <si>
     <t xml:space="preserve">149.652572631836</t>
   </si>
   <si>
-    <t xml:space="preserve">148.513076782227</t>
+    <t xml:space="preserve">148.513107299805</t>
   </si>
   <si>
     <t xml:space="preserve">146.803863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">143.955123901367</t>
+    <t xml:space="preserve">143.955108642578</t>
   </si>
   <si>
     <t xml:space="preserve">140.346740722656</t>
@@ -2276,46 +2276,46 @@
     <t xml:space="preserve">141.486251831055</t>
   </si>
   <si>
-    <t xml:space="preserve">143.575271606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.044189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.12141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.691223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.071014404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.83659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.69352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.220932006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.457229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.929824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.979949951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.175567626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.702941894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.984588623047</t>
+    <t xml:space="preserve">143.575286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.044174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.121459960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.691177368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.070999145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.836578369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.693572998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.220962524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.457214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.92985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.979934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.175552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.702926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.984603881836</t>
   </si>
   <si>
     <t xml:space="preserve">154.361770629883</t>
@@ -2324,49 +2324,49 @@
     <t xml:space="preserve">156.748306274414</t>
   </si>
   <si>
-    <t xml:space="preserve">157.225646972656</t>
+    <t xml:space="preserve">157.225631713867</t>
   </si>
   <si>
     <t xml:space="preserve">154.839080810547</t>
   </si>
   <si>
-    <t xml:space="preserve">156.366485595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.803085327148</t>
+    <t xml:space="preserve">156.366516113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.803070068359</t>
   </si>
   <si>
     <t xml:space="preserve">171.640380859375</t>
   </si>
   <si>
-    <t xml:space="preserve">170.876647949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.076995849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.00032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.36572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.749908447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.840667724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.222534179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.227188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.270278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.038681030273</t>
+    <t xml:space="preserve">170.876678466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.076950073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.000305175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.365707397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.749938964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.84065246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.222518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.22721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.270233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.038665771484</t>
   </si>
   <si>
     <t xml:space="preserve">178.800033569336</t>
@@ -2375,7 +2375,7 @@
     <t xml:space="preserve">174.265548706055</t>
   </si>
   <si>
-    <t xml:space="preserve">185.243682861328</t>
+    <t xml:space="preserve">185.243698120117</t>
   </si>
   <si>
     <t xml:space="preserve">184.527709960938</t>
@@ -2384,61 +2384,61 @@
     <t xml:space="preserve">182.093414306641</t>
   </si>
   <si>
-    <t xml:space="preserve">184.432235717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.291442871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.102798461914</t>
+    <t xml:space="preserve">184.432220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.291366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.102828979492</t>
   </si>
   <si>
     <t xml:space="preserve">187.773391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">189.491729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.918930053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.968994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.775787353516</t>
+    <t xml:space="preserve">189.491744995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.9189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.969055175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.775772094727</t>
   </si>
   <si>
     <t xml:space="preserve">192.069198608398</t>
   </si>
   <si>
-    <t xml:space="preserve">189.682647705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.446365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.828155517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.584838867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.677947998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.296112060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.591873168945</t>
+    <t xml:space="preserve">189.682632446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.446334838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.828170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.584823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.677963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.296142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.591857910156</t>
   </si>
   <si>
     <t xml:space="preserve">191.973739624023</t>
   </si>
   <si>
-    <t xml:space="preserve">193.882965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.983093261719</t>
+    <t xml:space="preserve">193.88298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.983139038086</t>
   </si>
   <si>
     <t xml:space="preserve">197.415069580078</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">196.269500732422</t>
   </si>
   <si>
-    <t xml:space="preserve">199.515213012695</t>
+    <t xml:space="preserve">199.515197753906</t>
   </si>
   <si>
     <t xml:space="preserve">197.319580078125</t>
@@ -2459,31 +2459,31 @@
     <t xml:space="preserve">197.987838745117</t>
   </si>
   <si>
-    <t xml:space="preserve">207.152145385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.739028930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.975357055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.929946899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.321197509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.703063964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.366561889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.498077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.564300537109</t>
+    <t xml:space="preserve">207.152160644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.739013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.975311279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.929916381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.321166992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.703079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.366577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.498107910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.564331054688</t>
   </si>
   <si>
     <t xml:space="preserve">221.917999267578</t>
@@ -2492,22 +2492,22 @@
     <t xml:space="preserve">223.930221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">221.534729003906</t>
+    <t xml:space="preserve">221.534713745117</t>
   </si>
   <si>
     <t xml:space="preserve">223.067825317383</t>
   </si>
   <si>
-    <t xml:space="preserve">222.205474853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.444107055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.156616210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.29426574707</t>
+    <t xml:space="preserve">222.205459594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.444046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.156600952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.294235229492</t>
   </si>
   <si>
     <t xml:space="preserve">212.048599243164</t>
@@ -2519,46 +2519,46 @@
     <t xml:space="preserve">211.18620300293</t>
   </si>
   <si>
-    <t xml:space="preserve">207.736724853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.982376098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.269836425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.994583129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.461471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.970199584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.058929443359</t>
+    <t xml:space="preserve">207.736709594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.982360839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.269821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.994598388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.461456298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.970169067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.058959960938</t>
   </si>
   <si>
     <t xml:space="preserve">196.621658325195</t>
   </si>
   <si>
-    <t xml:space="preserve">191.447387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.920364379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.495315551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.902099609375</t>
+    <t xml:space="preserve">191.447402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.920349121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.495300292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.902069091797</t>
   </si>
   <si>
     <t xml:space="preserve">187.087600708008</t>
   </si>
   <si>
-    <t xml:space="preserve">189.531005859375</t>
+    <t xml:space="preserve">189.530990600586</t>
   </si>
   <si>
     <t xml:space="preserve">189.626815795898</t>
@@ -2576,88 +2576,88 @@
     <t xml:space="preserve">185.889862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">182.152877807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.572814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.651260375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.770568847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.410766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.39338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.237426757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.501403808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.172180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.525817871094</t>
+    <t xml:space="preserve">182.152893066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.572830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.651245117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.770523071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.410751342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.393402099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.237411499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.501373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.172164916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.525848388672</t>
   </si>
   <si>
     <t xml:space="preserve">193.555435180664</t>
   </si>
   <si>
-    <t xml:space="preserve">193.938690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">194.992706298828</t>
+    <t xml:space="preserve">193.938705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194.992752075195</t>
   </si>
   <si>
     <t xml:space="preserve">195.471817016602</t>
   </si>
   <si>
-    <t xml:space="preserve">198.442260742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.729690551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.358612060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.538040161133</t>
+    <t xml:space="preserve">198.442245483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.72966003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.358596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.538055419922</t>
   </si>
   <si>
     <t xml:space="preserve">198.921356201172</t>
   </si>
   <si>
-    <t xml:space="preserve">201.987533569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.84992980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.215774536133</t>
+    <t xml:space="preserve">201.987548828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.849914550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.2158203125</t>
   </si>
   <si>
     <t xml:space="preserve">207.83251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">210.802963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.353454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.006790161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.989410400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.593933105469</t>
+    <t xml:space="preserve">210.802947998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.353424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.006774902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.989395141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.59391784668</t>
   </si>
   <si>
     <t xml:space="preserve">215.977188110352</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">219.905776977539</t>
   </si>
   <si>
-    <t xml:space="preserve">220.768142700195</t>
+    <t xml:space="preserve">220.768157958984</t>
   </si>
   <si>
     <t xml:space="preserve">218.892776489258</t>
@@ -2678,37 +2678,37 @@
     <t xml:space="preserve">219.277450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">221.297119140625</t>
+    <t xml:space="preserve">221.297103881836</t>
   </si>
   <si>
     <t xml:space="preserve">221.200958251953</t>
   </si>
   <si>
-    <t xml:space="preserve">223.316772460938</t>
+    <t xml:space="preserve">223.316787719727</t>
   </si>
   <si>
     <t xml:space="preserve">224.663238525391</t>
   </si>
   <si>
-    <t xml:space="preserve">223.509155273438</t>
+    <t xml:space="preserve">223.509140014648</t>
   </si>
   <si>
     <t xml:space="preserve">224.182373046875</t>
   </si>
   <si>
-    <t xml:space="preserve">227.067626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.162704467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.064376831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.238174438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.198822021484</t>
+    <t xml:space="preserve">227.067596435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.162689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.064407348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.238128662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.198852539062</t>
   </si>
   <si>
     <t xml:space="preserve">209.756195068359</t>
@@ -2717,49 +2717,49 @@
     <t xml:space="preserve">207.351837158203</t>
   </si>
   <si>
-    <t xml:space="preserve">203.985748291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.313583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.640350341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.507019042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.929931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.279586791992</t>
+    <t xml:space="preserve">203.985733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.313613891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.640365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.50700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.929946899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.279571533203</t>
   </si>
   <si>
     <t xml:space="preserve">237.646759033203</t>
   </si>
   <si>
-    <t xml:space="preserve">227.25993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">225.624954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.567047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">232.068649291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.81950378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.43473815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.530914306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">228.317855834961</t>
+    <t xml:space="preserve">227.259963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">225.624984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.56706237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.068664550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.819442749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.434753417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.530883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">228.31787109375</t>
   </si>
   <si>
     <t xml:space="preserve">227.644622802734</t>
@@ -2768,28 +2768,28 @@
     <t xml:space="preserve">220.527740478516</t>
   </si>
   <si>
-    <t xml:space="preserve">219.662155151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.12336730957</t>
+    <t xml:space="preserve">219.662170410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.123382568359</t>
   </si>
   <si>
     <t xml:space="preserve">219.373626708984</t>
   </si>
   <si>
-    <t xml:space="preserve">212.256729125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.197738647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.544174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.409759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.102661132812</t>
+    <t xml:space="preserve">212.256759643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.197769165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.544189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.409744262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.102645874023</t>
   </si>
   <si>
     <t xml:space="preserve">209.948577880859</t>
@@ -2798,25 +2798,25 @@
     <t xml:space="preserve">207.15950012207</t>
   </si>
   <si>
-    <t xml:space="preserve">200.042617797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.869903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.813064575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.121215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.928924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.986801147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.794494628906</t>
+    <t xml:space="preserve">200.042602539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.869918823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.813003540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.121231079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.928894042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.98681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.794479370117</t>
   </si>
   <si>
     <t xml:space="preserve">212.352920532227</t>
@@ -2825,22 +2825,22 @@
     <t xml:space="preserve">206.101593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">202.639297485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.158432006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.139877319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.927841186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.234924316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.959426879883</t>
+    <t xml:space="preserve">202.639282226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.158416748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.139831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.927825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.234939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.959457397461</t>
   </si>
   <si>
     <t xml:space="preserve">207.076309204102</t>
@@ -2852,43 +2852,43 @@
     <t xml:space="preserve">206.593154907227</t>
   </si>
   <si>
-    <t xml:space="preserve">204.85383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.892044067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203.404388427734</t>
+    <t xml:space="preserve">204.853851318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.892028808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203.404418945312</t>
   </si>
   <si>
     <t xml:space="preserve">205.916763305664</t>
   </si>
   <si>
-    <t xml:space="preserve">205.626846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">216.256103515625</t>
+    <t xml:space="preserve">205.626831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">216.256072998047</t>
   </si>
   <si>
     <t xml:space="preserve">214.13020324707</t>
   </si>
   <si>
-    <t xml:space="preserve">214.806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.957183837891</t>
+    <t xml:space="preserve">214.806579589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.957168579102</t>
   </si>
   <si>
     <t xml:space="preserve">223.116714477539</t>
   </si>
   <si>
-    <t xml:space="preserve">229.39762878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.910018920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">233.262786865234</t>
+    <t xml:space="preserve">229.397644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.90998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">233.262802124023</t>
   </si>
   <si>
     <t xml:space="preserve">232.393127441406</t>
@@ -2897,19 +2897,19 @@
     <t xml:space="preserve">231.233581542969</t>
   </si>
   <si>
-    <t xml:space="preserve">237.417846679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">236.161651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.312240600586</t>
+    <t xml:space="preserve">237.417861938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">236.161682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.312225341797</t>
   </si>
   <si>
     <t xml:space="preserve">243.408843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">246.307708740234</t>
+    <t xml:space="preserve">246.307739257812</t>
   </si>
   <si>
     <t xml:space="preserve">251.332473754883</t>
@@ -2918,13 +2918,13 @@
     <t xml:space="preserve">253.65153503418</t>
   </si>
   <si>
-    <t xml:space="preserve">249.883026123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.525695800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.105529785156</t>
+    <t xml:space="preserve">249.883010864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.525741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.105484008789</t>
   </si>
   <si>
     <t xml:space="preserve">255.29426574707</t>
@@ -2936,88 +2936,88 @@
     <t xml:space="preserve">251.622344970703</t>
   </si>
   <si>
-    <t xml:space="preserve">252.008865356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250.656066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.844833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">257.468444824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260.802062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266.020111083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.489776611328</t>
+    <t xml:space="preserve">252.008834838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250.656051635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.844802856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">257.468383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260.802093505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266.020080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.48974609375</t>
   </si>
   <si>
     <t xml:space="preserve">276.890838623047</t>
   </si>
   <si>
-    <t xml:space="preserve">275.006622314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.668395996094</t>
+    <t xml:space="preserve">275.006652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.66845703125</t>
   </si>
   <si>
     <t xml:space="preserve">269.305511474609</t>
   </si>
   <si>
-    <t xml:space="preserve">269.692047119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.295318603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.556060791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.796447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.347091674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.869476318359</t>
+    <t xml:space="preserve">269.691986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.295349121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.555969238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.796478271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.347030639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.869506835938</t>
   </si>
   <si>
     <t xml:space="preserve">269.595367431641</t>
   </si>
   <si>
-    <t xml:space="preserve">268.822326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.730102539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.536956787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">264.957153320312</t>
+    <t xml:space="preserve">268.822296142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.730194091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.536895751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">264.957183837891</t>
   </si>
   <si>
     <t xml:space="preserve">268.339233398438</t>
   </si>
   <si>
-    <t xml:space="preserve">265.10205078125</t>
+    <t xml:space="preserve">265.102111816406</t>
   </si>
   <si>
     <t xml:space="preserve">263.942565917969</t>
   </si>
   <si>
-    <t xml:space="preserve">258.579650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266.454895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">267.405212402344</t>
+    <t xml:space="preserve">258.579681396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266.454925537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">267.405242919922</t>
   </si>
   <si>
     <t xml:space="preserve">281.854370117188</t>
@@ -3026,82 +3026,82 @@
     <t xml:space="preserve">277.005615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">274.290344238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.623260498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">271.090209960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.599517822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.108551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">280.642211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">281.466461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">282.630187988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.532836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">280.205810546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">278.411773681641</t>
+    <t xml:space="preserve">274.290405273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.623291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271.090270996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.599578857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.108489990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">280.642181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281.466491699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">282.630126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.532867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">280.205780029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">278.411804199219</t>
   </si>
   <si>
     <t xml:space="preserve">284.084777832031</t>
   </si>
   <si>
-    <t xml:space="preserve">279.769439697266</t>
+    <t xml:space="preserve">279.769409179688</t>
   </si>
   <si>
     <t xml:space="preserve">275.066192626953</t>
   </si>
   <si>
-    <t xml:space="preserve">270.750885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.471984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">271.817474365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.611267089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.253997802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270.847808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.484344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.720916748047</t>
+    <t xml:space="preserve">270.750823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.471954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">271.817535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.253936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270.847778320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.484405517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.720947265625</t>
   </si>
   <si>
     <t xml:space="preserve">284.763549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">298.291381835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.455047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.576171875</t>
+    <t xml:space="preserve">298.291412353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.455017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.576110839844</t>
   </si>
   <si>
     <t xml:space="preserve">299.552062988281</t>
@@ -3110,25 +3110,25 @@
     <t xml:space="preserve">298.679321289062</t>
   </si>
   <si>
-    <t xml:space="preserve">299.842987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.946166992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.721954345703</t>
+    <t xml:space="preserve">299.842956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.946136474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.721923828125</t>
   </si>
   <si>
     <t xml:space="preserve">314.049682617188</t>
   </si>
   <si>
-    <t xml:space="preserve">312.740539550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.019409179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.365020751953</t>
+    <t xml:space="preserve">312.740447998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.019348144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.364990234375</t>
   </si>
   <si>
     <t xml:space="preserve">309.443389892578</t>
@@ -3137,16 +3137,16 @@
     <t xml:space="preserve">311.625305175781</t>
   </si>
   <si>
-    <t xml:space="preserve">318.122528076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.21337890625</t>
+    <t xml:space="preserve">318.12255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.213287353516</t>
   </si>
   <si>
     <t xml:space="preserve">309.879760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">306.825073242188</t>
+    <t xml:space="preserve">306.825103759766</t>
   </si>
   <si>
     <t xml:space="preserve">311.916168212891</t>
@@ -3155,16 +3155,16 @@
     <t xml:space="preserve">312.837432861328</t>
   </si>
   <si>
-    <t xml:space="preserve">316.231506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.4677734375</t>
+    <t xml:space="preserve">316.231567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.467834472656</t>
   </si>
   <si>
     <t xml:space="preserve">314.631591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">313.661773681641</t>
+    <t xml:space="preserve">313.661804199219</t>
   </si>
   <si>
     <t xml:space="preserve">308.425140380859</t>
@@ -3173,13 +3173,13 @@
     <t xml:space="preserve">308.473663330078</t>
   </si>
   <si>
-    <t xml:space="preserve">300.667297363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.854675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">288.836486816406</t>
+    <t xml:space="preserve">300.667358398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.854705810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">288.836517333984</t>
   </si>
   <si>
     <t xml:space="preserve">289.369873046875</t>
@@ -3188,46 +3188,46 @@
     <t xml:space="preserve">287.284912109375</t>
   </si>
   <si>
-    <t xml:space="preserve">285.539367675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">283.842315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.806762695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.298828125</t>
+    <t xml:space="preserve">285.539398193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">283.84228515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.806823730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.298797607422</t>
   </si>
   <si>
     <t xml:space="preserve">298.369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">305.812591552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.574615478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.428894042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.126281738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.996429443359</t>
+    <t xml:space="preserve">305.812530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.574676513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.428955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.126251220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.996490478516</t>
   </si>
   <si>
     <t xml:space="preserve">311.358612060547</t>
   </si>
   <si>
-    <t xml:space="preserve">309.41259765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.22900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.234130859375</t>
+    <t xml:space="preserve">309.412658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.228973388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.234069824219</t>
   </si>
   <si>
     <t xml:space="preserve">299.925903320312</t>
@@ -3236,109 +3236,109 @@
     <t xml:space="preserve">294.185272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">297.250244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.217834472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.888000488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.596282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.963806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.688262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.585571289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.969207763672</t>
+    <t xml:space="preserve">297.250183105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.2177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.887969970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.596343994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.963836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.688232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.585540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.298980712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.969177246094</t>
   </si>
   <si>
     <t xml:space="preserve">300.412414550781</t>
   </si>
   <si>
-    <t xml:space="preserve">299.342132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.796020507812</t>
+    <t xml:space="preserve">299.342071533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.796112060547</t>
   </si>
   <si>
     <t xml:space="preserve">293.990661621094</t>
   </si>
   <si>
-    <t xml:space="preserve">297.104248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.601928710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.845184326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.0830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.883666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327.656311035156</t>
+    <t xml:space="preserve">297.104278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.601837158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.84521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.082946777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.883697509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327.656341552734</t>
   </si>
   <si>
     <t xml:space="preserve">324.445404052734</t>
   </si>
   <si>
-    <t xml:space="preserve">316.612823486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320.066955566406</t>
+    <t xml:space="preserve">316.612854003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320.066986083984</t>
   </si>
   <si>
     <t xml:space="preserve">324.348114013672</t>
   </si>
   <si>
-    <t xml:space="preserve">330.721282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.650939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323.375152587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.758911132812</t>
+    <t xml:space="preserve">330.721252441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.650909423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.375122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.758941650391</t>
   </si>
   <si>
     <t xml:space="preserve">327.315795898438</t>
   </si>
   <si>
-    <t xml:space="preserve">324.883270263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.380676269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.521331787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.580718994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">326.245422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.710266113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.515869140625</t>
+    <t xml:space="preserve">324.883239746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.380645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.521270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.580627441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326.245513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.710327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.515899658203</t>
   </si>
   <si>
     <t xml:space="preserve">343.759338378906</t>
@@ -3347,22 +3347,22 @@
     <t xml:space="preserve">342.543151855469</t>
   </si>
   <si>
-    <t xml:space="preserve">347.456756591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">347.748687744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.710906982422</t>
+    <t xml:space="preserve">347.456787109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">347.748565673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.7109375</t>
   </si>
   <si>
     <t xml:space="preserve">354.802856445312</t>
   </si>
   <si>
-    <t xml:space="preserve">341.424133300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">353.829925537109</t>
+    <t xml:space="preserve">341.424163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">353.829864501953</t>
   </si>
   <si>
     <t xml:space="preserve">358.257049560547</t>
@@ -3374,40 +3374,40 @@
     <t xml:space="preserve">352.224456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">353.635284423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.429992675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">349.013580322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.672546386719</t>
+    <t xml:space="preserve">353.635314941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.429901123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">349.013549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.672607421875</t>
   </si>
   <si>
     <t xml:space="preserve">334.946655273438</t>
   </si>
   <si>
-    <t xml:space="preserve">331.531341552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.921630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.898651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.972076416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.728942871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.606750488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.581695556641</t>
+    <t xml:space="preserve">331.531280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.921600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.898681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.972015380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.728881835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.606719970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.581756591797</t>
   </si>
   <si>
     <t xml:space="preserve">339.093811035156</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">345.095031738281</t>
   </si>
   <si>
-    <t xml:space="preserve">341.435760498047</t>
+    <t xml:space="preserve">341.435729980469</t>
   </si>
   <si>
     <t xml:space="preserve">344.509552001953</t>
@@ -3431,52 +3431,52 @@
     <t xml:space="preserve">346.509979248047</t>
   </si>
   <si>
-    <t xml:space="preserve">345.826904296875</t>
+    <t xml:space="preserve">345.826873779297</t>
   </si>
   <si>
     <t xml:space="preserve">342.070007324219</t>
   </si>
   <si>
-    <t xml:space="preserve">345.582946777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.680206298828</t>
+    <t xml:space="preserve">345.582977294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.68017578125</t>
   </si>
   <si>
     <t xml:space="preserve">340.4111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">338.801147460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.239318847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.751098632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.945404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.994201660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.116363525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.118408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.654724121094</t>
+    <t xml:space="preserve">338.801086425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.239349365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.751037597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.945434570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.994171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.116394042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.118438720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.654693603516</t>
   </si>
   <si>
     <t xml:space="preserve">336.800659179688</t>
   </si>
   <si>
-    <t xml:space="preserve">335.141815185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.605926513672</t>
+    <t xml:space="preserve">335.141876220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.605895996094</t>
   </si>
   <si>
     <t xml:space="preserve">335.044219970703</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">336.703033447266</t>
   </si>
   <si>
-    <t xml:space="preserve">335.629699707031</t>
+    <t xml:space="preserve">335.629669189453</t>
   </si>
   <si>
     <t xml:space="preserve">337.28857421875</t>
@@ -3494,124 +3494,124 @@
     <t xml:space="preserve">330.897033691406</t>
   </si>
   <si>
-    <t xml:space="preserve">335.434478759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.774047851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.625610351562</t>
+    <t xml:space="preserve">335.434539794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.774017333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.625640869141</t>
   </si>
   <si>
     <t xml:space="preserve">321.529235839844</t>
   </si>
   <si>
-    <t xml:space="preserve">321.919586181641</t>
+    <t xml:space="preserve">321.919555664062</t>
   </si>
   <si>
     <t xml:space="preserve">326.017974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">323.968811035156</t>
+    <t xml:space="preserve">323.968780517578</t>
   </si>
   <si>
     <t xml:space="preserve">325.188537597656</t>
   </si>
   <si>
-    <t xml:space="preserve">320.065490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">317.528411865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.088043212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.672668457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.428833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">310.161102294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.039703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.184844970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.477203369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.131896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.331268310547</t>
+    <t xml:space="preserve">320.065551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">317.528472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.088073730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.672790527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.428771972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">310.1611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.039672851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.184783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.477233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.131958007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.331237792969</t>
   </si>
   <si>
     <t xml:space="preserve">306.160217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">306.501800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.575592041016</t>
+    <t xml:space="preserve">306.501739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.575653076172</t>
   </si>
   <si>
     <t xml:space="preserve">312.161499023438</t>
   </si>
   <si>
-    <t xml:space="preserve">316.796508789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.503814697266</t>
+    <t xml:space="preserve">316.796600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.503845214844</t>
   </si>
   <si>
     <t xml:space="preserve">318.393707275391</t>
   </si>
   <si>
-    <t xml:space="preserve">313.595581054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.558532714844</t>
+    <t xml:space="preserve">313.595550537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.558563232422</t>
   </si>
   <si>
     <t xml:space="preserve">301.942779541016</t>
   </si>
   <si>
-    <t xml:space="preserve">300.571929931641</t>
+    <t xml:space="preserve">300.571899414062</t>
   </si>
   <si>
     <t xml:space="preserve">302.775146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">304.146057128906</t>
+    <t xml:space="preserve">304.146087646484</t>
   </si>
   <si>
     <t xml:space="preserve">304.341918945312</t>
   </si>
   <si>
-    <t xml:space="preserve">299.886444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294.011138916016</t>
+    <t xml:space="preserve">299.886413574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.011108398438</t>
   </si>
   <si>
     <t xml:space="preserve">287.939910888672</t>
   </si>
   <si>
-    <t xml:space="preserve">290.192169189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.604614257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.080902099609</t>
+    <t xml:space="preserve">290.192199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.604583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.080841064453</t>
   </si>
   <si>
     <t xml:space="preserve">291.465148925781</t>
@@ -3620,49 +3620,49 @@
     <t xml:space="preserve">289.702545166016</t>
   </si>
   <si>
-    <t xml:space="preserve">288.380615234375</t>
+    <t xml:space="preserve">288.380645751953</t>
   </si>
   <si>
     <t xml:space="preserve">293.129821777344</t>
   </si>
   <si>
-    <t xml:space="preserve">292.052673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.528869628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.969573974609</t>
+    <t xml:space="preserve">292.052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.528930664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.969543457031</t>
   </si>
   <si>
     <t xml:space="preserve">304.195007324219</t>
   </si>
   <si>
-    <t xml:space="preserve">304.390869140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.089721679688</t>
+    <t xml:space="preserve">304.390899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.089660644531</t>
   </si>
   <si>
     <t xml:space="preserve">303.411682128906</t>
   </si>
   <si>
-    <t xml:space="preserve">299.592651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.110504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.984405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.3701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.488800048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.509582519531</t>
+    <t xml:space="preserve">299.592681884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.110443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.370147705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.488830566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.509552001953</t>
   </si>
   <si>
     <t xml:space="preserve">305.419036865234</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">307.965026855469</t>
   </si>
   <si>
-    <t xml:space="preserve">314.721649169922</t>
+    <t xml:space="preserve">314.721618652344</t>
   </si>
   <si>
     <t xml:space="preserve">318.442687988281</t>
@@ -3683,109 +3683,109 @@
     <t xml:space="preserve">325.884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">329.018249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.605834960938</t>
+    <t xml:space="preserve">329.018280029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.605865478516</t>
   </si>
   <si>
     <t xml:space="preserve">330.976715087891</t>
   </si>
   <si>
-    <t xml:space="preserve">333.326843261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.110198974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.543548583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.760040283203</t>
+    <t xml:space="preserve">333.326873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.110260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.543487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.760070800781</t>
   </si>
   <si>
     <t xml:space="preserve">341.944000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">340.768981933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">344.685821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.32373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">358.786529541016</t>
+    <t xml:space="preserve">340.768890380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.685791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.323760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">358.786560058594</t>
   </si>
   <si>
     <t xml:space="preserve">375.433380126953</t>
   </si>
   <si>
-    <t xml:space="preserve">380.133636474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">382.679534912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385.225555419922</t>
+    <t xml:space="preserve">380.133666992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">382.679565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385.2255859375</t>
   </si>
   <si>
     <t xml:space="preserve">385.421417236328</t>
   </si>
   <si>
-    <t xml:space="preserve">386.204803466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389.338256835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">395.358062744141</t>
+    <t xml:space="preserve">386.204742431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">389.338287353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">395.358032226562</t>
   </si>
   <si>
     <t xml:space="preserve">389.465972900391</t>
   </si>
   <si>
-    <t xml:space="preserve">393.393981933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.197570800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">398.304016113281</t>
+    <t xml:space="preserve">393.39404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.197631835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">398.304046630859</t>
   </si>
   <si>
     <t xml:space="preserve">401.0537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">402.428527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.483917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.091156005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">387.109130859375</t>
+    <t xml:space="preserve">402.428497314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.483978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.091186523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">387.109161376953</t>
   </si>
   <si>
     <t xml:space="preserve">391.233612060547</t>
   </si>
   <si>
-    <t xml:space="preserve">396.143646240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.680328369141</t>
+    <t xml:space="preserve">396.143676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.680358886719</t>
   </si>
   <si>
     <t xml:space="preserve">396.536437988281</t>
   </si>
   <si>
-    <t xml:space="preserve">406.160217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">408.124206542969</t>
+    <t xml:space="preserve">406.160186767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">408.124176025391</t>
   </si>
   <si>
     <t xml:space="preserve">404.785369873047</t>
@@ -3794,76 +3794,76 @@
     <t xml:space="preserve">405.963745117188</t>
   </si>
   <si>
-    <t xml:space="preserve">407.731384277344</t>
+    <t xml:space="preserve">407.731414794922</t>
   </si>
   <si>
     <t xml:space="preserve">403.999694824219</t>
   </si>
   <si>
-    <t xml:space="preserve">405.178131103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.821319580078</t>
+    <t xml:space="preserve">405.178161621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.821380615234</t>
   </si>
   <si>
     <t xml:space="preserve">407.534973144531</t>
   </si>
   <si>
-    <t xml:space="preserve">406.749389648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">413.034240722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">409.498992919922</t>
+    <t xml:space="preserve">406.749328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413.034271240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">409.4990234375</t>
   </si>
   <si>
     <t xml:space="preserve">417.551513671875</t>
   </si>
   <si>
-    <t xml:space="preserve">419.122741699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.479583740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.980255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.711944580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">420.497497558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.570922851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">403.60693359375</t>
+    <t xml:space="preserve">419.122711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.479522705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.980316162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.7119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420.49755859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.570983886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">403.606994628906</t>
   </si>
   <si>
     <t xml:space="preserve">397.518432617188</t>
   </si>
   <si>
-    <t xml:space="preserve">390.447967529297</t>
+    <t xml:space="preserve">390.448028564453</t>
   </si>
   <si>
     <t xml:space="preserve">383.377471923828</t>
   </si>
   <si>
-    <t xml:space="preserve">391.822784423828</t>
+    <t xml:space="preserve">391.822723388672</t>
   </si>
   <si>
     <t xml:space="preserve">395.947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">394.572387695312</t>
+    <t xml:space="preserve">394.572418212891</t>
   </si>
   <si>
     <t xml:space="preserve">407.338562011719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.284606933594</t>
+    <t xml:space="preserve">410.284637451172</t>
   </si>
   <si>
     <t xml:space="preserve">409.302581787109</t>
@@ -3872,64 +3872,64 @@
     <t xml:space="preserve">408.320587158203</t>
   </si>
   <si>
-    <t xml:space="preserve">407.142211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.356567382812</t>
+    <t xml:space="preserve">407.142150878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.356536865234</t>
   </si>
   <si>
     <t xml:space="preserve">402.232116699219</t>
   </si>
   <si>
-    <t xml:space="preserve">405.767425537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">413.819854736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404.588989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">400.464477539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">403.410552978516</t>
+    <t xml:space="preserve">405.767395019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413.819885253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404.588958740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">400.464508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">403.410522460938</t>
   </si>
   <si>
     <t xml:space="preserve">477.650665283203</t>
   </si>
   <si>
-    <t xml:space="preserve">474.508209228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">470.187316894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">474.115417480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">486.251983642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">488.614379882812</t>
+    <t xml:space="preserve">474.508239746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470.187347412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">474.115386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">486.252014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">488.614349365234</t>
   </si>
   <si>
     <t xml:space="preserve">495.110870361328</t>
   </si>
   <si>
-    <t xml:space="preserve">493.634429931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">492.157897949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">496.095123291016</t>
+    <t xml:space="preserve">493.634338378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">492.157928466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">496.095184326172</t>
   </si>
   <si>
     <t xml:space="preserve">500.524597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">499.048065185547</t>
+    <t xml:space="preserve">499.048126220703</t>
   </si>
   <si>
     <t xml:space="preserve">503.477508544922</t>
@@ -3938,16 +3938,16 @@
     <t xml:space="preserve">503.969696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">501.016754150391</t>
+    <t xml:space="preserve">501.016723632812</t>
   </si>
   <si>
     <t xml:space="preserve">495.60302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">500.032379150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">507.414794921875</t>
+    <t xml:space="preserve">500.032409667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">507.414764404297</t>
   </si>
   <si>
     <t xml:space="preserve">511.844177246094</t>
@@ -3956,16 +3956,16 @@
     <t xml:space="preserve">514.797180175781</t>
   </si>
   <si>
-    <t xml:space="preserve">509.383544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">527.59326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">535.9599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">547.279541015625</t>
+    <t xml:space="preserve">509.383453369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">527.593322753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">535.960021972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">547.279663085938</t>
   </si>
   <si>
     <t xml:space="preserve">546.295227050781</t>
@@ -3974,43 +3974,43 @@
     <t xml:space="preserve">546.787475585938</t>
   </si>
   <si>
-    <t xml:space="preserve">550.232543945312</t>
+    <t xml:space="preserve">550.232482910156</t>
   </si>
   <si>
     <t xml:space="preserve">539.897216796875</t>
   </si>
   <si>
-    <t xml:space="preserve">528.085388183594</t>
+    <t xml:space="preserve">528.08544921875</t>
   </si>
   <si>
     <t xml:space="preserve">526.116821289062</t>
   </si>
   <si>
-    <t xml:space="preserve">512.336364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">510.859832763672</t>
+    <t xml:space="preserve">512.336303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">510.859954833984</t>
   </si>
   <si>
     <t xml:space="preserve">489.992431640625</t>
   </si>
   <si>
-    <t xml:space="preserve">504.461822509766</t>
+    <t xml:space="preserve">504.461883544922</t>
   </si>
   <si>
     <t xml:space="preserve">517.750122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">532.514953613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">554.662048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.4423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567.950256347656</t>
+    <t xml:space="preserve">532.514831542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">554.661865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.442443847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567.9501953125</t>
   </si>
   <si>
     <t xml:space="preserve">575.824768066406</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">561.552185058594</t>
   </si>
   <si>
-    <t xml:space="preserve">569.426696777344</t>
+    <t xml:space="preserve">569.4267578125</t>
   </si>
   <si>
     <t xml:space="preserve">545.803100585938</t>
@@ -4031,25 +4031,25 @@
     <t xml:space="preserve">540.389404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">549.248291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">555.646301269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.022766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">523.655944824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">514.304931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">517.257873535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">534.975646972656</t>
+    <t xml:space="preserve">549.248168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">555.646240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.022705078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">523.656066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">514.304992675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">517.257934570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534.9755859375</t>
   </si>
   <si>
     <t xml:space="preserve">544.818786621094</t>
@@ -4058,55 +4058,55 @@
     <t xml:space="preserve">553.185485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">554.300109863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">536.053527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.108215332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">536.546691894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">542.464416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.532897949219</t>
+    <t xml:space="preserve">554.300048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">536.053466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.108276367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">536.546569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">542.46435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.532958984375</t>
   </si>
   <si>
     <t xml:space="preserve">541.478088378906</t>
   </si>
   <si>
-    <t xml:space="preserve">543.45068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">533.094421386719</t>
+    <t xml:space="preserve">543.450744628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">533.094604492188</t>
   </si>
   <si>
     <t xml:space="preserve">531.121948242188</t>
   </si>
   <si>
-    <t xml:space="preserve">538.026123046875</t>
+    <t xml:space="preserve">538.026062011719</t>
   </si>
   <si>
     <t xml:space="preserve">540.491760253906</t>
   </si>
   <si>
-    <t xml:space="preserve">532.601379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.039855957031</t>
+    <t xml:space="preserve">532.601440429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.039794921875</t>
   </si>
   <si>
     <t xml:space="preserve">534.080932617188</t>
   </si>
   <si>
-    <t xml:space="preserve">539.012390136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">526.190551757812</t>
+    <t xml:space="preserve">539.012451171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">526.190490722656</t>
   </si>
   <si>
     <t xml:space="preserve">531.615112304688</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">523.231628417969</t>
   </si>
   <si>
-    <t xml:space="preserve">519.779541015625</t>
+    <t xml:space="preserve">519.779479980469</t>
   </si>
   <si>
     <t xml:space="preserve">511.88916015625</t>
@@ -4130,10 +4130,10 @@
     <t xml:space="preserve">509.916564941406</t>
   </si>
   <si>
-    <t xml:space="preserve">511.396057128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">518.793273925781</t>
+    <t xml:space="preserve">511.395965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">518.793212890625</t>
   </si>
   <si>
     <t xml:space="preserve">520.765808105469</t>
@@ -4142,43 +4142,43 @@
     <t xml:space="preserve">527.669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">552.820617675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567.121826171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">557.258911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567.615112304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">565.642395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.108154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">573.532897949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">581.423278808594</t>
+    <t xml:space="preserve">552.820556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567.121887207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">557.258850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567.615051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">565.642456054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.108215332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">573.532775878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">581.423217773438</t>
   </si>
   <si>
     <t xml:space="preserve">583.888916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">575.012390136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">561.697326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569.094421386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.601318359375</t>
+    <t xml:space="preserve">575.012329101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">561.697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569.094482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.601379394531</t>
   </si>
   <si>
     <t xml:space="preserve">577.477966308594</t>
@@ -4193,22 +4193,22 @@
     <t xml:space="preserve">587.341064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">587.834228515625</t>
+    <t xml:space="preserve">587.834106445312</t>
   </si>
   <si>
     <t xml:space="preserve">585.861572265625</t>
   </si>
   <si>
-    <t xml:space="preserve">593.751892089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">609.03955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">646.025817871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">642.08056640625</t>
+    <t xml:space="preserve">593.751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">609.039611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">646.02587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">642.080688476562</t>
   </si>
   <si>
     <t xml:space="preserve">668.217529296875</t>
@@ -4217,22 +4217,22 @@
     <t xml:space="preserve">675.614807128906</t>
   </si>
   <si>
-    <t xml:space="preserve">677.09423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">671.176513671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">679.559997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">695.172973632812</t>
+    <t xml:space="preserve">677.094177246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">671.176452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679.559936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">695.173034667969</t>
   </si>
   <si>
     <t xml:space="preserve">698.631530761719</t>
   </si>
   <si>
-    <t xml:space="preserve">722.841491699219</t>
+    <t xml:space="preserve">722.841552734375</t>
   </si>
   <si>
     <t xml:space="preserve">726.300170898438</t>
@@ -4241,25 +4241,25 @@
     <t xml:space="preserve">700.113708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">681.338684082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">707.030944824219</t>
+    <t xml:space="preserve">681.338623046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">707.030883789062</t>
   </si>
   <si>
     <t xml:space="preserve">697.643310546875</t>
   </si>
   <si>
-    <t xml:space="preserve">705.054504394531</t>
+    <t xml:space="preserve">705.054565429688</t>
   </si>
   <si>
     <t xml:space="preserve">699.125610351562</t>
   </si>
   <si>
-    <t xml:space="preserve">688.255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">686.279479980469</t>
+    <t xml:space="preserve">688.255798339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">686.279418945312</t>
   </si>
   <si>
     <t xml:space="preserve">709.995361328125</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">710.489501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">711.971618652344</t>
+    <t xml:space="preserve">711.971740722656</t>
   </si>
   <si>
     <t xml:space="preserve">690.232116699219</t>
@@ -4280,28 +4280,28 @@
     <t xml:space="preserve">660.587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">678.868225097656</t>
+    <t xml:space="preserve">678.868286132812</t>
   </si>
   <si>
     <t xml:space="preserve">683.315002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">682.326904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">697.149353027344</t>
+    <t xml:space="preserve">682.326782226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">697.149291992188</t>
   </si>
   <si>
     <t xml:space="preserve">704.560485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">704.066467285156</t>
+    <t xml:space="preserve">704.06640625</t>
   </si>
   <si>
     <t xml:space="preserve">706.042724609375</t>
   </si>
   <si>
-    <t xml:space="preserve">720.865173339844</t>
+    <t xml:space="preserve">720.865234375</t>
   </si>
   <si>
     <t xml:space="preserve">698.829223632812</t>
@@ -4316,19 +4316,19 @@
     <t xml:space="preserve">709.204895019531</t>
   </si>
   <si>
-    <t xml:space="preserve">708.710876464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">689.738037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">701.991333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">702.090148925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">706.141540527344</t>
+    <t xml:space="preserve">708.710815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">689.738098144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">701.991271972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">702.090087890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706.141479492188</t>
   </si>
   <si>
     <t xml:space="preserve">695.469421386719</t>
@@ -4337,7 +4337,7 @@
     <t xml:space="preserve">694.283630371094</t>
   </si>
   <si>
-    <t xml:space="preserve">677.188415527344</t>
+    <t xml:space="preserve">677.188354492188</t>
   </si>
   <si>
     <t xml:space="preserve">676.6943359375</t>
@@ -4346,10 +4346,10 @@
     <t xml:space="preserve">685.390075683594</t>
   </si>
   <si>
-    <t xml:space="preserve">678.077697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">667.603210449219</t>
+    <t xml:space="preserve">678.077758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">667.603088378906</t>
   </si>
   <si>
     <t xml:space="preserve">680.745788574219</t>
@@ -4361,19 +4361,19 @@
     <t xml:space="preserve">711.576416015625</t>
   </si>
   <si>
-    <t xml:space="preserve">674.520324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">688.848693847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">709.106018066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">712.367004394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.13330078125</t>
+    <t xml:space="preserve">674.520263671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">688.848754882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">709.106079101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">712.367065429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.133422851562</t>
   </si>
   <si>
     <t xml:space="preserve">690.528564453125</t>
@@ -4391,7 +4391,7 @@
     <t xml:space="preserve">712.407653808594</t>
   </si>
   <si>
-    <t xml:space="preserve">732.603759765625</t>
+    <t xml:space="preserve">732.603820800781</t>
   </si>
   <si>
     <t xml:space="preserve">729.336730957031</t>
@@ -4403,58 +4403,58 @@
     <t xml:space="preserve">737.2568359375</t>
   </si>
   <si>
-    <t xml:space="preserve">739.434875488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">733.59375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">744.087890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">744.681884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">746.661926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.640930175781</t>
+    <t xml:space="preserve">739.434814453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">733.593811035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">744.087768554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">744.681823730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">746.661865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.640869140625</t>
   </si>
   <si>
     <t xml:space="preserve">754.185852050781</t>
   </si>
   <si>
-    <t xml:space="preserve">757.749938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">762.204895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">778.242980957031</t>
+    <t xml:space="preserve">757.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">762.204956054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">778.243041992188</t>
   </si>
   <si>
     <t xml:space="preserve">791.410095214844</t>
   </si>
   <si>
-    <t xml:space="preserve">793.588073730469</t>
+    <t xml:space="preserve">793.588134765625</t>
   </si>
   <si>
     <t xml:space="preserve">787.549072265625</t>
   </si>
   <si>
-    <t xml:space="preserve">807.250183105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">815.764282226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">815.962219238281</t>
+    <t xml:space="preserve">807.250244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">815.764221191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">815.962280273438</t>
   </si>
   <si>
     <t xml:space="preserve">825.565307617188</t>
   </si>
   <si>
-    <t xml:space="preserve">823.288208007812</t>
+    <t xml:space="preserve">823.288269042969</t>
   </si>
   <si>
     <t xml:space="preserve">833.386291503906</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">828.337280273438</t>
   </si>
   <si>
-    <t xml:space="preserve">838.732299804688</t>
+    <t xml:space="preserve">838.732360839844</t>
   </si>
   <si>
     <t xml:space="preserve">835.267333984375</t>
@@ -4478,25 +4478,25 @@
     <t xml:space="preserve">843.385437011719</t>
   </si>
   <si>
-    <t xml:space="preserve">845.266296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">828.931213378906</t>
+    <t xml:space="preserve">845.266357421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">828.931274414062</t>
   </si>
   <si>
     <t xml:space="preserve">818.932189941406</t>
   </si>
   <si>
-    <t xml:space="preserve">825.664306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">834.970397949219</t>
+    <t xml:space="preserve">825.664245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">834.970336914062</t>
   </si>
   <si>
     <t xml:space="preserve">839.722351074219</t>
   </si>
   <si>
-    <t xml:space="preserve">847.543273925781</t>
+    <t xml:space="preserve">847.543395996094</t>
   </si>
   <si>
     <t xml:space="preserve">861.403442382812</t>
@@ -4505,46 +4505,46 @@
     <t xml:space="preserve">845.563415527344</t>
   </si>
   <si>
-    <t xml:space="preserve">859.720458984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.977416992188</t>
+    <t xml:space="preserve">859.720520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.977478027344</t>
   </si>
   <si>
     <t xml:space="preserve">863.482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">830.020324707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">773.39208984375</t>
+    <t xml:space="preserve">830.020385742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">773.391967773438</t>
   </si>
   <si>
     <t xml:space="preserve">783.193054199219</t>
   </si>
   <si>
-    <t xml:space="preserve">784.282104492188</t>
+    <t xml:space="preserve">784.282043457031</t>
   </si>
   <si>
     <t xml:space="preserve">807.646118164062</t>
   </si>
   <si>
-    <t xml:space="preserve">782.401062011719</t>
+    <t xml:space="preserve">782.401000976562</t>
   </si>
   <si>
     <t xml:space="preserve">760.224914550781</t>
   </si>
   <si>
-    <t xml:space="preserve">743.790771484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">737.751831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">726.4658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">735.078796386719</t>
+    <t xml:space="preserve">743.790893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">737.751892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">726.465759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">735.078735351562</t>
   </si>
   <si>
     <t xml:space="preserve">761.016906738281</t>
@@ -4553,10 +4553,10 @@
     <t xml:space="preserve">720.030700683594</t>
   </si>
   <si>
-    <t xml:space="preserve">699.042724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720.327697753906</t>
+    <t xml:space="preserve">699.04248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720.32763671875</t>
   </si>
   <si>
     <t xml:space="preserve">702.804626464844</t>
@@ -4565,19 +4565,19 @@
     <t xml:space="preserve">755.967895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">812.794250488281</t>
+    <t xml:space="preserve">812.794189453125</t>
   </si>
   <si>
     <t xml:space="preserve">806.359252929688</t>
   </si>
   <si>
-    <t xml:space="preserve">817.744323730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">838.138366699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">836.353515625</t>
+    <t xml:space="preserve">817.744262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.138305664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">836.353576660156</t>
   </si>
   <si>
     <t xml:space="preserve">824.752746582031</t>
@@ -4586,28 +4586,28 @@
     <t xml:space="preserve">846.169738769531</t>
   </si>
   <si>
-    <t xml:space="preserve">841.806945800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">855.88671875</t>
+    <t xml:space="preserve">841.807006835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">855.886657714844</t>
   </si>
   <si>
     <t xml:space="preserve">840.220520019531</t>
   </si>
   <si>
-    <t xml:space="preserve">845.37646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">851.028137207031</t>
+    <t xml:space="preserve">845.376403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">851.028198242188</t>
   </si>
   <si>
     <t xml:space="preserve">845.673950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">850.631652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">846.7646484375</t>
+    <t xml:space="preserve">850.631591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">846.764587402344</t>
   </si>
   <si>
     <t xml:space="preserve">858.563781738281</t>
@@ -4619,7 +4619,7 @@
     <t xml:space="preserve">852.218017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">812.160278320312</t>
+    <t xml:space="preserve">812.160217285156</t>
   </si>
   <si>
     <t xml:space="preserve">806.012817382812</t>
@@ -4628,13 +4628,13 @@
     <t xml:space="preserve">807.995910644531</t>
   </si>
   <si>
-    <t xml:space="preserve">812.656066894531</t>
+    <t xml:space="preserve">812.656005859375</t>
   </si>
   <si>
     <t xml:space="preserve">812.953552246094</t>
   </si>
   <si>
-    <t xml:space="preserve">831.197631835938</t>
+    <t xml:space="preserve">831.197570800781</t>
   </si>
   <si>
     <t xml:space="preserve">835.064636230469</t>
@@ -4646,10 +4646,10 @@
     <t xml:space="preserve">812.556945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">808.987426757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">805.51708984375</t>
+    <t xml:space="preserve">808.987487792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">805.517028808594</t>
   </si>
   <si>
     <t xml:space="preserve">825.5458984375</t>
@@ -4664,10 +4664,10 @@
     <t xml:space="preserve">821.579772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">813.845886230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">779.737426757812</t>
+    <t xml:space="preserve">813.845947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">779.7373046875</t>
   </si>
   <si>
     <t xml:space="preserve">779.935607910156</t>
@@ -4676,34 +4676,34 @@
     <t xml:space="preserve">793.519592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">800.063720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">798.675537109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">794.709411621094</t>
+    <t xml:space="preserve">800.063659667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">798.675476074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">794.70947265625</t>
   </si>
   <si>
     <t xml:space="preserve">816.32470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">826.636596679688</t>
+    <t xml:space="preserve">826.636657714844</t>
   </si>
   <si>
     <t xml:space="preserve">829.313720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">836.948547363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">829.8095703125</t>
+    <t xml:space="preserve">836.948486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">829.809448242188</t>
   </si>
   <si>
     <t xml:space="preserve">832.982360839844</t>
   </si>
   <si>
-    <t xml:space="preserve">841.410339355469</t>
+    <t xml:space="preserve">841.410400390625</t>
   </si>
   <si>
     <t xml:space="preserve">838.435791015625</t>
@@ -4715,22 +4715,22 @@
     <t xml:space="preserve">833.279846191406</t>
   </si>
   <si>
-    <t xml:space="preserve">823.662048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819.2001953125</t>
+    <t xml:space="preserve">823.662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.200134277344</t>
   </si>
   <si>
     <t xml:space="preserve">822.868835449219</t>
   </si>
   <si>
-    <t xml:space="preserve">819.894226074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">827.132385253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761.790649414062</t>
+    <t xml:space="preserve">819.894287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">827.132446289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761.790710449219</t>
   </si>
   <si>
     <t xml:space="preserve">778.646667480469</t>
@@ -4742,58 +4742,58 @@
     <t xml:space="preserve">737.002502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">726.492248535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">716.973571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">725.401550292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766.549987792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">778.250122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761.691589355469</t>
+    <t xml:space="preserve">726.492309570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">716.9736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">725.401611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766.549926757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">778.250061035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761.691528320312</t>
   </si>
   <si>
     <t xml:space="preserve">771.309387207031</t>
   </si>
   <si>
-    <t xml:space="preserve">750.090698242188</t>
+    <t xml:space="preserve">750.090759277344</t>
   </si>
   <si>
     <t xml:space="preserve">713.241638183594</t>
   </si>
   <si>
-    <t xml:space="preserve">680.464965820312</t>
+    <t xml:space="preserve">680.464904785156</t>
   </si>
   <si>
     <t xml:space="preserve">679.670349121094</t>
   </si>
   <si>
-    <t xml:space="preserve">703.706665039062</t>
+    <t xml:space="preserve">703.706604003906</t>
   </si>
   <si>
     <t xml:space="preserve">705.295776367188</t>
   </si>
   <si>
-    <t xml:space="preserve">715.228088378906</t>
+    <t xml:space="preserve">715.228149414062</t>
   </si>
   <si>
     <t xml:space="preserve">760.916931152344</t>
   </si>
   <si>
-    <t xml:space="preserve">744.429260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">749.892028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">756.447387695312</t>
+    <t xml:space="preserve">744.42919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">749.891967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">756.447326660156</t>
   </si>
   <si>
     <t xml:space="preserve">766.776977539062</t>
@@ -4802,13 +4802,13 @@
     <t xml:space="preserve">790.416015625</t>
   </si>
   <si>
-    <t xml:space="preserve">774.623596191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">788.429565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760.519653320312</t>
+    <t xml:space="preserve">774.62353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">788.429504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760.519714355469</t>
   </si>
   <si>
     <t xml:space="preserve">756.348083496094</t>
@@ -4823,22 +4823,22 @@
     <t xml:space="preserve">740.952941894531</t>
   </si>
   <si>
-    <t xml:space="preserve">744.330017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">744.925842285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">735.7880859375</t>
+    <t xml:space="preserve">744.329956054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">744.925903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">735.788146972656</t>
   </si>
   <si>
     <t xml:space="preserve">725.756469726562</t>
   </si>
   <si>
-    <t xml:space="preserve">759.029846191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">745.521789550781</t>
+    <t xml:space="preserve">759.02978515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">745.521728515625</t>
   </si>
   <si>
     <t xml:space="preserve">748.700134277344</t>
@@ -4847,19 +4847,19 @@
     <t xml:space="preserve">738.569152832031</t>
   </si>
   <si>
-    <t xml:space="preserve">759.327819824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">753.070434570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">739.860412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">740.158325195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.731872558594</t>
+    <t xml:space="preserve">759.327758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">753.070373535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">739.8603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">740.158386230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.731811523438</t>
   </si>
   <si>
     <t xml:space="preserve">758.433837890625</t>
@@ -4871,22 +4871,22 @@
     <t xml:space="preserve">769.359436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">718.505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720.194274902344</t>
+    <t xml:space="preserve">718.505798339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720.1943359375</t>
   </si>
   <si>
     <t xml:space="preserve">734.993530273438</t>
   </si>
   <si>
-    <t xml:space="preserve">714.731506347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">693.674926757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">697.548583984375</t>
+    <t xml:space="preserve">714.731567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">693.674987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">697.548522949219</t>
   </si>
   <si>
     <t xml:space="preserve">724.663879394531</t>
@@ -4895,40 +4895,40 @@
     <t xml:space="preserve">722.876037597656</t>
   </si>
   <si>
-    <t xml:space="preserve">741.846923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">757.937255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766.181091308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">768.068176269531</t>
+    <t xml:space="preserve">741.846862792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.937133789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766.18115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">768.068237304688</t>
   </si>
   <si>
     <t xml:space="preserve">771.445251464844</t>
   </si>
   <si>
-    <t xml:space="preserve">784.555969238281</t>
+    <t xml:space="preserve">784.555908203125</t>
   </si>
   <si>
     <t xml:space="preserve">785.052551269531</t>
   </si>
   <si>
-    <t xml:space="preserve">775.914855957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">796.176696777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">842.759399414062</t>
+    <t xml:space="preserve">775.914794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">796.1767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">842.759460449219</t>
   </si>
   <si>
     <t xml:space="preserve">843.752685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">834.813659667969</t>
+    <t xml:space="preserve">834.813598632812</t>
   </si>
   <si>
     <t xml:space="preserve">833.025756835938</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">849.839111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">836.903991699219</t>
+    <t xml:space="preserve">836.903930664062</t>
   </si>
   <si>
     <t xml:space="preserve">852.426208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">863.968322753906</t>
+    <t xml:space="preserve">863.96826171875</t>
   </si>
   <si>
     <t xml:space="preserve">882.276489257812</t>
@@ -4982,13 +4982,13 @@
     <t xml:space="preserve">846.456115722656</t>
   </si>
   <si>
-    <t xml:space="preserve">849.043090820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">797.700500488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">774.914794921875</t>
+    <t xml:space="preserve">849.043151855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">797.700561523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">774.914733886719</t>
   </si>
   <si>
     <t xml:space="preserve">745.064392089844</t>
@@ -5000,10 +5000,10 @@
     <t xml:space="preserve">734.517333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">740.785888671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">749.14404296875</t>
+    <t xml:space="preserve">740.785949707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">749.143981933594</t>
   </si>
   <si>
     <t xml:space="preserve">743.969909667969</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">774.21826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">787.053894042969</t>
+    <t xml:space="preserve">787.053955078125</t>
   </si>
   <si>
     <t xml:space="preserve">770.63623046875</t>
@@ -5036,13 +5036,13 @@
     <t xml:space="preserve">753.322998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">742.178955078125</t>
+    <t xml:space="preserve">742.178894042969</t>
   </si>
   <si>
     <t xml:space="preserve">718.497619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">679.891174316406</t>
+    <t xml:space="preserve">679.891235351562</t>
   </si>
   <si>
     <t xml:space="preserve">650.836853027344</t>
@@ -5054,7 +5054,7 @@
     <t xml:space="preserve">625.961608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">631.633178710938</t>
+    <t xml:space="preserve">631.633117675781</t>
   </si>
   <si>
     <t xml:space="preserve">630.837158203125</t>
@@ -5063,7 +5063,7 @@
     <t xml:space="preserve">655.612976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">669.443542480469</t>
+    <t xml:space="preserve">669.443603515625</t>
   </si>
   <si>
     <t xml:space="preserve">654.418884277344</t>
@@ -5075,7 +5075,7 @@
     <t xml:space="preserve">711.134582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">720.089721679688</t>
+    <t xml:space="preserve">720.089660644531</t>
   </si>
   <si>
     <t xml:space="preserve">743.074401855469</t>
@@ -5084,7 +5084,7 @@
     <t xml:space="preserve">758.397583007812</t>
   </si>
   <si>
-    <t xml:space="preserve">760.188659667969</t>
+    <t xml:space="preserve">760.188598632812</t>
   </si>
   <si>
     <t xml:space="preserve">774.516784667969</t>
@@ -5093,10 +5093,10 @@
     <t xml:space="preserve">784.765441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">721.184204101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">718.796203613281</t>
+    <t xml:space="preserve">721.184143066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">718.796142578125</t>
   </si>
   <si>
     <t xml:space="preserve">697.204406738281</t>
@@ -5105,16 +5105,16 @@
     <t xml:space="preserve">680.289245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">657.901428222656</t>
+    <t xml:space="preserve">657.901489257812</t>
   </si>
   <si>
     <t xml:space="preserve">665.563110351562</t>
   </si>
   <si>
-    <t xml:space="preserve">672.528198242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">668.7470703125</t>
+    <t xml:space="preserve">672.528137207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">668.747009277344</t>
   </si>
   <si>
     <t xml:space="preserve">643.274780273438</t>
@@ -5457,6 +5457,9 @@
   </si>
   <si>
     <t xml:space="preserve">742.799987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">767.599975585938</t>
   </si>
 </sst>
 </file>
@@ -70847,7 +70850,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45961.6914930556</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>3506</v>
@@ -70868,6 +70871,32 @@
         <v>1814</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45964.6968287037</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>3580</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>769</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>746.099975585938</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>750.900024414062</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>767.599975585938</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1815</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="1816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="1817">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,82 +38,82 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3028717041016</t>
+    <t xml:space="preserve">38.3028755187988</t>
   </si>
   <si>
     <t xml:space="preserve">LLY.DE</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7578277587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.680061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1174964904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5549354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4298324584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9923858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.2426147460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8051681518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3677062988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9302825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0229911804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5942993164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1717300415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8681335449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.707145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5907974243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3309364318848</t>
+    <t xml:space="preserve">38.7578239440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6800575256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1174926757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.554931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4298477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9924240112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.2426071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8051605224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3677101135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9302787780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0229949951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.594295501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1717224121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8681297302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7071495056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5908050537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3309326171875</t>
   </si>
   <si>
     <t xml:space="preserve">53.359806060791</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0159759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.221263885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8039970397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3226585388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4815902709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2785148620605</t>
+    <t xml:space="preserve">54.015983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2212677001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8040084838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3226623535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4815864562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">56.4021224975586</t>
@@ -122,379 +122,379 @@
     <t xml:space="preserve">57.028995513916</t>
   </si>
   <si>
-    <t xml:space="preserve">57.5322914123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5963745117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4662055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2719650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5721626281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1218605041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9276161193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9717750549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6405181884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2167129516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5787162780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0754280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8082618713379</t>
+    <t xml:space="preserve">57.532283782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.596363067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4662132263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2719612121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5721588134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1218643188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9276313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9717636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6405143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2167015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5787200927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.075439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8082695007324</t>
   </si>
   <si>
     <t xml:space="preserve">56.0312919616699</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4286155700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2961730957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.890022277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4861373901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2323760986328</t>
+    <t xml:space="preserve">56.4286003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2961654663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8900184631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4861450195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2323684692383</t>
   </si>
   <si>
     <t xml:space="preserve">53.9034042358398</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1130256652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.369083404541</t>
+    <t xml:space="preserve">55.1130294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3690872192383</t>
   </si>
   <si>
     <t xml:space="preserve">55.6251335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9230690002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8811912536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5191841125488</t>
+    <t xml:space="preserve">56.9230575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8811874389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5191879272461</t>
   </si>
   <si>
     <t xml:space="preserve">56.7641296386719</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1019325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6934967041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5057907104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1614532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9936943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.543399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.949535369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.4793090820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9119415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5829620361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9162216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.366512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.18994140625</t>
+    <t xml:space="preserve">56.1019401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6935005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5057945251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1614456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9936981201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5433921813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9495315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.479305267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9119529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5829849243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9162101745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3665199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1899299621582</t>
   </si>
   <si>
     <t xml:space="preserve">58.3622436523438</t>
   </si>
   <si>
-    <t xml:space="preserve">57.655891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6294097900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.6271209716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.733081817627</t>
+    <t xml:space="preserve">57.6559104919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6294059753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.6271286010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7330932617188</t>
   </si>
   <si>
     <t xml:space="preserve">60.5166244506836</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0552024841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.5231704711914</t>
+    <t xml:space="preserve">61.0552062988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5231742858887</t>
   </si>
   <si>
     <t xml:space="preserve">61.4452857971191</t>
   </si>
   <si>
-    <t xml:space="preserve">61.7212257385254</t>
+    <t xml:space="preserve">61.7212181091309</t>
   </si>
   <si>
     <t xml:space="preserve">62.2998123168945</t>
   </si>
   <si>
-    <t xml:space="preserve">62.887279510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5134429931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.243335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2077217102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.394660949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.9376525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4093933105469</t>
+    <t xml:space="preserve">62.8872833251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5134315490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2433433532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2077369689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.394645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.9376335144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4094085693359</t>
   </si>
   <si>
     <t xml:space="preserve">65.1571044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">64.5696029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6586151123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2105102539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2549896240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7980117797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1006393432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6911926269531</t>
+    <t xml:space="preserve">64.5696105957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6586303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2104949951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2550201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7979736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1006164550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6911773681641</t>
   </si>
   <si>
     <t xml:space="preserve">66.4967269897461</t>
   </si>
   <si>
-    <t xml:space="preserve">66.728157043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8336181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9582366943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1615524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.303955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5220489501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3320617675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2608642578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8202667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2563934326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5189971923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7860336303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3988265991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3557052612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.121208190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1657257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1568298339844</t>
+    <t xml:space="preserve">66.7281875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8335952758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9581985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1615676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3039703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5220642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3320541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2608489990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8202514648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2564010620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5189819335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7860260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3988189697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3557205200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1212310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1657180786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1568450927734</t>
   </si>
   <si>
     <t xml:space="preserve">68.6018753051758</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3971405029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5960235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1448669433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6194152832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.5273208618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6221771240234</t>
+    <t xml:space="preserve">68.3971328735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5960159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1448822021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6193923950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.5273284912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6221923828125</t>
   </si>
   <si>
     <t xml:space="preserve">73.5153579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">74.9306716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.696174621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2124481201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8355255126953</t>
+    <t xml:space="preserve">74.9306488037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6961898803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2124633789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8355407714844</t>
   </si>
   <si>
     <t xml:space="preserve">78.4733657836914</t>
   </si>
   <si>
-    <t xml:space="preserve">78.9362182617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.5623550415039</t>
+    <t xml:space="preserve">78.9362335205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.5623779296875</t>
   </si>
   <si>
     <t xml:space="preserve">78.7136917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">79.8352661132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8441467285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.804817199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4318771362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9513931274414</t>
+    <t xml:space="preserve">79.8352584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8441390991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8048553466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4318542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9513854980469</t>
   </si>
   <si>
     <t xml:space="preserve">82.5694351196289</t>
   </si>
   <si>
-    <t xml:space="preserve">82.7844161987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4587326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3691329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9033813476562</t>
+    <t xml:space="preserve">82.784423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.4587249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3691558837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9033584594727</t>
   </si>
   <si>
     <t xml:space="preserve">80.6883926391602</t>
   </si>
   <si>
-    <t xml:space="preserve">80.6346588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.5809097290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9839782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8496170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2168807983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0914764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2527008056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.2853012084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3211212158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4888153076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.86181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7811965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3960189819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6109924316406</t>
+    <t xml:space="preserve">80.6346206665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.5808944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9839935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2168731689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0914993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2527084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.2853088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3211288452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.4888458251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8618240356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7812042236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3960266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6109848022461</t>
   </si>
   <si>
     <t xml:space="preserve">81.9782638549805</t>
@@ -503,76 +503,76 @@
     <t xml:space="preserve">80.3569717407227</t>
   </si>
   <si>
-    <t xml:space="preserve">81.1810455322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6077651977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0735778808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.2380065917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1158447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2949981689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2810440063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2247924804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5057220458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7980804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1531600952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2477035522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.4537353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8478546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3014755249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8958892822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3201065063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9976196289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7378616333008</t>
+    <t xml:space="preserve">81.181037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.607780456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0735549926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.2379989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1158599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2950134277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2810668945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2247848510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5057067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7980728149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1531448364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2477188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.4537200927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8478469848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3014526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.895881652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3201141357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9976348876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7378387451172</t>
   </si>
   <si>
     <t xml:space="preserve">85.3552017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7436065673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1402435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2680969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2029113769531</t>
+    <t xml:space="preserve">86.7435989379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1402206420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2681198120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2029190063477</t>
   </si>
   <si>
     <t xml:space="preserve">87.0660629272461</t>
@@ -581,202 +581,202 @@
     <t xml:space="preserve">84.8177490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6980895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.1287384033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.4472808837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9725112915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2061462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7289047241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.2369689941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3591690063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9741439819336</t>
+    <t xml:space="preserve">83.6981048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1287689208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.4472579956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9725036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2061614990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7289123535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.2369918823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3591766357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9741516113281</t>
   </si>
   <si>
     <t xml:space="preserve">87.7129211425781</t>
   </si>
   <si>
-    <t xml:space="preserve">89.532600402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5685272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9740447998047</t>
+    <t xml:space="preserve">89.532585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5685195922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9740676879883</t>
   </si>
   <si>
     <t xml:space="preserve">88.3705139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">90.1991729736328</t>
+    <t xml:space="preserve">90.1991882324219</t>
   </si>
   <si>
     <t xml:space="preserve">88.8839721679688</t>
   </si>
   <si>
-    <t xml:space="preserve">90.406379699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2171173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7665176391602</t>
+    <t xml:space="preserve">90.4063873291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2171249389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7665100097656</t>
   </si>
   <si>
     <t xml:space="preserve">93.8475112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">94.0456924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1541442871094</t>
+    <t xml:space="preserve">94.0456848144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1541519165039</t>
   </si>
   <si>
     <t xml:space="preserve">89.6046447753906</t>
   </si>
   <si>
-    <t xml:space="preserve">88.388542175293</t>
+    <t xml:space="preserve">88.3885269165039</t>
   </si>
   <si>
     <t xml:space="preserve">91.3161849975586</t>
   </si>
   <si>
-    <t xml:space="preserve">89.7487564086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.89306640625</t>
+    <t xml:space="preserve">89.7487716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8930740356445</t>
   </si>
   <si>
     <t xml:space="preserve">84.8933334350586</t>
   </si>
   <si>
-    <t xml:space="preserve">86.893180847168</t>
+    <t xml:space="preserve">86.8931732177734</t>
   </si>
   <si>
     <t xml:space="preserve">86.0644226074219</t>
   </si>
   <si>
-    <t xml:space="preserve">85.2627792358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7760467529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5056076049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3252792358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0191040039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1812515258789</t>
+    <t xml:space="preserve">85.2627716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7760620117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5056610107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3252868652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0191345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1812591552734</t>
   </si>
   <si>
     <t xml:space="preserve">90.6315765380859</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6135482788086</t>
+    <t xml:space="preserve">90.6135559082031</t>
   </si>
   <si>
     <t xml:space="preserve">91.4513092041016</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8748168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6676025390625</t>
+    <t xml:space="preserve">90.8747711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6676254272461</t>
   </si>
   <si>
     <t xml:space="preserve">89.9919815063477</t>
   </si>
   <si>
-    <t xml:space="preserve">89.7217483520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3521347045898</t>
+    <t xml:space="preserve">89.7217407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3521499633789</t>
   </si>
   <si>
     <t xml:space="preserve">93.3700714111328</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6675186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5863723754883</t>
+    <t xml:space="preserve">91.6675262451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5863571166992</t>
   </si>
   <si>
     <t xml:space="preserve">92.424201965332</t>
   </si>
   <si>
-    <t xml:space="preserve">93.0998382568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6674270629883</t>
+    <t xml:space="preserve">93.0998229980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6674041748047</t>
   </si>
   <si>
     <t xml:space="preserve">90.6586074829102</t>
   </si>
   <si>
-    <t xml:space="preserve">90.0820541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7666168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5051803588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4150161743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7394104003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6852035522461</t>
+    <t xml:space="preserve">90.0820693969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7666091918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5051956176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4150009155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7394332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6851654052734</t>
   </si>
   <si>
     <t xml:space="preserve">94.099739074707</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4961853027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.604377746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.9646072387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3969955444336</t>
+    <t xml:space="preserve">93.4961624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.604362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.9645919799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3969879150391</t>
   </si>
   <si>
     <t xml:space="preserve">94.1718139648438</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3154678344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6569442749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0890884399414</t>
+    <t xml:space="preserve">96.3154449462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6569595336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0890960693359</t>
   </si>
   <si>
     <t xml:space="preserve">97.6750946044922</t>
@@ -785,64 +785,64 @@
     <t xml:space="preserve">97.7385482788086</t>
   </si>
   <si>
-    <t xml:space="preserve">98.2370376586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0437774658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2522430419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3247528076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6963882446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.521224975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.518272399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.475898742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.189025878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.318885803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.234352111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.457778930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9078369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4970016479492</t>
+    <t xml:space="preserve">98.237060546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0437698364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2522506713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3247680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6963806152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.52123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.518280029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.47590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.189041137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.318878173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.234344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.45777130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9078216552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4969787597656</t>
   </si>
   <si>
     <t xml:space="preserve">99.1616134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">99.5967025756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.865669250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.034965515137</t>
+    <t xml:space="preserve">99.5966949462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.865676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.034950256348</t>
   </si>
   <si>
     <t xml:space="preserve">102.5244140625</t>
   </si>
   <si>
-    <t xml:space="preserve">102.823532104492</t>
+    <t xml:space="preserve">102.823524475098</t>
   </si>
   <si>
     <t xml:space="preserve">104.1015625</t>
@@ -851,19 +851,19 @@
     <t xml:space="preserve">105.588066101074</t>
   </si>
   <si>
-    <t xml:space="preserve">104.446006774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.862945556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.300987243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.270851135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.352401733398</t>
+    <t xml:space="preserve">104.445983886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.862953186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.300979614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.27082824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.352416992188</t>
   </si>
   <si>
     <t xml:space="preserve">103.494270324707</t>
@@ -872,52 +872,52 @@
     <t xml:space="preserve">101.346069335938</t>
   </si>
   <si>
-    <t xml:space="preserve">102.207145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.880851745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.78727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.068016052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.0165786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8862915039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.472282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7020645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.771614074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9347763061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7867965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0587158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5751571655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.973991394043</t>
+    <t xml:space="preserve">102.207168579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.880844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.787261962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.068023681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.0165710449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8862609863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4722671508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7020492553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7716217041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9347686767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7867813110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0587387084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5751495361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9739837646484</t>
   </si>
   <si>
     <t xml:space="preserve">93.9044189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7775039672852</t>
+    <t xml:space="preserve">93.7775192260742</t>
   </si>
   <si>
     <t xml:space="preserve">94.049430847168</t>
@@ -929,49 +929,49 @@
     <t xml:space="preserve">92.3816452026367</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4360427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1430435180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3061752319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.755241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6241989135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.8829498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4815979003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3903732299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.0802459716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.1350021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4086151123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2228546142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9376449584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9890518188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5728225708008</t>
+    <t xml:space="preserve">92.4360122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1430206298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3061676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7552337646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6242141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.882942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4816055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3903884887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0802612304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.1350173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4086380004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2228851318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9376831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9890441894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5728149414062</t>
   </si>
   <si>
     <t xml:space="preserve">91.6324081420898</t>
@@ -980,196 +980,196 @@
     <t xml:space="preserve">92.5627822875977</t>
   </si>
   <si>
-    <t xml:space="preserve">93.0918197631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5834732055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2128524780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7999496459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4201889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9093856811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6357650756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3107528686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2608871459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8719940185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3098526000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3405303955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2709121704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3621063232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7567749023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1249618530273</t>
+    <t xml:space="preserve">93.0918502807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5834655761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2128372192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7999572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4201965332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4931564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9094009399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6357498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3107452392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2608795166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8720245361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3098373413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3405609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2709197998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3621444702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7567825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1249847412109</t>
   </si>
   <si>
     <t xml:space="preserve">89.3885803222656</t>
   </si>
   <si>
-    <t xml:space="preserve">86.6521911621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5643310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.476448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.020378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5004806518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3818893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.5245056152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9349670410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9474334716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3064956665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3703460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9507598876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2243957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.118278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.775016784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3040390014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9176254272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5469665527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4980316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.745231628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7418823242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.431755065918</t>
+    <t xml:space="preserve">86.652214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.564323425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4764633178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.0203704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5004959106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3818969726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.5245208740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9349746704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9474182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3065032958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.370361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9507522583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2244110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1182708740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7750091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3040542602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9176330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.546989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4980545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7452163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7418746948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4317626953125</t>
   </si>
   <si>
     <t xml:space="preserve">92.0702590942383</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4236679077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.440788269043</t>
+    <t xml:space="preserve">92.4236755371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4407806396484</t>
   </si>
   <si>
     <t xml:space="preserve">90.7804565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">92.790885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0479049682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0748291015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4230422973633</t>
+    <t xml:space="preserve">92.7908630371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0478820800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.074836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4230575561523</t>
   </si>
   <si>
     <t xml:space="preserve">91.9095993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">92.754150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8190231323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6084899902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8104400634766</t>
+    <t xml:space="preserve">92.7541427612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8190155029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6084747314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.810432434082</t>
   </si>
   <si>
     <t xml:space="preserve">95.2878112792969</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0197525024414</t>
+    <t xml:space="preserve">92.0197601318359</t>
   </si>
   <si>
     <t xml:space="preserve">90.7712783813477</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6990737915039</t>
+    <t xml:space="preserve">92.6990661621094</t>
   </si>
   <si>
     <t xml:space="preserve">92.9193878173828</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0381088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6801071166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7443618774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9928283691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9389724731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7015151977539</t>
+    <t xml:space="preserve">92.0381011962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6800842285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7443542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9928359985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9389801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7015228271484</t>
   </si>
   <si>
     <t xml:space="preserve">94.4065322875977</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">93.433464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9940643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4714126586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6354141235352</t>
+    <t xml:space="preserve">94.9940567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4714202880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6354293823242</t>
   </si>
   <si>
     <t xml:space="preserve">89.9634399414062</t>
@@ -1196,16 +1196,16 @@
     <t xml:space="preserve">89.5044326782227</t>
   </si>
   <si>
-    <t xml:space="preserve">90.4224319458008</t>
+    <t xml:space="preserve">90.4224548339844</t>
   </si>
   <si>
     <t xml:space="preserve">90.8814315795898</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3404312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.796989440918</t>
+    <t xml:space="preserve">91.3404388427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7969665527344</t>
   </si>
   <si>
     <t xml:space="preserve">88.5589218139648</t>
@@ -1217,73 +1217,73 @@
     <t xml:space="preserve">92.2033462524414</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6886596679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1397171020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7174224853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0944213867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0931930541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.800666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.488525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0209732055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1494903564453</t>
+    <t xml:space="preserve">90.6886749267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1396942138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7174377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0944137573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0931777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8006744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4885559082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0209808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1495056152344</t>
   </si>
   <si>
     <t xml:space="preserve">94.4616165161133</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4500732421875</t>
+    <t xml:space="preserve">93.4500579833984</t>
   </si>
   <si>
     <t xml:space="preserve">94.6509704589844</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7433700561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4824142456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.0920791625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6856307983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0158920288086</t>
+    <t xml:space="preserve">94.7433776855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4823989868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.0920944213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6856384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0158767700195</t>
   </si>
   <si>
     <t xml:space="preserve">98.5493469238281</t>
   </si>
   <si>
-    <t xml:space="preserve">98.8634567260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3830947875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1267471313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4939498901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.600158691406</t>
+    <t xml:space="preserve">98.8634414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3830795288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1267166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4939422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.600166320801</t>
   </si>
   <si>
     <t xml:space="preserve">99.9165725708008</t>
@@ -1292,55 +1292,55 @@
     <t xml:space="preserve">100.359985351562</t>
   </si>
   <si>
-    <t xml:space="preserve">100.212188720703</t>
+    <t xml:space="preserve">100.212181091309</t>
   </si>
   <si>
     <t xml:space="preserve">100.78491973877</t>
   </si>
   <si>
-    <t xml:space="preserve">100.711013793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.727188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.202934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.269905090332</t>
+    <t xml:space="preserve">100.71102142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.727195739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.202926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.269882202148</t>
   </si>
   <si>
     <t xml:space="preserve">108.008918762207</t>
   </si>
   <si>
-    <t xml:space="preserve">110.429244995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.653244018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.988121032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.064338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.341499328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.265274047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.135925292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.819526672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.893447875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.886512756348</t>
+    <t xml:space="preserve">110.429237365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.65323638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.988136291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.064353942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.34147644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.265266418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.135932922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.819534301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.893440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.886505126953</t>
   </si>
   <si>
     <t xml:space="preserve">114.105895996094</t>
@@ -1349,373 +1349,373 @@
     <t xml:space="preserve">115.269866943359</t>
   </si>
   <si>
-    <t xml:space="preserve">115.454635620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.507759094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.062019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.376091003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.710983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.486938476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.394584655762</t>
+    <t xml:space="preserve">115.454627990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.507736206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.062004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.376098632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.710975646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.486946105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.394561767578</t>
   </si>
   <si>
     <t xml:space="preserve">117.320671081543</t>
   </si>
   <si>
-    <t xml:space="preserve">117.413055419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.322982788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.115127563477</t>
+    <t xml:space="preserve">117.413032531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.322967529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.115135192871</t>
   </si>
   <si>
     <t xml:space="preserve">120.092002868652</t>
   </si>
   <si>
-    <t xml:space="preserve">117.135894775391</t>
+    <t xml:space="preserve">117.135932922363</t>
   </si>
   <si>
     <t xml:space="preserve">117.339141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">119.611656188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.156669616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.473075866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.274467468262</t>
+    <t xml:space="preserve">119.611640930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623199462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.156684875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.473068237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.274490356445</t>
   </si>
   <si>
     <t xml:space="preserve">121.292938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">122.586250305176</t>
+    <t xml:space="preserve">122.586235046387</t>
   </si>
   <si>
     <t xml:space="preserve">122.54907989502</t>
   </si>
   <si>
-    <t xml:space="preserve">121.24853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.616844177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.229927062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.270416259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.78734588623</t>
+    <t xml:space="preserve">121.248527526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.616836547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.229934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.270401000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.787338256836</t>
   </si>
   <si>
     <t xml:space="preserve">119.780776977539</t>
   </si>
   <si>
-    <t xml:space="preserve">117.049629211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.009162902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.01789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.620063781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.057220458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.441940307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.104232788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.306419372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.507530212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.881286621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.936988830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.135940551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.700942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.565444946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.609153747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.123954772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.597137451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.056182861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.120643615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.768692016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.270347595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.771995544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.844131469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.680183410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.365455627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.798225402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.694465637207</t>
+    <t xml:space="preserve">117.049598693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.009170532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.017890930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.620056152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.057228088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.441925048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.104248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.306434631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.507514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.881294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.937019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.135971069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.700927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.565437316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.609161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.123924255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.597145080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.056198120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.120651245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.768684387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270309448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.771980285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.844108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.68017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.365463256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.798248291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.694450378418</t>
   </si>
   <si>
     <t xml:space="preserve">120.301002502441</t>
   </si>
   <si>
-    <t xml:space="preserve">122.623382568359</t>
+    <t xml:space="preserve">122.623428344727</t>
   </si>
   <si>
     <t xml:space="preserve">123.552368164062</t>
   </si>
   <si>
-    <t xml:space="preserve">126.339241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.661682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.913009643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.448577880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.628952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.377563476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.235458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.285751342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.679183959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.217987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.557861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.232192993164</t>
+    <t xml:space="preserve">126.33927154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.661666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.913024902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.448547363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.628921508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.377548217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.235427856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.285766601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.67919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.217971801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.557876586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.232147216797</t>
   </si>
   <si>
     <t xml:space="preserve">132.117401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">129.367660522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.272644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.40592956543</t>
+    <t xml:space="preserve">129.367706298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.272598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.405975341797</t>
   </si>
   <si>
     <t xml:space="preserve">133.492309570312</t>
   </si>
   <si>
-    <t xml:space="preserve">132.154571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.182998657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.263870239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.833282470703</t>
+    <t xml:space="preserve">132.154586791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.183029174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.263885498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.833312988281</t>
   </si>
   <si>
     <t xml:space="preserve">135.889282226562</t>
   </si>
   <si>
-    <t xml:space="preserve">135.347732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.561553955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.050918579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.911758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.942642211914</t>
+    <t xml:space="preserve">135.347778320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.561538696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.050903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.911819458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.942672729492</t>
   </si>
   <si>
     <t xml:space="preserve">129.689605712891</t>
   </si>
   <si>
-    <t xml:space="preserve">130.399200439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.34700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.771919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.766189575195</t>
+    <t xml:space="preserve">130.399215698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.346984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.771896362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.766166687012</t>
   </si>
   <si>
     <t xml:space="preserve">127.56079864502</t>
   </si>
   <si>
-    <t xml:space="preserve">126.589752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.95484161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.18083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.002456665039</t>
+    <t xml:space="preserve">126.589775085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.954849243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.180824279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.002464294434</t>
   </si>
   <si>
     <t xml:space="preserve">122.873672485352</t>
   </si>
   <si>
-    <t xml:space="preserve">124.143516540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.554290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.846572875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.016548156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.97274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.142364501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.07795715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.011642456055</t>
+    <t xml:space="preserve">124.143486022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.55428314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.846588134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.016563415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.972724914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.142379760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.077911376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.011581420898</t>
   </si>
   <si>
     <t xml:space="preserve">131.650344848633</t>
   </si>
   <si>
-    <t xml:space="preserve">132.322601318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.984588623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.455215454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.62141418457</t>
+    <t xml:space="preserve">132.32258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.98454284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.455230712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.621383666992</t>
   </si>
   <si>
     <t xml:space="preserve">134.488754272461</t>
   </si>
   <si>
-    <t xml:space="preserve">134.61946105957</t>
+    <t xml:space="preserve">134.619445800781</t>
   </si>
   <si>
     <t xml:space="preserve">136.412170410156</t>
   </si>
   <si>
-    <t xml:space="preserve">136.374801635742</t>
+    <t xml:space="preserve">136.37483215332</t>
   </si>
   <si>
     <t xml:space="preserve">135.441131591797</t>
   </si>
   <si>
-    <t xml:space="preserve">138.484970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.055480957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.148834228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.225402832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.123687744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.43083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.20866394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.179672241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.125564575195</t>
+    <t xml:space="preserve">138.484939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.055465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.148818969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.225463867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.123657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.430847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.208694458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.179702758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.125579833984</t>
   </si>
   <si>
     <t xml:space="preserve">135.833251953125</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">135.795959472656</t>
   </si>
   <si>
-    <t xml:space="preserve">131.239532470703</t>
+    <t xml:space="preserve">131.239501953125</t>
   </si>
   <si>
     <t xml:space="preserve">127.355369567871</t>
@@ -1736,319 +1736,319 @@
     <t xml:space="preserve">128.793273925781</t>
   </si>
   <si>
-    <t xml:space="preserve">120.334030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.802764892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.47314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.854988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.155670166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.717796325684</t>
+    <t xml:space="preserve">120.334007263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.802772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.473121643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.854957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.155662536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.717803955078</t>
   </si>
   <si>
     <t xml:space="preserve">120.800872802734</t>
   </si>
   <si>
-    <t xml:space="preserve">120.875556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.736473083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.221984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.245338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.733657836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.409805297852</t>
+    <t xml:space="preserve">120.875587463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.736457824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.221969604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.245346069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.73365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.409812927246</t>
   </si>
   <si>
     <t xml:space="preserve">120.578819274902</t>
   </si>
   <si>
-    <t xml:space="preserve">121.480361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.071723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.174781799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.062065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.207763671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.42350769043</t>
+    <t xml:space="preserve">121.480346679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.071731567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.174758911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.062080383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.207778930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.423492431641</t>
   </si>
   <si>
     <t xml:space="preserve">119.170196533203</t>
   </si>
   <si>
-    <t xml:space="preserve">117.479843139648</t>
+    <t xml:space="preserve">117.479835510254</t>
   </si>
   <si>
     <t xml:space="preserve">116.446853637695</t>
   </si>
   <si>
-    <t xml:space="preserve">116.052436828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.832138061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.30167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.099647521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.625518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.799133300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.686973571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.59252166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.554977416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.63973236084</t>
+    <t xml:space="preserve">116.052429199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.83211517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.301689147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.099662780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.625534057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.799140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.686965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.592552185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.554985046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.639755249023</t>
   </si>
   <si>
     <t xml:space="preserve">120.710289001465</t>
   </si>
   <si>
-    <t xml:space="preserve">120.729064941406</t>
+    <t xml:space="preserve">120.72908782959</t>
   </si>
   <si>
     <t xml:space="preserve">121.611839294434</t>
   </si>
   <si>
-    <t xml:space="preserve">120.597595214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.334663391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.583396911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.785438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.193542480469</t>
+    <t xml:space="preserve">120.597618103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.334671020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.583374023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.785400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.193565368652</t>
   </si>
   <si>
     <t xml:space="preserve">116.709800720215</t>
   </si>
   <si>
-    <t xml:space="preserve">115.977317810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.747352600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.108764648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.424011230469</t>
+    <t xml:space="preserve">115.977310180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.747360229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.108772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.424026489258</t>
   </si>
   <si>
     <t xml:space="preserve">124.335174560547</t>
   </si>
   <si>
-    <t xml:space="preserve">123.546340942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.23161315918</t>
+    <t xml:space="preserve">123.546363830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.231628417969</t>
   </si>
   <si>
     <t xml:space="preserve">118.869697570801</t>
   </si>
   <si>
-    <t xml:space="preserve">117.06664276123</t>
+    <t xml:space="preserve">117.066635131836</t>
   </si>
   <si>
     <t xml:space="preserve">117.34838104248</t>
   </si>
   <si>
-    <t xml:space="preserve">115.150901794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.122459411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.615379333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.939224243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.347854614258</t>
+    <t xml:space="preserve">115.150894165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.12247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.615371704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.939231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.347862243652</t>
   </si>
   <si>
     <t xml:space="preserve">111.563591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">106.229583740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.835144042969</t>
+    <t xml:space="preserve">106.22957611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.835166931152</t>
   </si>
   <si>
     <t xml:space="preserve">106.530082702637</t>
   </si>
   <si>
-    <t xml:space="preserve">105.666122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.684906005859</t>
+    <t xml:space="preserve">105.666130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.684913635254</t>
   </si>
   <si>
     <t xml:space="preserve">106.511291503906</t>
   </si>
   <si>
-    <t xml:space="preserve">118.137214660645</t>
+    <t xml:space="preserve">118.137199401855</t>
   </si>
   <si>
     <t xml:space="preserve">116.221466064453</t>
   </si>
   <si>
-    <t xml:space="preserve">116.202674865723</t>
+    <t xml:space="preserve">116.202682495117</t>
   </si>
   <si>
     <t xml:space="preserve">113.5732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">117.104217529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.319946289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.939094543457</t>
+    <t xml:space="preserve">117.104202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.319931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.939125061035</t>
   </si>
   <si>
     <t xml:space="preserve">113.97834777832</t>
   </si>
   <si>
-    <t xml:space="preserve">113.354804992676</t>
+    <t xml:space="preserve">113.354782104492</t>
   </si>
   <si>
     <t xml:space="preserve">112.221061706543</t>
   </si>
   <si>
-    <t xml:space="preserve">112.504486083984</t>
+    <t xml:space="preserve">112.504493713379</t>
   </si>
   <si>
     <t xml:space="preserve">112.164375305176</t>
   </si>
   <si>
-    <t xml:space="preserve">116.359214782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.901306152344</t>
+    <t xml:space="preserve">116.35920715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.90128326416</t>
   </si>
   <si>
     <t xml:space="preserve">115.338844299316</t>
   </si>
   <si>
-    <t xml:space="preserve">113.449272155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.318473815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.830123901367</t>
+    <t xml:space="preserve">113.449264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.318481445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.830108642578</t>
   </si>
   <si>
     <t xml:space="preserve">114.828666687012</t>
   </si>
   <si>
-    <t xml:space="preserve">113.846099853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.447814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.469627380371</t>
+    <t xml:space="preserve">113.846115112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.447799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.469619750977</t>
   </si>
   <si>
     <t xml:space="preserve">116.151351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">122.65145111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.841842651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.353507995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.843338012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.411689758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.327438354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.94807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.267837524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.7373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.964065551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.416061401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.583183288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.471282958984</t>
+    <t xml:space="preserve">122.651458740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.841827392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.353500366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.84334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.411651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.327453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.948089599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.267822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.737319946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.96403503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.416091918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.583198547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.471298217773</t>
   </si>
   <si>
     <t xml:space="preserve">129.113754272461</t>
   </si>
   <si>
-    <t xml:space="preserve">126.827392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.392753601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.904396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.016326904297</t>
+    <t xml:space="preserve">126.827369689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.392784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.904418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.016342163086</t>
   </si>
   <si>
     <t xml:space="preserve">128.603561401367</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">145.118316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">139.978698730469</t>
+    <t xml:space="preserve">139.978713989258</t>
   </si>
   <si>
     <t xml:space="preserve">144.645935058594</t>
@@ -2066,19 +2066,19 @@
     <t xml:space="preserve">146.119781494141</t>
   </si>
   <si>
-    <t xml:space="preserve">148.047119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.839294433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.714385986328</t>
+    <t xml:space="preserve">148.047164916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.839263916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.714370727539</t>
   </si>
   <si>
     <t xml:space="preserve">156.833602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">155.076293945312</t>
+    <t xml:space="preserve">155.076309204102</t>
   </si>
   <si>
     <t xml:space="preserve">158.760955810547</t>
@@ -2087,37 +2087,37 @@
     <t xml:space="preserve">164.032836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">164.996536254883</t>
+    <t xml:space="preserve">164.996520996094</t>
   </si>
   <si>
     <t xml:space="preserve">161.992111206055</t>
   </si>
   <si>
-    <t xml:space="preserve">163.125823974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.349655151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.804641723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.720275878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.962921142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.13737487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.704284667969</t>
+    <t xml:space="preserve">163.125869750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.349670410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.804611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.72021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.962936401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.137405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.70426940918</t>
   </si>
   <si>
     <t xml:space="preserve">160.461578369141</t>
   </si>
   <si>
-    <t xml:space="preserve">156.814712524414</t>
+    <t xml:space="preserve">156.814682006836</t>
   </si>
   <si>
     <t xml:space="preserve">159.157775878906</t>
@@ -2126,73 +2126,73 @@
     <t xml:space="preserve">158.008773803711</t>
   </si>
   <si>
-    <t xml:space="preserve">160.819519042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.560836791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.794006347656</t>
+    <t xml:space="preserve">160.819534301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.560852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.793975830078</t>
   </si>
   <si>
     <t xml:space="preserve">161.161376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">159.831985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.856857299805</t>
+    <t xml:space="preserve">159.831970214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.856842041016</t>
   </si>
   <si>
     <t xml:space="preserve">154.932159423828</t>
   </si>
   <si>
-    <t xml:space="preserve">159.205276489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.964889526367</t>
+    <t xml:space="preserve">159.20524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.964904785156</t>
   </si>
   <si>
     <t xml:space="preserve">157.970794677734</t>
   </si>
   <si>
-    <t xml:space="preserve">159.907928466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.376815795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.756637573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.958343505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.338195800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.617156982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.884338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.409561157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.890213012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.661712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.326370239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.741622924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.931518554688</t>
+    <t xml:space="preserve">159.907897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.376831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.756607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.958374023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.338165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.617172241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.884323120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.409530639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.890243530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.661727905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.326354980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.741592407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.931533813477</t>
   </si>
   <si>
     <t xml:space="preserve">149.082794189453</t>
@@ -2201,88 +2201,88 @@
     <t xml:space="preserve">147.183670043945</t>
   </si>
   <si>
-    <t xml:space="preserve">147.753387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.133224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.462661743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.474426269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.993743896484</t>
+    <t xml:space="preserve">147.753433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.133209228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.462631225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.47444152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.993774414062</t>
   </si>
   <si>
     <t xml:space="preserve">148.89289855957</t>
   </si>
   <si>
-    <t xml:space="preserve">150.602142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.792037963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.399780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.45671081543</t>
+    <t xml:space="preserve">150.602157592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.792022705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.399749755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.456756591797</t>
   </si>
   <si>
     <t xml:space="preserve">148.703002929688</t>
   </si>
   <si>
-    <t xml:space="preserve">145.284530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.234115600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.854278564453</t>
+    <t xml:space="preserve">145.284515380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.234100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.854293823242</t>
   </si>
   <si>
     <t xml:space="preserve">144.904708862305</t>
   </si>
   <si>
-    <t xml:space="preserve">146.424041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.323165893555</t>
+    <t xml:space="preserve">146.42399597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.323150634766</t>
   </si>
   <si>
     <t xml:space="preserve">149.842483520508</t>
   </si>
   <si>
-    <t xml:space="preserve">150.412185668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.652572631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.513107299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.803863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.955108642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.346740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.486251831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.575286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.044174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.121459960938</t>
+    <t xml:space="preserve">150.412216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.652526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.513031005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.803833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.955154418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.346755981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.486236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.575317382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.044189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.12141418457</t>
   </si>
   <si>
     <t xml:space="preserve">152.691177368164</t>
@@ -2291,82 +2291,82 @@
     <t xml:space="preserve">153.070999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">151.836578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.693572998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.220962524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.457214355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.92985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.979934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.175552368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.702926635742</t>
+    <t xml:space="preserve">151.83659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.69352722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.220932006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.457260131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.929824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.175521850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.702941894531</t>
   </si>
   <si>
     <t xml:space="preserve">155.984603881836</t>
   </si>
   <si>
-    <t xml:space="preserve">154.361770629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.748306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.225631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.839080810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.366516113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.803070068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.640380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.876678466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.076950073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">183.000305175781</t>
+    <t xml:space="preserve">154.361755371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.748336791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.225616455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.839096069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.366485595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.803115844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.640365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.876663208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.076995849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">183.000335693359</t>
   </si>
   <si>
     <t xml:space="preserve">176.365707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">177.749938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.84065246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.222518920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.22721862793</t>
+    <t xml:space="preserve">177.749923706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.840682983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.222549438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.227188110352</t>
   </si>
   <si>
     <t xml:space="preserve">176.270233154297</t>
   </si>
   <si>
-    <t xml:space="preserve">179.038665771484</t>
+    <t xml:space="preserve">179.038681030273</t>
   </si>
   <si>
     <t xml:space="preserve">178.800033569336</t>
@@ -2375,49 +2375,49 @@
     <t xml:space="preserve">174.265548706055</t>
   </si>
   <si>
-    <t xml:space="preserve">185.243698120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.527709960938</t>
+    <t xml:space="preserve">185.243682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.527679443359</t>
   </si>
   <si>
     <t xml:space="preserve">182.093414306641</t>
   </si>
   <si>
-    <t xml:space="preserve">184.432220458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.291366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.102828979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.773391723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.491744995117</t>
+    <t xml:space="preserve">184.432250976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.291412353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.102813720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.773422241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.491729736328</t>
   </si>
   <si>
     <t xml:space="preserve">188.9189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">189.969055175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.775772094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.069198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.682632446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.446334838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.828170776367</t>
+    <t xml:space="preserve">189.969024658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.775741577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.06916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.682647705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.446319580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.828186035156</t>
   </si>
   <si>
     <t xml:space="preserve">188.584823608398</t>
@@ -2426,10 +2426,10 @@
     <t xml:space="preserve">187.677963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">187.296142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.591857910156</t>
+    <t xml:space="preserve">187.296081542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.591888427734</t>
   </si>
   <si>
     <t xml:space="preserve">191.973739624023</t>
@@ -2438,22 +2438,22 @@
     <t xml:space="preserve">193.88298034668</t>
   </si>
   <si>
-    <t xml:space="preserve">195.983139038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.415069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.269500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">199.515197753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.319580078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.84228515625</t>
+    <t xml:space="preserve">195.983123779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.4150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.269546508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">199.515243530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.319610595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.842269897461</t>
   </si>
   <si>
     <t xml:space="preserve">197.987838745117</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">213.739013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">212.975311279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.929916381836</t>
+    <t xml:space="preserve">212.975341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.929946899414</t>
   </si>
   <si>
     <t xml:space="preserve">218.321166992188</t>
@@ -2477,37 +2477,37 @@
     <t xml:space="preserve">218.703079223633</t>
   </si>
   <si>
-    <t xml:space="preserve">217.366577148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.498107910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.564331054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.917999267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.930221557617</t>
+    <t xml:space="preserve">217.366546630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.498062133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.564346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.917984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.93017578125</t>
   </si>
   <si>
     <t xml:space="preserve">221.534713745117</t>
   </si>
   <si>
-    <t xml:space="preserve">223.067825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.205459594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.444046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.156600952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.294235229492</t>
+    <t xml:space="preserve">223.067810058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.205444335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.444061279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.156646728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.294250488281</t>
   </si>
   <si>
     <t xml:space="preserve">212.048599243164</t>
@@ -2516,13 +2516,13 @@
     <t xml:space="preserve">214.060791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">211.18620300293</t>
+    <t xml:space="preserve">211.186248779297</t>
   </si>
   <si>
     <t xml:space="preserve">207.736709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">208.982360839844</t>
+    <t xml:space="preserve">208.982376098633</t>
   </si>
   <si>
     <t xml:space="preserve">209.269821166992</t>
@@ -2531,94 +2531,94 @@
     <t xml:space="preserve">210.994598388672</t>
   </si>
   <si>
-    <t xml:space="preserve">209.461456298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.970169067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.058959960938</t>
+    <t xml:space="preserve">209.461471557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.970153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.058929443359</t>
   </si>
   <si>
     <t xml:space="preserve">196.621658325195</t>
   </si>
   <si>
-    <t xml:space="preserve">191.447402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.920349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.495300292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.902069091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.087600708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.530990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.626815795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.997909545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.632934570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.537124633789</t>
+    <t xml:space="preserve">191.447387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.920394897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.495315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.902084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.087615966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.531005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.626831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.997894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.632919311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.537094116211</t>
   </si>
   <si>
     <t xml:space="preserve">185.889862060547</t>
   </si>
   <si>
-    <t xml:space="preserve">182.152893066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.572830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.651245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">189.770523071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.410751342773</t>
+    <t xml:space="preserve">182.152908325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.572814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.651229858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">189.770553588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.410766601562</t>
   </si>
   <si>
     <t xml:space="preserve">190.393402099609</t>
   </si>
   <si>
-    <t xml:space="preserve">188.237411499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.501373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.172164916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.525848388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.555435180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.938705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">194.992752075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.471817016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.442245483398</t>
+    <t xml:space="preserve">188.237426757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.501388549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.172149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.525833129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.555419921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.938690185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194.992721557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.471801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.442230224609</t>
   </si>
   <si>
     <t xml:space="preserve">198.72966003418</t>
@@ -2627,43 +2627,43 @@
     <t xml:space="preserve">200.358596801758</t>
   </si>
   <si>
-    <t xml:space="preserve">198.538055419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.921356201172</t>
+    <t xml:space="preserve">198.537994384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.921310424805</t>
   </si>
   <si>
     <t xml:space="preserve">201.987548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">202.849914550781</t>
+    <t xml:space="preserve">202.84992980957</t>
   </si>
   <si>
     <t xml:space="preserve">208.2158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">207.83251953125</t>
+    <t xml:space="preserve">207.832550048828</t>
   </si>
   <si>
     <t xml:space="preserve">210.802947998047</t>
   </si>
   <si>
-    <t xml:space="preserve">207.353424072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.006774902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.989395141602</t>
+    <t xml:space="preserve">207.353454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.006805419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.989410400391</t>
   </si>
   <si>
     <t xml:space="preserve">215.59391784668</t>
   </si>
   <si>
-    <t xml:space="preserve">215.977188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.905776977539</t>
+    <t xml:space="preserve">215.977172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.905807495117</t>
   </si>
   <si>
     <t xml:space="preserve">220.768157958984</t>
@@ -2672,16 +2672,16 @@
     <t xml:space="preserve">218.892776489258</t>
   </si>
   <si>
-    <t xml:space="preserve">217.161636352539</t>
+    <t xml:space="preserve">217.16162109375</t>
   </si>
   <si>
     <t xml:space="preserve">219.277450561523</t>
   </si>
   <si>
-    <t xml:space="preserve">221.297103881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.200958251953</t>
+    <t xml:space="preserve">221.297134399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.200927734375</t>
   </si>
   <si>
     <t xml:space="preserve">223.316787719727</t>
@@ -2690,16 +2690,16 @@
     <t xml:space="preserve">224.663238525391</t>
   </si>
   <si>
-    <t xml:space="preserve">223.509140014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.182373046875</t>
+    <t xml:space="preserve">223.509124755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.182357788086</t>
   </si>
   <si>
     <t xml:space="preserve">227.067596435547</t>
   </si>
   <si>
-    <t xml:space="preserve">222.162689208984</t>
+    <t xml:space="preserve">222.162719726562</t>
   </si>
   <si>
     <t xml:space="preserve">212.064407348633</t>
@@ -2708,67 +2708,67 @@
     <t xml:space="preserve">215.238128662109</t>
   </si>
   <si>
-    <t xml:space="preserve">211.198852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.756195068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.351837158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203.985733032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.313613891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.640365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.50700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.929946899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.279571533203</t>
+    <t xml:space="preserve">211.198822021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.756225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.351867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203.985763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.313583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.640350341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.506988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.929962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.279602050781</t>
   </si>
   <si>
     <t xml:space="preserve">237.646759033203</t>
   </si>
   <si>
-    <t xml:space="preserve">227.259963989258</t>
+    <t xml:space="preserve">227.259918212891</t>
   </si>
   <si>
     <t xml:space="preserve">225.624984741211</t>
   </si>
   <si>
-    <t xml:space="preserve">224.56706237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">232.068664550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.819442749023</t>
+    <t xml:space="preserve">224.567047119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">232.06867980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.819458007812</t>
   </si>
   <si>
     <t xml:space="preserve">235.434753417969</t>
   </si>
   <si>
-    <t xml:space="preserve">235.530883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">228.31787109375</t>
+    <t xml:space="preserve">235.530914306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">228.317840576172</t>
   </si>
   <si>
     <t xml:space="preserve">227.644622802734</t>
   </si>
   <si>
-    <t xml:space="preserve">220.527740478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.662170410156</t>
+    <t xml:space="preserve">220.527755737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.662185668945</t>
   </si>
   <si>
     <t xml:space="preserve">218.123382568359</t>
@@ -2777,46 +2777,46 @@
     <t xml:space="preserve">219.373626708984</t>
   </si>
   <si>
-    <t xml:space="preserve">212.256759643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.197769165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.544189453125</t>
+    <t xml:space="preserve">212.256744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.19775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.544174194336</t>
   </si>
   <si>
     <t xml:space="preserve">208.409744262695</t>
   </si>
   <si>
-    <t xml:space="preserve">211.102645874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.948577880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.15950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.042602539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.869918823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.813003540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.121231079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.928894042969</t>
+    <t xml:space="preserve">211.102630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.948623657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.159484863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.042587280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.869873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.813095092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.121246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.92887878418</t>
   </si>
   <si>
     <t xml:space="preserve">208.98681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">208.794479370117</t>
+    <t xml:space="preserve">208.794464111328</t>
   </si>
   <si>
     <t xml:space="preserve">212.352920532227</t>
@@ -2825,22 +2825,22 @@
     <t xml:space="preserve">206.101593017578</t>
   </si>
   <si>
-    <t xml:space="preserve">202.639282226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.158416748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.139831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.927825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.234939575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.959457397461</t>
+    <t xml:space="preserve">202.63932800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.158432006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.139846801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.927810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.234954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.959442138672</t>
   </si>
   <si>
     <t xml:space="preserve">207.076309204102</t>
@@ -2849,40 +2849,40 @@
     <t xml:space="preserve">208.525726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">206.593154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204.853851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.892028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203.404418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.916763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.626831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">216.256072998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.13020324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.806579589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.957168579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.116714477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.397644042969</t>
+    <t xml:space="preserve">206.593170166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">204.85383605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.892044067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203.404403686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.916748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.626815795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">216.256057739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.130233764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.806655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.957183837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.116744995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.397583007812</t>
   </si>
   <si>
     <t xml:space="preserve">231.90998840332</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">233.262802124023</t>
   </si>
   <si>
-    <t xml:space="preserve">232.393127441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.233581542969</t>
+    <t xml:space="preserve">232.393142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.23356628418</t>
   </si>
   <si>
     <t xml:space="preserve">237.417861938477</t>
@@ -2903,67 +2903,67 @@
     <t xml:space="preserve">236.161682128906</t>
   </si>
   <si>
-    <t xml:space="preserve">243.312225341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.408843994141</t>
+    <t xml:space="preserve">243.312240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.40885925293</t>
   </si>
   <si>
     <t xml:space="preserve">246.307739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">251.332473754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.65153503418</t>
+    <t xml:space="preserve">251.332458496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.651580810547</t>
   </si>
   <si>
     <t xml:space="preserve">249.883010864258</t>
   </si>
   <si>
-    <t xml:space="preserve">251.525741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.105484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.29426574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.004348754883</t>
+    <t xml:space="preserve">251.525680541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.105499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.294219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.004333496094</t>
   </si>
   <si>
     <t xml:space="preserve">251.622344970703</t>
   </si>
   <si>
-    <t xml:space="preserve">252.008834838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250.656051635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.844802856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">257.468383789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260.802093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266.020080566406</t>
+    <t xml:space="preserve">252.008819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250.656021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.844787597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">257.468414306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260.802124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266.020050048828</t>
   </si>
   <si>
     <t xml:space="preserve">275.48974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">276.890838623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.006652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.66845703125</t>
+    <t xml:space="preserve">276.890869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.006591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.668426513672</t>
   </si>
   <si>
     <t xml:space="preserve">269.305511474609</t>
@@ -2972,61 +2972,61 @@
     <t xml:space="preserve">269.691986083984</t>
   </si>
   <si>
-    <t xml:space="preserve">265.295349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.555969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.796478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.347030639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.869506835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">269.595367431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.822296142578</t>
+    <t xml:space="preserve">265.295379638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.556030273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.796569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.347015380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.869537353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">269.595336914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.822357177734</t>
   </si>
   <si>
     <t xml:space="preserve">265.730194091797</t>
   </si>
   <si>
-    <t xml:space="preserve">265.536895751953</t>
+    <t xml:space="preserve">265.536926269531</t>
   </si>
   <si>
     <t xml:space="preserve">264.957183837891</t>
   </si>
   <si>
-    <t xml:space="preserve">268.339233398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.102111816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.942565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">258.579681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266.454925537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">267.405242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">281.854370117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">277.005615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.290405273438</t>
+    <t xml:space="preserve">268.339202880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.102172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.942535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258.579650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266.454956054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">267.4052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281.854400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">277.005645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.290374755859</t>
   </si>
   <si>
     <t xml:space="preserve">263.623291015625</t>
@@ -3035,22 +3035,22 @@
     <t xml:space="preserve">271.090270996094</t>
   </si>
   <si>
-    <t xml:space="preserve">275.599578857422</t>
+    <t xml:space="preserve">275.599609375</t>
   </si>
   <si>
     <t xml:space="preserve">272.108489990234</t>
   </si>
   <si>
-    <t xml:space="preserve">280.642181396484</t>
+    <t xml:space="preserve">280.642211914062</t>
   </si>
   <si>
     <t xml:space="preserve">281.466491699219</t>
   </si>
   <si>
-    <t xml:space="preserve">282.630126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.532867431641</t>
+    <t xml:space="preserve">282.630096435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.532836914062</t>
   </si>
   <si>
     <t xml:space="preserve">280.205780029297</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">278.411804199219</t>
   </si>
   <si>
-    <t xml:space="preserve">284.084777832031</t>
+    <t xml:space="preserve">284.084716796875</t>
   </si>
   <si>
     <t xml:space="preserve">279.769409179688</t>
   </si>
   <si>
-    <t xml:space="preserve">275.066192626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270.750823974609</t>
+    <t xml:space="preserve">275.066223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270.750793457031</t>
   </si>
   <si>
     <t xml:space="preserve">268.471954345703</t>
@@ -3077,55 +3077,55 @@
     <t xml:space="preserve">271.817535400391</t>
   </si>
   <si>
-    <t xml:space="preserve">265.611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.253936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270.847778320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.484405517578</t>
+    <t xml:space="preserve">265.611206054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.25390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270.847808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.484344482422</t>
   </si>
   <si>
     <t xml:space="preserve">279.720947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">284.763549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.291412353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.455017089844</t>
+    <t xml:space="preserve">284.763580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.291442871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.455047607422</t>
   </si>
   <si>
     <t xml:space="preserve">295.576110839844</t>
   </si>
   <si>
-    <t xml:space="preserve">299.552062988281</t>
+    <t xml:space="preserve">299.552093505859</t>
   </si>
   <si>
     <t xml:space="preserve">298.679321289062</t>
   </si>
   <si>
-    <t xml:space="preserve">299.842956542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.946136474609</t>
+    <t xml:space="preserve">299.843017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.946166992188</t>
   </si>
   <si>
     <t xml:space="preserve">303.721923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">314.049682617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.740447998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.019348144531</t>
+    <t xml:space="preserve">314.049652099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.740539550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.019409179688</t>
   </si>
   <si>
     <t xml:space="preserve">318.364990234375</t>
@@ -3134,100 +3134,100 @@
     <t xml:space="preserve">309.443389892578</t>
   </si>
   <si>
-    <t xml:space="preserve">311.625305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.12255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.213287353516</t>
+    <t xml:space="preserve">311.625335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.122528076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.213317871094</t>
   </si>
   <si>
     <t xml:space="preserve">309.879760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">306.825103759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.916168212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.837432861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.231567382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.467834472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.631591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.661804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.425140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.473663330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.667358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.854705810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">288.836517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.369873046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.284912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">285.539398193359</t>
+    <t xml:space="preserve">306.825134277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.916198730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.837493896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.231597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.4677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.631530761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.661773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.425170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.473724365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.667297363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.854644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">288.836456298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.369781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.284820556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">285.539337158203</t>
   </si>
   <si>
     <t xml:space="preserve">283.84228515625</t>
   </si>
   <si>
-    <t xml:space="preserve">289.806823730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.298797607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.812530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.574676513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">312.428955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.126251220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.996490478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.358612060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.412658691406</t>
+    <t xml:space="preserve">289.806762695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.369110107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.812591552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.574645996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">312.428894042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.126281738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.996459960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.358642578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.412689208984</t>
   </si>
   <si>
     <t xml:space="preserve">314.228973388672</t>
   </si>
   <si>
-    <t xml:space="preserve">303.234069824219</t>
+    <t xml:space="preserve">303.234130859375</t>
   </si>
   <si>
     <t xml:space="preserve">299.925903320312</t>
@@ -3239,208 +3239,208 @@
     <t xml:space="preserve">297.250183105469</t>
   </si>
   <si>
-    <t xml:space="preserve">300.2177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.887969970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.596343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.963836669922</t>
+    <t xml:space="preserve">300.217803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.888031005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.596313476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.963806152344</t>
   </si>
   <si>
     <t xml:space="preserve">306.688232421875</t>
   </si>
   <si>
-    <t xml:space="preserve">308.585540771484</t>
+    <t xml:space="preserve">308.585601806641</t>
   </si>
   <si>
     <t xml:space="preserve">306.298980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">301.969177246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.412414550781</t>
+    <t xml:space="preserve">301.96923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.412445068359</t>
   </si>
   <si>
     <t xml:space="preserve">299.342071533203</t>
   </si>
   <si>
-    <t xml:space="preserve">293.796112060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.990661621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.104278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.601837158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.84521484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.082946777344</t>
+    <t xml:space="preserve">293.796020507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.990692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.104217529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.601898193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.845092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.0830078125</t>
   </si>
   <si>
     <t xml:space="preserve">342.883697509766</t>
   </si>
   <si>
-    <t xml:space="preserve">327.656341552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.445404052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.612854003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320.066986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.348114013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.721252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.650909423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323.375122070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.758941650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327.315795898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.883239746094</t>
+    <t xml:space="preserve">327.656311035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.445373535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.612762451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320.066955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.348175048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.721282958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.650939941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.375152587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.758972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327.315765380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.88330078125</t>
   </si>
   <si>
     <t xml:space="preserve">330.380645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">332.521270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.580627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">326.245513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.710327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.515899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.759338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.543151855469</t>
+    <t xml:space="preserve">332.521240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.580688476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326.245452880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.710266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.515869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.759399414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.543090820312</t>
   </si>
   <si>
     <t xml:space="preserve">347.456787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">347.748565673828</t>
+    <t xml:space="preserve">347.748657226562</t>
   </si>
   <si>
     <t xml:space="preserve">352.7109375</t>
   </si>
   <si>
-    <t xml:space="preserve">354.802856445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.424163818359</t>
+    <t xml:space="preserve">354.802917480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.424194335938</t>
   </si>
   <si>
     <t xml:space="preserve">353.829864501953</t>
   </si>
   <si>
-    <t xml:space="preserve">358.257049560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350.473083496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.224456787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">353.635314941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.429901123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">349.013549804688</t>
+    <t xml:space="preserve">358.257019042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350.473022460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.224487304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">353.635284423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.429992675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">349.013610839844</t>
   </si>
   <si>
     <t xml:space="preserve">330.672607421875</t>
   </si>
   <si>
-    <t xml:space="preserve">334.946655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.531280517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.921600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.898681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.972015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">343.728881835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.606719970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.581756591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.093811035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.704345703125</t>
+    <t xml:space="preserve">334.946563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.53125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.921630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.898651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.972076416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">343.728942871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.606689453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.581695556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.093872070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.704315185547</t>
   </si>
   <si>
     <t xml:space="preserve">345.095031738281</t>
   </si>
   <si>
-    <t xml:space="preserve">341.435729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">344.509552001953</t>
+    <t xml:space="preserve">341.435760498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.509643554688</t>
   </si>
   <si>
     <t xml:space="preserve">344.119232177734</t>
   </si>
   <si>
-    <t xml:space="preserve">346.509979248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.826873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.070007324219</t>
+    <t xml:space="preserve">346.509948730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.826965332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.070037841797</t>
   </si>
   <si>
     <t xml:space="preserve">345.582977294922</t>
   </si>
   <si>
-    <t xml:space="preserve">343.68017578125</t>
+    <t xml:space="preserve">343.680114746094</t>
   </si>
   <si>
     <t xml:space="preserve">340.4111328125</t>
@@ -3449,19 +3449,19 @@
     <t xml:space="preserve">338.801086425781</t>
   </si>
   <si>
-    <t xml:space="preserve">335.239349365234</t>
+    <t xml:space="preserve">335.239379882812</t>
   </si>
   <si>
     <t xml:space="preserve">332.751037597656</t>
   </si>
   <si>
-    <t xml:space="preserve">328.945434570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.994171142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.116394042969</t>
+    <t xml:space="preserve">328.945404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.994201660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.116333007812</t>
   </si>
   <si>
     <t xml:space="preserve">340.118438720703</t>
@@ -3473,79 +3473,79 @@
     <t xml:space="preserve">336.800659179688</t>
   </si>
   <si>
-    <t xml:space="preserve">335.141876220703</t>
+    <t xml:space="preserve">335.141754150391</t>
   </si>
   <si>
     <t xml:space="preserve">338.605895996094</t>
   </si>
   <si>
-    <t xml:space="preserve">335.044219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.703033447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.629669189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">337.28857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.897033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.434539794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.774017333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.625640869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">321.529235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">321.919555664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">326.017974853516</t>
+    <t xml:space="preserve">335.044250488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.703094482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.629760742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">337.288543701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.89697265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.434509277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.774047851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.625549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">321.529266357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">321.919586181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326.018005371094</t>
   </si>
   <si>
     <t xml:space="preserve">323.968780517578</t>
   </si>
   <si>
-    <t xml:space="preserve">325.188537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320.065551757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">317.528472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.088073730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.672790527344</t>
+    <t xml:space="preserve">325.188507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320.065521240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">317.528442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.088043212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.672698974609</t>
   </si>
   <si>
     <t xml:space="preserve">307.428771972656</t>
   </si>
   <si>
-    <t xml:space="preserve">310.1611328125</t>
+    <t xml:space="preserve">310.161102294922</t>
   </si>
   <si>
     <t xml:space="preserve">313.039672851562</t>
   </si>
   <si>
-    <t xml:space="preserve">308.794982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.184783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.477233886719</t>
+    <t xml:space="preserve">308.794921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.184844970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.477203369141</t>
   </si>
   <si>
     <t xml:space="preserve">287.131958007812</t>
@@ -3554,13 +3554,13 @@
     <t xml:space="preserve">307.331237792969</t>
   </si>
   <si>
-    <t xml:space="preserve">306.160217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.501739501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.575653076172</t>
+    <t xml:space="preserve">306.160247802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.501770019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.575561523438</t>
   </si>
   <si>
     <t xml:space="preserve">312.161499023438</t>
@@ -3572,16 +3572,16 @@
     <t xml:space="preserve">316.503845214844</t>
   </si>
   <si>
-    <t xml:space="preserve">318.393707275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.595550537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.558563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">301.942779541016</t>
+    <t xml:space="preserve">318.393737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.595520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.558532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">301.942810058594</t>
   </si>
   <si>
     <t xml:space="preserve">300.571899414062</t>
@@ -3590,25 +3590,25 @@
     <t xml:space="preserve">302.775146484375</t>
   </si>
   <si>
-    <t xml:space="preserve">304.146087646484</t>
+    <t xml:space="preserve">304.146057128906</t>
   </si>
   <si>
     <t xml:space="preserve">304.341918945312</t>
   </si>
   <si>
-    <t xml:space="preserve">299.886413574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294.011108398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.939910888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290.192199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.604583740234</t>
+    <t xml:space="preserve">299.886444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.011138916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.93994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">290.192138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.604705810547</t>
   </si>
   <si>
     <t xml:space="preserve">293.080841064453</t>
@@ -3620,85 +3620,85 @@
     <t xml:space="preserve">289.702545166016</t>
   </si>
   <si>
-    <t xml:space="preserve">288.380645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.129821777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">292.052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.528930664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.969543457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.195007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.390899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.089660644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.411682128906</t>
+    <t xml:space="preserve">288.380615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.129791259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">292.052703857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.528869628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.969573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.195068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.390869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.089721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.411651611328</t>
   </si>
   <si>
     <t xml:space="preserve">299.592681884766</t>
   </si>
   <si>
-    <t xml:space="preserve">301.110443115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.370147705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.488830566406</t>
+    <t xml:space="preserve">301.110473632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.984344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.370086669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.48876953125</t>
   </si>
   <si>
     <t xml:space="preserve">303.509552001953</t>
   </si>
   <si>
-    <t xml:space="preserve">305.419036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.950225830078</t>
+    <t xml:space="preserve">305.419067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.9501953125</t>
   </si>
   <si>
     <t xml:space="preserve">307.965026855469</t>
   </si>
   <si>
-    <t xml:space="preserve">314.721618652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.442687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.884765625</t>
+    <t xml:space="preserve">314.721649169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.442749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.884735107422</t>
   </si>
   <si>
     <t xml:space="preserve">329.018280029297</t>
   </si>
   <si>
-    <t xml:space="preserve">329.605865478516</t>
+    <t xml:space="preserve">329.605834960938</t>
   </si>
   <si>
     <t xml:space="preserve">330.976715087891</t>
   </si>
   <si>
-    <t xml:space="preserve">333.326873779297</t>
+    <t xml:space="preserve">333.326812744141</t>
   </si>
   <si>
     <t xml:space="preserve">334.110260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">332.543487548828</t>
+    <t xml:space="preserve">332.543426513672</t>
   </si>
   <si>
     <t xml:space="preserve">331.760070800781</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">341.944000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">340.768890380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">344.685791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.323760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">358.786560058594</t>
+    <t xml:space="preserve">340.768920898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.685821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.32373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">358.786590576172</t>
   </si>
   <si>
     <t xml:space="preserve">375.433380126953</t>
@@ -3725,16 +3725,16 @@
     <t xml:space="preserve">380.133666992188</t>
   </si>
   <si>
-    <t xml:space="preserve">382.679565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385.2255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">385.421417236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">386.204742431641</t>
+    <t xml:space="preserve">382.679626464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385.225555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">385.421447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">386.204803466797</t>
   </si>
   <si>
     <t xml:space="preserve">389.338287353516</t>
@@ -3746,49 +3746,49 @@
     <t xml:space="preserve">389.465972900391</t>
   </si>
   <si>
-    <t xml:space="preserve">393.39404296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.197631835938</t>
+    <t xml:space="preserve">393.393951416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.197570800781</t>
   </si>
   <si>
     <t xml:space="preserve">398.304046630859</t>
   </si>
   <si>
-    <t xml:space="preserve">401.0537109375</t>
+    <t xml:space="preserve">401.053741455078</t>
   </si>
   <si>
     <t xml:space="preserve">402.428497314453</t>
   </si>
   <si>
-    <t xml:space="preserve">388.483978271484</t>
+    <t xml:space="preserve">388.483917236328</t>
   </si>
   <si>
     <t xml:space="preserve">388.091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">387.109161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">391.233612060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">396.143676757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">388.680358886719</t>
+    <t xml:space="preserve">387.109100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">391.233581542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">396.143615722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">388.680297851562</t>
   </si>
   <si>
     <t xml:space="preserve">396.536437988281</t>
   </si>
   <si>
-    <t xml:space="preserve">406.160186767578</t>
+    <t xml:space="preserve">406.16015625</t>
   </si>
   <si>
     <t xml:space="preserve">408.124176025391</t>
   </si>
   <si>
-    <t xml:space="preserve">404.785369873047</t>
+    <t xml:space="preserve">404.785339355469</t>
   </si>
   <si>
     <t xml:space="preserve">405.963745117188</t>
@@ -3797,13 +3797,13 @@
     <t xml:space="preserve">407.731414794922</t>
   </si>
   <si>
-    <t xml:space="preserve">403.999694824219</t>
+    <t xml:space="preserve">403.999755859375</t>
   </si>
   <si>
     <t xml:space="preserve">405.178161621094</t>
   </si>
   <si>
-    <t xml:space="preserve">402.821380615234</t>
+    <t xml:space="preserve">402.8212890625</t>
   </si>
   <si>
     <t xml:space="preserve">407.534973144531</t>
@@ -3818,19 +3818,19 @@
     <t xml:space="preserve">409.4990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">417.551513671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.122711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">421.479522705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">415.980316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">419.7119140625</t>
+    <t xml:space="preserve">417.551544189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.122741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">421.479614257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">415.980285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">419.711944580078</t>
   </si>
   <si>
     <t xml:space="preserve">420.49755859375</t>
@@ -3839,52 +3839,52 @@
     <t xml:space="preserve">405.570983886719</t>
   </si>
   <si>
-    <t xml:space="preserve">403.606994628906</t>
+    <t xml:space="preserve">403.606903076172</t>
   </si>
   <si>
     <t xml:space="preserve">397.518432617188</t>
   </si>
   <si>
-    <t xml:space="preserve">390.448028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">383.377471923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">391.822723388672</t>
+    <t xml:space="preserve">390.447967529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">383.37744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">391.822814941406</t>
   </si>
   <si>
     <t xml:space="preserve">395.947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">394.572418212891</t>
+    <t xml:space="preserve">394.572448730469</t>
   </si>
   <si>
     <t xml:space="preserve">407.338562011719</t>
   </si>
   <si>
-    <t xml:space="preserve">410.284637451172</t>
+    <t xml:space="preserve">410.284606933594</t>
   </si>
   <si>
     <t xml:space="preserve">409.302581787109</t>
   </si>
   <si>
-    <t xml:space="preserve">408.320587158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.142150878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.356536865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.232116699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.767395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">413.819885253906</t>
+    <t xml:space="preserve">408.320617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.142242431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.356567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.232086181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.767364501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">413.819854736328</t>
   </si>
   <si>
     <t xml:space="preserve">404.588958740234</t>
@@ -3893,16 +3893,16 @@
     <t xml:space="preserve">400.464508056641</t>
   </si>
   <si>
-    <t xml:space="preserve">403.410522460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">477.650665283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">474.508239746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">470.187347412109</t>
+    <t xml:space="preserve">403.410552978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">477.650634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">474.508178710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470.187316894531</t>
   </si>
   <si>
     <t xml:space="preserve">474.115386962891</t>
@@ -3917,28 +3917,28 @@
     <t xml:space="preserve">495.110870361328</t>
   </si>
   <si>
-    <t xml:space="preserve">493.634338378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">492.157928466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">496.095184326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.524597167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.048126220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">503.477508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">503.969696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">501.016723632812</t>
+    <t xml:space="preserve">493.634368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">492.157867431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">496.095153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.524566650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.048156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">503.4775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">503.969635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">501.016754150391</t>
   </si>
   <si>
     <t xml:space="preserve">495.60302734375</t>
@@ -3947,25 +3947,25 @@
     <t xml:space="preserve">500.032409667969</t>
   </si>
   <si>
-    <t xml:space="preserve">507.414764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">511.844177246094</t>
+    <t xml:space="preserve">507.414825439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">511.84423828125</t>
   </si>
   <si>
     <t xml:space="preserve">514.797180175781</t>
   </si>
   <si>
-    <t xml:space="preserve">509.383453369141</t>
+    <t xml:space="preserve">509.383422851562</t>
   </si>
   <si>
     <t xml:space="preserve">527.593322753906</t>
   </si>
   <si>
-    <t xml:space="preserve">535.960021972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">547.279663085938</t>
+    <t xml:space="preserve">535.959899902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">547.279602050781</t>
   </si>
   <si>
     <t xml:space="preserve">546.295227050781</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">546.787475585938</t>
   </si>
   <si>
-    <t xml:space="preserve">550.232482910156</t>
+    <t xml:space="preserve">550.232543945312</t>
   </si>
   <si>
     <t xml:space="preserve">539.897216796875</t>
@@ -3986,16 +3986,16 @@
     <t xml:space="preserve">526.116821289062</t>
   </si>
   <si>
-    <t xml:space="preserve">512.336303710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">510.859954833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">489.992431640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">504.461883544922</t>
+    <t xml:space="preserve">512.336364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">510.859893798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">489.992401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504.461853027344</t>
   </si>
   <si>
     <t xml:space="preserve">517.750122070312</t>
@@ -4004,10 +4004,10 @@
     <t xml:space="preserve">532.514831542969</t>
   </si>
   <si>
-    <t xml:space="preserve">554.661865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.442443847656</t>
+    <t xml:space="preserve">554.662048339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.4423828125</t>
   </si>
   <si>
     <t xml:space="preserve">567.9501953125</t>
@@ -4016,31 +4016,31 @@
     <t xml:space="preserve">575.824768066406</t>
   </si>
   <si>
-    <t xml:space="preserve">561.552185058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569.4267578125</t>
+    <t xml:space="preserve">561.552124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569.426635742188</t>
   </si>
   <si>
     <t xml:space="preserve">545.803100585938</t>
   </si>
   <si>
-    <t xml:space="preserve">543.34228515625</t>
+    <t xml:space="preserve">543.342346191406</t>
   </si>
   <si>
     <t xml:space="preserve">540.389404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">549.248168945312</t>
+    <t xml:space="preserve">549.248229980469</t>
   </si>
   <si>
     <t xml:space="preserve">555.646240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">532.022705078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">523.656066894531</t>
+    <t xml:space="preserve">532.022827148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">523.655944824219</t>
   </si>
   <si>
     <t xml:space="preserve">514.304992675781</t>
@@ -4055,58 +4055,58 @@
     <t xml:space="preserve">544.818786621094</t>
   </si>
   <si>
-    <t xml:space="preserve">553.185485839844</t>
+    <t xml:space="preserve">553.185546875</t>
   </si>
   <si>
     <t xml:space="preserve">554.300048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">536.053466796875</t>
+    <t xml:space="preserve">536.053405761719</t>
   </si>
   <si>
     <t xml:space="preserve">532.108276367188</t>
   </si>
   <si>
-    <t xml:space="preserve">536.546569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">542.46435546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.532958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">541.478088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">543.450744628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">533.094604492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">531.121948242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">538.026062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">540.491760253906</t>
+    <t xml:space="preserve">536.546630859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">542.464416503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.532836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">541.478149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">543.45068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">533.094665527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">531.121887207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">538.026123046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">540.491821289062</t>
   </si>
   <si>
     <t xml:space="preserve">532.601440429688</t>
   </si>
   <si>
-    <t xml:space="preserve">537.039794921875</t>
+    <t xml:space="preserve">537.039733886719</t>
   </si>
   <si>
     <t xml:space="preserve">534.080932617188</t>
   </si>
   <si>
-    <t xml:space="preserve">539.012451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">526.190490722656</t>
+    <t xml:space="preserve">539.012329101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">526.1904296875</t>
   </si>
   <si>
     <t xml:space="preserve">531.615112304688</t>
@@ -4121,16 +4121,16 @@
     <t xml:space="preserve">523.231628417969</t>
   </si>
   <si>
-    <t xml:space="preserve">519.779479980469</t>
+    <t xml:space="preserve">519.779541015625</t>
   </si>
   <si>
     <t xml:space="preserve">511.88916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">509.916564941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">511.395965576172</t>
+    <t xml:space="preserve">509.91650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">511.395935058594</t>
   </si>
   <si>
     <t xml:space="preserve">518.793212890625</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">520.765808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">527.669921875</t>
+    <t xml:space="preserve">527.669982910156</t>
   </si>
   <si>
     <t xml:space="preserve">552.820556640625</t>
@@ -4151,16 +4151,16 @@
     <t xml:space="preserve">557.258850097656</t>
   </si>
   <si>
-    <t xml:space="preserve">567.615051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">565.642456054688</t>
+    <t xml:space="preserve">567.615112304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">565.642395019531</t>
   </si>
   <si>
     <t xml:space="preserve">568.108215332031</t>
   </si>
   <si>
-    <t xml:space="preserve">573.532775878906</t>
+    <t xml:space="preserve">573.532836914062</t>
   </si>
   <si>
     <t xml:space="preserve">581.423217773438</t>
@@ -4169,19 +4169,19 @@
     <t xml:space="preserve">583.888916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">575.012329101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">561.697265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">569.094482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.601379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">577.477966308594</t>
+    <t xml:space="preserve">575.012390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">561.697326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">569.094543457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.601257324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">577.47802734375</t>
   </si>
   <si>
     <t xml:space="preserve">572.053405761719</t>
@@ -4190,103 +4190,103 @@
     <t xml:space="preserve">577.97119140625</t>
   </si>
   <si>
-    <t xml:space="preserve">587.341064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">587.834106445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">585.861572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">593.751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">609.039611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">646.02587890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">642.080688476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">668.217529296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">675.614807128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677.094177246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">671.176452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">679.559936523438</t>
+    <t xml:space="preserve">587.341003417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">587.834167480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">585.861633300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">593.752014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">609.03955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">646.025817871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">642.080627441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">668.217590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">675.614868164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">677.09423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">671.176391601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679.559997558594</t>
   </si>
   <si>
     <t xml:space="preserve">695.173034667969</t>
   </si>
   <si>
-    <t xml:space="preserve">698.631530761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">722.841552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">726.300170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">700.113708496094</t>
+    <t xml:space="preserve">698.631469726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722.841491699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">726.300109863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">700.11376953125</t>
   </si>
   <si>
     <t xml:space="preserve">681.338623046875</t>
   </si>
   <si>
-    <t xml:space="preserve">707.030883789062</t>
+    <t xml:space="preserve">707.030944824219</t>
   </si>
   <si>
     <t xml:space="preserve">697.643310546875</t>
   </si>
   <si>
-    <t xml:space="preserve">705.054565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">699.125610351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">688.255798339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">686.279418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">709.995361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">722.347412109375</t>
+    <t xml:space="preserve">705.054504394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">699.125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">688.255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">686.279479980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">709.995300292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">722.347351074219</t>
   </si>
   <si>
     <t xml:space="preserve">710.489501953125</t>
   </si>
   <si>
-    <t xml:space="preserve">711.971740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.232116699219</t>
+    <t xml:space="preserve">711.9716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.232238769531</t>
   </si>
   <si>
     <t xml:space="preserve">660.587219238281</t>
   </si>
   <si>
-    <t xml:space="preserve">678.868286132812</t>
+    <t xml:space="preserve">678.868225097656</t>
   </si>
   <si>
     <t xml:space="preserve">683.315002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">682.326782226562</t>
+    <t xml:space="preserve">682.326843261719</t>
   </si>
   <si>
     <t xml:space="preserve">697.149291992188</t>
@@ -4295,49 +4295,49 @@
     <t xml:space="preserve">704.560485839844</t>
   </si>
   <si>
-    <t xml:space="preserve">704.06640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">706.042724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720.865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">698.829223632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">709.896667480469</t>
+    <t xml:space="preserve">704.066345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706.042785644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720.865295410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">698.829162597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">709.896606445312</t>
   </si>
   <si>
     <t xml:space="preserve">704.165222167969</t>
   </si>
   <si>
-    <t xml:space="preserve">709.204895019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">708.710815429688</t>
+    <t xml:space="preserve">709.204833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">708.710876464844</t>
   </si>
   <si>
     <t xml:space="preserve">689.738098144531</t>
   </si>
   <si>
-    <t xml:space="preserve">701.991271972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">702.090087890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">706.141479492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">695.469421386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">694.283630371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677.188354492188</t>
+    <t xml:space="preserve">701.991333007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">702.090148925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">706.1416015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">695.469360351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">694.283569335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">677.188415527344</t>
   </si>
   <si>
     <t xml:space="preserve">676.6943359375</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">667.603088378906</t>
   </si>
   <si>
-    <t xml:space="preserve">680.745788574219</t>
+    <t xml:space="preserve">680.745849609375</t>
   </si>
   <si>
     <t xml:space="preserve">674.619201660156</t>
@@ -4361,40 +4361,40 @@
     <t xml:space="preserve">711.576416015625</t>
   </si>
   <si>
-    <t xml:space="preserve">674.520263671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">688.848754882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">709.106079101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">712.367065429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.133422851562</t>
+    <t xml:space="preserve">674.520385742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">688.848693847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">709.10595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">712.367004394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.13330078125</t>
   </si>
   <si>
     <t xml:space="preserve">690.528564453125</t>
   </si>
   <si>
-    <t xml:space="preserve">710.328674316406</t>
+    <t xml:space="preserve">710.328735351562</t>
   </si>
   <si>
     <t xml:space="preserve">705.57666015625</t>
   </si>
   <si>
-    <t xml:space="preserve">701.517700195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">712.407653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">732.603820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">729.336730957031</t>
+    <t xml:space="preserve">701.517639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">712.407592773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">732.603759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">729.336791992188</t>
   </si>
   <si>
     <t xml:space="preserve">744.186889648438</t>
@@ -4403,52 +4403,52 @@
     <t xml:space="preserve">737.2568359375</t>
   </si>
   <si>
-    <t xml:space="preserve">739.434814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">733.593811035156</t>
+    <t xml:space="preserve">739.434936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">733.59375</t>
   </si>
   <si>
     <t xml:space="preserve">744.087768554688</t>
   </si>
   <si>
-    <t xml:space="preserve">744.681823730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">746.661865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.640869140625</t>
+    <t xml:space="preserve">744.681884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">746.661804199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.640930175781</t>
   </si>
   <si>
     <t xml:space="preserve">754.185852050781</t>
   </si>
   <si>
-    <t xml:space="preserve">757.75</t>
+    <t xml:space="preserve">757.749938964844</t>
   </si>
   <si>
     <t xml:space="preserve">762.204956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">778.243041992188</t>
+    <t xml:space="preserve">778.242980957031</t>
   </si>
   <si>
     <t xml:space="preserve">791.410095214844</t>
   </si>
   <si>
-    <t xml:space="preserve">793.588134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">787.549072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">807.250244140625</t>
+    <t xml:space="preserve">793.588073730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">787.549011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">807.250183105469</t>
   </si>
   <si>
     <t xml:space="preserve">815.764221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">815.962280273438</t>
+    <t xml:space="preserve">815.962219238281</t>
   </si>
   <si>
     <t xml:space="preserve">825.565307617188</t>
@@ -4460,19 +4460,19 @@
     <t xml:space="preserve">833.386291503906</t>
   </si>
   <si>
-    <t xml:space="preserve">819.42724609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">828.337280273438</t>
+    <t xml:space="preserve">819.427307128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">828.337219238281</t>
   </si>
   <si>
     <t xml:space="preserve">838.732360839844</t>
   </si>
   <si>
-    <t xml:space="preserve">835.267333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">833.980346679688</t>
+    <t xml:space="preserve">835.267272949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">833.980285644531</t>
   </si>
   <si>
     <t xml:space="preserve">843.385437011719</t>
@@ -4487,22 +4487,22 @@
     <t xml:space="preserve">818.932189941406</t>
   </si>
   <si>
-    <t xml:space="preserve">825.664245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">834.970336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">839.722351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">847.543395996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">861.403442382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">845.563415527344</t>
+    <t xml:space="preserve">825.664367675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">834.970397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">839.722412109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">847.543273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">861.403381347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">845.563354492188</t>
   </si>
   <si>
     <t xml:space="preserve">859.720520019531</t>
@@ -4511,40 +4511,40 @@
     <t xml:space="preserve">863.977478027344</t>
   </si>
   <si>
-    <t xml:space="preserve">863.482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">830.020385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">773.391967773438</t>
+    <t xml:space="preserve">863.482543945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">830.020324707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">773.39208984375</t>
   </si>
   <si>
     <t xml:space="preserve">783.193054199219</t>
   </si>
   <si>
-    <t xml:space="preserve">784.282043457031</t>
+    <t xml:space="preserve">784.282104492188</t>
   </si>
   <si>
     <t xml:space="preserve">807.646118164062</t>
   </si>
   <si>
-    <t xml:space="preserve">782.401000976562</t>
+    <t xml:space="preserve">782.401062011719</t>
   </si>
   <si>
     <t xml:space="preserve">760.224914550781</t>
   </si>
   <si>
-    <t xml:space="preserve">743.790893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">737.751892089844</t>
+    <t xml:space="preserve">743.790832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">737.751831054688</t>
   </si>
   <si>
     <t xml:space="preserve">726.465759277344</t>
   </si>
   <si>
-    <t xml:space="preserve">735.078735351562</t>
+    <t xml:space="preserve">735.078857421875</t>
   </si>
   <si>
     <t xml:space="preserve">761.016906738281</t>
@@ -4553,13 +4553,13 @@
     <t xml:space="preserve">720.030700683594</t>
   </si>
   <si>
-    <t xml:space="preserve">699.04248046875</t>
+    <t xml:space="preserve">699.042663574219</t>
   </si>
   <si>
     <t xml:space="preserve">720.32763671875</t>
   </si>
   <si>
-    <t xml:space="preserve">702.804626464844</t>
+    <t xml:space="preserve">702.8046875</t>
   </si>
   <si>
     <t xml:space="preserve">755.967895507812</t>
@@ -4568,25 +4568,25 @@
     <t xml:space="preserve">812.794189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">806.359252929688</t>
+    <t xml:space="preserve">806.359191894531</t>
   </si>
   <si>
     <t xml:space="preserve">817.744262695312</t>
   </si>
   <si>
-    <t xml:space="preserve">838.138305664062</t>
+    <t xml:space="preserve">838.138366699219</t>
   </si>
   <si>
     <t xml:space="preserve">836.353576660156</t>
   </si>
   <si>
-    <t xml:space="preserve">824.752746582031</t>
+    <t xml:space="preserve">824.752685546875</t>
   </si>
   <si>
     <t xml:space="preserve">846.169738769531</t>
   </si>
   <si>
-    <t xml:space="preserve">841.807006835938</t>
+    <t xml:space="preserve">841.806945800781</t>
   </si>
   <si>
     <t xml:space="preserve">855.886657714844</t>
@@ -4595,34 +4595,34 @@
     <t xml:space="preserve">840.220520019531</t>
   </si>
   <si>
-    <t xml:space="preserve">845.376403808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">851.028198242188</t>
+    <t xml:space="preserve">845.37646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">851.028137207031</t>
   </si>
   <si>
     <t xml:space="preserve">845.673950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">850.631591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">846.764587402344</t>
+    <t xml:space="preserve">850.631652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">846.7646484375</t>
   </si>
   <si>
     <t xml:space="preserve">858.563781738281</t>
   </si>
   <si>
-    <t xml:space="preserve">867.586730957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">852.218017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">812.160217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">806.012817382812</t>
+    <t xml:space="preserve">867.586669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">852.218078613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812.160278320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">806.012878417969</t>
   </si>
   <si>
     <t xml:space="preserve">807.995910644531</t>
@@ -4634,25 +4634,25 @@
     <t xml:space="preserve">812.953552246094</t>
   </si>
   <si>
-    <t xml:space="preserve">831.197570800781</t>
+    <t xml:space="preserve">831.197631835938</t>
   </si>
   <si>
     <t xml:space="preserve">835.064636230469</t>
   </si>
   <si>
-    <t xml:space="preserve">824.05859375</t>
+    <t xml:space="preserve">824.058532714844</t>
   </si>
   <si>
     <t xml:space="preserve">812.556945800781</t>
   </si>
   <si>
-    <t xml:space="preserve">808.987487792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">805.517028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">825.5458984375</t>
+    <t xml:space="preserve">808.987365722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">805.517150878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">825.545959472656</t>
   </si>
   <si>
     <t xml:space="preserve">816.919677734375</t>
@@ -4664,22 +4664,22 @@
     <t xml:space="preserve">821.579772949219</t>
   </si>
   <si>
-    <t xml:space="preserve">813.845947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">779.7373046875</t>
+    <t xml:space="preserve">813.845886230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">779.737426757812</t>
   </si>
   <si>
     <t xml:space="preserve">779.935607910156</t>
   </si>
   <si>
-    <t xml:space="preserve">793.519592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">800.063659667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">798.675476074219</t>
+    <t xml:space="preserve">793.51953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800.063720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">798.675537109375</t>
   </si>
   <si>
     <t xml:space="preserve">794.70947265625</t>
@@ -4688,49 +4688,49 @@
     <t xml:space="preserve">816.32470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">826.636657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">829.313720703125</t>
+    <t xml:space="preserve">826.636596679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">829.313781738281</t>
   </si>
   <si>
     <t xml:space="preserve">836.948486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">829.809448242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">832.982360839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">841.410400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">838.435791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">830.0078125</t>
+    <t xml:space="preserve">829.8095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">832.982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">841.410339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">838.435729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">830.007751464844</t>
   </si>
   <si>
     <t xml:space="preserve">833.279846191406</t>
   </si>
   <si>
-    <t xml:space="preserve">823.662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">819.200134277344</t>
+    <t xml:space="preserve">823.662048339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.2001953125</t>
   </si>
   <si>
     <t xml:space="preserve">822.868835449219</t>
   </si>
   <si>
-    <t xml:space="preserve">819.894287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">827.132446289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761.790710449219</t>
+    <t xml:space="preserve">819.894226074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">827.132385253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761.790649414062</t>
   </si>
   <si>
     <t xml:space="preserve">778.646667480469</t>
@@ -4745,73 +4745,73 @@
     <t xml:space="preserve">726.492309570312</t>
   </si>
   <si>
-    <t xml:space="preserve">716.9736328125</t>
+    <t xml:space="preserve">716.973693847656</t>
   </si>
   <si>
     <t xml:space="preserve">725.401611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">766.549926757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">778.250061035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761.691528320312</t>
+    <t xml:space="preserve">766.549987792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">778.250122070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761.691589355469</t>
   </si>
   <si>
     <t xml:space="preserve">771.309387207031</t>
   </si>
   <si>
-    <t xml:space="preserve">750.090759277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">713.241638183594</t>
+    <t xml:space="preserve">750.090637207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">713.24169921875</t>
   </si>
   <si>
     <t xml:space="preserve">680.464904785156</t>
   </si>
   <si>
-    <t xml:space="preserve">679.670349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">703.706604003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.295776367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">715.228149414062</t>
+    <t xml:space="preserve">679.67041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">703.706665039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.295837402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">715.228088378906</t>
   </si>
   <si>
     <t xml:space="preserve">760.916931152344</t>
   </si>
   <si>
-    <t xml:space="preserve">744.42919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">749.891967773438</t>
+    <t xml:space="preserve">744.429260253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">749.892028808594</t>
   </si>
   <si>
     <t xml:space="preserve">756.447326660156</t>
   </si>
   <si>
-    <t xml:space="preserve">766.776977539062</t>
+    <t xml:space="preserve">766.777038574219</t>
   </si>
   <si>
     <t xml:space="preserve">790.416015625</t>
   </si>
   <si>
-    <t xml:space="preserve">774.62353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">788.429504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760.519714355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">756.348083496094</t>
+    <t xml:space="preserve">774.623596191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">788.429565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760.519653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">756.348022460938</t>
   </si>
   <si>
     <t xml:space="preserve">748.104248046875</t>
@@ -4820,13 +4820,13 @@
     <t xml:space="preserve">747.408935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">740.952941894531</t>
+    <t xml:space="preserve">740.952880859375</t>
   </si>
   <si>
     <t xml:space="preserve">744.329956054688</t>
   </si>
   <si>
-    <t xml:space="preserve">744.925903320312</t>
+    <t xml:space="preserve">744.925842285156</t>
   </si>
   <si>
     <t xml:space="preserve">735.788146972656</t>
@@ -4835,31 +4835,31 @@
     <t xml:space="preserve">725.756469726562</t>
   </si>
   <si>
-    <t xml:space="preserve">759.02978515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">745.521728515625</t>
+    <t xml:space="preserve">759.029846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">745.521789550781</t>
   </si>
   <si>
     <t xml:space="preserve">748.700134277344</t>
   </si>
   <si>
-    <t xml:space="preserve">738.569152832031</t>
+    <t xml:space="preserve">738.569213867188</t>
   </si>
   <si>
     <t xml:space="preserve">759.327758789062</t>
   </si>
   <si>
-    <t xml:space="preserve">753.070373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">739.8603515625</t>
+    <t xml:space="preserve">753.070434570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">739.860412597656</t>
   </si>
   <si>
     <t xml:space="preserve">740.158386230469</t>
   </si>
   <si>
-    <t xml:space="preserve">758.731811523438</t>
+    <t xml:space="preserve">758.731872558594</t>
   </si>
   <si>
     <t xml:space="preserve">758.433837890625</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">769.359436035156</t>
   </si>
   <si>
-    <t xml:space="preserve">718.505798339844</t>
+    <t xml:space="preserve">718.505859375</t>
   </si>
   <si>
     <t xml:space="preserve">720.1943359375</t>
@@ -4880,13 +4880,13 @@
     <t xml:space="preserve">734.993530273438</t>
   </si>
   <si>
-    <t xml:space="preserve">714.731567382812</t>
+    <t xml:space="preserve">714.731506347656</t>
   </si>
   <si>
     <t xml:space="preserve">693.674987792969</t>
   </si>
   <si>
-    <t xml:space="preserve">697.548522949219</t>
+    <t xml:space="preserve">697.548583984375</t>
   </si>
   <si>
     <t xml:space="preserve">724.663879394531</t>
@@ -4898,10 +4898,10 @@
     <t xml:space="preserve">741.846862792969</t>
   </si>
   <si>
-    <t xml:space="preserve">757.937133789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">766.18115234375</t>
+    <t xml:space="preserve">757.937255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">766.181091308594</t>
   </si>
   <si>
     <t xml:space="preserve">768.068237304688</t>
@@ -4910,13 +4910,13 @@
     <t xml:space="preserve">771.445251464844</t>
   </si>
   <si>
-    <t xml:space="preserve">784.555908203125</t>
+    <t xml:space="preserve">784.555969238281</t>
   </si>
   <si>
     <t xml:space="preserve">785.052551269531</t>
   </si>
   <si>
-    <t xml:space="preserve">775.914794921875</t>
+    <t xml:space="preserve">775.914855957031</t>
   </si>
   <si>
     <t xml:space="preserve">796.1767578125</t>
@@ -4928,7 +4928,7 @@
     <t xml:space="preserve">843.752685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">834.813598632812</t>
+    <t xml:space="preserve">834.813659667969</t>
   </si>
   <si>
     <t xml:space="preserve">833.025756835938</t>
@@ -4958,13 +4958,13 @@
     <t xml:space="preserve">849.839111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">836.903930664062</t>
+    <t xml:space="preserve">836.903991699219</t>
   </si>
   <si>
     <t xml:space="preserve">852.426208496094</t>
   </si>
   <si>
-    <t xml:space="preserve">863.96826171875</t>
+    <t xml:space="preserve">863.968322753906</t>
   </si>
   <si>
     <t xml:space="preserve">882.276489257812</t>
@@ -4982,13 +4982,13 @@
     <t xml:space="preserve">846.456115722656</t>
   </si>
   <si>
-    <t xml:space="preserve">849.043151855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">797.700561523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">774.914733886719</t>
+    <t xml:space="preserve">849.043090820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">797.700500488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">774.914794921875</t>
   </si>
   <si>
     <t xml:space="preserve">745.064392089844</t>
@@ -5000,10 +5000,10 @@
     <t xml:space="preserve">734.517333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">740.785949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">749.143981933594</t>
+    <t xml:space="preserve">740.785888671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">749.14404296875</t>
   </si>
   <si>
     <t xml:space="preserve">743.969909667969</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">774.21826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">787.053955078125</t>
+    <t xml:space="preserve">787.053894042969</t>
   </si>
   <si>
     <t xml:space="preserve">770.63623046875</t>
@@ -5036,13 +5036,13 @@
     <t xml:space="preserve">753.322998046875</t>
   </si>
   <si>
-    <t xml:space="preserve">742.178894042969</t>
+    <t xml:space="preserve">742.178955078125</t>
   </si>
   <si>
     <t xml:space="preserve">718.497619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">679.891235351562</t>
+    <t xml:space="preserve">679.891174316406</t>
   </si>
   <si>
     <t xml:space="preserve">650.836853027344</t>
@@ -5054,7 +5054,7 @@
     <t xml:space="preserve">625.961608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">631.633117675781</t>
+    <t xml:space="preserve">631.633178710938</t>
   </si>
   <si>
     <t xml:space="preserve">630.837158203125</t>
@@ -5063,7 +5063,7 @@
     <t xml:space="preserve">655.612976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">669.443603515625</t>
+    <t xml:space="preserve">669.443542480469</t>
   </si>
   <si>
     <t xml:space="preserve">654.418884277344</t>
@@ -5075,7 +5075,7 @@
     <t xml:space="preserve">711.134582519531</t>
   </si>
   <si>
-    <t xml:space="preserve">720.089660644531</t>
+    <t xml:space="preserve">720.089721679688</t>
   </si>
   <si>
     <t xml:space="preserve">743.074401855469</t>
@@ -5084,7 +5084,7 @@
     <t xml:space="preserve">758.397583007812</t>
   </si>
   <si>
-    <t xml:space="preserve">760.188598632812</t>
+    <t xml:space="preserve">760.188659667969</t>
   </si>
   <si>
     <t xml:space="preserve">774.516784667969</t>
@@ -5093,10 +5093,10 @@
     <t xml:space="preserve">784.765441894531</t>
   </si>
   <si>
-    <t xml:space="preserve">721.184143066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">718.796142578125</t>
+    <t xml:space="preserve">721.184204101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">718.796203613281</t>
   </si>
   <si>
     <t xml:space="preserve">697.204406738281</t>
@@ -5105,16 +5105,16 @@
     <t xml:space="preserve">680.289245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">657.901489257812</t>
+    <t xml:space="preserve">657.901428222656</t>
   </si>
   <si>
     <t xml:space="preserve">665.563110351562</t>
   </si>
   <si>
-    <t xml:space="preserve">672.528137207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">668.747009277344</t>
+    <t xml:space="preserve">672.528198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">668.7470703125</t>
   </si>
   <si>
     <t xml:space="preserve">643.274780273438</t>
@@ -5460,6 +5460,9 @@
   </si>
   <si>
     <t xml:space="preserve">767.599975585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">788.099975585938</t>
   </si>
 </sst>
 </file>
@@ -70876,7 +70879,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45964.6968287037</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>3580</v>
@@ -70897,6 +70900,32 @@
         <v>1815</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45965.6916319444</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>5399</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>795.5</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>766.099975585938</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>771</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>788.099975585938</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1816</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/LLY.DE.xlsx
+++ b/data/LLY.DE.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="1817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="1818">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">38.3028755187988</t>
+    <t xml:space="preserve">38.3028793334961</t>
   </si>
   <si>
     <t xml:space="preserve">LLY.DE</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7578239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.6800575256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1174926757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.554931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.4298477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.9924240112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.2426071166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.8051605224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3677101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.9302787780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0229949951172</t>
+    <t xml:space="preserve">38.7578277587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.6800651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1175231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5549621582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.4298286437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.9924011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.2425994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.8051490783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3677177429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.9302558898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0229797363281</t>
   </si>
   <si>
     <t xml:space="preserve">57.594295501709</t>
@@ -83,106 +83,106 @@
     <t xml:space="preserve">58.1717224121094</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8681297302246</t>
+    <t xml:space="preserve">56.8681449890137</t>
   </si>
   <si>
     <t xml:space="preserve">54.7071495056152</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5908050537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.359806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.015983581543</t>
+    <t xml:space="preserve">55.5907936096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.330940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3598098754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0159912109375</t>
   </si>
   <si>
     <t xml:space="preserve">54.2212677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8040084838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3226623535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4815864562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4021224975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.028995513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.532283782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.596363067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4662132263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2719612121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5721588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1218643188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9276313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9717636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6405143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2167015075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5787200927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.075439453125</t>
+    <t xml:space="preserve">54.8040046691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3226509094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4815826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2785186767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4021186828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.0290069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.5322952270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5963706970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4661979675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2719573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5721702575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1218566894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9276161193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.971752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6405258178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2166976928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5787048339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0754356384277</t>
   </si>
   <si>
     <t xml:space="preserve">56.8082695007324</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0312919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4286003112793</t>
+    <t xml:space="preserve">56.0312843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4286117553711</t>
   </si>
   <si>
     <t xml:space="preserve">56.2961654663086</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8900184631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4861450195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2323684692383</t>
+    <t xml:space="preserve">55.890022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4861488342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2323837280273</t>
   </si>
   <si>
     <t xml:space="preserve">53.9034042358398</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1130294799805</t>
+    <t xml:space="preserve">55.1130256652832</t>
   </si>
   <si>
     <t xml:space="preserve">55.3690872192383</t>
@@ -191,73 +191,73 @@
     <t xml:space="preserve">55.6251335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9230575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8811874389648</t>
+    <t xml:space="preserve">56.9230461120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8811988830566</t>
   </si>
   <si>
     <t xml:space="preserve">55.5191879272461</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7641296386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1019401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6935005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.5057945251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1614456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9936981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5433921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9495315551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.479305267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9119529724121</t>
+    <t xml:space="preserve">56.7641372680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.101936340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6934928894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.505802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.161449432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9936943054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5433959960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.949535369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.479320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9119491577148</t>
   </si>
   <si>
     <t xml:space="preserve">58.5829849243164</t>
   </si>
   <si>
-    <t xml:space="preserve">59.9162101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3665199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1899299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3622436523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6559104919434</t>
+    <t xml:space="preserve">59.9162178039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.366512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1899223327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.362247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6559028625488</t>
   </si>
   <si>
     <t xml:space="preserve">57.6294059753418</t>
   </si>
   <si>
-    <t xml:space="preserve">58.6271286010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.7330932617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.5166244506836</t>
+    <t xml:space="preserve">58.6271324157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.7330856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.5166168212891</t>
   </si>
   <si>
     <t xml:space="preserve">61.0552062988281</t>
@@ -266,154 +266,154 @@
     <t xml:space="preserve">61.5231742858887</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4452857971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7212181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2998123168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8872833251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5134315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2433433532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.2077369689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.394645690918</t>
+    <t xml:space="preserve">61.4452743530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7212219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2997970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8872871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5134391784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2433280944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.2077484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.3946418762207</t>
   </si>
   <si>
     <t xml:space="preserve">63.9376335144043</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4094085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.1571044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.5696105957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.6586303710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.2104949951172</t>
+    <t xml:space="preserve">64.4093856811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.1570892333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.5696258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.6586227416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.2105026245117</t>
   </si>
   <si>
     <t xml:space="preserve">65.2550201416016</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7979736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1006164550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.6911773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4967269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7281875610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.8335952758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9581985473633</t>
+    <t xml:space="preserve">65.7979888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1006393432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.6911926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4967575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.7281646728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8335876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9582138061523</t>
   </si>
   <si>
     <t xml:space="preserve">65.1615676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">65.3039703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5220642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3320541381836</t>
+    <t xml:space="preserve">65.3039627075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5220489501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3320693969727</t>
   </si>
   <si>
     <t xml:space="preserve">66.2608489990234</t>
   </si>
   <si>
-    <t xml:space="preserve">65.8202514648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.2564010620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5189819335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.7860260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3988189697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3557205200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1212310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1657180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.1568450927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6018753051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3971328735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5960159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.1448822021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6193923950195</t>
+    <t xml:space="preserve">65.8202438354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.2564239501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5190048217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.786018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3988265991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3556823730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.121208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1657257080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.1568374633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6018981933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3971557617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5960464477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.1448745727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6194000244141</t>
   </si>
   <si>
     <t xml:space="preserve">72.5273284912109</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6221923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5153579711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.9306488037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.6961898803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.2124633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.8355407714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.4733657836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.9362335205078</t>
+    <t xml:space="preserve">73.6221694946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5153656005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.9306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.6961669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.2124557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.8355255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.4733734130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.9362258911133</t>
   </si>
   <si>
     <t xml:space="preserve">78.5623779296875</t>
@@ -422,28 +422,28 @@
     <t xml:space="preserve">78.7136917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">79.8352584838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.8441390991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8048553466797</t>
+    <t xml:space="preserve">79.8352661132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.8441543579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.804801940918</t>
   </si>
   <si>
     <t xml:space="preserve">81.4318542480469</t>
   </si>
   <si>
-    <t xml:space="preserve">81.9513854980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.5694351196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.784423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.4587249755859</t>
+    <t xml:space="preserve">81.9513549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.5694427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.7844390869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.458740234375</t>
   </si>
   <si>
     <t xml:space="preserve">81.3691558837891</t>
@@ -452,28 +452,28 @@
     <t xml:space="preserve">80.9033584594727</t>
   </si>
   <si>
-    <t xml:space="preserve">80.6883926391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.6346206665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.5808944702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.9839935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2168731689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0914993286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.2527084350586</t>
+    <t xml:space="preserve">80.6884002685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.634635925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.5809173583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.9839782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8496170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2168579101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0914688110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.2527008056641</t>
   </si>
   <si>
     <t xml:space="preserve">80.2853088378906</t>
@@ -482,115 +482,115 @@
     <t xml:space="preserve">80.3211288452148</t>
   </si>
   <si>
-    <t xml:space="preserve">82.4888458251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8618240356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.7812042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.3960266113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.6109848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9782638549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.3569717407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.181037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.607780456543</t>
+    <t xml:space="preserve">82.4888076782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.86181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.7812194824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.3960189819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.6110153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9782562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.3569488525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1810607910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.6077728271484</t>
   </si>
   <si>
     <t xml:space="preserve">81.0735549926758</t>
   </si>
   <si>
-    <t xml:space="preserve">82.2379989624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1158599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.2950134277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.2810668945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2247848510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5057067871094</t>
+    <t xml:space="preserve">82.2380142211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.115852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.2949905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.2810592651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2248001098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5056991577148</t>
   </si>
   <si>
     <t xml:space="preserve">89.7980728149414</t>
   </si>
   <si>
-    <t xml:space="preserve">89.1531448364258</t>
+    <t xml:space="preserve">89.1531372070312</t>
   </si>
   <si>
     <t xml:space="preserve">85.2477188110352</t>
   </si>
   <si>
-    <t xml:space="preserve">85.4537200927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8478469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3014526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.895881652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3201141357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9976348876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7378387451172</t>
+    <t xml:space="preserve">85.453727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8478622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3014602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8958587646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3200988769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9976425170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7378845214844</t>
   </si>
   <si>
     <t xml:space="preserve">85.3552017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7435989379883</t>
+    <t xml:space="preserve">86.7435913085938</t>
   </si>
   <si>
     <t xml:space="preserve">85.1402206420898</t>
   </si>
   <si>
-    <t xml:space="preserve">83.2681198120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2029190063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0660629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8177490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6981048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.1287689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.4472579956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9725036621094</t>
+    <t xml:space="preserve">83.2681350708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2029342651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0660705566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.817756652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6980667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1287536621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.4472808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9725189208984</t>
   </si>
   <si>
     <t xml:space="preserve">86.2061614990234</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">90.2369918823242</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3591766357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.9741516113281</t>
+    <t xml:space="preserve">89.3591690063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.9741592407227</t>
   </si>
   <si>
     <t xml:space="preserve">87.7129211425781</t>
@@ -614,31 +614,31 @@
     <t xml:space="preserve">89.532585144043</t>
   </si>
   <si>
-    <t xml:space="preserve">90.5685195922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9740676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3705139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1991882324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.8839721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4063873291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2171249389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7665100097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8475112915039</t>
+    <t xml:space="preserve">90.5685119628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9740753173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3705062866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1991806030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8839950561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.406364440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2171020507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7665176391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8475189208984</t>
   </si>
   <si>
     <t xml:space="preserve">94.0456848144531</t>
@@ -650,142 +650,142 @@
     <t xml:space="preserve">89.6046447753906</t>
   </si>
   <si>
-    <t xml:space="preserve">88.3885269165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3161849975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7487716674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8930740356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.8933334350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8931732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0644226074219</t>
+    <t xml:space="preserve">88.3885345458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3162155151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7487869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8930816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.8933715820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8931579589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0644073486328</t>
   </si>
   <si>
     <t xml:space="preserve">85.2627716064453</t>
   </si>
   <si>
-    <t xml:space="preserve">86.7760620117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.5056610107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3252868652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0191345214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.1812591552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6315765380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6135559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4513092041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8747711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6676254272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9919815063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.7217407226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3521499633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3700714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6675262451172</t>
+    <t xml:space="preserve">86.7760543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.5056304931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3253021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0191116333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.1812515258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6315841674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6135482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4513397216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8747940063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6676330566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9919967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.7217559814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3521423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3700866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6675186157227</t>
   </si>
   <si>
     <t xml:space="preserve">92.5863571166992</t>
   </si>
   <si>
-    <t xml:space="preserve">92.424201965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0998229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6674041748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6586074829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.0820693969727</t>
+    <t xml:space="preserve">92.4242095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0998306274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6674346923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6585845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0820541381836</t>
   </si>
   <si>
     <t xml:space="preserve">91.7666091918945</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5051956176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4150009155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7394332885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.6851654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.099739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4961624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.604362487793</t>
+    <t xml:space="preserve">93.5052108764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4150314331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7394027709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.685188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0997543334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4961929321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6043701171875</t>
   </si>
   <si>
     <t xml:space="preserve">93.9645919799805</t>
   </si>
   <si>
-    <t xml:space="preserve">94.3969879150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1718139648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.3154449462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6569595336914</t>
+    <t xml:space="preserve">94.3969802856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1718063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.3154983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6569519042969</t>
   </si>
   <si>
     <t xml:space="preserve">99.0890960693359</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6750946044922</t>
+    <t xml:space="preserve">97.6751022338867</t>
   </si>
   <si>
     <t xml:space="preserve">97.7385482788086</t>
   </si>
   <si>
-    <t xml:space="preserve">98.237060546875</t>
+    <t xml:space="preserve">98.2370910644531</t>
   </si>
   <si>
     <t xml:space="preserve">99.0437698364258</t>
@@ -794,100 +794,100 @@
     <t xml:space="preserve">99.2522506713867</t>
   </si>
   <si>
-    <t xml:space="preserve">99.3247680664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6963806152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.52123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.518280029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.47590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.189041137695</t>
+    <t xml:space="preserve">99.3247756958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6963729858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.52124786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.51830291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.475914001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.189025878906</t>
   </si>
   <si>
     <t xml:space="preserve">101.318878173828</t>
   </si>
   <si>
-    <t xml:space="preserve">102.234344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.45777130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9078216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4969787597656</t>
+    <t xml:space="preserve">102.234352111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.457763671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9078063964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4969711303711</t>
   </si>
   <si>
     <t xml:space="preserve">99.1616134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">99.5966949462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.865676879883</t>
+    <t xml:space="preserve">99.5966873168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.865661621094</t>
   </si>
   <si>
     <t xml:space="preserve">102.034950256348</t>
   </si>
   <si>
-    <t xml:space="preserve">102.5244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.823524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.1015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.588066101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.445983886719</t>
+    <t xml:space="preserve">102.524406433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.823501586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.101554870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.588073730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.446022033691</t>
   </si>
   <si>
     <t xml:space="preserve">104.862953186035</t>
   </si>
   <si>
-    <t xml:space="preserve">104.300979614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.27082824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.352416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.494270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.346069335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.207168579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.880844116211</t>
+    <t xml:space="preserve">104.300971984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270820617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.352424621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.494262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.346054077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.207153320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.880836486816</t>
   </si>
   <si>
     <t xml:space="preserve">102.787261962891</t>
   </si>
   <si>
-    <t xml:space="preserve">100.068023681641</t>
+    <t xml:space="preserve">100.068016052246</t>
   </si>
   <si>
     <t xml:space="preserve">99.0165710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">93.8862609863281</t>
+    <t xml:space="preserve">93.8862915039062</t>
   </si>
   <si>
     <t xml:space="preserve">92.4722671508789</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">94.7020492553711</t>
   </si>
   <si>
-    <t xml:space="preserve">95.7716217041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9347686767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.7867813110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0587387084961</t>
+    <t xml:space="preserve">95.7716445922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9347763061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.7868041992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.058723449707</t>
   </si>
   <si>
     <t xml:space="preserve">94.5751495361328</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">94.9739837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">93.9044189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7775192260742</t>
+    <t xml:space="preserve">93.9044036865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7775268554688</t>
   </si>
   <si>
     <t xml:space="preserve">94.049430847168</t>
@@ -926,46 +926,46 @@
     <t xml:space="preserve">93.0342407226562</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3816452026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4360122680664</t>
+    <t xml:space="preserve">92.3816223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4360275268555</t>
   </si>
   <si>
     <t xml:space="preserve">93.1430206298828</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3061676025391</t>
+    <t xml:space="preserve">93.3061828613281</t>
   </si>
   <si>
     <t xml:space="preserve">95.7552337646484</t>
   </si>
   <si>
-    <t xml:space="preserve">94.6242141723633</t>
+    <t xml:space="preserve">94.6242065429688</t>
   </si>
   <si>
     <t xml:space="preserve">95.882942199707</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4816055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.3903884887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.0802612304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.1350173950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4086380004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2228851318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9376831054688</t>
+    <t xml:space="preserve">95.4816207885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.390380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0802917480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.135009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4086303710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2228622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9376602172852</t>
   </si>
   <si>
     <t xml:space="preserve">94.9890441894531</t>
@@ -974,151 +974,151 @@
     <t xml:space="preserve">95.5728149414062</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6324081420898</t>
+    <t xml:space="preserve">91.6324462890625</t>
   </si>
   <si>
     <t xml:space="preserve">92.5627822875977</t>
   </si>
   <si>
-    <t xml:space="preserve">93.0918502807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5834655761719</t>
+    <t xml:space="preserve">93.0918273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5834579467773</t>
   </si>
   <si>
     <t xml:space="preserve">91.2128372192383</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7999572753906</t>
+    <t xml:space="preserve">92.7999496459961</t>
   </si>
   <si>
     <t xml:space="preserve">93.4201965332031</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4931564331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9094009399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6357498168945</t>
+    <t xml:space="preserve">93.4931793212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9094161987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6357650756836</t>
   </si>
   <si>
     <t xml:space="preserve">93.3107452392578</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2608795166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8720245361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3098373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3405609130859</t>
+    <t xml:space="preserve">89.260871887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8720169067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3098449707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3405227661133</t>
   </si>
   <si>
     <t xml:space="preserve">92.2709197998047</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3621444702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7567825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1249847412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3885803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.652214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.564323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4764633178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.0203704833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5004959106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3818969726562</t>
+    <t xml:space="preserve">92.3621063232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7567749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1249694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3885879516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6521987915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5643310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4764404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.020378112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5005035400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3819046020508</t>
   </si>
   <si>
     <t xml:space="preserve">86.5245208740234</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9349746704102</t>
+    <t xml:space="preserve">86.9349594116211</t>
   </si>
   <si>
     <t xml:space="preserve">87.9474182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3065032958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.370361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.9507522583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2244110107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1182708740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7750091552734</t>
+    <t xml:space="preserve">89.3064956665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3703308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.9507675170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2243957519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.118293762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.775016784668</t>
   </si>
   <si>
     <t xml:space="preserve">91.3040542602539</t>
   </si>
   <si>
-    <t xml:space="preserve">89.9176330566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.546989440918</t>
+    <t xml:space="preserve">89.9176177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5469741821289</t>
   </si>
   <si>
     <t xml:space="preserve">89.4980545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7452163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7418746948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4317626953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0702590942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4236755371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4407806396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7804565429688</t>
+    <t xml:space="preserve">92.7452239990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7418899536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4317474365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0702362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4236679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.440788269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7804794311523</t>
   </si>
   <si>
     <t xml:space="preserve">92.7908630371094</t>
   </si>
   <si>
-    <t xml:space="preserve">93.0478820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.074836730957</t>
+    <t xml:space="preserve">93.0479202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.074821472168</t>
   </si>
   <si>
     <t xml:space="preserve">91.4230575561523</t>
@@ -1127,61 +1127,61 @@
     <t xml:space="preserve">91.9095993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">92.7541427612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8190155029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6084747314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.810432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2878112792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0197601318359</t>
+    <t xml:space="preserve">92.754150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8190307617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6084899902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8104400634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2878341674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0197448730469</t>
   </si>
   <si>
     <t xml:space="preserve">90.7712783813477</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6990661621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9193878173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0381011962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6800842285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7443542480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9928359985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9389801025391</t>
+    <t xml:space="preserve">92.6990509033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9194030761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0381088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6801223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7443618774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9928131103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9389572143555</t>
   </si>
   <si>
     <t xml:space="preserve">96.7015228271484</t>
   </si>
   <si>
-    <t xml:space="preserve">94.4065322875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.66357421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.433464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9940567016602</t>
+    <t xml:space="preserve">94.4065551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6635818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4334487915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9940490722656</t>
   </si>
   <si>
     <t xml:space="preserve">95.4714202880859</t>
@@ -1193,100 +1193,100 @@
     <t xml:space="preserve">89.9634399414062</t>
   </si>
   <si>
-    <t xml:space="preserve">89.5044326782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4224548339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8814315795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3404388427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7969665527344</t>
+    <t xml:space="preserve">89.5044479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4224395751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8814544677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3404159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7969741821289</t>
   </si>
   <si>
     <t xml:space="preserve">88.5589218139648</t>
   </si>
   <si>
-    <t xml:space="preserve">89.8165588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2033462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6886749267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.1396942138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.7174377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0944137573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0931777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.8006744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4885559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0209808349609</t>
+    <t xml:space="preserve">89.8165512084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2033538818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6886444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1397094726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.7174301147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0944213867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0931854248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8006591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4885482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0209732055664</t>
   </si>
   <si>
     <t xml:space="preserve">94.1495056152344</t>
   </si>
   <si>
-    <t xml:space="preserve">94.4616165161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4500579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.6509704589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7433776855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4823989868164</t>
+    <t xml:space="preserve">94.4616088867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.450080871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.6509857177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7433700561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4823913574219</t>
   </si>
   <si>
     <t xml:space="preserve">96.0920944213867</t>
   </si>
   <si>
-    <t xml:space="preserve">95.6856384277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.0158767700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5493469238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.8634414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3830795288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1267166137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4939422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.600166320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.9165725708008</t>
+    <t xml:space="preserve">95.6856307983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.0158615112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5493621826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8634490966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3830718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1267242431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4939270019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.600151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.9165802001953</t>
   </si>
   <si>
     <t xml:space="preserve">100.359985351562</t>
@@ -1295,13 +1295,13 @@
     <t xml:space="preserve">100.212181091309</t>
   </si>
   <si>
-    <t xml:space="preserve">100.78491973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.71102142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.727195739746</t>
+    <t xml:space="preserve">100.784912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.711006164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.727172851562</t>
   </si>
   <si>
     <t xml:space="preserve">104.202926635742</t>
@@ -1310,271 +1310,271 @@
     <t xml:space="preserve">107.269882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">108.008918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.429237365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.65323638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.988136291504</t>
+    <t xml:space="preserve">108.008911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.429244995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.653259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.988143920898</t>
   </si>
   <si>
     <t xml:space="preserve">108.064353942871</t>
   </si>
   <si>
-    <t xml:space="preserve">108.34147644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.265266418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.135932922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.819534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.893440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.886505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.105895996094</t>
+    <t xml:space="preserve">108.341484069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.265274047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.135948181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.819526672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.893432617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.886489868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.105903625488</t>
   </si>
   <si>
     <t xml:space="preserve">115.269866943359</t>
   </si>
   <si>
-    <t xml:space="preserve">115.454627990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.507736206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.062004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.376098632812</t>
+    <t xml:space="preserve">115.454620361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.50772857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.06201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.376106262207</t>
   </si>
   <si>
     <t xml:space="preserve">116.710975646973</t>
   </si>
   <si>
-    <t xml:space="preserve">117.486946105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.394561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.320671081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.413032531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.322967529297</t>
+    <t xml:space="preserve">117.486953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.394554138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.320648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.413055419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.32299041748</t>
   </si>
   <si>
     <t xml:space="preserve">118.115135192871</t>
   </si>
   <si>
-    <t xml:space="preserve">120.092002868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.135932922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.339141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.611640930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623199462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.156684875488</t>
+    <t xml:space="preserve">120.092025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.135917663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.339134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.611663818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623207092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.156677246094</t>
   </si>
   <si>
     <t xml:space="preserve">123.473068237305</t>
   </si>
   <si>
-    <t xml:space="preserve">121.274490356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.292938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.586235046387</t>
+    <t xml:space="preserve">121.274452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.292961120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.586227416992</t>
   </si>
   <si>
     <t xml:space="preserve">122.54907989502</t>
   </si>
   <si>
-    <t xml:space="preserve">121.248527526855</t>
+    <t xml:space="preserve">121.248519897461</t>
   </si>
   <si>
     <t xml:space="preserve">120.616836547852</t>
   </si>
   <si>
-    <t xml:space="preserve">121.229934692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.270401000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.787338256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.780776977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.049598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.009170532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.017890930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.620056152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.057228088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.441925048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.104248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.306434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.507514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.881294250488</t>
+    <t xml:space="preserve">121.229949951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.270393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.78734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.780754089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.049606323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.009162902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.017906188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.620063781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.057220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.441940307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.10424041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.306427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.507522583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.881271362305</t>
   </si>
   <si>
     <t xml:space="preserve">110.937019348145</t>
   </si>
   <si>
-    <t xml:space="preserve">115.135971069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.700927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.565437316895</t>
+    <t xml:space="preserve">115.135955810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.700950622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.5654296875</t>
   </si>
   <si>
     <t xml:space="preserve">112.609161376953</t>
   </si>
   <si>
-    <t xml:space="preserve">117.123924255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.597145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.056198120117</t>
+    <t xml:space="preserve">117.123931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.597137451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.056182861328</t>
   </si>
   <si>
     <t xml:space="preserve">116.120651245117</t>
   </si>
   <si>
-    <t xml:space="preserve">104.768684387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.270309448242</t>
+    <t xml:space="preserve">104.768692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.270332336426</t>
   </si>
   <si>
     <t xml:space="preserve">105.771980285645</t>
   </si>
   <si>
-    <t xml:space="preserve">110.844108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.68017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.365463256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.798248291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.694450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.301002502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.623428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.552368164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.33927154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.661666870117</t>
+    <t xml:space="preserve">110.844131469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.680198669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.365455627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.798210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.694427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.300987243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.623405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.552383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.339263916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.661651611328</t>
   </si>
   <si>
     <t xml:space="preserve">131.913024902344</t>
   </si>
   <si>
-    <t xml:space="preserve">131.448547363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.628921508789</t>
+    <t xml:space="preserve">131.448593139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.62890625</t>
   </si>
   <si>
     <t xml:space="preserve">132.377548217773</t>
   </si>
   <si>
-    <t xml:space="preserve">134.235427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.285766601562</t>
+    <t xml:space="preserve">134.235443115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.285736083984</t>
   </si>
   <si>
     <t xml:space="preserve">139.67919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">140.217971801758</t>
+    <t xml:space="preserve">140.218002319336</t>
   </si>
   <si>
     <t xml:space="preserve">136.557876586914</t>
   </si>
   <si>
-    <t xml:space="preserve">133.232147216797</t>
+    <t xml:space="preserve">133.232192993164</t>
   </si>
   <si>
     <t xml:space="preserve">132.117401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">129.367706298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.272598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.405975341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.492309570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.154586791992</t>
+    <t xml:space="preserve">129.367691040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.272613525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.405990600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.492294311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.154602050781</t>
   </si>
   <si>
     <t xml:space="preserve">135.183029174805</t>
@@ -1583,82 +1583,82 @@
     <t xml:space="preserve">137.263885498047</t>
   </si>
   <si>
-    <t xml:space="preserve">135.833312988281</t>
+    <t xml:space="preserve">135.833297729492</t>
   </si>
   <si>
     <t xml:space="preserve">135.889282226562</t>
   </si>
   <si>
-    <t xml:space="preserve">135.347778320312</t>
+    <t xml:space="preserve">135.347747802734</t>
   </si>
   <si>
     <t xml:space="preserve">136.561538696289</t>
   </si>
   <si>
-    <t xml:space="preserve">133.050903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.911819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.942672729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.689605712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.399215698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.346984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.771896362305</t>
+    <t xml:space="preserve">133.050918579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.911758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.942611694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.689575195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.399230957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.347007751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.771911621094</t>
   </si>
   <si>
     <t xml:space="preserve">127.766166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">127.56079864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.589775085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.954849243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.180824279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.002464294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.873672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.143486022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.55428314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.846588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.016563415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.972724914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.142379760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.077911376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.011581420898</t>
+    <t xml:space="preserve">127.56078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.589721679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.954833984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.180839538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.002471923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.873710632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.143478393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.554306030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.84659576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.016571044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.97274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.142318725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.077941894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.011627197266</t>
   </si>
   <si>
     <t xml:space="preserve">131.650344848633</t>
@@ -1667,22 +1667,22 @@
     <t xml:space="preserve">132.32258605957</t>
   </si>
   <si>
-    <t xml:space="preserve">133.98454284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.455230712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.621383666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.488754272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.619445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.412170410156</t>
+    <t xml:space="preserve">133.984573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.455261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.621398925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.48876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.619476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.412185668945</t>
   </si>
   <si>
     <t xml:space="preserve">136.37483215332</t>
@@ -1691,91 +1691,91 @@
     <t xml:space="preserve">135.441131591797</t>
   </si>
   <si>
-    <t xml:space="preserve">138.484939575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.055465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.148818969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.225463867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.123657226562</t>
+    <t xml:space="preserve">138.484954833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.055435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.148834228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.225433349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.123672485352</t>
   </si>
   <si>
     <t xml:space="preserve">136.430847167969</t>
   </si>
   <si>
-    <t xml:space="preserve">134.208694458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.179702758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.125579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.833251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.795959472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.239501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.355369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.448738098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.793273925781</t>
+    <t xml:space="preserve">134.208648681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.179718017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.125564575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.833282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.795928955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.239517211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.35538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.448722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.793258666992</t>
   </si>
   <si>
     <t xml:space="preserve">120.334007263184</t>
   </si>
   <si>
-    <t xml:space="preserve">118.802772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.473121643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.854957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.155662536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.717803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.800872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.875587463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.736457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.221969604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.245346069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.73365020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.409812927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.578819274902</t>
+    <t xml:space="preserve">118.802780151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.473152160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.85498046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.155654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.717796325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.800888061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.875564575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.736473083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.221961975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.245330810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.733657836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.409790039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.578842163086</t>
   </si>
   <si>
     <t xml:space="preserve">121.480346679688</t>
@@ -1784,199 +1784,199 @@
     <t xml:space="preserve">120.071731567383</t>
   </si>
   <si>
-    <t xml:space="preserve">118.174758911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.062080383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.207778930664</t>
+    <t xml:space="preserve">118.174766540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.06209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.207763671875</t>
   </si>
   <si>
     <t xml:space="preserve">117.423492431641</t>
   </si>
   <si>
-    <t xml:space="preserve">119.170196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.479835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.446853637695</t>
+    <t xml:space="preserve">119.170204162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.479858398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.446846008301</t>
   </si>
   <si>
     <t xml:space="preserve">116.052429199219</t>
   </si>
   <si>
-    <t xml:space="preserve">118.83211517334</t>
+    <t xml:space="preserve">118.832138061523</t>
   </si>
   <si>
     <t xml:space="preserve">119.301689147949</t>
   </si>
   <si>
-    <t xml:space="preserve">118.099662780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.625534057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.799140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.686965942383</t>
+    <t xml:space="preserve">118.099655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.625511169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.799133300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.686981201172</t>
   </si>
   <si>
     <t xml:space="preserve">117.592552185059</t>
   </si>
   <si>
-    <t xml:space="preserve">117.554985046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.639755249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.710289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.72908782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.611839294434</t>
+    <t xml:space="preserve">117.554977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.639762878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.710311889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.729095458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.61181640625</t>
   </si>
   <si>
     <t xml:space="preserve">120.597618103027</t>
   </si>
   <si>
-    <t xml:space="preserve">120.334671020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.583374023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.785400390625</t>
+    <t xml:space="preserve">120.334663391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.583404541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.785430908203</t>
   </si>
   <si>
     <t xml:space="preserve">118.193565368652</t>
   </si>
   <si>
-    <t xml:space="preserve">116.709800720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.977310180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.747360229492</t>
+    <t xml:space="preserve">116.709777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.977294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.747352600098</t>
   </si>
   <si>
     <t xml:space="preserve">116.108772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">121.424026489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.335174560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.546363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.231628417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.869697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.066635131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.34838104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.150894165039</t>
+    <t xml:space="preserve">121.424018859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.335159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.546348571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.231636047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.869689941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.066665649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.348373413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.150932312012</t>
   </si>
   <si>
     <t xml:space="preserve">113.12247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">112.615371704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.939231872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.347862243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.563591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.22957611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.835166931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.530082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.666130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.684913635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.511291503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.137199401855</t>
+    <t xml:space="preserve">112.615364074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.939224243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.347854614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.563606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.229583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.835151672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.530090332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.666137695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.684921264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.511299133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.137214660645</t>
   </si>
   <si>
     <t xml:space="preserve">116.221466064453</t>
   </si>
   <si>
-    <t xml:space="preserve">116.202682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.5732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.104202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.319931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.939125061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.97834777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.354782104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.221061706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.504493713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.164375305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.35920715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.90128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.338844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.449264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.318481445312</t>
+    <t xml:space="preserve">116.202690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.573249816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.104209899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.319953918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.939102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.978355407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.354797363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.221069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.50447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.164390563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.359199523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.901306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.338851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.449287414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.318473815918</t>
   </si>
   <si>
     <t xml:space="preserve">115.830108642578</t>
@@ -1985,34 +1985,34 @@
     <t xml:space="preserve">114.828666687012</t>
   </si>
   <si>
-    <t xml:space="preserve">113.846115112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.447799682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.469619750977</t>
+    <t xml:space="preserve">113.846069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.447807312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.469635009766</t>
   </si>
   <si>
     <t xml:space="preserve">116.151351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">122.651458740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.841827392578</t>
+    <t xml:space="preserve">122.65145111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.841850280762</t>
   </si>
   <si>
     <t xml:space="preserve">125.353500366211</t>
   </si>
   <si>
-    <t xml:space="preserve">124.84334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.411651611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.327453613281</t>
+    <t xml:space="preserve">124.843330383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.411682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.32746887207</t>
   </si>
   <si>
     <t xml:space="preserve">131.948089599609</t>
@@ -2021,16 +2021,16 @@
     <t xml:space="preserve">131.267822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">129.737319946289</t>
+    <t xml:space="preserve">129.7373046875</t>
   </si>
   <si>
     <t xml:space="preserve">129.96403503418</t>
   </si>
   <si>
-    <t xml:space="preserve">129.416091918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.583198547363</t>
+    <t xml:space="preserve">129.416076660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.583213806152</t>
   </si>
   <si>
     <t xml:space="preserve">128.471298217773</t>
@@ -2039,109 +2039,109 @@
     <t xml:space="preserve">129.113754272461</t>
   </si>
   <si>
-    <t xml:space="preserve">126.827369689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.392784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.904418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.016342163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.603561401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.118316650391</t>
+    <t xml:space="preserve">126.82740020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.392791748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.904411315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.016319274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.603607177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.118362426758</t>
   </si>
   <si>
     <t xml:space="preserve">139.978713989258</t>
   </si>
   <si>
-    <t xml:space="preserve">144.645935058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.119781494141</t>
+    <t xml:space="preserve">144.645965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.11979675293</t>
   </si>
   <si>
     <t xml:space="preserve">148.047164916992</t>
   </si>
   <si>
-    <t xml:space="preserve">147.839263916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.714370727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.833602905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.076309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.760955810547</t>
+    <t xml:space="preserve">147.839279174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.714324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.83366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.076293945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.760940551758</t>
   </si>
   <si>
     <t xml:space="preserve">164.032836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">164.996520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.992111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.125869750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.349670410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.804611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.72021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.962936401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.137405395508</t>
+    <t xml:space="preserve">164.996505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.992080688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.125823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.349685668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.804656982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.720230102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.962966918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.137435913086</t>
   </si>
   <si>
     <t xml:space="preserve">158.70426940918</t>
   </si>
   <si>
-    <t xml:space="preserve">160.461578369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.814682006836</t>
+    <t xml:space="preserve">160.461547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.814697265625</t>
   </si>
   <si>
     <t xml:space="preserve">159.157775878906</t>
   </si>
   <si>
-    <t xml:space="preserve">158.008773803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.819534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.560852050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.793975830078</t>
+    <t xml:space="preserve">158.008804321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.819519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.560791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.793991088867</t>
   </si>
   <si>
     <t xml:space="preserve">161.161376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">159.831970214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.856842041016</t>
+    <t xml:space="preserve">159.831985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.856872558594</t>
   </si>
   <si>
     <t xml:space="preserve">154.932159423828</t>
@@ -2150,157 +2150,157 @@
     <t xml:space="preserve">159.20524597168</t>
   </si>
   <si>
-    <t xml:space="preserve">159.964904785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.970794677734</t>
+    <t xml:space="preserve">159.964920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.970840454102</t>
   </si>
   <si>
     <t xml:space="preserve">159.907897949219</t>
   </si>
   <si>
-    <t xml:space="preserve">162.376831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.756607055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.958374023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.338165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.617172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.884323120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.409530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.890243530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.661727905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.326354980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.741592407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.931533813477</t>
+    <t xml:space="preserve">162.376815795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.756652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.95832824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.33821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.617141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.884368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.409515380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.890228271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.661712646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.326370239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.741622924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.931549072266</t>
   </si>
   <si>
     <t xml:space="preserve">149.082794189453</t>
   </si>
   <si>
-    <t xml:space="preserve">147.183670043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.753433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.133209228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.462631225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.47444152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.993774414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.89289855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.602157592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.792022705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.399749755859</t>
+    <t xml:space="preserve">147.183639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.753387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.133224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.462615966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.474426269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.993759155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.892883300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.602127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.792068481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.399765014648</t>
   </si>
   <si>
     <t xml:space="preserve">151.456756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">148.703002929688</t>
+    <t xml:space="preserve">148.702987670898</t>
   </si>
   <si>
     <t xml:space="preserve">145.284515380859</t>
   </si>
   <si>
-    <t xml:space="preserve">146.234100341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.854293823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.904708862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.42399597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.323150634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.842483520508</t>
+    <t xml:space="preserve">146.234085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.854263305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.904678344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.424026489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.323135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.84245300293</t>
   </si>
   <si>
     <t xml:space="preserve">150.412216186523</t>
   </si>
   <si>
-    <t xml:space="preserve">149.652526855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.513031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.803833007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.955154418945</t>
+    <t xml:space="preserve">149.652572631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.513046264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.803863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.955093383789</t>
   </si>
   <si>
     <t xml:space="preserve">140.346755981445</t>
   </si>
   <si>
-    <t xml:space="preserve">141.486236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.575317382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.044189453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.12141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.691177368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.070999145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.83659362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.69352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.220932006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.457260131836</t>
+    <t xml:space="preserve">141.486251831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.575286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.044174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.121429443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.691192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.071044921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.836547851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.693542480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.220947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.457244873047</t>
   </si>
   <si>
     <t xml:space="preserve">152.929824829102</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">153.979888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">156.175521850586</t>
+    <t xml:space="preserve">156.175552368164</t>
   </si>
   <si>
     <t xml:space="preserve">157.702941894531</t>
@@ -2321,22 +2321,22 @@
     <t xml:space="preserve">154.361755371094</t>
   </si>
   <si>
-    <t xml:space="preserve">156.748336791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.225616455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.839096069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.366485595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.803115844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.640365600586</t>
+    <t xml:space="preserve">156.748321533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.225631713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.839065551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.366455078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.803100585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.640380859375</t>
   </si>
   <si>
     <t xml:space="preserve">170.876663208008</t>
@@ -2345,217 +2345,217 @@
     <t xml:space="preserve">175.076995849609</t>
   </si>
   <si>
-    <t xml:space="preserve">183.000335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.365707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">177.749923706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">175.840682983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.222549438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.227188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.270233154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179.038681030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">178.800033569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.265548706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.243682861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.527679443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182.093414306641</t>
+    <t xml:space="preserve">183.00032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.365692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">177.749908447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">175.840667724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.222503662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.22721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.270248413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179.038619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">178.800018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.265579223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.24365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.527725219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182.09342956543</t>
   </si>
   <si>
     <t xml:space="preserve">184.432250976562</t>
   </si>
   <si>
-    <t xml:space="preserve">185.291412353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.102813720703</t>
+    <t xml:space="preserve">185.291381835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">186.102844238281</t>
   </si>
   <si>
     <t xml:space="preserve">187.773422241211</t>
   </si>
   <si>
-    <t xml:space="preserve">189.491729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.9189453125</t>
+    <t xml:space="preserve">189.491744995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.918960571289</t>
   </si>
   <si>
     <t xml:space="preserve">189.969024658203</t>
   </si>
   <si>
-    <t xml:space="preserve">188.775741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.06916809082</t>
+    <t xml:space="preserve">188.775756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.069198608398</t>
   </si>
   <si>
     <t xml:space="preserve">189.682647705078</t>
   </si>
   <si>
-    <t xml:space="preserve">190.446319580078</t>
+    <t xml:space="preserve">190.446334838867</t>
   </si>
   <si>
     <t xml:space="preserve">190.828186035156</t>
   </si>
   <si>
-    <t xml:space="preserve">188.584823608398</t>
+    <t xml:space="preserve">188.584854125977</t>
   </si>
   <si>
     <t xml:space="preserve">187.677963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">187.296081542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.591888427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.973739624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.88298034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.983123779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.4150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.269546508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">199.515243530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197.319610595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.842269897461</t>
+    <t xml:space="preserve">187.296112060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.591903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.973724365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.882965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.983139038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.415054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.26953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">199.515197753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197.319549560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.842300415039</t>
   </si>
   <si>
     <t xml:space="preserve">197.987838745117</t>
   </si>
   <si>
-    <t xml:space="preserve">207.152160644531</t>
+    <t xml:space="preserve">207.15217590332</t>
   </si>
   <si>
     <t xml:space="preserve">213.739013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">212.975341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.929946899414</t>
+    <t xml:space="preserve">212.975311279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.929931640625</t>
   </si>
   <si>
     <t xml:space="preserve">218.321166992188</t>
   </si>
   <si>
-    <t xml:space="preserve">218.703079223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.366546630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.498062133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">218.564346313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.917984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.93017578125</t>
+    <t xml:space="preserve">218.703033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.366577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.498077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">218.564300537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.917999267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.930191040039</t>
   </si>
   <si>
     <t xml:space="preserve">221.534713745117</t>
   </si>
   <si>
-    <t xml:space="preserve">223.067810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">222.205444335938</t>
+    <t xml:space="preserve">223.067825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">222.205459594727</t>
   </si>
   <si>
     <t xml:space="preserve">214.444061279297</t>
   </si>
   <si>
-    <t xml:space="preserve">214.156646728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.294250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.048599243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.060791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.186248779297</t>
+    <t xml:space="preserve">214.156631469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.294219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.048614501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.060806274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.18620300293</t>
   </si>
   <si>
     <t xml:space="preserve">207.736709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">208.982376098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.269821166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.994598388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.461471557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.970153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.058929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196.621658325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.447387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.920394897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">191.495315551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.902084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">187.087615966797</t>
+    <t xml:space="preserve">208.982360839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.269790649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.994567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.461486816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.970123291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.058898925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">196.621627807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.44743347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.920379638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">191.495330810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.902069091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">187.087600708008</t>
   </si>
   <si>
     <t xml:space="preserve">189.531005859375</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">187.997894287109</t>
   </si>
   <si>
-    <t xml:space="preserve">190.632919311523</t>
+    <t xml:space="preserve">190.632904052734</t>
   </si>
   <si>
     <t xml:space="preserve">190.537094116211</t>
@@ -2588,79 +2588,79 @@
     <t xml:space="preserve">189.770553588867</t>
   </si>
   <si>
-    <t xml:space="preserve">185.410766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">190.393402099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">188.237426757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">192.501388549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.172149658203</t>
+    <t xml:space="preserve">185.410781860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">190.39338684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">188.237442016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">192.501403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.172119140625</t>
   </si>
   <si>
     <t xml:space="preserve">196.525833129883</t>
   </si>
   <si>
-    <t xml:space="preserve">193.555419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">193.938690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">194.992721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">195.471801757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.442230224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.72966003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.358596801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">198.537994384766</t>
+    <t xml:space="preserve">193.555389404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">193.938674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194.992691040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">195.471832275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.44221496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.729675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.358627319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">198.538070678711</t>
   </si>
   <si>
     <t xml:space="preserve">198.921310424805</t>
   </si>
   <si>
-    <t xml:space="preserve">201.987548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">202.84992980957</t>
+    <t xml:space="preserve">201.987564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">202.849884033203</t>
   </si>
   <si>
     <t xml:space="preserve">208.2158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">207.832550048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.802947998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.353454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.006805419922</t>
+    <t xml:space="preserve">207.832565307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.802963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.353424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.006790161133</t>
   </si>
   <si>
     <t xml:space="preserve">217.989410400391</t>
   </si>
   <si>
-    <t xml:space="preserve">215.59391784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.977172851562</t>
+    <t xml:space="preserve">215.593902587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.977188110352</t>
   </si>
   <si>
     <t xml:space="preserve">219.905807495117</t>
@@ -2669,76 +2669,76 @@
     <t xml:space="preserve">220.768157958984</t>
   </si>
   <si>
-    <t xml:space="preserve">218.892776489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.16162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.277450561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.297134399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.200927734375</t>
+    <t xml:space="preserve">218.892807006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.161651611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.277465820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.297119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.200942993164</t>
   </si>
   <si>
     <t xml:space="preserve">223.316787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">224.663238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.509124755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">224.182357788086</t>
+    <t xml:space="preserve">224.663223266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.509140014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">224.182342529297</t>
   </si>
   <si>
     <t xml:space="preserve">227.067596435547</t>
   </si>
   <si>
-    <t xml:space="preserve">222.162719726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.064407348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">215.238128662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211.198822021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.756225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.351867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203.985763549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.313583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.640350341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">213.506988525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.929962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.279602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">237.646759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.259918212891</t>
+    <t xml:space="preserve">222.162704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.064376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">215.238159179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">211.198806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.756210327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.351852416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203.985733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.313629150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.640380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">213.50700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.929946899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.279571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">237.646789550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.25993347168</t>
   </si>
   <si>
     <t xml:space="preserve">225.624984741211</t>
@@ -2747,175 +2747,175 @@
     <t xml:space="preserve">224.567047119141</t>
   </si>
   <si>
-    <t xml:space="preserve">232.06867980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.819458007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">235.434753417969</t>
+    <t xml:space="preserve">232.068649291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.819427490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">235.434768676758</t>
   </si>
   <si>
     <t xml:space="preserve">235.530914306641</t>
   </si>
   <si>
-    <t xml:space="preserve">228.317840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">227.644622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220.527755737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">219.662185668945</t>
+    <t xml:space="preserve">228.317810058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">227.644607543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.527725219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">219.662124633789</t>
   </si>
   <si>
     <t xml:space="preserve">218.123382568359</t>
   </si>
   <si>
-    <t xml:space="preserve">219.373626708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">212.256744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.19775390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.544174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.409744262695</t>
+    <t xml:space="preserve">219.373657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">212.256729125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.197738647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.544219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.409759521484</t>
   </si>
   <si>
     <t xml:space="preserve">211.102630615234</t>
   </si>
   <si>
-    <t xml:space="preserve">209.948623657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.159484863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.042587280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.869873046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205.813095092773</t>
+    <t xml:space="preserve">209.948593139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.159515380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.042617797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201.869903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">205.813064575195</t>
   </si>
   <si>
     <t xml:space="preserve">208.121246337891</t>
   </si>
   <si>
-    <t xml:space="preserve">207.92887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.98681640625</t>
+    <t xml:space="preserve">207.928863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.986785888672</t>
   </si>
   <si>
     <t xml:space="preserve">208.794464111328</t>
   </si>
   <si>
-    <t xml:space="preserve">212.352920532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.101593017578</t>
+    <t xml:space="preserve">212.352905273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.1015625</t>
   </si>
   <si>
     <t xml:space="preserve">202.63932800293</t>
   </si>
   <si>
-    <t xml:space="preserve">202.158432006836</t>
+    <t xml:space="preserve">202.158447265625</t>
   </si>
   <si>
     <t xml:space="preserve">205.139846801758</t>
   </si>
   <si>
-    <t xml:space="preserve">202.927810668945</t>
+    <t xml:space="preserve">202.927825927734</t>
   </si>
   <si>
     <t xml:space="preserve">200.234954833984</t>
   </si>
   <si>
-    <t xml:space="preserve">198.959442138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">207.076309204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208.525726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">206.593170166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204.85383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.892044067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">203.404403686523</t>
+    <t xml:space="preserve">198.959426879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">207.076263427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208.525756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">206.593124389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">204.853820800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.891998291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">203.404388427734</t>
   </si>
   <si>
     <t xml:space="preserve">205.916748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">205.626815795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">216.256057739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.130233764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">214.806655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">221.957183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223.116744995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">229.397583007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">231.90998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">233.262802124023</t>
+    <t xml:space="preserve">205.626846313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">216.256072998047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.130249023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">214.806625366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">221.957168579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223.116714477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">229.397613525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">231.910018920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">233.262756347656</t>
   </si>
   <si>
     <t xml:space="preserve">232.393142700195</t>
   </si>
   <si>
-    <t xml:space="preserve">231.23356628418</t>
+    <t xml:space="preserve">231.233581542969</t>
   </si>
   <si>
     <t xml:space="preserve">237.417861938477</t>
   </si>
   <si>
-    <t xml:space="preserve">236.161682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.312240600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">243.40885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">246.307739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.332458496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.651580810547</t>
+    <t xml:space="preserve">236.161666870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.312255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">243.408874511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">246.307754516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.332473754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.651519775391</t>
   </si>
   <si>
     <t xml:space="preserve">249.883010864258</t>
@@ -2924,25 +2924,25 @@
     <t xml:space="preserve">251.525680541992</t>
   </si>
   <si>
-    <t xml:space="preserve">252.105499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.294219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">255.004333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">251.622344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.008819580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">250.656021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253.844787597656</t>
+    <t xml:space="preserve">252.10546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.294204711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">255.00439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">251.622375488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.008850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250.656051635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253.844833374023</t>
   </si>
   <si>
     <t xml:space="preserve">257.468414306641</t>
@@ -2951,124 +2951,124 @@
     <t xml:space="preserve">260.802124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">266.020050048828</t>
+    <t xml:space="preserve">266.020080566406</t>
   </si>
   <si>
     <t xml:space="preserve">275.48974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">276.890869140625</t>
+    <t xml:space="preserve">276.890838623047</t>
   </si>
   <si>
     <t xml:space="preserve">275.006591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">274.668426513672</t>
+    <t xml:space="preserve">274.66845703125</t>
   </si>
   <si>
     <t xml:space="preserve">269.305511474609</t>
   </si>
   <si>
-    <t xml:space="preserve">269.691986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.295379638672</t>
+    <t xml:space="preserve">269.692016601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.295349121094</t>
   </si>
   <si>
     <t xml:space="preserve">263.556030273438</t>
   </si>
   <si>
-    <t xml:space="preserve">253.796569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">252.347015380859</t>
+    <t xml:space="preserve">253.796493530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.347076416016</t>
   </si>
   <si>
     <t xml:space="preserve">258.869537353516</t>
   </si>
   <si>
-    <t xml:space="preserve">269.595336914062</t>
+    <t xml:space="preserve">269.595367431641</t>
   </si>
   <si>
     <t xml:space="preserve">268.822357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">265.730194091797</t>
+    <t xml:space="preserve">265.730163574219</t>
   </si>
   <si>
     <t xml:space="preserve">265.536926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">264.957183837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">268.339202880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265.102172851562</t>
+    <t xml:space="preserve">264.957214355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268.339263916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265.102111816406</t>
   </si>
   <si>
     <t xml:space="preserve">263.942535400391</t>
   </si>
   <si>
-    <t xml:space="preserve">258.579650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">266.454956054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">267.4052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">281.854400634766</t>
+    <t xml:space="preserve">258.579620361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">266.454895019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">267.405242919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281.854370117188</t>
   </si>
   <si>
     <t xml:space="preserve">277.005645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">274.290374755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">263.623291015625</t>
+    <t xml:space="preserve">274.290466308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">263.623352050781</t>
   </si>
   <si>
     <t xml:space="preserve">271.090270996094</t>
   </si>
   <si>
-    <t xml:space="preserve">275.599609375</t>
+    <t xml:space="preserve">275.599578857422</t>
   </si>
   <si>
     <t xml:space="preserve">272.108489990234</t>
   </si>
   <si>
-    <t xml:space="preserve">280.642211914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">281.466491699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">282.630096435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">274.532836914062</t>
+    <t xml:space="preserve">280.642181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">281.466461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">282.630157470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">274.532867431641</t>
   </si>
   <si>
     <t xml:space="preserve">280.205780029297</t>
   </si>
   <si>
-    <t xml:space="preserve">278.411804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">284.084716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.769409179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.066223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270.750793457031</t>
+    <t xml:space="preserve">278.411773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">284.084777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.769470214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.066192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270.750885009766</t>
   </si>
   <si>
     <t xml:space="preserve">268.471954345703</t>
@@ -3077,19 +3077,19 @@
     <t xml:space="preserve">271.817535400391</t>
   </si>
   <si>
-    <t xml:space="preserve">265.611206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">272.25390625</t>
+    <t xml:space="preserve">265.611267089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">272.254028320312</t>
   </si>
   <si>
     <t xml:space="preserve">270.847808837891</t>
   </si>
   <si>
-    <t xml:space="preserve">274.484344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">279.720947265625</t>
+    <t xml:space="preserve">274.484313964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">279.720886230469</t>
   </si>
   <si>
     <t xml:space="preserve">284.763580322266</t>
@@ -3101,106 +3101,106 @@
     <t xml:space="preserve">299.455047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">295.576110839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.552093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.679321289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.843017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.946166992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.721923828125</t>
+    <t xml:space="preserve">295.576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.552032470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.679351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.842987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">302.946136474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.721984863281</t>
   </si>
   <si>
     <t xml:space="preserve">314.049652099609</t>
   </si>
   <si>
-    <t xml:space="preserve">312.740539550781</t>
+    <t xml:space="preserve">312.740509033203</t>
   </si>
   <si>
     <t xml:space="preserve">315.019409179688</t>
   </si>
   <si>
-    <t xml:space="preserve">318.364990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.443389892578</t>
+    <t xml:space="preserve">318.364959716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.443359375</t>
   </si>
   <si>
     <t xml:space="preserve">311.625335693359</t>
   </si>
   <si>
-    <t xml:space="preserve">318.122528076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.213317871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">309.879760742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.825134277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.916198730469</t>
+    <t xml:space="preserve">318.122589111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.213348388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">309.879699707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.825103759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.916259765625</t>
   </si>
   <si>
     <t xml:space="preserve">312.837493896484</t>
   </si>
   <si>
-    <t xml:space="preserve">316.231597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.4677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.631530761719</t>
+    <t xml:space="preserve">316.231506347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.467742919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.631469726562</t>
   </si>
   <si>
     <t xml:space="preserve">313.661773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">308.425170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.473724365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300.667297363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.854644775391</t>
+    <t xml:space="preserve">308.425201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.4736328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300.667236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.854705810547</t>
   </si>
   <si>
     <t xml:space="preserve">288.836456298828</t>
   </si>
   <si>
-    <t xml:space="preserve">289.369781494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.284820556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">285.539337158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">283.84228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.806762695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">298.369110107422</t>
+    <t xml:space="preserve">289.369842529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.284912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">285.539306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">283.842346191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.806823730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.298858642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">298.369140625</t>
   </si>
   <si>
     <t xml:space="preserve">305.812591552734</t>
@@ -3221,64 +3221,64 @@
     <t xml:space="preserve">311.358642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">309.412689208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.228973388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.234130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.925903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294.185272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.250183105469</t>
+    <t xml:space="preserve">309.41259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.228942871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.234100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.925933837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.185241699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.250152587891</t>
   </si>
   <si>
     <t xml:space="preserve">300.217803955078</t>
   </si>
   <si>
-    <t xml:space="preserve">295.888031005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.596313476562</t>
+    <t xml:space="preserve">295.888000488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.596282958984</t>
   </si>
   <si>
     <t xml:space="preserve">303.963806152344</t>
   </si>
   <si>
-    <t xml:space="preserve">306.688232421875</t>
+    <t xml:space="preserve">306.688262939453</t>
   </si>
   <si>
     <t xml:space="preserve">308.585601806641</t>
   </si>
   <si>
-    <t xml:space="preserve">306.298980712891</t>
+    <t xml:space="preserve">306.299041748047</t>
   </si>
   <si>
     <t xml:space="preserve">301.96923828125</t>
   </si>
   <si>
-    <t xml:space="preserve">300.412445068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.342071533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.796020507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">293.990692138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">297.104217529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.601898193359</t>
+    <t xml:space="preserve">300.412414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.342102050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.796051025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">293.990631103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">297.104248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.601837158203</t>
   </si>
   <si>
     <t xml:space="preserve">311.845092773438</t>
@@ -3287,130 +3287,130 @@
     <t xml:space="preserve">314.0830078125</t>
   </si>
   <si>
-    <t xml:space="preserve">342.883697509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327.656311035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.445373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.612762451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320.066955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">324.348175048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.721282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.650939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323.375152587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.758972167969</t>
+    <t xml:space="preserve">342.883666992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327.656341552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.445404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.61279296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320.06689453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">324.348114013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.72119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.650909423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.375091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.758941650391</t>
   </si>
   <si>
     <t xml:space="preserve">327.315765380859</t>
   </si>
   <si>
-    <t xml:space="preserve">324.88330078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.380645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.521240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.580688476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">326.245452880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.710266113281</t>
+    <t xml:space="preserve">324.883270263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.380676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.521301269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.580627441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326.245513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.710296630859</t>
   </si>
   <si>
     <t xml:space="preserve">334.515869140625</t>
   </si>
   <si>
-    <t xml:space="preserve">343.759399414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.543090820312</t>
+    <t xml:space="preserve">343.759338378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.543151855469</t>
   </si>
   <si>
     <t xml:space="preserve">347.456787109375</t>
   </si>
   <si>
-    <t xml:space="preserve">347.748657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.7109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">354.802917480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.424194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">353.829864501953</t>
+    <t xml:space="preserve">347.748687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.710968017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">354.802886962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.424163818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">353.829895019531</t>
   </si>
   <si>
     <t xml:space="preserve">358.257019042969</t>
   </si>
   <si>
-    <t xml:space="preserve">350.473022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">352.224487304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">353.635284423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">357.429992675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">349.013610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.672607421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.946563720703</t>
+    <t xml:space="preserve">350.473083496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">352.224426269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">353.635314941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">357.430023193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">349.013580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.672576904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.946624755859</t>
   </si>
   <si>
     <t xml:space="preserve">331.53125</t>
   </si>
   <si>
-    <t xml:space="preserve">331.921630859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.898651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.972076416016</t>
+    <t xml:space="preserve">331.921600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.898620605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.972045898438</t>
   </si>
   <si>
     <t xml:space="preserve">343.728942871094</t>
   </si>
   <si>
-    <t xml:space="preserve">342.606689453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.581695556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">339.093872070312</t>
+    <t xml:space="preserve">342.606781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.581726074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">339.093841552734</t>
   </si>
   <si>
     <t xml:space="preserve">342.704315185547</t>
@@ -3419,145 +3419,145 @@
     <t xml:space="preserve">345.095031738281</t>
   </si>
   <si>
-    <t xml:space="preserve">341.435760498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">344.509643554688</t>
+    <t xml:space="preserve">341.435699462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">344.509552001953</t>
   </si>
   <si>
     <t xml:space="preserve">344.119232177734</t>
   </si>
   <si>
-    <t xml:space="preserve">346.509948730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.826965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">342.070037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">345.582977294922</t>
+    <t xml:space="preserve">346.510040283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.826904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">342.070068359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">345.582946777344</t>
   </si>
   <si>
     <t xml:space="preserve">343.680114746094</t>
   </si>
   <si>
-    <t xml:space="preserve">340.4111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.801086425781</t>
+    <t xml:space="preserve">340.411193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.801055908203</t>
   </si>
   <si>
     <t xml:space="preserve">335.239379882812</t>
   </si>
   <si>
-    <t xml:space="preserve">332.751037597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328.945404052734</t>
+    <t xml:space="preserve">332.751068115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328.945343017578</t>
   </si>
   <si>
     <t xml:space="preserve">328.994201660156</t>
   </si>
   <si>
-    <t xml:space="preserve">330.116333007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">340.118438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.654693603516</t>
+    <t xml:space="preserve">330.116363525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">340.118408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.654663085938</t>
   </si>
   <si>
     <t xml:space="preserve">336.800659179688</t>
   </si>
   <si>
-    <t xml:space="preserve">335.141754150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">338.605895996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.044250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">336.703094482422</t>
+    <t xml:space="preserve">335.141784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">338.60595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.044189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">336.703125</t>
   </si>
   <si>
     <t xml:space="preserve">335.629760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">337.288543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">330.89697265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">335.434509277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.774047851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">315.625549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">321.529266357422</t>
+    <t xml:space="preserve">337.288482666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">330.897033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">335.4345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.774017333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">315.625640869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">321.529296875</t>
   </si>
   <si>
     <t xml:space="preserve">321.919586181641</t>
   </si>
   <si>
-    <t xml:space="preserve">326.018005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">323.968780517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">325.188507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320.065521240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">317.528442382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">311.088043212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.672698974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.428771972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">310.161102294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">313.039672851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">308.794921875</t>
+    <t xml:space="preserve">326.017974853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">323.968811035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">325.188537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320.065551757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">317.528411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">311.088073730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.672729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.428833007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">310.161041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">313.039642333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">308.794982910156</t>
   </si>
   <si>
     <t xml:space="preserve">307.184844970703</t>
   </si>
   <si>
-    <t xml:space="preserve">305.477203369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.131958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.331237792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.160247802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">306.501770019531</t>
+    <t xml:space="preserve">305.477172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.131988525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.331207275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.160278320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">306.501831054688</t>
   </si>
   <si>
     <t xml:space="preserve">309.575561523438</t>
@@ -3566,10 +3566,10 @@
     <t xml:space="preserve">312.161499023438</t>
   </si>
   <si>
-    <t xml:space="preserve">316.796600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.503845214844</t>
+    <t xml:space="preserve">316.796569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.503875732422</t>
   </si>
   <si>
     <t xml:space="preserve">318.393737792969</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">313.595520019531</t>
   </si>
   <si>
-    <t xml:space="preserve">303.558532714844</t>
+    <t xml:space="preserve">303.558502197266</t>
   </si>
   <si>
     <t xml:space="preserve">301.942810058594</t>
@@ -3587,28 +3587,28 @@
     <t xml:space="preserve">300.571899414062</t>
   </si>
   <si>
-    <t xml:space="preserve">302.775146484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.146057128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">304.341918945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299.886444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294.011138916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.93994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290.192138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">289.604705810547</t>
+    <t xml:space="preserve">302.775177001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.146118164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">304.341949462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299.886474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">294.011077880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">287.939910888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">290.192199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">289.604644775391</t>
   </si>
   <si>
     <t xml:space="preserve">293.080841064453</t>
@@ -3617,34 +3617,34 @@
     <t xml:space="preserve">291.465148925781</t>
   </si>
   <si>
-    <t xml:space="preserve">289.702545166016</t>
+    <t xml:space="preserve">289.702514648438</t>
   </si>
   <si>
     <t xml:space="preserve">288.380615234375</t>
   </si>
   <si>
-    <t xml:space="preserve">293.129791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">292.052703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">295.528869628906</t>
+    <t xml:space="preserve">293.129852294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">292.052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">295.528900146484</t>
   </si>
   <si>
     <t xml:space="preserve">295.969573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">304.195068359375</t>
+    <t xml:space="preserve">304.195037841797</t>
   </si>
   <si>
     <t xml:space="preserve">304.390869140625</t>
   </si>
   <si>
-    <t xml:space="preserve">302.089721679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.411651611328</t>
+    <t xml:space="preserve">302.089691162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.411682128906</t>
   </si>
   <si>
     <t xml:space="preserve">299.592681884766</t>
@@ -3653,109 +3653,109 @@
     <t xml:space="preserve">301.110473632812</t>
   </si>
   <si>
-    <t xml:space="preserve">299.984344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.370086669922</t>
+    <t xml:space="preserve">299.984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.370056152344</t>
   </si>
   <si>
     <t xml:space="preserve">304.48876953125</t>
   </si>
   <si>
-    <t xml:space="preserve">303.509552001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">305.419067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">303.9501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">307.965026855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">314.721649169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">318.442749023438</t>
+    <t xml:space="preserve">303.509582519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">305.419036865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">303.950225830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">307.964996337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">314.721618652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">318.442718505859</t>
   </si>
   <si>
     <t xml:space="preserve">325.884735107422</t>
   </si>
   <si>
-    <t xml:space="preserve">329.018280029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">329.605834960938</t>
+    <t xml:space="preserve">329.018341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">329.605804443359</t>
   </si>
   <si>
     <t xml:space="preserve">330.976715087891</t>
   </si>
   <si>
-    <t xml:space="preserve">333.326812744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334.110260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">332.543426513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">331.760070800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">341.944000244141</t>
+    <t xml:space="preserve">333.326843261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334.110229492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">332.543518066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">331.760101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">341.944030761719</t>
   </si>
   <si>
     <t xml:space="preserve">340.768920898438</t>
   </si>
   <si>
-    <t xml:space="preserve">344.685821533203</t>
+    <t xml:space="preserve">344.685791015625</t>
   </si>
   <si>
     <t xml:space="preserve">352.32373046875</t>
   </si>
   <si>
-    <t xml:space="preserve">358.786590576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">375.433380126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">380.133666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">382.679626464844</t>
+    <t xml:space="preserve">358.786560058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">375.433349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">380.133605957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">382.679565429688</t>
   </si>
   <si>
     <t xml:space="preserve">385.225555419922</t>
   </si>
   <si>
-    <t xml:space="preserve">385.421447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">386.204803466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389.338287353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">395.358032226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">389.465972900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">393.393951416016</t>
+    <t xml:space="preserve">385.421356201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">386.204742431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">389.338317871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">395.358062744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">389.466003417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">393.394012451172</t>
   </si>
   <si>
     <t xml:space="preserve">393.197570800781</t>
   </si>
   <si>
-    <t xml:space="preserve">398.304046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">401.053741455078</t>
+    <t xml:space="preserve">398.304077148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">401.053680419922</t>
   </si>
   <si>
     <t xml:space="preserve">402.428497314453</t>
@@ -3764,13 +3764,13 @@
     <t xml:space="preserve">388.483917236328</t>
   </si>
   <si>
-    <t xml:space="preserve">388.091186523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">387.109100341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">391.233581542969</t>
+    <t xml:space="preserve">388.091125488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">387.109161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">391.233551025391</t>
   </si>
   <si>
     <t xml:space="preserve">396.143615722656</t>
@@ -3779,37 +3779,37 @@
     <t xml:space="preserve">388.680297851562</t>
   </si>
   <si>
-    <t xml:space="preserve">396.536437988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.16015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">408.124176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404.785339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.963745117188</t>
+    <t xml:space="preserve">396.536468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.160186767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">408.124206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404.785369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.963806152344</t>
   </si>
   <si>
     <t xml:space="preserve">407.731414794922</t>
   </si>
   <si>
-    <t xml:space="preserve">403.999755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">405.178161621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.8212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.534973144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.749328613281</t>
+    <t xml:space="preserve">403.999786376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">405.178192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.821380615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.535003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.749389648438</t>
   </si>
   <si>
     <t xml:space="preserve">413.034271240234</t>
@@ -3818,28 +3818,28 @@
     <t xml:space="preserve">409.4990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">417.551544189453</t>
+    <t xml:space="preserve">417.551483154297</t>
   </si>
   <si>
     <t xml:space="preserve">419.122741699219</t>
   </si>
   <si>
-    <t xml:space="preserve">421.479614257812</t>
+    <t xml:space="preserve">421.479553222656</t>
   </si>
   <si>
     <t xml:space="preserve">415.980285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">419.711944580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">420.49755859375</t>
+    <t xml:space="preserve">419.7119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">420.497528076172</t>
   </si>
   <si>
     <t xml:space="preserve">405.570983886719</t>
   </si>
   <si>
-    <t xml:space="preserve">403.606903076172</t>
+    <t xml:space="preserve">403.606964111328</t>
   </si>
   <si>
     <t xml:space="preserve">397.518432617188</t>
@@ -3848,37 +3848,37 @@
     <t xml:space="preserve">390.447967529297</t>
   </si>
   <si>
-    <t xml:space="preserve">383.37744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">391.822814941406</t>
+    <t xml:space="preserve">383.377471923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">391.822784423828</t>
   </si>
   <si>
     <t xml:space="preserve">395.947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">394.572448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.338562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">410.284606933594</t>
+    <t xml:space="preserve">394.572387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.338531494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">410.284637451172</t>
   </si>
   <si>
     <t xml:space="preserve">409.302581787109</t>
   </si>
   <si>
-    <t xml:space="preserve">408.320617675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">407.142242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">406.356567382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">402.232086181641</t>
+    <t xml:space="preserve">408.320587158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">407.142211914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">406.356597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">402.232116699219</t>
   </si>
   <si>
     <t xml:space="preserve">405.767364501953</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">477.650634765625</t>
   </si>
   <si>
-    <t xml:space="preserve">474.508178710938</t>
+    <t xml:space="preserve">474.508209228516</t>
   </si>
   <si>
     <t xml:space="preserve">470.187316894531</t>
@@ -3908,46 +3908,46 @@
     <t xml:space="preserve">474.115386962891</t>
   </si>
   <si>
-    <t xml:space="preserve">486.252014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">488.614349365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">495.110870361328</t>
+    <t xml:space="preserve">486.251983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">488.614379882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">495.11083984375</t>
   </si>
   <si>
     <t xml:space="preserve">493.634368896484</t>
   </si>
   <si>
-    <t xml:space="preserve">492.157867431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">496.095153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.524566650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499.048156738281</t>
+    <t xml:space="preserve">492.157897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">496.09521484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.524597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499.048126220703</t>
   </si>
   <si>
     <t xml:space="preserve">503.4775390625</t>
   </si>
   <si>
-    <t xml:space="preserve">503.969635009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">501.016754150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">495.60302734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">500.032409667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">507.414825439453</t>
+    <t xml:space="preserve">503.969665527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">501.016723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">495.602996826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500.032440185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">507.414794921875</t>
   </si>
   <si>
     <t xml:space="preserve">511.84423828125</t>
@@ -3956,19 +3956,19 @@
     <t xml:space="preserve">514.797180175781</t>
   </si>
   <si>
-    <t xml:space="preserve">509.383422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">527.593322753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">535.959899902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">547.279602050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">546.295227050781</t>
+    <t xml:space="preserve">509.383453369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">527.59326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">535.960021972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">547.279663085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">546.295166015625</t>
   </si>
   <si>
     <t xml:space="preserve">546.787475585938</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">528.08544921875</t>
   </si>
   <si>
-    <t xml:space="preserve">526.116821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">512.336364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">510.859893798828</t>
+    <t xml:space="preserve">526.11669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">512.336242675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">510.859924316406</t>
   </si>
   <si>
     <t xml:space="preserve">489.992401123047</t>
@@ -4001,31 +4001,31 @@
     <t xml:space="preserve">517.750122070312</t>
   </si>
   <si>
-    <t xml:space="preserve">532.514831542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">554.662048339844</t>
+    <t xml:space="preserve">532.514770507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">554.661987304688</t>
   </si>
   <si>
     <t xml:space="preserve">568.4423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">567.9501953125</t>
+    <t xml:space="preserve">567.950256347656</t>
   </si>
   <si>
     <t xml:space="preserve">575.824768066406</t>
   </si>
   <si>
-    <t xml:space="preserve">561.552124023438</t>
+    <t xml:space="preserve">561.552185058594</t>
   </si>
   <si>
     <t xml:space="preserve">569.426635742188</t>
   </si>
   <si>
-    <t xml:space="preserve">545.803100585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">543.342346191406</t>
+    <t xml:space="preserve">545.803161621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">543.34228515625</t>
   </si>
   <si>
     <t xml:space="preserve">540.389404296875</t>
@@ -4034,10 +4034,10 @@
     <t xml:space="preserve">549.248229980469</t>
   </si>
   <si>
-    <t xml:space="preserve">555.646240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.022827148438</t>
+    <t xml:space="preserve">555.646301269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.022705078125</t>
   </si>
   <si>
     <t xml:space="preserve">523.655944824219</t>
@@ -4046,46 +4046,46 @@
     <t xml:space="preserve">514.304992675781</t>
   </si>
   <si>
-    <t xml:space="preserve">517.257934570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">534.9755859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">544.818786621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">553.185546875</t>
+    <t xml:space="preserve">517.257995605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534.975708007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">544.81884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">553.185485839844</t>
   </si>
   <si>
     <t xml:space="preserve">554.300048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">536.053405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532.108276367188</t>
+    <t xml:space="preserve">536.053527832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532.108337402344</t>
   </si>
   <si>
     <t xml:space="preserve">536.546630859375</t>
   </si>
   <si>
-    <t xml:space="preserve">542.464416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">537.532836914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">541.478149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">543.45068359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">533.094665527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">531.121887207031</t>
+    <t xml:space="preserve">542.46435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">537.532958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">541.478088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">543.450744628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">533.094604492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">531.121948242188</t>
   </si>
   <si>
     <t xml:space="preserve">538.026123046875</t>
@@ -4097,10 +4097,10 @@
     <t xml:space="preserve">532.601440429688</t>
   </si>
   <si>
-    <t xml:space="preserve">537.039733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">534.080932617188</t>
+    <t xml:space="preserve">537.039855957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">534.080871582031</t>
   </si>
   <si>
     <t xml:space="preserve">539.012329101562</t>
@@ -4109,13 +4109,13 @@
     <t xml:space="preserve">526.1904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">531.615112304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">517.806945800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">513.368591308594</t>
+    <t xml:space="preserve">531.615234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">517.807006835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">513.368530273438</t>
   </si>
   <si>
     <t xml:space="preserve">523.231628417969</t>
@@ -4124,22 +4124,22 @@
     <t xml:space="preserve">519.779541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">511.88916015625</t>
+    <t xml:space="preserve">511.889221191406</t>
   </si>
   <si>
     <t xml:space="preserve">509.91650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">511.395935058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">518.793212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">520.765808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">527.669982910156</t>
+    <t xml:space="preserve">511.39599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">518.793273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">520.765869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">527.669921875</t>
   </si>
   <si>
     <t xml:space="preserve">552.820556640625</t>
@@ -4148,40 +4148,40 @@
     <t xml:space="preserve">567.121887207031</t>
   </si>
   <si>
-    <t xml:space="preserve">557.258850097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">567.615112304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">565.642395019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">568.108215332031</t>
+    <t xml:space="preserve">557.258911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">567.614929199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">565.642456054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">568.108276367188</t>
   </si>
   <si>
     <t xml:space="preserve">573.532836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">581.423217773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">583.888916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">575.012390136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">561.697326660156</t>
+    <t xml:space="preserve">581.423156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">583.888854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">575.01220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">561.697265625</t>
   </si>
   <si>
     <t xml:space="preserve">569.094543457031</t>
   </si>
   <si>
-    <t xml:space="preserve">568.601257324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">577.47802734375</t>
+    <t xml:space="preserve">568.601379394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">577.478088378906</t>
   </si>
   <si>
     <t xml:space="preserve">572.053405761719</t>
@@ -4196,97 +4196,97 @@
     <t xml:space="preserve">587.834167480469</t>
   </si>
   <si>
-    <t xml:space="preserve">585.861633300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">593.752014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">609.03955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">646.025817871094</t>
+    <t xml:space="preserve">585.861572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">593.752075195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">609.039611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">646.025756835938</t>
   </si>
   <si>
     <t xml:space="preserve">642.080627441406</t>
   </si>
   <si>
-    <t xml:space="preserve">668.217590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">675.614868164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">677.09423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">671.176391601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">679.559997558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">695.173034667969</t>
+    <t xml:space="preserve">668.217468261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">675.614807128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">677.094177246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">671.176452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">679.559936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">695.172912597656</t>
   </si>
   <si>
     <t xml:space="preserve">698.631469726562</t>
   </si>
   <si>
-    <t xml:space="preserve">722.841491699219</t>
+    <t xml:space="preserve">722.841613769531</t>
   </si>
   <si>
     <t xml:space="preserve">726.300109863281</t>
   </si>
   <si>
-    <t xml:space="preserve">700.11376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">681.338623046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">707.030944824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">697.643310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">705.054504394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">699.125549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">688.255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">686.279479980469</t>
+    <t xml:space="preserve">700.113708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">681.338562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">707.030883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">697.643371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">705.054565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">699.125610351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">688.255737304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">686.279541015625</t>
   </si>
   <si>
     <t xml:space="preserve">709.995300292969</t>
   </si>
   <si>
-    <t xml:space="preserve">722.347351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">710.489501953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">711.9716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">690.232238769531</t>
+    <t xml:space="preserve">722.347412109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">710.489440917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.971801757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690.23211